--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -1,13 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{280FF984-D9F3-4C0D-B786-CFB6B8741FD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="21490" yWindow="1460" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
+    <sheet name="050 - ICs - Analog" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -18,9 +25,95 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="27">
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Package</t>
+  </si>
+  <si>
+    <t>MPN</t>
+  </si>
+  <si>
+    <t>Manufacturer</t>
+  </si>
+  <si>
+    <t>Distributor PN</t>
+  </si>
+  <si>
+    <t>Distributor</t>
+  </si>
+  <si>
+    <t>Datasheet</t>
+  </si>
+  <si>
+    <t>Distributor Link</t>
+  </si>
+  <si>
+    <t>Library Ref</t>
+  </si>
+  <si>
+    <t>Library Path</t>
+  </si>
+  <si>
+    <t>Footprint Ref</t>
+  </si>
+  <si>
+    <t>Footprint Path</t>
+  </si>
+  <si>
+    <t>050-0001</t>
+  </si>
+  <si>
+    <t>Monitores y reguladores de corriente y energía Hi-Side Msmt Bi-Dir Current/Pwr Mon A 59 A 595-INA226AIDGST</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>MSOP-10</t>
+  </si>
+  <si>
+    <t>INA226AIDGSR</t>
+  </si>
+  <si>
+    <t>595-INA226AIDGSR</t>
+  </si>
+  <si>
+    <t>Texas Instruments</t>
+  </si>
+  <si>
+    <t>Mouser</t>
+  </si>
+  <si>
+    <t>https://www.ti.com/lit/ds/symlink/ina226.pdf?ts=1772078114731&amp;ref_url=https%253A%252F%252Fwww.ti.com%252Fproduct%252FINA226</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Texas-Instruments/INA226AIDGSR?qs=tQG3bEuiOZD4quG3egR36g%3D%3D&amp;srsltid=AfmBOopOjh8KVXQVeHwZlO8DxeOetC6-xgaoNkKslHEV4iGJ_SkIIo7K</t>
+  </si>
+  <si>
+    <t>INA226</t>
+  </si>
+  <si>
+    <t>eUSR_SchLibrary/eUSR_SchLibrary - Ics.SchLib</t>
+  </si>
+  <si>
+    <t>eUSR_PcbLibrary/eUSR_PcbLibrary.PcbLib</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -28,16 +121,38 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,14 +160,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -330,10 +466,182 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:N1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.1796875" customWidth="1"/>
+    <col min="2" max="2" width="11.08984375" customWidth="1"/>
+    <col min="4" max="4" width="8.81640625" customWidth="1"/>
+    <col min="6" max="6" width="12.6328125" customWidth="1"/>
+    <col min="7" max="7" width="15.453125" customWidth="1"/>
+    <col min="8" max="8" width="12.453125" customWidth="1"/>
+    <col min="9" max="9" width="11.1796875" customWidth="1"/>
+    <col min="10" max="10" width="14.7265625" customWidth="1"/>
+    <col min="11" max="11" width="12" customWidth="1"/>
+    <col min="12" max="12" width="13.1796875" customWidth="1"/>
+    <col min="13" max="13" width="12.54296875" customWidth="1"/>
+    <col min="14" max="14" width="17.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C98E1A12-072F-4773-8CB5-47FFE077E85B}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="93.81640625" customWidth="1"/>
+    <col min="5" max="5" width="16.1796875" customWidth="1"/>
+    <col min="6" max="6" width="17.81640625" customWidth="1"/>
+    <col min="7" max="7" width="16.7265625" customWidth="1"/>
+    <col min="9" max="9" width="24.7265625" customWidth="1"/>
+    <col min="10" max="10" width="23.6328125" customWidth="1"/>
+    <col min="12" max="12" width="22.1796875" customWidth="1"/>
+    <col min="13" max="13" width="14.90625" customWidth="1"/>
+    <col min="14" max="14" width="21.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M2" t="s">
+        <v>17</v>
+      </c>
+      <c r="N2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="I2" r:id="rId1" xr:uid="{1CFCC581-B5E5-4159-8EE1-35A941FCD4DF}"/>
+    <hyperlink ref="J2" r:id="rId2" xr:uid="{78125F11-BE4E-4312-8E61-0550889BB81F}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{280FF984-D9F3-4C0D-B786-CFB6B8741FD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47C4F35F-69C8-4DD0-95B8-D51AC0312B46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="21490" yWindow="1460" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -103,10 +103,10 @@
     <t>INA226</t>
   </si>
   <si>
-    <t>eUSR_SchLibrary/eUSR_SchLibrary - Ics.SchLib</t>
-  </si>
-  <si>
     <t>eUSR_PcbLibrary/eUSR_PcbLibrary.PcbLib</t>
+  </si>
+  <si>
+    <t>eUSR_SchLibrary/eUSR_SchLibrary - ICs.SchLib</t>
   </si>
 </sst>
 </file>
@@ -628,13 +628,13 @@
         <v>24</v>
       </c>
       <c r="L2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M2" t="s">
         <v>17</v>
       </c>
       <c r="N2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,13 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47C4F35F-69C8-4DD0-95B8-D51AC0312B46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D864AD46-11CA-4774-B56F-BAFB3B9F8C6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21490" yWindow="1460" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
-    <sheet name="050 - ICs - Analog" sheetId="2" r:id="rId2"/>
+    <sheet name="010 - Resistors - SMD" sheetId="4" r:id="rId2"/>
+    <sheet name="015 - Resistors - Shunt" sheetId="7" r:id="rId3"/>
+    <sheet name="020 - Inductor" sheetId="5" r:id="rId4"/>
+    <sheet name="050 - ICs - Analog" sheetId="2" r:id="rId5"/>
+    <sheet name="060 - ICs - Digital" sheetId="3" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="39">
   <si>
     <t>ID</t>
   </si>
@@ -107,6 +111,42 @@
   </si>
   <si>
     <t>eUSR_SchLibrary/eUSR_SchLibrary - ICs.SchLib</t>
+  </si>
+  <si>
+    <t>Resistores de detección de corriente - SMD 2512 3mohm 5% CS Mtl Strp AEC-Q200</t>
+  </si>
+  <si>
+    <t>015-0001</t>
+  </si>
+  <si>
+    <t>3mOhm 2W</t>
+  </si>
+  <si>
+    <t>PMR100HZPJV3L0</t>
+  </si>
+  <si>
+    <t>ROHM Semiconductor</t>
+  </si>
+  <si>
+    <t>755-PMR100HZPJV3L0</t>
+  </si>
+  <si>
+    <t>https://fscdn.rohm.com/en/products/databook/datasheet/passive/resistor/chip_resistor/pmr100-e.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/ROHM-Semiconductor/PMR100HZPJV3L0?qs=oBjDkOCjPF3EzAhPQYFY9g%3D%3D</t>
+  </si>
+  <si>
+    <t>RES</t>
+  </si>
+  <si>
+    <t>eUSR_SchLibrary/eUSR_SchLibrary - Resistor.SchLib</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	6432</t>
+  </si>
+  <si>
+    <t>SMD-6432</t>
   </si>
 </sst>
 </file>
@@ -534,6 +574,216 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60E8291E-4293-4634-B9E9-80CB520CA181}">
+  <dimension ref="A1:N1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81F9848D-6D60-47C0-9F84-A561FE4F106E}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="K2" t="s">
+        <v>35</v>
+      </c>
+      <c r="L2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="I2" r:id="rId1" xr:uid="{9FEE5192-80A9-4D8D-B0ED-453C4A95B2F9}"/>
+    <hyperlink ref="J2" r:id="rId2" xr:uid="{40967CA2-E6AE-4524-9EF5-66E92DD6A7B6}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01C6B0FD-D8A3-44EC-9532-03DDA232F922}">
+  <dimension ref="A1:N1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C98E1A12-072F-4773-8CB5-47FFE077E85B}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -644,4 +894,58 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59BC8B2E-A067-463D-937A-30E88D8BECD0}">
+  <dimension ref="A1:N1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D864AD46-11CA-4774-B56F-BAFB3B9F8C6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEEE4C12-6737-4209-9C98-38B04E63A21D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="49">
   <si>
     <t>ID</t>
   </si>
@@ -143,10 +143,40 @@
     <t>eUSR_SchLibrary/eUSR_SchLibrary - Resistor.SchLib</t>
   </si>
   <si>
-    <t xml:space="preserve">	6432</t>
-  </si>
-  <si>
-    <t>SMD-6432</t>
+    <t>010-0001</t>
+  </si>
+  <si>
+    <t>Resistores de película fina - SMD 2.2KOhms 0603 25ppm Tol 0.1% High Power Alum Nitride</t>
+  </si>
+  <si>
+    <t>2.2kOhm 500mW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	0603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2512</t>
+  </si>
+  <si>
+    <t>SMD-2512</t>
+  </si>
+  <si>
+    <t>https://www.seielect.com/Catalog/SEI-rnan.PDF</t>
+  </si>
+  <si>
+    <t>RNAN0603BKE2K20</t>
+  </si>
+  <si>
+    <t>708-RNAN0603BKE2K20</t>
+  </si>
+  <si>
+    <t>SEI Stackpole</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/SEI-Stackpole/RNAN0603BKE2K20?qs=sGAEpiMZZMtlubZbdhIBILBsAZ06Y%2Fzi8Vxe0iUb3Nw%3D</t>
+  </si>
+  <si>
+    <t>SMD-0603</t>
   </si>
 </sst>
 </file>
@@ -575,7 +605,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60E8291E-4293-4634-B9E9-80CB520CA181}">
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.35">
@@ -622,7 +652,55 @@
         <v>13</v>
       </c>
     </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K2" t="s">
+        <v>35</v>
+      </c>
+      <c r="L2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M2" t="s">
+        <v>48</v>
+      </c>
+      <c r="N2" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="I2" r:id="rId1" xr:uid="{CB6DE219-359C-4842-AF81-7B23417A5184}"/>
+    <hyperlink ref="J2" r:id="rId2" xr:uid="{B350CF59-B9E7-457A-A2EF-29B77103F361}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -687,7 +765,7 @@
         <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E2" t="s">
         <v>30</v>
@@ -714,7 +792,7 @@
         <v>36</v>
       </c>
       <c r="M2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="N2" t="s">
         <v>25</v>

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEEE4C12-6737-4209-9C98-38B04E63A21D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F40B6E08-C28A-4B05-8098-86C933DAFABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="57">
   <si>
     <t>ID</t>
   </si>
@@ -177,6 +177,30 @@
   </si>
   <si>
     <t>SMD-0603</t>
+  </si>
+  <si>
+    <t>Controlador de puerta High side driver with current sense analog feedback for automotive applications</t>
+  </si>
+  <si>
+    <t>Octapak-7</t>
+  </si>
+  <si>
+    <t>VN7007AHTR</t>
+  </si>
+  <si>
+    <t>511-VN7007AHTR</t>
+  </si>
+  <si>
+    <t>STMicroelectronics</t>
+  </si>
+  <si>
+    <t>050-0002</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/STMicroelectronics/VN7007AHTR?qs=mKNKSX85ZJecQmIqUrqpTA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://www.st.com/resource/en/datasheet/vn7007ah.pdf</t>
   </si>
 </sst>
 </file>
@@ -863,7 +887,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C98E1A12-072F-4773-8CB5-47FFE077E85B}">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="93.81640625" customWidth="1"/>
@@ -872,7 +896,7 @@
     <col min="7" max="7" width="16.7265625" customWidth="1"/>
     <col min="9" max="9" width="24.7265625" customWidth="1"/>
     <col min="10" max="10" width="23.6328125" customWidth="1"/>
-    <col min="12" max="12" width="22.1796875" customWidth="1"/>
+    <col min="12" max="12" width="32.453125" customWidth="1"/>
     <col min="13" max="13" width="14.90625" customWidth="1"/>
     <col min="14" max="14" width="21.81640625" customWidth="1"/>
   </cols>
@@ -965,10 +989,54 @@
         <v>25</v>
       </c>
     </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K3" t="s">
+        <v>51</v>
+      </c>
+      <c r="L3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3" t="s">
+        <v>50</v>
+      </c>
+      <c r="N3" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="I2" r:id="rId1" xr:uid="{1CFCC581-B5E5-4159-8EE1-35A941FCD4DF}"/>
-    <hyperlink ref="J2" r:id="rId2" xr:uid="{78125F11-BE4E-4312-8E61-0550889BB81F}"/>
+    <hyperlink ref="J2" r:id="rId1" xr:uid="{78125F11-BE4E-4312-8E61-0550889BB81F}"/>
+    <hyperlink ref="I2" r:id="rId2" xr:uid="{1CFCC581-B5E5-4159-8EE1-35A941FCD4DF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F40B6E08-C28A-4B05-8098-86C933DAFABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F439E50-77DC-4B2D-A14A-96EFE928F3DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="020 - Inductor" sheetId="5" r:id="rId4"/>
     <sheet name="050 - ICs - Analog" sheetId="2" r:id="rId5"/>
     <sheet name="060 - ICs - Digital" sheetId="3" r:id="rId6"/>
+    <sheet name="070 - Power Supply - DCDC" sheetId="8" r:id="rId7"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="68">
   <si>
     <t>ID</t>
   </si>
@@ -201,6 +202,39 @@
   </si>
   <si>
     <t>https://www.st.com/resource/en/datasheet/vn7007ah.pdf</t>
+  </si>
+  <si>
+    <t>070-0001</t>
+  </si>
+  <si>
+    <t>Convertidores DC/DC para montaje pasante 60W DC/DC Converter isolated, regulated in a PCB Mount Metal Case</t>
+  </si>
+  <si>
+    <t>24V/12V</t>
+  </si>
+  <si>
+    <t>TEN 60-2412N</t>
+  </si>
+  <si>
+    <t>TRACO Power</t>
+  </si>
+  <si>
+    <t>495-TEN60-2412N</t>
+  </si>
+  <si>
+    <t>50.8x25.4x10.2mm</t>
+  </si>
+  <si>
+    <t>https://www.tracopower.com/ten60n-datasheet</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/TRACO-Power/TEN-60-2412N?qs=ckJk83FOD0VXj1pRyQBddA%3D%3D</t>
+  </si>
+  <si>
+    <t>TEN 60</t>
+  </si>
+  <si>
+    <t>eUSR_SchLibrary/eUSR_SchLibrary - PowerSupplies.SchLib</t>
   </si>
 </sst>
 </file>
@@ -1094,4 +1128,109 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4BBBCF5-BAC9-459C-ABE9-2526B85FD81E}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="4" max="4" width="17.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G2" t="s">
+        <v>62</v>
+      </c>
+      <c r="H2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" t="s">
+        <v>64</v>
+      </c>
+      <c r="J2" t="s">
+        <v>65</v>
+      </c>
+      <c r="K2" t="s">
+        <v>66</v>
+      </c>
+      <c r="L2" t="s">
+        <v>67</v>
+      </c>
+      <c r="M2" t="s">
+        <v>66</v>
+      </c>
+      <c r="N2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F2" r:id="rId1" display="https://www.mouser.es/manufacturer/traco-power/" xr:uid="{ECDB474B-3F6C-47CA-A9E3-99AC9E81CCAB}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+</worksheet>
 </file>
--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,18 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F439E50-77DC-4B2D-A14A-96EFE928F3DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9167541-BD22-4C2B-9D20-30205B62276F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="21490" yWindow="1460" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
     <sheet name="010 - Resistors - SMD" sheetId="4" r:id="rId2"/>
     <sheet name="015 - Resistors - Shunt" sheetId="7" r:id="rId3"/>
     <sheet name="020 - Inductor" sheetId="5" r:id="rId4"/>
-    <sheet name="050 - ICs - Analog" sheetId="2" r:id="rId5"/>
-    <sheet name="060 - ICs - Digital" sheetId="3" r:id="rId6"/>
-    <sheet name="070 - Power Supply - DCDC" sheetId="8" r:id="rId7"/>
+    <sheet name="030 - Diodes" sheetId="9" r:id="rId5"/>
+    <sheet name="040 - Fuses" sheetId="10" r:id="rId6"/>
+    <sheet name="050 - ICs - Analog" sheetId="2" r:id="rId7"/>
+    <sheet name="060 - ICs - Digital" sheetId="3" r:id="rId8"/>
+    <sheet name="070 - Power Supply - DCDC" sheetId="8" r:id="rId9"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -31,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="78">
   <si>
     <t>ID</t>
   </si>
@@ -235,6 +237,36 @@
   </si>
   <si>
     <t>eUSR_SchLibrary/eUSR_SchLibrary - PowerSupplies.SchLib</t>
+  </si>
+  <si>
+    <t>040-0001</t>
+  </si>
+  <si>
+    <t>Portafusibles T/H 2 IN 1 AUTO BLDE HOLDER, BLUE 15A</t>
+  </si>
+  <si>
+    <t>THT,Vertical</t>
+  </si>
+  <si>
+    <t>3557-15</t>
+  </si>
+  <si>
+    <t>534-3557-15</t>
+  </si>
+  <si>
+    <t>Keystone Electronics</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/datasheet/3/201/1/3557_15.PDF</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Keystone-Electronics/3557-15?qs=iR2ablhfrmFh8obBV91Xhg%3D%3D</t>
+  </si>
+  <si>
+    <t>eUSR_SchLibrary/eUSR_SchLibrary - Fuses.SchLib</t>
+  </si>
+  <si>
+    <t>FUSE 2</t>
   </si>
 </sst>
 </file>
@@ -920,6 +952,165 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{652841DA-3619-42EE-A536-61B58BE1B457}">
+  <dimension ref="A1:N1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B6F0D32-9CE2-4DF7-927E-42E7BA331F12}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="13" max="13" width="13.36328125" customWidth="1"/>
+    <col min="14" max="14" width="16.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="J2" t="s">
+        <v>75</v>
+      </c>
+      <c r="K2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L2" t="s">
+        <v>76</v>
+      </c>
+      <c r="M2" t="s">
+        <v>71</v>
+      </c>
+      <c r="N2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="I2" r:id="rId1" xr:uid="{3DE7E9B7-7F71-48BD-A43F-56652EF48515}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C98E1A12-072F-4773-8CB5-47FFE077E85B}">
   <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1076,7 +1267,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59BC8B2E-A067-463D-937A-30E88D8BECD0}">
   <dimension ref="A1:N1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1130,7 +1321,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4BBBCF5-BAC9-459C-ABE9-2526B85FD81E}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9167541-BD22-4C2B-9D20-30205B62276F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39683E00-AE8E-4597-8373-2C005AA019D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21490" yWindow="1460" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10710" yWindow="0" windowWidth="10980" windowHeight="13770" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="86">
   <si>
     <t>ID</t>
   </si>
@@ -152,9 +152,6 @@
     <t>Resistores de película fina - SMD 2.2KOhms 0603 25ppm Tol 0.1% High Power Alum Nitride</t>
   </si>
   <si>
-    <t>2.2kOhm 500mW</t>
-  </si>
-  <si>
     <t xml:space="preserve">	0603</t>
   </si>
   <si>
@@ -179,9 +176,6 @@
     <t>https://www.mouser.es/ProductDetail/SEI-Stackpole/RNAN0603BKE2K20?qs=sGAEpiMZZMtlubZbdhIBILBsAZ06Y%2Fzi8Vxe0iUb3Nw%3D</t>
   </si>
   <si>
-    <t>SMD-0603</t>
-  </si>
-  <si>
     <t>Controlador de puerta High side driver with current sense analog feedback for automotive applications</t>
   </si>
   <si>
@@ -267,13 +261,64 @@
   </si>
   <si>
     <t>FUSE 2</t>
+  </si>
+  <si>
+    <t>010-0002</t>
+  </si>
+  <si>
+    <t>RES SMD 0603</t>
+  </si>
+  <si>
+    <t>Thick Film Resistors 1/4Watt 10ohms 1% Commercial Use</t>
+  </si>
+  <si>
+    <r>
+      <t>2.2k</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ω</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 500mW</t>
+    </r>
+  </si>
+  <si>
+    <t>10Ω 500mW</t>
+  </si>
+  <si>
+    <t>CRCW120610R0FKEBC</t>
+  </si>
+  <si>
+    <t>Vishay</t>
+  </si>
+  <si>
+    <t>71-CRCW120610R0FKEBC</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Vishay/CRCW120610R0FKEBC?qs=sGAEpiMZZMvdGkrng054t0DrEhLhGh8g1klCq9VIVJz32s822McPWQ%3D%3D</t>
+  </si>
+  <si>
+    <t>https://www.vishay.com/docs/28773/crcwce3.pdf</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -296,6 +341,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -695,8 +746,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60E8291E-4293-4634-B9E9-80CB520CA181}">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="3" width="19.90625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
@@ -750,28 +804,28 @@
         <v>38</v>
       </c>
       <c r="C2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D2" t="s">
         <v>39</v>
       </c>
-      <c r="D2" t="s">
-        <v>40</v>
-      </c>
       <c r="E2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G2" t="s">
         <v>44</v>
-      </c>
-      <c r="F2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G2" t="s">
-        <v>45</v>
       </c>
       <c r="H2" t="s">
         <v>21</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K2" t="s">
         <v>35</v>
@@ -780,9 +834,53 @@
         <v>36</v>
       </c>
       <c r="M2" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="N2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F3" t="s">
+        <v>82</v>
+      </c>
+      <c r="G3" t="s">
+        <v>83</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" t="s">
+        <v>85</v>
+      </c>
+      <c r="J3" t="s">
+        <v>84</v>
+      </c>
+      <c r="K3" t="s">
+        <v>35</v>
+      </c>
+      <c r="L3" t="s">
+        <v>36</v>
+      </c>
+      <c r="M3" t="s">
+        <v>77</v>
+      </c>
+      <c r="N3" t="s">
         <v>25</v>
       </c>
     </row>
@@ -792,6 +890,7 @@
     <hyperlink ref="J2" r:id="rId2" xr:uid="{B350CF59-B9E7-457A-A2EF-29B77103F361}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -855,7 +954,7 @@
         <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E2" t="s">
         <v>30</v>
@@ -882,7 +981,7 @@
         <v>36</v>
       </c>
       <c r="M2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N2" t="s">
         <v>25</v>
@@ -1060,43 +1159,43 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
         <v>16</v>
       </c>
       <c r="D2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G2" t="s">
         <v>70</v>
-      </c>
-      <c r="E2" t="s">
-        <v>71</v>
-      </c>
-      <c r="F2" t="s">
-        <v>73</v>
-      </c>
-      <c r="G2" t="s">
-        <v>72</v>
       </c>
       <c r="H2" t="s">
         <v>21</v>
       </c>
       <c r="I2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="J2" t="s">
+        <v>73</v>
+      </c>
+      <c r="K2" t="s">
+        <v>75</v>
+      </c>
+      <c r="L2" t="s">
         <v>74</v>
       </c>
-      <c r="J2" t="s">
-        <v>75</v>
-      </c>
-      <c r="K2" t="s">
-        <v>77</v>
-      </c>
-      <c r="L2" t="s">
-        <v>76</v>
-      </c>
       <c r="M2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="N2" t="s">
         <v>25</v>
@@ -1216,43 +1315,43 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C3" t="s">
         <v>16</v>
       </c>
       <c r="D3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F3" t="s">
         <v>50</v>
       </c>
-      <c r="E3" t="s">
+      <c r="G3" t="s">
         <v>51</v>
-      </c>
-      <c r="F3" t="s">
-        <v>52</v>
-      </c>
-      <c r="G3" t="s">
-        <v>53</v>
       </c>
       <c r="H3" t="s">
         <v>21</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="K3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
       </c>
       <c r="M3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N3" t="s">
         <v>25</v>
@@ -1375,43 +1474,43 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" t="s">
         <v>57</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E2" t="s">
         <v>58</v>
       </c>
-      <c r="C2" t="s">
+      <c r="F2" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>60</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G2" t="s">
-        <v>62</v>
       </c>
       <c r="H2" t="s">
         <v>21</v>
       </c>
       <c r="I2" t="s">
+        <v>62</v>
+      </c>
+      <c r="J2" t="s">
+        <v>63</v>
+      </c>
+      <c r="K2" t="s">
         <v>64</v>
       </c>
-      <c r="J2" t="s">
+      <c r="L2" t="s">
         <v>65</v>
       </c>
-      <c r="K2" t="s">
-        <v>66</v>
-      </c>
-      <c r="L2" t="s">
-        <v>67</v>
-      </c>
       <c r="M2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="N2" t="s">
         <v>25</v>

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39683E00-AE8E-4597-8373-2C005AA019D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CF94052-EC07-4BCA-B46D-5E10222CE00E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10710" yWindow="0" windowWidth="10980" windowHeight="13770" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10710" yWindow="0" windowWidth="10980" windowHeight="13770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="98">
   <si>
     <t>ID</t>
   </si>
@@ -312,6 +312,42 @@
   </si>
   <si>
     <t>https://www.vishay.com/docs/28773/crcwce3.pdf</t>
+  </si>
+  <si>
+    <t>001-0001</t>
+  </si>
+  <si>
+    <t>Condensadores de cerámica multicapa (MLCC- SMD/SMT) 16V 0.18uF X7R 0603 10%</t>
+  </si>
+  <si>
+    <t>25V 100nF X7R</t>
+  </si>
+  <si>
+    <t>0603</t>
+  </si>
+  <si>
+    <t>YAGEO</t>
+  </si>
+  <si>
+    <t>CC0603KRX7R8BB104</t>
+  </si>
+  <si>
+    <t>603-CC603KRX7R8BB104</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/datasheet/3/508/1/UPY_GPHC_X7R_6_3V_TO_250V.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/YAGEO/CC0603KRX7R8BB104?qs=AgBp2OyFlx%252B4QOgEm%2Fb3YQ%3D%3D</t>
+  </si>
+  <si>
+    <t>NON-POLARIZED CAP</t>
+  </si>
+  <si>
+    <t>eUSR_SchLibrary/eUSR_SchLibrary - Capacitors.SchLib</t>
+  </si>
+  <si>
+    <t>CAP SMD 0603</t>
   </si>
 </sst>
 </file>
@@ -391,12 +427,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -678,7 +715,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.1796875" customWidth="1"/>
@@ -737,6 +774,50 @@
       </c>
       <c r="N1" s="1" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" t="s">
+        <v>93</v>
+      </c>
+      <c r="J2" t="s">
+        <v>94</v>
+      </c>
+      <c r="K2" t="s">
+        <v>95</v>
+      </c>
+      <c r="L2" t="s">
+        <v>96</v>
+      </c>
+      <c r="M2" t="s">
+        <v>97</v>
+      </c>
+      <c r="N2" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61DCB4DD-F761-440C-9261-D6CE44240758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50A552C4-0472-427E-A8C7-C77A01BCF3B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06409C09-0DBE-4737-8E92-BFF68DBA9FFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED3E5BF4-6ADE-4390-B2F5-7FB720DD6368}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="21490" yWindow="1460" windowWidth="19420" windowHeight="10300" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3400" uniqueCount="1680">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3428" uniqueCount="1691">
   <si>
     <t>ID</t>
   </si>
@@ -5072,7 +5072,40 @@
     <t>TEN 2</t>
   </si>
   <si>
-    <t>TEN 2-2433</t>
+    <t>070-0002</t>
+  </si>
+  <si>
+    <t>Convertidores DC/DC para montaje pasante 6.5-36Vin 5V 2A SIP switching regulator</t>
+  </si>
+  <si>
+    <t>24V-5V</t>
+  </si>
+  <si>
+    <t>TSR 2-2450</t>
+  </si>
+  <si>
+    <t>495-TSR2-2450</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/TRACO-Power/TSR-2-2450?qs=NtE2QagKf6RzknAolzm%2FTQ%3D%3D</t>
+  </si>
+  <si>
+    <t>070-0003</t>
+  </si>
+  <si>
+    <t>Convertidores DC/DC para montaje pasante 15-36Vin 12V 2A SIP switching regulator</t>
+  </si>
+  <si>
+    <t>24V-12V</t>
+  </si>
+  <si>
+    <t>TSR 2-24120</t>
+  </si>
+  <si>
+    <t>495-TSR2-24120</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/TRACO-Power/TSR-2-24120?qs=NtE2QagKf6T34HiGRDOLrw%3D%3D</t>
   </si>
 </sst>
 </file>
@@ -16411,7 +16444,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4BBBCF5-BAC9-459C-ABE9-2526B85FD81E}">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="4" max="4" width="17.54296875" customWidth="1"/>
@@ -16477,7 +16510,7 @@
       <c r="E2" t="s">
         <v>1676</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" t="s">
         <v>46</v>
       </c>
       <c r="G2" t="s">
@@ -16499,19 +16532,106 @@
         <v>47</v>
       </c>
       <c r="M2" t="s">
+        <v>1678</v>
+      </c>
+      <c r="N2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
         <v>1679</v>
       </c>
-      <c r="N2" t="s">
+      <c r="B3" t="s">
+        <v>1680</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1681</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1673</v>
+      </c>
+      <c r="E3" t="s">
+        <v>1682</v>
+      </c>
+      <c r="F3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G3" t="s">
+        <v>1683</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" t="s">
+        <v>1674</v>
+      </c>
+      <c r="J3" t="s">
+        <v>1684</v>
+      </c>
+      <c r="K3" t="s">
+        <v>1678</v>
+      </c>
+      <c r="L3" t="s">
+        <v>47</v>
+      </c>
+      <c r="M3" t="s">
+        <v>1678</v>
+      </c>
+      <c r="N3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>1685</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1686</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1687</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1673</v>
+      </c>
+      <c r="E4" t="s">
+        <v>1688</v>
+      </c>
+      <c r="F4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G4" t="s">
+        <v>1689</v>
+      </c>
+      <c r="H4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" t="s">
+        <v>1674</v>
+      </c>
+      <c r="J4" t="s">
+        <v>1690</v>
+      </c>
+      <c r="K4" t="s">
+        <v>1678</v>
+      </c>
+      <c r="L4" t="s">
+        <v>47</v>
+      </c>
+      <c r="M4" t="s">
+        <v>1678</v>
+      </c>
+      <c r="N4" t="s">
         <v>25</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" display="https://www.mouser.es/manufacturer/traco-power/" xr:uid="{ECDB474B-3F6C-47CA-A9E3-99AC9E81CCAB}"/>
-    <hyperlink ref="I2" r:id="rId2" xr:uid="{08280A44-0F58-4FDE-B5FD-3A95A0F423CB}"/>
-    <hyperlink ref="J2" r:id="rId3" xr:uid="{85F326FF-BAE0-4072-815D-1EE4E7995C53}"/>
+    <hyperlink ref="I2" r:id="rId1" xr:uid="{08280A44-0F58-4FDE-B5FD-3A95A0F423CB}"/>
+    <hyperlink ref="J2" r:id="rId2" xr:uid="{85F326FF-BAE0-4072-815D-1EE4E7995C53}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,20 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{134ACE75-A3F6-4402-9049-AB2B5C56D66C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A714708A-4030-41BF-8D74-53C922F5E575}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21490" yWindow="1460" windowWidth="19420" windowHeight="10300" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
     <sheet name="010 - Resistors - SMD" sheetId="4" r:id="rId2"/>
     <sheet name="015 - Resistors - Shunt" sheetId="7" r:id="rId3"/>
     <sheet name="020 - Inductor" sheetId="5" r:id="rId4"/>
-    <sheet name="030 - Diodes" sheetId="9" r:id="rId5"/>
-    <sheet name="040 - Fuses" sheetId="10" r:id="rId6"/>
-    <sheet name="050 - ICs - Analog" sheetId="2" r:id="rId7"/>
-    <sheet name="060 - ICs - Digital" sheetId="3" r:id="rId8"/>
-    <sheet name="070 - Power Supply - DCDC" sheetId="8" r:id="rId9"/>
+    <sheet name="030 - Diode - Rectifier" sheetId="9" r:id="rId5"/>
+    <sheet name="031 - Diode - Schottky" sheetId="11" r:id="rId6"/>
+    <sheet name="033 - Diode - LED" sheetId="12" r:id="rId7"/>
+    <sheet name="040 - Fuses" sheetId="10" r:id="rId8"/>
+    <sheet name="050 - ICs - Analog" sheetId="2" r:id="rId9"/>
+    <sheet name="060 - ICs - Digital" sheetId="3" r:id="rId10"/>
+    <sheet name="070 - Power Supply - DCDC" sheetId="8" r:id="rId11"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -33,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3428" uniqueCount="1691">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4281" uniqueCount="2168">
   <si>
     <t>ID</t>
   </si>
@@ -5106,6 +5108,1437 @@
   </si>
   <si>
     <t>FUSE 2P</t>
+  </si>
+  <si>
+    <t>Shenzhen JDT Fuse</t>
+  </si>
+  <si>
+    <t>5A</t>
+  </si>
+  <si>
+    <t>50A SMD Fuse 750mA 63V 63V 1206 Fuses ROHS</t>
+  </si>
+  <si>
+    <t>750mA</t>
+  </si>
+  <si>
+    <t>0466.750NRHF</t>
+  </si>
+  <si>
+    <t>Littelfuse</t>
+  </si>
+  <si>
+    <t>C187594</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2304140030_Littelfuse-0466-750NRHF_C187594.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/Fuses_Littelfuse-0466-750NRHF_C187594.html</t>
+  </si>
+  <si>
+    <t>FUSE</t>
+  </si>
+  <si>
+    <t>FUSE SMD 1206</t>
+  </si>
+  <si>
+    <t>3A 125V (with holder) SMD,9.7x5mm Disposable fuses ROHS</t>
+  </si>
+  <si>
+    <t>3A</t>
+  </si>
+  <si>
+    <t>SMD,9.7x5mm</t>
+  </si>
+  <si>
+    <t>0154003.DRT</t>
+  </si>
+  <si>
+    <t>C206913</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2409302135_Littelfuse-0154003-DRT_C206913.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/Disposable-fuses_Littelfuse-0154003-DRT_C206913.html</t>
+  </si>
+  <si>
+    <t>LITTLE154</t>
+  </si>
+  <si>
+    <t>50A SMD Fuse 1A 63V 63V 1206 Disposable fuses ROHS</t>
+  </si>
+  <si>
+    <t>1A</t>
+  </si>
+  <si>
+    <t>C136343</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2305151205_Shenzhen-JDT-Fuse-JFC1206-1100FS_C136343.pdf</t>
+  </si>
+  <si>
+    <t>https://jlcpcb.com/partdetail/Shenzhen_JdtFuse-JFC12061100FS/C136343</t>
+  </si>
+  <si>
+    <t>16V 250mA 100A 500mA 1206 Resettable Fuses ROHS</t>
+  </si>
+  <si>
+    <t>250mA</t>
+  </si>
+  <si>
+    <t>C2830238</t>
+  </si>
+  <si>
+    <t>Jinrui Electronic Materials Co.</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2105311902_Jinrui-Electronic-Materials-Co--JK-nSMD025-16V_C2830238.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/Resettable-Fuses_Jinrui-Electronic-Materials-Co-JK-nSMD025-16V_C2830238.html</t>
+  </si>
+  <si>
+    <t>50A SMD Fuse 5A 125V 125V SMD,6.1x2.7mm Disposable fuses ROHS</t>
+  </si>
+  <si>
+    <t>SMD,6.1x2.7mm</t>
+  </si>
+  <si>
+    <t>0454005.MR</t>
+  </si>
+  <si>
+    <t>C179007</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2410122030_Littelfuse-0454005-MR_C179007.pdf</t>
+  </si>
+  <si>
+    <t>https://lcsc.com/product-detail/Disposable-fuses_Littelfuse-0454005-MR_C179007.html</t>
+  </si>
+  <si>
+    <t>FUSE SMD 6.1x2.7mm</t>
+  </si>
+  <si>
+    <t>50A SMD Fuse 3A 63V 1206 Disposable fuses ROHS</t>
+  </si>
+  <si>
+    <t>12H1300C</t>
+  </si>
+  <si>
+    <t>Shenzhen lanson Elec</t>
+  </si>
+  <si>
+    <t>C182445</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2410122025_Shenzhen-lanson-Elec-12H1300C_C182445.pdf</t>
+  </si>
+  <si>
+    <t>https://lcsc.com/product-detail/Disposable-fuses_Shenzhen-lanson-Elec-12H1300C_C182445.html</t>
+  </si>
+  <si>
+    <t>50A SMD Fuse 1A 63V 1206 Disposable fuses ROHS</t>
+  </si>
+  <si>
+    <t>12H1100C</t>
+  </si>
+  <si>
+    <t>C182308</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2410122025_Shenzhen-lanson-Elec-12H1100C_C182308.pdf</t>
+  </si>
+  <si>
+    <t>https://lcsc.com/product-detail/Disposable-fuses_Shenzhen-lanson-Elec-12H1100C_C182308.html</t>
+  </si>
+  <si>
+    <t>16V 2.5A 40A 5A 1812 Resettable Fuses ROHS</t>
+  </si>
+  <si>
+    <t>2,5A</t>
+  </si>
+  <si>
+    <t>1812L250/16GR</t>
+  </si>
+  <si>
+    <t>LUTE</t>
+  </si>
+  <si>
+    <t>C19078727</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2310251505_LUTE-1812L250-16GR_C19078727.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/Resettable-Fuses_LUTE-1812L250-16GR_C19078727.html?s_z=n_JK-nSMD200</t>
+  </si>
+  <si>
+    <t>FUSE SMD 1812</t>
+  </si>
+  <si>
+    <t>24V 1.5A 40A 3A 40mΩ 1812 PTC Resettable Fuses RoHS</t>
+  </si>
+  <si>
+    <t>1.5A</t>
+  </si>
+  <si>
+    <t>1812L150/24GR</t>
+  </si>
+  <si>
+    <t>C22392774</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/C22392774.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C22392774.html?s_z=n_1812L150%252F24GR</t>
+  </si>
+  <si>
+    <t>Fuses with Leads - Through Hole 10A 250V SR-5F</t>
+  </si>
+  <si>
+    <t>10A</t>
+  </si>
+  <si>
+    <t>THT,D8.5xL7.6mm</t>
+  </si>
+  <si>
+    <t>SR-5F-10A-AP</t>
+  </si>
+  <si>
+    <t>Eaton Electronics</t>
+  </si>
+  <si>
+    <t>504-SR-5F-10A-AP</t>
+  </si>
+  <si>
+    <t>https://www.eaton.com/content/dam/eaton/products/electronic-components/resources/data-sheet/eaton-sr-5f-subminiature-fast-acting-fuses-data-sheet.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Eaton-Electronics/SR-5F-10A-AP?qs=jGANiKWBgcj73AguR930Aw%3D%3D</t>
+  </si>
+  <si>
+    <t>FUSE SR-5F</t>
+  </si>
+  <si>
+    <t>Polymeric PTC Resettable Fuse 16V 2A Surface Mount 1812</t>
+  </si>
+  <si>
+    <t>2A</t>
+  </si>
+  <si>
+    <t>1812L200/16GR</t>
+  </si>
+  <si>
+    <t>C18198340</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/C18198340.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C18198340.html?s_z=n_1812L200%252F16GR</t>
+  </si>
+  <si>
+    <t>Polymeric PTC Resettable Fuse 16V 2A Surface Mount 1206</t>
+  </si>
+  <si>
+    <t>1206L200/16NR</t>
+  </si>
+  <si>
+    <t>C22374899</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/C22374899.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C22374899.html</t>
+  </si>
+  <si>
+    <t>4A 72V Fuse Surface Mount 1206</t>
+  </si>
+  <si>
+    <t>4A</t>
+  </si>
+  <si>
+    <t>BSMD1206C-1400T</t>
+  </si>
+  <si>
+    <t>BHFUSE</t>
+  </si>
+  <si>
+    <t>C41367227</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/C41367227.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C41367227.html</t>
+  </si>
+  <si>
+    <t>Fusibles de montaje en superficie 32V 0603 4A V/FA HALIDE FREE</t>
+  </si>
+  <si>
+    <t>0467004.NRHF</t>
+  </si>
+  <si>
+    <t>576-0467004.NRHF</t>
+  </si>
+  <si>
+    <t>https://www.littelfuse.com/assetdocs/littelfuse_fuse_467_datasheet.pdf?assetguid=4a59f034-1cca-460e-a5ba-e1e66247c76d</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Littelfuse/0467004.NRHF?qs=PalBzRKzfnueyHMjEWtHJQ%3D%3D</t>
+  </si>
+  <si>
+    <t>FUSE SMD 0603</t>
+  </si>
+  <si>
+    <t>Fusibles de montaje en superficie 32V 0603 2A V/FA HALIDE FREE</t>
+  </si>
+  <si>
+    <t>0467002.NRHF</t>
+  </si>
+  <si>
+    <t>576-0467002.NRHF</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Littelfuse/0467002.NRHF?qs=n5MbhIql%252BRnna7dCryodUA%3D%3D</t>
+  </si>
+  <si>
+    <t>Polymeric PTC Resettable Fuse 33V 100mA Surface Mount 0603</t>
+  </si>
+  <si>
+    <t>100mA</t>
+  </si>
+  <si>
+    <t>0603L010/33XR</t>
+  </si>
+  <si>
+    <t>C7472521</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/C7472516.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C7472521.html?s_z=n_0603L010%252F33XR</t>
+  </si>
+  <si>
+    <t>Polymeric PTC Resettable Fuse 30V 2A Surface Mount 1812</t>
+  </si>
+  <si>
+    <t>1812L200/30GR</t>
+  </si>
+  <si>
+    <t>C18198342</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/C19078727.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C18198342.html?s_z=n_1812L200%252F30GR</t>
+  </si>
+  <si>
+    <t>Polymeric PTC Resettable Fuse 30V 5A Surface Mount 2920</t>
+  </si>
+  <si>
+    <t>2920</t>
+  </si>
+  <si>
+    <t>2920L500/30GR</t>
+  </si>
+  <si>
+    <t>C19078763</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/C19078763.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C19078763.html</t>
+  </si>
+  <si>
+    <t>FUSE SMD 2920</t>
+  </si>
+  <si>
+    <t>Polymeric PTC Resettable Fuse 24V 3A Surface Mount 1812</t>
+  </si>
+  <si>
+    <t>1812L300/24GR</t>
+  </si>
+  <si>
+    <t>C20627123</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/C20627123.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C20627123.html</t>
+  </si>
+  <si>
+    <t>040-0002</t>
+  </si>
+  <si>
+    <t>040-0003</t>
+  </si>
+  <si>
+    <t>040-0004</t>
+  </si>
+  <si>
+    <t>040-0005</t>
+  </si>
+  <si>
+    <t>040-0006</t>
+  </si>
+  <si>
+    <t>040-0007</t>
+  </si>
+  <si>
+    <t>040-0008</t>
+  </si>
+  <si>
+    <t>040-0009</t>
+  </si>
+  <si>
+    <t>040-0010</t>
+  </si>
+  <si>
+    <t>040-0011</t>
+  </si>
+  <si>
+    <t>040-0012</t>
+  </si>
+  <si>
+    <t>040-0013</t>
+  </si>
+  <si>
+    <t>040-0014</t>
+  </si>
+  <si>
+    <t>040-0015</t>
+  </si>
+  <si>
+    <t>040-0016</t>
+  </si>
+  <si>
+    <t>040-0017</t>
+  </si>
+  <si>
+    <t>040-0018</t>
+  </si>
+  <si>
+    <t>040-0019</t>
+  </si>
+  <si>
+    <t>040-0020</t>
+  </si>
+  <si>
+    <t>030-0001</t>
+  </si>
+  <si>
+    <t>920mV@2A 25ns 2A 50V SMA Fast Recovery / High Efficiency Diodes ROHS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">920mV@2A </t>
+  </si>
+  <si>
+    <t>SMA</t>
+  </si>
+  <si>
+    <t>ES2AA-13-F</t>
+  </si>
+  <si>
+    <t>Diodes Incorporated</t>
+  </si>
+  <si>
+    <t>C151575</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2304140030_Diodes-Incorporated-ES2AA-13-F_C151575.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/Fast-Recovery-High-Efficiency-Diodes_Diodes-Incorporated-ES2AA-13-F_C151575.html?s_z=n_ES2AA-13-F</t>
+  </si>
+  <si>
+    <t>DIODE</t>
+  </si>
+  <si>
+    <t>DIODE SMA</t>
+  </si>
+  <si>
+    <t>030-0002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1V@100mA 200mA 30V SOD-323 Schottky Diodes ROHS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1V@100mA 200mA </t>
+  </si>
+  <si>
+    <t>SOD-323</t>
+  </si>
+  <si>
+    <t>BAT54WS</t>
+  </si>
+  <si>
+    <t>hongjiacheng</t>
+  </si>
+  <si>
+    <t>C7502694</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2308281443_hongjiacheng-BAT54WS_C7502694.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/Schottky-Diodes_hongjiacheng-BAT54WS_C7502694.html?s_z=n_BAT54</t>
+  </si>
+  <si>
+    <t>DIODE SOD323</t>
+  </si>
+  <si>
+    <t>030-0003</t>
+  </si>
+  <si>
+    <t>1V@10mA 4ns 200mA 100V  SOT-23 Switching Diodes ROHS</t>
+  </si>
+  <si>
+    <t>1V@10mA 200mA</t>
+  </si>
+  <si>
+    <t>SOT-23</t>
+  </si>
+  <si>
+    <t>MMBD4148CC</t>
+  </si>
+  <si>
+    <t>onsemi</t>
+  </si>
+  <si>
+    <t>C236939</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2410121737_onsemi-MMBD4148CC_C236939.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/Switching-Diodes_onsemi-MMBD4148CC_C236939.html?s_z=n_MMBD4148CC</t>
+  </si>
+  <si>
+    <t>DIODE CC</t>
+  </si>
+  <si>
+    <t>DIODE SOT-23</t>
+  </si>
+  <si>
+    <t>030-0004</t>
+  </si>
+  <si>
+    <t>1A 1kV 1.1V@1A SOD-123FL Diodes - General Purpose ROHS</t>
+  </si>
+  <si>
+    <t>SOD-123</t>
+  </si>
+  <si>
+    <t>SM4007PL A7</t>
+  </si>
+  <si>
+    <t>Slkor(SLKORMICRO Elec.)</t>
+  </si>
+  <si>
+    <t>C426570</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_1912111437_Slkor-SLKORMICRO-Elec--SM4007PL-A7_C426570.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/Diodes-General-Purpose_Slkor-SLKORMICRO-Elec-SM4007PL-A7_C426570.html?s_z=n_C426570</t>
+  </si>
+  <si>
+    <t>030-0005</t>
+  </si>
+  <si>
+    <t>80A 40V Independent 520mV@3A 3A SOD-123FL Single Diodes ROHS</t>
+  </si>
+  <si>
+    <t>40V 3A</t>
+  </si>
+  <si>
+    <t>SOD-123FL</t>
+  </si>
+  <si>
+    <t>DSK34</t>
+  </si>
+  <si>
+    <t>TWGMC</t>
+  </si>
+  <si>
+    <t>C727076</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/C727076.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C727076.html</t>
+  </si>
+  <si>
+    <t>SOD-123FL2</t>
+  </si>
+  <si>
+    <t>030-0006</t>
+  </si>
+  <si>
+    <t>Rectifiers 6.0 Amp 600 Volt 400 Amp IFSM</t>
+  </si>
+  <si>
+    <t>600V 22A</t>
+  </si>
+  <si>
+    <t>P600</t>
+  </si>
+  <si>
+    <t>P600J-E3/73</t>
+  </si>
+  <si>
+    <t>Vishay General Semiconductor</t>
+  </si>
+  <si>
+    <t>625-P600J-E3/73</t>
+  </si>
+  <si>
+    <t>https://www.vishay.com/docs/88692/p600a.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Vishay-General-Semiconductor/P600J-E3-73?qs=E3OxquYwg8HdCumpNQmXxA%3D%3D</t>
+  </si>
+  <si>
+    <t>P600J</t>
+  </si>
+  <si>
+    <t>030-0007</t>
+  </si>
+  <si>
+    <t>Rectifiers Ultrafast, DO-41, 50V, 1A, 175C</t>
+  </si>
+  <si>
+    <t>50V 1A</t>
+  </si>
+  <si>
+    <t>DO-41</t>
+  </si>
+  <si>
+    <t>UF4001</t>
+  </si>
+  <si>
+    <t>Diotec Semiconductor</t>
+  </si>
+  <si>
+    <t>637-UF4001</t>
+  </si>
+  <si>
+    <t>https://diotec.com/request/datasheet/uf4001.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Diotec-Semiconductor/UF4001?qs=OlC7AqGiEDm1RpsmSECQSQ%3D%3D</t>
+  </si>
+  <si>
+    <t>030-0008</t>
+  </si>
+  <si>
+    <t>Rectifiers Ultrafast, DO-214AC, 1200V, 1A</t>
+  </si>
+  <si>
+    <t>1200V 1A</t>
+  </si>
+  <si>
+    <t>DO-214AC</t>
+  </si>
+  <si>
+    <t>STTH112A-FS</t>
+  </si>
+  <si>
+    <t>FUXINSEMI</t>
+  </si>
+  <si>
+    <t>C5563725</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/C5563725.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C5563725.html?s_z=n_STTH112</t>
+  </si>
+  <si>
+    <t>eUSR_SchLibrary/eUSR_SchLibrary - Diode.SchLib</t>
+  </si>
+  <si>
+    <t>031-0001</t>
+  </si>
+  <si>
+    <t>40V 550mV@2A 2A 0603 Schottky Diodes ROHS</t>
+  </si>
+  <si>
+    <t>40V 550mV@2A 2A</t>
+  </si>
+  <si>
+    <t>NSR20F40NXT5G</t>
+  </si>
+  <si>
+    <t>C153761</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_1809111720_onsemi-NSR20F40NXT5G_C153761.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/Schottky-Diodes_onsemi-NSR20F40NXT5G_C153761.html</t>
+  </si>
+  <si>
+    <t>DIODE SCHOTTKY</t>
+  </si>
+  <si>
+    <t>DIODE SMD 0603</t>
+  </si>
+  <si>
+    <t>031-0002</t>
+  </si>
+  <si>
+    <t>40V 900mV@100mA 300mA SOD-523 Schottky Diodes ROHS</t>
+  </si>
+  <si>
+    <t>40V 900mV@100mA 300mA</t>
+  </si>
+  <si>
+    <t>SOD-523</t>
+  </si>
+  <si>
+    <t>BAT54KFILM</t>
+  </si>
+  <si>
+    <t>C283259</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2304140030_STMicroelectronics-BAT54KFILM_C283259.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/Schottky-Diodes_STMicroelectronics-BAT54KFILM_C283259.html</t>
+  </si>
+  <si>
+    <t>031-0003</t>
+  </si>
+  <si>
+    <t>40V Independent Type 550mV@5A 5A SMA(DO-214AC) Schottky Diodes ROHS</t>
+  </si>
+  <si>
+    <t>40V 550mV@5A 5A</t>
+  </si>
+  <si>
+    <t>SS54</t>
+  </si>
+  <si>
+    <t>MDD(Microdiode Semiconductor)</t>
+  </si>
+  <si>
+    <t>C22452</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2411211945_MDD-Microdiode-Semiconductor-SS54_C22452.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/Schottky-Diodes_MDD-Microdiode-Semiconductor-SS54_C22452.html?s_z=n_C22452</t>
+  </si>
+  <si>
+    <t>031-0004</t>
+  </si>
+  <si>
+    <t>30V 1 pair in series 1V@100mA 200mA SOT-23 Schottky Diodes ROHS</t>
+  </si>
+  <si>
+    <t>30V 1V@100mA 200mA</t>
+  </si>
+  <si>
+    <t>BAT54S</t>
+  </si>
+  <si>
+    <t>C727126</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2410122023_TWGMC-BAT54S_C727126.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/Schottky-Barrier-Diodes-SBD_TWGMC-BAT54S_C727126.html</t>
+  </si>
+  <si>
+    <t>DIODE SCHOTTKY 3P</t>
+  </si>
+  <si>
+    <t>031-0005</t>
+  </si>
+  <si>
+    <t>60V 10A 700mV@10A SMB Schottky Diodes ROHS</t>
+  </si>
+  <si>
+    <t>60V 700mV@10A 10A</t>
+  </si>
+  <si>
+    <t>DO-214AA</t>
+  </si>
+  <si>
+    <t>SS1060B</t>
+  </si>
+  <si>
+    <t>C18208635</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2309281727_Slkor-SLKORMICRO-Elec--SS1060B_C18208635.pdf</t>
+  </si>
+  <si>
+    <t>https://lcsc.com/product-detail/Schottky-Diodes_Slkor-SLKORMICRO-Elec-SS1060B_C18208635.html?s_z=s_Diodes%257CSchottky%2520Diodes</t>
+  </si>
+  <si>
+    <t>031-0006</t>
+  </si>
+  <si>
+    <t>Zener Diodes 5.1 Volt 0.5W 5%</t>
+  </si>
+  <si>
+    <t>5.1V 100nA</t>
+  </si>
+  <si>
+    <t>DO-35-2</t>
+  </si>
+  <si>
+    <t>BZX55C5V1-TR</t>
+  </si>
+  <si>
+    <t>Vishay Semiconductors</t>
+  </si>
+  <si>
+    <t>78-BZX55C5V1</t>
+  </si>
+  <si>
+    <t>https://www.vishay.com/docs/85604/bzx55.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Vishay-Semiconductors/BZX55C5V1-TR?qs=WLTup5mM6hhy%252Bqloxl7%2FIQ%3D%3D&amp;utm_id=20109199436&amp;utm_source=google&amp;utm_medium=cpc&amp;utm_marketing_tactic=emeacorp&amp;gad_source=1&amp;gad_campaignid=20109199436&amp;gbraid=0AAAAADn_wf2RhF_lSG_YlgnN1Yzlq3oak&amp;gclid=Cj0KCQiAhtvMBhDBARIsAL26pjE6pviBOpVaBUJ07A83YFMQUf7QkOHJpiHMP9nHJbQo8SvNA6LellYaAlJaEALw_wcB</t>
+  </si>
+  <si>
+    <t>031-0007</t>
+  </si>
+  <si>
+    <t>DIODE SCHOTTKY 40V SMA(DO-214AC)</t>
+  </si>
+  <si>
+    <t>SMA(DO-214AC)</t>
+  </si>
+  <si>
+    <t>SS34</t>
+  </si>
+  <si>
+    <t>GOODWORK</t>
+  </si>
+  <si>
+    <t>C908680</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/C908680.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C908680.html?s_z=n_SS34</t>
+  </si>
+  <si>
+    <t>031-0008</t>
+  </si>
+  <si>
+    <t>Diode 40V 1A Surface Mount SMA(DO-214AC)</t>
+  </si>
+  <si>
+    <t>41V 1A</t>
+  </si>
+  <si>
+    <t>SS14</t>
+  </si>
+  <si>
+    <t>JSMSEMI</t>
+  </si>
+  <si>
+    <t>C2837270</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/C2837270.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C2837270.html?s_z=n_C2837270</t>
+  </si>
+  <si>
+    <t>031-0009</t>
+  </si>
+  <si>
+    <t>Diode 40V 200mA Surface Mount 0603</t>
+  </si>
+  <si>
+    <t>580mV@2A</t>
+  </si>
+  <si>
+    <t>CD0603-B0240R</t>
+  </si>
+  <si>
+    <t>BOURNS</t>
+  </si>
+  <si>
+    <t>C3312582</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/C3312582.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C3312582.html</t>
+  </si>
+  <si>
+    <t>DIODE_SMD_0603</t>
+  </si>
+  <si>
+    <t>031-0010</t>
+  </si>
+  <si>
+    <t>Diodos y rectificadores Schottky 10A, 200V, SMPC TRENCH SKY RECT.</t>
+  </si>
+  <si>
+    <t>200V 10A</t>
+  </si>
+  <si>
+    <t>SMPC (TO-277A-3)</t>
+  </si>
+  <si>
+    <t>V10P22HM3_A/H</t>
+  </si>
+  <si>
+    <t>78-V10P22HM3_A/H</t>
+  </si>
+  <si>
+    <t>https://www.vishay.com/docs/87002/v10p22.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Vishay/V10P22HM3_A-H?qs=sGAEpiMZZMtbRapU8LlZD8qu4xuMq4%252BSxFIcXPYKbhU%252BdoNGIetOdA%3D%3D</t>
+  </si>
+  <si>
+    <t>TO-277A-3</t>
+  </si>
+  <si>
+    <t>031-0011</t>
+  </si>
+  <si>
+    <t>Diode 60V 3A Surface Mount SOD-123FL</t>
+  </si>
+  <si>
+    <t>60V 3A</t>
+  </si>
+  <si>
+    <t>S-LMBR360FT1G</t>
+  </si>
+  <si>
+    <t>LRC</t>
+  </si>
+  <si>
+    <t>C5383051</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/C5383051.pdf?spm=wm.sxq.inf.ggs___wm.ssy.bg.5.xh&amp;lcsc_vid=RABbXwFTQFhZUlVVRVZYUlJXEwdcBAFSTgJbUVxeT1IxVlNRQ1FeUFRQT1hdVTsOAxUeFF5JWBYZEEoKFBINSQcJGk4eFQsCAgIaSgADAwAHC0slQlJWVFRTRk8GEwkK</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C5383051.html?s_z=n_Schottky%252C%2520MBR360&amp;spm=wm.ssy.bg.5.xh&amp;lcsc_vid=RABbXwFTQFhZUlVVRVZYUlJXEwdcBAFSTgJbUVxeT1IxVlNRQ1FeUFRQT1hdVTsOAxUeFF5JWBYZEEoKFBINSQcJGk4eFQsCAgIaSgADAwAHC0slQlJWVFRTRk8GEwkK</t>
+  </si>
+  <si>
+    <t>032-0001</t>
+  </si>
+  <si>
+    <t>6A@8/20us 12V 5.1V 5V FBP-02C ESD and Surge Protection (TVS/ESD) ROHS</t>
+  </si>
+  <si>
+    <t>FBP-02C</t>
+  </si>
+  <si>
+    <t>ESD5471X-2/TR</t>
+  </si>
+  <si>
+    <t>WILLSEMI(Will Semicon)</t>
+  </si>
+  <si>
+    <t>C239631</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2004031411_WILLSEMI-Will-Semicon-ESD5471X-2-TR_C239631.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/span-style-background-color-ff0-ESD-span-and-Surge-Protection-TVS-span-style-background-color-ff0-ESD-span_WILLSEMI-Will-Semicon-ESD5471X-2-TR_C239631.html</t>
+  </si>
+  <si>
+    <t>TVS</t>
+  </si>
+  <si>
+    <t>032-0002</t>
+  </si>
+  <si>
+    <t>5A 100W 15V 6V Bidirectional 5V DFN1006 ESD and Surge Protection (TVS/ESD) ROHS</t>
+  </si>
+  <si>
+    <t>DFN1006</t>
+  </si>
+  <si>
+    <t>AZ5825-01F</t>
+  </si>
+  <si>
+    <t>KUU</t>
+  </si>
+  <si>
+    <t>C5119557</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2207261800_KUU-AZ5825-01F_C5119557.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/ESD-and-Surge-Protection-TVS-ESD_KUU-AZ5825-01F_C5119557.html</t>
+  </si>
+  <si>
+    <t>032-0003</t>
+  </si>
+  <si>
+    <t>7A 11V 72W 8.4V Bidirectional 5V 0402 ESD and Surge Protection (TVS/ESD) ROHS</t>
+  </si>
+  <si>
+    <t>ESD5451N-TP</t>
+  </si>
+  <si>
+    <t>TECH PUBLIC</t>
+  </si>
+  <si>
+    <t>C2830311</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2411121100_TECH-PUBLIC-ESD5451N-TP_C2830311.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/ESD-and-Surge-Protection-TVS-ESD_TECH-PUBLIC-ESD5451N-TP_C2830311.html</t>
+  </si>
+  <si>
+    <t>TVS SMD 0402</t>
+  </si>
+  <si>
+    <t>032-0004</t>
+  </si>
+  <si>
+    <t>1A 9.8V 5.4V Unidirectional 5V SOD-923 ESD and Surge Protection (TVS/ESD) ROHS</t>
+  </si>
+  <si>
+    <t>SOD-923</t>
+  </si>
+  <si>
+    <t>ESD9L5.0ST5G</t>
+  </si>
+  <si>
+    <t>C82326</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2410010231_onsemi-ESD9L5-0ST5G_C82326.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/ESD-and-Surge-Protection-TVS-ESD_onsemi-ESD9L5-0ST5G_C82326.html</t>
+  </si>
+  <si>
+    <t>032-0005</t>
+  </si>
+  <si>
+    <t>100W 30V 6.5V 5.5V SLP1616-6 ESD and Surge Protection (TVS/ESD) ROHS</t>
+  </si>
+  <si>
+    <t>SLP1616-6</t>
+  </si>
+  <si>
+    <t>RCLAMP0854P.TCT</t>
+  </si>
+  <si>
+    <t>SEMTECH</t>
+  </si>
+  <si>
+    <t>C842842</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2411011545_SEMTECH-RCLAMP0854P-TCT_C842842.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/ESD-and-Surge-Protection-TVS-ESD_SEMTECH-RCLAMP0854P-TCT_C842842.html</t>
+  </si>
+  <si>
+    <t>RCLAMP0854P-TCT</t>
+  </si>
+  <si>
+    <t>SLP1616P6-6L</t>
+  </si>
+  <si>
+    <t>032-0006</t>
+  </si>
+  <si>
+    <t>54.4A 1.5kW 27.6V 18.9V 17V DO-214AB ESD and Surge Protection (TVS/ESD) ROHS</t>
+  </si>
+  <si>
+    <t>DO-214AB</t>
+  </si>
+  <si>
+    <t>SMCJ17A</t>
+  </si>
+  <si>
+    <t>C2938306</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2410122003_Littelfuse-SMCJ17A_C2938306.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/ESD-and-Surge-Protection-TVS-ESD_Littelfuse-SMCJ17A_C2938306.html?s_z=n_SMCJ17A</t>
+  </si>
+  <si>
+    <t>TVS S</t>
+  </si>
+  <si>
+    <t>032-0007</t>
+  </si>
+  <si>
+    <t>Independent Type 5W 19V SMB Zener Diodes ROHS</t>
+  </si>
+  <si>
+    <t>SMBJ5356B-MS</t>
+  </si>
+  <si>
+    <t>MSKSEMI</t>
+  </si>
+  <si>
+    <t>C18547763</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2410121938_Littelfuse-015402-5DR_C206922.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/Zener-Diodes_MSKSEMI-SMBJ5356B-MS_C18547763.html?s_z=n_C18547763</t>
+  </si>
+  <si>
+    <t>DO-214AA B</t>
+  </si>
+  <si>
+    <t>032-0008</t>
+  </si>
+  <si>
+    <t>30.2A 19.9V 13.3V 12V SMB ESD and Surge Protection (TVS/ESD) ROHS</t>
+  </si>
+  <si>
+    <t>SMBJ12A</t>
+  </si>
+  <si>
+    <t>YFW</t>
+  </si>
+  <si>
+    <t>C2898391</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2410121738_YFW-SMBJ12A_C2898391.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/TVS_YFW-SMBJ12A_C2898391.html</t>
+  </si>
+  <si>
+    <t>032-0009</t>
+  </si>
+  <si>
+    <t>400W SOT-23 ESD and Surge Protection (TVS/ESD) ROHS</t>
+  </si>
+  <si>
+    <t>CDSOT23-SM712</t>
+  </si>
+  <si>
+    <t>C404012</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2410121813_BOURNS-CDSOT23-SM712_C404012.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/ESD-and-Surge-Protection-TVS-ESD_BOURNS-CDSOT23-SM712_C404012.html?s_z=n_CDSOT23-SM712</t>
+  </si>
+  <si>
+    <t>Dual TVS</t>
+  </si>
+  <si>
+    <t>032-0010</t>
+  </si>
+  <si>
+    <t>369W 12.3V 4V 3.3V SOT-23 ESD and Surge Protection (TVS/ESD) ROHS</t>
+  </si>
+  <si>
+    <t>GSOT03C-E3-08</t>
+  </si>
+  <si>
+    <t>C435893</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2410121813_Vishay-Intertech-GSOT03C-E3-08_C435893.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/ESD-and-Surge-Protection-TVS-ESD_Vishay-Intertech-GSOT03C-E3-08_C435893.html?s_z=n_GSOT03C-E3-08</t>
+  </si>
+  <si>
+    <t>ESD 2-line</t>
+  </si>
+  <si>
+    <t>032-0011</t>
+  </si>
+  <si>
+    <t>6A 320W 38V 26.5V Bidirectional 24V SOT-23 ESD and Surge Protection (TVS/ESD) ROHS</t>
+  </si>
+  <si>
+    <t>ESD2CAN24-ES</t>
+  </si>
+  <si>
+    <t>ElecSuper</t>
+  </si>
+  <si>
+    <t>C19170841</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2412061751_ElecSuper-ESD2CAN24-ES_C19170841.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/ESD-and-Surge-Protection-TVS-ESD_ElecSuper-ESD2CAN24-ES_C19170841.html?s_z=n_ESD2CAN24</t>
+  </si>
+  <si>
+    <t>032-0012</t>
+  </si>
+  <si>
+    <t>DFN2510-10L ESD and Surge Protection 4 channels(TVS/ESD) ROHS</t>
+  </si>
+  <si>
+    <t>DFN2510-10L</t>
+  </si>
+  <si>
+    <t>ESD73034D-10/TR</t>
+  </si>
+  <si>
+    <t>C2941834</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2410121434_WILLSEMI-Will-Semicon-ESD73034D-10-TR_C2941834.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/ESD-Protection-Devices_WILLSEMI-Will-Semicon-ESD73034D-10-TR_C2941834.html</t>
+  </si>
+  <si>
+    <t>ESD73034D</t>
+  </si>
+  <si>
+    <t>032-0013</t>
+  </si>
+  <si>
+    <t>ESD Protection Diodes / TVS Diodes WE-TVS Diode Array 3.3V 0.18pF 2Channel</t>
+  </si>
+  <si>
+    <t>DFN-1210-6</t>
+  </si>
+  <si>
+    <t>Wurth Elektronik</t>
+  </si>
+  <si>
+    <t>710-824012823</t>
+  </si>
+  <si>
+    <t>MOUSER</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/824012823.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/824012823?qs=rrS6PyfT74dPtw7q26tZFg%3D%3D</t>
+  </si>
+  <si>
+    <t>DFN1210-6L</t>
+  </si>
+  <si>
+    <t>032-0014</t>
+  </si>
+  <si>
+    <t>25A 20V 4V Unidirectional 3.3V SOT-23 ESD and Surge Protection (TVS/ESD) ROHS</t>
+  </si>
+  <si>
+    <t>PESD3V3S2UT-ES</t>
+  </si>
+  <si>
+    <t>C5199192</t>
+  </si>
+  <si>
+    <t>https://lcsc.com/datasheet/lcsc_datasheet_2504101957_ElecSuper-PESD3V3L2BT-ES_C5180242.pdf</t>
+  </si>
+  <si>
+    <t>https://lcsc.com/product-detail/ESD-and-Surge-Protection-TVS-ESD_ElecSuper-PESD3V3S2UT-ES_C5199192.html</t>
+  </si>
+  <si>
+    <t>032-0015</t>
+  </si>
+  <si>
+    <t>4A@8/20us 100W@8/20us 15V 4.2V 3.3V SOT-23 ESD and Surge Protection (TVS/ESD) ROHS</t>
+  </si>
+  <si>
+    <t>TPESD3V3X2UTR</t>
+  </si>
+  <si>
+    <t>C48586723</t>
+  </si>
+  <si>
+    <t>https://lcsc.com/datasheet/lcsc_datasheet_2504281715_TECH-PUBLIC-TPESD3V3X2UTR_C48586723.pdf</t>
+  </si>
+  <si>
+    <t>DIODE 3P R</t>
+  </si>
+  <si>
+    <t>032-0016</t>
+  </si>
+  <si>
+    <t>6A 15V 150W 9V 5V SOT-23-6 ESD and Surge Protection (TVS/ESD) ROHS</t>
+  </si>
+  <si>
+    <t>SOT-23-6</t>
+  </si>
+  <si>
+    <t>USBLC6-2SC6</t>
+  </si>
+  <si>
+    <t>C5250994</t>
+  </si>
+  <si>
+    <t>https://lcsc.com/datasheet/lcsc_datasheet_2410121815_TWGMC-USBLC6-2SC6_C5250994.pdf</t>
+  </si>
+  <si>
+    <t>https://lcsc.com/product-detail/ESD-and-Surge-Protection-TVS-ESD_TWGMC-USBLC6-2SC6_C5250994.html?s_z=n_C5250994</t>
+  </si>
+  <si>
+    <t>DUAL_TVS_DIODE</t>
+  </si>
+  <si>
+    <t>032-0017</t>
+  </si>
+  <si>
+    <t>SOT-23 ESD and Surge Protection (TVS/ESD) ROHS</t>
+  </si>
+  <si>
+    <t>RLST23A032C</t>
+  </si>
+  <si>
+    <t>RUILON(Shenzhen Ruilongyuan Elec)</t>
+  </si>
+  <si>
+    <t>C46970949</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2504101957_RUILON-Shenzhen-Ruilongyuan-Elec-RLST23A032C_C46970949.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/ESD-and-Surge-Protection-TVS-ESD_RUILON-Shenzhen-Ruilongyuan-Elec-RLST23A032C_C46970949.html?s_z=n_RLST23A032C</t>
+  </si>
+  <si>
+    <t>032-0018</t>
+  </si>
+  <si>
+    <t>40A@8/20us 27.7V 1.12kW@8/20us 25.9V Unidirectional 22V WSON-6-EP(2x2) ESD and Surge Protection (TVS/ESD) ROHS</t>
+  </si>
+  <si>
+    <t>WSON-6-EP(2x2)</t>
+  </si>
+  <si>
+    <t>TVS2200DRVR</t>
+  </si>
+  <si>
+    <t>C523793</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/C523793.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C523793.html?s_z=n_TVS2200DRVR</t>
+  </si>
+  <si>
+    <t>032-0019</t>
+  </si>
+  <si>
+    <t>High-speed serial interface common mode filter with ESD protection</t>
+  </si>
+  <si>
+    <t>microQFN-6L</t>
+  </si>
+  <si>
+    <t>ECMF2-40A100N6</t>
+  </si>
+  <si>
+    <t>C5267592</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/C5267592.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C5267592.html?s_z=n_ECMF2-40A100N6</t>
+  </si>
+  <si>
+    <t>MICROQFN-6L</t>
+  </si>
+  <si>
+    <t>032-0020</t>
+  </si>
+  <si>
+    <t>Zener Diode 7.5V 250mW Surface Mount SOT-23</t>
+  </si>
+  <si>
+    <t>BZX84C7V5LT1G</t>
+  </si>
+  <si>
+    <t>C236201</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/C236201.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C236201.html</t>
+  </si>
+  <si>
+    <t>ZENER_SOT23</t>
+  </si>
+  <si>
+    <t>032-0021</t>
+  </si>
+  <si>
+    <t>10.3VC Clamp 38.8A Ipp TVS DIODE DO-214AC(SMA)</t>
+  </si>
+  <si>
+    <t>DO-214AC(SMA)</t>
+  </si>
+  <si>
+    <t>SMAJ6.0A</t>
+  </si>
+  <si>
+    <t>C223993</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/C223993.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C223993.html</t>
+  </si>
+  <si>
+    <t>032-0022</t>
+  </si>
+  <si>
+    <t>TVS DIODE 14VWM 23.2VC DO-214AA</t>
+  </si>
+  <si>
+    <t>SMBJ13A</t>
+  </si>
+  <si>
+    <t>C151252</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/C151252.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C151252.html</t>
   </si>
 </sst>
 </file>
@@ -5115,7 +6548,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5201,8 +6634,31 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0563C1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5213,6 +6669,12 @@
       <patternFill patternType="solid">
         <fgColor theme="2"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD0CECE"/>
+        <bgColor rgb="FFD0CECE"/>
       </patternFill>
     </fill>
   </fills>
@@ -5246,7 +6708,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -5281,6 +6743,56 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -9685,6 +11197,254 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59BC8B2E-A067-463D-937A-30E88D8BECD0}">
+  <dimension ref="A1:N1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4BBBCF5-BAC9-459C-ABE9-2526B85FD81E}">
+  <dimension ref="A1:N4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="4" max="4" width="17.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1669</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1670</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1671</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1674</v>
+      </c>
+      <c r="F2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G2" t="s">
+        <v>1675</v>
+      </c>
+      <c r="H2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>1672</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>1673</v>
+      </c>
+      <c r="K2" t="s">
+        <v>1676</v>
+      </c>
+      <c r="L2" t="s">
+        <v>1689</v>
+      </c>
+      <c r="M2" t="s">
+        <v>1676</v>
+      </c>
+      <c r="N2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>1677</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1678</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1679</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1671</v>
+      </c>
+      <c r="E3" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G3" t="s">
+        <v>1681</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" t="s">
+        <v>1672</v>
+      </c>
+      <c r="J3" t="s">
+        <v>1682</v>
+      </c>
+      <c r="K3" t="s">
+        <v>1676</v>
+      </c>
+      <c r="L3" t="s">
+        <v>1689</v>
+      </c>
+      <c r="M3" t="s">
+        <v>1676</v>
+      </c>
+      <c r="N3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>1683</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1684</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1685</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1671</v>
+      </c>
+      <c r="E4" t="s">
+        <v>1686</v>
+      </c>
+      <c r="F4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G4" t="s">
+        <v>1687</v>
+      </c>
+      <c r="H4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" t="s">
+        <v>1672</v>
+      </c>
+      <c r="J4" t="s">
+        <v>1688</v>
+      </c>
+      <c r="K4" t="s">
+        <v>1676</v>
+      </c>
+      <c r="L4" t="s">
+        <v>1689</v>
+      </c>
+      <c r="M4" t="s">
+        <v>1676</v>
+      </c>
+      <c r="N4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="I2" r:id="rId1" xr:uid="{08280A44-0F58-4FDE-B5FD-3A95A0F423CB}"/>
+    <hyperlink ref="J2" r:id="rId2" xr:uid="{85F326FF-BAE0-4072-815D-1EE4E7995C53}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60E8291E-4293-4634-B9E9-80CB520CA181}">
   <dimension ref="A1:N136"/>
@@ -15981,7 +17741,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{652841DA-3619-42EE-A536-61B58BE1B457}">
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:14">
@@ -16028,21 +17788,1975 @@
         <v>13</v>
       </c>
     </row>
+    <row r="2" spans="1:14">
+      <c r="A2" s="32" t="s">
+        <v>1832</v>
+      </c>
+      <c r="B2" s="32" t="s">
+        <v>1833</v>
+      </c>
+      <c r="C2" s="34" t="s">
+        <v>1834</v>
+      </c>
+      <c r="D2" s="32" t="s">
+        <v>1835</v>
+      </c>
+      <c r="E2" s="32" t="s">
+        <v>1836</v>
+      </c>
+      <c r="F2" s="32" t="s">
+        <v>1837</v>
+      </c>
+      <c r="G2" s="32" t="s">
+        <v>1838</v>
+      </c>
+      <c r="H2" s="32" t="s">
+        <v>69</v>
+      </c>
+      <c r="I2" s="32" t="s">
+        <v>1839</v>
+      </c>
+      <c r="J2" s="32" t="s">
+        <v>1840</v>
+      </c>
+      <c r="K2" s="32" t="s">
+        <v>1841</v>
+      </c>
+      <c r="L2" s="32" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M2" s="32" t="s">
+        <v>1842</v>
+      </c>
+      <c r="N2" s="32" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="32" t="s">
+        <v>1843</v>
+      </c>
+      <c r="B3" s="32" t="s">
+        <v>1844</v>
+      </c>
+      <c r="C3" s="32" t="s">
+        <v>1845</v>
+      </c>
+      <c r="D3" s="32" t="s">
+        <v>1846</v>
+      </c>
+      <c r="E3" s="32" t="s">
+        <v>1847</v>
+      </c>
+      <c r="F3" s="32" t="s">
+        <v>1848</v>
+      </c>
+      <c r="G3" s="32" t="s">
+        <v>1849</v>
+      </c>
+      <c r="H3" s="32" t="s">
+        <v>69</v>
+      </c>
+      <c r="I3" s="32" t="s">
+        <v>1850</v>
+      </c>
+      <c r="J3" s="32" t="s">
+        <v>1851</v>
+      </c>
+      <c r="K3" s="32" t="s">
+        <v>1841</v>
+      </c>
+      <c r="L3" s="32" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M3" s="32" t="s">
+        <v>1852</v>
+      </c>
+      <c r="N3" s="32" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="32" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B4" s="32" t="s">
+        <v>1854</v>
+      </c>
+      <c r="C4" s="32" t="s">
+        <v>1855</v>
+      </c>
+      <c r="D4" s="32" t="s">
+        <v>1856</v>
+      </c>
+      <c r="E4" s="32" t="s">
+        <v>1857</v>
+      </c>
+      <c r="F4" s="32" t="s">
+        <v>1858</v>
+      </c>
+      <c r="G4" s="32" t="s">
+        <v>1859</v>
+      </c>
+      <c r="H4" s="32" t="s">
+        <v>69</v>
+      </c>
+      <c r="I4" s="32" t="s">
+        <v>1860</v>
+      </c>
+      <c r="J4" s="32" t="s">
+        <v>1861</v>
+      </c>
+      <c r="K4" s="32" t="s">
+        <v>1862</v>
+      </c>
+      <c r="L4" s="32" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M4" s="32" t="s">
+        <v>1863</v>
+      </c>
+      <c r="N4" s="32" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="32" t="s">
+        <v>1864</v>
+      </c>
+      <c r="B5" s="32" t="s">
+        <v>1865</v>
+      </c>
+      <c r="C5" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="32" t="s">
+        <v>1866</v>
+      </c>
+      <c r="E5" s="32" t="s">
+        <v>1867</v>
+      </c>
+      <c r="F5" s="32" t="s">
+        <v>1868</v>
+      </c>
+      <c r="G5" s="32" t="s">
+        <v>1869</v>
+      </c>
+      <c r="H5" s="32" t="s">
+        <v>69</v>
+      </c>
+      <c r="I5" s="33" t="s">
+        <v>1870</v>
+      </c>
+      <c r="J5" s="33" t="s">
+        <v>1871</v>
+      </c>
+      <c r="K5" s="32" t="s">
+        <v>1841</v>
+      </c>
+      <c r="L5" s="32" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M5" s="32" t="s">
+        <v>1866</v>
+      </c>
+      <c r="N5" s="32" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="32" t="s">
+        <v>1872</v>
+      </c>
+      <c r="B6" s="32" t="s">
+        <v>1873</v>
+      </c>
+      <c r="C6" s="32" t="s">
+        <v>1874</v>
+      </c>
+      <c r="D6" s="32" t="s">
+        <v>1875</v>
+      </c>
+      <c r="E6" s="32" t="s">
+        <v>1876</v>
+      </c>
+      <c r="F6" s="32" t="s">
+        <v>1877</v>
+      </c>
+      <c r="G6" s="32" t="s">
+        <v>1878</v>
+      </c>
+      <c r="H6" s="32" t="s">
+        <v>69</v>
+      </c>
+      <c r="I6" s="31" t="s">
+        <v>1879</v>
+      </c>
+      <c r="J6" s="31" t="s">
+        <v>1880</v>
+      </c>
+      <c r="K6" s="32" t="s">
+        <v>1841</v>
+      </c>
+      <c r="L6" s="32" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M6" s="31" t="s">
+        <v>1881</v>
+      </c>
+      <c r="N6" s="32" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="32" t="s">
+        <v>1882</v>
+      </c>
+      <c r="B7" s="31" t="s">
+        <v>1883</v>
+      </c>
+      <c r="C7" s="35" t="s">
+        <v>1884</v>
+      </c>
+      <c r="D7" s="35" t="s">
+        <v>1885</v>
+      </c>
+      <c r="E7" s="31" t="s">
+        <v>1886</v>
+      </c>
+      <c r="F7" s="35" t="s">
+        <v>1887</v>
+      </c>
+      <c r="G7" s="35" t="s">
+        <v>1888</v>
+      </c>
+      <c r="H7" s="35" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="31" t="s">
+        <v>1889</v>
+      </c>
+      <c r="J7" s="31" t="s">
+        <v>1890</v>
+      </c>
+      <c r="K7" s="35" t="s">
+        <v>1841</v>
+      </c>
+      <c r="L7" s="32" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M7" s="35" t="s">
+        <v>1891</v>
+      </c>
+      <c r="N7" s="32" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="35" t="s">
+        <v>1892</v>
+      </c>
+      <c r="B8" s="36" t="s">
+        <v>1893</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>1894</v>
+      </c>
+      <c r="D8" s="36" t="s">
+        <v>1895</v>
+      </c>
+      <c r="E8" s="36" t="s">
+        <v>1896</v>
+      </c>
+      <c r="F8" s="35" t="s">
+        <v>1897</v>
+      </c>
+      <c r="G8" s="35" t="s">
+        <v>1898</v>
+      </c>
+      <c r="H8" s="35" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" s="37" t="s">
+        <v>1899</v>
+      </c>
+      <c r="J8" s="37" t="s">
+        <v>1900</v>
+      </c>
+      <c r="K8" s="35" t="s">
+        <v>1841</v>
+      </c>
+      <c r="L8" s="32" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M8" s="35" t="s">
+        <v>1895</v>
+      </c>
+      <c r="N8" s="32" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="35" t="s">
+        <v>1901</v>
+      </c>
+      <c r="B9" s="36" t="s">
+        <v>1902</v>
+      </c>
+      <c r="C9" s="35" t="s">
+        <v>1903</v>
+      </c>
+      <c r="D9" s="35" t="s">
+        <v>1904</v>
+      </c>
+      <c r="E9" s="31" t="s">
+        <v>1905</v>
+      </c>
+      <c r="F9" s="31" t="s">
+        <v>1906</v>
+      </c>
+      <c r="G9" s="31" t="s">
+        <v>1907</v>
+      </c>
+      <c r="H9" s="32" t="s">
+        <v>69</v>
+      </c>
+      <c r="I9" s="31" t="s">
+        <v>1908</v>
+      </c>
+      <c r="J9" s="31" t="s">
+        <v>1909</v>
+      </c>
+      <c r="K9" s="35" t="s">
+        <v>1841</v>
+      </c>
+      <c r="L9" s="32" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M9" s="31" t="s">
+        <v>1904</v>
+      </c>
+      <c r="N9" s="32" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="I5" r:id="rId1" xr:uid="{00000000-0004-0000-0800-000000000000}"/>
+    <hyperlink ref="J5" r:id="rId2" xr:uid="{00000000-0004-0000-0800-000001000000}"/>
+    <hyperlink ref="I8" r:id="rId3" xr:uid="{ABAB45EA-9261-4561-98A3-C830A74C7893}"/>
+    <hyperlink ref="J8" r:id="rId4" xr:uid="{E0090D85-56DB-4EF7-BD41-6F63EB17645B}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FE2008B-4BF4-4C9A-883A-FEE5873AEAF4}">
+  <dimension ref="A1:N12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetData>
+    <row r="1" spans="1:14" ht="16" customHeight="1">
+      <c r="A1" s="39" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="39" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="39" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="39" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="39" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="39" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="16" customHeight="1">
+      <c r="A2" s="40" t="s">
+        <v>1911</v>
+      </c>
+      <c r="B2" s="40" t="s">
+        <v>1912</v>
+      </c>
+      <c r="C2" s="40" t="s">
+        <v>1913</v>
+      </c>
+      <c r="D2" s="41" t="s">
+        <v>59</v>
+      </c>
+      <c r="E2" s="40" t="s">
+        <v>1914</v>
+      </c>
+      <c r="F2" s="40" t="s">
+        <v>1858</v>
+      </c>
+      <c r="G2" s="40" t="s">
+        <v>1915</v>
+      </c>
+      <c r="H2" s="40" t="s">
+        <v>69</v>
+      </c>
+      <c r="I2" s="40" t="s">
+        <v>1916</v>
+      </c>
+      <c r="J2" s="40" t="s">
+        <v>1917</v>
+      </c>
+      <c r="K2" s="40" t="s">
+        <v>1918</v>
+      </c>
+      <c r="L2" s="40" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M2" s="41" t="s">
+        <v>1919</v>
+      </c>
+      <c r="N2" s="40" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="16" customHeight="1">
+      <c r="A3" s="40" t="s">
+        <v>1920</v>
+      </c>
+      <c r="B3" s="40" t="s">
+        <v>1921</v>
+      </c>
+      <c r="C3" s="40" t="s">
+        <v>1922</v>
+      </c>
+      <c r="D3" s="40" t="s">
+        <v>1923</v>
+      </c>
+      <c r="E3" s="40" t="s">
+        <v>1924</v>
+      </c>
+      <c r="F3" s="42" t="s">
+        <v>41</v>
+      </c>
+      <c r="G3" s="40" t="s">
+        <v>1925</v>
+      </c>
+      <c r="H3" s="40" t="s">
+        <v>69</v>
+      </c>
+      <c r="I3" s="43" t="s">
+        <v>1926</v>
+      </c>
+      <c r="J3" s="40" t="s">
+        <v>1927</v>
+      </c>
+      <c r="K3" s="40" t="s">
+        <v>1918</v>
+      </c>
+      <c r="L3" s="52" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M3" s="40" t="s">
+        <v>1923</v>
+      </c>
+      <c r="N3" s="52" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="16" customHeight="1">
+      <c r="A4" s="40" t="s">
+        <v>1928</v>
+      </c>
+      <c r="B4" s="40" t="s">
+        <v>1929</v>
+      </c>
+      <c r="C4" s="40" t="s">
+        <v>1930</v>
+      </c>
+      <c r="D4" s="40" t="s">
+        <v>1904</v>
+      </c>
+      <c r="E4" s="40" t="s">
+        <v>1931</v>
+      </c>
+      <c r="F4" s="40" t="s">
+        <v>1932</v>
+      </c>
+      <c r="G4" s="40" t="s">
+        <v>1933</v>
+      </c>
+      <c r="H4" s="40" t="s">
+        <v>69</v>
+      </c>
+      <c r="I4" s="40" t="s">
+        <v>1934</v>
+      </c>
+      <c r="J4" s="40" t="s">
+        <v>1935</v>
+      </c>
+      <c r="K4" s="40" t="s">
+        <v>1918</v>
+      </c>
+      <c r="L4" s="52" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M4" s="40" t="s">
+        <v>1904</v>
+      </c>
+      <c r="N4" s="52" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="16" customHeight="1">
+      <c r="A5" s="40" t="s">
+        <v>1936</v>
+      </c>
+      <c r="B5" s="40" t="s">
+        <v>1937</v>
+      </c>
+      <c r="C5" s="40" t="s">
+        <v>1938</v>
+      </c>
+      <c r="D5" s="40" t="s">
+        <v>1856</v>
+      </c>
+      <c r="E5" s="40" t="s">
+        <v>1939</v>
+      </c>
+      <c r="F5" s="40" t="s">
+        <v>1877</v>
+      </c>
+      <c r="G5" s="40" t="s">
+        <v>1940</v>
+      </c>
+      <c r="H5" s="40" t="s">
+        <v>69</v>
+      </c>
+      <c r="I5" s="45" t="s">
+        <v>1941</v>
+      </c>
+      <c r="J5" s="45" t="s">
+        <v>1942</v>
+      </c>
+      <c r="K5" s="40" t="s">
+        <v>1943</v>
+      </c>
+      <c r="L5" s="52" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M5" s="41" t="s">
+        <v>1856</v>
+      </c>
+      <c r="N5" s="52" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="16" customHeight="1">
+      <c r="A6" s="40" t="s">
+        <v>1944</v>
+      </c>
+      <c r="B6" s="44" t="s">
+        <v>1945</v>
+      </c>
+      <c r="C6" s="40" t="s">
+        <v>1946</v>
+      </c>
+      <c r="D6" s="40" t="s">
+        <v>1947</v>
+      </c>
+      <c r="E6" s="44" t="s">
+        <v>1948</v>
+      </c>
+      <c r="F6" s="44" t="s">
+        <v>1868</v>
+      </c>
+      <c r="G6" s="44" t="s">
+        <v>1949</v>
+      </c>
+      <c r="H6" s="40" t="s">
+        <v>69</v>
+      </c>
+      <c r="I6" s="44" t="s">
+        <v>1950</v>
+      </c>
+      <c r="J6" s="44" t="s">
+        <v>1951</v>
+      </c>
+      <c r="K6" s="40" t="s">
+        <v>1918</v>
+      </c>
+      <c r="L6" s="52" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M6" s="40" t="s">
+        <v>1904</v>
+      </c>
+      <c r="N6" s="52" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="16" customHeight="1">
+      <c r="A7" s="40" t="s">
+        <v>1952</v>
+      </c>
+      <c r="B7" s="38" t="s">
+        <v>1953</v>
+      </c>
+      <c r="C7" s="40" t="s">
+        <v>1954</v>
+      </c>
+      <c r="D7" s="40" t="s">
+        <v>1955</v>
+      </c>
+      <c r="E7" s="40" t="s">
+        <v>1956</v>
+      </c>
+      <c r="F7" s="40" t="s">
+        <v>1957</v>
+      </c>
+      <c r="G7" s="40" t="s">
+        <v>1958</v>
+      </c>
+      <c r="H7" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="48" t="s">
+        <v>1959</v>
+      </c>
+      <c r="J7" s="48" t="s">
+        <v>1960</v>
+      </c>
+      <c r="K7" s="40" t="s">
+        <v>1918</v>
+      </c>
+      <c r="L7" s="52" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M7" s="40" t="s">
+        <v>1955</v>
+      </c>
+      <c r="N7" s="52" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="16" customHeight="1">
+      <c r="A8" s="40" t="s">
+        <v>1961</v>
+      </c>
+      <c r="B8" s="38" t="s">
+        <v>1962</v>
+      </c>
+      <c r="C8" s="40" t="s">
+        <v>1874</v>
+      </c>
+      <c r="D8" s="40" t="s">
+        <v>1963</v>
+      </c>
+      <c r="E8" s="38" t="s">
+        <v>1964</v>
+      </c>
+      <c r="F8" s="40" t="s">
+        <v>1965</v>
+      </c>
+      <c r="G8" s="40" t="s">
+        <v>1966</v>
+      </c>
+      <c r="H8" s="40" t="s">
+        <v>69</v>
+      </c>
+      <c r="I8" s="48" t="s">
+        <v>1967</v>
+      </c>
+      <c r="J8" s="38" t="s">
+        <v>1968</v>
+      </c>
+      <c r="K8" s="40" t="s">
+        <v>1918</v>
+      </c>
+      <c r="L8" s="52" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M8" s="40" t="s">
+        <v>1904</v>
+      </c>
+      <c r="N8" s="52" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="16" customHeight="1">
+      <c r="A9" s="40" t="s">
+        <v>1969</v>
+      </c>
+      <c r="B9" s="38" t="s">
+        <v>1970</v>
+      </c>
+      <c r="C9" s="40" t="s">
+        <v>1971</v>
+      </c>
+      <c r="D9" s="40" t="s">
+        <v>1963</v>
+      </c>
+      <c r="E9" s="40" t="s">
+        <v>1972</v>
+      </c>
+      <c r="F9" s="40" t="s">
+        <v>1973</v>
+      </c>
+      <c r="G9" s="40" t="s">
+        <v>1974</v>
+      </c>
+      <c r="H9" s="40" t="s">
+        <v>69</v>
+      </c>
+      <c r="I9" s="48" t="s">
+        <v>1975</v>
+      </c>
+      <c r="J9" s="48" t="s">
+        <v>1976</v>
+      </c>
+      <c r="K9" s="40" t="s">
+        <v>1918</v>
+      </c>
+      <c r="L9" s="52" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M9" s="40" t="s">
+        <v>1904</v>
+      </c>
+      <c r="N9" s="52" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="16" customHeight="1">
+      <c r="A10" s="46" t="s">
+        <v>1977</v>
+      </c>
+      <c r="B10" s="38" t="s">
+        <v>1978</v>
+      </c>
+      <c r="C10" s="48" t="s">
+        <v>1979</v>
+      </c>
+      <c r="D10" s="47" t="s">
+        <v>59</v>
+      </c>
+      <c r="E10" s="47" t="s">
+        <v>1980</v>
+      </c>
+      <c r="F10" s="38" t="s">
+        <v>1981</v>
+      </c>
+      <c r="G10" s="46" t="s">
+        <v>1982</v>
+      </c>
+      <c r="H10" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="I10" s="48" t="s">
+        <v>1983</v>
+      </c>
+      <c r="J10" s="38" t="s">
+        <v>1984</v>
+      </c>
+      <c r="K10" s="40" t="s">
+        <v>1918</v>
+      </c>
+      <c r="L10" s="52" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M10" s="46" t="s">
+        <v>1985</v>
+      </c>
+      <c r="N10" s="52" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="16" customHeight="1">
+      <c r="A11" s="46" t="s">
+        <v>1986</v>
+      </c>
+      <c r="B11" s="38" t="s">
+        <v>1987</v>
+      </c>
+      <c r="C11" s="49" t="s">
+        <v>1988</v>
+      </c>
+      <c r="D11" s="47" t="s">
+        <v>1989</v>
+      </c>
+      <c r="E11" s="47" t="s">
+        <v>1990</v>
+      </c>
+      <c r="F11" s="47" t="s">
+        <v>1957</v>
+      </c>
+      <c r="G11" s="47" t="s">
+        <v>1991</v>
+      </c>
+      <c r="H11" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I11" s="48" t="s">
+        <v>1992</v>
+      </c>
+      <c r="J11" s="38" t="s">
+        <v>1993</v>
+      </c>
+      <c r="K11" s="40" t="s">
+        <v>1918</v>
+      </c>
+      <c r="L11" s="52" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M11" s="46" t="s">
+        <v>1994</v>
+      </c>
+      <c r="N11" s="52" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="16" customHeight="1">
+      <c r="A12" s="46" t="s">
+        <v>1995</v>
+      </c>
+      <c r="B12" s="38" t="s">
+        <v>1996</v>
+      </c>
+      <c r="C12" s="49" t="s">
+        <v>1997</v>
+      </c>
+      <c r="D12" s="38" t="s">
+        <v>1875</v>
+      </c>
+      <c r="E12" s="47" t="s">
+        <v>1998</v>
+      </c>
+      <c r="F12" s="38" t="s">
+        <v>1999</v>
+      </c>
+      <c r="G12" s="47" t="s">
+        <v>2000</v>
+      </c>
+      <c r="H12" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="I12" s="48" t="s">
+        <v>2001</v>
+      </c>
+      <c r="J12" s="38" t="s">
+        <v>2002</v>
+      </c>
+      <c r="K12" s="40" t="s">
+        <v>1918</v>
+      </c>
+      <c r="L12" s="52" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M12" s="40" t="s">
+        <v>1881</v>
+      </c>
+      <c r="N12" s="52" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="I3" r:id="rId1" xr:uid="{00000000-0004-0000-0900-000000000000}"/>
+    <hyperlink ref="I5" r:id="rId2" xr:uid="{00000000-0004-0000-0900-000001000000}"/>
+    <hyperlink ref="J5" r:id="rId3" xr:uid="{00000000-0004-0000-0900-000002000000}"/>
+    <hyperlink ref="I7" r:id="rId4" xr:uid="{8F1A973E-B5AB-44F6-96AD-40713F29721B}"/>
+    <hyperlink ref="J7" r:id="rId5" display="https://www.mouser.es/ProductDetail/Vishay-Semiconductors/BZX55C5V1-TR?qs=WLTup5mM6hhy%252Bqloxl7%2FIQ%3D%3D&amp;utm_id=20109199436&amp;utm_source=google&amp;utm_medium=cpc&amp;utm_marketing_tactic=emeacorp&amp;gad_source=1&amp;gad_campaignid=20109199436&amp;gbraid=0AAAAADn_wf2RhF_lSG_YlgnN1Yzlq3oak&amp;gclid=Cj0KCQiAhtvMBhDBARIsAL26pjE6pviBOpVaBUJ07A83YFMQUf7QkOHJpiHMP9nHJbQo8SvNA6LellYaAlJaEALw_wcB" xr:uid="{F2496565-AD95-4399-945A-CAC2965FBB51}"/>
+    <hyperlink ref="I8" r:id="rId6" xr:uid="{0E407122-DEDC-4464-8361-A36EA45E6AB5}"/>
+    <hyperlink ref="J9" r:id="rId7" xr:uid="{3E5FFD60-2B94-43D5-BD33-FCAB73A614C5}"/>
+    <hyperlink ref="I9" r:id="rId8" xr:uid="{FAF085BE-308D-4591-BB1A-0398244BD98C}"/>
+    <hyperlink ref="I10" r:id="rId9" xr:uid="{43EA2952-ABB5-4F52-94F7-A96F82DE8560}"/>
+    <hyperlink ref="I11" r:id="rId10" xr:uid="{E8167B89-7FBA-4877-BC25-3D4C05ED8AA6}"/>
+    <hyperlink ref="I12" r:id="rId11" xr:uid="{C4B46D5B-BD3F-4DBC-A61E-40C494B3D177}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89BFA1EF-29B2-41E4-A9D1-F8E90A663FA1}">
+  <dimension ref="A1:N23"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetData>
+    <row r="1" spans="1:14" ht="14.5" customHeight="1">
+      <c r="A1" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="51" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="51" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="51" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="51" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="51" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="51" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="51" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="51" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" s="52" t="s">
+        <v>2003</v>
+      </c>
+      <c r="B2" s="52" t="s">
+        <v>2004</v>
+      </c>
+      <c r="C2" s="52" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="55" t="s">
+        <v>2005</v>
+      </c>
+      <c r="E2" s="52" t="s">
+        <v>2006</v>
+      </c>
+      <c r="F2" s="52" t="s">
+        <v>2007</v>
+      </c>
+      <c r="G2" s="52" t="s">
+        <v>2008</v>
+      </c>
+      <c r="H2" s="52" t="s">
+        <v>69</v>
+      </c>
+      <c r="I2" s="52" t="s">
+        <v>2009</v>
+      </c>
+      <c r="J2" s="52" t="s">
+        <v>2010</v>
+      </c>
+      <c r="K2" s="52" t="s">
+        <v>2011</v>
+      </c>
+      <c r="L2" s="52" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M2" s="52"/>
+      <c r="N2" s="52" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="52" t="s">
+        <v>2012</v>
+      </c>
+      <c r="B3" s="52" t="s">
+        <v>2013</v>
+      </c>
+      <c r="C3" s="52" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="52" t="s">
+        <v>2014</v>
+      </c>
+      <c r="E3" s="52" t="s">
+        <v>2015</v>
+      </c>
+      <c r="F3" s="52" t="s">
+        <v>2016</v>
+      </c>
+      <c r="G3" s="52" t="s">
+        <v>2017</v>
+      </c>
+      <c r="H3" s="52" t="s">
+        <v>69</v>
+      </c>
+      <c r="I3" s="53" t="s">
+        <v>2018</v>
+      </c>
+      <c r="J3" s="53" t="s">
+        <v>2019</v>
+      </c>
+      <c r="K3" s="52" t="s">
+        <v>2011</v>
+      </c>
+      <c r="L3" s="52" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M3" s="52" t="s">
+        <v>2014</v>
+      </c>
+      <c r="N3" s="52" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="52" t="s">
+        <v>2020</v>
+      </c>
+      <c r="B4" s="52" t="s">
+        <v>2021</v>
+      </c>
+      <c r="C4" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="55" t="s">
+        <v>65</v>
+      </c>
+      <c r="E4" s="52" t="s">
+        <v>2022</v>
+      </c>
+      <c r="F4" s="52" t="s">
+        <v>2023</v>
+      </c>
+      <c r="G4" s="52" t="s">
+        <v>2024</v>
+      </c>
+      <c r="H4" s="52" t="s">
+        <v>69</v>
+      </c>
+      <c r="I4" s="57" t="s">
+        <v>2025</v>
+      </c>
+      <c r="J4" s="57" t="s">
+        <v>2026</v>
+      </c>
+      <c r="K4" s="52" t="s">
+        <v>2011</v>
+      </c>
+      <c r="L4" s="52" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M4" s="52" t="s">
+        <v>2027</v>
+      </c>
+      <c r="N4" s="52" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="52" t="s">
+        <v>2028</v>
+      </c>
+      <c r="B5" s="52" t="s">
+        <v>2029</v>
+      </c>
+      <c r="C5" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="52" t="s">
+        <v>2030</v>
+      </c>
+      <c r="E5" s="59" t="s">
+        <v>2031</v>
+      </c>
+      <c r="F5" s="52" t="s">
+        <v>1858</v>
+      </c>
+      <c r="G5" s="52" t="s">
+        <v>2032</v>
+      </c>
+      <c r="H5" s="52" t="s">
+        <v>69</v>
+      </c>
+      <c r="I5" s="57" t="s">
+        <v>2033</v>
+      </c>
+      <c r="J5" s="57" t="s">
+        <v>2034</v>
+      </c>
+      <c r="K5" s="52" t="s">
+        <v>1918</v>
+      </c>
+      <c r="L5" s="52" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M5" s="52" t="s">
+        <v>2030</v>
+      </c>
+      <c r="N5" s="52" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="52" t="s">
+        <v>2035</v>
+      </c>
+      <c r="B6" s="52" t="s">
+        <v>2036</v>
+      </c>
+      <c r="C6" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="52" t="s">
+        <v>2037</v>
+      </c>
+      <c r="E6" s="52" t="s">
+        <v>2038</v>
+      </c>
+      <c r="F6" s="52" t="s">
+        <v>2039</v>
+      </c>
+      <c r="G6" s="52" t="s">
+        <v>2040</v>
+      </c>
+      <c r="H6" s="52" t="s">
+        <v>69</v>
+      </c>
+      <c r="I6" s="57" t="s">
+        <v>2041</v>
+      </c>
+      <c r="J6" s="57" t="s">
+        <v>2042</v>
+      </c>
+      <c r="K6" s="52" t="s">
+        <v>2043</v>
+      </c>
+      <c r="L6" s="52" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M6" s="52" t="s">
+        <v>2044</v>
+      </c>
+      <c r="N6" s="52" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="52" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B7" s="52" t="s">
+        <v>2046</v>
+      </c>
+      <c r="C7" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="52" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E7" s="52" t="s">
+        <v>2048</v>
+      </c>
+      <c r="F7" s="52" t="s">
+        <v>1696</v>
+      </c>
+      <c r="G7" s="52" t="s">
+        <v>2049</v>
+      </c>
+      <c r="H7" s="52" t="s">
+        <v>69</v>
+      </c>
+      <c r="I7" s="52" t="s">
+        <v>2050</v>
+      </c>
+      <c r="J7" s="52" t="s">
+        <v>2051</v>
+      </c>
+      <c r="K7" s="52" t="s">
+        <v>2052</v>
+      </c>
+      <c r="L7" s="52" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M7" s="52" t="s">
+        <v>2047</v>
+      </c>
+      <c r="N7" s="52" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="52" t="s">
+        <v>2053</v>
+      </c>
+      <c r="B8" s="52" t="s">
+        <v>2054</v>
+      </c>
+      <c r="C8" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="52" t="s">
+        <v>1947</v>
+      </c>
+      <c r="E8" s="52" t="s">
+        <v>2055</v>
+      </c>
+      <c r="F8" s="52" t="s">
+        <v>2056</v>
+      </c>
+      <c r="G8" s="52" t="s">
+        <v>2057</v>
+      </c>
+      <c r="H8" s="52" t="s">
+        <v>69</v>
+      </c>
+      <c r="I8" s="52" t="s">
+        <v>2058</v>
+      </c>
+      <c r="J8" s="57" t="s">
+        <v>2059</v>
+      </c>
+      <c r="K8" s="52" t="s">
+        <v>2052</v>
+      </c>
+      <c r="L8" s="52" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M8" s="52" t="s">
+        <v>2060</v>
+      </c>
+      <c r="N8" s="52" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="52" t="s">
+        <v>2061</v>
+      </c>
+      <c r="B9" s="52" t="s">
+        <v>2062</v>
+      </c>
+      <c r="C9" s="52" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="52" t="s">
+        <v>1947</v>
+      </c>
+      <c r="E9" s="52" t="s">
+        <v>2063</v>
+      </c>
+      <c r="F9" s="52" t="s">
+        <v>2064</v>
+      </c>
+      <c r="G9" s="52" t="s">
+        <v>2065</v>
+      </c>
+      <c r="H9" s="52" t="s">
+        <v>69</v>
+      </c>
+      <c r="I9" s="57" t="s">
+        <v>2066</v>
+      </c>
+      <c r="J9" s="57" t="s">
+        <v>2067</v>
+      </c>
+      <c r="K9" s="52" t="s">
+        <v>2052</v>
+      </c>
+      <c r="L9" s="52" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M9" s="52" t="s">
+        <v>1947</v>
+      </c>
+      <c r="N9" s="52" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="52" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B10" s="52" t="s">
+        <v>2069</v>
+      </c>
+      <c r="C10" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="52" t="s">
+        <v>2070</v>
+      </c>
+      <c r="E10" s="52" t="s">
+        <v>2070</v>
+      </c>
+      <c r="F10" s="52" t="s">
+        <v>1981</v>
+      </c>
+      <c r="G10" s="52" t="s">
+        <v>2071</v>
+      </c>
+      <c r="H10" s="52" t="s">
+        <v>69</v>
+      </c>
+      <c r="I10" s="52" t="s">
+        <v>2072</v>
+      </c>
+      <c r="J10" s="52" t="s">
+        <v>2073</v>
+      </c>
+      <c r="K10" s="52" t="s">
+        <v>2074</v>
+      </c>
+      <c r="L10" s="52" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M10" s="52" t="s">
+        <v>1856</v>
+      </c>
+      <c r="N10" s="52" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="52" t="s">
+        <v>2075</v>
+      </c>
+      <c r="B11" s="52" t="s">
+        <v>2076</v>
+      </c>
+      <c r="C11" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="52" t="s">
+        <v>1856</v>
+      </c>
+      <c r="E11" s="52" t="s">
+        <v>2077</v>
+      </c>
+      <c r="F11" s="52" t="s">
+        <v>945</v>
+      </c>
+      <c r="G11" s="52" t="s">
+        <v>2078</v>
+      </c>
+      <c r="H11" s="52" t="s">
+        <v>69</v>
+      </c>
+      <c r="I11" s="52" t="s">
+        <v>2079</v>
+      </c>
+      <c r="J11" s="52" t="s">
+        <v>2080</v>
+      </c>
+      <c r="K11" s="52" t="s">
+        <v>2081</v>
+      </c>
+      <c r="L11" s="52" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M11" s="52" t="s">
+        <v>1856</v>
+      </c>
+      <c r="N11" s="52" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="52" t="s">
+        <v>2082</v>
+      </c>
+      <c r="B12" s="52" t="s">
+        <v>2083</v>
+      </c>
+      <c r="C12" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="52" t="s">
+        <v>1856</v>
+      </c>
+      <c r="E12" s="52" t="s">
+        <v>2084</v>
+      </c>
+      <c r="F12" s="52" t="s">
+        <v>2085</v>
+      </c>
+      <c r="G12" s="52" t="s">
+        <v>2086</v>
+      </c>
+      <c r="H12" s="52" t="s">
+        <v>69</v>
+      </c>
+      <c r="I12" s="52" t="s">
+        <v>2087</v>
+      </c>
+      <c r="J12" s="52" t="s">
+        <v>2088</v>
+      </c>
+      <c r="K12" s="52" t="s">
+        <v>2074</v>
+      </c>
+      <c r="L12" s="52" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M12" s="52" t="s">
+        <v>1856</v>
+      </c>
+      <c r="N12" s="52" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="13.5" customHeight="1">
+      <c r="A13" s="52" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B13" s="52" t="s">
+        <v>2090</v>
+      </c>
+      <c r="C13" s="52" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="52" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E13" s="52" t="s">
+        <v>2092</v>
+      </c>
+      <c r="F13" s="52" t="s">
+        <v>2007</v>
+      </c>
+      <c r="G13" s="52" t="s">
+        <v>2093</v>
+      </c>
+      <c r="H13" s="52" t="s">
+        <v>69</v>
+      </c>
+      <c r="I13" s="54" t="s">
+        <v>2094</v>
+      </c>
+      <c r="J13" s="54" t="s">
+        <v>2095</v>
+      </c>
+      <c r="K13" s="52" t="s">
+        <v>2096</v>
+      </c>
+      <c r="L13" s="52" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M13" s="52" t="s">
+        <v>2091</v>
+      </c>
+      <c r="N13" s="52" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="15" customHeight="1">
+      <c r="A14" s="52" t="s">
+        <v>2097</v>
+      </c>
+      <c r="B14" s="56" t="s">
+        <v>2098</v>
+      </c>
+      <c r="C14" s="52" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="52" t="s">
+        <v>2099</v>
+      </c>
+      <c r="E14" s="52">
+        <v>824012823</v>
+      </c>
+      <c r="F14" s="52" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G14" s="52" t="s">
+        <v>2101</v>
+      </c>
+      <c r="H14" s="52" t="s">
+        <v>2102</v>
+      </c>
+      <c r="I14" s="57" t="s">
+        <v>2103</v>
+      </c>
+      <c r="J14" s="57" t="s">
+        <v>2104</v>
+      </c>
+      <c r="K14" s="52">
+        <v>824012823</v>
+      </c>
+      <c r="L14" s="52" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M14" s="52" t="s">
+        <v>2105</v>
+      </c>
+      <c r="N14" s="52" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="52" t="s">
+        <v>2106</v>
+      </c>
+      <c r="B15" s="52" t="s">
+        <v>2107</v>
+      </c>
+      <c r="C15" s="52" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" s="52" t="s">
+        <v>1856</v>
+      </c>
+      <c r="E15" s="52" t="s">
+        <v>2108</v>
+      </c>
+      <c r="F15" s="52" t="s">
+        <v>2085</v>
+      </c>
+      <c r="G15" s="52" t="s">
+        <v>2109</v>
+      </c>
+      <c r="H15" s="52" t="s">
+        <v>69</v>
+      </c>
+      <c r="I15" s="54" t="s">
+        <v>2110</v>
+      </c>
+      <c r="J15" s="54" t="s">
+        <v>2111</v>
+      </c>
+      <c r="K15" s="52" t="s">
+        <v>1943</v>
+      </c>
+      <c r="L15" s="52" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M15" s="52" t="s">
+        <v>1856</v>
+      </c>
+      <c r="N15" s="52" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="52" t="s">
+        <v>2112</v>
+      </c>
+      <c r="B16" s="52" t="s">
+        <v>2113</v>
+      </c>
+      <c r="C16" s="52" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" s="52" t="s">
+        <v>1856</v>
+      </c>
+      <c r="E16" s="52" t="s">
+        <v>2114</v>
+      </c>
+      <c r="F16" s="52" t="s">
+        <v>2023</v>
+      </c>
+      <c r="G16" s="52" t="s">
+        <v>2115</v>
+      </c>
+      <c r="H16" s="52" t="s">
+        <v>69</v>
+      </c>
+      <c r="I16" s="54" t="s">
+        <v>2116</v>
+      </c>
+      <c r="J16" s="54" t="s">
+        <v>2116</v>
+      </c>
+      <c r="K16" s="52" t="s">
+        <v>2117</v>
+      </c>
+      <c r="L16" s="52" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M16" s="52" t="s">
+        <v>1856</v>
+      </c>
+      <c r="N16" s="52" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" s="52" t="s">
+        <v>2118</v>
+      </c>
+      <c r="B17" s="52" t="s">
+        <v>2119</v>
+      </c>
+      <c r="C17" s="52" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="52" t="s">
+        <v>2120</v>
+      </c>
+      <c r="E17" s="52" t="s">
+        <v>2121</v>
+      </c>
+      <c r="F17" s="52" t="s">
+        <v>1877</v>
+      </c>
+      <c r="G17" s="52" t="s">
+        <v>2122</v>
+      </c>
+      <c r="H17" s="52" t="s">
+        <v>69</v>
+      </c>
+      <c r="I17" s="54" t="s">
+        <v>2123</v>
+      </c>
+      <c r="J17" s="54" t="s">
+        <v>2124</v>
+      </c>
+      <c r="K17" s="52" t="s">
+        <v>2125</v>
+      </c>
+      <c r="L17" s="52" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M17" s="52" t="s">
+        <v>2120</v>
+      </c>
+      <c r="N17" s="52" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" s="52" t="s">
+        <v>2126</v>
+      </c>
+      <c r="B18" s="52" t="s">
+        <v>2127</v>
+      </c>
+      <c r="C18" s="52" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" s="52" t="s">
+        <v>1856</v>
+      </c>
+      <c r="E18" s="52" t="s">
+        <v>2128</v>
+      </c>
+      <c r="F18" s="58" t="s">
+        <v>2129</v>
+      </c>
+      <c r="G18" s="58" t="s">
+        <v>2130</v>
+      </c>
+      <c r="H18" s="52" t="s">
+        <v>69</v>
+      </c>
+      <c r="I18" s="58" t="s">
+        <v>2131</v>
+      </c>
+      <c r="J18" s="58" t="s">
+        <v>2132</v>
+      </c>
+      <c r="K18" s="52" t="s">
+        <v>1943</v>
+      </c>
+      <c r="L18" s="52" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M18" s="52" t="s">
+        <v>1856</v>
+      </c>
+      <c r="N18" s="52" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" s="52" t="s">
+        <v>2133</v>
+      </c>
+      <c r="B19" s="50" t="s">
+        <v>2134</v>
+      </c>
+      <c r="C19" s="52" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="50" t="s">
+        <v>2135</v>
+      </c>
+      <c r="E19" s="50" t="s">
+        <v>2136</v>
+      </c>
+      <c r="F19" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="G19" s="50" t="s">
+        <v>2137</v>
+      </c>
+      <c r="H19" s="52" t="s">
+        <v>69</v>
+      </c>
+      <c r="I19" s="50" t="s">
+        <v>2138</v>
+      </c>
+      <c r="J19" s="50" t="s">
+        <v>2139</v>
+      </c>
+      <c r="K19" s="52" t="s">
+        <v>2136</v>
+      </c>
+      <c r="L19" s="52" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M19" s="52" t="s">
+        <v>2136</v>
+      </c>
+      <c r="N19" s="52" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" s="52" t="s">
+        <v>2140</v>
+      </c>
+      <c r="B20" s="50" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C20" s="52" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="50" t="s">
+        <v>2142</v>
+      </c>
+      <c r="E20" s="50" t="s">
+        <v>2143</v>
+      </c>
+      <c r="F20" s="50" t="s">
+        <v>1658</v>
+      </c>
+      <c r="G20" s="50" t="s">
+        <v>2144</v>
+      </c>
+      <c r="H20" s="52" t="s">
+        <v>69</v>
+      </c>
+      <c r="I20" s="50" t="s">
+        <v>2145</v>
+      </c>
+      <c r="J20" s="50" t="s">
+        <v>2146</v>
+      </c>
+      <c r="K20" s="50" t="s">
+        <v>2143</v>
+      </c>
+      <c r="L20" s="52" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M20" s="50" t="s">
+        <v>2147</v>
+      </c>
+      <c r="N20" s="52" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" s="59" t="s">
+        <v>2148</v>
+      </c>
+      <c r="B21" s="50" t="s">
+        <v>2149</v>
+      </c>
+      <c r="C21" s="52" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" s="50" t="s">
+        <v>1856</v>
+      </c>
+      <c r="E21" s="50" t="s">
+        <v>2150</v>
+      </c>
+      <c r="F21" s="50" t="s">
+        <v>1858</v>
+      </c>
+      <c r="G21" s="50" t="s">
+        <v>2151</v>
+      </c>
+      <c r="H21" s="59" t="s">
+        <v>69</v>
+      </c>
+      <c r="I21" s="61" t="s">
+        <v>2152</v>
+      </c>
+      <c r="J21" s="50" t="s">
+        <v>2153</v>
+      </c>
+      <c r="K21" s="60" t="s">
+        <v>2154</v>
+      </c>
+      <c r="L21" s="52" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M21" s="52" t="s">
+        <v>1856</v>
+      </c>
+      <c r="N21" s="52" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" s="59" t="s">
+        <v>2155</v>
+      </c>
+      <c r="B22" s="50" t="s">
+        <v>2156</v>
+      </c>
+      <c r="C22" s="52" t="s">
+        <v>16</v>
+      </c>
+      <c r="D22" s="52" t="s">
+        <v>2157</v>
+      </c>
+      <c r="E22" s="50" t="s">
+        <v>2158</v>
+      </c>
+      <c r="F22" s="50" t="s">
+        <v>1696</v>
+      </c>
+      <c r="G22" s="50" t="s">
+        <v>2159</v>
+      </c>
+      <c r="H22" s="59" t="s">
+        <v>69</v>
+      </c>
+      <c r="I22" s="50" t="s">
+        <v>2160</v>
+      </c>
+      <c r="J22" s="50" t="s">
+        <v>2161</v>
+      </c>
+      <c r="K22" s="50" t="s">
+        <v>2052</v>
+      </c>
+      <c r="L22" s="52" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M22" s="52" t="s">
+        <v>1904</v>
+      </c>
+      <c r="N22" s="52" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" s="59" t="s">
+        <v>2162</v>
+      </c>
+      <c r="B23" s="50" t="s">
+        <v>2163</v>
+      </c>
+      <c r="C23" s="52" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="52" t="s">
+        <v>1947</v>
+      </c>
+      <c r="E23" s="50" t="s">
+        <v>2164</v>
+      </c>
+      <c r="F23" s="50" t="s">
+        <v>1696</v>
+      </c>
+      <c r="G23" s="50" t="s">
+        <v>2165</v>
+      </c>
+      <c r="H23" s="59" t="s">
+        <v>69</v>
+      </c>
+      <c r="I23" s="50" t="s">
+        <v>2166</v>
+      </c>
+      <c r="J23" s="61" t="s">
+        <v>2167</v>
+      </c>
+      <c r="K23" s="52" t="s">
+        <v>2052</v>
+      </c>
+      <c r="L23" s="52" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M23" s="52" t="s">
+        <v>2060</v>
+      </c>
+      <c r="N23" s="52" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="I3" r:id="rId1" xr:uid="{00000000-0004-0000-0A00-000000000000}"/>
+    <hyperlink ref="J3" r:id="rId2" xr:uid="{00000000-0004-0000-0A00-000001000000}"/>
+    <hyperlink ref="I4" r:id="rId3" xr:uid="{00000000-0004-0000-0A00-000002000000}"/>
+    <hyperlink ref="J4" r:id="rId4" xr:uid="{00000000-0004-0000-0A00-000003000000}"/>
+    <hyperlink ref="I5" r:id="rId5" xr:uid="{00000000-0004-0000-0A00-000004000000}"/>
+    <hyperlink ref="J5" r:id="rId6" xr:uid="{00000000-0004-0000-0A00-000005000000}"/>
+    <hyperlink ref="I6" r:id="rId7" xr:uid="{00000000-0004-0000-0A00-000006000000}"/>
+    <hyperlink ref="J6" r:id="rId8" xr:uid="{00000000-0004-0000-0A00-000007000000}"/>
+    <hyperlink ref="J8" r:id="rId9" xr:uid="{00000000-0004-0000-0A00-000008000000}"/>
+    <hyperlink ref="I9" r:id="rId10" xr:uid="{00000000-0004-0000-0A00-000009000000}"/>
+    <hyperlink ref="J9" r:id="rId11" xr:uid="{00000000-0004-0000-0A00-00000A000000}"/>
+    <hyperlink ref="I13" r:id="rId12" xr:uid="{00000000-0004-0000-0A00-00000B000000}"/>
+    <hyperlink ref="J13" r:id="rId13" xr:uid="{00000000-0004-0000-0A00-00000C000000}"/>
+    <hyperlink ref="I14" r:id="rId14" xr:uid="{00000000-0004-0000-0A00-00000D000000}"/>
+    <hyperlink ref="J14" r:id="rId15" xr:uid="{00000000-0004-0000-0A00-00000E000000}"/>
+    <hyperlink ref="I15" r:id="rId16" xr:uid="{00000000-0004-0000-0A00-00000F000000}"/>
+    <hyperlink ref="J15" r:id="rId17" xr:uid="{00000000-0004-0000-0A00-000010000000}"/>
+    <hyperlink ref="I16" r:id="rId18" xr:uid="{00000000-0004-0000-0A00-000011000000}"/>
+    <hyperlink ref="J16" r:id="rId19" xr:uid="{00000000-0004-0000-0A00-000012000000}"/>
+    <hyperlink ref="I17" r:id="rId20" xr:uid="{00000000-0004-0000-0A00-000013000000}"/>
+    <hyperlink ref="J17" r:id="rId21" xr:uid="{00000000-0004-0000-0A00-000014000000}"/>
+    <hyperlink ref="I21" r:id="rId22" xr:uid="{E5D95628-DADF-425D-8DC6-0740E7A281C6}"/>
+    <hyperlink ref="J23" r:id="rId23" xr:uid="{21B09737-BF9A-463D-87B2-ED444DC9196C}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B6F0D32-9CE2-4DF7-927E-42E7BA331F12}">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="13" max="13" width="13.36328125" customWidth="1"/>
     <col min="14" max="14" width="16.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -16086,7 +19800,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -16130,15 +19844,879 @@
         <v>25</v>
       </c>
     </row>
+    <row r="3" spans="1:15">
+      <c r="A3" t="s">
+        <v>1813</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>1693</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D3" s="26">
+        <v>1206</v>
+      </c>
+      <c r="E3" s="23" t="s">
+        <v>1695</v>
+      </c>
+      <c r="F3" s="23" t="s">
+        <v>1696</v>
+      </c>
+      <c r="G3" s="23" t="s">
+        <v>1697</v>
+      </c>
+      <c r="H3" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="I3" s="23" t="s">
+        <v>1698</v>
+      </c>
+      <c r="J3" s="23" t="s">
+        <v>1699</v>
+      </c>
+      <c r="K3" s="23" t="s">
+        <v>1700</v>
+      </c>
+      <c r="L3" t="s">
+        <v>55</v>
+      </c>
+      <c r="M3" s="23" t="s">
+        <v>1701</v>
+      </c>
+      <c r="N3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O3" s="23"/>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" t="s">
+        <v>1814</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>1702</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>1703</v>
+      </c>
+      <c r="D4" s="23" t="s">
+        <v>1704</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>1705</v>
+      </c>
+      <c r="F4" s="23" t="s">
+        <v>1696</v>
+      </c>
+      <c r="G4" s="23" t="s">
+        <v>1706</v>
+      </c>
+      <c r="H4" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="I4" s="23" t="s">
+        <v>1707</v>
+      </c>
+      <c r="J4" s="23" t="s">
+        <v>1708</v>
+      </c>
+      <c r="K4" s="23" t="s">
+        <v>1700</v>
+      </c>
+      <c r="L4" t="s">
+        <v>55</v>
+      </c>
+      <c r="M4" s="23" t="s">
+        <v>1709</v>
+      </c>
+      <c r="N4" t="s">
+        <v>25</v>
+      </c>
+      <c r="O4" s="23"/>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" t="s">
+        <v>1815</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>1710</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>1711</v>
+      </c>
+      <c r="D5" s="23">
+        <v>1206</v>
+      </c>
+      <c r="E5" s="23" t="s">
+        <v>1712</v>
+      </c>
+      <c r="F5" s="23" t="s">
+        <v>1691</v>
+      </c>
+      <c r="G5" s="23" t="s">
+        <v>1712</v>
+      </c>
+      <c r="H5" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="I5" s="24" t="s">
+        <v>1713</v>
+      </c>
+      <c r="J5" s="24" t="s">
+        <v>1714</v>
+      </c>
+      <c r="K5" s="23" t="s">
+        <v>1700</v>
+      </c>
+      <c r="L5" t="s">
+        <v>55</v>
+      </c>
+      <c r="M5" s="23" t="s">
+        <v>1701</v>
+      </c>
+      <c r="N5" t="s">
+        <v>25</v>
+      </c>
+      <c r="O5" s="22"/>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" t="s">
+        <v>1816</v>
+      </c>
+      <c r="B6" s="23" t="s">
+        <v>1715</v>
+      </c>
+      <c r="C6" s="23" t="s">
+        <v>1716</v>
+      </c>
+      <c r="D6" s="23">
+        <v>1206</v>
+      </c>
+      <c r="E6" s="23" t="s">
+        <v>1717</v>
+      </c>
+      <c r="F6" s="23" t="s">
+        <v>1718</v>
+      </c>
+      <c r="G6" s="23" t="s">
+        <v>1717</v>
+      </c>
+      <c r="H6" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="I6" s="24" t="s">
+        <v>1719</v>
+      </c>
+      <c r="J6" s="24" t="s">
+        <v>1720</v>
+      </c>
+      <c r="K6" s="23" t="s">
+        <v>1700</v>
+      </c>
+      <c r="L6" t="s">
+        <v>55</v>
+      </c>
+      <c r="M6" s="23" t="s">
+        <v>1701</v>
+      </c>
+      <c r="N6" t="s">
+        <v>25</v>
+      </c>
+      <c r="O6" s="22"/>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" t="s">
+        <v>1817</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>1721</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>1692</v>
+      </c>
+      <c r="D7" s="23" t="s">
+        <v>1722</v>
+      </c>
+      <c r="E7" s="25" t="s">
+        <v>1723</v>
+      </c>
+      <c r="F7" s="25" t="s">
+        <v>1696</v>
+      </c>
+      <c r="G7" s="25" t="s">
+        <v>1724</v>
+      </c>
+      <c r="H7" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="I7" s="25" t="s">
+        <v>1725</v>
+      </c>
+      <c r="J7" s="25" t="s">
+        <v>1726</v>
+      </c>
+      <c r="K7" s="23" t="s">
+        <v>1700</v>
+      </c>
+      <c r="L7" t="s">
+        <v>55</v>
+      </c>
+      <c r="M7" s="25" t="s">
+        <v>1727</v>
+      </c>
+      <c r="N7" t="s">
+        <v>25</v>
+      </c>
+      <c r="O7" s="22"/>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" t="s">
+        <v>1818</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>1728</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>1703</v>
+      </c>
+      <c r="D8" s="23">
+        <v>1206</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>1729</v>
+      </c>
+      <c r="F8" s="25" t="s">
+        <v>1730</v>
+      </c>
+      <c r="G8" s="25" t="s">
+        <v>1731</v>
+      </c>
+      <c r="H8" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="I8" s="25" t="s">
+        <v>1732</v>
+      </c>
+      <c r="J8" s="25" t="s">
+        <v>1733</v>
+      </c>
+      <c r="K8" s="23" t="s">
+        <v>1700</v>
+      </c>
+      <c r="L8" t="s">
+        <v>55</v>
+      </c>
+      <c r="M8" s="23" t="s">
+        <v>1701</v>
+      </c>
+      <c r="N8" t="s">
+        <v>25</v>
+      </c>
+      <c r="O8" s="22"/>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" t="s">
+        <v>1819</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>1734</v>
+      </c>
+      <c r="C9" s="23" t="s">
+        <v>1711</v>
+      </c>
+      <c r="D9" s="23">
+        <v>1206</v>
+      </c>
+      <c r="E9" s="25" t="s">
+        <v>1735</v>
+      </c>
+      <c r="F9" s="25" t="s">
+        <v>1730</v>
+      </c>
+      <c r="G9" s="25" t="s">
+        <v>1736</v>
+      </c>
+      <c r="H9" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="I9" s="25" t="s">
+        <v>1737</v>
+      </c>
+      <c r="J9" s="25" t="s">
+        <v>1738</v>
+      </c>
+      <c r="K9" s="23" t="s">
+        <v>1700</v>
+      </c>
+      <c r="L9" t="s">
+        <v>55</v>
+      </c>
+      <c r="M9" s="23" t="s">
+        <v>1701</v>
+      </c>
+      <c r="N9" t="s">
+        <v>25</v>
+      </c>
+      <c r="O9" s="22"/>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" t="s">
+        <v>1820</v>
+      </c>
+      <c r="B10" s="25" t="s">
+        <v>1739</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>1740</v>
+      </c>
+      <c r="D10" s="23">
+        <v>1812</v>
+      </c>
+      <c r="E10" s="25" t="s">
+        <v>1741</v>
+      </c>
+      <c r="F10" s="25" t="s">
+        <v>1742</v>
+      </c>
+      <c r="G10" s="25" t="s">
+        <v>1743</v>
+      </c>
+      <c r="H10" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="I10" s="24" t="s">
+        <v>1744</v>
+      </c>
+      <c r="J10" s="24" t="s">
+        <v>1745</v>
+      </c>
+      <c r="K10" s="23" t="s">
+        <v>1700</v>
+      </c>
+      <c r="L10" t="s">
+        <v>55</v>
+      </c>
+      <c r="M10" s="23" t="s">
+        <v>1746</v>
+      </c>
+      <c r="N10" t="s">
+        <v>25</v>
+      </c>
+      <c r="O10" s="22"/>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" t="s">
+        <v>1821</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>1747</v>
+      </c>
+      <c r="C11" s="23" t="s">
+        <v>1748</v>
+      </c>
+      <c r="D11" s="23">
+        <v>1812</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>1749</v>
+      </c>
+      <c r="F11" s="22" t="s">
+        <v>1742</v>
+      </c>
+      <c r="G11" s="22" t="s">
+        <v>1750</v>
+      </c>
+      <c r="H11" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="I11" s="22" t="s">
+        <v>1751</v>
+      </c>
+      <c r="J11" s="22" t="s">
+        <v>1752</v>
+      </c>
+      <c r="K11" s="23" t="s">
+        <v>1700</v>
+      </c>
+      <c r="L11" t="s">
+        <v>55</v>
+      </c>
+      <c r="M11" s="23" t="s">
+        <v>1746</v>
+      </c>
+      <c r="N11" t="s">
+        <v>25</v>
+      </c>
+      <c r="O11" s="22"/>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" t="s">
+        <v>1822</v>
+      </c>
+      <c r="B12" s="22" t="s">
+        <v>1753</v>
+      </c>
+      <c r="C12" s="23" t="s">
+        <v>1754</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>1755</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>1756</v>
+      </c>
+      <c r="F12" s="28" t="s">
+        <v>1757</v>
+      </c>
+      <c r="G12" s="28" t="s">
+        <v>1758</v>
+      </c>
+      <c r="H12" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="I12" s="29" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J12" s="29" t="s">
+        <v>1760</v>
+      </c>
+      <c r="K12" s="28" t="s">
+        <v>1700</v>
+      </c>
+      <c r="L12" t="s">
+        <v>55</v>
+      </c>
+      <c r="M12" s="28" t="s">
+        <v>1761</v>
+      </c>
+      <c r="N12" t="s">
+        <v>25</v>
+      </c>
+      <c r="O12" s="22"/>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" t="s">
+        <v>1823</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>1762</v>
+      </c>
+      <c r="C13" s="23" t="s">
+        <v>1763</v>
+      </c>
+      <c r="D13" s="22">
+        <v>1812</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>1764</v>
+      </c>
+      <c r="F13" s="28" t="s">
+        <v>1742</v>
+      </c>
+      <c r="G13" s="28" t="s">
+        <v>1765</v>
+      </c>
+      <c r="H13" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="I13" s="29" t="s">
+        <v>1766</v>
+      </c>
+      <c r="J13" s="29" t="s">
+        <v>1767</v>
+      </c>
+      <c r="K13" s="28" t="s">
+        <v>1700</v>
+      </c>
+      <c r="L13" t="s">
+        <v>55</v>
+      </c>
+      <c r="M13" s="23" t="s">
+        <v>1746</v>
+      </c>
+      <c r="N13" t="s">
+        <v>25</v>
+      </c>
+      <c r="O13" s="22"/>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" t="s">
+        <v>1824</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>1768</v>
+      </c>
+      <c r="C14" s="23" t="s">
+        <v>1763</v>
+      </c>
+      <c r="D14" s="23">
+        <v>1206</v>
+      </c>
+      <c r="E14" s="23" t="s">
+        <v>1769</v>
+      </c>
+      <c r="F14" s="28" t="s">
+        <v>1742</v>
+      </c>
+      <c r="G14" s="22" t="s">
+        <v>1770</v>
+      </c>
+      <c r="H14" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="I14" s="22" t="s">
+        <v>1771</v>
+      </c>
+      <c r="J14" s="29" t="s">
+        <v>1772</v>
+      </c>
+      <c r="K14" s="28" t="s">
+        <v>1700</v>
+      </c>
+      <c r="L14" t="s">
+        <v>55</v>
+      </c>
+      <c r="M14" s="23" t="s">
+        <v>1701</v>
+      </c>
+      <c r="N14" t="s">
+        <v>25</v>
+      </c>
+      <c r="O14" s="22"/>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15" t="s">
+        <v>1825</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>1773</v>
+      </c>
+      <c r="C15" s="23" t="s">
+        <v>1774</v>
+      </c>
+      <c r="D15" s="23">
+        <v>1206</v>
+      </c>
+      <c r="E15" s="23" t="s">
+        <v>1775</v>
+      </c>
+      <c r="F15" s="22" t="s">
+        <v>1776</v>
+      </c>
+      <c r="G15" s="22" t="s">
+        <v>1777</v>
+      </c>
+      <c r="H15" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="I15" s="22" t="s">
+        <v>1778</v>
+      </c>
+      <c r="J15" s="22" t="s">
+        <v>1779</v>
+      </c>
+      <c r="K15" s="28" t="s">
+        <v>1700</v>
+      </c>
+      <c r="L15" t="s">
+        <v>55</v>
+      </c>
+      <c r="M15" s="23" t="s">
+        <v>1701</v>
+      </c>
+      <c r="N15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>1780</v>
+      </c>
+      <c r="C16" s="27" t="s">
+        <v>1774</v>
+      </c>
+      <c r="D16" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="E16" s="27" t="s">
+        <v>1781</v>
+      </c>
+      <c r="F16" s="27" t="s">
+        <v>1696</v>
+      </c>
+      <c r="G16" s="27" t="s">
+        <v>1782</v>
+      </c>
+      <c r="H16" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="I16" s="22" t="s">
+        <v>1783</v>
+      </c>
+      <c r="J16" s="22" t="s">
+        <v>1784</v>
+      </c>
+      <c r="K16" s="28" t="s">
+        <v>1700</v>
+      </c>
+      <c r="L16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M16" s="27" t="s">
+        <v>1785</v>
+      </c>
+      <c r="N16" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" t="s">
+        <v>1827</v>
+      </c>
+      <c r="B17" s="22" t="s">
+        <v>1786</v>
+      </c>
+      <c r="C17" s="27" t="s">
+        <v>1763</v>
+      </c>
+      <c r="D17" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="E17" s="27" t="s">
+        <v>1787</v>
+      </c>
+      <c r="F17" s="27" t="s">
+        <v>1696</v>
+      </c>
+      <c r="G17" s="27" t="s">
+        <v>1788</v>
+      </c>
+      <c r="H17" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="I17" s="22" t="s">
+        <v>1789</v>
+      </c>
+      <c r="J17" s="22" t="s">
+        <v>1783</v>
+      </c>
+      <c r="K17" s="28" t="s">
+        <v>1700</v>
+      </c>
+      <c r="L17" t="s">
+        <v>55</v>
+      </c>
+      <c r="M17" s="27" t="s">
+        <v>1785</v>
+      </c>
+      <c r="N17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" t="s">
+        <v>1828</v>
+      </c>
+      <c r="B18" s="22" t="s">
+        <v>1790</v>
+      </c>
+      <c r="C18" s="27" t="s">
+        <v>1791</v>
+      </c>
+      <c r="D18" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="E18" s="22" t="s">
+        <v>1792</v>
+      </c>
+      <c r="F18" s="22" t="s">
+        <v>1742</v>
+      </c>
+      <c r="G18" s="22" t="s">
+        <v>1793</v>
+      </c>
+      <c r="H18" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="I18" s="22" t="s">
+        <v>1794</v>
+      </c>
+      <c r="J18" s="22" t="s">
+        <v>1795</v>
+      </c>
+      <c r="K18" s="28" t="s">
+        <v>1700</v>
+      </c>
+      <c r="L18" t="s">
+        <v>55</v>
+      </c>
+      <c r="M18" s="27" t="s">
+        <v>1785</v>
+      </c>
+      <c r="N18" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B19" s="22" t="s">
+        <v>1796</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>1763</v>
+      </c>
+      <c r="D19" s="22">
+        <v>1812</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>1797</v>
+      </c>
+      <c r="F19" s="22" t="s">
+        <v>1742</v>
+      </c>
+      <c r="G19" s="22" t="s">
+        <v>1798</v>
+      </c>
+      <c r="H19" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="I19" s="29" t="s">
+        <v>1799</v>
+      </c>
+      <c r="J19" s="22" t="s">
+        <v>1800</v>
+      </c>
+      <c r="K19" s="28" t="s">
+        <v>1700</v>
+      </c>
+      <c r="L19" t="s">
+        <v>55</v>
+      </c>
+      <c r="M19" s="23" t="s">
+        <v>1746</v>
+      </c>
+      <c r="N19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" t="s">
+        <v>1830</v>
+      </c>
+      <c r="B20" s="22" t="s">
+        <v>1801</v>
+      </c>
+      <c r="C20" s="27" t="s">
+        <v>1692</v>
+      </c>
+      <c r="D20" s="30" t="s">
+        <v>1802</v>
+      </c>
+      <c r="E20" s="22" t="s">
+        <v>1803</v>
+      </c>
+      <c r="F20" s="22" t="s">
+        <v>1742</v>
+      </c>
+      <c r="G20" s="22" t="s">
+        <v>1804</v>
+      </c>
+      <c r="H20" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="I20" s="29" t="s">
+        <v>1805</v>
+      </c>
+      <c r="J20" s="29" t="s">
+        <v>1806</v>
+      </c>
+      <c r="K20" s="28" t="s">
+        <v>1700</v>
+      </c>
+      <c r="L20" t="s">
+        <v>55</v>
+      </c>
+      <c r="M20" s="22" t="s">
+        <v>1807</v>
+      </c>
+      <c r="N20" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" t="s">
+        <v>1831</v>
+      </c>
+      <c r="B21" s="22" t="s">
+        <v>1808</v>
+      </c>
+      <c r="C21" s="23" t="s">
+        <v>1703</v>
+      </c>
+      <c r="D21" s="23">
+        <v>1812</v>
+      </c>
+      <c r="E21" s="22" t="s">
+        <v>1809</v>
+      </c>
+      <c r="F21" s="22" t="s">
+        <v>1742</v>
+      </c>
+      <c r="G21" s="22" t="s">
+        <v>1810</v>
+      </c>
+      <c r="H21" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="I21" s="22" t="s">
+        <v>1811</v>
+      </c>
+      <c r="J21" s="29" t="s">
+        <v>1812</v>
+      </c>
+      <c r="K21" s="23" t="s">
+        <v>1700</v>
+      </c>
+      <c r="L21" t="s">
+        <v>55</v>
+      </c>
+      <c r="M21" s="23" t="s">
+        <v>1746</v>
+      </c>
+      <c r="N21" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="16" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1" xr:uid="{3DE7E9B7-7F71-48BD-A43F-56652EF48515}"/>
+    <hyperlink ref="I5" r:id="rId2" xr:uid="{00000000-0004-0000-0C00-000001000000}"/>
+    <hyperlink ref="J5" r:id="rId3" xr:uid="{00000000-0004-0000-0C00-000002000000}"/>
+    <hyperlink ref="I6" r:id="rId4" xr:uid="{00000000-0004-0000-0C00-000003000000}"/>
+    <hyperlink ref="J6" r:id="rId5" xr:uid="{00000000-0004-0000-0C00-000004000000}"/>
+    <hyperlink ref="I10" r:id="rId6" xr:uid="{00000000-0004-0000-0C00-000005000000}"/>
+    <hyperlink ref="J10" r:id="rId7" xr:uid="{00000000-0004-0000-0C00-000006000000}"/>
+    <hyperlink ref="I12" r:id="rId8" xr:uid="{DC4D0F7D-FABA-4F27-A8C4-C8F1159FEA34}"/>
+    <hyperlink ref="J12" r:id="rId9" xr:uid="{7C1A203F-2505-4DF3-8487-119DA9DE1A1B}"/>
+    <hyperlink ref="J13" r:id="rId10" xr:uid="{6F374EEE-953D-426D-AF07-D3E5C1F03D55}"/>
+    <hyperlink ref="I13" r:id="rId11" xr:uid="{959671DE-63B1-4C42-9AE2-A4D45EAFA482}"/>
+    <hyperlink ref="J14" r:id="rId12" xr:uid="{D0E41C99-5015-461D-998D-DD06CC299D2B}"/>
+    <hyperlink ref="I19" r:id="rId13" xr:uid="{EAFB85FD-4F43-4B6C-AEDE-D6E5C0E93BD1}"/>
+    <hyperlink ref="I20" r:id="rId14" xr:uid="{6C9DFF48-0956-4B25-8972-EC0656F1483E}"/>
+    <hyperlink ref="J20" r:id="rId15" xr:uid="{6EF40273-C6D8-4BC3-9EF6-1B4C76903848}"/>
+    <hyperlink ref="J21" r:id="rId16" xr:uid="{FFB17F08-401F-47B0-899B-612CD8B9FB6B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C98E1A12-072F-4773-8CB5-47FFE077E85B}">
   <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -16386,252 +20964,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59BC8B2E-A067-463D-937A-30E88D8BECD0}">
-  <dimension ref="A1:N1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
-  <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4BBBCF5-BAC9-459C-ABE9-2526B85FD81E}">
-  <dimension ref="A1:N4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
-  <cols>
-    <col min="4" max="4" width="17.54296875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1669</v>
-      </c>
-      <c r="C2" t="s">
-        <v>1670</v>
-      </c>
-      <c r="D2" t="s">
-        <v>1671</v>
-      </c>
-      <c r="E2" t="s">
-        <v>1674</v>
-      </c>
-      <c r="F2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G2" t="s">
-        <v>1675</v>
-      </c>
-      <c r="H2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>1672</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>1673</v>
-      </c>
-      <c r="K2" t="s">
-        <v>1676</v>
-      </c>
-      <c r="L2" t="s">
-        <v>1689</v>
-      </c>
-      <c r="M2" t="s">
-        <v>1676</v>
-      </c>
-      <c r="N2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
-        <v>1677</v>
-      </c>
-      <c r="B3" t="s">
-        <v>1678</v>
-      </c>
-      <c r="C3" t="s">
-        <v>1679</v>
-      </c>
-      <c r="D3" t="s">
-        <v>1671</v>
-      </c>
-      <c r="E3" t="s">
-        <v>1680</v>
-      </c>
-      <c r="F3" t="s">
-        <v>46</v>
-      </c>
-      <c r="G3" t="s">
-        <v>1681</v>
-      </c>
-      <c r="H3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" t="s">
-        <v>1672</v>
-      </c>
-      <c r="J3" t="s">
-        <v>1682</v>
-      </c>
-      <c r="K3" t="s">
-        <v>1676</v>
-      </c>
-      <c r="L3" t="s">
-        <v>1689</v>
-      </c>
-      <c r="M3" t="s">
-        <v>1676</v>
-      </c>
-      <c r="N3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" t="s">
-        <v>1683</v>
-      </c>
-      <c r="B4" t="s">
-        <v>1684</v>
-      </c>
-      <c r="C4" t="s">
-        <v>1685</v>
-      </c>
-      <c r="D4" t="s">
-        <v>1671</v>
-      </c>
-      <c r="E4" t="s">
-        <v>1686</v>
-      </c>
-      <c r="F4" t="s">
-        <v>46</v>
-      </c>
-      <c r="G4" t="s">
-        <v>1687</v>
-      </c>
-      <c r="H4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" t="s">
-        <v>1672</v>
-      </c>
-      <c r="J4" t="s">
-        <v>1688</v>
-      </c>
-      <c r="K4" t="s">
-        <v>1676</v>
-      </c>
-      <c r="L4" t="s">
-        <v>1689</v>
-      </c>
-      <c r="M4" t="s">
-        <v>1676</v>
-      </c>
-      <c r="N4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="I2" r:id="rId1" xr:uid="{08280A44-0F58-4FDE-B5FD-3A95A0F423CB}"/>
-    <hyperlink ref="J2" r:id="rId2" xr:uid="{85F326FF-BAE0-4072-815D-1EE4E7995C53}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
-</worksheet>
 </file>
--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A714708A-4030-41BF-8D74-53C922F5E575}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{403B5372-1E92-4065-93FF-7BB6EAE5862F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="1596" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -24,6 +24,7 @@
     <sheet name="050 - ICs - Analog" sheetId="2" r:id="rId9"/>
     <sheet name="060 - ICs - Digital" sheetId="3" r:id="rId10"/>
     <sheet name="070 - Power Supply - DCDC" sheetId="8" r:id="rId11"/>
+    <sheet name="110 - Connectors" sheetId="13" r:id="rId12"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4281" uniqueCount="2168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5038" uniqueCount="2583">
   <si>
     <t>ID</t>
   </si>
@@ -6539,6 +6540,1251 @@
   </si>
   <si>
     <t>https://www.lcsc.com/product-detail/C151252.html</t>
+  </si>
+  <si>
+    <t>110-0001</t>
+  </si>
+  <si>
+    <t>1x2P 2P ZH Tin 2 -25℃~+85℃ 1A 1 1.5mm Brass Horizontal attachment SMD,P=1.5mm,Surface Mount，Right Angle Wire To Board Connector ROHS</t>
+  </si>
+  <si>
+    <t>2P</t>
+  </si>
+  <si>
+    <t>S2B-ZR-SM4A-TF(LF)(SN)</t>
+  </si>
+  <si>
+    <t>JST</t>
+  </si>
+  <si>
+    <t>C265329</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_1912111437_JST-S2B-ZR-SM4A-TF-LF-SN_C265329.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/Wire-To-Board-Connector_JST-S2B-ZR-SM4A-TF-LF-SN_C265329.html</t>
+  </si>
+  <si>
+    <t>CONN 2P</t>
+  </si>
+  <si>
+    <t>CONN S2B-ZR-SM4A-TF</t>
+  </si>
+  <si>
+    <t>110-0002</t>
+  </si>
+  <si>
+    <t>USB-C (USB TYPE-C) USB 3.2 Gen 2 (USB 3.1 Gen 2, Superspeed + (USB 3.1)) Receptáculo Conector 24 Posiciones Montaje en superficie, ángulo recto, orificio pasante</t>
+  </si>
+  <si>
+    <t>USB C</t>
+  </si>
+  <si>
+    <t>USB C SCREW</t>
+  </si>
+  <si>
+    <t>124018792112A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Amphenol ICC (Commercial Products)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	124018792112A</t>
+  </si>
+  <si>
+    <t>DigiKey</t>
+  </si>
+  <si>
+    <t>https://cdn.amphenol-cs.com/media/wysiwyg/files/drawing/c12401879.pdf</t>
+  </si>
+  <si>
+    <t>https://www.digikey.es/es/products/detail/amphenol-icc-(commercial-products)/124018792112A/9825366?utm_adgroup=&amp;utm_source=google&amp;utm_medium=cpc&amp;utm_campaign=PMax_Product_All%20Products&amp;utm_term=&amp;productid=9825366&amp;utm_content=&amp;utm_id=go_cmp-20199915072_adg-_ad-__dev-c_ext-_prd-9825366_sig-Cj0KCQjwurS3BhCGARIsADdUH53tLR7lLfETpZIPoyzxX6VJnl5KdspJmVtxF43AOHqFHwIOO-UdycoaAj67EALw_wcB&amp;gad_source=1&amp;gclid=Cj0KCQjwurS3BhCGARIsADdUH53tLR7lLfETpZIPoyzxX6VJnl5KdspJmVtxF43AOHqFHwIOO-UdycoaAj67EALw_wcB</t>
+  </si>
+  <si>
+    <t>110-0003</t>
+  </si>
+  <si>
+    <t>SMD Coaxial Connectors (RF) ROHS</t>
+  </si>
+  <si>
+    <t>U.FL</t>
+  </si>
+  <si>
+    <t>CONUFL001-SMD-T</t>
+  </si>
+  <si>
+    <t>TE Connectivity</t>
+  </si>
+  <si>
+    <t>C22418213</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2410010030_TE-Connectivity-CONUFL001-SMD-T_C22418213.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/Coaxial-Connectors-RF_TE-Connectivity-CONUFL001-SMD-T_C22418213.html</t>
+  </si>
+  <si>
+    <t>110-0004</t>
+  </si>
+  <si>
+    <t>Conectores placa a placa y mezzanine CONN SOCKET F4S 30 POS 0.4mm</t>
+  </si>
+  <si>
+    <t>30 pin</t>
+  </si>
+  <si>
+    <t>CONN AXT-530124</t>
+  </si>
+  <si>
+    <t>AXT530124</t>
+  </si>
+  <si>
+    <t>Panasonic Industrial Devices</t>
+  </si>
+  <si>
+    <t>769-AXT530124</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/datasheet/2/315/con_eng_f4s-1075761.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Panasonic-Industrial-Devices/AXT530124?qs=2rFUEsTwVNyiwPOEKkiHLw%3D%3D</t>
+  </si>
+  <si>
+    <t>CONN AXT530124</t>
+  </si>
+  <si>
+    <t>110-0005</t>
+  </si>
+  <si>
+    <t>FFC &amp; FPC Connectors WR-FPC 0.5mm SMT ZIF 40Pin Hrztl Top Cont</t>
+  </si>
+  <si>
+    <t>40 pin</t>
+  </si>
+  <si>
+    <t>CONN 68714014022</t>
+  </si>
+  <si>
+    <t>710-68714014022</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/68714014022.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/68714014022?qs=gQDq3jdaPP9DDL2zQpyIEw%3D%3D</t>
+  </si>
+  <si>
+    <t>110-0006</t>
+  </si>
+  <si>
+    <t>M2 Connector TypeB</t>
+  </si>
+  <si>
+    <t>TypeB</t>
+  </si>
+  <si>
+    <t>M.2</t>
+  </si>
+  <si>
+    <t>2199230-3</t>
+  </si>
+  <si>
+    <t>C590859</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2104301136_TE-Connectivity-2199230-3_C590859.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/Hard-Disk-Connector-SAS-SATA-M-2_TE-Connectivity-2199230-3_C590859.html</t>
+  </si>
+  <si>
+    <t>M.2 TypeB</t>
+  </si>
+  <si>
+    <t>M2_TypeB</t>
+  </si>
+  <si>
+    <t>110-0007</t>
+  </si>
+  <si>
+    <t>Test Point</t>
+  </si>
+  <si>
+    <t>TP1mm</t>
+  </si>
+  <si>
+    <t>TP_SMD_1MM</t>
+  </si>
+  <si>
+    <t>110-0008</t>
+  </si>
+  <si>
+    <t>Jumper 1.27mm</t>
+  </si>
+  <si>
+    <t>X1311WVS-02J-C40D42R1</t>
+  </si>
+  <si>
+    <t>XKB Connection</t>
+  </si>
+  <si>
+    <t>C5243486</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2211031030_XKB-Connection-X1311WVS-02J-C40D42R1_C5243486.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/Pin-Headers_XKB-Connection-X1311WVS-02J-C40D42R1_C5243486.html</t>
+  </si>
+  <si>
+    <t>JUMPER</t>
+  </si>
+  <si>
+    <t>JUMPER_SMD_1-27mm</t>
+  </si>
+  <si>
+    <t>110-0009</t>
+  </si>
+  <si>
+    <t>JST 3P Vertical</t>
+  </si>
+  <si>
+    <t>3P</t>
+  </si>
+  <si>
+    <t>B3B-XH-A(LF)(SN)</t>
+  </si>
+  <si>
+    <t>C144394</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2304140030_JST-B3B-XH-A-LF-SN_C144394.pdf</t>
+  </si>
+  <si>
+    <t>https://jlcpcb.com/partdetail/Jst-B3B_XH_A_LF_SN/C144394</t>
+  </si>
+  <si>
+    <t>CONN 3P</t>
+  </si>
+  <si>
+    <t>CONNECTOR_JST_B3B-XH-A(LF)(SN)</t>
+  </si>
+  <si>
+    <t>110-0010</t>
+  </si>
+  <si>
+    <t>JST 3P 90º</t>
+  </si>
+  <si>
+    <t>S3B-XH-A-1(LF)(SN)</t>
+  </si>
+  <si>
+    <t>C163036</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2411192352_JST-S3B-XH-A-1-LF-SN_C163036.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/Wire-To-Board-Connector_JST-S3B-XH-A-1-LF-SN_C163036.html</t>
+  </si>
+  <si>
+    <t>CONNECTOR_JST_S3B-XH-A-1(LF)(SN)</t>
+  </si>
+  <si>
+    <t>110-0011</t>
+  </si>
+  <si>
+    <t>JST 2P 90º</t>
+  </si>
+  <si>
+    <t>S2B-XH-A-1(LF)(SN)</t>
+  </si>
+  <si>
+    <t>C163035</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2410121940_JST-S2B-XH-A-1-LF-SN_C163035.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/Wire-To-Board-Connector_JST-S2B-XH-A-1-LF-SN_C163035.html</t>
+  </si>
+  <si>
+    <t>CONNECTOR_JST_S2B-XH-A-1 (LF)(SN)</t>
+  </si>
+  <si>
+    <t>110-0012</t>
+  </si>
+  <si>
+    <t>JACK 3.5mm</t>
+  </si>
+  <si>
+    <t>Jack</t>
+  </si>
+  <si>
+    <t>PJ-3420-A-SMT</t>
+  </si>
+  <si>
+    <t>C319102</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2110151630_XKB-Connection-PJ-3420-A-SMT_C319102.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/Audio-Connectors_XKB-Connection-PJ-3420-A-SMT_C319102.html</t>
+  </si>
+  <si>
+    <t>JACK 3.5MM</t>
+  </si>
+  <si>
+    <t>110-0013</t>
+  </si>
+  <si>
+    <t>USB 2.0 1 Bend-in 4P Female -40℃~+85℃ Type-A Plugin USB Connectors ROHS</t>
+  </si>
+  <si>
+    <t>USB A Fem</t>
+  </si>
+  <si>
+    <t>UE27AC54100</t>
+  </si>
+  <si>
+    <t>Amphenol ICC</t>
+  </si>
+  <si>
+    <t>C464564</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2411220157_Amphenol-ICC-UE27AC54100_C464564.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/USB-Connectors_Amphenol-ICC-UE27AC54100_C464564.html</t>
+  </si>
+  <si>
+    <t>USB A 2.0</t>
+  </si>
+  <si>
+    <t>USBA_TH_F</t>
+  </si>
+  <si>
+    <t>110-0014</t>
+  </si>
+  <si>
+    <t>10 Straight Needle 1 3.5mm Green Plugin Pluggable System Terminal Block ROHS</t>
+  </si>
+  <si>
+    <t>10P PCB</t>
+  </si>
+  <si>
+    <t>1843871</t>
+  </si>
+  <si>
+    <t>Phoenix Contact</t>
+  </si>
+  <si>
+    <t>C5479577</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2501081540_Phoenix-Contact-1843871_C5479577.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/Pluggable-System-Terminal-Block_Phoenix-Contact-1843871_C5479577.html?s_z=n_1843871</t>
+  </si>
+  <si>
+    <t>CON 10P PCB 1843871</t>
+  </si>
+  <si>
+    <t>110-0015</t>
+  </si>
+  <si>
+    <t>110-0016</t>
+  </si>
+  <si>
+    <t>1A Tin 10P -40℃~+105℃ 1.27mm Double Row Black Copper alloy 1.27mm SMD,P=1.27mm Pin Headers ROHS</t>
+  </si>
+  <si>
+    <t>10P SMD</t>
+  </si>
+  <si>
+    <t>M50-3600542</t>
+  </si>
+  <si>
+    <t>Harwin</t>
+  </si>
+  <si>
+    <t>C7297889</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2411041559_Harwin-M50-3600542_C7297889.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/Pin-Headers_Harwin-M50-3600542_C7297889.html?s_z=n_M50-3600542</t>
+  </si>
+  <si>
+    <t>M50-3600542P</t>
+  </si>
+  <si>
+    <t>110-0017</t>
+  </si>
+  <si>
+    <t>3A 1 Horizontal attachment 24P Female -20℃~+60℃ Type-C SMD USB Connectors ROHS</t>
+  </si>
+  <si>
+    <t>SMD</t>
+  </si>
+  <si>
+    <t>USB-307B-B-SU</t>
+  </si>
+  <si>
+    <t>C309374</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2411212332_HOOYA-USB-307B-B-SU_C309374.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/span-style-background-color-ff0-USB-span-Connectors_HOOYA-USB-307B_C309374.html</t>
+  </si>
+  <si>
+    <t>110-0018</t>
+  </si>
+  <si>
+    <t>Bend-in DC Power Receptacle -25℃~+85℃ 2mm 6.4mm 1A 12V Plugin DC Power Connectors ROHS</t>
+  </si>
+  <si>
+    <t>Barrel Jack 2.1mm</t>
+  </si>
+  <si>
+    <t>DC-005 2.0</t>
+  </si>
+  <si>
+    <t>BOOMELE(Boom Precision Elec)</t>
+  </si>
+  <si>
+    <t>C16214</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2308221657_BOOMELE-Boom-Precision-Elec-DC-005-2-0_C16214.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/AC-DC-Power-Connectors_BOOMELE-Boom-Precision-Elec-DC-005-2-0_C16214.html</t>
+  </si>
+  <si>
+    <t>Barrel_Jack</t>
+  </si>
+  <si>
+    <t>BARREL_JACK_2.5MM</t>
+  </si>
+  <si>
+    <t>110-0019</t>
+  </si>
+  <si>
+    <t>3A Policy 2.5mm 2P 6mm -40℃~+105℃ 3mm 2.54mm Single Row Black 1x2P Plugin,P=2.54mm Pin Headers ROHS</t>
+  </si>
+  <si>
+    <t>Jumper 2P</t>
+  </si>
+  <si>
+    <t>1x2</t>
+  </si>
+  <si>
+    <t>PH-01078</t>
+  </si>
+  <si>
+    <t>Liansheng</t>
+  </si>
+  <si>
+    <t>C2685195</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2411220015_Liansheng-PH-01078_C2685195.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/Pin-Headers_Liansheng-PH-01078_C2685195.html</t>
+  </si>
+  <si>
+    <t>PIN_HEADER_THT_2P</t>
+  </si>
+  <si>
+    <t>110-0020</t>
+  </si>
+  <si>
+    <t>Bloques terminales conectables 20 Pos 3.5mm Dbl Row Through Hole Header</t>
+  </si>
+  <si>
+    <t>PCB 40P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,5mm </t>
+  </si>
+  <si>
+    <t>1787195</t>
+  </si>
+  <si>
+    <t>651-1787195</t>
+  </si>
+  <si>
+    <t>https://www.phoenixcontact.com/us/products/1787195/pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Phoenix-Contact/1787195?qs=c9g5C7Q1WQsip8cyYtZ5HQ%3D%3D</t>
+  </si>
+  <si>
+    <t>CON 1787195</t>
+  </si>
+  <si>
+    <t>110-0021</t>
+  </si>
+  <si>
+    <t>Bloques terminales conectables 15 Pos 3.5mm Dbl Row Through Hole Header</t>
+  </si>
+  <si>
+    <t>PCB 30P</t>
+  </si>
+  <si>
+    <t>1787140</t>
+  </si>
+  <si>
+    <t>651-1787140</t>
+  </si>
+  <si>
+    <t>https://www.phoenixcontact.com/us/products/1787140/pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Phoenix-Contact/1787140?qs=sGAEpiMZZMvlX3nhDDO4AB9Q3y1dl1MlPUoiTuyBrWE%3D</t>
+  </si>
+  <si>
+    <t>CON 1787140</t>
+  </si>
+  <si>
+    <t>110-0022</t>
+  </si>
+  <si>
+    <t>Bloques terminales conectables 20 Pos 3.5mm Dbl Row Plug 24-16AWG Sprin</t>
+  </si>
+  <si>
+    <t>AER 40P</t>
+  </si>
+  <si>
+    <t>1790661</t>
+  </si>
+  <si>
+    <t>651-1790661</t>
+  </si>
+  <si>
+    <t>https://www.phoenixcontact.com/us/products/1790661/pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Phoenix-Contact/1790661?qs=c9g5C7Q1WQtAyR9bB0yIiw%3D%3D</t>
+  </si>
+  <si>
+    <t>CON 1790661</t>
+  </si>
+  <si>
+    <t>110-0023</t>
+  </si>
+  <si>
+    <t>Bloques terminales conectables 15 Pos 3.5mm Dbl Row Plug 24-16AWG Sprin</t>
+  </si>
+  <si>
+    <t>AER 30P</t>
+  </si>
+  <si>
+    <t>1790616</t>
+  </si>
+  <si>
+    <t>651-1790616</t>
+  </si>
+  <si>
+    <t>https://www.phoenixcontact.com/us/products/1790616/pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Phoenix-Contact/1790616?qs=sGAEpiMZZMvlX3nhDDO4AB9Q3y1dl1MlWg0KBNPI4Mw%3D</t>
+  </si>
+  <si>
+    <t>CON 1790616</t>
+  </si>
+  <si>
+    <t>110-0024</t>
+  </si>
+  <si>
+    <t>3.5mm Headphone Jack 30V 500mA Plugin Audio Connectors ROHS</t>
+  </si>
+  <si>
+    <t>PJ-3760M</t>
+  </si>
+  <si>
+    <t>Korean Hroparts Elec</t>
+  </si>
+  <si>
+    <t>C707254</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2008221834_Korean-Hroparts-Elec-PJ-3760M_C707254.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/Audio-Connectors_Korean-Hroparts-Elec-PJ-3760M_C707254.html?s_z=n_C707254</t>
+  </si>
+  <si>
+    <t>JACK 3.5mm 3P</t>
+  </si>
+  <si>
+    <t>JACK 3.5MM 3P</t>
+  </si>
+  <si>
+    <t>110-0025</t>
+  </si>
+  <si>
+    <t>USB 3.1 Standing paste 16P Female Type-C Plugin USB Connectors ROHS</t>
+  </si>
+  <si>
+    <t>USB C TH</t>
+  </si>
+  <si>
+    <t>UT11113-1200L-7H</t>
+  </si>
+  <si>
+    <t>FOXCONN</t>
+  </si>
+  <si>
+    <t>C2994779</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2410121536_FOXCONN-UT11113-1200L-7H_C2994779.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/USB-Connectors_FOXCONN-UT11113-1200L-7H_C2994779.html</t>
+  </si>
+  <si>
+    <t>110-0026</t>
+  </si>
+  <si>
+    <t>JST 2P Vertical</t>
+  </si>
+  <si>
+    <t>B2B-XH-A(LF)(SN)</t>
+  </si>
+  <si>
+    <t>C158012</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2304140030_JST-B2B-XH-A-LF-SN_C158012.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/Wire-To-Board-Wire-To-Wire-Connector_JST-Sales-America-B2B-XH-A-LF-SN_C158012.html</t>
+  </si>
+  <si>
+    <t>CONNECTOR_JST_B2B-XH-A(LF)(SN)</t>
+  </si>
+  <si>
+    <t>110-0027</t>
+  </si>
+  <si>
+    <t>1x5P 5P XH Tin 5 -25℃~+85℃ 3A 1 2.5mm Brass Direct Insert Plugin,P=2.5mm Wire To Board Connector ROHS</t>
+  </si>
+  <si>
+    <t>5P</t>
+  </si>
+  <si>
+    <t>2.5mm</t>
+  </si>
+  <si>
+    <t>B5B-XH-A(LF)(SN)</t>
+  </si>
+  <si>
+    <t>C157991</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2304140030_JST-B5B-XH-A-LF-SN_C157991.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/Wire-To-Board-Connector_JST-B5B-XH-A-LF-SN_C157991.html?s_z=n_JST%20B5B-XH-A%28LF%29%28SN%29</t>
+  </si>
+  <si>
+    <t>CONN 5P</t>
+  </si>
+  <si>
+    <t>CONNECTOR_JST_B5B-XH-A(LF)(SN)</t>
+  </si>
+  <si>
+    <t>110-0028</t>
+  </si>
+  <si>
+    <t>2P 2.54mm Single Row 1x2P Plugin,P=2.54mm Pin Headers ROHS</t>
+  </si>
+  <si>
+    <t>2.54mm</t>
+  </si>
+  <si>
+    <t>G800W306018EU</t>
+  </si>
+  <si>
+    <t>C5426960</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2411220040_Amphenol-ICC-G800W306018EU_C5426960.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/Pin-Headers_Amphenol-ICC-G800W306018EU_C5426960.html</t>
+  </si>
+  <si>
+    <t>Jumper THT 2.54</t>
+  </si>
+  <si>
+    <t>110-0029</t>
+  </si>
+  <si>
+    <t>SMD,P=1.27mm Pin Headers ROHS</t>
+  </si>
+  <si>
+    <t>14P</t>
+  </si>
+  <si>
+    <t>1.27mm</t>
+  </si>
+  <si>
+    <t>FTSH-107-01-F-DV-K-P-TR</t>
+  </si>
+  <si>
+    <t>Samtec</t>
+  </si>
+  <si>
+    <t>C5276598</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2410010331_Samtec-FTSH-107-01-F-DV-K-P-TR_C5276598.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/Pin-Headers_Samtec-FTSH-107-01-F-DV-K-P-TR_C5276598.html?s_z=n_FTSH-107-01-F-DV-K-P-TR</t>
+  </si>
+  <si>
+    <t>JTAG 14 pin</t>
+  </si>
+  <si>
+    <t>CONN SMD 1.27mm 14P</t>
+  </si>
+  <si>
+    <t>110-0030</t>
+  </si>
+  <si>
+    <t>1x5P 5P XH Tin 6 -25℃~+85℃ 3A 1 2.5mm Brass Through Hole Plugin,P=2.5mm Wire To Board Connector ROHS</t>
+  </si>
+  <si>
+    <t>6P</t>
+  </si>
+  <si>
+    <t>B6B-XH-A(LF)(SN)</t>
+  </si>
+  <si>
+    <t>C144397</t>
+  </si>
+  <si>
+    <t>https://lcsc.com/datasheet/lcsc_datasheet_2304140030_JST-B6B-XH-A-LF-SN_C144397.pdf</t>
+  </si>
+  <si>
+    <t>https://lcsc.com/product-detail/Wire-To-Board-Connector_JST-B6B-XH-A-LF-SN_C144397.html?s_z=n_JST%2520B6B-XH-A%28LF%29%28SN%29</t>
+  </si>
+  <si>
+    <t>CONN 6P</t>
+  </si>
+  <si>
+    <t>CONNECTOR_JST B6B-XH-A(LF)(SN)</t>
+  </si>
+  <si>
+    <t>110-0031</t>
+  </si>
+  <si>
+    <t>5A 1 16P Female Type-C SMD USB Connectors ROHS</t>
+  </si>
+  <si>
+    <t>TYPE-C-31-M-12</t>
+  </si>
+  <si>
+    <t>C165948</t>
+  </si>
+  <si>
+    <t>https://lcsc.com/datasheet/lcsc_datasheet_2410010003_Korean-Hroparts-Elec-TYPE-C-31-M-12_C165948.pdf</t>
+  </si>
+  <si>
+    <t>https://lcsc.com/product-detail/USB-Connectors_Korean-Hroparts-Elec-TYPE-C-31-M-12_C165948.html?s_z=n_C165948</t>
+  </si>
+  <si>
+    <t>110-0032</t>
+  </si>
+  <si>
+    <t>Pad Connector SMD 2,54mm x 5,08mm</t>
+  </si>
+  <si>
+    <t>Pad SMD</t>
+  </si>
+  <si>
+    <t>Pad 2,54mm x 5,08mm</t>
+  </si>
+  <si>
+    <t>PAD_254_508</t>
+  </si>
+  <si>
+    <t>CONN 1P</t>
+  </si>
+  <si>
+    <t>110-0033</t>
+  </si>
+  <si>
+    <t>Pad THT 1,50mm x 2,54mm</t>
+  </si>
+  <si>
+    <t>Pad THT</t>
+  </si>
+  <si>
+    <t>PAD_THT_150_254</t>
+  </si>
+  <si>
+    <t>CONN 1P_THT</t>
+  </si>
+  <si>
+    <t>110-0034</t>
+  </si>
+  <si>
+    <t>Edge Card connector 7-5530843-5_EdgeSide</t>
+  </si>
+  <si>
+    <t>12P PCB edge side</t>
+  </si>
+  <si>
+    <t>2,54mm PCB edge side</t>
+  </si>
+  <si>
+    <t>7-5530843-5_EdgeSide</t>
+  </si>
+  <si>
+    <t>7-5530843-5_PCB</t>
+  </si>
+  <si>
+    <t>CONN 12P</t>
+  </si>
+  <si>
+    <t>110-0035</t>
+  </si>
+  <si>
+    <t>Card connector 7-5530843-5</t>
+  </si>
+  <si>
+    <t>12P PCB</t>
+  </si>
+  <si>
+    <t>2,54mm PCB</t>
+  </si>
+  <si>
+    <t>7-5530843-5</t>
+  </si>
+  <si>
+    <t>C4836879</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/C4836879.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C4836879.html?s_z=n_7-5530843-5</t>
+  </si>
+  <si>
+    <t>110-0036</t>
+  </si>
+  <si>
+    <t>Bloques terminales fijos SPT-THR 1 5/ 4-V-3 5 P20 R44</t>
+  </si>
+  <si>
+    <t>4P</t>
+  </si>
+  <si>
+    <t>651-1823214</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/datasheet/3/507/7/phoenix_contact_1823214_en.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Phoenix-Contact/1823214?qs=2WS7V4AoKFraaY4Z%252BwnLUg%3D%3D</t>
+  </si>
+  <si>
+    <t>CONN 4Pd</t>
+  </si>
+  <si>
+    <t>110-0037</t>
+  </si>
+  <si>
+    <t>Terminales SCREW TERMINAL RED</t>
+  </si>
+  <si>
+    <t>Bulk</t>
+  </si>
+  <si>
+    <t>8195-2</t>
+  </si>
+  <si>
+    <t>534-8195-2</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/datasheet/3/201/1/8195_2_8195_7.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Keystone-Electronics/8195-2?qs=sGAEpiMZZMvlX3nhDDO4ABXB%2FmI1TXWXNV5o2iEv8FQ%3D</t>
+  </si>
+  <si>
+    <t>CONN 4P</t>
+  </si>
+  <si>
+    <t>110-0038</t>
+  </si>
+  <si>
+    <t>Alojamientos de cables y cabecera 2.54MM HIGH TEMP PCB HDR STRIP</t>
+  </si>
+  <si>
+    <t>5.84/2.54mm</t>
+  </si>
+  <si>
+    <t>HTSW-103-07-G-S</t>
+  </si>
+  <si>
+    <t>200-HTSW10307GS</t>
+  </si>
+  <si>
+    <t>mouser.es/datasheet/3/85/1/htsw_th.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Samtec/HTSW-103-07-G-S?qs=0lQeLiL1qyYZ%252B%2F6nDbu9tg%3D%3D</t>
+  </si>
+  <si>
+    <t>PIN_HEADER_THT_3P</t>
+  </si>
+  <si>
+    <t>110-0039</t>
+  </si>
+  <si>
+    <t>Test Point 1mm THT</t>
+  </si>
+  <si>
+    <t>1mm</t>
+  </si>
+  <si>
+    <t>TP</t>
+  </si>
+  <si>
+    <t>TP_THT_1MM</t>
+  </si>
+  <si>
+    <t>110-0040</t>
+  </si>
+  <si>
+    <t>Test Point 1.5mm THT</t>
+  </si>
+  <si>
+    <t>1.5mm</t>
+  </si>
+  <si>
+    <t>TP_THT_1.5MM</t>
+  </si>
+  <si>
+    <t>110-0041</t>
+  </si>
+  <si>
+    <t>CONNECTOR_JST_B3B-XH-A(LF)(SN)_V1</t>
+  </si>
+  <si>
+    <t>110-0042</t>
+  </si>
+  <si>
+    <t>CONNECTOR_JST_B2B-XH-A(LF)(SN)_V1</t>
+  </si>
+  <si>
+    <t>110-0043</t>
+  </si>
+  <si>
+    <t>Terminales WP-PLUG Direct Plug 120A Black</t>
+  </si>
+  <si>
+    <t>1P</t>
+  </si>
+  <si>
+    <t>14.8x14.8 mm</t>
+  </si>
+  <si>
+    <t>710-7464100</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/7464100.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/7464100?qs=vHuUswq2%252BszjGOqwiN7d3A%3D%3D</t>
+  </si>
+  <si>
+    <t>CONN 1P_Black</t>
+  </si>
+  <si>
+    <t>WE_WP-PLUG</t>
+  </si>
+  <si>
+    <t>110-0044</t>
+  </si>
+  <si>
+    <t>Terminales WP-PLUG Direct Plug 120A Red</t>
+  </si>
+  <si>
+    <t>710-7464000</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/7464000.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/7464000?qs=lBTPRtX1sU8mAI0X46tmEQ%3D%3D</t>
+  </si>
+  <si>
+    <t>CONN 1P_Red</t>
+  </si>
+  <si>
+    <t>110-0045</t>
+  </si>
+  <si>
+    <t>Alojamientos de cables y cabecera PAD HEADER (SIDE)</t>
+  </si>
+  <si>
+    <t>16P</t>
+  </si>
+  <si>
+    <t>18,0x10,5mm</t>
+  </si>
+  <si>
+    <t>S16B-PADSS-1(LF)(SN)</t>
+  </si>
+  <si>
+    <t>JST Commercial</t>
+  </si>
+  <si>
+    <t>306-S16BPADSS1LFSN</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/datasheet/3/1070/1/ePAD.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/JST-Commercial/S16B-PADSS-1LFSN?qs=QpmGXVUTftGxYno%252BaOPShA%3D%3D&amp;srsltid=AfmBOoo55tbOTcT4WNUMdoF-8xR-EeIrk2sriOWFj03mkhWOt7wKx9cp</t>
+  </si>
+  <si>
+    <t>JST 16 pin</t>
+  </si>
+  <si>
+    <t>110-0046</t>
+  </si>
+  <si>
+    <t>Cabezal de conector Montaje en superficie, ángulo recto 10 posiciones 0.039" (1.00mm)</t>
+  </si>
+  <si>
+    <t>10P</t>
+  </si>
+  <si>
+    <t>9,0x12,0mm</t>
+  </si>
+  <si>
+    <t>SM10B-NSHSS-TB</t>
+  </si>
+  <si>
+    <t>JST Sales America Inc.</t>
+  </si>
+  <si>
+    <t>455-SM10B-NSHSS-TBTR-ND</t>
+  </si>
+  <si>
+    <t>https://www.jst-mfg.com/product/pdf/eng/eNSH.pdf</t>
+  </si>
+  <si>
+    <t>https://www.digikey.es/es/products/detail/jst-sales-america-inc/SM10B-NSHSS-TB/3313643?s=N4IgTCBcDaIMoFkCMAGAQgWgHJwBJzgwBU0AKAGQDEBKUuLakAXQF8g</t>
+  </si>
+  <si>
+    <t>110-0047</t>
+  </si>
+  <si>
+    <t>Connector Receptacle SMA Female Pin 50Ω Through Hole Right Angle</t>
+  </si>
+  <si>
+    <t>KH-SMA-K513-G</t>
+  </si>
+  <si>
+    <t>kinghelm</t>
+  </si>
+  <si>
+    <t>C411575</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/C411575.pdf?spm=wm.sxq.inf.ggs&amp;lcsc_vid=FFdbBlZWFFYIUldUFFBbVgAFElJWUFBURwJaUVEFEQMxVlNRQlBcVFBRRFVYVTsOAxUeFF5JWBYZEEoBGA4JCwFIFA4DSA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C411575.html?s_z=n_C411575</t>
+  </si>
+  <si>
+    <t>110-0048</t>
+  </si>
+  <si>
+    <t>10 Position 3.5mm Pitch Straight Pin</t>
+  </si>
+  <si>
+    <t>Through Hole,P=3.5mm</t>
+  </si>
+  <si>
+    <t>C3584805</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/C3584805.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C3584805.html</t>
+  </si>
+  <si>
+    <t>CONN 10P</t>
+  </si>
+  <si>
+    <t>110-0049</t>
+  </si>
+  <si>
+    <t>10 Position 3.5mm Pitch</t>
+  </si>
+  <si>
+    <t>Aereo</t>
+  </si>
+  <si>
+    <t>C6046522</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/C6046522.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C6046522.html</t>
+  </si>
+  <si>
+    <t>AEREO</t>
+  </si>
+  <si>
+    <t>110-0050</t>
+  </si>
+  <si>
+    <t>Female Header 6 Position 2.54mm Pitch Single Row Through Hole -40℃~+105℃</t>
+  </si>
+  <si>
+    <t>THT 2,54mm</t>
+  </si>
+  <si>
+    <t>PM254V-11-06-H85</t>
+  </si>
+  <si>
+    <t>XFCN</t>
+  </si>
+  <si>
+    <t>C2832269</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/C2832269.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C2832269.html</t>
+  </si>
+  <si>
+    <t>110-0051</t>
+  </si>
+  <si>
+    <t>Pin Header 6 Position 2.54mm Pitch Single Row Through Hole -55℃~+105℃</t>
+  </si>
+  <si>
+    <t>2541WV-06P</t>
+  </si>
+  <si>
+    <t>HanElectricity</t>
+  </si>
+  <si>
+    <t>C5383115</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/C5383115.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C5383115.html</t>
+  </si>
+  <si>
+    <t>HEADERS_MALE_6P_2.54MM</t>
+  </si>
+  <si>
+    <t>110-0052</t>
+  </si>
+  <si>
+    <t>CONN SOCKET 8POS 2.54mm SINGLE ROW TH</t>
+  </si>
+  <si>
+    <t>8P</t>
+  </si>
+  <si>
+    <t>PM254V-11-08-H85</t>
+  </si>
+  <si>
+    <t>C46595973</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/C46595973.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C46595973.html</t>
+  </si>
+  <si>
+    <t>CONN 8P</t>
+  </si>
+  <si>
+    <t>110-0053</t>
+  </si>
+  <si>
+    <t>CONN HEADER 8POS 2.54mm SINGLE ROW TH</t>
+  </si>
+  <si>
+    <t>2541WV-08P</t>
+  </si>
+  <si>
+    <t>C5383116</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/C5383116.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C5383116.html</t>
+  </si>
+  <si>
+    <t>PIN_HEADER_THT_1x8P</t>
+  </si>
+  <si>
+    <t>eUSR_SchLibrary/eUSR_SchLibrary - Connectors.SchLib</t>
+  </si>
+  <si>
+    <t>Pluggable Terminal Blocks 4 Pos 7.62mm pitch Through Hole Header</t>
+  </si>
+  <si>
+    <t>THT 7,62mm</t>
+  </si>
+  <si>
+    <t>651-1804810</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/datasheet/3/507/5/phoenix_contact_1804810_en.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Phoenix-Contact/1804810?qs=CXo1rOUe%2FWvHt6BEjoev5A%3D%3D</t>
+  </si>
+  <si>
+    <t>110-0054</t>
+  </si>
+  <si>
+    <t>Pluggable Terminal Blocks 4 Pos 7.62mm pitch Plug 24-10 AWG Screw</t>
+  </si>
+  <si>
+    <t>651-1804920</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/datasheet/3/507/9/phoenix_contact_1804920_en.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Phoenix-Contact/1804920?qs=bbdZqDPQhEUmz%252BLlbRELng%3D%3D</t>
   </si>
 </sst>
 </file>
@@ -6708,7 +7954,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -6743,56 +7989,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -11445,6 +12651,2488 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE14AD29-8DB0-4C42-AB91-A73B867AE121}">
+  <dimension ref="A1:N55"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="25" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" s="7" t="s">
+        <v>2168</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>2169</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>2170</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>2171</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>2172</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>2173</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>2174</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>2175</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>2176</v>
+      </c>
+      <c r="L2" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M2" s="7" t="s">
+        <v>2177</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="7" t="s">
+        <v>2178</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>2179</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>2180</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>2181</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>2182</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>2183</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>2184</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>2185</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>2186</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>2187</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>2180</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>2181</v>
+      </c>
+      <c r="N3" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="7" t="s">
+        <v>2188</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>2189</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>2190</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>2190</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>2191</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>2192</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>2193</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>2194</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>2195</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>1835</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>2190</v>
+      </c>
+      <c r="N4" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="7" t="s">
+        <v>2196</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>2197</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>2198</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>2199</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>2200</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>2201</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>2202</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>2203</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>2204</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>2205</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N5" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="7" t="s">
+        <v>2206</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>2207</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>2208</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>2209</v>
+      </c>
+      <c r="E6" s="7">
+        <v>68714014022</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>2210</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>2211</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>2212</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>2209</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>2209</v>
+      </c>
+      <c r="N6" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="7" t="s">
+        <v>2213</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>2214</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>2215</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>2216</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>2217</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>2192</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>2218</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I7" s="15" t="s">
+        <v>2219</v>
+      </c>
+      <c r="J7" s="15" t="s">
+        <v>2220</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>2221</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M7" s="7" t="s">
+        <v>2222</v>
+      </c>
+      <c r="N7" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="7" t="s">
+        <v>2223</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>2224</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>2225</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>2226</v>
+      </c>
+      <c r="N8" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="7" t="s">
+        <v>2227</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>2228</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>2170</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>2229</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>2230</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>2231</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>2232</v>
+      </c>
+      <c r="J9" s="11" t="s">
+        <v>2233</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>2234</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M9" s="7" t="s">
+        <v>2235</v>
+      </c>
+      <c r="N9" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="7" t="s">
+        <v>2236</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>2237</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>2238</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>2239</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>2172</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>2240</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I10" s="26" t="s">
+        <v>2241</v>
+      </c>
+      <c r="J10" s="26" t="s">
+        <v>2242</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>2243</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M10" s="7" t="s">
+        <v>2244</v>
+      </c>
+      <c r="N10" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="7" t="s">
+        <v>2245</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>2246</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>2238</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>2247</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>2172</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>2248</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I11" s="15" t="s">
+        <v>2249</v>
+      </c>
+      <c r="J11" s="15" t="s">
+        <v>2250</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>2243</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M11" s="7" t="s">
+        <v>2251</v>
+      </c>
+      <c r="N11" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="7" t="s">
+        <v>2252</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>2253</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>2170</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>2254</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>2172</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>2255</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I12" s="15" t="s">
+        <v>2256</v>
+      </c>
+      <c r="J12" s="15" t="s">
+        <v>2257</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>2176</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M12" s="7" t="s">
+        <v>2258</v>
+      </c>
+      <c r="N12" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="7" t="s">
+        <v>2259</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>2260</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>2261</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>2262</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>2230</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>2263</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I13" s="15" t="s">
+        <v>2264</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>2265</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>2260</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M13" s="7" t="s">
+        <v>2266</v>
+      </c>
+      <c r="N13" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="7" t="s">
+        <v>2267</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>2268</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>2269</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>2270</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>2271</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>2272</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>2273</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>2274</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>2275</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M14" s="7" t="s">
+        <v>2276</v>
+      </c>
+      <c r="N14" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="7" t="s">
+        <v>2277</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>2278</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>2279</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>2280</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>2281</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>2282</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>2283</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>2284</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>2285</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M15" s="7" t="s">
+        <v>2285</v>
+      </c>
+      <c r="N15" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="7" t="s">
+        <v>2286</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>2288</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>2289</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>2290</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>2291</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>2292</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>2293</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>2294</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>2295</v>
+      </c>
+      <c r="L16" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M16" s="7" t="s">
+        <v>2295</v>
+      </c>
+      <c r="N16" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" s="7" t="s">
+        <v>2287</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>2297</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>2180</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>2298</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>2299</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>2300</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>2300</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I17" s="15" t="s">
+        <v>2301</v>
+      </c>
+      <c r="J17" s="15" t="s">
+        <v>2302</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>2180</v>
+      </c>
+      <c r="L17" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M17" s="7" t="s">
+        <v>2180</v>
+      </c>
+      <c r="N17" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" s="7" t="s">
+        <v>2296</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>2304</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>2261</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>2305</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>2306</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>2307</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>2308</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I18" s="15" t="s">
+        <v>2309</v>
+      </c>
+      <c r="J18" s="15" t="s">
+        <v>2310</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>2311</v>
+      </c>
+      <c r="L18" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M18" s="7" t="s">
+        <v>2312</v>
+      </c>
+      <c r="N18" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" s="7" t="s">
+        <v>2303</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>2314</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>2315</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>2316</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>2317</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>2318</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>2319</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I19" s="15" t="s">
+        <v>2320</v>
+      </c>
+      <c r="J19" s="15" t="s">
+        <v>2321</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>2176</v>
+      </c>
+      <c r="L19" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M19" s="7" t="s">
+        <v>2322</v>
+      </c>
+      <c r="N19" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" s="7" t="s">
+        <v>2313</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>2324</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>2325</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>2326</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>2327</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>2281</v>
+      </c>
+      <c r="G20" s="13" t="s">
+        <v>2328</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I20" s="15" t="s">
+        <v>2329</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>2330</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>2331</v>
+      </c>
+      <c r="L20" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M20" s="7" t="s">
+        <v>2331</v>
+      </c>
+      <c r="N20" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" s="7" t="s">
+        <v>2323</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>2333</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>2334</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>2326</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>2335</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>2281</v>
+      </c>
+      <c r="G21" s="13" t="s">
+        <v>2336</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>2337</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>2338</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>2339</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M21" s="7" t="s">
+        <v>2339</v>
+      </c>
+      <c r="N21" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" s="7" t="s">
+        <v>2332</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>2341</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>2342</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>2326</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>2343</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>2281</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I22" s="15" t="s">
+        <v>2345</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>2346</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>2347</v>
+      </c>
+      <c r="L22" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M22" s="7" t="s">
+        <v>2347</v>
+      </c>
+      <c r="N22" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" s="7" t="s">
+        <v>2340</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>2349</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>2350</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>2326</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>2351</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>2281</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>2352</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I23" s="15" t="s">
+        <v>2353</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>2354</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>2355</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M23" s="7" t="s">
+        <v>2355</v>
+      </c>
+      <c r="N23" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" s="7" t="s">
+        <v>2348</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>2357</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>2261</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>2326</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>2358</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>2359</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>2360</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I24" s="15" t="s">
+        <v>2361</v>
+      </c>
+      <c r="J24" s="15" t="s">
+        <v>2362</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>2363</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M24" s="7" t="s">
+        <v>2364</v>
+      </c>
+      <c r="N24" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" s="7" t="s">
+        <v>2356</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>2366</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>2180</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>2367</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>2368</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>2369</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>2370</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I25" s="18" t="s">
+        <v>2371</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>2372</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>2180</v>
+      </c>
+      <c r="L25" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M25" s="7" t="s">
+        <v>2368</v>
+      </c>
+      <c r="N25" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" s="7" t="s">
+        <v>2365</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>2374</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>2170</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>2375</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>2172</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>2376</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I26" s="15" t="s">
+        <v>2377</v>
+      </c>
+      <c r="J26" s="15" t="s">
+        <v>2378</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>2176</v>
+      </c>
+      <c r="L26" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M26" s="7" t="s">
+        <v>2379</v>
+      </c>
+      <c r="N26" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" s="7" t="s">
+        <v>2373</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>2381</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>2382</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>2383</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>2384</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>2172</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>2385</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I27" s="7" t="s">
+        <v>2386</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>2387</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>2388</v>
+      </c>
+      <c r="L27" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M27" s="7" t="s">
+        <v>2389</v>
+      </c>
+      <c r="N27" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" s="7" t="s">
+        <v>2380</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>2391</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>2170</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>2392</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>2393</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>2271</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>2394</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I28" s="15" t="s">
+        <v>2395</v>
+      </c>
+      <c r="J28" s="15" t="s">
+        <v>2396</v>
+      </c>
+      <c r="K28" s="7" t="s">
+        <v>2234</v>
+      </c>
+      <c r="L28" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M28" s="7" t="s">
+        <v>2397</v>
+      </c>
+      <c r="N28" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29" s="7" t="s">
+        <v>2390</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>2399</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>2400</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>2401</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>2402</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>2403</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>2404</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I29" s="15" t="s">
+        <v>2405</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>2406</v>
+      </c>
+      <c r="K29" s="7" t="s">
+        <v>2407</v>
+      </c>
+      <c r="L29" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M29" s="7" t="s">
+        <v>2408</v>
+      </c>
+      <c r="N29" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" s="7" t="s">
+        <v>2398</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>2410</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>2411</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>2383</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>2412</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>2172</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>2413</v>
+      </c>
+      <c r="H30" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>2414</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>2415</v>
+      </c>
+      <c r="K30" s="7" t="s">
+        <v>2416</v>
+      </c>
+      <c r="L30" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M30" s="17" t="s">
+        <v>2417</v>
+      </c>
+      <c r="N30" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" s="7" t="s">
+        <v>2409</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>2419</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>2180</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>2180</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>2420</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>2359</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>2421</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I31" s="18" t="s">
+        <v>2422</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>2423</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>2420</v>
+      </c>
+      <c r="L31" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M31" s="3" t="s">
+        <v>2420</v>
+      </c>
+      <c r="N31" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" s="7" t="s">
+        <v>2418</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>2425</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>2426</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>2427</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>2428</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>2428</v>
+      </c>
+      <c r="G32" s="7" t="s">
+        <v>2428</v>
+      </c>
+      <c r="H32" s="7" t="s">
+        <v>2428</v>
+      </c>
+      <c r="I32" s="7" t="s">
+        <v>2428</v>
+      </c>
+      <c r="J32" s="7" t="s">
+        <v>2428</v>
+      </c>
+      <c r="K32" s="7" t="s">
+        <v>2429</v>
+      </c>
+      <c r="L32" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M32" s="7" t="s">
+        <v>2428</v>
+      </c>
+      <c r="N32" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
+      <c r="A33" s="7" t="s">
+        <v>2424</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>2431</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>2432</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>2431</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>2433</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>2433</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>2433</v>
+      </c>
+      <c r="H33" s="7" t="s">
+        <v>2433</v>
+      </c>
+      <c r="I33" s="7" t="s">
+        <v>2433</v>
+      </c>
+      <c r="J33" s="7" t="s">
+        <v>2433</v>
+      </c>
+      <c r="K33" s="7" t="s">
+        <v>2434</v>
+      </c>
+      <c r="L33" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M33" s="7" t="s">
+        <v>2433</v>
+      </c>
+      <c r="N33" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
+      <c r="A34" s="7" t="s">
+        <v>2430</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>2436</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>2437</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>2438</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>2439</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>2439</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>2440</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>2440</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>2440</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>2440</v>
+      </c>
+      <c r="K34" s="7" t="s">
+        <v>2441</v>
+      </c>
+      <c r="L34" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M34" s="3" t="s">
+        <v>2440</v>
+      </c>
+      <c r="N34" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
+      <c r="A35" s="7" t="s">
+        <v>2435</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>2443</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>2444</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>2445</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>2446</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>2192</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>2447</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>2448</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>2449</v>
+      </c>
+      <c r="K35" s="7" t="s">
+        <v>2441</v>
+      </c>
+      <c r="L35" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>2446</v>
+      </c>
+      <c r="N35" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
+      <c r="A36" s="7" t="s">
+        <v>2442</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>2451</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>2452</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>2326</v>
+      </c>
+      <c r="E36" s="3">
+        <v>1823214</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>2281</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>2453</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>2454</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>2455</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>2456</v>
+      </c>
+      <c r="L36" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M36" s="3">
+        <v>1823214</v>
+      </c>
+      <c r="N36" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
+      <c r="A37" s="7" t="s">
+        <v>2450</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>2458</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>2452</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>2459</v>
+      </c>
+      <c r="E37" s="17" t="s">
+        <v>2460</v>
+      </c>
+      <c r="F37" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="G37" s="17" t="s">
+        <v>2461</v>
+      </c>
+      <c r="H37" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="I37" s="18" t="s">
+        <v>2462</v>
+      </c>
+      <c r="J37" s="18" t="s">
+        <v>2463</v>
+      </c>
+      <c r="K37" s="17" t="s">
+        <v>2464</v>
+      </c>
+      <c r="L37" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M37" s="17" t="s">
+        <v>2460</v>
+      </c>
+      <c r="N37" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
+      <c r="A38" s="7" t="s">
+        <v>2457</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>2466</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>2238</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>2467</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>2468</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>2403</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>2469</v>
+      </c>
+      <c r="H38" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I38" s="7" t="s">
+        <v>2470</v>
+      </c>
+      <c r="J38" s="18" t="s">
+        <v>2471</v>
+      </c>
+      <c r="K38" s="7" t="s">
+        <v>2243</v>
+      </c>
+      <c r="L38" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M38" s="7" t="s">
+        <v>2472</v>
+      </c>
+      <c r="N38" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
+      <c r="A39" s="7" t="s">
+        <v>2465</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>2474</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>2475</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H39" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I39" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J39" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K39" s="7" t="s">
+        <v>2476</v>
+      </c>
+      <c r="L39" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M39" s="3" t="s">
+        <v>2477</v>
+      </c>
+      <c r="N39" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
+      <c r="A40" s="7" t="s">
+        <v>2473</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>2479</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>2480</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G40" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H40" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I40" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J40" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K40" s="7" t="s">
+        <v>2476</v>
+      </c>
+      <c r="L40" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M40" s="3" t="s">
+        <v>2481</v>
+      </c>
+      <c r="N40" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
+      <c r="A41" s="7" t="s">
+        <v>2478</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>2237</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>2238</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>2239</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>2172</v>
+      </c>
+      <c r="G41" s="7" t="s">
+        <v>2240</v>
+      </c>
+      <c r="H41" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I41" s="26" t="s">
+        <v>2241</v>
+      </c>
+      <c r="J41" s="26" t="s">
+        <v>2242</v>
+      </c>
+      <c r="K41" s="7" t="s">
+        <v>2243</v>
+      </c>
+      <c r="L41" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M41" s="7" t="s">
+        <v>2483</v>
+      </c>
+      <c r="N41" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
+      <c r="A42" s="7" t="s">
+        <v>2482</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>2374</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>2170</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>2375</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>2172</v>
+      </c>
+      <c r="G42" s="7" t="s">
+        <v>2376</v>
+      </c>
+      <c r="H42" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I42" s="15" t="s">
+        <v>2377</v>
+      </c>
+      <c r="J42" s="15" t="s">
+        <v>2378</v>
+      </c>
+      <c r="K42" s="7" t="s">
+        <v>2176</v>
+      </c>
+      <c r="L42" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M42" s="7" t="s">
+        <v>2485</v>
+      </c>
+      <c r="N42" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14">
+      <c r="A43" s="7" t="s">
+        <v>2484</v>
+      </c>
+      <c r="B43" s="16" t="s">
+        <v>2487</v>
+      </c>
+      <c r="C43" s="16" t="s">
+        <v>2488</v>
+      </c>
+      <c r="D43" s="16" t="s">
+        <v>2489</v>
+      </c>
+      <c r="E43" s="3">
+        <v>7464100</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>2490</v>
+      </c>
+      <c r="H43" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>2491</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>2492</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>2493</v>
+      </c>
+      <c r="L43" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>2494</v>
+      </c>
+      <c r="N43" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
+      <c r="A44" s="7" t="s">
+        <v>2486</v>
+      </c>
+      <c r="B44" s="16" t="s">
+        <v>2496</v>
+      </c>
+      <c r="C44" s="16" t="s">
+        <v>2488</v>
+      </c>
+      <c r="D44" s="16" t="s">
+        <v>2489</v>
+      </c>
+      <c r="E44" s="3">
+        <v>7464000</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>2497</v>
+      </c>
+      <c r="H44" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>2498</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>2499</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>2500</v>
+      </c>
+      <c r="L44" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>2494</v>
+      </c>
+      <c r="N44" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
+      <c r="A45" s="7" t="s">
+        <v>2495</v>
+      </c>
+      <c r="B45" s="16" t="s">
+        <v>2502</v>
+      </c>
+      <c r="C45" s="16" t="s">
+        <v>2503</v>
+      </c>
+      <c r="D45" s="16" t="s">
+        <v>2504</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>2505</v>
+      </c>
+      <c r="F45" s="17" t="s">
+        <v>2506</v>
+      </c>
+      <c r="G45" s="17" t="s">
+        <v>2507</v>
+      </c>
+      <c r="H45" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I45" s="18" t="s">
+        <v>2508</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>2509</v>
+      </c>
+      <c r="K45" s="17" t="s">
+        <v>2510</v>
+      </c>
+      <c r="L45" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M45" s="17" t="s">
+        <v>2505</v>
+      </c>
+      <c r="N45" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14">
+      <c r="A46" s="7" t="s">
+        <v>2501</v>
+      </c>
+      <c r="B46" s="16" t="s">
+        <v>2512</v>
+      </c>
+      <c r="C46" s="16" t="s">
+        <v>2513</v>
+      </c>
+      <c r="D46" s="16" t="s">
+        <v>2514</v>
+      </c>
+      <c r="E46" s="16" t="s">
+        <v>2515</v>
+      </c>
+      <c r="F46" s="16" t="s">
+        <v>2516</v>
+      </c>
+      <c r="G46" s="16" t="s">
+        <v>2517</v>
+      </c>
+      <c r="H46" s="16" t="s">
+        <v>2185</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>2518</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>2519</v>
+      </c>
+      <c r="K46" s="17" t="s">
+        <v>2441</v>
+      </c>
+      <c r="L46" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M46" s="3" t="s">
+        <v>2515</v>
+      </c>
+      <c r="N46" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14">
+      <c r="A47" s="7" t="s">
+        <v>2511</v>
+      </c>
+      <c r="B47" s="16" t="s">
+        <v>2521</v>
+      </c>
+      <c r="C47" s="16" t="s">
+        <v>2170</v>
+      </c>
+      <c r="D47" s="16" t="s">
+        <v>1835</v>
+      </c>
+      <c r="E47" s="16" t="s">
+        <v>2522</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>2523</v>
+      </c>
+      <c r="G47" s="16" t="s">
+        <v>2524</v>
+      </c>
+      <c r="H47" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I47" s="18" t="s">
+        <v>2525</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>2526</v>
+      </c>
+      <c r="K47" s="17" t="s">
+        <v>1835</v>
+      </c>
+      <c r="L47" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>2522</v>
+      </c>
+      <c r="N47" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14">
+      <c r="A48" s="7" t="s">
+        <v>2520</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>2528</v>
+      </c>
+      <c r="C48" s="16" t="s">
+        <v>2513</v>
+      </c>
+      <c r="D48" s="16" t="s">
+        <v>2529</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1844294</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>2281</v>
+      </c>
+      <c r="G48" s="7" t="s">
+        <v>2530</v>
+      </c>
+      <c r="H48" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I48" s="18" t="s">
+        <v>2531</v>
+      </c>
+      <c r="J48" s="18" t="s">
+        <v>2532</v>
+      </c>
+      <c r="K48" s="17" t="s">
+        <v>2533</v>
+      </c>
+      <c r="L48" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M48" s="3">
+        <v>1844294</v>
+      </c>
+      <c r="N48" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14">
+      <c r="A49" s="7" t="s">
+        <v>2527</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>2535</v>
+      </c>
+      <c r="C49" s="16" t="s">
+        <v>2513</v>
+      </c>
+      <c r="D49" s="16" t="s">
+        <v>2536</v>
+      </c>
+      <c r="E49" s="3">
+        <v>1840447</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>2281</v>
+      </c>
+      <c r="G49" s="7" t="s">
+        <v>2537</v>
+      </c>
+      <c r="H49" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I49" s="18" t="s">
+        <v>2538</v>
+      </c>
+      <c r="J49" s="18" t="s">
+        <v>2539</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>2540</v>
+      </c>
+      <c r="L49" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M49" s="3">
+        <v>1840447</v>
+      </c>
+      <c r="N49" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14">
+      <c r="A50" s="7" t="s">
+        <v>2534</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>2542</v>
+      </c>
+      <c r="C50" s="16" t="s">
+        <v>2411</v>
+      </c>
+      <c r="D50" s="16" t="s">
+        <v>2543</v>
+      </c>
+      <c r="E50" s="16" t="s">
+        <v>2544</v>
+      </c>
+      <c r="F50" s="16" t="s">
+        <v>2545</v>
+      </c>
+      <c r="G50" s="16" t="s">
+        <v>2546</v>
+      </c>
+      <c r="H50" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I50" s="18" t="s">
+        <v>2547</v>
+      </c>
+      <c r="J50" s="18" t="s">
+        <v>2548</v>
+      </c>
+      <c r="K50" s="17" t="s">
+        <v>2416</v>
+      </c>
+      <c r="L50" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M50" s="3" t="s">
+        <v>2544</v>
+      </c>
+      <c r="N50" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14">
+      <c r="A51" s="7" t="s">
+        <v>2541</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>2550</v>
+      </c>
+      <c r="C51" s="16" t="s">
+        <v>2411</v>
+      </c>
+      <c r="D51" s="16" t="s">
+        <v>2543</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>2551</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>2552</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>2553</v>
+      </c>
+      <c r="H51" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>2554</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>2555</v>
+      </c>
+      <c r="K51" s="17" t="s">
+        <v>2416</v>
+      </c>
+      <c r="L51" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M51" s="3" t="s">
+        <v>2556</v>
+      </c>
+      <c r="N51" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14">
+      <c r="A52" s="7" t="s">
+        <v>2549</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>2558</v>
+      </c>
+      <c r="C52" s="16" t="s">
+        <v>2559</v>
+      </c>
+      <c r="D52" s="16" t="s">
+        <v>2543</v>
+      </c>
+      <c r="E52" s="16" t="s">
+        <v>2560</v>
+      </c>
+      <c r="F52" s="16" t="s">
+        <v>2545</v>
+      </c>
+      <c r="G52" s="16" t="s">
+        <v>2561</v>
+      </c>
+      <c r="H52" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I52" s="18" t="s">
+        <v>2562</v>
+      </c>
+      <c r="J52" s="18" t="s">
+        <v>2563</v>
+      </c>
+      <c r="K52" s="17" t="s">
+        <v>2564</v>
+      </c>
+      <c r="L52" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M52" s="7" t="s">
+        <v>2560</v>
+      </c>
+      <c r="N52" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14">
+      <c r="A53" s="7" t="s">
+        <v>2557</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>2566</v>
+      </c>
+      <c r="C53" s="16" t="s">
+        <v>2559</v>
+      </c>
+      <c r="D53" s="16" t="s">
+        <v>2543</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>2567</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>2552</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>2568</v>
+      </c>
+      <c r="H53" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>2569</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>2570</v>
+      </c>
+      <c r="K53" s="17" t="s">
+        <v>2564</v>
+      </c>
+      <c r="L53" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M53" s="7" t="s">
+        <v>2571</v>
+      </c>
+      <c r="N53" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14">
+      <c r="A54" s="7" t="s">
+        <v>2565</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>2573</v>
+      </c>
+      <c r="C54" s="16" t="s">
+        <v>2452</v>
+      </c>
+      <c r="D54" s="16" t="s">
+        <v>2574</v>
+      </c>
+      <c r="E54">
+        <v>1804810</v>
+      </c>
+      <c r="F54" s="7" t="s">
+        <v>2281</v>
+      </c>
+      <c r="G54" t="s">
+        <v>2575</v>
+      </c>
+      <c r="H54" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I54" t="s">
+        <v>2576</v>
+      </c>
+      <c r="J54" t="s">
+        <v>2577</v>
+      </c>
+      <c r="K54" s="17" t="s">
+        <v>2564</v>
+      </c>
+      <c r="L54" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M54">
+        <v>1804810</v>
+      </c>
+      <c r="N54" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14">
+      <c r="A55" s="16" t="s">
+        <v>2578</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>2579</v>
+      </c>
+      <c r="C55" s="16" t="s">
+        <v>2452</v>
+      </c>
+      <c r="D55" s="16" t="s">
+        <v>2574</v>
+      </c>
+      <c r="E55">
+        <v>1804920</v>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>2281</v>
+      </c>
+      <c r="G55" s="16" t="s">
+        <v>2580</v>
+      </c>
+      <c r="H55" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I55" s="27" t="s">
+        <v>2581</v>
+      </c>
+      <c r="J55" t="s">
+        <v>2582</v>
+      </c>
+      <c r="K55" s="3" t="s">
+        <v>2540</v>
+      </c>
+      <c r="L55" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M55">
+        <v>1804920</v>
+      </c>
+      <c r="N55" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="16" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="J3" r:id="rId1" xr:uid="{00000000-0004-0000-1D00-000000000000}"/>
+    <hyperlink ref="I7" r:id="rId2" xr:uid="{00000000-0004-0000-1D00-000001000000}"/>
+    <hyperlink ref="J7" r:id="rId3" xr:uid="{00000000-0004-0000-1D00-000002000000}"/>
+    <hyperlink ref="I9" r:id="rId4" xr:uid="{00000000-0004-0000-1D00-000003000000}"/>
+    <hyperlink ref="J9" r:id="rId5" xr:uid="{00000000-0004-0000-1D00-000004000000}"/>
+    <hyperlink ref="I10" r:id="rId6" xr:uid="{00000000-0004-0000-1D00-000005000000}"/>
+    <hyperlink ref="J10" r:id="rId7" xr:uid="{00000000-0004-0000-1D00-000006000000}"/>
+    <hyperlink ref="I11" r:id="rId8" xr:uid="{00000000-0004-0000-1D00-000007000000}"/>
+    <hyperlink ref="J11" r:id="rId9" xr:uid="{00000000-0004-0000-1D00-000008000000}"/>
+    <hyperlink ref="I12" r:id="rId10" xr:uid="{00000000-0004-0000-1D00-000009000000}"/>
+    <hyperlink ref="J12" r:id="rId11" xr:uid="{00000000-0004-0000-1D00-00000A000000}"/>
+    <hyperlink ref="I13" r:id="rId12" xr:uid="{00000000-0004-0000-1D00-00000B000000}"/>
+    <hyperlink ref="J13" r:id="rId13" xr:uid="{00000000-0004-0000-1D00-00000C000000}"/>
+    <hyperlink ref="I17" r:id="rId14" xr:uid="{00000000-0004-0000-1D00-00000D000000}"/>
+    <hyperlink ref="J17" r:id="rId15" xr:uid="{00000000-0004-0000-1D00-00000E000000}"/>
+    <hyperlink ref="I18" r:id="rId16" xr:uid="{00000000-0004-0000-1D00-00000F000000}"/>
+    <hyperlink ref="J18" r:id="rId17" xr:uid="{00000000-0004-0000-1D00-000010000000}"/>
+    <hyperlink ref="I19" r:id="rId18" xr:uid="{00000000-0004-0000-1D00-000011000000}"/>
+    <hyperlink ref="J19" r:id="rId19" xr:uid="{00000000-0004-0000-1D00-000012000000}"/>
+    <hyperlink ref="I20" r:id="rId20" xr:uid="{00000000-0004-0000-1D00-000013000000}"/>
+    <hyperlink ref="I22" r:id="rId21" xr:uid="{00000000-0004-0000-1D00-000014000000}"/>
+    <hyperlink ref="I23" r:id="rId22" xr:uid="{00000000-0004-0000-1D00-000015000000}"/>
+    <hyperlink ref="I24" r:id="rId23" xr:uid="{00000000-0004-0000-1D00-000016000000}"/>
+    <hyperlink ref="J24" r:id="rId24" xr:uid="{00000000-0004-0000-1D00-000017000000}"/>
+    <hyperlink ref="I26" r:id="rId25" xr:uid="{00000000-0004-0000-1D00-000018000000}"/>
+    <hyperlink ref="J26" r:id="rId26" xr:uid="{00000000-0004-0000-1D00-000019000000}"/>
+    <hyperlink ref="I28" r:id="rId27" xr:uid="{00000000-0004-0000-1D00-00001A000000}"/>
+    <hyperlink ref="J28" r:id="rId28" xr:uid="{00000000-0004-0000-1D00-00001B000000}"/>
+    <hyperlink ref="I29" r:id="rId29" xr:uid="{00000000-0004-0000-1D00-00001C000000}"/>
+    <hyperlink ref="I31" r:id="rId30" xr:uid="{B889E894-AE28-4673-8E7D-B0B1EEEEAAC9}"/>
+    <hyperlink ref="I37" r:id="rId31" xr:uid="{A5EF1718-034C-4629-9593-D99CD89D3C39}"/>
+    <hyperlink ref="J37" r:id="rId32" xr:uid="{9B6BA1C9-0475-4CCF-8D26-2D3D91FEFB77}"/>
+    <hyperlink ref="J38" r:id="rId33" xr:uid="{8CD8A486-EA06-47DF-9F3F-C642DA019FC4}"/>
+    <hyperlink ref="I25" r:id="rId34" xr:uid="{0FD3F93C-970F-462D-9D99-3368C1254DCD}"/>
+    <hyperlink ref="I41" r:id="rId35" xr:uid="{24EA0A72-4869-4E5C-BD6A-CA5115A046B8}"/>
+    <hyperlink ref="J41" r:id="rId36" xr:uid="{CDF0CF32-7F98-45EF-A9A3-407374BF993D}"/>
+    <hyperlink ref="I42" r:id="rId37" xr:uid="{560483C0-DEA7-463C-92EF-955BDD611FB3}"/>
+    <hyperlink ref="J42" r:id="rId38" xr:uid="{CB0C6813-29FA-4A18-832B-94DC8E2799EA}"/>
+    <hyperlink ref="I45" r:id="rId39" xr:uid="{5CFBFA28-E01A-462F-8A96-EDC78CDD8754}"/>
+    <hyperlink ref="I47" r:id="rId40" xr:uid="{48A761C6-8F23-4E15-A00D-4FEBA1F44E39}"/>
+    <hyperlink ref="J48" r:id="rId41" xr:uid="{4CABD0E0-0658-43B5-A6D9-351CB41C79AC}"/>
+    <hyperlink ref="I48" r:id="rId42" xr:uid="{50C93A3A-8C77-4A5C-A4C0-521A9952F333}"/>
+    <hyperlink ref="J49" r:id="rId43" xr:uid="{DDB5C1DF-984A-484F-88F7-F7B30D64D5B0}"/>
+    <hyperlink ref="I49" r:id="rId44" xr:uid="{DC28A411-B37E-44BA-8D9C-11FEB67FF371}"/>
+    <hyperlink ref="J50" r:id="rId45" xr:uid="{6F543371-70DF-42AB-8851-D507F8BED9FA}"/>
+    <hyperlink ref="I50" r:id="rId46" xr:uid="{FE98799C-B6BE-43A0-8E8A-2DA3A1AA0F8F}"/>
+    <hyperlink ref="J52" r:id="rId47" xr:uid="{E897E496-BD4D-4176-A529-0242E26116CB}"/>
+    <hyperlink ref="I52" r:id="rId48" xr:uid="{A225907D-3E4C-4582-95BF-8DEDA99E88ED}"/>
+    <hyperlink ref="I55" r:id="rId49" xr:uid="{A1002F44-75AF-44AC-BBCA-828DA38BB4E6}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60E8291E-4293-4634-B9E9-80CB520CA181}">
   <dimension ref="A1:N136"/>
@@ -17789,354 +21477,354 @@
       </c>
     </row>
     <row r="2" spans="1:14">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="7" t="s">
         <v>1832</v>
       </c>
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="7" t="s">
         <v>1833</v>
       </c>
-      <c r="C2" s="34" t="s">
+      <c r="C2" s="24" t="s">
         <v>1834</v>
       </c>
-      <c r="D2" s="32" t="s">
+      <c r="D2" s="7" t="s">
         <v>1835</v>
       </c>
-      <c r="E2" s="32" t="s">
+      <c r="E2" s="7" t="s">
         <v>1836</v>
       </c>
-      <c r="F2" s="32" t="s">
+      <c r="F2" s="7" t="s">
         <v>1837</v>
       </c>
-      <c r="G2" s="32" t="s">
+      <c r="G2" s="7" t="s">
         <v>1838</v>
       </c>
-      <c r="H2" s="32" t="s">
-        <v>69</v>
-      </c>
-      <c r="I2" s="32" t="s">
+      <c r="H2" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I2" s="7" t="s">
         <v>1839</v>
       </c>
-      <c r="J2" s="32" t="s">
+      <c r="J2" s="7" t="s">
         <v>1840</v>
       </c>
-      <c r="K2" s="32" t="s">
+      <c r="K2" s="7" t="s">
         <v>1841</v>
       </c>
-      <c r="L2" s="32" t="s">
+      <c r="L2" s="7" t="s">
         <v>1910</v>
       </c>
-      <c r="M2" s="32" t="s">
+      <c r="M2" s="7" t="s">
         <v>1842</v>
       </c>
-      <c r="N2" s="32" t="s">
+      <c r="N2" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:14">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="7" t="s">
         <v>1843</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="7" t="s">
         <v>1844</v>
       </c>
-      <c r="C3" s="32" t="s">
+      <c r="C3" s="7" t="s">
         <v>1845</v>
       </c>
-      <c r="D3" s="32" t="s">
+      <c r="D3" s="7" t="s">
         <v>1846</v>
       </c>
-      <c r="E3" s="32" t="s">
+      <c r="E3" s="7" t="s">
         <v>1847</v>
       </c>
-      <c r="F3" s="32" t="s">
+      <c r="F3" s="7" t="s">
         <v>1848</v>
       </c>
-      <c r="G3" s="32" t="s">
+      <c r="G3" s="7" t="s">
         <v>1849</v>
       </c>
-      <c r="H3" s="32" t="s">
-        <v>69</v>
-      </c>
-      <c r="I3" s="32" t="s">
+      <c r="H3" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I3" s="7" t="s">
         <v>1850</v>
       </c>
-      <c r="J3" s="32" t="s">
+      <c r="J3" s="7" t="s">
         <v>1851</v>
       </c>
-      <c r="K3" s="32" t="s">
+      <c r="K3" s="7" t="s">
         <v>1841</v>
       </c>
-      <c r="L3" s="32" t="s">
+      <c r="L3" s="7" t="s">
         <v>1910</v>
       </c>
-      <c r="M3" s="32" t="s">
+      <c r="M3" s="7" t="s">
         <v>1852</v>
       </c>
-      <c r="N3" s="32" t="s">
+      <c r="N3" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:14">
-      <c r="A4" s="32" t="s">
+      <c r="A4" s="7" t="s">
         <v>1853</v>
       </c>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="7" t="s">
         <v>1854</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="7" t="s">
         <v>1855</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="D4" s="7" t="s">
         <v>1856</v>
       </c>
-      <c r="E4" s="32" t="s">
+      <c r="E4" s="7" t="s">
         <v>1857</v>
       </c>
-      <c r="F4" s="32" t="s">
+      <c r="F4" s="7" t="s">
         <v>1858</v>
       </c>
-      <c r="G4" s="32" t="s">
+      <c r="G4" s="7" t="s">
         <v>1859</v>
       </c>
-      <c r="H4" s="32" t="s">
-        <v>69</v>
-      </c>
-      <c r="I4" s="32" t="s">
+      <c r="H4" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I4" s="7" t="s">
         <v>1860</v>
       </c>
-      <c r="J4" s="32" t="s">
+      <c r="J4" s="7" t="s">
         <v>1861</v>
       </c>
-      <c r="K4" s="32" t="s">
+      <c r="K4" s="7" t="s">
         <v>1862</v>
       </c>
-      <c r="L4" s="32" t="s">
+      <c r="L4" s="7" t="s">
         <v>1910</v>
       </c>
-      <c r="M4" s="32" t="s">
+      <c r="M4" s="7" t="s">
         <v>1863</v>
       </c>
-      <c r="N4" s="32" t="s">
+      <c r="N4" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:14">
-      <c r="A5" s="32" t="s">
+      <c r="A5" s="7" t="s">
         <v>1864</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="7" t="s">
         <v>1865</v>
       </c>
-      <c r="C5" s="32" t="s">
+      <c r="C5" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="32" t="s">
+      <c r="D5" s="7" t="s">
         <v>1866</v>
       </c>
-      <c r="E5" s="32" t="s">
+      <c r="E5" s="7" t="s">
         <v>1867</v>
       </c>
-      <c r="F5" s="32" t="s">
+      <c r="F5" s="7" t="s">
         <v>1868</v>
       </c>
-      <c r="G5" s="32" t="s">
+      <c r="G5" s="7" t="s">
         <v>1869</v>
       </c>
-      <c r="H5" s="32" t="s">
-        <v>69</v>
-      </c>
-      <c r="I5" s="33" t="s">
+      <c r="H5" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I5" s="15" t="s">
         <v>1870</v>
       </c>
-      <c r="J5" s="33" t="s">
+      <c r="J5" s="15" t="s">
         <v>1871</v>
       </c>
-      <c r="K5" s="32" t="s">
+      <c r="K5" s="7" t="s">
         <v>1841</v>
       </c>
-      <c r="L5" s="32" t="s">
+      <c r="L5" s="7" t="s">
         <v>1910</v>
       </c>
-      <c r="M5" s="32" t="s">
+      <c r="M5" s="7" t="s">
         <v>1866</v>
       </c>
-      <c r="N5" s="32" t="s">
+      <c r="N5" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:14">
-      <c r="A6" s="32" t="s">
+      <c r="A6" s="7" t="s">
         <v>1872</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="B6" s="7" t="s">
         <v>1873</v>
       </c>
-      <c r="C6" s="32" t="s">
+      <c r="C6" s="7" t="s">
         <v>1874</v>
       </c>
-      <c r="D6" s="32" t="s">
+      <c r="D6" s="7" t="s">
         <v>1875</v>
       </c>
-      <c r="E6" s="32" t="s">
+      <c r="E6" s="7" t="s">
         <v>1876</v>
       </c>
-      <c r="F6" s="32" t="s">
+      <c r="F6" s="7" t="s">
         <v>1877</v>
       </c>
-      <c r="G6" s="32" t="s">
+      <c r="G6" s="7" t="s">
         <v>1878</v>
       </c>
-      <c r="H6" s="32" t="s">
-        <v>69</v>
-      </c>
-      <c r="I6" s="31" t="s">
+      <c r="H6" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>1879</v>
       </c>
-      <c r="J6" s="31" t="s">
+      <c r="J6" s="3" t="s">
         <v>1880</v>
       </c>
-      <c r="K6" s="32" t="s">
+      <c r="K6" s="7" t="s">
         <v>1841</v>
       </c>
-      <c r="L6" s="32" t="s">
+      <c r="L6" s="7" t="s">
         <v>1910</v>
       </c>
-      <c r="M6" s="31" t="s">
+      <c r="M6" s="3" t="s">
         <v>1881</v>
       </c>
-      <c r="N6" s="32" t="s">
+      <c r="N6" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7" s="32" t="s">
+      <c r="A7" s="7" t="s">
         <v>1882</v>
       </c>
-      <c r="B7" s="31" t="s">
+      <c r="B7" s="3" t="s">
         <v>1883</v>
       </c>
-      <c r="C7" s="35" t="s">
+      <c r="C7" s="16" t="s">
         <v>1884</v>
       </c>
-      <c r="D7" s="35" t="s">
+      <c r="D7" s="16" t="s">
         <v>1885</v>
       </c>
-      <c r="E7" s="31" t="s">
+      <c r="E7" s="3" t="s">
         <v>1886</v>
       </c>
-      <c r="F7" s="35" t="s">
+      <c r="F7" s="16" t="s">
         <v>1887</v>
       </c>
-      <c r="G7" s="35" t="s">
+      <c r="G7" s="16" t="s">
         <v>1888</v>
       </c>
-      <c r="H7" s="35" t="s">
+      <c r="H7" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I7" s="31" t="s">
+      <c r="I7" s="3" t="s">
         <v>1889</v>
       </c>
-      <c r="J7" s="31" t="s">
+      <c r="J7" s="3" t="s">
         <v>1890</v>
       </c>
-      <c r="K7" s="35" t="s">
+      <c r="K7" s="16" t="s">
         <v>1841</v>
       </c>
-      <c r="L7" s="32" t="s">
+      <c r="L7" s="7" t="s">
         <v>1910</v>
       </c>
-      <c r="M7" s="35" t="s">
+      <c r="M7" s="16" t="s">
         <v>1891</v>
       </c>
-      <c r="N7" s="32" t="s">
+      <c r="N7" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:14">
-      <c r="A8" s="35" t="s">
+      <c r="A8" s="16" t="s">
         <v>1892</v>
       </c>
-      <c r="B8" s="36" t="s">
+      <c r="B8" s="17" t="s">
         <v>1893</v>
       </c>
-      <c r="C8" s="35" t="s">
+      <c r="C8" s="16" t="s">
         <v>1894</v>
       </c>
-      <c r="D8" s="36" t="s">
+      <c r="D8" s="17" t="s">
         <v>1895</v>
       </c>
-      <c r="E8" s="36" t="s">
+      <c r="E8" s="17" t="s">
         <v>1896</v>
       </c>
-      <c r="F8" s="35" t="s">
+      <c r="F8" s="16" t="s">
         <v>1897</v>
       </c>
-      <c r="G8" s="35" t="s">
+      <c r="G8" s="16" t="s">
         <v>1898</v>
       </c>
-      <c r="H8" s="35" t="s">
+      <c r="H8" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I8" s="37" t="s">
+      <c r="I8" s="18" t="s">
         <v>1899</v>
       </c>
-      <c r="J8" s="37" t="s">
+      <c r="J8" s="18" t="s">
         <v>1900</v>
       </c>
-      <c r="K8" s="35" t="s">
+      <c r="K8" s="16" t="s">
         <v>1841</v>
       </c>
-      <c r="L8" s="32" t="s">
+      <c r="L8" s="7" t="s">
         <v>1910</v>
       </c>
-      <c r="M8" s="35" t="s">
+      <c r="M8" s="16" t="s">
         <v>1895</v>
       </c>
-      <c r="N8" s="32" t="s">
+      <c r="N8" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:14">
-      <c r="A9" s="35" t="s">
+      <c r="A9" s="16" t="s">
         <v>1901</v>
       </c>
-      <c r="B9" s="36" t="s">
+      <c r="B9" s="17" t="s">
         <v>1902</v>
       </c>
-      <c r="C9" s="35" t="s">
+      <c r="C9" s="16" t="s">
         <v>1903</v>
       </c>
-      <c r="D9" s="35" t="s">
+      <c r="D9" s="16" t="s">
         <v>1904</v>
       </c>
-      <c r="E9" s="31" t="s">
+      <c r="E9" s="3" t="s">
         <v>1905</v>
       </c>
-      <c r="F9" s="31" t="s">
+      <c r="F9" s="3" t="s">
         <v>1906</v>
       </c>
-      <c r="G9" s="31" t="s">
+      <c r="G9" s="3" t="s">
         <v>1907</v>
       </c>
-      <c r="H9" s="32" t="s">
-        <v>69</v>
-      </c>
-      <c r="I9" s="31" t="s">
+      <c r="H9" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>1908</v>
       </c>
-      <c r="J9" s="31" t="s">
+      <c r="J9" s="3" t="s">
         <v>1909</v>
       </c>
-      <c r="K9" s="35" t="s">
+      <c r="K9" s="16" t="s">
         <v>1841</v>
       </c>
-      <c r="L9" s="32" t="s">
+      <c r="L9" s="7" t="s">
         <v>1910</v>
       </c>
-      <c r="M9" s="31" t="s">
+      <c r="M9" s="3" t="s">
         <v>1904</v>
       </c>
-      <c r="N9" s="32" t="s">
+      <c r="N9" s="7" t="s">
         <v>25</v>
       </c>
     </row>
@@ -18157,530 +21845,530 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:14" ht="16" customHeight="1">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="39" t="s">
+      <c r="C1" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="39" t="s">
+      <c r="D1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="39" t="s">
+      <c r="E1" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="39" t="s">
+      <c r="F1" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="39" t="s">
+      <c r="G1" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="39" t="s">
+      <c r="H1" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="39" t="s">
+      <c r="I1" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="39" t="s">
+      <c r="J1" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="39" t="s">
+      <c r="K1" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="39" t="s">
+      <c r="L1" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="39" t="s">
+      <c r="M1" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="39" t="s">
+      <c r="N1" s="25" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="16" customHeight="1">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="7" t="s">
         <v>1911</v>
       </c>
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="7" t="s">
         <v>1912</v>
       </c>
-      <c r="C2" s="40" t="s">
+      <c r="C2" s="7" t="s">
         <v>1913</v>
       </c>
-      <c r="D2" s="41" t="s">
+      <c r="D2" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="E2" s="40" t="s">
+      <c r="E2" s="7" t="s">
         <v>1914</v>
       </c>
-      <c r="F2" s="40" t="s">
+      <c r="F2" s="7" t="s">
         <v>1858</v>
       </c>
-      <c r="G2" s="40" t="s">
+      <c r="G2" s="7" t="s">
         <v>1915</v>
       </c>
-      <c r="H2" s="40" t="s">
-        <v>69</v>
-      </c>
-      <c r="I2" s="40" t="s">
+      <c r="H2" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I2" s="7" t="s">
         <v>1916</v>
       </c>
-      <c r="J2" s="40" t="s">
+      <c r="J2" s="7" t="s">
         <v>1917</v>
       </c>
-      <c r="K2" s="40" t="s">
+      <c r="K2" s="7" t="s">
         <v>1918</v>
       </c>
-      <c r="L2" s="40" t="s">
+      <c r="L2" s="7" t="s">
         <v>1910</v>
       </c>
-      <c r="M2" s="41" t="s">
+      <c r="M2" s="13" t="s">
         <v>1919</v>
       </c>
-      <c r="N2" s="40" t="s">
+      <c r="N2" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="16" customHeight="1">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="7" t="s">
         <v>1920</v>
       </c>
-      <c r="B3" s="40" t="s">
+      <c r="B3" s="7" t="s">
         <v>1921</v>
       </c>
-      <c r="C3" s="40" t="s">
+      <c r="C3" s="7" t="s">
         <v>1922</v>
       </c>
-      <c r="D3" s="40" t="s">
+      <c r="D3" s="7" t="s">
         <v>1923</v>
       </c>
-      <c r="E3" s="40" t="s">
+      <c r="E3" s="7" t="s">
         <v>1924</v>
       </c>
-      <c r="F3" s="42" t="s">
+      <c r="F3" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="40" t="s">
+      <c r="G3" s="7" t="s">
         <v>1925</v>
       </c>
-      <c r="H3" s="40" t="s">
-        <v>69</v>
-      </c>
-      <c r="I3" s="43" t="s">
+      <c r="H3" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I3" s="15" t="s">
         <v>1926</v>
       </c>
-      <c r="J3" s="40" t="s">
+      <c r="J3" s="7" t="s">
         <v>1927</v>
       </c>
-      <c r="K3" s="40" t="s">
+      <c r="K3" s="7" t="s">
         <v>1918</v>
       </c>
-      <c r="L3" s="52" t="s">
+      <c r="L3" s="7" t="s">
         <v>1910</v>
       </c>
-      <c r="M3" s="40" t="s">
+      <c r="M3" s="7" t="s">
         <v>1923</v>
       </c>
-      <c r="N3" s="52" t="s">
+      <c r="N3" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="16" customHeight="1">
-      <c r="A4" s="40" t="s">
+      <c r="A4" s="7" t="s">
         <v>1928</v>
       </c>
-      <c r="B4" s="40" t="s">
+      <c r="B4" s="7" t="s">
         <v>1929</v>
       </c>
-      <c r="C4" s="40" t="s">
+      <c r="C4" s="7" t="s">
         <v>1930</v>
       </c>
-      <c r="D4" s="40" t="s">
+      <c r="D4" s="7" t="s">
         <v>1904</v>
       </c>
-      <c r="E4" s="40" t="s">
+      <c r="E4" s="7" t="s">
         <v>1931</v>
       </c>
-      <c r="F4" s="40" t="s">
+      <c r="F4" s="7" t="s">
         <v>1932</v>
       </c>
-      <c r="G4" s="40" t="s">
+      <c r="G4" s="7" t="s">
         <v>1933</v>
       </c>
-      <c r="H4" s="40" t="s">
-        <v>69</v>
-      </c>
-      <c r="I4" s="40" t="s">
+      <c r="H4" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I4" s="7" t="s">
         <v>1934</v>
       </c>
-      <c r="J4" s="40" t="s">
+      <c r="J4" s="7" t="s">
         <v>1935</v>
       </c>
-      <c r="K4" s="40" t="s">
+      <c r="K4" s="7" t="s">
         <v>1918</v>
       </c>
-      <c r="L4" s="52" t="s">
+      <c r="L4" s="7" t="s">
         <v>1910</v>
       </c>
-      <c r="M4" s="40" t="s">
+      <c r="M4" s="7" t="s">
         <v>1904</v>
       </c>
-      <c r="N4" s="52" t="s">
+      <c r="N4" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="16" customHeight="1">
-      <c r="A5" s="40" t="s">
+      <c r="A5" s="7" t="s">
         <v>1936</v>
       </c>
-      <c r="B5" s="40" t="s">
+      <c r="B5" s="7" t="s">
         <v>1937</v>
       </c>
-      <c r="C5" s="40" t="s">
+      <c r="C5" s="7" t="s">
         <v>1938</v>
       </c>
-      <c r="D5" s="40" t="s">
+      <c r="D5" s="7" t="s">
         <v>1856</v>
       </c>
-      <c r="E5" s="40" t="s">
+      <c r="E5" s="7" t="s">
         <v>1939</v>
       </c>
-      <c r="F5" s="40" t="s">
+      <c r="F5" s="7" t="s">
         <v>1877</v>
       </c>
-      <c r="G5" s="40" t="s">
+      <c r="G5" s="7" t="s">
         <v>1940</v>
       </c>
-      <c r="H5" s="40" t="s">
-        <v>69</v>
-      </c>
-      <c r="I5" s="45" t="s">
+      <c r="H5" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I5" s="26" t="s">
         <v>1941</v>
       </c>
-      <c r="J5" s="45" t="s">
+      <c r="J5" s="26" t="s">
         <v>1942</v>
       </c>
-      <c r="K5" s="40" t="s">
+      <c r="K5" s="7" t="s">
         <v>1943</v>
       </c>
-      <c r="L5" s="52" t="s">
+      <c r="L5" s="7" t="s">
         <v>1910</v>
       </c>
-      <c r="M5" s="41" t="s">
+      <c r="M5" s="13" t="s">
         <v>1856</v>
       </c>
-      <c r="N5" s="52" t="s">
+      <c r="N5" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="16" customHeight="1">
-      <c r="A6" s="40" t="s">
+      <c r="A6" s="7" t="s">
         <v>1944</v>
       </c>
-      <c r="B6" s="44" t="s">
+      <c r="B6" s="3" t="s">
         <v>1945</v>
       </c>
-      <c r="C6" s="40" t="s">
+      <c r="C6" s="7" t="s">
         <v>1946</v>
       </c>
-      <c r="D6" s="40" t="s">
+      <c r="D6" s="7" t="s">
         <v>1947</v>
       </c>
-      <c r="E6" s="44" t="s">
+      <c r="E6" s="3" t="s">
         <v>1948</v>
       </c>
-      <c r="F6" s="44" t="s">
+      <c r="F6" s="3" t="s">
         <v>1868</v>
       </c>
-      <c r="G6" s="44" t="s">
+      <c r="G6" s="3" t="s">
         <v>1949</v>
       </c>
-      <c r="H6" s="40" t="s">
-        <v>69</v>
-      </c>
-      <c r="I6" s="44" t="s">
+      <c r="H6" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>1950</v>
       </c>
-      <c r="J6" s="44" t="s">
+      <c r="J6" s="3" t="s">
         <v>1951</v>
       </c>
-      <c r="K6" s="40" t="s">
+      <c r="K6" s="7" t="s">
         <v>1918</v>
       </c>
-      <c r="L6" s="52" t="s">
+      <c r="L6" s="7" t="s">
         <v>1910</v>
       </c>
-      <c r="M6" s="40" t="s">
+      <c r="M6" s="7" t="s">
         <v>1904</v>
       </c>
-      <c r="N6" s="52" t="s">
+      <c r="N6" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="16" customHeight="1">
-      <c r="A7" s="40" t="s">
+      <c r="A7" s="7" t="s">
         <v>1952</v>
       </c>
-      <c r="B7" s="38" t="s">
+      <c r="B7" s="3" t="s">
         <v>1953</v>
       </c>
-      <c r="C7" s="40" t="s">
+      <c r="C7" s="7" t="s">
         <v>1954</v>
       </c>
-      <c r="D7" s="40" t="s">
+      <c r="D7" s="7" t="s">
         <v>1955</v>
       </c>
-      <c r="E7" s="40" t="s">
+      <c r="E7" s="7" t="s">
         <v>1956</v>
       </c>
-      <c r="F7" s="40" t="s">
+      <c r="F7" s="7" t="s">
         <v>1957</v>
       </c>
-      <c r="G7" s="40" t="s">
+      <c r="G7" s="7" t="s">
         <v>1958</v>
       </c>
-      <c r="H7" s="40" t="s">
+      <c r="H7" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="I7" s="48" t="s">
+      <c r="I7" s="18" t="s">
         <v>1959</v>
       </c>
-      <c r="J7" s="48" t="s">
+      <c r="J7" s="18" t="s">
         <v>1960</v>
       </c>
-      <c r="K7" s="40" t="s">
+      <c r="K7" s="7" t="s">
         <v>1918</v>
       </c>
-      <c r="L7" s="52" t="s">
+      <c r="L7" s="7" t="s">
         <v>1910</v>
       </c>
-      <c r="M7" s="40" t="s">
+      <c r="M7" s="7" t="s">
         <v>1955</v>
       </c>
-      <c r="N7" s="52" t="s">
+      <c r="N7" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="16" customHeight="1">
-      <c r="A8" s="40" t="s">
+      <c r="A8" s="7" t="s">
         <v>1961</v>
       </c>
-      <c r="B8" s="38" t="s">
+      <c r="B8" s="3" t="s">
         <v>1962</v>
       </c>
-      <c r="C8" s="40" t="s">
+      <c r="C8" s="7" t="s">
         <v>1874</v>
       </c>
-      <c r="D8" s="40" t="s">
+      <c r="D8" s="7" t="s">
         <v>1963</v>
       </c>
-      <c r="E8" s="38" t="s">
+      <c r="E8" s="3" t="s">
         <v>1964</v>
       </c>
-      <c r="F8" s="40" t="s">
+      <c r="F8" s="7" t="s">
         <v>1965</v>
       </c>
-      <c r="G8" s="40" t="s">
+      <c r="G8" s="7" t="s">
         <v>1966</v>
       </c>
-      <c r="H8" s="40" t="s">
-        <v>69</v>
-      </c>
-      <c r="I8" s="48" t="s">
+      <c r="H8" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I8" s="18" t="s">
         <v>1967</v>
       </c>
-      <c r="J8" s="38" t="s">
+      <c r="J8" s="3" t="s">
         <v>1968</v>
       </c>
-      <c r="K8" s="40" t="s">
+      <c r="K8" s="7" t="s">
         <v>1918</v>
       </c>
-      <c r="L8" s="52" t="s">
+      <c r="L8" s="7" t="s">
         <v>1910</v>
       </c>
-      <c r="M8" s="40" t="s">
+      <c r="M8" s="7" t="s">
         <v>1904</v>
       </c>
-      <c r="N8" s="52" t="s">
+      <c r="N8" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="16" customHeight="1">
-      <c r="A9" s="40" t="s">
+      <c r="A9" s="7" t="s">
         <v>1969</v>
       </c>
-      <c r="B9" s="38" t="s">
+      <c r="B9" s="3" t="s">
         <v>1970</v>
       </c>
-      <c r="C9" s="40" t="s">
+      <c r="C9" s="7" t="s">
         <v>1971</v>
       </c>
-      <c r="D9" s="40" t="s">
+      <c r="D9" s="7" t="s">
         <v>1963</v>
       </c>
-      <c r="E9" s="40" t="s">
+      <c r="E9" s="7" t="s">
         <v>1972</v>
       </c>
-      <c r="F9" s="40" t="s">
+      <c r="F9" s="7" t="s">
         <v>1973</v>
       </c>
-      <c r="G9" s="40" t="s">
+      <c r="G9" s="7" t="s">
         <v>1974</v>
       </c>
-      <c r="H9" s="40" t="s">
-        <v>69</v>
-      </c>
-      <c r="I9" s="48" t="s">
+      <c r="H9" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I9" s="18" t="s">
         <v>1975</v>
       </c>
-      <c r="J9" s="48" t="s">
+      <c r="J9" s="18" t="s">
         <v>1976</v>
       </c>
-      <c r="K9" s="40" t="s">
+      <c r="K9" s="7" t="s">
         <v>1918</v>
       </c>
-      <c r="L9" s="52" t="s">
+      <c r="L9" s="7" t="s">
         <v>1910</v>
       </c>
-      <c r="M9" s="40" t="s">
+      <c r="M9" s="7" t="s">
         <v>1904</v>
       </c>
-      <c r="N9" s="52" t="s">
+      <c r="N9" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="16" customHeight="1">
-      <c r="A10" s="46" t="s">
+      <c r="A10" s="16" t="s">
         <v>1977</v>
       </c>
-      <c r="B10" s="38" t="s">
+      <c r="B10" s="3" t="s">
         <v>1978</v>
       </c>
-      <c r="C10" s="48" t="s">
+      <c r="C10" s="18" t="s">
         <v>1979</v>
       </c>
-      <c r="D10" s="47" t="s">
+      <c r="D10" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="E10" s="47" t="s">
+      <c r="E10" s="17" t="s">
         <v>1980</v>
       </c>
-      <c r="F10" s="38" t="s">
+      <c r="F10" s="3" t="s">
         <v>1981</v>
       </c>
-      <c r="G10" s="46" t="s">
+      <c r="G10" s="16" t="s">
         <v>1982</v>
       </c>
-      <c r="H10" s="46" t="s">
-        <v>69</v>
-      </c>
-      <c r="I10" s="48" t="s">
+      <c r="H10" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="I10" s="18" t="s">
         <v>1983</v>
       </c>
-      <c r="J10" s="38" t="s">
+      <c r="J10" s="3" t="s">
         <v>1984</v>
       </c>
-      <c r="K10" s="40" t="s">
+      <c r="K10" s="7" t="s">
         <v>1918</v>
       </c>
-      <c r="L10" s="52" t="s">
+      <c r="L10" s="7" t="s">
         <v>1910</v>
       </c>
-      <c r="M10" s="46" t="s">
+      <c r="M10" s="16" t="s">
         <v>1985</v>
       </c>
-      <c r="N10" s="52" t="s">
+      <c r="N10" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="16" customHeight="1">
-      <c r="A11" s="46" t="s">
+      <c r="A11" s="16" t="s">
         <v>1986</v>
       </c>
-      <c r="B11" s="38" t="s">
+      <c r="B11" s="3" t="s">
         <v>1987</v>
       </c>
-      <c r="C11" s="49" t="s">
+      <c r="C11" s="7" t="s">
         <v>1988</v>
       </c>
-      <c r="D11" s="47" t="s">
+      <c r="D11" s="17" t="s">
         <v>1989</v>
       </c>
-      <c r="E11" s="47" t="s">
+      <c r="E11" s="17" t="s">
         <v>1990</v>
       </c>
-      <c r="F11" s="47" t="s">
+      <c r="F11" s="17" t="s">
         <v>1957</v>
       </c>
-      <c r="G11" s="47" t="s">
+      <c r="G11" s="17" t="s">
         <v>1991</v>
       </c>
-      <c r="H11" s="40" t="s">
+      <c r="H11" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="I11" s="48" t="s">
+      <c r="I11" s="18" t="s">
         <v>1992</v>
       </c>
-      <c r="J11" s="38" t="s">
+      <c r="J11" s="3" t="s">
         <v>1993</v>
       </c>
-      <c r="K11" s="40" t="s">
+      <c r="K11" s="7" t="s">
         <v>1918</v>
       </c>
-      <c r="L11" s="52" t="s">
+      <c r="L11" s="7" t="s">
         <v>1910</v>
       </c>
-      <c r="M11" s="46" t="s">
+      <c r="M11" s="16" t="s">
         <v>1994</v>
       </c>
-      <c r="N11" s="52" t="s">
+      <c r="N11" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="16" customHeight="1">
-      <c r="A12" s="46" t="s">
+      <c r="A12" s="16" t="s">
         <v>1995</v>
       </c>
-      <c r="B12" s="38" t="s">
+      <c r="B12" s="3" t="s">
         <v>1996</v>
       </c>
-      <c r="C12" s="49" t="s">
+      <c r="C12" s="7" t="s">
         <v>1997</v>
       </c>
-      <c r="D12" s="38" t="s">
+      <c r="D12" s="3" t="s">
         <v>1875</v>
       </c>
-      <c r="E12" s="47" t="s">
+      <c r="E12" s="17" t="s">
         <v>1998</v>
       </c>
-      <c r="F12" s="38" t="s">
+      <c r="F12" s="3" t="s">
         <v>1999</v>
       </c>
-      <c r="G12" s="47" t="s">
+      <c r="G12" s="17" t="s">
         <v>2000</v>
       </c>
-      <c r="H12" s="46" t="s">
-        <v>69</v>
-      </c>
-      <c r="I12" s="48" t="s">
+      <c r="H12" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="I12" s="18" t="s">
         <v>2001</v>
       </c>
-      <c r="J12" s="38" t="s">
+      <c r="J12" s="3" t="s">
         <v>2002</v>
       </c>
-      <c r="K12" s="40" t="s">
+      <c r="K12" s="7" t="s">
         <v>1918</v>
       </c>
-      <c r="L12" s="52" t="s">
+      <c r="L12" s="7" t="s">
         <v>1910</v>
       </c>
-      <c r="M12" s="40" t="s">
+      <c r="M12" s="7" t="s">
         <v>1881</v>
       </c>
-      <c r="N12" s="52" t="s">
+      <c r="N12" s="7" t="s">
         <v>25</v>
       </c>
     </row>
@@ -18708,1012 +22396,1012 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:14" ht="14.5" customHeight="1">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="51" t="s">
+      <c r="B1" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="51" t="s">
+      <c r="C1" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="51" t="s">
+      <c r="D1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="51" t="s">
+      <c r="E1" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="51" t="s">
+      <c r="F1" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="51" t="s">
+      <c r="G1" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="51" t="s">
+      <c r="H1" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="51" t="s">
+      <c r="I1" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="51" t="s">
+      <c r="J1" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="51" t="s">
+      <c r="K1" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="51" t="s">
+      <c r="L1" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="51" t="s">
+      <c r="M1" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="51" t="s">
+      <c r="N1" s="25" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:14">
-      <c r="A2" s="52" t="s">
+      <c r="A2" s="7" t="s">
         <v>2003</v>
       </c>
-      <c r="B2" s="52" t="s">
+      <c r="B2" s="7" t="s">
         <v>2004</v>
       </c>
-      <c r="C2" s="52" t="s">
+      <c r="C2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="55" t="s">
+      <c r="D2" s="13" t="s">
         <v>2005</v>
       </c>
-      <c r="E2" s="52" t="s">
+      <c r="E2" s="7" t="s">
         <v>2006</v>
       </c>
-      <c r="F2" s="52" t="s">
+      <c r="F2" s="7" t="s">
         <v>2007</v>
       </c>
-      <c r="G2" s="52" t="s">
+      <c r="G2" s="7" t="s">
         <v>2008</v>
       </c>
-      <c r="H2" s="52" t="s">
-        <v>69</v>
-      </c>
-      <c r="I2" s="52" t="s">
+      <c r="H2" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I2" s="7" t="s">
         <v>2009</v>
       </c>
-      <c r="J2" s="52" t="s">
+      <c r="J2" s="7" t="s">
         <v>2010</v>
       </c>
-      <c r="K2" s="52" t="s">
+      <c r="K2" s="7" t="s">
         <v>2011</v>
       </c>
-      <c r="L2" s="52" t="s">
+      <c r="L2" s="7" t="s">
         <v>1910</v>
       </c>
-      <c r="M2" s="52"/>
-      <c r="N2" s="52" t="s">
+      <c r="M2" s="7"/>
+      <c r="N2" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:14">
-      <c r="A3" s="52" t="s">
+      <c r="A3" s="7" t="s">
         <v>2012</v>
       </c>
-      <c r="B3" s="52" t="s">
+      <c r="B3" s="7" t="s">
         <v>2013</v>
       </c>
-      <c r="C3" s="52" t="s">
+      <c r="C3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="52" t="s">
+      <c r="D3" s="7" t="s">
         <v>2014</v>
       </c>
-      <c r="E3" s="52" t="s">
+      <c r="E3" s="7" t="s">
         <v>2015</v>
       </c>
-      <c r="F3" s="52" t="s">
+      <c r="F3" s="7" t="s">
         <v>2016</v>
       </c>
-      <c r="G3" s="52" t="s">
+      <c r="G3" s="7" t="s">
         <v>2017</v>
       </c>
-      <c r="H3" s="52" t="s">
-        <v>69</v>
-      </c>
-      <c r="I3" s="53" t="s">
+      <c r="H3" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I3" s="10" t="s">
         <v>2018</v>
       </c>
-      <c r="J3" s="53" t="s">
+      <c r="J3" s="10" t="s">
         <v>2019</v>
       </c>
-      <c r="K3" s="52" t="s">
+      <c r="K3" s="7" t="s">
         <v>2011</v>
       </c>
-      <c r="L3" s="52" t="s">
+      <c r="L3" s="7" t="s">
         <v>1910</v>
       </c>
-      <c r="M3" s="52" t="s">
+      <c r="M3" s="7" t="s">
         <v>2014</v>
       </c>
-      <c r="N3" s="52" t="s">
+      <c r="N3" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:14">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="7" t="s">
         <v>2020</v>
       </c>
-      <c r="B4" s="52" t="s">
+      <c r="B4" s="7" t="s">
         <v>2021</v>
       </c>
-      <c r="C4" s="55" t="s">
+      <c r="C4" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="55" t="s">
+      <c r="D4" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="E4" s="52" t="s">
+      <c r="E4" s="7" t="s">
         <v>2022</v>
       </c>
-      <c r="F4" s="52" t="s">
+      <c r="F4" s="7" t="s">
         <v>2023</v>
       </c>
-      <c r="G4" s="52" t="s">
+      <c r="G4" s="7" t="s">
         <v>2024</v>
       </c>
-      <c r="H4" s="52" t="s">
-        <v>69</v>
-      </c>
-      <c r="I4" s="57" t="s">
+      <c r="H4" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I4" s="15" t="s">
         <v>2025</v>
       </c>
-      <c r="J4" s="57" t="s">
+      <c r="J4" s="15" t="s">
         <v>2026</v>
       </c>
-      <c r="K4" s="52" t="s">
+      <c r="K4" s="7" t="s">
         <v>2011</v>
       </c>
-      <c r="L4" s="52" t="s">
+      <c r="L4" s="7" t="s">
         <v>1910</v>
       </c>
-      <c r="M4" s="52" t="s">
+      <c r="M4" s="7" t="s">
         <v>2027</v>
       </c>
-      <c r="N4" s="52" t="s">
+      <c r="N4" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:14">
-      <c r="A5" s="52" t="s">
+      <c r="A5" s="7" t="s">
         <v>2028</v>
       </c>
-      <c r="B5" s="52" t="s">
+      <c r="B5" s="7" t="s">
         <v>2029</v>
       </c>
-      <c r="C5" s="55" t="s">
+      <c r="C5" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="52" t="s">
+      <c r="D5" s="7" t="s">
         <v>2030</v>
       </c>
-      <c r="E5" s="59" t="s">
+      <c r="E5" s="16" t="s">
         <v>2031</v>
       </c>
-      <c r="F5" s="52" t="s">
+      <c r="F5" s="7" t="s">
         <v>1858</v>
       </c>
-      <c r="G5" s="52" t="s">
+      <c r="G5" s="7" t="s">
         <v>2032</v>
       </c>
-      <c r="H5" s="52" t="s">
-        <v>69</v>
-      </c>
-      <c r="I5" s="57" t="s">
+      <c r="H5" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I5" s="15" t="s">
         <v>2033</v>
       </c>
-      <c r="J5" s="57" t="s">
+      <c r="J5" s="15" t="s">
         <v>2034</v>
       </c>
-      <c r="K5" s="52" t="s">
+      <c r="K5" s="7" t="s">
         <v>1918</v>
       </c>
-      <c r="L5" s="52" t="s">
+      <c r="L5" s="7" t="s">
         <v>1910</v>
       </c>
-      <c r="M5" s="52" t="s">
+      <c r="M5" s="7" t="s">
         <v>2030</v>
       </c>
-      <c r="N5" s="52" t="s">
+      <c r="N5" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:14">
-      <c r="A6" s="52" t="s">
+      <c r="A6" s="7" t="s">
         <v>2035</v>
       </c>
-      <c r="B6" s="52" t="s">
+      <c r="B6" s="7" t="s">
         <v>2036</v>
       </c>
-      <c r="C6" s="55" t="s">
+      <c r="C6" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="52" t="s">
+      <c r="D6" s="7" t="s">
         <v>2037</v>
       </c>
-      <c r="E6" s="52" t="s">
+      <c r="E6" s="7" t="s">
         <v>2038</v>
       </c>
-      <c r="F6" s="52" t="s">
+      <c r="F6" s="7" t="s">
         <v>2039</v>
       </c>
-      <c r="G6" s="52" t="s">
+      <c r="G6" s="7" t="s">
         <v>2040</v>
       </c>
-      <c r="H6" s="52" t="s">
-        <v>69</v>
-      </c>
-      <c r="I6" s="57" t="s">
+      <c r="H6" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I6" s="15" t="s">
         <v>2041</v>
       </c>
-      <c r="J6" s="57" t="s">
+      <c r="J6" s="15" t="s">
         <v>2042</v>
       </c>
-      <c r="K6" s="52" t="s">
+      <c r="K6" s="7" t="s">
         <v>2043</v>
       </c>
-      <c r="L6" s="52" t="s">
+      <c r="L6" s="7" t="s">
         <v>1910</v>
       </c>
-      <c r="M6" s="52" t="s">
+      <c r="M6" s="7" t="s">
         <v>2044</v>
       </c>
-      <c r="N6" s="52" t="s">
+      <c r="N6" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="7" t="s">
         <v>2045</v>
       </c>
-      <c r="B7" s="52" t="s">
+      <c r="B7" s="7" t="s">
         <v>2046</v>
       </c>
-      <c r="C7" s="55" t="s">
+      <c r="C7" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="52" t="s">
+      <c r="D7" s="7" t="s">
         <v>2047</v>
       </c>
-      <c r="E7" s="52" t="s">
+      <c r="E7" s="7" t="s">
         <v>2048</v>
       </c>
-      <c r="F7" s="52" t="s">
+      <c r="F7" s="7" t="s">
         <v>1696</v>
       </c>
-      <c r="G7" s="52" t="s">
+      <c r="G7" s="7" t="s">
         <v>2049</v>
       </c>
-      <c r="H7" s="52" t="s">
-        <v>69</v>
-      </c>
-      <c r="I7" s="52" t="s">
+      <c r="H7" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I7" s="7" t="s">
         <v>2050</v>
       </c>
-      <c r="J7" s="52" t="s">
+      <c r="J7" s="7" t="s">
         <v>2051</v>
       </c>
-      <c r="K7" s="52" t="s">
+      <c r="K7" s="7" t="s">
         <v>2052</v>
       </c>
-      <c r="L7" s="52" t="s">
+      <c r="L7" s="7" t="s">
         <v>1910</v>
       </c>
-      <c r="M7" s="52" t="s">
+      <c r="M7" s="7" t="s">
         <v>2047</v>
       </c>
-      <c r="N7" s="52" t="s">
+      <c r="N7" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:14">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="7" t="s">
         <v>2053</v>
       </c>
-      <c r="B8" s="52" t="s">
+      <c r="B8" s="7" t="s">
         <v>2054</v>
       </c>
-      <c r="C8" s="55" t="s">
+      <c r="C8" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="52" t="s">
+      <c r="D8" s="7" t="s">
         <v>1947</v>
       </c>
-      <c r="E8" s="52" t="s">
+      <c r="E8" s="7" t="s">
         <v>2055</v>
       </c>
-      <c r="F8" s="52" t="s">
+      <c r="F8" s="7" t="s">
         <v>2056</v>
       </c>
-      <c r="G8" s="52" t="s">
+      <c r="G8" s="7" t="s">
         <v>2057</v>
       </c>
-      <c r="H8" s="52" t="s">
-        <v>69</v>
-      </c>
-      <c r="I8" s="52" t="s">
+      <c r="H8" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I8" s="7" t="s">
         <v>2058</v>
       </c>
-      <c r="J8" s="57" t="s">
+      <c r="J8" s="15" t="s">
         <v>2059</v>
       </c>
-      <c r="K8" s="52" t="s">
+      <c r="K8" s="7" t="s">
         <v>2052</v>
       </c>
-      <c r="L8" s="52" t="s">
+      <c r="L8" s="7" t="s">
         <v>1910</v>
       </c>
-      <c r="M8" s="52" t="s">
+      <c r="M8" s="7" t="s">
         <v>2060</v>
       </c>
-      <c r="N8" s="52" t="s">
+      <c r="N8" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:14">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="7" t="s">
         <v>2061</v>
       </c>
-      <c r="B9" s="52" t="s">
+      <c r="B9" s="7" t="s">
         <v>2062</v>
       </c>
-      <c r="C9" s="52" t="s">
+      <c r="C9" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="52" t="s">
+      <c r="D9" s="7" t="s">
         <v>1947</v>
       </c>
-      <c r="E9" s="52" t="s">
+      <c r="E9" s="7" t="s">
         <v>2063</v>
       </c>
-      <c r="F9" s="52" t="s">
+      <c r="F9" s="7" t="s">
         <v>2064</v>
       </c>
-      <c r="G9" s="52" t="s">
+      <c r="G9" s="7" t="s">
         <v>2065</v>
       </c>
-      <c r="H9" s="52" t="s">
-        <v>69</v>
-      </c>
-      <c r="I9" s="57" t="s">
+      <c r="H9" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I9" s="15" t="s">
         <v>2066</v>
       </c>
-      <c r="J9" s="57" t="s">
+      <c r="J9" s="15" t="s">
         <v>2067</v>
       </c>
-      <c r="K9" s="52" t="s">
+      <c r="K9" s="7" t="s">
         <v>2052</v>
       </c>
-      <c r="L9" s="52" t="s">
+      <c r="L9" s="7" t="s">
         <v>1910</v>
       </c>
-      <c r="M9" s="52" t="s">
+      <c r="M9" s="7" t="s">
         <v>1947</v>
       </c>
-      <c r="N9" s="52" t="s">
+      <c r="N9" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:14">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="7" t="s">
         <v>2068</v>
       </c>
-      <c r="B10" s="52" t="s">
+      <c r="B10" s="7" t="s">
         <v>2069</v>
       </c>
-      <c r="C10" s="55" t="s">
+      <c r="C10" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="52" t="s">
+      <c r="D10" s="7" t="s">
         <v>2070</v>
       </c>
-      <c r="E10" s="52" t="s">
+      <c r="E10" s="7" t="s">
         <v>2070</v>
       </c>
-      <c r="F10" s="52" t="s">
+      <c r="F10" s="7" t="s">
         <v>1981</v>
       </c>
-      <c r="G10" s="52" t="s">
+      <c r="G10" s="7" t="s">
         <v>2071</v>
       </c>
-      <c r="H10" s="52" t="s">
-        <v>69</v>
-      </c>
-      <c r="I10" s="52" t="s">
+      <c r="H10" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I10" s="7" t="s">
         <v>2072</v>
       </c>
-      <c r="J10" s="52" t="s">
+      <c r="J10" s="7" t="s">
         <v>2073</v>
       </c>
-      <c r="K10" s="52" t="s">
+      <c r="K10" s="7" t="s">
         <v>2074</v>
       </c>
-      <c r="L10" s="52" t="s">
+      <c r="L10" s="7" t="s">
         <v>1910</v>
       </c>
-      <c r="M10" s="52" t="s">
+      <c r="M10" s="7" t="s">
         <v>1856</v>
       </c>
-      <c r="N10" s="52" t="s">
+      <c r="N10" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:14">
-      <c r="A11" s="52" t="s">
+      <c r="A11" s="7" t="s">
         <v>2075</v>
       </c>
-      <c r="B11" s="52" t="s">
+      <c r="B11" s="7" t="s">
         <v>2076</v>
       </c>
-      <c r="C11" s="55" t="s">
+      <c r="C11" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="52" t="s">
+      <c r="D11" s="7" t="s">
         <v>1856</v>
       </c>
-      <c r="E11" s="52" t="s">
+      <c r="E11" s="7" t="s">
         <v>2077</v>
       </c>
-      <c r="F11" s="52" t="s">
+      <c r="F11" s="7" t="s">
         <v>945</v>
       </c>
-      <c r="G11" s="52" t="s">
+      <c r="G11" s="7" t="s">
         <v>2078</v>
       </c>
-      <c r="H11" s="52" t="s">
-        <v>69</v>
-      </c>
-      <c r="I11" s="52" t="s">
+      <c r="H11" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I11" s="7" t="s">
         <v>2079</v>
       </c>
-      <c r="J11" s="52" t="s">
+      <c r="J11" s="7" t="s">
         <v>2080</v>
       </c>
-      <c r="K11" s="52" t="s">
+      <c r="K11" s="7" t="s">
         <v>2081</v>
       </c>
-      <c r="L11" s="52" t="s">
+      <c r="L11" s="7" t="s">
         <v>1910</v>
       </c>
-      <c r="M11" s="52" t="s">
+      <c r="M11" s="7" t="s">
         <v>1856</v>
       </c>
-      <c r="N11" s="52" t="s">
+      <c r="N11" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:14">
-      <c r="A12" s="52" t="s">
+      <c r="A12" s="7" t="s">
         <v>2082</v>
       </c>
-      <c r="B12" s="52" t="s">
+      <c r="B12" s="7" t="s">
         <v>2083</v>
       </c>
-      <c r="C12" s="55" t="s">
+      <c r="C12" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="52" t="s">
+      <c r="D12" s="7" t="s">
         <v>1856</v>
       </c>
-      <c r="E12" s="52" t="s">
+      <c r="E12" s="7" t="s">
         <v>2084</v>
       </c>
-      <c r="F12" s="52" t="s">
+      <c r="F12" s="7" t="s">
         <v>2085</v>
       </c>
-      <c r="G12" s="52" t="s">
+      <c r="G12" s="7" t="s">
         <v>2086</v>
       </c>
-      <c r="H12" s="52" t="s">
-        <v>69</v>
-      </c>
-      <c r="I12" s="52" t="s">
+      <c r="H12" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I12" s="7" t="s">
         <v>2087</v>
       </c>
-      <c r="J12" s="52" t="s">
+      <c r="J12" s="7" t="s">
         <v>2088</v>
       </c>
-      <c r="K12" s="52" t="s">
+      <c r="K12" s="7" t="s">
         <v>2074</v>
       </c>
-      <c r="L12" s="52" t="s">
+      <c r="L12" s="7" t="s">
         <v>1910</v>
       </c>
-      <c r="M12" s="52" t="s">
+      <c r="M12" s="7" t="s">
         <v>1856</v>
       </c>
-      <c r="N12" s="52" t="s">
+      <c r="N12" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="13.5" customHeight="1">
-      <c r="A13" s="52" t="s">
+      <c r="A13" s="7" t="s">
         <v>2089</v>
       </c>
-      <c r="B13" s="52" t="s">
+      <c r="B13" s="7" t="s">
         <v>2090</v>
       </c>
-      <c r="C13" s="52" t="s">
+      <c r="C13" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="52" t="s">
+      <c r="D13" s="7" t="s">
         <v>2091</v>
       </c>
-      <c r="E13" s="52" t="s">
+      <c r="E13" s="7" t="s">
         <v>2092</v>
       </c>
-      <c r="F13" s="52" t="s">
+      <c r="F13" s="7" t="s">
         <v>2007</v>
       </c>
-      <c r="G13" s="52" t="s">
+      <c r="G13" s="7" t="s">
         <v>2093</v>
       </c>
-      <c r="H13" s="52" t="s">
-        <v>69</v>
-      </c>
-      <c r="I13" s="54" t="s">
+      <c r="H13" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I13" s="11" t="s">
         <v>2094</v>
       </c>
-      <c r="J13" s="54" t="s">
+      <c r="J13" s="11" t="s">
         <v>2095</v>
       </c>
-      <c r="K13" s="52" t="s">
+      <c r="K13" s="7" t="s">
         <v>2096</v>
       </c>
-      <c r="L13" s="52" t="s">
+      <c r="L13" s="7" t="s">
         <v>1910</v>
       </c>
-      <c r="M13" s="52" t="s">
+      <c r="M13" s="7" t="s">
         <v>2091</v>
       </c>
-      <c r="N13" s="52" t="s">
+      <c r="N13" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="15" customHeight="1">
-      <c r="A14" s="52" t="s">
+      <c r="A14" s="7" t="s">
         <v>2097</v>
       </c>
-      <c r="B14" s="56" t="s">
+      <c r="B14" s="14" t="s">
         <v>2098</v>
       </c>
-      <c r="C14" s="52" t="s">
+      <c r="C14" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D14" s="52" t="s">
+      <c r="D14" s="7" t="s">
         <v>2099</v>
       </c>
-      <c r="E14" s="52">
+      <c r="E14" s="7">
         <v>824012823</v>
       </c>
-      <c r="F14" s="52" t="s">
+      <c r="F14" s="7" t="s">
         <v>2100</v>
       </c>
-      <c r="G14" s="52" t="s">
+      <c r="G14" s="7" t="s">
         <v>2101</v>
       </c>
-      <c r="H14" s="52" t="s">
+      <c r="H14" s="7" t="s">
         <v>2102</v>
       </c>
-      <c r="I14" s="57" t="s">
+      <c r="I14" s="15" t="s">
         <v>2103</v>
       </c>
-      <c r="J14" s="57" t="s">
+      <c r="J14" s="15" t="s">
         <v>2104</v>
       </c>
-      <c r="K14" s="52">
+      <c r="K14" s="7">
         <v>824012823</v>
       </c>
-      <c r="L14" s="52" t="s">
+      <c r="L14" s="7" t="s">
         <v>1910</v>
       </c>
-      <c r="M14" s="52" t="s">
+      <c r="M14" s="7" t="s">
         <v>2105</v>
       </c>
-      <c r="N14" s="52" t="s">
+      <c r="N14" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:14">
-      <c r="A15" s="52" t="s">
+      <c r="A15" s="7" t="s">
         <v>2106</v>
       </c>
-      <c r="B15" s="52" t="s">
+      <c r="B15" s="7" t="s">
         <v>2107</v>
       </c>
-      <c r="C15" s="52" t="s">
+      <c r="C15" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="52" t="s">
+      <c r="D15" s="7" t="s">
         <v>1856</v>
       </c>
-      <c r="E15" s="52" t="s">
+      <c r="E15" s="7" t="s">
         <v>2108</v>
       </c>
-      <c r="F15" s="52" t="s">
+      <c r="F15" s="7" t="s">
         <v>2085</v>
       </c>
-      <c r="G15" s="52" t="s">
+      <c r="G15" s="7" t="s">
         <v>2109</v>
       </c>
-      <c r="H15" s="52" t="s">
-        <v>69</v>
-      </c>
-      <c r="I15" s="54" t="s">
+      <c r="H15" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I15" s="11" t="s">
         <v>2110</v>
       </c>
-      <c r="J15" s="54" t="s">
+      <c r="J15" s="11" t="s">
         <v>2111</v>
       </c>
-      <c r="K15" s="52" t="s">
+      <c r="K15" s="7" t="s">
         <v>1943</v>
       </c>
-      <c r="L15" s="52" t="s">
+      <c r="L15" s="7" t="s">
         <v>1910</v>
       </c>
-      <c r="M15" s="52" t="s">
+      <c r="M15" s="7" t="s">
         <v>1856</v>
       </c>
-      <c r="N15" s="52" t="s">
+      <c r="N15" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:14">
-      <c r="A16" s="52" t="s">
+      <c r="A16" s="7" t="s">
         <v>2112</v>
       </c>
-      <c r="B16" s="52" t="s">
+      <c r="B16" s="7" t="s">
         <v>2113</v>
       </c>
-      <c r="C16" s="52" t="s">
+      <c r="C16" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D16" s="52" t="s">
+      <c r="D16" s="7" t="s">
         <v>1856</v>
       </c>
-      <c r="E16" s="52" t="s">
+      <c r="E16" s="7" t="s">
         <v>2114</v>
       </c>
-      <c r="F16" s="52" t="s">
+      <c r="F16" s="7" t="s">
         <v>2023</v>
       </c>
-      <c r="G16" s="52" t="s">
+      <c r="G16" s="7" t="s">
         <v>2115</v>
       </c>
-      <c r="H16" s="52" t="s">
-        <v>69</v>
-      </c>
-      <c r="I16" s="54" t="s">
+      <c r="H16" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I16" s="11" t="s">
         <v>2116</v>
       </c>
-      <c r="J16" s="54" t="s">
+      <c r="J16" s="11" t="s">
         <v>2116</v>
       </c>
-      <c r="K16" s="52" t="s">
+      <c r="K16" s="7" t="s">
         <v>2117</v>
       </c>
-      <c r="L16" s="52" t="s">
+      <c r="L16" s="7" t="s">
         <v>1910</v>
       </c>
-      <c r="M16" s="52" t="s">
+      <c r="M16" s="7" t="s">
         <v>1856</v>
       </c>
-      <c r="N16" s="52" t="s">
+      <c r="N16" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:14">
-      <c r="A17" s="52" t="s">
+      <c r="A17" s="7" t="s">
         <v>2118</v>
       </c>
-      <c r="B17" s="52" t="s">
+      <c r="B17" s="7" t="s">
         <v>2119</v>
       </c>
-      <c r="C17" s="52" t="s">
+      <c r="C17" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="52" t="s">
+      <c r="D17" s="7" t="s">
         <v>2120</v>
       </c>
-      <c r="E17" s="52" t="s">
+      <c r="E17" s="7" t="s">
         <v>2121</v>
       </c>
-      <c r="F17" s="52" t="s">
+      <c r="F17" s="7" t="s">
         <v>1877</v>
       </c>
-      <c r="G17" s="52" t="s">
+      <c r="G17" s="7" t="s">
         <v>2122</v>
       </c>
-      <c r="H17" s="52" t="s">
-        <v>69</v>
-      </c>
-      <c r="I17" s="54" t="s">
+      <c r="H17" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I17" s="11" t="s">
         <v>2123</v>
       </c>
-      <c r="J17" s="54" t="s">
+      <c r="J17" s="11" t="s">
         <v>2124</v>
       </c>
-      <c r="K17" s="52" t="s">
+      <c r="K17" s="7" t="s">
         <v>2125</v>
       </c>
-      <c r="L17" s="52" t="s">
+      <c r="L17" s="7" t="s">
         <v>1910</v>
       </c>
-      <c r="M17" s="52" t="s">
+      <c r="M17" s="7" t="s">
         <v>2120</v>
       </c>
-      <c r="N17" s="52" t="s">
+      <c r="N17" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:14">
-      <c r="A18" s="52" t="s">
+      <c r="A18" s="7" t="s">
         <v>2126</v>
       </c>
-      <c r="B18" s="52" t="s">
+      <c r="B18" s="7" t="s">
         <v>2127</v>
       </c>
-      <c r="C18" s="52" t="s">
+      <c r="C18" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D18" s="52" t="s">
+      <c r="D18" s="7" t="s">
         <v>1856</v>
       </c>
-      <c r="E18" s="52" t="s">
+      <c r="E18" s="7" t="s">
         <v>2128</v>
       </c>
-      <c r="F18" s="58" t="s">
+      <c r="F18" s="3" t="s">
         <v>2129</v>
       </c>
-      <c r="G18" s="58" t="s">
+      <c r="G18" s="3" t="s">
         <v>2130</v>
       </c>
-      <c r="H18" s="52" t="s">
-        <v>69</v>
-      </c>
-      <c r="I18" s="58" t="s">
+      <c r="H18" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>2131</v>
       </c>
-      <c r="J18" s="58" t="s">
+      <c r="J18" s="3" t="s">
         <v>2132</v>
       </c>
-      <c r="K18" s="52" t="s">
+      <c r="K18" s="7" t="s">
         <v>1943</v>
       </c>
-      <c r="L18" s="52" t="s">
+      <c r="L18" s="7" t="s">
         <v>1910</v>
       </c>
-      <c r="M18" s="52" t="s">
+      <c r="M18" s="7" t="s">
         <v>1856</v>
       </c>
-      <c r="N18" s="52" t="s">
+      <c r="N18" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:14">
-      <c r="A19" s="52" t="s">
+      <c r="A19" s="7" t="s">
         <v>2133</v>
       </c>
-      <c r="B19" s="50" t="s">
+      <c r="B19" s="3" t="s">
         <v>2134</v>
       </c>
-      <c r="C19" s="52" t="s">
+      <c r="C19" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D19" s="50" t="s">
+      <c r="D19" s="3" t="s">
         <v>2135</v>
       </c>
-      <c r="E19" s="50" t="s">
+      <c r="E19" s="3" t="s">
         <v>2136</v>
       </c>
-      <c r="F19" s="50" t="s">
+      <c r="F19" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G19" s="50" t="s">
+      <c r="G19" s="3" t="s">
         <v>2137</v>
       </c>
-      <c r="H19" s="52" t="s">
-        <v>69</v>
-      </c>
-      <c r="I19" s="50" t="s">
+      <c r="H19" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>2138</v>
       </c>
-      <c r="J19" s="50" t="s">
+      <c r="J19" s="3" t="s">
         <v>2139</v>
       </c>
-      <c r="K19" s="52" t="s">
+      <c r="K19" s="7" t="s">
         <v>2136</v>
       </c>
-      <c r="L19" s="52" t="s">
+      <c r="L19" s="7" t="s">
         <v>1910</v>
       </c>
-      <c r="M19" s="52" t="s">
+      <c r="M19" s="7" t="s">
         <v>2136</v>
       </c>
-      <c r="N19" s="52" t="s">
+      <c r="N19" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:14">
-      <c r="A20" s="52" t="s">
+      <c r="A20" s="7" t="s">
         <v>2140</v>
       </c>
-      <c r="B20" s="50" t="s">
+      <c r="B20" s="3" t="s">
         <v>2141</v>
       </c>
-      <c r="C20" s="52" t="s">
+      <c r="C20" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D20" s="50" t="s">
+      <c r="D20" s="3" t="s">
         <v>2142</v>
       </c>
-      <c r="E20" s="50" t="s">
+      <c r="E20" s="3" t="s">
         <v>2143</v>
       </c>
-      <c r="F20" s="50" t="s">
+      <c r="F20" s="3" t="s">
         <v>1658</v>
       </c>
-      <c r="G20" s="50" t="s">
+      <c r="G20" s="3" t="s">
         <v>2144</v>
       </c>
-      <c r="H20" s="52" t="s">
-        <v>69</v>
-      </c>
-      <c r="I20" s="50" t="s">
+      <c r="H20" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>2145</v>
       </c>
-      <c r="J20" s="50" t="s">
+      <c r="J20" s="3" t="s">
         <v>2146</v>
       </c>
-      <c r="K20" s="50" t="s">
+      <c r="K20" s="3" t="s">
         <v>2143</v>
       </c>
-      <c r="L20" s="52" t="s">
+      <c r="L20" s="7" t="s">
         <v>1910</v>
       </c>
-      <c r="M20" s="50" t="s">
+      <c r="M20" s="3" t="s">
         <v>2147</v>
       </c>
-      <c r="N20" s="52" t="s">
+      <c r="N20" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:14">
-      <c r="A21" s="59" t="s">
+      <c r="A21" s="16" t="s">
         <v>2148</v>
       </c>
-      <c r="B21" s="50" t="s">
+      <c r="B21" s="3" t="s">
         <v>2149</v>
       </c>
-      <c r="C21" s="52" t="s">
+      <c r="C21" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="50" t="s">
+      <c r="D21" s="3" t="s">
         <v>1856</v>
       </c>
-      <c r="E21" s="50" t="s">
+      <c r="E21" s="3" t="s">
         <v>2150</v>
       </c>
-      <c r="F21" s="50" t="s">
+      <c r="F21" s="3" t="s">
         <v>1858</v>
       </c>
-      <c r="G21" s="50" t="s">
+      <c r="G21" s="3" t="s">
         <v>2151</v>
       </c>
-      <c r="H21" s="59" t="s">
-        <v>69</v>
-      </c>
-      <c r="I21" s="61" t="s">
+      <c r="H21" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="I21" s="18" t="s">
         <v>2152</v>
       </c>
-      <c r="J21" s="50" t="s">
+      <c r="J21" s="3" t="s">
         <v>2153</v>
       </c>
-      <c r="K21" s="60" t="s">
+      <c r="K21" s="17" t="s">
         <v>2154</v>
       </c>
-      <c r="L21" s="52" t="s">
+      <c r="L21" s="7" t="s">
         <v>1910</v>
       </c>
-      <c r="M21" s="52" t="s">
+      <c r="M21" s="7" t="s">
         <v>1856</v>
       </c>
-      <c r="N21" s="52" t="s">
+      <c r="N21" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:14">
-      <c r="A22" s="59" t="s">
+      <c r="A22" s="16" t="s">
         <v>2155</v>
       </c>
-      <c r="B22" s="50" t="s">
+      <c r="B22" s="3" t="s">
         <v>2156</v>
       </c>
-      <c r="C22" s="52" t="s">
+      <c r="C22" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="52" t="s">
+      <c r="D22" s="7" t="s">
         <v>2157</v>
       </c>
-      <c r="E22" s="50" t="s">
+      <c r="E22" s="3" t="s">
         <v>2158</v>
       </c>
-      <c r="F22" s="50" t="s">
+      <c r="F22" s="3" t="s">
         <v>1696</v>
       </c>
-      <c r="G22" s="50" t="s">
+      <c r="G22" s="3" t="s">
         <v>2159</v>
       </c>
-      <c r="H22" s="59" t="s">
-        <v>69</v>
-      </c>
-      <c r="I22" s="50" t="s">
+      <c r="H22" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>2160</v>
       </c>
-      <c r="J22" s="50" t="s">
+      <c r="J22" s="3" t="s">
         <v>2161</v>
       </c>
-      <c r="K22" s="50" t="s">
+      <c r="K22" s="3" t="s">
         <v>2052</v>
       </c>
-      <c r="L22" s="52" t="s">
+      <c r="L22" s="7" t="s">
         <v>1910</v>
       </c>
-      <c r="M22" s="52" t="s">
+      <c r="M22" s="7" t="s">
         <v>1904</v>
       </c>
-      <c r="N22" s="52" t="s">
+      <c r="N22" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:14">
-      <c r="A23" s="59" t="s">
+      <c r="A23" s="16" t="s">
         <v>2162</v>
       </c>
-      <c r="B23" s="50" t="s">
+      <c r="B23" s="3" t="s">
         <v>2163</v>
       </c>
-      <c r="C23" s="52" t="s">
+      <c r="C23" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D23" s="52" t="s">
+      <c r="D23" s="7" t="s">
         <v>1947</v>
       </c>
-      <c r="E23" s="50" t="s">
+      <c r="E23" s="3" t="s">
         <v>2164</v>
       </c>
-      <c r="F23" s="50" t="s">
+      <c r="F23" s="3" t="s">
         <v>1696</v>
       </c>
-      <c r="G23" s="50" t="s">
+      <c r="G23" s="3" t="s">
         <v>2165</v>
       </c>
-      <c r="H23" s="59" t="s">
-        <v>69</v>
-      </c>
-      <c r="I23" s="50" t="s">
+      <c r="H23" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>2166</v>
       </c>
-      <c r="J23" s="61" t="s">
+      <c r="J23" s="18" t="s">
         <v>2167</v>
       </c>
-      <c r="K23" s="52" t="s">
+      <c r="K23" s="7" t="s">
         <v>2052</v>
       </c>
-      <c r="L23" s="52" t="s">
+      <c r="L23" s="7" t="s">
         <v>1910</v>
       </c>
-      <c r="M23" s="52" t="s">
+      <c r="M23" s="7" t="s">
         <v>2060</v>
       </c>
-      <c r="N23" s="52" t="s">
+      <c r="N23" s="7" t="s">
         <v>25</v>
       </c>
     </row>
@@ -19848,580 +23536,580 @@
       <c r="A3" t="s">
         <v>1813</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="7" t="s">
         <v>1693</v>
       </c>
-      <c r="C3" s="23" t="s">
+      <c r="C3" s="7" t="s">
         <v>1694</v>
       </c>
-      <c r="D3" s="26">
+      <c r="D3" s="22">
         <v>1206</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="E3" s="7" t="s">
         <v>1695</v>
       </c>
-      <c r="F3" s="23" t="s">
+      <c r="F3" s="7" t="s">
         <v>1696</v>
       </c>
-      <c r="G3" s="23" t="s">
+      <c r="G3" s="7" t="s">
         <v>1697</v>
       </c>
-      <c r="H3" s="23" t="s">
-        <v>69</v>
-      </c>
-      <c r="I3" s="23" t="s">
+      <c r="H3" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I3" s="7" t="s">
         <v>1698</v>
       </c>
-      <c r="J3" s="23" t="s">
+      <c r="J3" s="7" t="s">
         <v>1699</v>
       </c>
-      <c r="K3" s="23" t="s">
+      <c r="K3" s="7" t="s">
         <v>1700</v>
       </c>
       <c r="L3" t="s">
         <v>55</v>
       </c>
-      <c r="M3" s="23" t="s">
+      <c r="M3" s="7" t="s">
         <v>1701</v>
       </c>
       <c r="N3" t="s">
         <v>25</v>
       </c>
-      <c r="O3" s="23"/>
+      <c r="O3" s="7"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" t="s">
         <v>1814</v>
       </c>
-      <c r="B4" s="23" t="s">
+      <c r="B4" s="7" t="s">
         <v>1702</v>
       </c>
-      <c r="C4" s="23" t="s">
+      <c r="C4" s="7" t="s">
         <v>1703</v>
       </c>
-      <c r="D4" s="23" t="s">
+      <c r="D4" s="7" t="s">
         <v>1704</v>
       </c>
-      <c r="E4" s="23" t="s">
+      <c r="E4" s="7" t="s">
         <v>1705</v>
       </c>
-      <c r="F4" s="23" t="s">
+      <c r="F4" s="7" t="s">
         <v>1696</v>
       </c>
-      <c r="G4" s="23" t="s">
+      <c r="G4" s="7" t="s">
         <v>1706</v>
       </c>
-      <c r="H4" s="23" t="s">
-        <v>69</v>
-      </c>
-      <c r="I4" s="23" t="s">
+      <c r="H4" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I4" s="7" t="s">
         <v>1707</v>
       </c>
-      <c r="J4" s="23" t="s">
+      <c r="J4" s="7" t="s">
         <v>1708</v>
       </c>
-      <c r="K4" s="23" t="s">
+      <c r="K4" s="7" t="s">
         <v>1700</v>
       </c>
       <c r="L4" t="s">
         <v>55</v>
       </c>
-      <c r="M4" s="23" t="s">
+      <c r="M4" s="7" t="s">
         <v>1709</v>
       </c>
       <c r="N4" t="s">
         <v>25</v>
       </c>
-      <c r="O4" s="23"/>
+      <c r="O4" s="7"/>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" t="s">
         <v>1815</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="7" t="s">
         <v>1710</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="7" t="s">
         <v>1711</v>
       </c>
-      <c r="D5" s="23">
+      <c r="D5" s="7">
         <v>1206</v>
       </c>
-      <c r="E5" s="23" t="s">
+      <c r="E5" s="7" t="s">
         <v>1712</v>
       </c>
-      <c r="F5" s="23" t="s">
+      <c r="F5" s="7" t="s">
         <v>1691</v>
       </c>
-      <c r="G5" s="23" t="s">
+      <c r="G5" s="7" t="s">
         <v>1712</v>
       </c>
-      <c r="H5" s="23" t="s">
-        <v>69</v>
-      </c>
-      <c r="I5" s="24" t="s">
+      <c r="H5" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I5" s="15" t="s">
         <v>1713</v>
       </c>
-      <c r="J5" s="24" t="s">
+      <c r="J5" s="15" t="s">
         <v>1714</v>
       </c>
-      <c r="K5" s="23" t="s">
+      <c r="K5" s="7" t="s">
         <v>1700</v>
       </c>
       <c r="L5" t="s">
         <v>55</v>
       </c>
-      <c r="M5" s="23" t="s">
+      <c r="M5" s="7" t="s">
         <v>1701</v>
       </c>
       <c r="N5" t="s">
         <v>25</v>
       </c>
-      <c r="O5" s="22"/>
+      <c r="O5" s="3"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" t="s">
         <v>1816</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="7" t="s">
         <v>1715</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="7" t="s">
         <v>1716</v>
       </c>
-      <c r="D6" s="23">
+      <c r="D6" s="7">
         <v>1206</v>
       </c>
-      <c r="E6" s="23" t="s">
+      <c r="E6" s="7" t="s">
         <v>1717</v>
       </c>
-      <c r="F6" s="23" t="s">
+      <c r="F6" s="7" t="s">
         <v>1718</v>
       </c>
-      <c r="G6" s="23" t="s">
+      <c r="G6" s="7" t="s">
         <v>1717</v>
       </c>
-      <c r="H6" s="23" t="s">
-        <v>69</v>
-      </c>
-      <c r="I6" s="24" t="s">
+      <c r="H6" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I6" s="15" t="s">
         <v>1719</v>
       </c>
-      <c r="J6" s="24" t="s">
+      <c r="J6" s="15" t="s">
         <v>1720</v>
       </c>
-      <c r="K6" s="23" t="s">
+      <c r="K6" s="7" t="s">
         <v>1700</v>
       </c>
       <c r="L6" t="s">
         <v>55</v>
       </c>
-      <c r="M6" s="23" t="s">
+      <c r="M6" s="7" t="s">
         <v>1701</v>
       </c>
       <c r="N6" t="s">
         <v>25</v>
       </c>
-      <c r="O6" s="22"/>
+      <c r="O6" s="3"/>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" t="s">
         <v>1817</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="3" t="s">
         <v>1721</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C7" s="7" t="s">
         <v>1692</v>
       </c>
-      <c r="D7" s="23" t="s">
+      <c r="D7" s="7" t="s">
         <v>1722</v>
       </c>
-      <c r="E7" s="25" t="s">
+      <c r="E7" s="3" t="s">
         <v>1723</v>
       </c>
-      <c r="F7" s="25" t="s">
+      <c r="F7" s="3" t="s">
         <v>1696</v>
       </c>
-      <c r="G7" s="25" t="s">
+      <c r="G7" s="3" t="s">
         <v>1724</v>
       </c>
-      <c r="H7" s="23" t="s">
-        <v>69</v>
-      </c>
-      <c r="I7" s="25" t="s">
+      <c r="H7" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>1725</v>
       </c>
-      <c r="J7" s="25" t="s">
+      <c r="J7" s="3" t="s">
         <v>1726</v>
       </c>
-      <c r="K7" s="23" t="s">
+      <c r="K7" s="7" t="s">
         <v>1700</v>
       </c>
       <c r="L7" t="s">
         <v>55</v>
       </c>
-      <c r="M7" s="25" t="s">
+      <c r="M7" s="3" t="s">
         <v>1727</v>
       </c>
       <c r="N7" t="s">
         <v>25</v>
       </c>
-      <c r="O7" s="22"/>
+      <c r="O7" s="3"/>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" t="s">
         <v>1818</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="3" t="s">
         <v>1728</v>
       </c>
-      <c r="C8" s="23" t="s">
+      <c r="C8" s="7" t="s">
         <v>1703</v>
       </c>
-      <c r="D8" s="23">
+      <c r="D8" s="7">
         <v>1206</v>
       </c>
-      <c r="E8" s="25" t="s">
+      <c r="E8" s="3" t="s">
         <v>1729</v>
       </c>
-      <c r="F8" s="25" t="s">
+      <c r="F8" s="3" t="s">
         <v>1730</v>
       </c>
-      <c r="G8" s="25" t="s">
+      <c r="G8" s="3" t="s">
         <v>1731</v>
       </c>
-      <c r="H8" s="23" t="s">
-        <v>69</v>
-      </c>
-      <c r="I8" s="25" t="s">
+      <c r="H8" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>1732</v>
       </c>
-      <c r="J8" s="25" t="s">
+      <c r="J8" s="3" t="s">
         <v>1733</v>
       </c>
-      <c r="K8" s="23" t="s">
+      <c r="K8" s="7" t="s">
         <v>1700</v>
       </c>
       <c r="L8" t="s">
         <v>55</v>
       </c>
-      <c r="M8" s="23" t="s">
+      <c r="M8" s="7" t="s">
         <v>1701</v>
       </c>
       <c r="N8" t="s">
         <v>25</v>
       </c>
-      <c r="O8" s="22"/>
+      <c r="O8" s="3"/>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" t="s">
         <v>1819</v>
       </c>
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="3" t="s">
         <v>1734</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="C9" s="7" t="s">
         <v>1711</v>
       </c>
-      <c r="D9" s="23">
+      <c r="D9" s="7">
         <v>1206</v>
       </c>
-      <c r="E9" s="25" t="s">
+      <c r="E9" s="3" t="s">
         <v>1735</v>
       </c>
-      <c r="F9" s="25" t="s">
+      <c r="F9" s="3" t="s">
         <v>1730</v>
       </c>
-      <c r="G9" s="25" t="s">
+      <c r="G9" s="3" t="s">
         <v>1736</v>
       </c>
-      <c r="H9" s="23" t="s">
-        <v>69</v>
-      </c>
-      <c r="I9" s="25" t="s">
+      <c r="H9" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>1737</v>
       </c>
-      <c r="J9" s="25" t="s">
+      <c r="J9" s="3" t="s">
         <v>1738</v>
       </c>
-      <c r="K9" s="23" t="s">
+      <c r="K9" s="7" t="s">
         <v>1700</v>
       </c>
       <c r="L9" t="s">
         <v>55</v>
       </c>
-      <c r="M9" s="23" t="s">
+      <c r="M9" s="7" t="s">
         <v>1701</v>
       </c>
       <c r="N9" t="s">
         <v>25</v>
       </c>
-      <c r="O9" s="22"/>
+      <c r="O9" s="3"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" t="s">
         <v>1820</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="3" t="s">
         <v>1739</v>
       </c>
-      <c r="C10" s="23" t="s">
+      <c r="C10" s="7" t="s">
         <v>1740</v>
       </c>
-      <c r="D10" s="23">
+      <c r="D10" s="7">
         <v>1812</v>
       </c>
-      <c r="E10" s="25" t="s">
+      <c r="E10" s="3" t="s">
         <v>1741</v>
       </c>
-      <c r="F10" s="25" t="s">
+      <c r="F10" s="3" t="s">
         <v>1742</v>
       </c>
-      <c r="G10" s="25" t="s">
+      <c r="G10" s="3" t="s">
         <v>1743</v>
       </c>
-      <c r="H10" s="23" t="s">
-        <v>69</v>
-      </c>
-      <c r="I10" s="24" t="s">
+      <c r="H10" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I10" s="15" t="s">
         <v>1744</v>
       </c>
-      <c r="J10" s="24" t="s">
+      <c r="J10" s="15" t="s">
         <v>1745</v>
       </c>
-      <c r="K10" s="23" t="s">
+      <c r="K10" s="7" t="s">
         <v>1700</v>
       </c>
       <c r="L10" t="s">
         <v>55</v>
       </c>
-      <c r="M10" s="23" t="s">
+      <c r="M10" s="7" t="s">
         <v>1746</v>
       </c>
       <c r="N10" t="s">
         <v>25</v>
       </c>
-      <c r="O10" s="22"/>
+      <c r="O10" s="3"/>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" t="s">
         <v>1821</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="3" t="s">
         <v>1747</v>
       </c>
-      <c r="C11" s="23" t="s">
+      <c r="C11" s="7" t="s">
         <v>1748</v>
       </c>
-      <c r="D11" s="23">
+      <c r="D11" s="7">
         <v>1812</v>
       </c>
-      <c r="E11" s="22" t="s">
+      <c r="E11" s="3" t="s">
         <v>1749</v>
       </c>
-      <c r="F11" s="22" t="s">
+      <c r="F11" s="3" t="s">
         <v>1742</v>
       </c>
-      <c r="G11" s="22" t="s">
+      <c r="G11" s="3" t="s">
         <v>1750</v>
       </c>
-      <c r="H11" s="23" t="s">
-        <v>69</v>
-      </c>
-      <c r="I11" s="22" t="s">
+      <c r="H11" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>1751</v>
       </c>
-      <c r="J11" s="22" t="s">
+      <c r="J11" s="3" t="s">
         <v>1752</v>
       </c>
-      <c r="K11" s="23" t="s">
+      <c r="K11" s="7" t="s">
         <v>1700</v>
       </c>
       <c r="L11" t="s">
         <v>55</v>
       </c>
-      <c r="M11" s="23" t="s">
+      <c r="M11" s="7" t="s">
         <v>1746</v>
       </c>
       <c r="N11" t="s">
         <v>25</v>
       </c>
-      <c r="O11" s="22"/>
+      <c r="O11" s="3"/>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" t="s">
         <v>1822</v>
       </c>
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="3" t="s">
         <v>1753</v>
       </c>
-      <c r="C12" s="23" t="s">
+      <c r="C12" s="7" t="s">
         <v>1754</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="D12" s="3" t="s">
         <v>1755</v>
       </c>
-      <c r="E12" s="22" t="s">
+      <c r="E12" s="3" t="s">
         <v>1756</v>
       </c>
-      <c r="F12" s="28" t="s">
+      <c r="F12" s="17" t="s">
         <v>1757</v>
       </c>
-      <c r="G12" s="28" t="s">
+      <c r="G12" s="17" t="s">
         <v>1758</v>
       </c>
-      <c r="H12" s="28" t="s">
+      <c r="H12" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="I12" s="29" t="s">
+      <c r="I12" s="18" t="s">
         <v>1759</v>
       </c>
-      <c r="J12" s="29" t="s">
+      <c r="J12" s="18" t="s">
         <v>1760</v>
       </c>
-      <c r="K12" s="28" t="s">
+      <c r="K12" s="17" t="s">
         <v>1700</v>
       </c>
       <c r="L12" t="s">
         <v>55</v>
       </c>
-      <c r="M12" s="28" t="s">
+      <c r="M12" s="17" t="s">
         <v>1761</v>
       </c>
       <c r="N12" t="s">
         <v>25</v>
       </c>
-      <c r="O12" s="22"/>
+      <c r="O12" s="3"/>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" t="s">
         <v>1823</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="3" t="s">
         <v>1762</v>
       </c>
-      <c r="C13" s="23" t="s">
+      <c r="C13" s="7" t="s">
         <v>1763</v>
       </c>
-      <c r="D13" s="22">
+      <c r="D13" s="3">
         <v>1812</v>
       </c>
-      <c r="E13" s="22" t="s">
+      <c r="E13" s="3" t="s">
         <v>1764</v>
       </c>
-      <c r="F13" s="28" t="s">
+      <c r="F13" s="17" t="s">
         <v>1742</v>
       </c>
-      <c r="G13" s="28" t="s">
+      <c r="G13" s="17" t="s">
         <v>1765</v>
       </c>
-      <c r="H13" s="28" t="s">
-        <v>69</v>
-      </c>
-      <c r="I13" s="29" t="s">
+      <c r="H13" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="I13" s="18" t="s">
         <v>1766</v>
       </c>
-      <c r="J13" s="29" t="s">
+      <c r="J13" s="18" t="s">
         <v>1767</v>
       </c>
-      <c r="K13" s="28" t="s">
+      <c r="K13" s="17" t="s">
         <v>1700</v>
       </c>
       <c r="L13" t="s">
         <v>55</v>
       </c>
-      <c r="M13" s="23" t="s">
+      <c r="M13" s="7" t="s">
         <v>1746</v>
       </c>
       <c r="N13" t="s">
         <v>25</v>
       </c>
-      <c r="O13" s="22"/>
+      <c r="O13" s="3"/>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" t="s">
         <v>1824</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="3" t="s">
         <v>1768</v>
       </c>
-      <c r="C14" s="23" t="s">
+      <c r="C14" s="7" t="s">
         <v>1763</v>
       </c>
-      <c r="D14" s="23">
+      <c r="D14" s="7">
         <v>1206</v>
       </c>
-      <c r="E14" s="23" t="s">
+      <c r="E14" s="7" t="s">
         <v>1769</v>
       </c>
-      <c r="F14" s="28" t="s">
+      <c r="F14" s="17" t="s">
         <v>1742</v>
       </c>
-      <c r="G14" s="22" t="s">
+      <c r="G14" s="3" t="s">
         <v>1770</v>
       </c>
-      <c r="H14" s="28" t="s">
-        <v>69</v>
-      </c>
-      <c r="I14" s="22" t="s">
+      <c r="H14" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>1771</v>
       </c>
-      <c r="J14" s="29" t="s">
+      <c r="J14" s="18" t="s">
         <v>1772</v>
       </c>
-      <c r="K14" s="28" t="s">
+      <c r="K14" s="17" t="s">
         <v>1700</v>
       </c>
       <c r="L14" t="s">
         <v>55</v>
       </c>
-      <c r="M14" s="23" t="s">
+      <c r="M14" s="7" t="s">
         <v>1701</v>
       </c>
       <c r="N14" t="s">
         <v>25</v>
       </c>
-      <c r="O14" s="22"/>
+      <c r="O14" s="3"/>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" t="s">
         <v>1825</v>
       </c>
-      <c r="B15" s="22" t="s">
+      <c r="B15" s="3" t="s">
         <v>1773</v>
       </c>
-      <c r="C15" s="23" t="s">
+      <c r="C15" s="7" t="s">
         <v>1774</v>
       </c>
-      <c r="D15" s="23">
+      <c r="D15" s="7">
         <v>1206</v>
       </c>
-      <c r="E15" s="23" t="s">
+      <c r="E15" s="7" t="s">
         <v>1775</v>
       </c>
-      <c r="F15" s="22" t="s">
+      <c r="F15" s="3" t="s">
         <v>1776</v>
       </c>
-      <c r="G15" s="22" t="s">
+      <c r="G15" s="3" t="s">
         <v>1777</v>
       </c>
-      <c r="H15" s="28" t="s">
-        <v>69</v>
-      </c>
-      <c r="I15" s="22" t="s">
+      <c r="H15" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>1778</v>
       </c>
-      <c r="J15" s="22" t="s">
+      <c r="J15" s="3" t="s">
         <v>1779</v>
       </c>
-      <c r="K15" s="28" t="s">
+      <c r="K15" s="17" t="s">
         <v>1700</v>
       </c>
       <c r="L15" t="s">
         <v>55</v>
       </c>
-      <c r="M15" s="23" t="s">
+      <c r="M15" s="7" t="s">
         <v>1701</v>
       </c>
       <c r="N15" t="s">
@@ -20432,40 +24120,40 @@
       <c r="A16" t="s">
         <v>1826</v>
       </c>
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="3" t="s">
         <v>1780</v>
       </c>
-      <c r="C16" s="27" t="s">
+      <c r="C16" s="16" t="s">
         <v>1774</v>
       </c>
-      <c r="D16" s="27" t="s">
+      <c r="D16" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="E16" s="27" t="s">
+      <c r="E16" s="16" t="s">
         <v>1781</v>
       </c>
-      <c r="F16" s="27" t="s">
+      <c r="F16" s="16" t="s">
         <v>1696</v>
       </c>
-      <c r="G16" s="27" t="s">
+      <c r="G16" s="16" t="s">
         <v>1782</v>
       </c>
-      <c r="H16" s="28" t="s">
+      <c r="H16" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="I16" s="22" t="s">
+      <c r="I16" s="3" t="s">
         <v>1783</v>
       </c>
-      <c r="J16" s="22" t="s">
+      <c r="J16" s="3" t="s">
         <v>1784</v>
       </c>
-      <c r="K16" s="28" t="s">
+      <c r="K16" s="17" t="s">
         <v>1700</v>
       </c>
       <c r="L16" t="s">
         <v>55</v>
       </c>
-      <c r="M16" s="27" t="s">
+      <c r="M16" s="16" t="s">
         <v>1785</v>
       </c>
       <c r="N16" t="s">
@@ -20476,40 +24164,40 @@
       <c r="A17" t="s">
         <v>1827</v>
       </c>
-      <c r="B17" s="22" t="s">
+      <c r="B17" s="3" t="s">
         <v>1786</v>
       </c>
-      <c r="C17" s="27" t="s">
+      <c r="C17" s="16" t="s">
         <v>1763</v>
       </c>
-      <c r="D17" s="27" t="s">
+      <c r="D17" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="E17" s="27" t="s">
+      <c r="E17" s="16" t="s">
         <v>1787</v>
       </c>
-      <c r="F17" s="27" t="s">
+      <c r="F17" s="16" t="s">
         <v>1696</v>
       </c>
-      <c r="G17" s="27" t="s">
+      <c r="G17" s="16" t="s">
         <v>1788</v>
       </c>
-      <c r="H17" s="28" t="s">
+      <c r="H17" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="I17" s="22" t="s">
+      <c r="I17" s="3" t="s">
         <v>1789</v>
       </c>
-      <c r="J17" s="22" t="s">
+      <c r="J17" s="3" t="s">
         <v>1783</v>
       </c>
-      <c r="K17" s="28" t="s">
+      <c r="K17" s="17" t="s">
         <v>1700</v>
       </c>
       <c r="L17" t="s">
         <v>55</v>
       </c>
-      <c r="M17" s="27" t="s">
+      <c r="M17" s="16" t="s">
         <v>1785</v>
       </c>
       <c r="N17" t="s">
@@ -20520,40 +24208,40 @@
       <c r="A18" t="s">
         <v>1828</v>
       </c>
-      <c r="B18" s="22" t="s">
+      <c r="B18" s="3" t="s">
         <v>1790</v>
       </c>
-      <c r="C18" s="27" t="s">
+      <c r="C18" s="16" t="s">
         <v>1791</v>
       </c>
-      <c r="D18" s="27" t="s">
+      <c r="D18" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="E18" s="22" t="s">
+      <c r="E18" s="3" t="s">
         <v>1792</v>
       </c>
-      <c r="F18" s="22" t="s">
+      <c r="F18" s="3" t="s">
         <v>1742</v>
       </c>
-      <c r="G18" s="22" t="s">
+      <c r="G18" s="3" t="s">
         <v>1793</v>
       </c>
-      <c r="H18" s="28" t="s">
-        <v>69</v>
-      </c>
-      <c r="I18" s="22" t="s">
+      <c r="H18" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>1794</v>
       </c>
-      <c r="J18" s="22" t="s">
+      <c r="J18" s="3" t="s">
         <v>1795</v>
       </c>
-      <c r="K18" s="28" t="s">
+      <c r="K18" s="17" t="s">
         <v>1700</v>
       </c>
       <c r="L18" t="s">
         <v>55</v>
       </c>
-      <c r="M18" s="27" t="s">
+      <c r="M18" s="16" t="s">
         <v>1785</v>
       </c>
       <c r="N18" t="s">
@@ -20564,40 +24252,40 @@
       <c r="A19" t="s">
         <v>1829</v>
       </c>
-      <c r="B19" s="22" t="s">
+      <c r="B19" s="3" t="s">
         <v>1796</v>
       </c>
-      <c r="C19" s="27" t="s">
+      <c r="C19" s="16" t="s">
         <v>1763</v>
       </c>
-      <c r="D19" s="22">
+      <c r="D19" s="3">
         <v>1812</v>
       </c>
-      <c r="E19" s="22" t="s">
+      <c r="E19" s="3" t="s">
         <v>1797</v>
       </c>
-      <c r="F19" s="22" t="s">
+      <c r="F19" s="3" t="s">
         <v>1742</v>
       </c>
-      <c r="G19" s="22" t="s">
+      <c r="G19" s="3" t="s">
         <v>1798</v>
       </c>
-      <c r="H19" s="28" t="s">
-        <v>69</v>
-      </c>
-      <c r="I19" s="29" t="s">
+      <c r="H19" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="I19" s="18" t="s">
         <v>1799</v>
       </c>
-      <c r="J19" s="22" t="s">
+      <c r="J19" s="3" t="s">
         <v>1800</v>
       </c>
-      <c r="K19" s="28" t="s">
+      <c r="K19" s="17" t="s">
         <v>1700</v>
       </c>
       <c r="L19" t="s">
         <v>55</v>
       </c>
-      <c r="M19" s="23" t="s">
+      <c r="M19" s="7" t="s">
         <v>1746</v>
       </c>
       <c r="N19" t="s">
@@ -20608,40 +24296,40 @@
       <c r="A20" t="s">
         <v>1830</v>
       </c>
-      <c r="B20" s="22" t="s">
+      <c r="B20" s="3" t="s">
         <v>1801</v>
       </c>
-      <c r="C20" s="27" t="s">
+      <c r="C20" s="16" t="s">
         <v>1692</v>
       </c>
-      <c r="D20" s="30" t="s">
+      <c r="D20" s="23" t="s">
         <v>1802</v>
       </c>
-      <c r="E20" s="22" t="s">
+      <c r="E20" s="3" t="s">
         <v>1803</v>
       </c>
-      <c r="F20" s="22" t="s">
+      <c r="F20" s="3" t="s">
         <v>1742</v>
       </c>
-      <c r="G20" s="22" t="s">
+      <c r="G20" s="3" t="s">
         <v>1804</v>
       </c>
-      <c r="H20" s="28" t="s">
-        <v>69</v>
-      </c>
-      <c r="I20" s="29" t="s">
+      <c r="H20" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="I20" s="18" t="s">
         <v>1805</v>
       </c>
-      <c r="J20" s="29" t="s">
+      <c r="J20" s="18" t="s">
         <v>1806</v>
       </c>
-      <c r="K20" s="28" t="s">
+      <c r="K20" s="17" t="s">
         <v>1700</v>
       </c>
       <c r="L20" t="s">
         <v>55</v>
       </c>
-      <c r="M20" s="22" t="s">
+      <c r="M20" s="3" t="s">
         <v>1807</v>
       </c>
       <c r="N20" t="s">
@@ -20652,40 +24340,40 @@
       <c r="A21" t="s">
         <v>1831</v>
       </c>
-      <c r="B21" s="22" t="s">
+      <c r="B21" s="3" t="s">
         <v>1808</v>
       </c>
-      <c r="C21" s="23" t="s">
+      <c r="C21" s="7" t="s">
         <v>1703</v>
       </c>
-      <c r="D21" s="23">
+      <c r="D21" s="7">
         <v>1812</v>
       </c>
-      <c r="E21" s="22" t="s">
+      <c r="E21" s="3" t="s">
         <v>1809</v>
       </c>
-      <c r="F21" s="22" t="s">
+      <c r="F21" s="3" t="s">
         <v>1742</v>
       </c>
-      <c r="G21" s="22" t="s">
+      <c r="G21" s="3" t="s">
         <v>1810</v>
       </c>
-      <c r="H21" s="23" t="s">
-        <v>69</v>
-      </c>
-      <c r="I21" s="22" t="s">
+      <c r="H21" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>1811</v>
       </c>
-      <c r="J21" s="29" t="s">
+      <c r="J21" s="18" t="s">
         <v>1812</v>
       </c>
-      <c r="K21" s="23" t="s">
+      <c r="K21" s="7" t="s">
         <v>1700</v>
       </c>
       <c r="L21" t="s">
         <v>55</v>
       </c>
-      <c r="M21" s="23" t="s">
+      <c r="M21" s="7" t="s">
         <v>1746</v>
       </c>
       <c r="N21" t="s">

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{403B5372-1E92-4065-93FF-7BB6EAE5862F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A235B2DA-ECEA-46D4-91B3-71E35DD00E8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="1596" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -19,12 +19,13 @@
     <sheet name="020 - Inductor" sheetId="5" r:id="rId4"/>
     <sheet name="030 - Diode - Rectifier" sheetId="9" r:id="rId5"/>
     <sheet name="031 - Diode - Schottky" sheetId="11" r:id="rId6"/>
-    <sheet name="033 - Diode - LED" sheetId="12" r:id="rId7"/>
-    <sheet name="040 - Fuses" sheetId="10" r:id="rId8"/>
-    <sheet name="050 - ICs - Analog" sheetId="2" r:id="rId9"/>
-    <sheet name="060 - ICs - Digital" sheetId="3" r:id="rId10"/>
-    <sheet name="070 - Power Supply - DCDC" sheetId="8" r:id="rId11"/>
-    <sheet name="110 - Connectors" sheetId="13" r:id="rId12"/>
+    <sheet name="032 - Diode - TVS" sheetId="14" r:id="rId7"/>
+    <sheet name="033 - Diode - LED" sheetId="12" r:id="rId8"/>
+    <sheet name="040 - Fuses" sheetId="10" r:id="rId9"/>
+    <sheet name="050 - ICs - Analog" sheetId="2" r:id="rId10"/>
+    <sheet name="060 - ICs - Digital" sheetId="3" r:id="rId11"/>
+    <sheet name="070 - Power Supply - DCDC" sheetId="8" r:id="rId12"/>
+    <sheet name="110 - Connectors" sheetId="13" r:id="rId13"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5038" uniqueCount="2583">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5356" uniqueCount="2585">
   <si>
     <t>ID</t>
   </si>
@@ -7785,6 +7786,12 @@
   </si>
   <si>
     <t>https://www.mouser.es/ProductDetail/Phoenix-Contact/1804920?qs=bbdZqDPQhEUmz%252BLlbRELng%3D%3D</t>
+  </si>
+  <si>
+    <t>Pleeda_SchLibrary/Pleeda_SchLibrary - Diode.SchLib</t>
+  </si>
+  <si>
+    <t>Pleeda_PcbLibrary/Pleeda_PcbLibrary.PcbLib</t>
   </si>
 </sst>
 </file>
@@ -12404,6 +12411,256 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C98E1A12-072F-4773-8CB5-47FFE077E85B}">
+  <dimension ref="A1:N9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="2" max="2" width="93.81640625" customWidth="1"/>
+    <col min="5" max="5" width="16.1796875" customWidth="1"/>
+    <col min="6" max="6" width="17.81640625" customWidth="1"/>
+    <col min="7" max="7" width="16.7265625" customWidth="1"/>
+    <col min="9" max="9" width="24.7265625" customWidth="1"/>
+    <col min="10" max="10" width="23.6328125" customWidth="1"/>
+    <col min="12" max="12" width="32.453125" customWidth="1"/>
+    <col min="13" max="13" width="14.90625" customWidth="1"/>
+    <col min="14" max="14" width="21.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M2" t="s">
+        <v>17</v>
+      </c>
+      <c r="N2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J3" t="s">
+        <v>43</v>
+      </c>
+      <c r="K3" t="s">
+        <v>39</v>
+      </c>
+      <c r="L3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3" t="s">
+        <v>38</v>
+      </c>
+      <c r="N3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>1649</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1650</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1651</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" t="s">
+        <v>1652</v>
+      </c>
+      <c r="G4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" t="s">
+        <v>69</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>1654</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>1653</v>
+      </c>
+      <c r="K4" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" t="s">
+        <v>26</v>
+      </c>
+      <c r="M4" t="s">
+        <v>1651</v>
+      </c>
+      <c r="N4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>1655</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1656</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" t="s">
+        <v>1657</v>
+      </c>
+      <c r="G5" t="s">
+        <v>1658</v>
+      </c>
+      <c r="H5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I5" t="s">
+        <v>1659</v>
+      </c>
+      <c r="J5" t="s">
+        <v>1660</v>
+      </c>
+      <c r="K5" t="s">
+        <v>39</v>
+      </c>
+      <c r="L5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5" t="s">
+        <v>38</v>
+      </c>
+      <c r="N5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="L9" s="21"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="J2" r:id="rId1" xr:uid="{78125F11-BE4E-4312-8E61-0550889BB81F}"/>
+    <hyperlink ref="I2" r:id="rId2" xr:uid="{1CFCC581-B5E5-4159-8EE1-35A941FCD4DF}"/>
+    <hyperlink ref="J4" r:id="rId3" xr:uid="{BD7BCD4B-25F3-483F-8F98-D146F94F5AAF}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59BC8B2E-A067-463D-937A-30E88D8BECD0}">
   <dimension ref="A1:N1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -12457,7 +12714,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4BBBCF5-BAC9-459C-ABE9-2526B85FD81E}">
   <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -12651,7 +12908,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE14AD29-8DB0-4C42-AB91-A73B867AE121}">
   <dimension ref="A1:N55"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -22391,6 +22648,1025 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79E65951-BFD2-4888-A0A6-19D5130CB4A6}">
+  <dimension ref="A1:N23"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="25" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
+        <v>2003</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2004</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2005</v>
+      </c>
+      <c r="E2" t="s">
+        <v>2006</v>
+      </c>
+      <c r="F2" t="s">
+        <v>2007</v>
+      </c>
+      <c r="G2" t="s">
+        <v>2008</v>
+      </c>
+      <c r="H2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I2" t="s">
+        <v>2009</v>
+      </c>
+      <c r="J2" t="s">
+        <v>2010</v>
+      </c>
+      <c r="K2" t="s">
+        <v>2011</v>
+      </c>
+      <c r="L2" t="s">
+        <v>2583</v>
+      </c>
+      <c r="N2" t="s">
+        <v>2584</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>2012</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2013</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>2014</v>
+      </c>
+      <c r="E3" t="s">
+        <v>2015</v>
+      </c>
+      <c r="F3" t="s">
+        <v>2016</v>
+      </c>
+      <c r="G3" t="s">
+        <v>2017</v>
+      </c>
+      <c r="H3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I3" t="s">
+        <v>2018</v>
+      </c>
+      <c r="J3" t="s">
+        <v>2019</v>
+      </c>
+      <c r="K3" t="s">
+        <v>2011</v>
+      </c>
+      <c r="L3" t="s">
+        <v>2583</v>
+      </c>
+      <c r="M3" t="s">
+        <v>2014</v>
+      </c>
+      <c r="N3" t="s">
+        <v>2584</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>2020</v>
+      </c>
+      <c r="B4" t="s">
+        <v>2021</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4">
+        <v>402</v>
+      </c>
+      <c r="E4" t="s">
+        <v>2022</v>
+      </c>
+      <c r="F4" t="s">
+        <v>2023</v>
+      </c>
+      <c r="G4" t="s">
+        <v>2024</v>
+      </c>
+      <c r="H4" t="s">
+        <v>69</v>
+      </c>
+      <c r="I4" t="s">
+        <v>2025</v>
+      </c>
+      <c r="J4" t="s">
+        <v>2026</v>
+      </c>
+      <c r="K4" t="s">
+        <v>2011</v>
+      </c>
+      <c r="L4" t="s">
+        <v>2583</v>
+      </c>
+      <c r="M4" t="s">
+        <v>2027</v>
+      </c>
+      <c r="N4" t="s">
+        <v>2584</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>2028</v>
+      </c>
+      <c r="B5" t="s">
+        <v>2029</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s">
+        <v>2030</v>
+      </c>
+      <c r="E5" t="s">
+        <v>2031</v>
+      </c>
+      <c r="F5" t="s">
+        <v>1858</v>
+      </c>
+      <c r="G5" t="s">
+        <v>2032</v>
+      </c>
+      <c r="H5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I5" t="s">
+        <v>2033</v>
+      </c>
+      <c r="J5" t="s">
+        <v>2034</v>
+      </c>
+      <c r="K5" t="s">
+        <v>1918</v>
+      </c>
+      <c r="L5" t="s">
+        <v>2583</v>
+      </c>
+      <c r="M5" t="s">
+        <v>2030</v>
+      </c>
+      <c r="N5" t="s">
+        <v>2584</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>2035</v>
+      </c>
+      <c r="B6" t="s">
+        <v>2036</v>
+      </c>
+      <c r="C6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" t="s">
+        <v>2037</v>
+      </c>
+      <c r="E6" t="s">
+        <v>2038</v>
+      </c>
+      <c r="F6" t="s">
+        <v>2039</v>
+      </c>
+      <c r="G6" t="s">
+        <v>2040</v>
+      </c>
+      <c r="H6" t="s">
+        <v>69</v>
+      </c>
+      <c r="I6" t="s">
+        <v>2041</v>
+      </c>
+      <c r="J6" t="s">
+        <v>2042</v>
+      </c>
+      <c r="K6" t="s">
+        <v>2043</v>
+      </c>
+      <c r="L6" t="s">
+        <v>2583</v>
+      </c>
+      <c r="M6" t="s">
+        <v>2044</v>
+      </c>
+      <c r="N6" t="s">
+        <v>2584</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B7" t="s">
+        <v>2046</v>
+      </c>
+      <c r="C7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E7" t="s">
+        <v>2048</v>
+      </c>
+      <c r="F7" t="s">
+        <v>1696</v>
+      </c>
+      <c r="G7" t="s">
+        <v>2049</v>
+      </c>
+      <c r="H7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I7" t="s">
+        <v>2050</v>
+      </c>
+      <c r="J7" t="s">
+        <v>2051</v>
+      </c>
+      <c r="K7" t="s">
+        <v>2052</v>
+      </c>
+      <c r="L7" t="s">
+        <v>2583</v>
+      </c>
+      <c r="M7" t="s">
+        <v>2047</v>
+      </c>
+      <c r="N7" t="s">
+        <v>2584</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>2053</v>
+      </c>
+      <c r="B8" t="s">
+        <v>2054</v>
+      </c>
+      <c r="C8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1947</v>
+      </c>
+      <c r="E8" t="s">
+        <v>2055</v>
+      </c>
+      <c r="F8" t="s">
+        <v>2056</v>
+      </c>
+      <c r="G8" t="s">
+        <v>2057</v>
+      </c>
+      <c r="H8" t="s">
+        <v>69</v>
+      </c>
+      <c r="I8" t="s">
+        <v>2058</v>
+      </c>
+      <c r="J8" t="s">
+        <v>2059</v>
+      </c>
+      <c r="K8" t="s">
+        <v>2052</v>
+      </c>
+      <c r="L8" t="s">
+        <v>2583</v>
+      </c>
+      <c r="M8" t="s">
+        <v>2060</v>
+      </c>
+      <c r="N8" t="s">
+        <v>2584</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>2061</v>
+      </c>
+      <c r="B9" t="s">
+        <v>2062</v>
+      </c>
+      <c r="C9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1947</v>
+      </c>
+      <c r="E9" t="s">
+        <v>2063</v>
+      </c>
+      <c r="F9" t="s">
+        <v>2064</v>
+      </c>
+      <c r="G9" t="s">
+        <v>2065</v>
+      </c>
+      <c r="H9" t="s">
+        <v>69</v>
+      </c>
+      <c r="I9" t="s">
+        <v>2066</v>
+      </c>
+      <c r="J9" t="s">
+        <v>2067</v>
+      </c>
+      <c r="K9" t="s">
+        <v>2052</v>
+      </c>
+      <c r="L9" t="s">
+        <v>2583</v>
+      </c>
+      <c r="M9" t="s">
+        <v>1947</v>
+      </c>
+      <c r="N9" t="s">
+        <v>2584</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B10" t="s">
+        <v>2069</v>
+      </c>
+      <c r="C10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" t="s">
+        <v>2070</v>
+      </c>
+      <c r="E10" t="s">
+        <v>2070</v>
+      </c>
+      <c r="F10" t="s">
+        <v>1981</v>
+      </c>
+      <c r="G10" t="s">
+        <v>2071</v>
+      </c>
+      <c r="H10" t="s">
+        <v>69</v>
+      </c>
+      <c r="I10" t="s">
+        <v>2072</v>
+      </c>
+      <c r="J10" t="s">
+        <v>2073</v>
+      </c>
+      <c r="K10" t="s">
+        <v>2074</v>
+      </c>
+      <c r="L10" t="s">
+        <v>2583</v>
+      </c>
+      <c r="M10" t="s">
+        <v>1856</v>
+      </c>
+      <c r="N10" t="s">
+        <v>2584</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" t="s">
+        <v>2075</v>
+      </c>
+      <c r="B11" t="s">
+        <v>2076</v>
+      </c>
+      <c r="C11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" t="s">
+        <v>1856</v>
+      </c>
+      <c r="E11" t="s">
+        <v>2077</v>
+      </c>
+      <c r="F11" t="s">
+        <v>945</v>
+      </c>
+      <c r="G11" t="s">
+        <v>2078</v>
+      </c>
+      <c r="H11" t="s">
+        <v>69</v>
+      </c>
+      <c r="I11" t="s">
+        <v>2079</v>
+      </c>
+      <c r="J11" t="s">
+        <v>2080</v>
+      </c>
+      <c r="K11" t="s">
+        <v>2081</v>
+      </c>
+      <c r="L11" t="s">
+        <v>2583</v>
+      </c>
+      <c r="M11" t="s">
+        <v>1856</v>
+      </c>
+      <c r="N11" t="s">
+        <v>2584</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" t="s">
+        <v>2082</v>
+      </c>
+      <c r="B12" t="s">
+        <v>2083</v>
+      </c>
+      <c r="C12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1856</v>
+      </c>
+      <c r="E12" t="s">
+        <v>2084</v>
+      </c>
+      <c r="F12" t="s">
+        <v>2085</v>
+      </c>
+      <c r="G12" t="s">
+        <v>2086</v>
+      </c>
+      <c r="H12" t="s">
+        <v>69</v>
+      </c>
+      <c r="I12" t="s">
+        <v>2087</v>
+      </c>
+      <c r="J12" t="s">
+        <v>2088</v>
+      </c>
+      <c r="K12" t="s">
+        <v>2074</v>
+      </c>
+      <c r="L12" t="s">
+        <v>2583</v>
+      </c>
+      <c r="M12" t="s">
+        <v>1856</v>
+      </c>
+      <c r="N12" t="s">
+        <v>2584</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B13" t="s">
+        <v>2090</v>
+      </c>
+      <c r="C13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E13" t="s">
+        <v>2092</v>
+      </c>
+      <c r="F13" t="s">
+        <v>2007</v>
+      </c>
+      <c r="G13" t="s">
+        <v>2093</v>
+      </c>
+      <c r="H13" t="s">
+        <v>69</v>
+      </c>
+      <c r="I13" t="s">
+        <v>2094</v>
+      </c>
+      <c r="J13" t="s">
+        <v>2095</v>
+      </c>
+      <c r="K13" t="s">
+        <v>2096</v>
+      </c>
+      <c r="L13" t="s">
+        <v>2583</v>
+      </c>
+      <c r="M13" t="s">
+        <v>2091</v>
+      </c>
+      <c r="N13" t="s">
+        <v>2584</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" t="s">
+        <v>2097</v>
+      </c>
+      <c r="B14" t="s">
+        <v>2098</v>
+      </c>
+      <c r="C14" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" t="s">
+        <v>2099</v>
+      </c>
+      <c r="E14">
+        <v>824012823</v>
+      </c>
+      <c r="F14" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G14" t="s">
+        <v>2101</v>
+      </c>
+      <c r="H14" t="s">
+        <v>2102</v>
+      </c>
+      <c r="I14" t="s">
+        <v>2103</v>
+      </c>
+      <c r="J14" t="s">
+        <v>2104</v>
+      </c>
+      <c r="K14">
+        <v>824012823</v>
+      </c>
+      <c r="L14" t="s">
+        <v>2583</v>
+      </c>
+      <c r="M14" t="s">
+        <v>2105</v>
+      </c>
+      <c r="N14" t="s">
+        <v>2584</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" t="s">
+        <v>2106</v>
+      </c>
+      <c r="B15" t="s">
+        <v>2107</v>
+      </c>
+      <c r="C15" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" t="s">
+        <v>1856</v>
+      </c>
+      <c r="E15" t="s">
+        <v>2108</v>
+      </c>
+      <c r="F15" t="s">
+        <v>2085</v>
+      </c>
+      <c r="G15" t="s">
+        <v>2109</v>
+      </c>
+      <c r="H15" t="s">
+        <v>69</v>
+      </c>
+      <c r="I15" t="s">
+        <v>2110</v>
+      </c>
+      <c r="J15" t="s">
+        <v>2111</v>
+      </c>
+      <c r="K15" t="s">
+        <v>1943</v>
+      </c>
+      <c r="L15" t="s">
+        <v>2583</v>
+      </c>
+      <c r="M15" t="s">
+        <v>1856</v>
+      </c>
+      <c r="N15" t="s">
+        <v>2584</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" t="s">
+        <v>2112</v>
+      </c>
+      <c r="B16" t="s">
+        <v>2113</v>
+      </c>
+      <c r="C16" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" t="s">
+        <v>1856</v>
+      </c>
+      <c r="E16" t="s">
+        <v>2114</v>
+      </c>
+      <c r="F16" t="s">
+        <v>2023</v>
+      </c>
+      <c r="G16" t="s">
+        <v>2115</v>
+      </c>
+      <c r="H16" t="s">
+        <v>69</v>
+      </c>
+      <c r="I16" t="s">
+        <v>2116</v>
+      </c>
+      <c r="J16" t="s">
+        <v>2116</v>
+      </c>
+      <c r="K16" t="s">
+        <v>2117</v>
+      </c>
+      <c r="L16" t="s">
+        <v>2583</v>
+      </c>
+      <c r="M16" t="s">
+        <v>1856</v>
+      </c>
+      <c r="N16" t="s">
+        <v>2584</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" t="s">
+        <v>2118</v>
+      </c>
+      <c r="B17" t="s">
+        <v>2119</v>
+      </c>
+      <c r="C17" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" t="s">
+        <v>2120</v>
+      </c>
+      <c r="E17" t="s">
+        <v>2121</v>
+      </c>
+      <c r="F17" t="s">
+        <v>1877</v>
+      </c>
+      <c r="G17" t="s">
+        <v>2122</v>
+      </c>
+      <c r="H17" t="s">
+        <v>69</v>
+      </c>
+      <c r="I17" t="s">
+        <v>2123</v>
+      </c>
+      <c r="J17" t="s">
+        <v>2124</v>
+      </c>
+      <c r="K17" t="s">
+        <v>2125</v>
+      </c>
+      <c r="L17" t="s">
+        <v>2583</v>
+      </c>
+      <c r="M17" t="s">
+        <v>2120</v>
+      </c>
+      <c r="N17" t="s">
+        <v>2584</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" t="s">
+        <v>2126</v>
+      </c>
+      <c r="B18" t="s">
+        <v>2127</v>
+      </c>
+      <c r="C18" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" t="s">
+        <v>1856</v>
+      </c>
+      <c r="E18" t="s">
+        <v>2128</v>
+      </c>
+      <c r="F18" t="s">
+        <v>2129</v>
+      </c>
+      <c r="G18" t="s">
+        <v>2130</v>
+      </c>
+      <c r="H18" t="s">
+        <v>69</v>
+      </c>
+      <c r="I18" t="s">
+        <v>2131</v>
+      </c>
+      <c r="J18" t="s">
+        <v>2132</v>
+      </c>
+      <c r="K18" t="s">
+        <v>1943</v>
+      </c>
+      <c r="L18" t="s">
+        <v>2583</v>
+      </c>
+      <c r="M18" t="s">
+        <v>1856</v>
+      </c>
+      <c r="N18" t="s">
+        <v>2584</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" t="s">
+        <v>2133</v>
+      </c>
+      <c r="B19" t="s">
+        <v>2134</v>
+      </c>
+      <c r="C19" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" t="s">
+        <v>2135</v>
+      </c>
+      <c r="E19" t="s">
+        <v>2136</v>
+      </c>
+      <c r="F19" t="s">
+        <v>20</v>
+      </c>
+      <c r="G19" t="s">
+        <v>2137</v>
+      </c>
+      <c r="H19" t="s">
+        <v>69</v>
+      </c>
+      <c r="I19" t="s">
+        <v>2138</v>
+      </c>
+      <c r="J19" t="s">
+        <v>2139</v>
+      </c>
+      <c r="K19" t="s">
+        <v>2136</v>
+      </c>
+      <c r="L19" t="s">
+        <v>2583</v>
+      </c>
+      <c r="M19" t="s">
+        <v>2136</v>
+      </c>
+      <c r="N19" t="s">
+        <v>2584</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" t="s">
+        <v>2140</v>
+      </c>
+      <c r="B20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" t="s">
+        <v>2142</v>
+      </c>
+      <c r="E20" t="s">
+        <v>2143</v>
+      </c>
+      <c r="F20" t="s">
+        <v>1658</v>
+      </c>
+      <c r="G20" t="s">
+        <v>2144</v>
+      </c>
+      <c r="H20" t="s">
+        <v>69</v>
+      </c>
+      <c r="I20" t="s">
+        <v>2145</v>
+      </c>
+      <c r="J20" t="s">
+        <v>2146</v>
+      </c>
+      <c r="K20" t="s">
+        <v>2143</v>
+      </c>
+      <c r="L20" t="s">
+        <v>2583</v>
+      </c>
+      <c r="M20" t="s">
+        <v>2147</v>
+      </c>
+      <c r="N20" t="s">
+        <v>2584</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" t="s">
+        <v>2148</v>
+      </c>
+      <c r="B21" t="s">
+        <v>2149</v>
+      </c>
+      <c r="C21" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" t="s">
+        <v>1856</v>
+      </c>
+      <c r="E21" t="s">
+        <v>2150</v>
+      </c>
+      <c r="F21" t="s">
+        <v>1858</v>
+      </c>
+      <c r="G21" t="s">
+        <v>2151</v>
+      </c>
+      <c r="H21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I21" t="s">
+        <v>2152</v>
+      </c>
+      <c r="J21" t="s">
+        <v>2153</v>
+      </c>
+      <c r="K21" t="s">
+        <v>2154</v>
+      </c>
+      <c r="L21" t="s">
+        <v>2583</v>
+      </c>
+      <c r="M21" t="s">
+        <v>1856</v>
+      </c>
+      <c r="N21" t="s">
+        <v>2584</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" t="s">
+        <v>2155</v>
+      </c>
+      <c r="B22" t="s">
+        <v>2156</v>
+      </c>
+      <c r="C22" t="s">
+        <v>16</v>
+      </c>
+      <c r="D22" t="s">
+        <v>2157</v>
+      </c>
+      <c r="E22" t="s">
+        <v>2158</v>
+      </c>
+      <c r="F22" t="s">
+        <v>1696</v>
+      </c>
+      <c r="G22" t="s">
+        <v>2159</v>
+      </c>
+      <c r="H22" t="s">
+        <v>69</v>
+      </c>
+      <c r="I22" t="s">
+        <v>2160</v>
+      </c>
+      <c r="J22" t="s">
+        <v>2161</v>
+      </c>
+      <c r="K22" t="s">
+        <v>2052</v>
+      </c>
+      <c r="L22" t="s">
+        <v>2583</v>
+      </c>
+      <c r="M22" t="s">
+        <v>1904</v>
+      </c>
+      <c r="N22" t="s">
+        <v>2584</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" t="s">
+        <v>2162</v>
+      </c>
+      <c r="B23" t="s">
+        <v>2163</v>
+      </c>
+      <c r="C23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" t="s">
+        <v>1947</v>
+      </c>
+      <c r="E23" t="s">
+        <v>2164</v>
+      </c>
+      <c r="F23" t="s">
+        <v>1696</v>
+      </c>
+      <c r="G23" t="s">
+        <v>2165</v>
+      </c>
+      <c r="H23" t="s">
+        <v>69</v>
+      </c>
+      <c r="I23" t="s">
+        <v>2166</v>
+      </c>
+      <c r="J23" t="s">
+        <v>2167</v>
+      </c>
+      <c r="K23" t="s">
+        <v>2052</v>
+      </c>
+      <c r="L23" t="s">
+        <v>2583</v>
+      </c>
+      <c r="M23" t="s">
+        <v>2060</v>
+      </c>
+      <c r="N23" t="s">
+        <v>2584</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89BFA1EF-29B2-41E4-A9D1-F8E90A663FA1}">
   <dimension ref="A1:N23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -23435,7 +24711,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B6F0D32-9CE2-4DF7-927E-42E7BA331F12}">
   <dimension ref="A1:O21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -24402,254 +25678,4 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C98E1A12-072F-4773-8CB5-47FFE077E85B}">
-  <dimension ref="A1:N9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
-  <cols>
-    <col min="2" max="2" width="93.81640625" customWidth="1"/>
-    <col min="5" max="5" width="16.1796875" customWidth="1"/>
-    <col min="6" max="6" width="17.81640625" customWidth="1"/>
-    <col min="7" max="7" width="16.7265625" customWidth="1"/>
-    <col min="9" max="9" width="24.7265625" customWidth="1"/>
-    <col min="10" max="10" width="23.6328125" customWidth="1"/>
-    <col min="12" max="12" width="32.453125" customWidth="1"/>
-    <col min="13" max="13" width="14.90625" customWidth="1"/>
-    <col min="14" max="14" width="21.81640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F3" t="s">
-        <v>40</v>
-      </c>
-      <c r="G3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J3" t="s">
-        <v>43</v>
-      </c>
-      <c r="K3" t="s">
-        <v>39</v>
-      </c>
-      <c r="L3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M3" t="s">
-        <v>38</v>
-      </c>
-      <c r="N3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" t="s">
-        <v>1649</v>
-      </c>
-      <c r="B4" t="s">
-        <v>1650</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
-        <v>1651</v>
-      </c>
-      <c r="E4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" t="s">
-        <v>1652</v>
-      </c>
-      <c r="G4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" t="s">
-        <v>69</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>1654</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>1653</v>
-      </c>
-      <c r="K4" t="s">
-        <v>24</v>
-      </c>
-      <c r="L4" t="s">
-        <v>26</v>
-      </c>
-      <c r="M4" t="s">
-        <v>1651</v>
-      </c>
-      <c r="N4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" t="s">
-        <v>1655</v>
-      </c>
-      <c r="B5" t="s">
-        <v>1656</v>
-      </c>
-      <c r="C5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E5" t="s">
-        <v>39</v>
-      </c>
-      <c r="F5" t="s">
-        <v>1657</v>
-      </c>
-      <c r="G5" t="s">
-        <v>1658</v>
-      </c>
-      <c r="H5" t="s">
-        <v>69</v>
-      </c>
-      <c r="I5" t="s">
-        <v>1659</v>
-      </c>
-      <c r="J5" t="s">
-        <v>1660</v>
-      </c>
-      <c r="K5" t="s">
-        <v>39</v>
-      </c>
-      <c r="L5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M5" t="s">
-        <v>38</v>
-      </c>
-      <c r="N5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="L9" s="21"/>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="J2" r:id="rId1" xr:uid="{78125F11-BE4E-4312-8E61-0550889BB81F}"/>
-    <hyperlink ref="I2" r:id="rId2" xr:uid="{1CFCC581-B5E5-4159-8EE1-35A941FCD4DF}"/>
-    <hyperlink ref="J4" r:id="rId3" xr:uid="{BD7BCD4B-25F3-483F-8F98-D146F94F5AAF}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
-</worksheet>
 </file>
--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A235B2DA-ECEA-46D4-91B3-71E35DD00E8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC46636A-9846-467B-9B7C-C4FB9965F905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32280" yWindow="2235" windowWidth="29040" windowHeight="15720" firstSheet="9" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5356" uniqueCount="2585">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5380" uniqueCount="2597">
   <si>
     <t>ID</t>
   </si>
@@ -7792,6 +7792,42 @@
   </si>
   <si>
     <t>Pleeda_PcbLibrary/Pleeda_PcbLibrary.PcbLib</t>
+  </si>
+  <si>
+    <t>110-0055</t>
+  </si>
+  <si>
+    <t>110-0056</t>
+  </si>
+  <si>
+    <t>Pluggable Terminal Blocks 12 Pos 3.5mm pitch Plug 24-16AWG Spring</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Phoenix-Contact/1844317?qs=p6trItWzfMW9CXyhJ87RMQ%3D%3D</t>
+  </si>
+  <si>
+    <t>12P</t>
+  </si>
+  <si>
+    <t>THT 3,5mm</t>
+  </si>
+  <si>
+    <t>Pluggable Terminal Blocks 12 Pos 3.5mm pitch Through Hole Header</t>
+  </si>
+  <si>
+    <t>651-1844317</t>
+  </si>
+  <si>
+    <t>651-1952364</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/datasheet/3/507/9/phoenix_contact_1844317_en.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Phoenix-Contact/1952364?qs=6i0QExrCb7PyJNJO9S2%2Ffw%3D%3D</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/datasheet/3/507/9/phoenix_contact_1952364_en.pdf</t>
   </si>
 </sst>
 </file>
@@ -7961,7 +7997,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -8006,6 +8042,7 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -12910,7 +12947,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE14AD29-8DB0-4C42-AB91-A73B867AE121}">
-  <dimension ref="A1:N55"/>
+  <dimension ref="A1:N57"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:14">
@@ -15330,6 +15367,94 @@
         <v>1804920</v>
       </c>
       <c r="N55" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14">
+      <c r="A56" s="16" t="s">
+        <v>2585</v>
+      </c>
+      <c r="B56" t="s">
+        <v>2591</v>
+      </c>
+      <c r="C56" s="28" t="s">
+        <v>2589</v>
+      </c>
+      <c r="D56" s="16" t="s">
+        <v>2590</v>
+      </c>
+      <c r="E56">
+        <v>1844317</v>
+      </c>
+      <c r="F56" s="7" t="s">
+        <v>2281</v>
+      </c>
+      <c r="G56" s="28" t="s">
+        <v>2592</v>
+      </c>
+      <c r="H56" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I56" s="27" t="s">
+        <v>2594</v>
+      </c>
+      <c r="J56" s="2" t="s">
+        <v>2588</v>
+      </c>
+      <c r="K56" s="7" t="s">
+        <v>2441</v>
+      </c>
+      <c r="L56" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M56">
+        <v>1844317</v>
+      </c>
+      <c r="N56" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14">
+      <c r="A57" s="16" t="s">
+        <v>2586</v>
+      </c>
+      <c r="B57" t="s">
+        <v>2587</v>
+      </c>
+      <c r="C57" t="s">
+        <v>2589</v>
+      </c>
+      <c r="D57" s="16" t="s">
+        <v>2590</v>
+      </c>
+      <c r="E57">
+        <v>1952364</v>
+      </c>
+      <c r="F57" s="7" t="s">
+        <v>2281</v>
+      </c>
+      <c r="G57" t="s">
+        <v>2593</v>
+      </c>
+      <c r="H57" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I57" s="27" t="s">
+        <v>2596</v>
+      </c>
+      <c r="J57" s="2" t="s">
+        <v>2595</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>2540</v>
+      </c>
+      <c r="L57" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M57">
+        <v>1952364</v>
+      </c>
+      <c r="N57" s="7" t="s">
         <v>25</v>
       </c>
     </row>
@@ -15385,6 +15510,10 @@
     <hyperlink ref="J52" r:id="rId47" xr:uid="{E897E496-BD4D-4176-A529-0242E26116CB}"/>
     <hyperlink ref="I52" r:id="rId48" xr:uid="{A225907D-3E4C-4582-95BF-8DEDA99E88ED}"/>
     <hyperlink ref="I55" r:id="rId49" xr:uid="{A1002F44-75AF-44AC-BBCA-828DA38BB4E6}"/>
+    <hyperlink ref="J56" r:id="rId50" xr:uid="{8195B8EC-E2EB-40EB-9C49-2D817013AE1F}"/>
+    <hyperlink ref="I56" r:id="rId51" xr:uid="{CE941FB5-1D41-41B6-9CFD-C1256871C52E}"/>
+    <hyperlink ref="J57" r:id="rId52" xr:uid="{72ED46D3-1227-48FD-9800-7E78EA501F81}"/>
+    <hyperlink ref="I57" r:id="rId53" xr:uid="{30F29B76-2559-4C1E-A762-9F9E7C2882A4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -22651,6 +22780,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79E65951-BFD2-4888-A0A6-19D5130CB4A6}">
   <dimension ref="A1:N23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="2" max="2" width="41.1796875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="25" t="s">

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC46636A-9846-467B-9B7C-C4FB9965F905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B5541C4-0E93-40DB-A1EF-40B5365C76F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32280" yWindow="2235" windowWidth="29040" windowHeight="15720" firstSheet="9" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25812" yWindow="2904" windowWidth="23256" windowHeight="12456" firstSheet="9" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,8 @@
     <sheet name="050 - ICs - Analog" sheetId="2" r:id="rId10"/>
     <sheet name="060 - ICs - Digital" sheetId="3" r:id="rId11"/>
     <sheet name="070 - Power Supply - DCDC" sheetId="8" r:id="rId12"/>
-    <sheet name="110 - Connectors" sheetId="13" r:id="rId13"/>
+    <sheet name="100 - Electromechanicals" sheetId="15" r:id="rId13"/>
+    <sheet name="110 - Connectors" sheetId="13" r:id="rId14"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5380" uniqueCount="2597">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5714" uniqueCount="2768">
   <si>
     <t>ID</t>
   </si>
@@ -7828,6 +7829,519 @@
   </si>
   <si>
     <t>https://www.mouser.es/datasheet/3/507/9/phoenix_contact_1952364_en.pdf</t>
+  </si>
+  <si>
+    <t>100-0001</t>
+  </si>
+  <si>
+    <t>Interruptores táctiles 50mA@12VDC 260g OF Silver contacts</t>
+  </si>
+  <si>
+    <t>SWITCH TL3330</t>
+  </si>
+  <si>
+    <t>TL3330AF260QG</t>
+  </si>
+  <si>
+    <t>E-Switch</t>
+  </si>
+  <si>
+    <t>C2886886</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2110120930_E-Switch-TL3330AF260QG_C2886886.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/Tactile-Switches_E-Switch-TL3330AF260QG_C2886886.html</t>
+  </si>
+  <si>
+    <t>SWITCH</t>
+  </si>
+  <si>
+    <t>100-0002</t>
+  </si>
+  <si>
+    <t>M3 Screw</t>
+  </si>
+  <si>
+    <t>SCREW M3</t>
+  </si>
+  <si>
+    <t>M3</t>
+  </si>
+  <si>
+    <t>100-0003</t>
+  </si>
+  <si>
+    <t>Horizontal attachment 50mA Single Pole Double Throw (SPDT) 12V 10,000 times White SMD Slide Switches ROHS</t>
+  </si>
+  <si>
+    <t>SWITCH MSK12C02</t>
+  </si>
+  <si>
+    <t>MSK12C02</t>
+  </si>
+  <si>
+    <t>SHOU HAN</t>
+  </si>
+  <si>
+    <t>C431540</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2304140030_SHOU-HAN-MSK12C02_C431540.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/Slide-Switches_SHOU-HAN-MSK12C02_C431540.html</t>
+  </si>
+  <si>
+    <t>SLIDE SWITCH</t>
+  </si>
+  <si>
+    <t>100-0004</t>
+  </si>
+  <si>
+    <t>IQL-IMX258FF Mechanical</t>
+  </si>
+  <si>
+    <t>IQL-IMX258/FF</t>
+  </si>
+  <si>
+    <t>Image Quality Labs, Inc.</t>
+  </si>
+  <si>
+    <t>5449-IQL-IMX258/FF-ND</t>
+  </si>
+  <si>
+    <t>https://www.digikey.es/es/products/detail/image-quality-labs-inc/IQL-IMX258-FF/22033273</t>
+  </si>
+  <si>
+    <t>CAMERA</t>
+  </si>
+  <si>
+    <t>IQL-IMX258FF</t>
+  </si>
+  <si>
+    <t>100-0005</t>
+  </si>
+  <si>
+    <t>PCI Express/PCI Connectors .5PITCH 3.2H KEY B EMBOSS NGFF MINICARD</t>
+  </si>
+  <si>
+    <t>M2 Connector</t>
+  </si>
+  <si>
+    <t>CONN 3042-S3</t>
+  </si>
+  <si>
+    <t>2199119-3</t>
+  </si>
+  <si>
+    <t>571-2199119-3</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/datasheet/2/418/9/ENG_DS_1_1773702_1NGFFQRG_EN_0214_1_1773702_1NGFF_-3328635.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/TE-Connectivity/2199119-3?qs=EQCnRgr4b6Gv3vL0NE37dw%3D%3D</t>
+  </si>
+  <si>
+    <t>100-0006</t>
+  </si>
+  <si>
+    <t>SIMM Connectors PUSH-PUSH NANO SIM CONNECTOR</t>
+  </si>
+  <si>
+    <t>2336582-1</t>
+  </si>
+  <si>
+    <t>571-2336582-1</t>
+  </si>
+  <si>
+    <t>https://www.te.com/commerce/DocumentDelivery/DDEController?Action=srchrtrv&amp;DocNm=2336582&amp;DocType=Customer%20Drawing&amp;DocLang=English&amp;DocFormat=pdf&amp;PartCntxt=2336582-1</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/TE-Connectivity/2336582-1?qs=4ASt3YYao0UNpChcAI9ryg%3D%3D</t>
+  </si>
+  <si>
+    <t>SIM</t>
+  </si>
+  <si>
+    <t>NANO SIM CARD</t>
+  </si>
+  <si>
+    <t>100-0007</t>
+  </si>
+  <si>
+    <t>-40℃~+85℃ Card Slot MicroSD card (TF card) Self-bouncing SMD SD Card / Memory Card Connector ROHS</t>
+  </si>
+  <si>
+    <t>MOLEX</t>
+  </si>
+  <si>
+    <t>C293569</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2407022014_MOLEX-473521001_C293569.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/SD-Card-Memory-Card-Connector_MOLEX-473521001_C293569.html</t>
+  </si>
+  <si>
+    <t>SD CARD</t>
+  </si>
+  <si>
+    <t>100-0008</t>
+  </si>
+  <si>
+    <t>6mm 5mm Round Button 50mA Standing paste 6mm SPST 24V SMD Tactile Switches ROHS</t>
+  </si>
+  <si>
+    <t>4-1437565-2</t>
+  </si>
+  <si>
+    <t>C86487</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2304140030_TE-Connectivity-4-1437565-2_C86487.pdf</t>
+  </si>
+  <si>
+    <t>SWITCH 4-1437565-2</t>
+  </si>
+  <si>
+    <t>100-0009</t>
+  </si>
+  <si>
+    <t>Rectangle button 50mA Standing paste SPST - normally open 250gf 12V Tactile Switches ROHS</t>
+  </si>
+  <si>
+    <t>PTS636SK25SMTRLFS</t>
+  </si>
+  <si>
+    <t>C&amp;K</t>
+  </si>
+  <si>
+    <t>C2689642</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2410121617_C-K-PTS636SK25SMTRLFS_C2689642.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/Tactile-Switches_C-K-PTS636SK25SMTRLFS_C2689642.html</t>
+  </si>
+  <si>
+    <t>BUTTON SMD</t>
+  </si>
+  <si>
+    <t>100-0010</t>
+  </si>
+  <si>
+    <t>Potentiometers PANEL CONTROL - 9MM-ST-CARBON 10kOhms</t>
+  </si>
+  <si>
+    <t>PTV09A-3015F-B103</t>
+  </si>
+  <si>
+    <t>652-PTV09A-3015FB103</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/datasheet/2/54/ptv09-777818.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Bourns/PTV09A-3015F-B103?qs=5aG0NVq1C4zLnnFa8osaDg%3D%3D</t>
+  </si>
+  <si>
+    <t>PTV09A3015FB103</t>
+  </si>
+  <si>
+    <t>100-0011</t>
+  </si>
+  <si>
+    <t>±10% ±100ppm/℃ 500mW 10kΩ Plugin-3P,7x6.6mm Potentiometers, Variable Resistors ROHS</t>
+  </si>
+  <si>
+    <t>3362P-1-103LF</t>
+  </si>
+  <si>
+    <t>C58159</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2410121851_BOURNS-3362P-1-103LF_C58159.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/Potentiometers-Variable-Resistors_BOURNS-3362P-1-103LF_C58159.html</t>
+  </si>
+  <si>
+    <t>100-0012</t>
+  </si>
+  <si>
+    <t>3A Direct Insert Single Pole Double Throw (SPDT) 125V Black 10,000 times Plugin Slide Switches ROHS</t>
+  </si>
+  <si>
+    <t>SS-12D10L5</t>
+  </si>
+  <si>
+    <t>C319012</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2409302232_XKB-Connection-SS-12D10L5_C319012.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/Slide-Switches_XKB-Connection-SS-12D10L5_C319012.html</t>
+  </si>
+  <si>
+    <t>100-0013</t>
+  </si>
+  <si>
+    <t>Bend-in 3A Single Pole Double Throw (SPDT) 125V Black 10,000 times Plugin Slide Switches ROHS</t>
+  </si>
+  <si>
+    <t>SS-12D11G5R</t>
+  </si>
+  <si>
+    <t>C388633</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2110151730_XKB-Connection-SS-12D11G5R_C388633.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/Slide-Switches_XKB-Connection-SS-12D11G5R_C388633.html</t>
+  </si>
+  <si>
+    <t>SS12D11G5R</t>
+  </si>
+  <si>
+    <t>100-0014</t>
+  </si>
+  <si>
+    <t>M2.2 Screw</t>
+  </si>
+  <si>
+    <t>SCREW M2.2</t>
+  </si>
+  <si>
+    <t>M2.2</t>
+  </si>
+  <si>
+    <t>100-0015</t>
+  </si>
+  <si>
+    <t>M2x0.4 2.5mm NUT</t>
+  </si>
+  <si>
+    <t>9774025243R</t>
+  </si>
+  <si>
+    <t>Würth Elektronik</t>
+  </si>
+  <si>
+    <t>710-9774025243R</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/9774025243R.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/9774025243R?qs=KRpiEsko4Hk6kXQfB%252BOLaw%3D%3D</t>
+  </si>
+  <si>
+    <t>NUT M2x0.4 2.5mm</t>
+  </si>
+  <si>
+    <t>M2x0.4 2.5mm</t>
+  </si>
+  <si>
+    <t>100-0016</t>
+  </si>
+  <si>
+    <t>Led pipe</t>
+  </si>
+  <si>
+    <t>3x1</t>
+  </si>
+  <si>
+    <t>3 leds</t>
+  </si>
+  <si>
+    <t>515-1064F</t>
+  </si>
+  <si>
+    <t>Dialight</t>
+  </si>
+  <si>
+    <t>645-515-1064F</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/datasheet/2/109/DIACS02106_1-2541644.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Dialight/515-1064F?qs=Lbk6Md3wKLuSohCKHtGmow%3D%3D&amp;srsltid=AfmBOop-mnTt990trH7q1nL9lA-GBrMfhTKMf1tx32mNp4FM5HBS-m4L</t>
+  </si>
+  <si>
+    <t>Led Pipe 3x1</t>
+  </si>
+  <si>
+    <t>LED PIPE 3 leds</t>
+  </si>
+  <si>
+    <t>100-0017</t>
+  </si>
+  <si>
+    <t>M4 Screw</t>
+  </si>
+  <si>
+    <t>SCREW M4</t>
+  </si>
+  <si>
+    <t>M4</t>
+  </si>
+  <si>
+    <t>100-0018</t>
+  </si>
+  <si>
+    <t>8.5mm 3.95mm Round Button 50mA Surface Mount,Vertical 8.5mm SPST 16V SMD Tactile Switches ROHS</t>
+  </si>
+  <si>
+    <t>SKSTACE010</t>
+  </si>
+  <si>
+    <t>ALPSALPINE</t>
+  </si>
+  <si>
+    <t>C341731</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/C341731.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C341731.html?s_z=n_SKSTACE010</t>
+  </si>
+  <si>
+    <t>100-0019</t>
+  </si>
+  <si>
+    <t>1 24V 25mA 5000 cycles Red Slide, Rocked Through Hole DIP Switches/SIP Switches RoHS</t>
+  </si>
+  <si>
+    <t>THT</t>
+  </si>
+  <si>
+    <t>SMQS-01R-TP</t>
+  </si>
+  <si>
+    <t>SM Switch</t>
+  </si>
+  <si>
+    <t>C5299502</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/C5299502.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C5299502.html?s_z=n_418117270901</t>
+  </si>
+  <si>
+    <t>SWITCH2</t>
+  </si>
+  <si>
+    <t>SWITCH_418117270901</t>
+  </si>
+  <si>
+    <t>100-0020</t>
+  </si>
+  <si>
+    <t>Precision Potentiometers 7/8"WW 50Kohms 0.25% 10turn</t>
+  </si>
+  <si>
+    <t>50k</t>
+  </si>
+  <si>
+    <t>3590S-2-503L</t>
+  </si>
+  <si>
+    <t>652-3590S-2-503L</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/datasheet/3/40/1/3590.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Bourns/3590S-2-503L?qs=ka0oSW1bB1JSm13%252BOBM7sg%3D%3D</t>
+  </si>
+  <si>
+    <t>Potenciometer</t>
+  </si>
+  <si>
+    <t>3590S</t>
+  </si>
+  <si>
+    <t>100-0021</t>
+  </si>
+  <si>
+    <t>Tactile Switch SPST 160gf 2mm SMD (SMT) Tab 4mm x 3mm Surface Mount</t>
+  </si>
+  <si>
+    <t>SMD,4x3mm</t>
+  </si>
+  <si>
+    <t>TS-1088-AR02016</t>
+  </si>
+  <si>
+    <t>XUNPU</t>
+  </si>
+  <si>
+    <t>C720477</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/C720477.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C720477.html</t>
+  </si>
+  <si>
+    <t>BUTTON SMD,4x3mm</t>
+  </si>
+  <si>
+    <t>100-0022</t>
+  </si>
+  <si>
+    <t>Conmutadores giratorio 8 Pos 0.3 Amp at 16 Volts</t>
+  </si>
+  <si>
+    <t>8 pos</t>
+  </si>
+  <si>
+    <t>SRBV181004</t>
+  </si>
+  <si>
+    <t>688-SRBV181004</t>
+  </si>
+  <si>
+    <t>https://docs.rs-online.com/47c9/0900766b8152d5b2.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Alps-Alpine/SRBV181004?qs=YMSFtX0bdJCnOlZQh4GDrA%3D%3D&amp;srsltid=AfmBOooFNq_nH20SG4zXm7xm5pij0Uqr6AHHnHbfDp4KMa-rPMhSe6U-</t>
+  </si>
+  <si>
+    <t>SRBV1</t>
+  </si>
+  <si>
+    <t>100-0023</t>
+  </si>
+  <si>
+    <t>Conmutadores giratorio 3 Pos 0.3 Amp at 16 Volts</t>
+  </si>
+  <si>
+    <t>3 pos</t>
+  </si>
+  <si>
+    <t>SRBV131803</t>
+  </si>
+  <si>
+    <t>688-SRBV131803</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Alps-Alpine/SRBV131803?qs=YMSFtX0bdJDOFh3k1w%2FD5w%3D%3D</t>
+  </si>
+  <si>
+    <t>eUSR_SchLibrary/eUSR_SchLibrary - Electromechanicals.SchLib</t>
   </si>
 </sst>
 </file>
@@ -7997,7 +8511,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -8042,7 +8556,6 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -12946,6 +13459,1089 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69A1C46E-DEF3-467B-A5BD-162AB66E6A86}">
+  <dimension ref="A1:N24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" s="7" t="s">
+        <v>2597</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>2598</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>2599</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>2600</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>2601</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>2602</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>2603</v>
+      </c>
+      <c r="J2" s="15" t="s">
+        <v>2604</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>2605</v>
+      </c>
+      <c r="L2" s="7" t="s">
+        <v>2767</v>
+      </c>
+      <c r="M2" s="7" t="s">
+        <v>2599</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="7" t="s">
+        <v>2606</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>2607</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>2608</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>2767</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>2609</v>
+      </c>
+      <c r="N3" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="7" t="s">
+        <v>2610</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>2611</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>2612</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>2613</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>2614</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>2615</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>2616</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>2617</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>2618</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>2767</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>2612</v>
+      </c>
+      <c r="N4" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="7" t="s">
+        <v>2619</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>2620</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>2621</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>2622</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>2623</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>2185</v>
+      </c>
+      <c r="I5" s="3"/>
+      <c r="J5" s="7" t="s">
+        <v>2624</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>2625</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>2767</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>2626</v>
+      </c>
+      <c r="N5" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="7" t="s">
+        <v>2627</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>2628</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>2629</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>2630</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>2631</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>2192</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>2632</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>2633</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>2634</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>2630</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>2767</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>2630</v>
+      </c>
+      <c r="N6" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="7" t="s">
+        <v>2635</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>2636</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>2637</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>2192</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>2638</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>2639</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>2640</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>2641</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>2767</v>
+      </c>
+      <c r="M7" s="7" t="s">
+        <v>2642</v>
+      </c>
+      <c r="N7" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="7" t="s">
+        <v>2643</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>2644</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="7">
+        <v>473521001</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>2645</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>2646</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>2647</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>2648</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>2649</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>2767</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>2649</v>
+      </c>
+      <c r="N8" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="7" t="s">
+        <v>2650</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>2651</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>2652</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>2192</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>2653</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I9" s="15" t="s">
+        <v>2654</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>2648</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>2605</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>2767</v>
+      </c>
+      <c r="M9" s="7" t="s">
+        <v>2655</v>
+      </c>
+      <c r="N9" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="7" t="s">
+        <v>2656</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>2657</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>2658</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>2659</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>2660</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I10" s="15" t="s">
+        <v>2661</v>
+      </c>
+      <c r="J10" s="15" t="s">
+        <v>2662</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>2663</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>2767</v>
+      </c>
+      <c r="M10" s="7" t="s">
+        <v>2663</v>
+      </c>
+      <c r="N10" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="7" t="s">
+        <v>2664</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>2665</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>2666</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>1516</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>2667</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I11" s="15" t="s">
+        <v>2668</v>
+      </c>
+      <c r="J11" s="15" t="s">
+        <v>2669</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>2670</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>2767</v>
+      </c>
+      <c r="M11" s="7" t="s">
+        <v>2670</v>
+      </c>
+      <c r="N11" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="7" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>2673</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>1516</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>2674</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I12" s="15" t="s">
+        <v>2675</v>
+      </c>
+      <c r="J12" s="15" t="s">
+        <v>2676</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>2673</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>2767</v>
+      </c>
+      <c r="M12" s="7" t="s">
+        <v>2673</v>
+      </c>
+      <c r="N12" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="7" t="s">
+        <v>2677</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>2678</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>2679</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>2230</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>2680</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I13" s="15" t="s">
+        <v>2681</v>
+      </c>
+      <c r="J13" s="15" t="s">
+        <v>2682</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>2679</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>2767</v>
+      </c>
+      <c r="M13" s="7" t="s">
+        <v>2679</v>
+      </c>
+      <c r="N13" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="7" t="s">
+        <v>2683</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>2684</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>2685</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>2230</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>2686</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I14" s="15" t="s">
+        <v>2687</v>
+      </c>
+      <c r="J14" s="15" t="s">
+        <v>2688</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>2685</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>2767</v>
+      </c>
+      <c r="M14" s="7" t="s">
+        <v>2689</v>
+      </c>
+      <c r="N14" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="7" t="s">
+        <v>2690</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>2691</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>2692</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>2767</v>
+      </c>
+      <c r="M15" s="7" t="s">
+        <v>2693</v>
+      </c>
+      <c r="N15" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="7" t="s">
+        <v>2694</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>2695</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>2696</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>2697</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>2698</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I16" s="15" t="s">
+        <v>2699</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>2700</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>2701</v>
+      </c>
+      <c r="L16" s="7" t="s">
+        <v>2767</v>
+      </c>
+      <c r="M16" s="7" t="s">
+        <v>2702</v>
+      </c>
+      <c r="N16" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" s="7" t="s">
+        <v>2703</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>2704</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>2705</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>2706</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>2707</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>2708</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>2709</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I17" s="15" t="s">
+        <v>2710</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>2711</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>2712</v>
+      </c>
+      <c r="L17" s="7" t="s">
+        <v>2767</v>
+      </c>
+      <c r="M17" s="7" t="s">
+        <v>2713</v>
+      </c>
+      <c r="N17" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" s="7" t="s">
+        <v>2714</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>2715</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>2716</v>
+      </c>
+      <c r="L18" s="7" t="s">
+        <v>2767</v>
+      </c>
+      <c r="M18" s="7" t="s">
+        <v>2717</v>
+      </c>
+      <c r="N18" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" s="7" t="s">
+        <v>2718</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>2719</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>2720</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>2721</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>2722</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>2723</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>2724</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>2663</v>
+      </c>
+      <c r="L19" s="7" t="s">
+        <v>2767</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>2720</v>
+      </c>
+      <c r="N19" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" s="7" t="s">
+        <v>2725</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>2726</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>2727</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>2728</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>2729</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>2730</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>2731</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>2732</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>2733</v>
+      </c>
+      <c r="L20" s="7" t="s">
+        <v>2767</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>2734</v>
+      </c>
+      <c r="N20" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" s="7" t="s">
+        <v>2735</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>2736</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>2737</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>2738</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>1516</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>2739</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I21" s="18" t="s">
+        <v>2740</v>
+      </c>
+      <c r="J21" s="18" t="s">
+        <v>2741</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>2742</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>2767</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>2743</v>
+      </c>
+      <c r="N21" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" s="16" t="s">
+        <v>2744</v>
+      </c>
+      <c r="B22" s="17" t="s">
+        <v>2745</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>2746</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>2747</v>
+      </c>
+      <c r="F22" s="16" t="s">
+        <v>2748</v>
+      </c>
+      <c r="G22" s="16" t="s">
+        <v>2749</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I22" s="18" t="s">
+        <v>2750</v>
+      </c>
+      <c r="J22" s="18" t="s">
+        <v>2751</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>2663</v>
+      </c>
+      <c r="L22" s="7" t="s">
+        <v>2767</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>2752</v>
+      </c>
+      <c r="N22" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" s="16" t="s">
+        <v>2753</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>2754</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>2755</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>2756</v>
+      </c>
+      <c r="F23" s="16" t="s">
+        <v>2721</v>
+      </c>
+      <c r="G23" s="16" t="s">
+        <v>2757</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>2758</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>2759</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>2760</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>2767</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>2760</v>
+      </c>
+      <c r="N23" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" s="16" t="s">
+        <v>2761</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>2762</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>2763</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>2764</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>2721</v>
+      </c>
+      <c r="G24" s="16" t="s">
+        <v>2765</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>2758</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>2766</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>2760</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>2767</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>2760</v>
+      </c>
+      <c r="N24" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="J2" r:id="rId1" xr:uid="{00000000-0004-0000-1C00-000000000000}"/>
+    <hyperlink ref="I9" r:id="rId2" xr:uid="{00000000-0004-0000-1C00-000001000000}"/>
+    <hyperlink ref="I10" r:id="rId3" xr:uid="{00000000-0004-0000-1C00-000002000000}"/>
+    <hyperlink ref="J10" r:id="rId4" xr:uid="{00000000-0004-0000-1C00-000003000000}"/>
+    <hyperlink ref="I11" r:id="rId5" xr:uid="{00000000-0004-0000-1C00-000004000000}"/>
+    <hyperlink ref="J11" r:id="rId6" xr:uid="{00000000-0004-0000-1C00-000005000000}"/>
+    <hyperlink ref="I12" r:id="rId7" xr:uid="{00000000-0004-0000-1C00-000006000000}"/>
+    <hyperlink ref="J12" r:id="rId8" xr:uid="{00000000-0004-0000-1C00-000007000000}"/>
+    <hyperlink ref="I13" r:id="rId9" xr:uid="{00000000-0004-0000-1C00-000008000000}"/>
+    <hyperlink ref="J13" r:id="rId10" xr:uid="{00000000-0004-0000-1C00-000009000000}"/>
+    <hyperlink ref="I14" r:id="rId11" xr:uid="{00000000-0004-0000-1C00-00000A000000}"/>
+    <hyperlink ref="J14" r:id="rId12" xr:uid="{00000000-0004-0000-1C00-00000B000000}"/>
+    <hyperlink ref="I16" r:id="rId13" xr:uid="{00000000-0004-0000-1C00-00000C000000}"/>
+    <hyperlink ref="I17" r:id="rId14" xr:uid="{00000000-0004-0000-1C00-00000D000000}"/>
+    <hyperlink ref="I21" r:id="rId15" xr:uid="{AD5A87ED-A0D2-49BB-BF8B-5EA637022C09}"/>
+    <hyperlink ref="J21" r:id="rId16" xr:uid="{E50D755E-D0F0-4B33-91BE-C8BA1C67603C}"/>
+    <hyperlink ref="I22" r:id="rId17" xr:uid="{181D1681-B006-4138-A389-4F31BE31FFD2}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE14AD29-8DB0-4C42-AB91-A73B867AE121}">
   <dimension ref="A1:N57"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -15377,7 +16973,7 @@
       <c r="B56" t="s">
         <v>2591</v>
       </c>
-      <c r="C56" s="28" t="s">
+      <c r="C56" s="16" t="s">
         <v>2589</v>
       </c>
       <c r="D56" s="16" t="s">
@@ -15389,7 +16985,7 @@
       <c r="F56" s="7" t="s">
         <v>2281</v>
       </c>
-      <c r="G56" s="28" t="s">
+      <c r="G56" s="16" t="s">
         <v>2592</v>
       </c>
       <c r="H56" s="16" t="s">

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B5541C4-0E93-40DB-A1EF-40B5365C76F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56290A70-B004-48E3-8E25-4B08EC159660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25812" yWindow="2904" windowWidth="23256" windowHeight="12456" firstSheet="9" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25812" yWindow="2904" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5714" uniqueCount="2768">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5716" uniqueCount="2880">
   <si>
     <t>ID</t>
   </si>
@@ -8342,6 +8342,342 @@
   </si>
   <si>
     <t>eUSR_SchLibrary/eUSR_SchLibrary - Electromechanicals.SchLib</t>
+  </si>
+  <si>
+    <t>033-0001</t>
+  </si>
+  <si>
+    <t>350mA 5000K White 120° 2.8V 3535 LED Indication - Discrete ROHS</t>
+  </si>
+  <si>
+    <t>White</t>
+  </si>
+  <si>
+    <t>SPHWH2L3D30CD4RTP3</t>
+  </si>
+  <si>
+    <t>Samsung</t>
+  </si>
+  <si>
+    <t>C17347838</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2311050349_Samsung-SPHWH2L3D30CD4RTP3_C17347838.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/LED-Indication-Discrete_Samsung-SPHWH2L3D30CD4RTP3_C17347838.html</t>
+  </si>
+  <si>
+    <t>LED WHITE</t>
+  </si>
+  <si>
+    <t>Pleeda_SchLibrary/Pleeda_SchLibrary - LEDs.SchLib</t>
+  </si>
+  <si>
+    <t>LED SMD 3535</t>
+  </si>
+  <si>
+    <t>033-0002</t>
+  </si>
+  <si>
+    <t>20mA 660mcd Yellow lens -20℃~+85℃ Positive Stick White 120° 70mW 3.3V 0805 LED Indication - Discrete ROHS</t>
+  </si>
+  <si>
+    <t>XL-2012UWC</t>
+  </si>
+  <si>
+    <t>XINGLIGHT</t>
+  </si>
+  <si>
+    <t>C965818</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2402181505_XINGLIGHT-XL-2012UWC_C965818.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/LED-Indication-Discrete_XINGLIGHT-XL-2012UWC_C965818.html</t>
+  </si>
+  <si>
+    <t>LED SMD 0805 WHITE</t>
+  </si>
+  <si>
+    <t>033-0003</t>
+  </si>
+  <si>
+    <t>20mA Colorless Transparent Lens 20mcd~55mcd 468nm~478nm -30℃~+85℃ Blue 130° 72mW 2.5V~3.6V 0805 LED Indication - Discrete ROHS</t>
+  </si>
+  <si>
+    <t>Blue</t>
+  </si>
+  <si>
+    <t>NCD0805B2</t>
+  </si>
+  <si>
+    <t>Foshan NationStar Optoelectronics</t>
+  </si>
+  <si>
+    <t>C84259</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2409272203_Foshan-NationStar-Optoelectronics-NCD0805B2_C84259.pdf</t>
+  </si>
+  <si>
+    <t>033-0004</t>
+  </si>
+  <si>
+    <t>20mA 215mcd Colorless Transparent Lens 565nm~575nm -20℃~+85℃ Positive Stick Yellow-green 120° 50mW 2.3V 0805 LED Indication - Discrete ROHS</t>
+  </si>
+  <si>
+    <t>Green</t>
+  </si>
+  <si>
+    <t>XL-2012SYGC</t>
+  </si>
+  <si>
+    <t>XINGLIGHT XL-2012SYGC</t>
+  </si>
+  <si>
+    <t>C965816</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2410121310_XINGLIGHT-XL-2012SYGC_C965816.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/Light-Emitting-Diodes-span-style-background-color-ff0-LED-span_XINGLIGHT-XL-2012SYGC_C965816.html</t>
+  </si>
+  <si>
+    <t>033-0005</t>
+  </si>
+  <si>
+    <t>25mA 67mcd~195mcd -30℃~+85℃ 615nm~630nm Independent Diode Red 130° 65mW 1.6V~2.6V 0805 LED Indication - Discrete ROHS</t>
+  </si>
+  <si>
+    <t>Red</t>
+  </si>
+  <si>
+    <t>NCD0805R1</t>
+  </si>
+  <si>
+    <t>C84256</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2409272203_Foshan-NationStar-Optoelectronics-NCD0805R1_C84256.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/LED-Indication-Discrete_Foshan-NationStar-Optoelectronics-NCD0805R1_C84256.html</t>
+  </si>
+  <si>
+    <t>033-0006</t>
+  </si>
+  <si>
+    <t>Single Colour LEDs 302nm UVB</t>
+  </si>
+  <si>
+    <t>UV</t>
+  </si>
+  <si>
+    <t>3.5x3.5mm</t>
+  </si>
+  <si>
+    <t>XBT-3535-UV-A130H-M-CB-300-00</t>
+  </si>
+  <si>
+    <t>Luminus Devices</t>
+  </si>
+  <si>
+    <t>896-XBT3535UV130MCB3</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/datasheet/2/245/Luminus_XBT_3535_UV_Mini_308_Datasheet-3474139.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Luminus-Devices/XBT-3535-UV-A130H-M-CB-300-00?qs=IKkN%2F947nfCah%2FvUXVr1TQ%3D%3D</t>
+  </si>
+  <si>
+    <t>LED UV</t>
+  </si>
+  <si>
+    <t>XBT-3535</t>
+  </si>
+  <si>
+    <t>033-0007</t>
+  </si>
+  <si>
+    <t>LED UV Nichia, λ 375nm, 110 °, 9,9mW, mont. superficial de 2 pines</t>
+  </si>
+  <si>
+    <t>3x2mm</t>
+  </si>
+  <si>
+    <t>NSSU100DT</t>
+  </si>
+  <si>
+    <t>Nichia</t>
+  </si>
+  <si>
+    <t>890-3966</t>
+  </si>
+  <si>
+    <t>RS</t>
+  </si>
+  <si>
+    <t>https://docs.rs-online.com/d92d/0900766b81427cbe.pdf</t>
+  </si>
+  <si>
+    <t>https://es.rs-online.com/web/p/leds-uv/8903966</t>
+  </si>
+  <si>
+    <t>LED_NSSU100DT</t>
+  </si>
+  <si>
+    <t>033-0008</t>
+  </si>
+  <si>
+    <t>60mA 20000mcd Water Clear -40℃~+100℃ 440nm~460nm Blue 60° 2.6V~3.3V SMD2835 LED Indication - Discrete ROHS</t>
+  </si>
+  <si>
+    <t>SMD2835</t>
+  </si>
+  <si>
+    <t>JNJ-LTJB0102W60</t>
+  </si>
+  <si>
+    <t>JNJ OPTOELECTRONICS</t>
+  </si>
+  <si>
+    <t>C7500141</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2410121451_JNJ-OPTOELECTRONICS-JNJ-LTJB0102W60-9x26mil-440-460NM_C7500141.pdf</t>
+  </si>
+  <si>
+    <t>https://lcsc.com/product-detail/LED-Indication-Discrete_JNJ-OPTOELECTRONICS-JNJ-LTJB0102W60-9x26mil-440-460NM_C7500141.html</t>
+  </si>
+  <si>
+    <t>LED_SMD_2835</t>
+  </si>
+  <si>
+    <t>033-0009</t>
+  </si>
+  <si>
+    <t>20mA 45408K 520mcd -40℃~+85℃ 470nm Cold White 120° 70mW 2.6V~3.1V 1206 LED Indication - Discrete ROHS</t>
+  </si>
+  <si>
+    <t>YLED1206WFT</t>
+  </si>
+  <si>
+    <t>YONGYUTAI</t>
+  </si>
+  <si>
+    <t>C41383589</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/lcsc_datasheet_2411220031_YONGYUTAI-YLED1206WFT_C41383589.pdf</t>
+  </si>
+  <si>
+    <t>https://lcsc.com/product-detail/LED-Indication-Discrete_YONGYUTAI-YLED1206WFT_C41383589.html</t>
+  </si>
+  <si>
+    <t>LED_1206</t>
+  </si>
+  <si>
+    <t>033-0010</t>
+  </si>
+  <si>
+    <t>LED de un solo color PURE GREEN WTR CLR</t>
+  </si>
+  <si>
+    <t>Gren</t>
+  </si>
+  <si>
+    <t>APL3015PGC</t>
+  </si>
+  <si>
+    <t>Kingbright</t>
+  </si>
+  <si>
+    <t>604-APL3015PGC</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/datasheet/2/216/kingbright_kngbd00006-6-1736201.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Kingbright/APL3015PGC?qs=E09Sz5t5voVlJOJdR4AFPQ%3D%3D</t>
+  </si>
+  <si>
+    <t>033-0011</t>
+  </si>
+  <si>
+    <t>LED UV Seoul Viosys, λ 420nm, 1W, encapsulado 3535</t>
+  </si>
+  <si>
+    <t>SMD3535</t>
+  </si>
+  <si>
+    <t>CUN26A1B</t>
+  </si>
+  <si>
+    <t>Seoul Viosys</t>
+  </si>
+  <si>
+    <t>247-1986</t>
+  </si>
+  <si>
+    <t>https://docs.rs-online.com/cbb4/A700000008908489.pdf</t>
+  </si>
+  <si>
+    <t>https://es.rs-online.com/web/p/leds-uv/2471986</t>
+  </si>
+  <si>
+    <t>033-0012</t>
+  </si>
+  <si>
+    <t>SMD,2.2x2mm RGB LEDs(Built-in IC) ROHS</t>
+  </si>
+  <si>
+    <t>RGB</t>
+  </si>
+  <si>
+    <t>SMD,2.2x2mm</t>
+  </si>
+  <si>
+    <t>WS2812B-2020</t>
+  </si>
+  <si>
+    <t>Worldsemi</t>
+  </si>
+  <si>
+    <t>C965555</t>
+  </si>
+  <si>
+    <t>https://lcsc.com/datasheet/lcsc_datasheet_2412051755_Worldsemi-WS2812B-2020_C965555.pdf</t>
+  </si>
+  <si>
+    <t>https://lcsc.com/product-detail/RGB-LEDs-Built-in-IC_Worldsemi-WS2812B-2020_C965555.html?s_z=n_C965555</t>
+  </si>
+  <si>
+    <t>LED RGB_IC</t>
+  </si>
+  <si>
+    <t>033-0013</t>
+  </si>
+  <si>
+    <t>Emerald Green 525nm LED Indication - Discrete 2.6V~3V 0603</t>
+  </si>
+  <si>
+    <t>XL-1608PGC-06</t>
+  </si>
+  <si>
+    <t>C7371905</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/datasheet/C7371905.pdf</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C7371905.html</t>
+  </si>
+  <si>
+    <t>LED SMD 0603</t>
   </si>
 </sst>
 </file>
@@ -8511,7 +8847,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -8556,6 +8892,21 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -25444,573 +25795,575 @@
       </c>
     </row>
     <row r="2" spans="1:14">
-      <c r="A2" s="7" t="s">
-        <v>2003</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>2004</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>2005</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>2006</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>2007</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>2008</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>2009</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>2010</v>
-      </c>
-      <c r="K2" s="7" t="s">
-        <v>2011</v>
-      </c>
-      <c r="L2" s="7" t="s">
-        <v>1910</v>
-      </c>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7" t="s">
-        <v>25</v>
+      <c r="A2" s="29" t="s">
+        <v>2768</v>
+      </c>
+      <c r="B2" s="29" t="s">
+        <v>2769</v>
+      </c>
+      <c r="C2" s="29" t="s">
+        <v>2770</v>
+      </c>
+      <c r="D2" s="29">
+        <v>3535</v>
+      </c>
+      <c r="E2" s="29" t="s">
+        <v>2771</v>
+      </c>
+      <c r="F2" s="29" t="s">
+        <v>2772</v>
+      </c>
+      <c r="G2" s="29" t="s">
+        <v>2773</v>
+      </c>
+      <c r="H2" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="I2" s="29" t="s">
+        <v>2774</v>
+      </c>
+      <c r="J2" s="29" t="s">
+        <v>2775</v>
+      </c>
+      <c r="K2" s="29" t="s">
+        <v>2776</v>
+      </c>
+      <c r="L2" s="29" t="s">
+        <v>2777</v>
+      </c>
+      <c r="M2" s="29" t="s">
+        <v>2778</v>
+      </c>
+      <c r="N2" s="29" t="s">
+        <v>2584</v>
       </c>
     </row>
     <row r="3" spans="1:14">
-      <c r="A3" s="7" t="s">
-        <v>2012</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>2013</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>2014</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>2015</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>2016</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>2017</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I3" s="10" t="s">
-        <v>2018</v>
-      </c>
-      <c r="J3" s="10" t="s">
-        <v>2019</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>2011</v>
-      </c>
-      <c r="L3" s="7" t="s">
-        <v>1910</v>
-      </c>
-      <c r="M3" s="7" t="s">
-        <v>2014</v>
-      </c>
-      <c r="N3" s="7" t="s">
-        <v>25</v>
+      <c r="A3" s="29" t="s">
+        <v>2779</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>2780</v>
+      </c>
+      <c r="C3" s="29" t="s">
+        <v>2770</v>
+      </c>
+      <c r="D3" s="32" t="s">
+        <v>240</v>
+      </c>
+      <c r="E3" s="29" t="s">
+        <v>2781</v>
+      </c>
+      <c r="F3" s="29" t="s">
+        <v>2782</v>
+      </c>
+      <c r="G3" s="29" t="s">
+        <v>2783</v>
+      </c>
+      <c r="H3" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="I3" s="29" t="s">
+        <v>2784</v>
+      </c>
+      <c r="J3" s="33" t="s">
+        <v>2785</v>
+      </c>
+      <c r="K3" s="29" t="s">
+        <v>2776</v>
+      </c>
+      <c r="L3" s="29" t="s">
+        <v>2777</v>
+      </c>
+      <c r="M3" s="29" t="s">
+        <v>2786</v>
+      </c>
+      <c r="N3" s="29" t="s">
+        <v>2584</v>
       </c>
     </row>
     <row r="4" spans="1:14">
-      <c r="A4" s="7" t="s">
-        <v>2020</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>2021</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>2022</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>2023</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>2024</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I4" s="15" t="s">
-        <v>2025</v>
-      </c>
-      <c r="J4" s="15" t="s">
-        <v>2026</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>2011</v>
-      </c>
-      <c r="L4" s="7" t="s">
-        <v>1910</v>
-      </c>
-      <c r="M4" s="7" t="s">
-        <v>2027</v>
-      </c>
-      <c r="N4" s="7" t="s">
-        <v>25</v>
+      <c r="A4" s="29" t="s">
+        <v>2787</v>
+      </c>
+      <c r="B4" s="29" t="s">
+        <v>2788</v>
+      </c>
+      <c r="C4" s="29" t="s">
+        <v>2789</v>
+      </c>
+      <c r="D4" s="32" t="s">
+        <v>240</v>
+      </c>
+      <c r="E4" s="29" t="s">
+        <v>2790</v>
+      </c>
+      <c r="F4" s="29" t="s">
+        <v>2791</v>
+      </c>
+      <c r="G4" s="29" t="s">
+        <v>2792</v>
+      </c>
+      <c r="H4" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="I4" s="29" t="s">
+        <v>2793</v>
+      </c>
+      <c r="J4" s="29" t="s">
+        <v>2793</v>
+      </c>
+      <c r="K4" s="29" t="s">
+        <v>2776</v>
+      </c>
+      <c r="L4" s="29" t="s">
+        <v>2777</v>
+      </c>
+      <c r="M4" s="29" t="s">
+        <v>2786</v>
+      </c>
+      <c r="N4" s="29" t="s">
+        <v>2584</v>
       </c>
     </row>
     <row r="5" spans="1:14">
-      <c r="A5" s="7" t="s">
-        <v>2028</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>2029</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>2030</v>
-      </c>
-      <c r="E5" s="16" t="s">
-        <v>2031</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>1858</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>2032</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I5" s="15" t="s">
-        <v>2033</v>
-      </c>
-      <c r="J5" s="15" t="s">
-        <v>2034</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>1918</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>1910</v>
-      </c>
-      <c r="M5" s="7" t="s">
-        <v>2030</v>
-      </c>
-      <c r="N5" s="7" t="s">
-        <v>25</v>
+      <c r="A5" s="29" t="s">
+        <v>2794</v>
+      </c>
+      <c r="B5" s="29" t="s">
+        <v>2795</v>
+      </c>
+      <c r="C5" s="29" t="s">
+        <v>2796</v>
+      </c>
+      <c r="D5" s="32" t="s">
+        <v>240</v>
+      </c>
+      <c r="E5" s="29" t="s">
+        <v>2797</v>
+      </c>
+      <c r="F5" s="29" t="s">
+        <v>2798</v>
+      </c>
+      <c r="G5" s="29" t="s">
+        <v>2799</v>
+      </c>
+      <c r="H5" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="I5" s="33" t="s">
+        <v>2800</v>
+      </c>
+      <c r="J5" s="33" t="s">
+        <v>2801</v>
+      </c>
+      <c r="K5" s="29" t="s">
+        <v>2776</v>
+      </c>
+      <c r="L5" s="29" t="s">
+        <v>2777</v>
+      </c>
+      <c r="M5" s="29" t="s">
+        <v>2786</v>
+      </c>
+      <c r="N5" s="29" t="s">
+        <v>2584</v>
       </c>
     </row>
     <row r="6" spans="1:14">
-      <c r="A6" s="7" t="s">
-        <v>2035</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>2036</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>2037</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>2038</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>2039</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>2040</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I6" s="15" t="s">
-        <v>2041</v>
-      </c>
-      <c r="J6" s="15" t="s">
-        <v>2042</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>2043</v>
-      </c>
-      <c r="L6" s="7" t="s">
-        <v>1910</v>
-      </c>
-      <c r="M6" s="7" t="s">
-        <v>2044</v>
-      </c>
-      <c r="N6" s="7" t="s">
-        <v>25</v>
+      <c r="A6" s="29" t="s">
+        <v>2802</v>
+      </c>
+      <c r="B6" s="29" t="s">
+        <v>2803</v>
+      </c>
+      <c r="C6" s="29" t="s">
+        <v>2804</v>
+      </c>
+      <c r="D6" s="32" t="s">
+        <v>240</v>
+      </c>
+      <c r="E6" s="29" t="s">
+        <v>2805</v>
+      </c>
+      <c r="F6" s="29" t="s">
+        <v>2791</v>
+      </c>
+      <c r="G6" s="29" t="s">
+        <v>2806</v>
+      </c>
+      <c r="H6" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="I6" s="31" t="s">
+        <v>2807</v>
+      </c>
+      <c r="J6" s="31" t="s">
+        <v>2808</v>
+      </c>
+      <c r="K6" s="29" t="s">
+        <v>2776</v>
+      </c>
+      <c r="L6" s="29" t="s">
+        <v>2777</v>
+      </c>
+      <c r="M6" s="29" t="s">
+        <v>2786</v>
+      </c>
+      <c r="N6" s="29" t="s">
+        <v>2584</v>
       </c>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7" s="7" t="s">
-        <v>2045</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>2046</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>2048</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>1696</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>2049</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>2050</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>2051</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>2052</v>
-      </c>
-      <c r="L7" s="7" t="s">
-        <v>1910</v>
-      </c>
-      <c r="M7" s="7" t="s">
-        <v>2047</v>
-      </c>
-      <c r="N7" s="7" t="s">
-        <v>25</v>
+      <c r="A7" s="29" t="s">
+        <v>2809</v>
+      </c>
+      <c r="B7" s="29" t="s">
+        <v>2810</v>
+      </c>
+      <c r="C7" s="29" t="s">
+        <v>2811</v>
+      </c>
+      <c r="D7" s="29" t="s">
+        <v>2812</v>
+      </c>
+      <c r="E7" s="29" t="s">
+        <v>2813</v>
+      </c>
+      <c r="F7" s="30" t="s">
+        <v>2814</v>
+      </c>
+      <c r="G7" s="29" t="s">
+        <v>2815</v>
+      </c>
+      <c r="H7" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="34" t="s">
+        <v>2816</v>
+      </c>
+      <c r="J7" s="34" t="s">
+        <v>2817</v>
+      </c>
+      <c r="K7" s="29" t="s">
+        <v>2818</v>
+      </c>
+      <c r="L7" s="29" t="s">
+        <v>2777</v>
+      </c>
+      <c r="M7" s="34" t="s">
+        <v>2819</v>
+      </c>
+      <c r="N7" s="29" t="s">
+        <v>2584</v>
       </c>
     </row>
     <row r="8" spans="1:14">
-      <c r="A8" s="7" t="s">
-        <v>2053</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>2054</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>1947</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>2055</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>2056</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>2057</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>2058</v>
-      </c>
-      <c r="J8" s="15" t="s">
-        <v>2059</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>2052</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>1910</v>
-      </c>
-      <c r="M8" s="7" t="s">
-        <v>2060</v>
-      </c>
-      <c r="N8" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="7" t="s">
-        <v>2061</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>2062</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>1947</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>2063</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>2064</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>2065</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I9" s="15" t="s">
-        <v>2066</v>
-      </c>
-      <c r="J9" s="15" t="s">
-        <v>2067</v>
-      </c>
-      <c r="K9" s="7" t="s">
-        <v>2052</v>
-      </c>
-      <c r="L9" s="7" t="s">
-        <v>1910</v>
-      </c>
-      <c r="M9" s="7" t="s">
-        <v>1947</v>
-      </c>
-      <c r="N9" s="7" t="s">
-        <v>25</v>
+      <c r="A8" s="29" t="s">
+        <v>2820</v>
+      </c>
+      <c r="B8" s="29" t="s">
+        <v>2821</v>
+      </c>
+      <c r="C8" s="29" t="s">
+        <v>2811</v>
+      </c>
+      <c r="D8" s="29" t="s">
+        <v>2822</v>
+      </c>
+      <c r="E8" s="29" t="s">
+        <v>2823</v>
+      </c>
+      <c r="F8" s="36" t="s">
+        <v>2824</v>
+      </c>
+      <c r="G8" s="36" t="s">
+        <v>2825</v>
+      </c>
+      <c r="H8" s="36" t="s">
+        <v>2826</v>
+      </c>
+      <c r="I8" s="28" t="s">
+        <v>2827</v>
+      </c>
+      <c r="J8" s="28" t="s">
+        <v>2828</v>
+      </c>
+      <c r="K8" s="29" t="s">
+        <v>2776</v>
+      </c>
+      <c r="L8" s="29" t="s">
+        <v>2777</v>
+      </c>
+      <c r="M8" s="28" t="s">
+        <v>2829</v>
+      </c>
+      <c r="N8" s="29" t="s">
+        <v>2584</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="14.5" customHeight="1">
+      <c r="A9" s="29" t="s">
+        <v>2830</v>
+      </c>
+      <c r="B9" s="28" t="s">
+        <v>2831</v>
+      </c>
+      <c r="C9" s="35" t="s">
+        <v>2789</v>
+      </c>
+      <c r="D9" s="28" t="s">
+        <v>2832</v>
+      </c>
+      <c r="E9" s="38" t="s">
+        <v>2833</v>
+      </c>
+      <c r="F9" s="36" t="s">
+        <v>2834</v>
+      </c>
+      <c r="G9" s="36" t="s">
+        <v>2835</v>
+      </c>
+      <c r="H9" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="I9" s="28" t="s">
+        <v>2836</v>
+      </c>
+      <c r="J9" s="28" t="s">
+        <v>2837</v>
+      </c>
+      <c r="K9" s="29" t="s">
+        <v>2776</v>
+      </c>
+      <c r="L9" s="29" t="s">
+        <v>2777</v>
+      </c>
+      <c r="M9" s="35" t="s">
+        <v>2838</v>
+      </c>
+      <c r="N9" s="29" t="s">
+        <v>2584</v>
       </c>
     </row>
     <row r="10" spans="1:14">
-      <c r="A10" s="7" t="s">
-        <v>2068</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>2069</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>2070</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>2070</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>1981</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>2071</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>2072</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>2073</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>2074</v>
-      </c>
-      <c r="L10" s="7" t="s">
-        <v>1910</v>
-      </c>
-      <c r="M10" s="7" t="s">
-        <v>1856</v>
-      </c>
-      <c r="N10" s="7" t="s">
-        <v>25</v>
+      <c r="A10" s="29" t="s">
+        <v>2839</v>
+      </c>
+      <c r="B10" s="37" t="s">
+        <v>2840</v>
+      </c>
+      <c r="C10" s="35" t="s">
+        <v>2789</v>
+      </c>
+      <c r="D10" s="39" t="s">
+        <v>249</v>
+      </c>
+      <c r="E10" s="28" t="s">
+        <v>2841</v>
+      </c>
+      <c r="F10" s="28" t="s">
+        <v>2842</v>
+      </c>
+      <c r="G10" s="28" t="s">
+        <v>2843</v>
+      </c>
+      <c r="H10" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="I10" s="28" t="s">
+        <v>2844</v>
+      </c>
+      <c r="J10" s="28" t="s">
+        <v>2845</v>
+      </c>
+      <c r="K10" s="29" t="s">
+        <v>2776</v>
+      </c>
+      <c r="L10" s="29" t="s">
+        <v>2777</v>
+      </c>
+      <c r="M10" s="35" t="s">
+        <v>2846</v>
+      </c>
+      <c r="N10" s="29" t="s">
+        <v>2584</v>
       </c>
     </row>
     <row r="11" spans="1:14">
-      <c r="A11" s="7" t="s">
-        <v>2075</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>2076</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>1856</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>2077</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>945</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>2078</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>2079</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>2080</v>
-      </c>
-      <c r="K11" s="7" t="s">
-        <v>2081</v>
-      </c>
-      <c r="L11" s="7" t="s">
-        <v>1910</v>
-      </c>
-      <c r="M11" s="7" t="s">
-        <v>1856</v>
-      </c>
-      <c r="N11" s="7" t="s">
-        <v>25</v>
+      <c r="A11" s="29" t="s">
+        <v>2847</v>
+      </c>
+      <c r="B11" s="37" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C11" s="35" t="s">
+        <v>2849</v>
+      </c>
+      <c r="D11" s="39" t="s">
+        <v>249</v>
+      </c>
+      <c r="E11" s="28" t="s">
+        <v>2850</v>
+      </c>
+      <c r="F11" s="37" t="s">
+        <v>2851</v>
+      </c>
+      <c r="G11" s="28" t="s">
+        <v>2852</v>
+      </c>
+      <c r="H11" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="I11" s="28" t="s">
+        <v>2853</v>
+      </c>
+      <c r="J11" s="28" t="s">
+        <v>2854</v>
+      </c>
+      <c r="K11" s="29" t="s">
+        <v>2776</v>
+      </c>
+      <c r="L11" s="29" t="s">
+        <v>2777</v>
+      </c>
+      <c r="M11" s="35" t="s">
+        <v>2846</v>
+      </c>
+      <c r="N11" s="29" t="s">
+        <v>2584</v>
       </c>
     </row>
     <row r="12" spans="1:14">
-      <c r="A12" s="7" t="s">
-        <v>2082</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>2083</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>1856</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>2084</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>2085</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>2086</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>2087</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>2088</v>
-      </c>
-      <c r="K12" s="7" t="s">
-        <v>2074</v>
-      </c>
-      <c r="L12" s="7" t="s">
-        <v>1910</v>
-      </c>
-      <c r="M12" s="7" t="s">
-        <v>1856</v>
-      </c>
-      <c r="N12" s="7" t="s">
-        <v>25</v>
+      <c r="A12" s="29" t="s">
+        <v>2855</v>
+      </c>
+      <c r="B12" s="37" t="s">
+        <v>2856</v>
+      </c>
+      <c r="C12" s="35" t="s">
+        <v>2811</v>
+      </c>
+      <c r="D12" s="35" t="s">
+        <v>2857</v>
+      </c>
+      <c r="E12" s="35" t="s">
+        <v>2858</v>
+      </c>
+      <c r="F12" s="35" t="s">
+        <v>2859</v>
+      </c>
+      <c r="G12" s="28" t="s">
+        <v>2860</v>
+      </c>
+      <c r="H12" s="36" t="s">
+        <v>2826</v>
+      </c>
+      <c r="I12" s="28" t="s">
+        <v>2861</v>
+      </c>
+      <c r="J12" s="28" t="s">
+        <v>2862</v>
+      </c>
+      <c r="K12" s="29" t="s">
+        <v>2818</v>
+      </c>
+      <c r="L12" s="29" t="s">
+        <v>2777</v>
+      </c>
+      <c r="M12" s="28" t="s">
+        <v>2858</v>
+      </c>
+      <c r="N12" s="29" t="s">
+        <v>2584</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="13.5" customHeight="1">
-      <c r="A13" s="7" t="s">
-        <v>2089</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>2090</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>2091</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>2092</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>2007</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>2093</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I13" s="11" t="s">
-        <v>2094</v>
-      </c>
-      <c r="J13" s="11" t="s">
-        <v>2095</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>2096</v>
-      </c>
-      <c r="L13" s="7" t="s">
-        <v>1910</v>
-      </c>
-      <c r="M13" s="7" t="s">
-        <v>2091</v>
-      </c>
-      <c r="N13" s="7" t="s">
-        <v>25</v>
+      <c r="A13" s="29" t="s">
+        <v>2863</v>
+      </c>
+      <c r="B13" s="28" t="s">
+        <v>2864</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>2865</v>
+      </c>
+      <c r="D13" s="28" t="s">
+        <v>2866</v>
+      </c>
+      <c r="E13" s="28" t="s">
+        <v>2867</v>
+      </c>
+      <c r="F13" s="28" t="s">
+        <v>2868</v>
+      </c>
+      <c r="G13" s="28" t="s">
+        <v>2869</v>
+      </c>
+      <c r="H13" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="I13" s="28" t="s">
+        <v>2870</v>
+      </c>
+      <c r="J13" s="28" t="s">
+        <v>2871</v>
+      </c>
+      <c r="K13" s="29" t="s">
+        <v>2872</v>
+      </c>
+      <c r="L13" s="29" t="s">
+        <v>2777</v>
+      </c>
+      <c r="M13" s="28" t="s">
+        <v>2867</v>
+      </c>
+      <c r="N13" s="29" t="s">
+        <v>2584</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="15" customHeight="1">
-      <c r="A14" s="7" t="s">
-        <v>2097</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>2098</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>2099</v>
-      </c>
-      <c r="E14" s="7">
-        <v>824012823</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>2100</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>2101</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>2102</v>
-      </c>
-      <c r="I14" s="15" t="s">
-        <v>2103</v>
-      </c>
-      <c r="J14" s="15" t="s">
-        <v>2104</v>
-      </c>
-      <c r="K14" s="7">
-        <v>824012823</v>
-      </c>
-      <c r="L14" s="7" t="s">
-        <v>1910</v>
-      </c>
-      <c r="M14" s="7" t="s">
-        <v>2105</v>
-      </c>
-      <c r="N14" s="7" t="s">
-        <v>25</v>
+      <c r="A14" s="29" t="s">
+        <v>2873</v>
+      </c>
+      <c r="B14" s="28" t="s">
+        <v>2874</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>2796</v>
+      </c>
+      <c r="D14" s="40" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" s="28" t="s">
+        <v>2875</v>
+      </c>
+      <c r="F14" s="28" t="s">
+        <v>2782</v>
+      </c>
+      <c r="G14" s="28" t="s">
+        <v>2876</v>
+      </c>
+      <c r="H14" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>2877</v>
+      </c>
+      <c r="J14" s="28" t="s">
+        <v>2878</v>
+      </c>
+      <c r="K14" s="29" t="s">
+        <v>2776</v>
+      </c>
+      <c r="L14" s="29" t="s">
+        <v>2777</v>
+      </c>
+      <c r="M14" s="28" t="s">
+        <v>2879</v>
+      </c>
+      <c r="N14" s="29" t="s">
+        <v>2584</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -26411,29 +26764,21 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="I3" r:id="rId1" xr:uid="{00000000-0004-0000-0A00-000000000000}"/>
-    <hyperlink ref="J3" r:id="rId2" xr:uid="{00000000-0004-0000-0A00-000001000000}"/>
-    <hyperlink ref="I4" r:id="rId3" xr:uid="{00000000-0004-0000-0A00-000002000000}"/>
-    <hyperlink ref="J4" r:id="rId4" xr:uid="{00000000-0004-0000-0A00-000003000000}"/>
-    <hyperlink ref="I5" r:id="rId5" xr:uid="{00000000-0004-0000-0A00-000004000000}"/>
-    <hyperlink ref="J5" r:id="rId6" xr:uid="{00000000-0004-0000-0A00-000005000000}"/>
-    <hyperlink ref="I6" r:id="rId7" xr:uid="{00000000-0004-0000-0A00-000006000000}"/>
-    <hyperlink ref="J6" r:id="rId8" xr:uid="{00000000-0004-0000-0A00-000007000000}"/>
-    <hyperlink ref="J8" r:id="rId9" xr:uid="{00000000-0004-0000-0A00-000008000000}"/>
-    <hyperlink ref="I9" r:id="rId10" xr:uid="{00000000-0004-0000-0A00-000009000000}"/>
-    <hyperlink ref="J9" r:id="rId11" xr:uid="{00000000-0004-0000-0A00-00000A000000}"/>
-    <hyperlink ref="I13" r:id="rId12" xr:uid="{00000000-0004-0000-0A00-00000B000000}"/>
-    <hyperlink ref="J13" r:id="rId13" xr:uid="{00000000-0004-0000-0A00-00000C000000}"/>
-    <hyperlink ref="I14" r:id="rId14" xr:uid="{00000000-0004-0000-0A00-00000D000000}"/>
-    <hyperlink ref="J14" r:id="rId15" xr:uid="{00000000-0004-0000-0A00-00000E000000}"/>
-    <hyperlink ref="I15" r:id="rId16" xr:uid="{00000000-0004-0000-0A00-00000F000000}"/>
-    <hyperlink ref="J15" r:id="rId17" xr:uid="{00000000-0004-0000-0A00-000010000000}"/>
-    <hyperlink ref="I16" r:id="rId18" xr:uid="{00000000-0004-0000-0A00-000011000000}"/>
-    <hyperlink ref="J16" r:id="rId19" xr:uid="{00000000-0004-0000-0A00-000012000000}"/>
-    <hyperlink ref="I17" r:id="rId20" xr:uid="{00000000-0004-0000-0A00-000013000000}"/>
-    <hyperlink ref="J17" r:id="rId21" xr:uid="{00000000-0004-0000-0A00-000014000000}"/>
-    <hyperlink ref="I21" r:id="rId22" xr:uid="{E5D95628-DADF-425D-8DC6-0740E7A281C6}"/>
-    <hyperlink ref="J23" r:id="rId23" xr:uid="{21B09737-BF9A-463D-87B2-ED444DC9196C}"/>
+    <hyperlink ref="I15" r:id="rId1" xr:uid="{00000000-0004-0000-0A00-00000F000000}"/>
+    <hyperlink ref="J15" r:id="rId2" xr:uid="{00000000-0004-0000-0A00-000010000000}"/>
+    <hyperlink ref="I16" r:id="rId3" xr:uid="{00000000-0004-0000-0A00-000011000000}"/>
+    <hyperlink ref="J16" r:id="rId4" xr:uid="{00000000-0004-0000-0A00-000012000000}"/>
+    <hyperlink ref="I17" r:id="rId5" xr:uid="{00000000-0004-0000-0A00-000013000000}"/>
+    <hyperlink ref="J17" r:id="rId6" xr:uid="{00000000-0004-0000-0A00-000014000000}"/>
+    <hyperlink ref="I21" r:id="rId7" xr:uid="{E5D95628-DADF-425D-8DC6-0740E7A281C6}"/>
+    <hyperlink ref="J23" r:id="rId8" xr:uid="{21B09737-BF9A-463D-87B2-ED444DC9196C}"/>
+    <hyperlink ref="J3" r:id="rId9" xr:uid="{00000000-0004-0000-0B00-000000000000}"/>
+    <hyperlink ref="I5" r:id="rId10" xr:uid="{00000000-0004-0000-0B00-000001000000}"/>
+    <hyperlink ref="J5" r:id="rId11" xr:uid="{00000000-0004-0000-0B00-000002000000}"/>
+    <hyperlink ref="I6" r:id="rId12" xr:uid="{00000000-0004-0000-0B00-000003000000}"/>
+    <hyperlink ref="J6" r:id="rId13" xr:uid="{00000000-0004-0000-0B00-000004000000}"/>
+    <hyperlink ref="F7" r:id="rId14" xr:uid="{00000000-0004-0000-0B00-000005000000}"/>
+    <hyperlink ref="I14" r:id="rId15" xr:uid="{BFE50862-7088-44B1-9DAF-F4C51270ACE8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56290A70-B004-48E3-8E25-4B08EC159660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D62A594-312B-4529-ABA1-0D99DBEEA679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25812" yWindow="2904" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25812" yWindow="2904" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5716" uniqueCount="2880">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5716" uniqueCount="2878">
   <si>
     <t>ID</t>
   </si>
@@ -7789,12 +7789,6 @@
     <t>https://www.mouser.es/ProductDetail/Phoenix-Contact/1804920?qs=bbdZqDPQhEUmz%252BLlbRELng%3D%3D</t>
   </si>
   <si>
-    <t>Pleeda_SchLibrary/Pleeda_SchLibrary - Diode.SchLib</t>
-  </si>
-  <si>
-    <t>Pleeda_PcbLibrary/Pleeda_PcbLibrary.PcbLib</t>
-  </si>
-  <si>
     <t>110-0055</t>
   </si>
   <si>
@@ -8371,9 +8365,6 @@
     <t>LED WHITE</t>
   </si>
   <si>
-    <t>Pleeda_SchLibrary/Pleeda_SchLibrary - LEDs.SchLib</t>
-  </si>
-  <si>
     <t>LED SMD 3535</t>
   </si>
   <si>
@@ -8678,6 +8669,9 @@
   </si>
   <si>
     <t>LED SMD 0603</t>
+  </si>
+  <si>
+    <t>eUSR_SchLibrary/eUSR_SchLibrary - LEDs.SchLib</t>
   </si>
 </sst>
 </file>
@@ -8847,7 +8841,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -8892,21 +8886,10 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -13860,43 +13843,43 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="7" t="s">
-        <v>2597</v>
+        <v>2595</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>2598</v>
+        <v>2596</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>16</v>
       </c>
       <c r="D2" s="7" t="s">
+        <v>2597</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>2598</v>
+      </c>
+      <c r="F2" s="7" t="s">
         <v>2599</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="G2" s="7" t="s">
         <v>2600</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="H2" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I2" s="7" t="s">
         <v>2601</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="J2" s="15" t="s">
         <v>2602</v>
       </c>
-      <c r="H2" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I2" s="7" t="s">
+      <c r="K2" s="7" t="s">
         <v>2603</v>
       </c>
-      <c r="J2" s="15" t="s">
-        <v>2604</v>
-      </c>
-      <c r="K2" s="7" t="s">
-        <v>2605</v>
-      </c>
       <c r="L2" s="7" t="s">
-        <v>2767</v>
+        <v>2765</v>
       </c>
       <c r="M2" s="7" t="s">
-        <v>2599</v>
+        <v>2597</v>
       </c>
       <c r="N2" s="7" t="s">
         <v>25</v>
@@ -13904,10 +13887,10 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="7" t="s">
-        <v>2606</v>
+        <v>2604</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>2607</v>
+        <v>2605</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>16</v>
@@ -13934,13 +13917,13 @@
         <v>16</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>2608</v>
+        <v>2606</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>2767</v>
+        <v>2765</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>2609</v>
+        <v>2607</v>
       </c>
       <c r="N3" s="7" t="s">
         <v>25</v>
@@ -13948,43 +13931,43 @@
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="7" t="s">
-        <v>2610</v>
+        <v>2608</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>2611</v>
+        <v>2609</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>16</v>
       </c>
       <c r="D4" s="7" t="s">
+        <v>2610</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>2611</v>
+      </c>
+      <c r="F4" s="7" t="s">
         <v>2612</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="G4" s="9" t="s">
         <v>2613</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="H4" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I4" s="7" t="s">
         <v>2614</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="J4" s="7" t="s">
         <v>2615</v>
       </c>
-      <c r="H4" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I4" s="7" t="s">
+      <c r="K4" s="7" t="s">
         <v>2616</v>
       </c>
-      <c r="J4" s="7" t="s">
-        <v>2617</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>2618</v>
-      </c>
       <c r="L4" s="7" t="s">
-        <v>2767</v>
+        <v>2765</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>2612</v>
+        <v>2610</v>
       </c>
       <c r="N4" s="7" t="s">
         <v>25</v>
@@ -13992,10 +13975,10 @@
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="7" t="s">
-        <v>2619</v>
+        <v>2617</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>2620</v>
+        <v>2618</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>16</v>
@@ -14004,29 +13987,29 @@
         <v>16</v>
       </c>
       <c r="E5" s="7" t="s">
+        <v>2619</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>2620</v>
+      </c>
+      <c r="G5" s="7" t="s">
         <v>2621</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>2622</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>2623</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>2185</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="7" t="s">
+        <v>2622</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>2623</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>2765</v>
+      </c>
+      <c r="M5" s="7" t="s">
         <v>2624</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>2625</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>2767</v>
-      </c>
-      <c r="M5" s="7" t="s">
-        <v>2626</v>
       </c>
       <c r="N5" s="7" t="s">
         <v>25</v>
@@ -14034,43 +14017,43 @@
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="7" t="s">
+        <v>2625</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>2626</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>2627</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="D6" s="7" t="s">
         <v>2628</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="E6" s="7" t="s">
         <v>2629</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>2630</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>2631</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>2192</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>2632</v>
+        <v>2630</v>
       </c>
       <c r="H6" s="7" t="s">
         <v>21</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>2633</v>
+        <v>2631</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>2634</v>
+        <v>2632</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>2630</v>
+        <v>2628</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>2767</v>
+        <v>2765</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>2630</v>
+        <v>2628</v>
       </c>
       <c r="N6" s="7" t="s">
         <v>25</v>
@@ -14078,10 +14061,10 @@
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="7" t="s">
-        <v>2635</v>
+        <v>2633</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>2636</v>
+        <v>2634</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>16</v>
@@ -14090,31 +14073,31 @@
         <v>16</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>2637</v>
+        <v>2635</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>2192</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>2638</v>
+        <v>2636</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>21</v>
       </c>
       <c r="I7" s="7" t="s">
+        <v>2637</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>2638</v>
+      </c>
+      <c r="K7" s="7" t="s">
         <v>2639</v>
       </c>
-      <c r="J7" s="7" t="s">
+      <c r="L7" s="7" t="s">
+        <v>2765</v>
+      </c>
+      <c r="M7" s="7" t="s">
         <v>2640</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>2641</v>
-      </c>
-      <c r="L7" s="7" t="s">
-        <v>2767</v>
-      </c>
-      <c r="M7" s="7" t="s">
-        <v>2642</v>
       </c>
       <c r="N7" s="7" t="s">
         <v>25</v>
@@ -14122,10 +14105,10 @@
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="7" t="s">
-        <v>2643</v>
+        <v>2641</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>2644</v>
+        <v>2642</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>16</v>
@@ -14137,28 +14120,28 @@
         <v>473521001</v>
       </c>
       <c r="F8" s="7" t="s">
+        <v>2643</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>2644</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I8" s="7" t="s">
         <v>2645</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="J8" s="7" t="s">
         <v>2646</v>
       </c>
-      <c r="H8" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I8" s="7" t="s">
+      <c r="K8" s="7" t="s">
         <v>2647</v>
       </c>
-      <c r="J8" s="7" t="s">
-        <v>2648</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>2649</v>
-      </c>
       <c r="L8" s="7" t="s">
-        <v>2767</v>
+        <v>2765</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>2649</v>
+        <v>2647</v>
       </c>
       <c r="N8" s="7" t="s">
         <v>25</v>
@@ -14166,10 +14149,10 @@
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="7" t="s">
-        <v>2650</v>
+        <v>2648</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>2651</v>
+        <v>2649</v>
       </c>
       <c r="C9" s="13" t="s">
         <v>16</v>
@@ -14178,31 +14161,31 @@
         <v>16</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>2652</v>
+        <v>2650</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>2192</v>
       </c>
       <c r="G9" s="7" t="s">
+        <v>2651</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I9" s="15" t="s">
+        <v>2652</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>2646</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>2603</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>2765</v>
+      </c>
+      <c r="M9" s="7" t="s">
         <v>2653</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I9" s="15" t="s">
-        <v>2654</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>2648</v>
-      </c>
-      <c r="K9" s="7" t="s">
-        <v>2605</v>
-      </c>
-      <c r="L9" s="7" t="s">
-        <v>2767</v>
-      </c>
-      <c r="M9" s="7" t="s">
-        <v>2655</v>
       </c>
       <c r="N9" s="7" t="s">
         <v>25</v>
@@ -14210,10 +14193,10 @@
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="7" t="s">
-        <v>2656</v>
+        <v>2654</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>2657</v>
+        <v>2655</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>16</v>
@@ -14222,31 +14205,31 @@
         <v>16</v>
       </c>
       <c r="E10" s="7" t="s">
+        <v>2656</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>2657</v>
+      </c>
+      <c r="G10" s="7" t="s">
         <v>2658</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="H10" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I10" s="15" t="s">
         <v>2659</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="J10" s="15" t="s">
         <v>2660</v>
       </c>
-      <c r="H10" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I10" s="15" t="s">
+      <c r="K10" s="7" t="s">
         <v>2661</v>
       </c>
-      <c r="J10" s="15" t="s">
-        <v>2662</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>2663</v>
-      </c>
       <c r="L10" s="7" t="s">
-        <v>2767</v>
+        <v>2765</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>2663</v>
+        <v>2661</v>
       </c>
       <c r="N10" s="7" t="s">
         <v>25</v>
@@ -14254,10 +14237,10 @@
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="7" t="s">
-        <v>2664</v>
+        <v>2662</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>2665</v>
+        <v>2663</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>16</v>
@@ -14266,31 +14249,31 @@
         <v>16</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>2666</v>
+        <v>2664</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>1516</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>2667</v>
+        <v>2665</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>21</v>
       </c>
       <c r="I11" s="15" t="s">
+        <v>2666</v>
+      </c>
+      <c r="J11" s="15" t="s">
+        <v>2667</v>
+      </c>
+      <c r="K11" s="7" t="s">
         <v>2668</v>
       </c>
-      <c r="J11" s="15" t="s">
-        <v>2669</v>
-      </c>
-      <c r="K11" s="7" t="s">
-        <v>2670</v>
-      </c>
       <c r="L11" s="7" t="s">
-        <v>2767</v>
+        <v>2765</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>2670</v>
+        <v>2668</v>
       </c>
       <c r="N11" s="7" t="s">
         <v>25</v>
@@ -14298,10 +14281,10 @@
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="7" t="s">
-        <v>2671</v>
+        <v>2669</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>2672</v>
+        <v>2670</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>16</v>
@@ -14310,31 +14293,31 @@
         <v>16</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>2673</v>
+        <v>2671</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>1516</v>
       </c>
       <c r="G12" s="7" t="s">
+        <v>2672</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I12" s="15" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J12" s="15" t="s">
         <v>2674</v>
       </c>
-      <c r="H12" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I12" s="15" t="s">
-        <v>2675</v>
-      </c>
-      <c r="J12" s="15" t="s">
-        <v>2676</v>
-      </c>
       <c r="K12" s="7" t="s">
-        <v>2673</v>
+        <v>2671</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>2767</v>
+        <v>2765</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>2673</v>
+        <v>2671</v>
       </c>
       <c r="N12" s="7" t="s">
         <v>25</v>
@@ -14342,10 +14325,10 @@
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="7" t="s">
-        <v>2677</v>
+        <v>2675</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>2678</v>
+        <v>2676</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>16</v>
@@ -14354,31 +14337,31 @@
         <v>16</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>2679</v>
+        <v>2677</v>
       </c>
       <c r="F13" s="7" t="s">
         <v>2230</v>
       </c>
       <c r="G13" s="7" t="s">
+        <v>2678</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I13" s="15" t="s">
+        <v>2679</v>
+      </c>
+      <c r="J13" s="15" t="s">
         <v>2680</v>
       </c>
-      <c r="H13" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I13" s="15" t="s">
-        <v>2681</v>
-      </c>
-      <c r="J13" s="15" t="s">
-        <v>2682</v>
-      </c>
       <c r="K13" s="7" t="s">
-        <v>2679</v>
+        <v>2677</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>2767</v>
+        <v>2765</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>2679</v>
+        <v>2677</v>
       </c>
       <c r="N13" s="7" t="s">
         <v>25</v>
@@ -14386,10 +14369,10 @@
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="7" t="s">
-        <v>2683</v>
+        <v>2681</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>2684</v>
+        <v>2682</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>16</v>
@@ -14398,31 +14381,31 @@
         <v>16</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>2685</v>
+        <v>2683</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>2230</v>
       </c>
       <c r="G14" s="7" t="s">
+        <v>2684</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I14" s="15" t="s">
+        <v>2685</v>
+      </c>
+      <c r="J14" s="15" t="s">
         <v>2686</v>
       </c>
-      <c r="H14" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I14" s="15" t="s">
+      <c r="K14" s="7" t="s">
+        <v>2683</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>2765</v>
+      </c>
+      <c r="M14" s="7" t="s">
         <v>2687</v>
-      </c>
-      <c r="J14" s="15" t="s">
-        <v>2688</v>
-      </c>
-      <c r="K14" s="7" t="s">
-        <v>2685</v>
-      </c>
-      <c r="L14" s="7" t="s">
-        <v>2767</v>
-      </c>
-      <c r="M14" s="7" t="s">
-        <v>2689</v>
       </c>
       <c r="N14" s="7" t="s">
         <v>25</v>
@@ -14430,10 +14413,10 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="7" t="s">
-        <v>2690</v>
+        <v>2688</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>2691</v>
+        <v>2689</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>16</v>
@@ -14460,13 +14443,13 @@
         <v>16</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>2692</v>
+        <v>2690</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>2767</v>
+        <v>2765</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>2693</v>
+        <v>2691</v>
       </c>
       <c r="N15" s="7" t="s">
         <v>25</v>
@@ -14474,10 +14457,10 @@
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="7" t="s">
-        <v>2694</v>
+        <v>2692</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>2695</v>
+        <v>2693</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>16</v>
@@ -14486,31 +14469,31 @@
         <v>16</v>
       </c>
       <c r="E16" s="7" t="s">
+        <v>2694</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>2695</v>
+      </c>
+      <c r="G16" s="7" t="s">
         <v>2696</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>2697</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>2698</v>
       </c>
       <c r="H16" s="7" t="s">
         <v>21</v>
       </c>
       <c r="I16" s="15" t="s">
+        <v>2697</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>2698</v>
+      </c>
+      <c r="K16" s="7" t="s">
         <v>2699</v>
       </c>
-      <c r="J16" s="7" t="s">
+      <c r="L16" s="7" t="s">
+        <v>2765</v>
+      </c>
+      <c r="M16" s="7" t="s">
         <v>2700</v>
-      </c>
-      <c r="K16" s="7" t="s">
-        <v>2701</v>
-      </c>
-      <c r="L16" s="7" t="s">
-        <v>2767</v>
-      </c>
-      <c r="M16" s="7" t="s">
-        <v>2702</v>
       </c>
       <c r="N16" s="7" t="s">
         <v>25</v>
@@ -14518,43 +14501,43 @@
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="7" t="s">
+        <v>2701</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>2702</v>
+      </c>
+      <c r="C17" s="7" t="s">
         <v>2703</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="D17" s="7" t="s">
         <v>2704</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="E17" s="7" t="s">
         <v>2705</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="F17" s="7" t="s">
         <v>2706</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="G17" s="7" t="s">
         <v>2707</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>2708</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>2709</v>
       </c>
       <c r="H17" s="7" t="s">
         <v>21</v>
       </c>
       <c r="I17" s="15" t="s">
+        <v>2708</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>2709</v>
+      </c>
+      <c r="K17" s="7" t="s">
         <v>2710</v>
       </c>
-      <c r="J17" s="7" t="s">
+      <c r="L17" s="7" t="s">
+        <v>2765</v>
+      </c>
+      <c r="M17" s="7" t="s">
         <v>2711</v>
-      </c>
-      <c r="K17" s="7" t="s">
-        <v>2712</v>
-      </c>
-      <c r="L17" s="7" t="s">
-        <v>2767</v>
-      </c>
-      <c r="M17" s="7" t="s">
-        <v>2713</v>
       </c>
       <c r="N17" s="7" t="s">
         <v>25</v>
@@ -14562,10 +14545,10 @@
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="7" t="s">
-        <v>2714</v>
+        <v>2712</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>2715</v>
+        <v>2713</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>16</v>
@@ -14592,13 +14575,13 @@
         <v>16</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>2716</v>
+        <v>2714</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>2767</v>
+        <v>2765</v>
       </c>
       <c r="M18" s="7" t="s">
-        <v>2717</v>
+        <v>2715</v>
       </c>
       <c r="N18" s="7" t="s">
         <v>25</v>
@@ -14606,10 +14589,10 @@
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="7" t="s">
-        <v>2718</v>
+        <v>2716</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>2719</v>
+        <v>2717</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>16</v>
@@ -14618,31 +14601,31 @@
         <v>16</v>
       </c>
       <c r="E19" s="3" t="s">
+        <v>2718</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>2719</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>2720</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="H19" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>2721</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="J19" s="3" t="s">
         <v>2722</v>
       </c>
-      <c r="H19" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>2723</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>2724</v>
-      </c>
       <c r="K19" s="7" t="s">
-        <v>2663</v>
+        <v>2661</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>2767</v>
+        <v>2765</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>2720</v>
+        <v>2718</v>
       </c>
       <c r="N19" s="7" t="s">
         <v>25</v>
@@ -14650,43 +14633,43 @@
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="7" t="s">
-        <v>2725</v>
+        <v>2723</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>2726</v>
+        <v>2724</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>16</v>
       </c>
       <c r="D20" s="7" t="s">
+        <v>2725</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>2726</v>
+      </c>
+      <c r="F20" s="3" t="s">
         <v>2727</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="G20" s="3" t="s">
         <v>2728</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="H20" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>2729</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>2730</v>
       </c>
-      <c r="H20" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I20" s="3" t="s">
+      <c r="K20" s="7" t="s">
         <v>2731</v>
       </c>
-      <c r="J20" s="3" t="s">
+      <c r="L20" s="7" t="s">
+        <v>2765</v>
+      </c>
+      <c r="M20" s="3" t="s">
         <v>2732</v>
-      </c>
-      <c r="K20" s="7" t="s">
-        <v>2733</v>
-      </c>
-      <c r="L20" s="7" t="s">
-        <v>2767</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>2734</v>
       </c>
       <c r="N20" s="7" t="s">
         <v>25</v>
@@ -14694,43 +14677,43 @@
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="7" t="s">
+        <v>2733</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>2734</v>
+      </c>
+      <c r="C21" s="7" t="s">
         <v>2735</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>2736</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>2737</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>16</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>2738</v>
+        <v>2736</v>
       </c>
       <c r="F21" s="7" t="s">
         <v>1516</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>2739</v>
+        <v>2737</v>
       </c>
       <c r="H21" s="7" t="s">
         <v>21</v>
       </c>
       <c r="I21" s="18" t="s">
+        <v>2738</v>
+      </c>
+      <c r="J21" s="18" t="s">
+        <v>2739</v>
+      </c>
+      <c r="K21" s="7" t="s">
         <v>2740</v>
       </c>
-      <c r="J21" s="18" t="s">
+      <c r="L21" s="7" t="s">
+        <v>2765</v>
+      </c>
+      <c r="M21" s="3" t="s">
         <v>2741</v>
-      </c>
-      <c r="K21" s="7" t="s">
-        <v>2742</v>
-      </c>
-      <c r="L21" s="7" t="s">
-        <v>2767</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>2743</v>
       </c>
       <c r="N21" s="7" t="s">
         <v>25</v>
@@ -14738,43 +14721,43 @@
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="16" t="s">
-        <v>2744</v>
+        <v>2742</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>2745</v>
+        <v>2743</v>
       </c>
       <c r="C22" s="16" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="16" t="s">
+        <v>2744</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>2745</v>
+      </c>
+      <c r="F22" s="16" t="s">
         <v>2746</v>
       </c>
-      <c r="E22" s="16" t="s">
+      <c r="G22" s="16" t="s">
         <v>2747</v>
       </c>
-      <c r="F22" s="16" t="s">
+      <c r="H22" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I22" s="18" t="s">
         <v>2748</v>
       </c>
-      <c r="G22" s="16" t="s">
+      <c r="J22" s="18" t="s">
         <v>2749</v>
       </c>
-      <c r="H22" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I22" s="18" t="s">
+      <c r="K22" s="16" t="s">
+        <v>2661</v>
+      </c>
+      <c r="L22" s="7" t="s">
+        <v>2765</v>
+      </c>
+      <c r="M22" s="16" t="s">
         <v>2750</v>
-      </c>
-      <c r="J22" s="18" t="s">
-        <v>2751</v>
-      </c>
-      <c r="K22" s="16" t="s">
-        <v>2663</v>
-      </c>
-      <c r="L22" s="7" t="s">
-        <v>2767</v>
-      </c>
-      <c r="M22" s="16" t="s">
-        <v>2752</v>
       </c>
       <c r="N22" s="7" t="s">
         <v>25</v>
@@ -14782,43 +14765,43 @@
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="16" t="s">
+        <v>2751</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>2752</v>
+      </c>
+      <c r="C23" s="16" t="s">
         <v>2753</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>2754</v>
-      </c>
-      <c r="C23" s="16" t="s">
-        <v>2755</v>
       </c>
       <c r="D23" s="16" t="s">
         <v>16</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>2756</v>
+        <v>2754</v>
       </c>
       <c r="F23" s="16" t="s">
-        <v>2721</v>
+        <v>2719</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>2757</v>
+        <v>2755</v>
       </c>
       <c r="H23" s="7" t="s">
         <v>21</v>
       </c>
       <c r="I23" s="3" t="s">
+        <v>2756</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>2757</v>
+      </c>
+      <c r="K23" s="3" t="s">
         <v>2758</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>2759</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>2760</v>
-      </c>
       <c r="L23" s="7" t="s">
-        <v>2767</v>
+        <v>2765</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>2760</v>
+        <v>2758</v>
       </c>
       <c r="N23" s="7" t="s">
         <v>25</v>
@@ -14826,43 +14809,43 @@
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="16" t="s">
+        <v>2759</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>2760</v>
+      </c>
+      <c r="C24" s="16" t="s">
         <v>2761</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>2762</v>
-      </c>
-      <c r="C24" s="16" t="s">
-        <v>2763</v>
       </c>
       <c r="D24" s="16" t="s">
         <v>16</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>2764</v>
+        <v>2762</v>
       </c>
       <c r="F24" s="16" t="s">
-        <v>2721</v>
+        <v>2719</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>2765</v>
+        <v>2763</v>
       </c>
       <c r="H24" s="7" t="s">
         <v>21</v>
       </c>
       <c r="I24" s="3" t="s">
+        <v>2756</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>2764</v>
+      </c>
+      <c r="K24" s="3" t="s">
         <v>2758</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>2766</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>2760</v>
-      </c>
       <c r="L24" s="7" t="s">
-        <v>2767</v>
+        <v>2765</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>2760</v>
+        <v>2758</v>
       </c>
       <c r="N24" s="7" t="s">
         <v>25</v>
@@ -17319,16 +17302,16 @@
     </row>
     <row r="56" spans="1:14">
       <c r="A56" s="16" t="s">
-        <v>2585</v>
+        <v>2583</v>
       </c>
       <c r="B56" t="s">
-        <v>2591</v>
+        <v>2589</v>
       </c>
       <c r="C56" s="16" t="s">
-        <v>2589</v>
+        <v>2587</v>
       </c>
       <c r="D56" s="16" t="s">
-        <v>2590</v>
+        <v>2588</v>
       </c>
       <c r="E56">
         <v>1844317</v>
@@ -17337,16 +17320,16 @@
         <v>2281</v>
       </c>
       <c r="G56" s="16" t="s">
-        <v>2592</v>
+        <v>2590</v>
       </c>
       <c r="H56" s="16" t="s">
         <v>21</v>
       </c>
       <c r="I56" s="27" t="s">
-        <v>2594</v>
+        <v>2592</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>2588</v>
+        <v>2586</v>
       </c>
       <c r="K56" s="7" t="s">
         <v>2441</v>
@@ -17363,16 +17346,16 @@
     </row>
     <row r="57" spans="1:14">
       <c r="A57" s="16" t="s">
-        <v>2586</v>
+        <v>2584</v>
       </c>
       <c r="B57" t="s">
+        <v>2585</v>
+      </c>
+      <c r="C57" t="s">
         <v>2587</v>
       </c>
-      <c r="C57" t="s">
-        <v>2589</v>
-      </c>
       <c r="D57" s="16" t="s">
-        <v>2590</v>
+        <v>2588</v>
       </c>
       <c r="E57">
         <v>1952364</v>
@@ -17381,16 +17364,16 @@
         <v>2281</v>
       </c>
       <c r="G57" t="s">
-        <v>2593</v>
+        <v>2591</v>
       </c>
       <c r="H57" s="16" t="s">
         <v>21</v>
       </c>
       <c r="I57" s="27" t="s">
-        <v>2596</v>
+        <v>2594</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>2595</v>
+        <v>2593</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>2540</v>
@@ -24810,10 +24793,10 @@
         <v>2011</v>
       </c>
       <c r="L2" t="s">
-        <v>2583</v>
+        <v>1910</v>
       </c>
       <c r="N2" t="s">
-        <v>2584</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -24851,13 +24834,13 @@
         <v>2011</v>
       </c>
       <c r="L3" t="s">
-        <v>2583</v>
+        <v>1910</v>
       </c>
       <c r="M3" t="s">
         <v>2014</v>
       </c>
       <c r="N3" t="s">
-        <v>2584</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -24895,13 +24878,13 @@
         <v>2011</v>
       </c>
       <c r="L4" t="s">
-        <v>2583</v>
+        <v>1910</v>
       </c>
       <c r="M4" t="s">
         <v>2027</v>
       </c>
       <c r="N4" t="s">
-        <v>2584</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -24939,13 +24922,13 @@
         <v>1918</v>
       </c>
       <c r="L5" t="s">
-        <v>2583</v>
+        <v>1910</v>
       </c>
       <c r="M5" t="s">
         <v>2030</v>
       </c>
       <c r="N5" t="s">
-        <v>2584</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -24983,13 +24966,13 @@
         <v>2043</v>
       </c>
       <c r="L6" t="s">
-        <v>2583</v>
+        <v>1910</v>
       </c>
       <c r="M6" t="s">
         <v>2044</v>
       </c>
       <c r="N6" t="s">
-        <v>2584</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -25027,13 +25010,13 @@
         <v>2052</v>
       </c>
       <c r="L7" t="s">
-        <v>2583</v>
+        <v>1910</v>
       </c>
       <c r="M7" t="s">
         <v>2047</v>
       </c>
       <c r="N7" t="s">
-        <v>2584</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -25071,13 +25054,13 @@
         <v>2052</v>
       </c>
       <c r="L8" t="s">
-        <v>2583</v>
+        <v>1910</v>
       </c>
       <c r="M8" t="s">
         <v>2060</v>
       </c>
       <c r="N8" t="s">
-        <v>2584</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -25115,13 +25098,13 @@
         <v>2052</v>
       </c>
       <c r="L9" t="s">
-        <v>2583</v>
+        <v>1910</v>
       </c>
       <c r="M9" t="s">
         <v>1947</v>
       </c>
       <c r="N9" t="s">
-        <v>2584</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -25159,13 +25142,13 @@
         <v>2074</v>
       </c>
       <c r="L10" t="s">
-        <v>2583</v>
+        <v>1910</v>
       </c>
       <c r="M10" t="s">
         <v>1856</v>
       </c>
       <c r="N10" t="s">
-        <v>2584</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -25203,13 +25186,13 @@
         <v>2081</v>
       </c>
       <c r="L11" t="s">
-        <v>2583</v>
+        <v>1910</v>
       </c>
       <c r="M11" t="s">
         <v>1856</v>
       </c>
       <c r="N11" t="s">
-        <v>2584</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -25247,13 +25230,13 @@
         <v>2074</v>
       </c>
       <c r="L12" t="s">
-        <v>2583</v>
+        <v>1910</v>
       </c>
       <c r="M12" t="s">
         <v>1856</v>
       </c>
       <c r="N12" t="s">
-        <v>2584</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -25291,13 +25274,13 @@
         <v>2096</v>
       </c>
       <c r="L13" t="s">
-        <v>2583</v>
+        <v>1910</v>
       </c>
       <c r="M13" t="s">
         <v>2091</v>
       </c>
       <c r="N13" t="s">
-        <v>2584</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -25335,13 +25318,13 @@
         <v>824012823</v>
       </c>
       <c r="L14" t="s">
-        <v>2583</v>
+        <v>1910</v>
       </c>
       <c r="M14" t="s">
         <v>2105</v>
       </c>
       <c r="N14" t="s">
-        <v>2584</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -25379,13 +25362,13 @@
         <v>1943</v>
       </c>
       <c r="L15" t="s">
-        <v>2583</v>
+        <v>1910</v>
       </c>
       <c r="M15" t="s">
         <v>1856</v>
       </c>
       <c r="N15" t="s">
-        <v>2584</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -25423,13 +25406,13 @@
         <v>2117</v>
       </c>
       <c r="L16" t="s">
-        <v>2583</v>
+        <v>1910</v>
       </c>
       <c r="M16" t="s">
         <v>1856</v>
       </c>
       <c r="N16" t="s">
-        <v>2584</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -25467,13 +25450,13 @@
         <v>2125</v>
       </c>
       <c r="L17" t="s">
-        <v>2583</v>
+        <v>1910</v>
       </c>
       <c r="M17" t="s">
         <v>2120</v>
       </c>
       <c r="N17" t="s">
-        <v>2584</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -25511,13 +25494,13 @@
         <v>1943</v>
       </c>
       <c r="L18" t="s">
-        <v>2583</v>
+        <v>1910</v>
       </c>
       <c r="M18" t="s">
         <v>1856</v>
       </c>
       <c r="N18" t="s">
-        <v>2584</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -25555,13 +25538,13 @@
         <v>2136</v>
       </c>
       <c r="L19" t="s">
-        <v>2583</v>
+        <v>1910</v>
       </c>
       <c r="M19" t="s">
         <v>2136</v>
       </c>
       <c r="N19" t="s">
-        <v>2584</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -25599,13 +25582,13 @@
         <v>2143</v>
       </c>
       <c r="L20" t="s">
-        <v>2583</v>
+        <v>1910</v>
       </c>
       <c r="M20" t="s">
         <v>2147</v>
       </c>
       <c r="N20" t="s">
-        <v>2584</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -25643,13 +25626,13 @@
         <v>2154</v>
       </c>
       <c r="L21" t="s">
-        <v>2583</v>
+        <v>1910</v>
       </c>
       <c r="M21" t="s">
         <v>1856</v>
       </c>
       <c r="N21" t="s">
-        <v>2584</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -25687,13 +25670,13 @@
         <v>2052</v>
       </c>
       <c r="L22" t="s">
-        <v>2583</v>
+        <v>1910</v>
       </c>
       <c r="M22" t="s">
         <v>1904</v>
       </c>
       <c r="N22" t="s">
-        <v>2584</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -25731,13 +25714,13 @@
         <v>2052</v>
       </c>
       <c r="L23" t="s">
-        <v>2583</v>
+        <v>1910</v>
       </c>
       <c r="M23" t="s">
         <v>2060</v>
       </c>
       <c r="N23" t="s">
-        <v>2584</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -25795,575 +25778,575 @@
       </c>
     </row>
     <row r="2" spans="1:14">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="7" t="s">
+        <v>2766</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>2767</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>2768</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="D2" s="7">
+        <v>3535</v>
+      </c>
+      <c r="E2" s="7" t="s">
         <v>2769</v>
       </c>
-      <c r="C2" s="29" t="s">
+      <c r="F2" s="7" t="s">
         <v>2770</v>
       </c>
-      <c r="D2" s="29">
-        <v>3535</v>
-      </c>
-      <c r="E2" s="29" t="s">
+      <c r="G2" s="7" t="s">
         <v>2771</v>
       </c>
-      <c r="F2" s="29" t="s">
+      <c r="H2" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I2" s="7" t="s">
         <v>2772</v>
       </c>
-      <c r="G2" s="29" t="s">
+      <c r="J2" s="7" t="s">
         <v>2773</v>
       </c>
-      <c r="H2" s="29" t="s">
-        <v>69</v>
-      </c>
-      <c r="I2" s="29" t="s">
+      <c r="K2" s="7" t="s">
         <v>2774</v>
       </c>
-      <c r="J2" s="29" t="s">
+      <c r="L2" s="7" t="s">
+        <v>2877</v>
+      </c>
+      <c r="M2" s="7" t="s">
         <v>2775</v>
       </c>
-      <c r="K2" s="29" t="s">
+      <c r="N2" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="7" t="s">
         <v>2776</v>
       </c>
-      <c r="L2" s="29" t="s">
+      <c r="B3" s="7" t="s">
         <v>2777</v>
       </c>
-      <c r="M2" s="29" t="s">
+      <c r="C3" s="7" t="s">
+        <v>2768</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>2778</v>
       </c>
-      <c r="N2" s="29" t="s">
-        <v>2584</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="29" t="s">
+      <c r="F3" s="7" t="s">
         <v>2779</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="G3" s="7" t="s">
         <v>2780</v>
       </c>
-      <c r="C3" s="29" t="s">
-        <v>2770</v>
-      </c>
-      <c r="D3" s="32" t="s">
+      <c r="H3" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>2781</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>2782</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>2774</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>2877</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>2783</v>
+      </c>
+      <c r="N3" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="7" t="s">
+        <v>2784</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>2785</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>2786</v>
+      </c>
+      <c r="D4" s="13" t="s">
         <v>240</v>
       </c>
-      <c r="E3" s="29" t="s">
-        <v>2781</v>
-      </c>
-      <c r="F3" s="29" t="s">
-        <v>2782</v>
-      </c>
-      <c r="G3" s="29" t="s">
+      <c r="E4" s="7" t="s">
+        <v>2787</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>2788</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>2789</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>2790</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>2790</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>2774</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>2877</v>
+      </c>
+      <c r="M4" s="7" t="s">
         <v>2783</v>
       </c>
-      <c r="H3" s="29" t="s">
-        <v>69</v>
-      </c>
-      <c r="I3" s="29" t="s">
-        <v>2784</v>
-      </c>
-      <c r="J3" s="33" t="s">
-        <v>2785</v>
-      </c>
-      <c r="K3" s="29" t="s">
-        <v>2776</v>
-      </c>
-      <c r="L3" s="29" t="s">
-        <v>2777</v>
-      </c>
-      <c r="M3" s="29" t="s">
+      <c r="N4" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="7" t="s">
+        <v>2791</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>2792</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>2793</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>2794</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>2795</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>2796</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I5" s="15" t="s">
+        <v>2797</v>
+      </c>
+      <c r="J5" s="15" t="s">
+        <v>2798</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>2774</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>2877</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>2783</v>
+      </c>
+      <c r="N5" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="7" t="s">
+        <v>2799</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>2800</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>2801</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>2802</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>2788</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>2803</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>2804</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>2805</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>2774</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>2877</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>2783</v>
+      </c>
+      <c r="N6" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="7" t="s">
+        <v>2806</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>2807</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>2808</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>2809</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>2810</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>2811</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>2812</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>2813</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>2814</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>2815</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>2877</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>2816</v>
+      </c>
+      <c r="N7" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="7" t="s">
+        <v>2817</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>2818</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>2808</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>2819</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>2820</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>2821</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>2822</v>
+      </c>
+      <c r="H8" s="16" t="s">
+        <v>2823</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>2824</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>2825</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>2774</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>2877</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>2826</v>
+      </c>
+      <c r="N8" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="14.5" customHeight="1">
+      <c r="A9" s="7" t="s">
+        <v>2827</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>2828</v>
+      </c>
+      <c r="C9" s="16" t="s">
         <v>2786</v>
       </c>
-      <c r="N3" s="29" t="s">
-        <v>2584</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="29" t="s">
-        <v>2787</v>
-      </c>
-      <c r="B4" s="29" t="s">
-        <v>2788</v>
-      </c>
-      <c r="C4" s="29" t="s">
-        <v>2789</v>
-      </c>
-      <c r="D4" s="32" t="s">
-        <v>240</v>
-      </c>
-      <c r="E4" s="29" t="s">
-        <v>2790</v>
-      </c>
-      <c r="F4" s="29" t="s">
-        <v>2791</v>
-      </c>
-      <c r="G4" s="29" t="s">
-        <v>2792</v>
-      </c>
-      <c r="H4" s="29" t="s">
-        <v>69</v>
-      </c>
-      <c r="I4" s="29" t="s">
+      <c r="D9" s="3" t="s">
+        <v>2829</v>
+      </c>
+      <c r="E9" s="28" t="s">
+        <v>2830</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>2831</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>2832</v>
+      </c>
+      <c r="H9" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>2833</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>2834</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>2774</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>2877</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>2835</v>
+      </c>
+      <c r="N9" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="7" t="s">
+        <v>2836</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>2837</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>2786</v>
+      </c>
+      <c r="D10" s="29" t="s">
+        <v>249</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>2838</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>2839</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>2840</v>
+      </c>
+      <c r="H10" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>2841</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>2842</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>2774</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>2877</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>2843</v>
+      </c>
+      <c r="N10" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="7" t="s">
+        <v>2844</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>2845</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>2846</v>
+      </c>
+      <c r="D11" s="29" t="s">
+        <v>249</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>2847</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>2848</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>2849</v>
+      </c>
+      <c r="H11" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>2850</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>2851</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>2774</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>2877</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>2843</v>
+      </c>
+      <c r="N11" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="7" t="s">
+        <v>2852</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>2853</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>2808</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>2854</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>2855</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>2856</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>2857</v>
+      </c>
+      <c r="H12" s="16" t="s">
+        <v>2823</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>2858</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>2859</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>2815</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>2877</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>2855</v>
+      </c>
+      <c r="N12" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="13.5" customHeight="1">
+      <c r="A13" s="7" t="s">
+        <v>2860</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>2861</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>2862</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>2863</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>2864</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>2865</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>2866</v>
+      </c>
+      <c r="H13" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>2867</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>2868</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>2869</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>2877</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>2864</v>
+      </c>
+      <c r="N13" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="15" customHeight="1">
+      <c r="A14" s="7" t="s">
+        <v>2870</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>2871</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>2793</v>
       </c>
-      <c r="J4" s="29" t="s">
-        <v>2793</v>
-      </c>
-      <c r="K4" s="29" t="s">
-        <v>2776</v>
-      </c>
-      <c r="L4" s="29" t="s">
-        <v>2777</v>
-      </c>
-      <c r="M4" s="29" t="s">
-        <v>2786</v>
-      </c>
-      <c r="N4" s="29" t="s">
-        <v>2584</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="29" t="s">
-        <v>2794</v>
-      </c>
-      <c r="B5" s="29" t="s">
-        <v>2795</v>
-      </c>
-      <c r="C5" s="29" t="s">
-        <v>2796</v>
-      </c>
-      <c r="D5" s="32" t="s">
-        <v>240</v>
-      </c>
-      <c r="E5" s="29" t="s">
-        <v>2797</v>
-      </c>
-      <c r="F5" s="29" t="s">
-        <v>2798</v>
-      </c>
-      <c r="G5" s="29" t="s">
-        <v>2799</v>
-      </c>
-      <c r="H5" s="29" t="s">
-        <v>69</v>
-      </c>
-      <c r="I5" s="33" t="s">
-        <v>2800</v>
-      </c>
-      <c r="J5" s="33" t="s">
-        <v>2801</v>
-      </c>
-      <c r="K5" s="29" t="s">
-        <v>2776</v>
-      </c>
-      <c r="L5" s="29" t="s">
-        <v>2777</v>
-      </c>
-      <c r="M5" s="29" t="s">
-        <v>2786</v>
-      </c>
-      <c r="N5" s="29" t="s">
-        <v>2584</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="29" t="s">
-        <v>2802</v>
-      </c>
-      <c r="B6" s="29" t="s">
-        <v>2803</v>
-      </c>
-      <c r="C6" s="29" t="s">
-        <v>2804</v>
-      </c>
-      <c r="D6" s="32" t="s">
-        <v>240</v>
-      </c>
-      <c r="E6" s="29" t="s">
-        <v>2805</v>
-      </c>
-      <c r="F6" s="29" t="s">
-        <v>2791</v>
-      </c>
-      <c r="G6" s="29" t="s">
-        <v>2806</v>
-      </c>
-      <c r="H6" s="29" t="s">
-        <v>69</v>
-      </c>
-      <c r="I6" s="31" t="s">
-        <v>2807</v>
-      </c>
-      <c r="J6" s="31" t="s">
-        <v>2808</v>
-      </c>
-      <c r="K6" s="29" t="s">
-        <v>2776</v>
-      </c>
-      <c r="L6" s="29" t="s">
-        <v>2777</v>
-      </c>
-      <c r="M6" s="29" t="s">
-        <v>2786</v>
-      </c>
-      <c r="N6" s="29" t="s">
-        <v>2584</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="29" t="s">
-        <v>2809</v>
-      </c>
-      <c r="B7" s="29" t="s">
-        <v>2810</v>
-      </c>
-      <c r="C7" s="29" t="s">
-        <v>2811</v>
-      </c>
-      <c r="D7" s="29" t="s">
-        <v>2812</v>
-      </c>
-      <c r="E7" s="29" t="s">
-        <v>2813</v>
-      </c>
-      <c r="F7" s="30" t="s">
-        <v>2814</v>
-      </c>
-      <c r="G7" s="29" t="s">
-        <v>2815</v>
-      </c>
-      <c r="H7" s="29" t="s">
-        <v>21</v>
-      </c>
-      <c r="I7" s="34" t="s">
-        <v>2816</v>
-      </c>
-      <c r="J7" s="34" t="s">
-        <v>2817</v>
-      </c>
-      <c r="K7" s="29" t="s">
-        <v>2818</v>
-      </c>
-      <c r="L7" s="29" t="s">
-        <v>2777</v>
-      </c>
-      <c r="M7" s="34" t="s">
-        <v>2819</v>
-      </c>
-      <c r="N7" s="29" t="s">
-        <v>2584</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="29" t="s">
-        <v>2820</v>
-      </c>
-      <c r="B8" s="29" t="s">
-        <v>2821</v>
-      </c>
-      <c r="C8" s="29" t="s">
-        <v>2811</v>
-      </c>
-      <c r="D8" s="29" t="s">
-        <v>2822</v>
-      </c>
-      <c r="E8" s="29" t="s">
-        <v>2823</v>
-      </c>
-      <c r="F8" s="36" t="s">
-        <v>2824</v>
-      </c>
-      <c r="G8" s="36" t="s">
-        <v>2825</v>
-      </c>
-      <c r="H8" s="36" t="s">
-        <v>2826</v>
-      </c>
-      <c r="I8" s="28" t="s">
-        <v>2827</v>
-      </c>
-      <c r="J8" s="28" t="s">
-        <v>2828</v>
-      </c>
-      <c r="K8" s="29" t="s">
-        <v>2776</v>
-      </c>
-      <c r="L8" s="29" t="s">
-        <v>2777</v>
-      </c>
-      <c r="M8" s="28" t="s">
-        <v>2829</v>
-      </c>
-      <c r="N8" s="29" t="s">
-        <v>2584</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="14.5" customHeight="1">
-      <c r="A9" s="29" t="s">
-        <v>2830</v>
-      </c>
-      <c r="B9" s="28" t="s">
-        <v>2831</v>
-      </c>
-      <c r="C9" s="35" t="s">
-        <v>2789</v>
-      </c>
-      <c r="D9" s="28" t="s">
-        <v>2832</v>
-      </c>
-      <c r="E9" s="38" t="s">
-        <v>2833</v>
-      </c>
-      <c r="F9" s="36" t="s">
-        <v>2834</v>
-      </c>
-      <c r="G9" s="36" t="s">
-        <v>2835</v>
-      </c>
-      <c r="H9" s="36" t="s">
-        <v>69</v>
-      </c>
-      <c r="I9" s="28" t="s">
-        <v>2836</v>
-      </c>
-      <c r="J9" s="28" t="s">
-        <v>2837</v>
-      </c>
-      <c r="K9" s="29" t="s">
-        <v>2776</v>
-      </c>
-      <c r="L9" s="29" t="s">
-        <v>2777</v>
-      </c>
-      <c r="M9" s="35" t="s">
-        <v>2838</v>
-      </c>
-      <c r="N9" s="29" t="s">
-        <v>2584</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="29" t="s">
-        <v>2839</v>
-      </c>
-      <c r="B10" s="37" t="s">
-        <v>2840</v>
-      </c>
-      <c r="C10" s="35" t="s">
-        <v>2789</v>
-      </c>
-      <c r="D10" s="39" t="s">
-        <v>249</v>
-      </c>
-      <c r="E10" s="28" t="s">
-        <v>2841</v>
-      </c>
-      <c r="F10" s="28" t="s">
-        <v>2842</v>
-      </c>
-      <c r="G10" s="28" t="s">
-        <v>2843</v>
-      </c>
-      <c r="H10" s="36" t="s">
-        <v>69</v>
-      </c>
-      <c r="I10" s="28" t="s">
-        <v>2844</v>
-      </c>
-      <c r="J10" s="28" t="s">
-        <v>2845</v>
-      </c>
-      <c r="K10" s="29" t="s">
-        <v>2776</v>
-      </c>
-      <c r="L10" s="29" t="s">
-        <v>2777</v>
-      </c>
-      <c r="M10" s="35" t="s">
-        <v>2846</v>
-      </c>
-      <c r="N10" s="29" t="s">
-        <v>2584</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="29" t="s">
-        <v>2847</v>
-      </c>
-      <c r="B11" s="37" t="s">
-        <v>2848</v>
-      </c>
-      <c r="C11" s="35" t="s">
-        <v>2849</v>
-      </c>
-      <c r="D11" s="39" t="s">
-        <v>249</v>
-      </c>
-      <c r="E11" s="28" t="s">
-        <v>2850</v>
-      </c>
-      <c r="F11" s="37" t="s">
-        <v>2851</v>
-      </c>
-      <c r="G11" s="28" t="s">
-        <v>2852</v>
-      </c>
-      <c r="H11" s="36" t="s">
-        <v>21</v>
-      </c>
-      <c r="I11" s="28" t="s">
-        <v>2853</v>
-      </c>
-      <c r="J11" s="28" t="s">
-        <v>2854</v>
-      </c>
-      <c r="K11" s="29" t="s">
-        <v>2776</v>
-      </c>
-      <c r="L11" s="29" t="s">
-        <v>2777</v>
-      </c>
-      <c r="M11" s="35" t="s">
-        <v>2846</v>
-      </c>
-      <c r="N11" s="29" t="s">
-        <v>2584</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="29" t="s">
-        <v>2855</v>
-      </c>
-      <c r="B12" s="37" t="s">
-        <v>2856</v>
-      </c>
-      <c r="C12" s="35" t="s">
-        <v>2811</v>
-      </c>
-      <c r="D12" s="35" t="s">
-        <v>2857</v>
-      </c>
-      <c r="E12" s="35" t="s">
-        <v>2858</v>
-      </c>
-      <c r="F12" s="35" t="s">
-        <v>2859</v>
-      </c>
-      <c r="G12" s="28" t="s">
-        <v>2860</v>
-      </c>
-      <c r="H12" s="36" t="s">
-        <v>2826</v>
-      </c>
-      <c r="I12" s="28" t="s">
-        <v>2861</v>
-      </c>
-      <c r="J12" s="28" t="s">
-        <v>2862</v>
-      </c>
-      <c r="K12" s="29" t="s">
-        <v>2818</v>
-      </c>
-      <c r="L12" s="29" t="s">
-        <v>2777</v>
-      </c>
-      <c r="M12" s="28" t="s">
-        <v>2858</v>
-      </c>
-      <c r="N12" s="29" t="s">
-        <v>2584</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="13.5" customHeight="1">
-      <c r="A13" s="29" t="s">
-        <v>2863</v>
-      </c>
-      <c r="B13" s="28" t="s">
-        <v>2864</v>
-      </c>
-      <c r="C13" s="28" t="s">
-        <v>2865</v>
-      </c>
-      <c r="D13" s="28" t="s">
-        <v>2866</v>
-      </c>
-      <c r="E13" s="28" t="s">
-        <v>2867</v>
-      </c>
-      <c r="F13" s="28" t="s">
-        <v>2868</v>
-      </c>
-      <c r="G13" s="28" t="s">
-        <v>2869</v>
-      </c>
-      <c r="H13" s="36" t="s">
-        <v>69</v>
-      </c>
-      <c r="I13" s="28" t="s">
-        <v>2870</v>
-      </c>
-      <c r="J13" s="28" t="s">
-        <v>2871</v>
-      </c>
-      <c r="K13" s="29" t="s">
+      <c r="D14" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>2872</v>
       </c>
-      <c r="L13" s="29" t="s">
-        <v>2777</v>
-      </c>
-      <c r="M13" s="28" t="s">
-        <v>2867</v>
-      </c>
-      <c r="N13" s="29" t="s">
-        <v>2584</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="15" customHeight="1">
-      <c r="A14" s="29" t="s">
+      <c r="F14" s="3" t="s">
+        <v>2779</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>2873</v>
       </c>
-      <c r="B14" s="28" t="s">
+      <c r="H14" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>2874</v>
       </c>
-      <c r="C14" s="28" t="s">
-        <v>2796</v>
-      </c>
-      <c r="D14" s="40" t="s">
-        <v>59</v>
-      </c>
-      <c r="E14" s="28" t="s">
+      <c r="J14" s="3" t="s">
         <v>2875</v>
       </c>
-      <c r="F14" s="28" t="s">
-        <v>2782</v>
-      </c>
-      <c r="G14" s="28" t="s">
+      <c r="K14" s="7" t="s">
+        <v>2774</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>2877</v>
+      </c>
+      <c r="M14" s="3" t="s">
         <v>2876</v>
       </c>
-      <c r="H14" s="36" t="s">
-        <v>69</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>2877</v>
-      </c>
-      <c r="J14" s="28" t="s">
-        <v>2878</v>
-      </c>
-      <c r="K14" s="29" t="s">
-        <v>2776</v>
-      </c>
-      <c r="L14" s="29" t="s">
-        <v>2777</v>
-      </c>
-      <c r="M14" s="28" t="s">
-        <v>2879</v>
-      </c>
-      <c r="N14" s="29" t="s">
-        <v>2584</v>
+      <c r="N14" s="7" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -26401,7 +26384,7 @@
         <v>1943</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>1910</v>
+        <v>2877</v>
       </c>
       <c r="M15" s="7" t="s">
         <v>1856</v>
@@ -26445,7 +26428,7 @@
         <v>2117</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>1910</v>
+        <v>2877</v>
       </c>
       <c r="M16" s="7" t="s">
         <v>1856</v>
@@ -26489,7 +26472,7 @@
         <v>2125</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>1910</v>
+        <v>2877</v>
       </c>
       <c r="M17" s="7" t="s">
         <v>2120</v>
@@ -26533,7 +26516,7 @@
         <v>1943</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>1910</v>
+        <v>2877</v>
       </c>
       <c r="M18" s="7" t="s">
         <v>1856</v>
@@ -26577,7 +26560,7 @@
         <v>2136</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>1910</v>
+        <v>2877</v>
       </c>
       <c r="M19" s="7" t="s">
         <v>2136</v>
@@ -26621,7 +26604,7 @@
         <v>2143</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>1910</v>
+        <v>2877</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>2147</v>
@@ -26665,7 +26648,7 @@
         <v>2154</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>1910</v>
+        <v>2877</v>
       </c>
       <c r="M21" s="7" t="s">
         <v>1856</v>
@@ -26709,7 +26692,7 @@
         <v>2052</v>
       </c>
       <c r="L22" s="7" t="s">
-        <v>1910</v>
+        <v>2877</v>
       </c>
       <c r="M22" s="7" t="s">
         <v>1904</v>
@@ -26753,7 +26736,7 @@
         <v>2052</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>1910</v>
+        <v>2877</v>
       </c>
       <c r="M23" s="7" t="s">
         <v>2060</v>

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D62A594-312B-4529-ABA1-0D99DBEEA679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD01ACC6-B416-44F9-9ABC-893A0914DBFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25812" yWindow="2904" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" firstSheet="8" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5716" uniqueCount="2878">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5760" uniqueCount="2896">
   <si>
     <t>ID</t>
   </si>
@@ -8672,6 +8672,60 @@
   </si>
   <si>
     <t>eUSR_SchLibrary/eUSR_SchLibrary - LEDs.SchLib</t>
+  </si>
+  <si>
+    <t>110-0057</t>
+  </si>
+  <si>
+    <t>110-0058</t>
+  </si>
+  <si>
+    <t>110-0059</t>
+  </si>
+  <si>
+    <t>110-0060</t>
+  </si>
+  <si>
+    <t>WR-MPC5 Male Header Dual Row</t>
+  </si>
+  <si>
+    <t>THT 5,7mm</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/657012240101.pdf</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/en/components/products/WTB_WR_MPC5_DUAL_ROW</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/657012250201.pdf</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/en/components/products/WTB_WR_MPC5_RECEPTACLE_PLUG_DUAL_ROW#/articles/WTB_WR_MCP5_DUAL_ROW_RECEPTACLE_HOUSING</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/657004140101.pdf</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/en/components/products/WTB_WR_MPC5_SINGLE_ROW</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/657004150201.pdf</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/en/components/products/WTB_WR_MPC5_RECEPTACLE_PLUG_SINGLE_ROW#/articles/WTB_WR_MPC5_SINGLE_ROW_RECEPTACLE_HOUSING</t>
+  </si>
+  <si>
+    <t>WR-MPC5 Receptacle Dual Row</t>
+  </si>
+  <si>
+    <t>WR-MPC5 Male Header Single Row</t>
+  </si>
+  <si>
+    <t>Receptacle Single Row</t>
+  </si>
+  <si>
+    <t>CONN 14P</t>
   </si>
 </sst>
 </file>
@@ -8841,7 +8895,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -8890,6 +8944,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -14877,8 +14934,13 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE14AD29-8DB0-4C42-AB91-A73B867AE121}">
-  <dimension ref="A1:N57"/>
+  <dimension ref="A1:N61"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="5" max="5" width="16.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.26953125" customWidth="1"/>
+    <col min="13" max="13" width="14.453125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="25" t="s">
@@ -17385,6 +17447,182 @@
         <v>1952364</v>
       </c>
       <c r="N57" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14">
+      <c r="A58" s="16" t="s">
+        <v>2878</v>
+      </c>
+      <c r="B58" t="s">
+        <v>2882</v>
+      </c>
+      <c r="C58" t="s">
+        <v>2587</v>
+      </c>
+      <c r="D58" s="16" t="s">
+        <v>2883</v>
+      </c>
+      <c r="E58" s="30">
+        <v>657012240101</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G58" s="30">
+        <v>657012240101</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>2100</v>
+      </c>
+      <c r="I58" t="s">
+        <v>2884</v>
+      </c>
+      <c r="J58" t="s">
+        <v>2885</v>
+      </c>
+      <c r="K58" s="32" t="s">
+        <v>2895</v>
+      </c>
+      <c r="L58" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M58" s="30">
+        <v>657012240101</v>
+      </c>
+      <c r="N58" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14">
+      <c r="A59" s="16" t="s">
+        <v>2879</v>
+      </c>
+      <c r="B59" t="s">
+        <v>2892</v>
+      </c>
+      <c r="C59" t="s">
+        <v>2587</v>
+      </c>
+      <c r="D59" s="16" t="s">
+        <v>2883</v>
+      </c>
+      <c r="E59" s="30">
+        <v>657012250201</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G59" s="30">
+        <v>657012250201</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>2100</v>
+      </c>
+      <c r="I59" t="s">
+        <v>2886</v>
+      </c>
+      <c r="J59" t="s">
+        <v>2887</v>
+      </c>
+      <c r="K59" s="3" t="s">
+        <v>2540</v>
+      </c>
+      <c r="L59" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M59" s="30">
+        <v>657012250201</v>
+      </c>
+      <c r="N59" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14">
+      <c r="A60" s="16" t="s">
+        <v>2880</v>
+      </c>
+      <c r="B60" t="s">
+        <v>2893</v>
+      </c>
+      <c r="C60" s="16" t="s">
+        <v>2452</v>
+      </c>
+      <c r="D60" s="16" t="s">
+        <v>2883</v>
+      </c>
+      <c r="E60" s="30">
+        <v>657004140101</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G60" s="30">
+        <v>657004140101</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>2100</v>
+      </c>
+      <c r="I60" t="s">
+        <v>2888</v>
+      </c>
+      <c r="J60" t="s">
+        <v>2889</v>
+      </c>
+      <c r="K60" s="32" t="s">
+        <v>2416</v>
+      </c>
+      <c r="L60" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M60" s="30">
+        <v>657004140101</v>
+      </c>
+      <c r="N60" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14">
+      <c r="A61" s="16" t="s">
+        <v>2881</v>
+      </c>
+      <c r="B61" t="s">
+        <v>2894</v>
+      </c>
+      <c r="C61" s="16" t="s">
+        <v>2452</v>
+      </c>
+      <c r="D61" s="16" t="s">
+        <v>2883</v>
+      </c>
+      <c r="E61" s="30">
+        <v>657004150201</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G61" s="30">
+        <v>657004150201</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>2100</v>
+      </c>
+      <c r="I61" t="s">
+        <v>2890</v>
+      </c>
+      <c r="J61" t="s">
+        <v>2891</v>
+      </c>
+      <c r="K61" s="31" t="s">
+        <v>2540</v>
+      </c>
+      <c r="L61" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M61" s="30">
+        <v>657004150201</v>
+      </c>
+      <c r="N61" s="7" t="s">
         <v>25</v>
       </c>
     </row>

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,25 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD01ACC6-B416-44F9-9ABC-893A0914DBFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B74AA2D8-E955-4948-8612-3823F2A6CDFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" firstSheet="8" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
-    <sheet name="010 - Resistors - SMD" sheetId="4" r:id="rId2"/>
-    <sheet name="015 - Resistors - Shunt" sheetId="7" r:id="rId3"/>
-    <sheet name="020 - Inductor" sheetId="5" r:id="rId4"/>
-    <sheet name="030 - Diode - Rectifier" sheetId="9" r:id="rId5"/>
-    <sheet name="031 - Diode - Schottky" sheetId="11" r:id="rId6"/>
-    <sheet name="032 - Diode - TVS" sheetId="14" r:id="rId7"/>
-    <sheet name="033 - Diode - LED" sheetId="12" r:id="rId8"/>
-    <sheet name="040 - Fuses" sheetId="10" r:id="rId9"/>
-    <sheet name="050 - ICs - Analog" sheetId="2" r:id="rId10"/>
-    <sheet name="060 - ICs - Digital" sheetId="3" r:id="rId11"/>
-    <sheet name="070 - Power Supply - DCDC" sheetId="8" r:id="rId12"/>
-    <sheet name="100 - Electromechanicals" sheetId="15" r:id="rId13"/>
-    <sheet name="110 - Connectors" sheetId="13" r:id="rId14"/>
+    <sheet name="003 - Capacitors - THT Electrol" sheetId="17" r:id="rId2"/>
+    <sheet name="010 - Resistors - SMD" sheetId="4" r:id="rId3"/>
+    <sheet name="015 - Resistors - Shunt" sheetId="7" r:id="rId4"/>
+    <sheet name="020 - Inductor" sheetId="5" r:id="rId5"/>
+    <sheet name="023 - Inductor - CMM" sheetId="16" r:id="rId6"/>
+    <sheet name="030 - Diode - Rectifier" sheetId="9" r:id="rId7"/>
+    <sheet name="031 - Diode - Schottky" sheetId="11" r:id="rId8"/>
+    <sheet name="032 - Diode - TVS" sheetId="14" r:id="rId9"/>
+    <sheet name="033 - Diode - LED" sheetId="12" r:id="rId10"/>
+    <sheet name="040 - Fuses" sheetId="10" r:id="rId11"/>
+    <sheet name="050 - ICs - Analog" sheetId="2" r:id="rId12"/>
+    <sheet name="060 - ICs - Digital" sheetId="3" r:id="rId13"/>
+    <sheet name="070 - Power Supply - DCDC" sheetId="8" r:id="rId14"/>
+    <sheet name="100 - Electromechanicals" sheetId="15" r:id="rId15"/>
+    <sheet name="110 - Connectors" sheetId="13" r:id="rId16"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -38,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5760" uniqueCount="2896">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5814" uniqueCount="2916">
   <si>
     <t>ID</t>
   </si>
@@ -8726,6 +8728,66 @@
   </si>
   <si>
     <t>CONN 14P</t>
+  </si>
+  <si>
+    <t>023-0001</t>
+  </si>
+  <si>
+    <t>Common Mode Chokes / Filters WE-CMB Type XXL .5mH 35A 2.3mOhm</t>
+  </si>
+  <si>
+    <t>0.5mH 35A 2.3mOhm</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/7448263505?qs=2kOmHSv6VfR2wo62vNWXfg%3D%3D</t>
+  </si>
+  <si>
+    <t>47x43x23.5mm</t>
+  </si>
+  <si>
+    <t>710-7448263505</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/7448263505.pdf</t>
+  </si>
+  <si>
+    <t>IND CMM</t>
+  </si>
+  <si>
+    <t>eUSR_SchLibrary/eUSR_SchLibrary - Inductor.SchLib</t>
+  </si>
+  <si>
+    <t>IND_CMM_THT_10x18.5mm</t>
+  </si>
+  <si>
+    <t>003-0001</t>
+  </si>
+  <si>
+    <t>Aluminium Electrolytic Capacitors - Radial Leaded WCAP-ATG5 470uF 50V 20% Radial</t>
+  </si>
+  <si>
+    <t>470uF 50V 20%</t>
+  </si>
+  <si>
+    <t>THT;D10xL20mm</t>
+  </si>
+  <si>
+    <t>Wurth Elektonik</t>
+  </si>
+  <si>
+    <t>710-860020675022</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/860020675022.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/860020675022?qs=0KOYDY2FL28clmrWTWQzzg%3D%3D</t>
+  </si>
+  <si>
+    <t>CAP polarized</t>
+  </si>
+  <si>
+    <t>CAP_10Dx20L</t>
   </si>
 </sst>
 </file>
@@ -8895,7 +8957,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -8945,8 +9007,7 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -13352,6 +13413,2014 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89BFA1EF-29B2-41E4-A9D1-F8E90A663FA1}">
+  <dimension ref="A1:N23"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetData>
+    <row r="1" spans="1:14" ht="14.5" customHeight="1">
+      <c r="A1" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="25" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" s="7" t="s">
+        <v>2766</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>2767</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>2768</v>
+      </c>
+      <c r="D2" s="7">
+        <v>3535</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>2769</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>2770</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>2771</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>2772</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>2773</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>2774</v>
+      </c>
+      <c r="L2" s="7" t="s">
+        <v>2877</v>
+      </c>
+      <c r="M2" s="7" t="s">
+        <v>2775</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="7" t="s">
+        <v>2776</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>2777</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>2768</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>2778</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>2779</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>2780</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>2781</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>2782</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>2774</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>2877</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>2783</v>
+      </c>
+      <c r="N3" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="7" t="s">
+        <v>2784</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>2785</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>2786</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>2787</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>2788</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>2789</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>2790</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>2790</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>2774</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>2877</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>2783</v>
+      </c>
+      <c r="N4" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="7" t="s">
+        <v>2791</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>2792</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>2793</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>2794</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>2795</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>2796</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I5" s="15" t="s">
+        <v>2797</v>
+      </c>
+      <c r="J5" s="15" t="s">
+        <v>2798</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>2774</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>2877</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>2783</v>
+      </c>
+      <c r="N5" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="7" t="s">
+        <v>2799</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>2800</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>2801</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>2802</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>2788</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>2803</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>2804</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>2805</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>2774</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>2877</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>2783</v>
+      </c>
+      <c r="N6" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="7" t="s">
+        <v>2806</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>2807</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>2808</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>2809</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>2810</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>2811</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>2812</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>2813</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>2814</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>2815</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>2877</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>2816</v>
+      </c>
+      <c r="N7" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="7" t="s">
+        <v>2817</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>2818</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>2808</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>2819</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>2820</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>2821</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>2822</v>
+      </c>
+      <c r="H8" s="16" t="s">
+        <v>2823</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>2824</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>2825</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>2774</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>2877</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>2826</v>
+      </c>
+      <c r="N8" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="14.5" customHeight="1">
+      <c r="A9" s="7" t="s">
+        <v>2827</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>2828</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>2786</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>2829</v>
+      </c>
+      <c r="E9" s="28" t="s">
+        <v>2830</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>2831</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>2832</v>
+      </c>
+      <c r="H9" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>2833</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>2834</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>2774</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>2877</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>2835</v>
+      </c>
+      <c r="N9" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="7" t="s">
+        <v>2836</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>2837</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>2786</v>
+      </c>
+      <c r="D10" s="29" t="s">
+        <v>249</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>2838</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>2839</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>2840</v>
+      </c>
+      <c r="H10" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>2841</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>2842</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>2774</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>2877</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>2843</v>
+      </c>
+      <c r="N10" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="7" t="s">
+        <v>2844</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>2845</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>2846</v>
+      </c>
+      <c r="D11" s="29" t="s">
+        <v>249</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>2847</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>2848</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>2849</v>
+      </c>
+      <c r="H11" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>2850</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>2851</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>2774</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>2877</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>2843</v>
+      </c>
+      <c r="N11" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="7" t="s">
+        <v>2852</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>2853</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>2808</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>2854</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>2855</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>2856</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>2857</v>
+      </c>
+      <c r="H12" s="16" t="s">
+        <v>2823</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>2858</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>2859</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>2815</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>2877</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>2855</v>
+      </c>
+      <c r="N12" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="13.5" customHeight="1">
+      <c r="A13" s="7" t="s">
+        <v>2860</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>2861</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>2862</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>2863</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>2864</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>2865</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>2866</v>
+      </c>
+      <c r="H13" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>2867</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>2868</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>2869</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>2877</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>2864</v>
+      </c>
+      <c r="N13" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="15" customHeight="1">
+      <c r="A14" s="7" t="s">
+        <v>2870</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>2871</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>2793</v>
+      </c>
+      <c r="D14" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>2872</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>2779</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>2873</v>
+      </c>
+      <c r="H14" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>2874</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>2875</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>2774</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>2877</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>2876</v>
+      </c>
+      <c r="N14" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="7" t="s">
+        <v>2106</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>2107</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>1856</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>2108</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>2085</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>2109</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I15" s="11" t="s">
+        <v>2110</v>
+      </c>
+      <c r="J15" s="11" t="s">
+        <v>2111</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>1943</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>2877</v>
+      </c>
+      <c r="M15" s="7" t="s">
+        <v>1856</v>
+      </c>
+      <c r="N15" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="7" t="s">
+        <v>2112</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>2113</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>1856</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>2114</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>2023</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>2115</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I16" s="11" t="s">
+        <v>2116</v>
+      </c>
+      <c r="J16" s="11" t="s">
+        <v>2116</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>2117</v>
+      </c>
+      <c r="L16" s="7" t="s">
+        <v>2877</v>
+      </c>
+      <c r="M16" s="7" t="s">
+        <v>1856</v>
+      </c>
+      <c r="N16" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" s="7" t="s">
+        <v>2118</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>2119</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>2120</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>2121</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>1877</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>2122</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I17" s="11" t="s">
+        <v>2123</v>
+      </c>
+      <c r="J17" s="11" t="s">
+        <v>2124</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>2125</v>
+      </c>
+      <c r="L17" s="7" t="s">
+        <v>2877</v>
+      </c>
+      <c r="M17" s="7" t="s">
+        <v>2120</v>
+      </c>
+      <c r="N17" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" s="7" t="s">
+        <v>2126</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>2127</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>1856</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>2128</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>2129</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>2130</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>2131</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>2132</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>1943</v>
+      </c>
+      <c r="L18" s="7" t="s">
+        <v>2877</v>
+      </c>
+      <c r="M18" s="7" t="s">
+        <v>1856</v>
+      </c>
+      <c r="N18" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" s="7" t="s">
+        <v>2133</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>2134</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>2135</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>2136</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>2137</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>2138</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>2139</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>2136</v>
+      </c>
+      <c r="L19" s="7" t="s">
+        <v>2877</v>
+      </c>
+      <c r="M19" s="7" t="s">
+        <v>2136</v>
+      </c>
+      <c r="N19" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" s="7" t="s">
+        <v>2140</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>2142</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>2143</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>2144</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>2145</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>2146</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>2143</v>
+      </c>
+      <c r="L20" s="7" t="s">
+        <v>2877</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>2147</v>
+      </c>
+      <c r="N20" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" s="16" t="s">
+        <v>2148</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>2149</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>1856</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>2150</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>1858</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>2151</v>
+      </c>
+      <c r="H21" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="I21" s="18" t="s">
+        <v>2152</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>2153</v>
+      </c>
+      <c r="K21" s="17" t="s">
+        <v>2154</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>2877</v>
+      </c>
+      <c r="M21" s="7" t="s">
+        <v>1856</v>
+      </c>
+      <c r="N21" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" s="16" t="s">
+        <v>2155</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>2156</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>2157</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>2158</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>1696</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>2159</v>
+      </c>
+      <c r="H22" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>2160</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>2161</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>2052</v>
+      </c>
+      <c r="L22" s="7" t="s">
+        <v>2877</v>
+      </c>
+      <c r="M22" s="7" t="s">
+        <v>1904</v>
+      </c>
+      <c r="N22" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" s="16" t="s">
+        <v>2162</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>2163</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>1947</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>2164</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>1696</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>2165</v>
+      </c>
+      <c r="H23" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>2166</v>
+      </c>
+      <c r="J23" s="18" t="s">
+        <v>2167</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>2052</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>2877</v>
+      </c>
+      <c r="M23" s="7" t="s">
+        <v>2060</v>
+      </c>
+      <c r="N23" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="I15" r:id="rId1" xr:uid="{00000000-0004-0000-0A00-00000F000000}"/>
+    <hyperlink ref="J15" r:id="rId2" xr:uid="{00000000-0004-0000-0A00-000010000000}"/>
+    <hyperlink ref="I16" r:id="rId3" xr:uid="{00000000-0004-0000-0A00-000011000000}"/>
+    <hyperlink ref="J16" r:id="rId4" xr:uid="{00000000-0004-0000-0A00-000012000000}"/>
+    <hyperlink ref="I17" r:id="rId5" xr:uid="{00000000-0004-0000-0A00-000013000000}"/>
+    <hyperlink ref="J17" r:id="rId6" xr:uid="{00000000-0004-0000-0A00-000014000000}"/>
+    <hyperlink ref="I21" r:id="rId7" xr:uid="{E5D95628-DADF-425D-8DC6-0740E7A281C6}"/>
+    <hyperlink ref="J23" r:id="rId8" xr:uid="{21B09737-BF9A-463D-87B2-ED444DC9196C}"/>
+    <hyperlink ref="J3" r:id="rId9" xr:uid="{00000000-0004-0000-0B00-000000000000}"/>
+    <hyperlink ref="I5" r:id="rId10" xr:uid="{00000000-0004-0000-0B00-000001000000}"/>
+    <hyperlink ref="J5" r:id="rId11" xr:uid="{00000000-0004-0000-0B00-000002000000}"/>
+    <hyperlink ref="I6" r:id="rId12" xr:uid="{00000000-0004-0000-0B00-000003000000}"/>
+    <hyperlink ref="J6" r:id="rId13" xr:uid="{00000000-0004-0000-0B00-000004000000}"/>
+    <hyperlink ref="F7" r:id="rId14" xr:uid="{00000000-0004-0000-0B00-000005000000}"/>
+    <hyperlink ref="I14" r:id="rId15" xr:uid="{BFE50862-7088-44B1-9DAF-F4C51270ACE8}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B6F0D32-9CE2-4DF7-927E-42E7BA331F12}">
+  <dimension ref="A1:O21"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="13" max="13" width="13.36328125" customWidth="1"/>
+    <col min="14" max="14" width="16.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="J2" t="s">
+        <v>54</v>
+      </c>
+      <c r="K2" t="s">
+        <v>1690</v>
+      </c>
+      <c r="L2" t="s">
+        <v>55</v>
+      </c>
+      <c r="M2" t="s">
+        <v>50</v>
+      </c>
+      <c r="N2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" t="s">
+        <v>1813</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>1693</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D3" s="22">
+        <v>1206</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>1695</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>1696</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>1697</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>1698</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>1699</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>1700</v>
+      </c>
+      <c r="L3" t="s">
+        <v>55</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>1701</v>
+      </c>
+      <c r="N3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O3" s="7"/>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" t="s">
+        <v>1814</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>1702</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>1703</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>1704</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>1705</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>1696</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>1706</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>1707</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>1708</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>1700</v>
+      </c>
+      <c r="L4" t="s">
+        <v>55</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>1709</v>
+      </c>
+      <c r="N4" t="s">
+        <v>25</v>
+      </c>
+      <c r="O4" s="7"/>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" t="s">
+        <v>1815</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>1710</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>1711</v>
+      </c>
+      <c r="D5" s="7">
+        <v>1206</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>1712</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>1691</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>1712</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I5" s="15" t="s">
+        <v>1713</v>
+      </c>
+      <c r="J5" s="15" t="s">
+        <v>1714</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>1700</v>
+      </c>
+      <c r="L5" t="s">
+        <v>55</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>1701</v>
+      </c>
+      <c r="N5" t="s">
+        <v>25</v>
+      </c>
+      <c r="O5" s="3"/>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" t="s">
+        <v>1816</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>1715</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>1716</v>
+      </c>
+      <c r="D6" s="7">
+        <v>1206</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>1717</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>1718</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>1717</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I6" s="15" t="s">
+        <v>1719</v>
+      </c>
+      <c r="J6" s="15" t="s">
+        <v>1720</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>1700</v>
+      </c>
+      <c r="L6" t="s">
+        <v>55</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>1701</v>
+      </c>
+      <c r="N6" t="s">
+        <v>25</v>
+      </c>
+      <c r="O6" s="3"/>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" t="s">
+        <v>1817</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>1721</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>1692</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>1722</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>1723</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>1696</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>1724</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>1725</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>1726</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>1700</v>
+      </c>
+      <c r="L7" t="s">
+        <v>55</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>1727</v>
+      </c>
+      <c r="N7" t="s">
+        <v>25</v>
+      </c>
+      <c r="O7" s="3"/>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" t="s">
+        <v>1818</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>1728</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>1703</v>
+      </c>
+      <c r="D8" s="7">
+        <v>1206</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>1729</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>1730</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>1731</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>1732</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>1733</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>1700</v>
+      </c>
+      <c r="L8" t="s">
+        <v>55</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>1701</v>
+      </c>
+      <c r="N8" t="s">
+        <v>25</v>
+      </c>
+      <c r="O8" s="3"/>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" t="s">
+        <v>1819</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>1734</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>1711</v>
+      </c>
+      <c r="D9" s="7">
+        <v>1206</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>1735</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>1730</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>1736</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>1737</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>1738</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>1700</v>
+      </c>
+      <c r="L9" t="s">
+        <v>55</v>
+      </c>
+      <c r="M9" s="7" t="s">
+        <v>1701</v>
+      </c>
+      <c r="N9" t="s">
+        <v>25</v>
+      </c>
+      <c r="O9" s="3"/>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" t="s">
+        <v>1820</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>1739</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>1740</v>
+      </c>
+      <c r="D10" s="7">
+        <v>1812</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>1741</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>1742</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>1743</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I10" s="15" t="s">
+        <v>1744</v>
+      </c>
+      <c r="J10" s="15" t="s">
+        <v>1745</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>1700</v>
+      </c>
+      <c r="L10" t="s">
+        <v>55</v>
+      </c>
+      <c r="M10" s="7" t="s">
+        <v>1746</v>
+      </c>
+      <c r="N10" t="s">
+        <v>25</v>
+      </c>
+      <c r="O10" s="3"/>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" t="s">
+        <v>1821</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>1747</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>1748</v>
+      </c>
+      <c r="D11" s="7">
+        <v>1812</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>1749</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>1742</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>1750</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>1751</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>1752</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>1700</v>
+      </c>
+      <c r="L11" t="s">
+        <v>55</v>
+      </c>
+      <c r="M11" s="7" t="s">
+        <v>1746</v>
+      </c>
+      <c r="N11" t="s">
+        <v>25</v>
+      </c>
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" t="s">
+        <v>1822</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>1753</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>1754</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>1755</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>1756</v>
+      </c>
+      <c r="F12" s="17" t="s">
+        <v>1757</v>
+      </c>
+      <c r="G12" s="17" t="s">
+        <v>1758</v>
+      </c>
+      <c r="H12" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="I12" s="18" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J12" s="18" t="s">
+        <v>1760</v>
+      </c>
+      <c r="K12" s="17" t="s">
+        <v>1700</v>
+      </c>
+      <c r="L12" t="s">
+        <v>55</v>
+      </c>
+      <c r="M12" s="17" t="s">
+        <v>1761</v>
+      </c>
+      <c r="N12" t="s">
+        <v>25</v>
+      </c>
+      <c r="O12" s="3"/>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" t="s">
+        <v>1823</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>1762</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>1763</v>
+      </c>
+      <c r="D13" s="3">
+        <v>1812</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>1764</v>
+      </c>
+      <c r="F13" s="17" t="s">
+        <v>1742</v>
+      </c>
+      <c r="G13" s="17" t="s">
+        <v>1765</v>
+      </c>
+      <c r="H13" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="I13" s="18" t="s">
+        <v>1766</v>
+      </c>
+      <c r="J13" s="18" t="s">
+        <v>1767</v>
+      </c>
+      <c r="K13" s="17" t="s">
+        <v>1700</v>
+      </c>
+      <c r="L13" t="s">
+        <v>55</v>
+      </c>
+      <c r="M13" s="7" t="s">
+        <v>1746</v>
+      </c>
+      <c r="N13" t="s">
+        <v>25</v>
+      </c>
+      <c r="O13" s="3"/>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" t="s">
+        <v>1824</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>1768</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>1763</v>
+      </c>
+      <c r="D14" s="7">
+        <v>1206</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>1769</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>1742</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>1770</v>
+      </c>
+      <c r="H14" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>1771</v>
+      </c>
+      <c r="J14" s="18" t="s">
+        <v>1772</v>
+      </c>
+      <c r="K14" s="17" t="s">
+        <v>1700</v>
+      </c>
+      <c r="L14" t="s">
+        <v>55</v>
+      </c>
+      <c r="M14" s="7" t="s">
+        <v>1701</v>
+      </c>
+      <c r="N14" t="s">
+        <v>25</v>
+      </c>
+      <c r="O14" s="3"/>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15" t="s">
+        <v>1825</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>1773</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>1774</v>
+      </c>
+      <c r="D15" s="7">
+        <v>1206</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>1775</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>1776</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>1777</v>
+      </c>
+      <c r="H15" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>1778</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>1779</v>
+      </c>
+      <c r="K15" s="17" t="s">
+        <v>1700</v>
+      </c>
+      <c r="L15" t="s">
+        <v>55</v>
+      </c>
+      <c r="M15" s="7" t="s">
+        <v>1701</v>
+      </c>
+      <c r="N15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>1780</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>1774</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>1781</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>1696</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>1782</v>
+      </c>
+      <c r="H16" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>1783</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>1784</v>
+      </c>
+      <c r="K16" s="17" t="s">
+        <v>1700</v>
+      </c>
+      <c r="L16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>1785</v>
+      </c>
+      <c r="N16" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" t="s">
+        <v>1827</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>1786</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>1763</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>1787</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>1696</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>1788</v>
+      </c>
+      <c r="H17" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>1789</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>1783</v>
+      </c>
+      <c r="K17" s="17" t="s">
+        <v>1700</v>
+      </c>
+      <c r="L17" t="s">
+        <v>55</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>1785</v>
+      </c>
+      <c r="N17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" t="s">
+        <v>1828</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>1790</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>1791</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>1792</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>1742</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>1793</v>
+      </c>
+      <c r="H18" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>1794</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>1795</v>
+      </c>
+      <c r="K18" s="17" t="s">
+        <v>1700</v>
+      </c>
+      <c r="L18" t="s">
+        <v>55</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>1785</v>
+      </c>
+      <c r="N18" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>1796</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>1763</v>
+      </c>
+      <c r="D19" s="3">
+        <v>1812</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>1797</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>1742</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>1798</v>
+      </c>
+      <c r="H19" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="I19" s="18" t="s">
+        <v>1799</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>1800</v>
+      </c>
+      <c r="K19" s="17" t="s">
+        <v>1700</v>
+      </c>
+      <c r="L19" t="s">
+        <v>55</v>
+      </c>
+      <c r="M19" s="7" t="s">
+        <v>1746</v>
+      </c>
+      <c r="N19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" t="s">
+        <v>1830</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>1801</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>1692</v>
+      </c>
+      <c r="D20" s="23" t="s">
+        <v>1802</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>1803</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>1742</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>1804</v>
+      </c>
+      <c r="H20" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="I20" s="18" t="s">
+        <v>1805</v>
+      </c>
+      <c r="J20" s="18" t="s">
+        <v>1806</v>
+      </c>
+      <c r="K20" s="17" t="s">
+        <v>1700</v>
+      </c>
+      <c r="L20" t="s">
+        <v>55</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>1807</v>
+      </c>
+      <c r="N20" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" t="s">
+        <v>1831</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>1808</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>1703</v>
+      </c>
+      <c r="D21" s="7">
+        <v>1812</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>1809</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>1742</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>1810</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>1811</v>
+      </c>
+      <c r="J21" s="18" t="s">
+        <v>1812</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>1700</v>
+      </c>
+      <c r="L21" t="s">
+        <v>55</v>
+      </c>
+      <c r="M21" s="7" t="s">
+        <v>1746</v>
+      </c>
+      <c r="N21" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="16" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="I2" r:id="rId1" xr:uid="{3DE7E9B7-7F71-48BD-A43F-56652EF48515}"/>
+    <hyperlink ref="I5" r:id="rId2" xr:uid="{00000000-0004-0000-0C00-000001000000}"/>
+    <hyperlink ref="J5" r:id="rId3" xr:uid="{00000000-0004-0000-0C00-000002000000}"/>
+    <hyperlink ref="I6" r:id="rId4" xr:uid="{00000000-0004-0000-0C00-000003000000}"/>
+    <hyperlink ref="J6" r:id="rId5" xr:uid="{00000000-0004-0000-0C00-000004000000}"/>
+    <hyperlink ref="I10" r:id="rId6" xr:uid="{00000000-0004-0000-0C00-000005000000}"/>
+    <hyperlink ref="J10" r:id="rId7" xr:uid="{00000000-0004-0000-0C00-000006000000}"/>
+    <hyperlink ref="I12" r:id="rId8" xr:uid="{DC4D0F7D-FABA-4F27-A8C4-C8F1159FEA34}"/>
+    <hyperlink ref="J12" r:id="rId9" xr:uid="{7C1A203F-2505-4DF3-8487-119DA9DE1A1B}"/>
+    <hyperlink ref="J13" r:id="rId10" xr:uid="{6F374EEE-953D-426D-AF07-D3E5C1F03D55}"/>
+    <hyperlink ref="I13" r:id="rId11" xr:uid="{959671DE-63B1-4C42-9AE2-A4D45EAFA482}"/>
+    <hyperlink ref="J14" r:id="rId12" xr:uid="{D0E41C99-5015-461D-998D-DD06CC299D2B}"/>
+    <hyperlink ref="I19" r:id="rId13" xr:uid="{EAFB85FD-4F43-4B6C-AEDE-D6E5C0E93BD1}"/>
+    <hyperlink ref="I20" r:id="rId14" xr:uid="{6C9DFF48-0956-4B25-8972-EC0656F1483E}"/>
+    <hyperlink ref="J20" r:id="rId15" xr:uid="{6EF40273-C6D8-4BC3-9EF6-1B4C76903848}"/>
+    <hyperlink ref="J21" r:id="rId16" xr:uid="{FFB17F08-401F-47B0-899B-612CD8B9FB6B}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C98E1A12-072F-4773-8CB5-47FFE077E85B}">
   <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -13601,7 +15670,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59BC8B2E-A067-463D-937A-30E88D8BECD0}">
   <dimension ref="A1:N1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -13655,7 +15724,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4BBBCF5-BAC9-459C-ABE9-2526B85FD81E}">
   <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -13849,7 +15918,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69A1C46E-DEF3-467B-A5BD-162AB66E6A86}">
   <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -14932,7 +17001,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE14AD29-8DB0-4C42-AB91-A73B867AE121}">
   <dimension ref="A1:N61"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -17481,7 +19550,7 @@
       <c r="J58" t="s">
         <v>2885</v>
       </c>
-      <c r="K58" s="32" t="s">
+      <c r="K58" s="31" t="s">
         <v>2895</v>
       </c>
       <c r="L58" s="7" t="s">
@@ -17569,7 +19638,7 @@
       <c r="J60" t="s">
         <v>2889</v>
       </c>
-      <c r="K60" s="32" t="s">
+      <c r="K60" s="31" t="s">
         <v>2416</v>
       </c>
       <c r="L60" s="7" t="s">
@@ -17613,7 +19682,7 @@
       <c r="J61" t="s">
         <v>2891</v>
       </c>
-      <c r="K61" s="31" t="s">
+      <c r="K61" s="3" t="s">
         <v>2540</v>
       </c>
       <c r="L61" s="7" t="s">
@@ -17688,6 +19757,113 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E05CC479-3669-40F7-BE22-BA5CFBFF29E9}">
+  <dimension ref="A1:N3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="5" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
+        <v>2906</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2907</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2908</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2909</v>
+      </c>
+      <c r="E2">
+        <v>860020675022</v>
+      </c>
+      <c r="F2" t="s">
+        <v>2910</v>
+      </c>
+      <c r="G2" t="s">
+        <v>2911</v>
+      </c>
+      <c r="H2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>2912</v>
+      </c>
+      <c r="J2" t="s">
+        <v>2913</v>
+      </c>
+      <c r="K2" t="s">
+        <v>2914</v>
+      </c>
+      <c r="L2" t="s">
+        <v>61</v>
+      </c>
+      <c r="M2" t="s">
+        <v>2915</v>
+      </c>
+      <c r="N2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="M3" s="7"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="I2" r:id="rId1" xr:uid="{BB2EDAB8-75EB-46D2-BA14-384BF06E1A6E}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60E8291E-4293-4634-B9E9-80CB520CA181}">
   <dimension ref="A1:N136"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -23777,7 +25953,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81F9848D-6D60-47C0-9F84-A561FE4F106E}">
   <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -23927,7 +26103,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01C6B0FD-D8A3-44EC-9532-03DDA232F922}">
   <dimension ref="A1:N1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -23981,7 +26157,108 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D956EFE-E955-4E62-8478-2294E6413DC1}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
+        <v>2896</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2897</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2898</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2900</v>
+      </c>
+      <c r="E2">
+        <v>7448263505</v>
+      </c>
+      <c r="F2" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G2" t="s">
+        <v>2901</v>
+      </c>
+      <c r="H2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>2902</v>
+      </c>
+      <c r="J2" t="s">
+        <v>2899</v>
+      </c>
+      <c r="K2" t="s">
+        <v>2903</v>
+      </c>
+      <c r="L2" t="s">
+        <v>2904</v>
+      </c>
+      <c r="M2" t="s">
+        <v>2905</v>
+      </c>
+      <c r="N2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="I2" r:id="rId1" xr:uid="{1A9E4CB0-A8E7-4FC1-A9A7-FA5E28311F4C}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{652841DA-3619-42EE-A536-61B58BE1B457}">
   <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -24393,7 +26670,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FE2008B-4BF4-4C9A-883A-FEE5873AEAF4}">
   <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -24944,7 +27221,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79E65951-BFD2-4888-A0A6-19D5130CB4A6}">
   <dimension ref="A1:N23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -25964,2012 +28241,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89BFA1EF-29B2-41E4-A9D1-F8E90A663FA1}">
-  <dimension ref="A1:N23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
-  <sheetData>
-    <row r="1" spans="1:14" ht="14.5" customHeight="1">
-      <c r="A1" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="25" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="25" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="7" t="s">
-        <v>2766</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>2767</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>2768</v>
-      </c>
-      <c r="D2" s="7">
-        <v>3535</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>2769</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>2770</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>2771</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>2772</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>2773</v>
-      </c>
-      <c r="K2" s="7" t="s">
-        <v>2774</v>
-      </c>
-      <c r="L2" s="7" t="s">
-        <v>2877</v>
-      </c>
-      <c r="M2" s="7" t="s">
-        <v>2775</v>
-      </c>
-      <c r="N2" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="7" t="s">
-        <v>2776</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>2777</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>2768</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>2778</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>2779</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>2780</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>2781</v>
-      </c>
-      <c r="J3" s="15" t="s">
-        <v>2782</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>2774</v>
-      </c>
-      <c r="L3" s="7" t="s">
-        <v>2877</v>
-      </c>
-      <c r="M3" s="7" t="s">
-        <v>2783</v>
-      </c>
-      <c r="N3" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="7" t="s">
-        <v>2784</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>2785</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>2786</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>2787</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>2788</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>2789</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>2790</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>2790</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>2774</v>
-      </c>
-      <c r="L4" s="7" t="s">
-        <v>2877</v>
-      </c>
-      <c r="M4" s="7" t="s">
-        <v>2783</v>
-      </c>
-      <c r="N4" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="7" t="s">
-        <v>2791</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>2792</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>2793</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>2794</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>2795</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>2796</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I5" s="15" t="s">
-        <v>2797</v>
-      </c>
-      <c r="J5" s="15" t="s">
-        <v>2798</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>2774</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>2877</v>
-      </c>
-      <c r="M5" s="7" t="s">
-        <v>2783</v>
-      </c>
-      <c r="N5" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="7" t="s">
-        <v>2799</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>2800</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>2801</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>2802</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>2788</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>2803</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I6" s="11" t="s">
-        <v>2804</v>
-      </c>
-      <c r="J6" s="11" t="s">
-        <v>2805</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>2774</v>
-      </c>
-      <c r="L6" s="7" t="s">
-        <v>2877</v>
-      </c>
-      <c r="M6" s="7" t="s">
-        <v>2783</v>
-      </c>
-      <c r="N6" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="7" t="s">
-        <v>2806</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>2807</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>2808</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>2809</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>2810</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>2811</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>2812</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>2813</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>2814</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>2815</v>
-      </c>
-      <c r="L7" s="7" t="s">
-        <v>2877</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>2816</v>
-      </c>
-      <c r="N7" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="7" t="s">
-        <v>2817</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>2818</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>2808</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>2819</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>2820</v>
-      </c>
-      <c r="F8" s="16" t="s">
-        <v>2821</v>
-      </c>
-      <c r="G8" s="16" t="s">
-        <v>2822</v>
-      </c>
-      <c r="H8" s="16" t="s">
-        <v>2823</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>2824</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>2825</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>2774</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>2877</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>2826</v>
-      </c>
-      <c r="N8" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="14.5" customHeight="1">
-      <c r="A9" s="7" t="s">
-        <v>2827</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>2828</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>2786</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>2829</v>
-      </c>
-      <c r="E9" s="28" t="s">
-        <v>2830</v>
-      </c>
-      <c r="F9" s="16" t="s">
-        <v>2831</v>
-      </c>
-      <c r="G9" s="16" t="s">
-        <v>2832</v>
-      </c>
-      <c r="H9" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>2833</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>2834</v>
-      </c>
-      <c r="K9" s="7" t="s">
-        <v>2774</v>
-      </c>
-      <c r="L9" s="7" t="s">
-        <v>2877</v>
-      </c>
-      <c r="M9" s="16" t="s">
-        <v>2835</v>
-      </c>
-      <c r="N9" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="7" t="s">
-        <v>2836</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>2837</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>2786</v>
-      </c>
-      <c r="D10" s="29" t="s">
-        <v>249</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>2838</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>2839</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>2840</v>
-      </c>
-      <c r="H10" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>2841</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>2842</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>2774</v>
-      </c>
-      <c r="L10" s="7" t="s">
-        <v>2877</v>
-      </c>
-      <c r="M10" s="16" t="s">
-        <v>2843</v>
-      </c>
-      <c r="N10" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="7" t="s">
-        <v>2844</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>2845</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>2846</v>
-      </c>
-      <c r="D11" s="29" t="s">
-        <v>249</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>2847</v>
-      </c>
-      <c r="F11" s="17" t="s">
-        <v>2848</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>2849</v>
-      </c>
-      <c r="H11" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>2850</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>2851</v>
-      </c>
-      <c r="K11" s="7" t="s">
-        <v>2774</v>
-      </c>
-      <c r="L11" s="7" t="s">
-        <v>2877</v>
-      </c>
-      <c r="M11" s="16" t="s">
-        <v>2843</v>
-      </c>
-      <c r="N11" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="7" t="s">
-        <v>2852</v>
-      </c>
-      <c r="B12" s="17" t="s">
-        <v>2853</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>2808</v>
-      </c>
-      <c r="D12" s="16" t="s">
-        <v>2854</v>
-      </c>
-      <c r="E12" s="16" t="s">
-        <v>2855</v>
-      </c>
-      <c r="F12" s="16" t="s">
-        <v>2856</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>2857</v>
-      </c>
-      <c r="H12" s="16" t="s">
-        <v>2823</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>2858</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>2859</v>
-      </c>
-      <c r="K12" s="7" t="s">
-        <v>2815</v>
-      </c>
-      <c r="L12" s="7" t="s">
-        <v>2877</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>2855</v>
-      </c>
-      <c r="N12" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="13.5" customHeight="1">
-      <c r="A13" s="7" t="s">
-        <v>2860</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>2861</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>2862</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>2863</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>2864</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>2865</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>2866</v>
-      </c>
-      <c r="H13" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>2867</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>2868</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>2869</v>
-      </c>
-      <c r="L13" s="7" t="s">
-        <v>2877</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>2864</v>
-      </c>
-      <c r="N13" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="15" customHeight="1">
-      <c r="A14" s="7" t="s">
-        <v>2870</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>2871</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>2793</v>
-      </c>
-      <c r="D14" s="23" t="s">
-        <v>59</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>2872</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>2779</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>2873</v>
-      </c>
-      <c r="H14" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>2874</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>2875</v>
-      </c>
-      <c r="K14" s="7" t="s">
-        <v>2774</v>
-      </c>
-      <c r="L14" s="7" t="s">
-        <v>2877</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>2876</v>
-      </c>
-      <c r="N14" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="A15" s="7" t="s">
-        <v>2106</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>2107</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>1856</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>2108</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>2085</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>2109</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I15" s="11" t="s">
-        <v>2110</v>
-      </c>
-      <c r="J15" s="11" t="s">
-        <v>2111</v>
-      </c>
-      <c r="K15" s="7" t="s">
-        <v>1943</v>
-      </c>
-      <c r="L15" s="7" t="s">
-        <v>2877</v>
-      </c>
-      <c r="M15" s="7" t="s">
-        <v>1856</v>
-      </c>
-      <c r="N15" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="A16" s="7" t="s">
-        <v>2112</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>2113</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>1856</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>2114</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>2023</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>2115</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I16" s="11" t="s">
-        <v>2116</v>
-      </c>
-      <c r="J16" s="11" t="s">
-        <v>2116</v>
-      </c>
-      <c r="K16" s="7" t="s">
-        <v>2117</v>
-      </c>
-      <c r="L16" s="7" t="s">
-        <v>2877</v>
-      </c>
-      <c r="M16" s="7" t="s">
-        <v>1856</v>
-      </c>
-      <c r="N16" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
-      <c r="A17" s="7" t="s">
-        <v>2118</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>2119</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>2120</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>2121</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>1877</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>2122</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I17" s="11" t="s">
-        <v>2123</v>
-      </c>
-      <c r="J17" s="11" t="s">
-        <v>2124</v>
-      </c>
-      <c r="K17" s="7" t="s">
-        <v>2125</v>
-      </c>
-      <c r="L17" s="7" t="s">
-        <v>2877</v>
-      </c>
-      <c r="M17" s="7" t="s">
-        <v>2120</v>
-      </c>
-      <c r="N17" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
-      <c r="A18" s="7" t="s">
-        <v>2126</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>2127</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>1856</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>2128</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>2129</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>2130</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>2131</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>2132</v>
-      </c>
-      <c r="K18" s="7" t="s">
-        <v>1943</v>
-      </c>
-      <c r="L18" s="7" t="s">
-        <v>2877</v>
-      </c>
-      <c r="M18" s="7" t="s">
-        <v>1856</v>
-      </c>
-      <c r="N18" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
-      <c r="A19" s="7" t="s">
-        <v>2133</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>2134</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>2135</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>2136</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>2137</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>2138</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>2139</v>
-      </c>
-      <c r="K19" s="7" t="s">
-        <v>2136</v>
-      </c>
-      <c r="L19" s="7" t="s">
-        <v>2877</v>
-      </c>
-      <c r="M19" s="7" t="s">
-        <v>2136</v>
-      </c>
-      <c r="N19" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
-      <c r="A20" s="7" t="s">
-        <v>2140</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>2141</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>2142</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>2143</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>1658</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>2144</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>2145</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>2146</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>2143</v>
-      </c>
-      <c r="L20" s="7" t="s">
-        <v>2877</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>2147</v>
-      </c>
-      <c r="N20" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14">
-      <c r="A21" s="16" t="s">
-        <v>2148</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>2149</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>1856</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>2150</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>1858</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>2151</v>
-      </c>
-      <c r="H21" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="I21" s="18" t="s">
-        <v>2152</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>2153</v>
-      </c>
-      <c r="K21" s="17" t="s">
-        <v>2154</v>
-      </c>
-      <c r="L21" s="7" t="s">
-        <v>2877</v>
-      </c>
-      <c r="M21" s="7" t="s">
-        <v>1856</v>
-      </c>
-      <c r="N21" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14">
-      <c r="A22" s="16" t="s">
-        <v>2155</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>2156</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>2157</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>2158</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>1696</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>2159</v>
-      </c>
-      <c r="H22" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>2160</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>2161</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>2052</v>
-      </c>
-      <c r="L22" s="7" t="s">
-        <v>2877</v>
-      </c>
-      <c r="M22" s="7" t="s">
-        <v>1904</v>
-      </c>
-      <c r="N22" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14">
-      <c r="A23" s="16" t="s">
-        <v>2162</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>2163</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>1947</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>2164</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>1696</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>2165</v>
-      </c>
-      <c r="H23" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>2166</v>
-      </c>
-      <c r="J23" s="18" t="s">
-        <v>2167</v>
-      </c>
-      <c r="K23" s="7" t="s">
-        <v>2052</v>
-      </c>
-      <c r="L23" s="7" t="s">
-        <v>2877</v>
-      </c>
-      <c r="M23" s="7" t="s">
-        <v>2060</v>
-      </c>
-      <c r="N23" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="I15" r:id="rId1" xr:uid="{00000000-0004-0000-0A00-00000F000000}"/>
-    <hyperlink ref="J15" r:id="rId2" xr:uid="{00000000-0004-0000-0A00-000010000000}"/>
-    <hyperlink ref="I16" r:id="rId3" xr:uid="{00000000-0004-0000-0A00-000011000000}"/>
-    <hyperlink ref="J16" r:id="rId4" xr:uid="{00000000-0004-0000-0A00-000012000000}"/>
-    <hyperlink ref="I17" r:id="rId5" xr:uid="{00000000-0004-0000-0A00-000013000000}"/>
-    <hyperlink ref="J17" r:id="rId6" xr:uid="{00000000-0004-0000-0A00-000014000000}"/>
-    <hyperlink ref="I21" r:id="rId7" xr:uid="{E5D95628-DADF-425D-8DC6-0740E7A281C6}"/>
-    <hyperlink ref="J23" r:id="rId8" xr:uid="{21B09737-BF9A-463D-87B2-ED444DC9196C}"/>
-    <hyperlink ref="J3" r:id="rId9" xr:uid="{00000000-0004-0000-0B00-000000000000}"/>
-    <hyperlink ref="I5" r:id="rId10" xr:uid="{00000000-0004-0000-0B00-000001000000}"/>
-    <hyperlink ref="J5" r:id="rId11" xr:uid="{00000000-0004-0000-0B00-000002000000}"/>
-    <hyperlink ref="I6" r:id="rId12" xr:uid="{00000000-0004-0000-0B00-000003000000}"/>
-    <hyperlink ref="J6" r:id="rId13" xr:uid="{00000000-0004-0000-0B00-000004000000}"/>
-    <hyperlink ref="F7" r:id="rId14" xr:uid="{00000000-0004-0000-0B00-000005000000}"/>
-    <hyperlink ref="I14" r:id="rId15" xr:uid="{BFE50862-7088-44B1-9DAF-F4C51270ACE8}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B6F0D32-9CE2-4DF7-927E-42E7BA331F12}">
-  <dimension ref="A1:O21"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
-  <cols>
-    <col min="13" max="13" width="13.36328125" customWidth="1"/>
-    <col min="14" max="14" width="16.1796875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:15">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="J2" t="s">
-        <v>54</v>
-      </c>
-      <c r="K2" t="s">
-        <v>1690</v>
-      </c>
-      <c r="L2" t="s">
-        <v>55</v>
-      </c>
-      <c r="M2" t="s">
-        <v>50</v>
-      </c>
-      <c r="N2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
-      <c r="A3" t="s">
-        <v>1813</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>1693</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>1694</v>
-      </c>
-      <c r="D3" s="22">
-        <v>1206</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>1695</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>1696</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>1697</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>1698</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>1699</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>1700</v>
-      </c>
-      <c r="L3" t="s">
-        <v>55</v>
-      </c>
-      <c r="M3" s="7" t="s">
-        <v>1701</v>
-      </c>
-      <c r="N3" t="s">
-        <v>25</v>
-      </c>
-      <c r="O3" s="7"/>
-    </row>
-    <row r="4" spans="1:15">
-      <c r="A4" t="s">
-        <v>1814</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>1702</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>1703</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>1704</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>1705</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>1696</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>1706</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>1707</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>1708</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>1700</v>
-      </c>
-      <c r="L4" t="s">
-        <v>55</v>
-      </c>
-      <c r="M4" s="7" t="s">
-        <v>1709</v>
-      </c>
-      <c r="N4" t="s">
-        <v>25</v>
-      </c>
-      <c r="O4" s="7"/>
-    </row>
-    <row r="5" spans="1:15">
-      <c r="A5" t="s">
-        <v>1815</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>1710</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>1711</v>
-      </c>
-      <c r="D5" s="7">
-        <v>1206</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>1712</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>1691</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>1712</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I5" s="15" t="s">
-        <v>1713</v>
-      </c>
-      <c r="J5" s="15" t="s">
-        <v>1714</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>1700</v>
-      </c>
-      <c r="L5" t="s">
-        <v>55</v>
-      </c>
-      <c r="M5" s="7" t="s">
-        <v>1701</v>
-      </c>
-      <c r="N5" t="s">
-        <v>25</v>
-      </c>
-      <c r="O5" s="3"/>
-    </row>
-    <row r="6" spans="1:15">
-      <c r="A6" t="s">
-        <v>1816</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>1715</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>1716</v>
-      </c>
-      <c r="D6" s="7">
-        <v>1206</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>1717</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>1718</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>1717</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I6" s="15" t="s">
-        <v>1719</v>
-      </c>
-      <c r="J6" s="15" t="s">
-        <v>1720</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>1700</v>
-      </c>
-      <c r="L6" t="s">
-        <v>55</v>
-      </c>
-      <c r="M6" s="7" t="s">
-        <v>1701</v>
-      </c>
-      <c r="N6" t="s">
-        <v>25</v>
-      </c>
-      <c r="O6" s="3"/>
-    </row>
-    <row r="7" spans="1:15">
-      <c r="A7" t="s">
-        <v>1817</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>1721</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>1692</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>1722</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>1723</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>1696</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>1724</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>1725</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>1726</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>1700</v>
-      </c>
-      <c r="L7" t="s">
-        <v>55</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>1727</v>
-      </c>
-      <c r="N7" t="s">
-        <v>25</v>
-      </c>
-      <c r="O7" s="3"/>
-    </row>
-    <row r="8" spans="1:15">
-      <c r="A8" t="s">
-        <v>1818</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>1728</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>1703</v>
-      </c>
-      <c r="D8" s="7">
-        <v>1206</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>1729</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>1730</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>1731</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>1732</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>1733</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>1700</v>
-      </c>
-      <c r="L8" t="s">
-        <v>55</v>
-      </c>
-      <c r="M8" s="7" t="s">
-        <v>1701</v>
-      </c>
-      <c r="N8" t="s">
-        <v>25</v>
-      </c>
-      <c r="O8" s="3"/>
-    </row>
-    <row r="9" spans="1:15">
-      <c r="A9" t="s">
-        <v>1819</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>1734</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>1711</v>
-      </c>
-      <c r="D9" s="7">
-        <v>1206</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>1735</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>1730</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>1736</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>1737</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>1738</v>
-      </c>
-      <c r="K9" s="7" t="s">
-        <v>1700</v>
-      </c>
-      <c r="L9" t="s">
-        <v>55</v>
-      </c>
-      <c r="M9" s="7" t="s">
-        <v>1701</v>
-      </c>
-      <c r="N9" t="s">
-        <v>25</v>
-      </c>
-      <c r="O9" s="3"/>
-    </row>
-    <row r="10" spans="1:15">
-      <c r="A10" t="s">
-        <v>1820</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>1739</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>1740</v>
-      </c>
-      <c r="D10" s="7">
-        <v>1812</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>1741</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>1742</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>1743</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I10" s="15" t="s">
-        <v>1744</v>
-      </c>
-      <c r="J10" s="15" t="s">
-        <v>1745</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>1700</v>
-      </c>
-      <c r="L10" t="s">
-        <v>55</v>
-      </c>
-      <c r="M10" s="7" t="s">
-        <v>1746</v>
-      </c>
-      <c r="N10" t="s">
-        <v>25</v>
-      </c>
-      <c r="O10" s="3"/>
-    </row>
-    <row r="11" spans="1:15">
-      <c r="A11" t="s">
-        <v>1821</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>1747</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>1748</v>
-      </c>
-      <c r="D11" s="7">
-        <v>1812</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>1749</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>1742</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>1750</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>1751</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>1752</v>
-      </c>
-      <c r="K11" s="7" t="s">
-        <v>1700</v>
-      </c>
-      <c r="L11" t="s">
-        <v>55</v>
-      </c>
-      <c r="M11" s="7" t="s">
-        <v>1746</v>
-      </c>
-      <c r="N11" t="s">
-        <v>25</v>
-      </c>
-      <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15">
-      <c r="A12" t="s">
-        <v>1822</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>1753</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>1754</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>1755</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>1756</v>
-      </c>
-      <c r="F12" s="17" t="s">
-        <v>1757</v>
-      </c>
-      <c r="G12" s="17" t="s">
-        <v>1758</v>
-      </c>
-      <c r="H12" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="I12" s="18" t="s">
-        <v>1759</v>
-      </c>
-      <c r="J12" s="18" t="s">
-        <v>1760</v>
-      </c>
-      <c r="K12" s="17" t="s">
-        <v>1700</v>
-      </c>
-      <c r="L12" t="s">
-        <v>55</v>
-      </c>
-      <c r="M12" s="17" t="s">
-        <v>1761</v>
-      </c>
-      <c r="N12" t="s">
-        <v>25</v>
-      </c>
-      <c r="O12" s="3"/>
-    </row>
-    <row r="13" spans="1:15">
-      <c r="A13" t="s">
-        <v>1823</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>1762</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>1763</v>
-      </c>
-      <c r="D13" s="3">
-        <v>1812</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>1764</v>
-      </c>
-      <c r="F13" s="17" t="s">
-        <v>1742</v>
-      </c>
-      <c r="G13" s="17" t="s">
-        <v>1765</v>
-      </c>
-      <c r="H13" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="I13" s="18" t="s">
-        <v>1766</v>
-      </c>
-      <c r="J13" s="18" t="s">
-        <v>1767</v>
-      </c>
-      <c r="K13" s="17" t="s">
-        <v>1700</v>
-      </c>
-      <c r="L13" t="s">
-        <v>55</v>
-      </c>
-      <c r="M13" s="7" t="s">
-        <v>1746</v>
-      </c>
-      <c r="N13" t="s">
-        <v>25</v>
-      </c>
-      <c r="O13" s="3"/>
-    </row>
-    <row r="14" spans="1:15">
-      <c r="A14" t="s">
-        <v>1824</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>1768</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>1763</v>
-      </c>
-      <c r="D14" s="7">
-        <v>1206</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>1769</v>
-      </c>
-      <c r="F14" s="17" t="s">
-        <v>1742</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>1770</v>
-      </c>
-      <c r="H14" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>1771</v>
-      </c>
-      <c r="J14" s="18" t="s">
-        <v>1772</v>
-      </c>
-      <c r="K14" s="17" t="s">
-        <v>1700</v>
-      </c>
-      <c r="L14" t="s">
-        <v>55</v>
-      </c>
-      <c r="M14" s="7" t="s">
-        <v>1701</v>
-      </c>
-      <c r="N14" t="s">
-        <v>25</v>
-      </c>
-      <c r="O14" s="3"/>
-    </row>
-    <row r="15" spans="1:15">
-      <c r="A15" t="s">
-        <v>1825</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>1773</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>1774</v>
-      </c>
-      <c r="D15" s="7">
-        <v>1206</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>1775</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>1776</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>1777</v>
-      </c>
-      <c r="H15" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>1778</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>1779</v>
-      </c>
-      <c r="K15" s="17" t="s">
-        <v>1700</v>
-      </c>
-      <c r="L15" t="s">
-        <v>55</v>
-      </c>
-      <c r="M15" s="7" t="s">
-        <v>1701</v>
-      </c>
-      <c r="N15" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
-      <c r="A16" t="s">
-        <v>1826</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>1780</v>
-      </c>
-      <c r="C16" s="16" t="s">
-        <v>1774</v>
-      </c>
-      <c r="D16" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="E16" s="16" t="s">
-        <v>1781</v>
-      </c>
-      <c r="F16" s="16" t="s">
-        <v>1696</v>
-      </c>
-      <c r="G16" s="16" t="s">
-        <v>1782</v>
-      </c>
-      <c r="H16" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>1783</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>1784</v>
-      </c>
-      <c r="K16" s="17" t="s">
-        <v>1700</v>
-      </c>
-      <c r="L16" t="s">
-        <v>55</v>
-      </c>
-      <c r="M16" s="16" t="s">
-        <v>1785</v>
-      </c>
-      <c r="N16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
-      <c r="A17" t="s">
-        <v>1827</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>1786</v>
-      </c>
-      <c r="C17" s="16" t="s">
-        <v>1763</v>
-      </c>
-      <c r="D17" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="E17" s="16" t="s">
-        <v>1787</v>
-      </c>
-      <c r="F17" s="16" t="s">
-        <v>1696</v>
-      </c>
-      <c r="G17" s="16" t="s">
-        <v>1788</v>
-      </c>
-      <c r="H17" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>1789</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>1783</v>
-      </c>
-      <c r="K17" s="17" t="s">
-        <v>1700</v>
-      </c>
-      <c r="L17" t="s">
-        <v>55</v>
-      </c>
-      <c r="M17" s="16" t="s">
-        <v>1785</v>
-      </c>
-      <c r="N17" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
-      <c r="A18" t="s">
-        <v>1828</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>1790</v>
-      </c>
-      <c r="C18" s="16" t="s">
-        <v>1791</v>
-      </c>
-      <c r="D18" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>1792</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>1742</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>1793</v>
-      </c>
-      <c r="H18" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>1794</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>1795</v>
-      </c>
-      <c r="K18" s="17" t="s">
-        <v>1700</v>
-      </c>
-      <c r="L18" t="s">
-        <v>55</v>
-      </c>
-      <c r="M18" s="16" t="s">
-        <v>1785</v>
-      </c>
-      <c r="N18" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
-      <c r="A19" t="s">
-        <v>1829</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>1796</v>
-      </c>
-      <c r="C19" s="16" t="s">
-        <v>1763</v>
-      </c>
-      <c r="D19" s="3">
-        <v>1812</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>1797</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>1742</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>1798</v>
-      </c>
-      <c r="H19" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="I19" s="18" t="s">
-        <v>1799</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>1800</v>
-      </c>
-      <c r="K19" s="17" t="s">
-        <v>1700</v>
-      </c>
-      <c r="L19" t="s">
-        <v>55</v>
-      </c>
-      <c r="M19" s="7" t="s">
-        <v>1746</v>
-      </c>
-      <c r="N19" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
-      <c r="A20" t="s">
-        <v>1830</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>1801</v>
-      </c>
-      <c r="C20" s="16" t="s">
-        <v>1692</v>
-      </c>
-      <c r="D20" s="23" t="s">
-        <v>1802</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>1803</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>1742</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>1804</v>
-      </c>
-      <c r="H20" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="I20" s="18" t="s">
-        <v>1805</v>
-      </c>
-      <c r="J20" s="18" t="s">
-        <v>1806</v>
-      </c>
-      <c r="K20" s="17" t="s">
-        <v>1700</v>
-      </c>
-      <c r="L20" t="s">
-        <v>55</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>1807</v>
-      </c>
-      <c r="N20" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14">
-      <c r="A21" t="s">
-        <v>1831</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>1808</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>1703</v>
-      </c>
-      <c r="D21" s="7">
-        <v>1812</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>1809</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>1742</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>1810</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>1811</v>
-      </c>
-      <c r="J21" s="18" t="s">
-        <v>1812</v>
-      </c>
-      <c r="K21" s="7" t="s">
-        <v>1700</v>
-      </c>
-      <c r="L21" t="s">
-        <v>55</v>
-      </c>
-      <c r="M21" s="7" t="s">
-        <v>1746</v>
-      </c>
-      <c r="N21" t="s">
-        <v>25</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="16" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="I2" r:id="rId1" xr:uid="{3DE7E9B7-7F71-48BD-A43F-56652EF48515}"/>
-    <hyperlink ref="I5" r:id="rId2" xr:uid="{00000000-0004-0000-0C00-000001000000}"/>
-    <hyperlink ref="J5" r:id="rId3" xr:uid="{00000000-0004-0000-0C00-000002000000}"/>
-    <hyperlink ref="I6" r:id="rId4" xr:uid="{00000000-0004-0000-0C00-000003000000}"/>
-    <hyperlink ref="J6" r:id="rId5" xr:uid="{00000000-0004-0000-0C00-000004000000}"/>
-    <hyperlink ref="I10" r:id="rId6" xr:uid="{00000000-0004-0000-0C00-000005000000}"/>
-    <hyperlink ref="J10" r:id="rId7" xr:uid="{00000000-0004-0000-0C00-000006000000}"/>
-    <hyperlink ref="I12" r:id="rId8" xr:uid="{DC4D0F7D-FABA-4F27-A8C4-C8F1159FEA34}"/>
-    <hyperlink ref="J12" r:id="rId9" xr:uid="{7C1A203F-2505-4DF3-8487-119DA9DE1A1B}"/>
-    <hyperlink ref="J13" r:id="rId10" xr:uid="{6F374EEE-953D-426D-AF07-D3E5C1F03D55}"/>
-    <hyperlink ref="I13" r:id="rId11" xr:uid="{959671DE-63B1-4C42-9AE2-A4D45EAFA482}"/>
-    <hyperlink ref="J14" r:id="rId12" xr:uid="{D0E41C99-5015-461D-998D-DD06CC299D2B}"/>
-    <hyperlink ref="I19" r:id="rId13" xr:uid="{EAFB85FD-4F43-4B6C-AEDE-D6E5C0E93BD1}"/>
-    <hyperlink ref="I20" r:id="rId14" xr:uid="{6C9DFF48-0956-4B25-8972-EC0656F1483E}"/>
-    <hyperlink ref="J20" r:id="rId15" xr:uid="{6EF40273-C6D8-4BC3-9EF6-1B4C76903848}"/>
-    <hyperlink ref="J21" r:id="rId16" xr:uid="{FFB17F08-401F-47B0-899B-612CD8B9FB6B}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B74AA2D8-E955-4948-8612-3823F2A6CDFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2F8A1BE-3970-4568-BD7A-4D709525CAC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5814" uniqueCount="2916">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5842" uniqueCount="2925">
   <si>
     <t>ID</t>
   </si>
@@ -8788,6 +8788,33 @@
   </si>
   <si>
     <t>CAP_10Dx20L</t>
+  </si>
+  <si>
+    <t>110-0061</t>
+  </si>
+  <si>
+    <t>HTSW-102-07-G-S</t>
+  </si>
+  <si>
+    <t>200-HTSW10207GS</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/datasheet/3/85/1/htsw_th.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Samtec/HTSW-102-07-G-S?qs=FESYatJ8odI1BCBanfu%2FIg%3D%3D</t>
+  </si>
+  <si>
+    <t>010-0136</t>
+  </si>
+  <si>
+    <t>603-RC0603FR-7W10KL</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/datasheet/3/508/1/PYU_RC_GROUP_51_ROHS_L.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/YAGEO/RC0603FR-7W10KL?qs=AQlKX63v8Ru%2F1n5uALWRmg%3D%3D</t>
   </si>
 </sst>
 </file>
@@ -17003,7 +17030,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE14AD29-8DB0-4C42-AB91-A73B867AE121}">
-  <dimension ref="A1:N61"/>
+  <dimension ref="A1:N62"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="5" max="5" width="16.36328125" bestFit="1" customWidth="1"/>
@@ -19692,6 +19719,50 @@
         <v>657004150201</v>
       </c>
       <c r="N61" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14">
+      <c r="A62" s="16" t="s">
+        <v>2916</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>2466</v>
+      </c>
+      <c r="C62" s="16" t="s">
+        <v>2170</v>
+      </c>
+      <c r="D62" s="16" t="s">
+        <v>2543</v>
+      </c>
+      <c r="E62" s="7" t="s">
+        <v>2917</v>
+      </c>
+      <c r="F62" s="7" t="s">
+        <v>2403</v>
+      </c>
+      <c r="G62" s="16" t="s">
+        <v>2918</v>
+      </c>
+      <c r="H62" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I62" s="7" t="s">
+        <v>2919</v>
+      </c>
+      <c r="J62" s="18" t="s">
+        <v>2920</v>
+      </c>
+      <c r="K62" s="16" t="s">
+        <v>2176</v>
+      </c>
+      <c r="L62" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M62" s="16" t="s">
+        <v>2322</v>
+      </c>
+      <c r="N62" s="7" t="s">
         <v>25</v>
       </c>
     </row>
@@ -19865,7 +19936,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60E8291E-4293-4634-B9E9-80CB520CA181}">
-  <dimension ref="A1:N136"/>
+  <dimension ref="A1:N137"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="3" max="3" width="19.90625" customWidth="1"/>
@@ -25856,7 +25927,52 @@
         <v>25</v>
       </c>
     </row>
+    <row r="137" spans="1:14">
+      <c r="A137" s="16" t="s">
+        <v>2921</v>
+      </c>
+      <c r="B137" s="7" t="s">
+        <v>906</v>
+      </c>
+      <c r="C137" s="7" t="s">
+        <v>907</v>
+      </c>
+      <c r="D137" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E137" s="7" t="s">
+        <v>908</v>
+      </c>
+      <c r="F137" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G137" s="16" t="s">
+        <v>2922</v>
+      </c>
+      <c r="H137" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I137" s="15" t="s">
+        <v>2923</v>
+      </c>
+      <c r="J137" s="2" t="s">
+        <v>2924</v>
+      </c>
+      <c r="K137" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="L137" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M137" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="N137" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="16" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="J5" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
     <hyperlink ref="I20" r:id="rId2" xr:uid="{00000000-0004-0000-0400-000001000000}"/>
@@ -25947,9 +26063,10 @@
     <hyperlink ref="I126" r:id="rId87" xr:uid="{D5217351-58DE-4063-B05F-2AAD973A6964}"/>
     <hyperlink ref="I127" r:id="rId88" xr:uid="{445CA2DB-DCDC-4D49-B3FC-95650287197F}"/>
     <hyperlink ref="I136" r:id="rId89" xr:uid="{4FA7D577-C2BC-4C3D-92A8-50A98BB0C15F}"/>
+    <hyperlink ref="J137" r:id="rId90" xr:uid="{270FAB0D-B47D-4805-A699-C4BB16679313}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId90"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId91"/>
 </worksheet>
 </file>
 

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2F8A1BE-3970-4568-BD7A-4D709525CAC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39849982-C04A-4265-AA5E-5CD885176695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5842" uniqueCount="2925">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5968" uniqueCount="2992">
   <si>
     <t>ID</t>
   </si>
@@ -8815,6 +8815,207 @@
   </si>
   <si>
     <t>https://www.mouser.es/ProductDetail/YAGEO/RC0603FR-7W10KL?qs=AQlKX63v8Ru%2F1n5uALWRmg%3D%3D</t>
+  </si>
+  <si>
+    <t>010-0137</t>
+  </si>
+  <si>
+    <t>Resistores de película gruesa - SMD 0.33W 10ohms 5% High Power AEC-Q200</t>
+  </si>
+  <si>
+    <t>71-CRCW060310R0JNEAH</t>
+  </si>
+  <si>
+    <t>https://www.vishay.com/docs/20043/crcwhpe3.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Vishay/CRCW060310R0JNEAHP?qs=k2%2FDWSARqgEB1LI%252BjPBTjg%3D%3D</t>
+  </si>
+  <si>
+    <t>010-0138</t>
+  </si>
+  <si>
+    <t>Resistores de película gruesa - SMD CRCW 603 4K00 0.01 100 ppm/K</t>
+  </si>
+  <si>
+    <t>CRCW06034K00FKTA</t>
+  </si>
+  <si>
+    <t>71-CRCW06034K00FKTA</t>
+  </si>
+  <si>
+    <t>https://www.vishay.com/docs/20008/dcrcw.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Vishay/CRCW06034K00FKTA?qs=WI1XYtAgnMkbyTUP7%2FnzOA%3D%3D</t>
+  </si>
+  <si>
+    <t>010-0139</t>
+  </si>
+  <si>
+    <t>Resistores de película fina - SMD 1/10W 50 Ohm 75V .1%</t>
+  </si>
+  <si>
+    <t>50Ω 100mW ±1%</t>
+  </si>
+  <si>
+    <t>RT0603BRE0750RL</t>
+  </si>
+  <si>
+    <t>603-RT0603BRE0750RL</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/datasheet/3/72/1/PYU_RT_1_TO_0_01_ROHS_L.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/YAGEO/RT0603BRE0750RL?qs=sGAEpiMZZMtlubZbdhIBINSnPd898yDPudX1JlFp2aw%3D</t>
+  </si>
+  <si>
+    <t>010-0140</t>
+  </si>
+  <si>
+    <t>Resistores de película gruesa - SMD 0603 330ohm 1% Anti-Surge AEC-Q200</t>
+  </si>
+  <si>
+    <t>330Ω 333mW ±1%</t>
+  </si>
+  <si>
+    <t>667-ERJ-PA3F3300V</t>
+  </si>
+  <si>
+    <t>https://industrial.panasonic.com/cdbs/www-data/pdf/RDO0000/RDO0000C334.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Panasonic/ERJ-PA3F3300V?qs=BzJM0faLVqV%252BdjJR48HqGQ%3D%3D</t>
+  </si>
+  <si>
+    <t>010-0141</t>
+  </si>
+  <si>
+    <t>Resistores de película gruesa - SMD 1.8 kOhms 1/10 W 75 V 5% 0603 100 PPM / C - 55 C / + 155 C AEC-Q200</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/datasheet/3/508/1/PYU_AC_51_ROHS_L.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/YAGEO/AC0603JR-071K8L?qs=ygRr%2Ftkhtesbqtk4RgJA%2FQ%3D%3D</t>
+  </si>
+  <si>
+    <t>603-AC0603JR-071K8L</t>
+  </si>
+  <si>
+    <t>AC0603JR-071K8L</t>
+  </si>
+  <si>
+    <t>LED de un solo color Green 525nm 1400mcd 2.85V 73deg 0603</t>
+  </si>
+  <si>
+    <t>VLMTG1400-GS08</t>
+  </si>
+  <si>
+    <t>78-VLMTG1400-GS08</t>
+  </si>
+  <si>
+    <t>https://www.vishay.com/docs/84393/vlmtg1400.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Vishay-Semiconductors/VLMTG1400-GS08?qs=gt1LBUVyoHlZ6yHd8iEIzQ%3D%3D</t>
+  </si>
+  <si>
+    <t>033-0014</t>
+  </si>
+  <si>
+    <t>033-0015</t>
+  </si>
+  <si>
+    <t>033-0016</t>
+  </si>
+  <si>
+    <t>033-0017</t>
+  </si>
+  <si>
+    <t>033-0018</t>
+  </si>
+  <si>
+    <t>033-0019</t>
+  </si>
+  <si>
+    <t>033-0020</t>
+  </si>
+  <si>
+    <t>033-0021</t>
+  </si>
+  <si>
+    <t>033-0022</t>
+  </si>
+  <si>
+    <t>033-0023</t>
+  </si>
+  <si>
+    <t>015-0003</t>
+  </si>
+  <si>
+    <t>Resistores de detección de corriente - SMD 3W 0.007ohm 1% 50ppm</t>
+  </si>
+  <si>
+    <t>7mΩ 3W ±1%</t>
+  </si>
+  <si>
+    <t>1225 (Reversed)</t>
+  </si>
+  <si>
+    <t>KRL6432E-M-R007-F-T1</t>
+  </si>
+  <si>
+    <t>Susumu</t>
+  </si>
+  <si>
+    <t>754-KRL6432EMR007FT1</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/datasheet/3/826/1/n_catalog_partition19_en.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Susumu/KRL6432E-M-R007-F-T1?qs=FG09h9tFCuA5fgBuyupdEw%3D%3D</t>
+  </si>
+  <si>
+    <t>RES SMD 1225 Reversed</t>
+  </si>
+  <si>
+    <t>001-0092</t>
+  </si>
+  <si>
+    <t>Condensadores de cerámica multicapa (MLCC- SMD/SMT) 16 V 0.1uF X7R 0603 10%</t>
+  </si>
+  <si>
+    <t>16V 0.1uF X7R</t>
+  </si>
+  <si>
+    <t>603-CC603KRX7R7BB104</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/datasheet/3/508/1/UPY_GPHC_X7R_6_3V_TO_250V.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/YAGEO/CC0603KRX7R7BB104?qs=AgBp2OyFlx8KPmNTlFoWXA%3D%3D</t>
+  </si>
+  <si>
+    <t>001-0093</t>
+  </si>
+  <si>
+    <t>Condensadores de cerámica multicapa (MLCC- SMD/SMT) 16V 1uF X7R 0603 10% HI CV</t>
+  </si>
+  <si>
+    <t>16V 1uF X7R</t>
+  </si>
+  <si>
+    <t>CC0603KRX7R7BB105</t>
+  </si>
+  <si>
+    <t>603-CC603KRX7R7BB105</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/YAGEO/CC0603KRX7R7BB105?qs=Z5EW3TBnpq2UUKiQ6CZTSQ%3D%3D</t>
   </si>
 </sst>
 </file>
@@ -8984,7 +9185,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -9035,6 +9236,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -9318,7 +9524,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N92"/>
+  <dimension ref="A1:N94"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="11.1796875" customWidth="1"/>
@@ -13382,7 +13588,96 @@
         <v>25</v>
       </c>
     </row>
+    <row r="93" spans="1:14">
+      <c r="A93" s="4" t="s">
+        <v>2980</v>
+      </c>
+      <c r="B93" s="32" t="s">
+        <v>2981</v>
+      </c>
+      <c r="C93" s="35" t="s">
+        <v>2982</v>
+      </c>
+      <c r="D93" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E93" t="s">
+        <v>304</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G93" s="32" t="s">
+        <v>2983</v>
+      </c>
+      <c r="H93" s="34" t="s">
+        <v>21</v>
+      </c>
+      <c r="I93" s="27" t="s">
+        <v>2984</v>
+      </c>
+      <c r="J93" s="27" t="s">
+        <v>2985</v>
+      </c>
+      <c r="K93" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="L93" t="s">
+        <v>61</v>
+      </c>
+      <c r="M93" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="N93" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14">
+      <c r="A94" s="4" t="s">
+        <v>2986</v>
+      </c>
+      <c r="B94" s="32" t="s">
+        <v>2987</v>
+      </c>
+      <c r="C94" s="35" t="s">
+        <v>2988</v>
+      </c>
+      <c r="D94" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E94" s="34" t="s">
+        <v>2989</v>
+      </c>
+      <c r="F94" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="G94" s="32" t="s">
+        <v>2990</v>
+      </c>
+      <c r="H94" s="34" t="s">
+        <v>21</v>
+      </c>
+      <c r="I94" s="27" t="s">
+        <v>2984</v>
+      </c>
+      <c r="J94" s="36" t="s">
+        <v>2991</v>
+      </c>
+      <c r="K94" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="L94" t="s">
+        <v>61</v>
+      </c>
+      <c r="M94" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="N94" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="16" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="I22" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="I23" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
@@ -13434,6 +13729,10 @@
     <hyperlink ref="I89" r:id="rId48" xr:uid="{54C8C95D-2C8A-4B14-B3F8-1B69A2587372}"/>
     <hyperlink ref="I82" r:id="rId49" xr:uid="{B234FDA3-9881-49C7-9757-E6B50F09E652}"/>
     <hyperlink ref="I92" r:id="rId50" xr:uid="{629DD39D-5539-4595-B551-7C70898E50E5}"/>
+    <hyperlink ref="I93" r:id="rId51" xr:uid="{C9324AD1-D443-4B4A-88F6-7342BEEBC444}"/>
+    <hyperlink ref="J93" r:id="rId52" xr:uid="{02ABAA1D-5CBA-4945-9449-F11890AA00C1}"/>
+    <hyperlink ref="I94" r:id="rId53" xr:uid="{CD066ABD-A9CF-4B23-B64F-6EFECB0682A9}"/>
+    <hyperlink ref="J94" r:id="rId54" xr:uid="{DE191AC8-7CDC-47D8-8778-80293EDB2FDD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -13441,7 +13740,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89BFA1EF-29B2-41E4-A9D1-F8E90A663FA1}">
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:14" ht="14.5" customHeight="1">
@@ -14062,7 +14361,7 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="7" t="s">
-        <v>2106</v>
+        <v>2960</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>2107</v>
@@ -14106,7 +14405,7 @@
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="7" t="s">
-        <v>2112</v>
+        <v>2961</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>2113</v>
@@ -14150,7 +14449,7 @@
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="7" t="s">
-        <v>2118</v>
+        <v>2962</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>2119</v>
@@ -14194,7 +14493,7 @@
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="7" t="s">
-        <v>2126</v>
+        <v>2963</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>2127</v>
@@ -14238,7 +14537,7 @@
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="7" t="s">
-        <v>2133</v>
+        <v>2964</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>2134</v>
@@ -14282,7 +14581,7 @@
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="7" t="s">
-        <v>2140</v>
+        <v>2965</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>2141</v>
@@ -14325,8 +14624,8 @@
       </c>
     </row>
     <row r="21" spans="1:14">
-      <c r="A21" s="16" t="s">
-        <v>2148</v>
+      <c r="A21" s="7" t="s">
+        <v>2966</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>2149</v>
@@ -14369,8 +14668,8 @@
       </c>
     </row>
     <row r="22" spans="1:14">
-      <c r="A22" s="16" t="s">
-        <v>2155</v>
+      <c r="A22" s="7" t="s">
+        <v>2967</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>2156</v>
@@ -14413,8 +14712,8 @@
       </c>
     </row>
     <row r="23" spans="1:14">
-      <c r="A23" s="16" t="s">
-        <v>2162</v>
+      <c r="A23" s="7" t="s">
+        <v>2968</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>2163</v>
@@ -14456,7 +14755,52 @@
         <v>25</v>
       </c>
     </row>
+    <row r="24" spans="1:14">
+      <c r="A24" s="7" t="s">
+        <v>2969</v>
+      </c>
+      <c r="B24" s="32" t="s">
+        <v>2955</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>2793</v>
+      </c>
+      <c r="D24" s="34" t="s">
+        <v>59</v>
+      </c>
+      <c r="E24" s="32" t="s">
+        <v>2956</v>
+      </c>
+      <c r="F24" s="32" t="s">
+        <v>1957</v>
+      </c>
+      <c r="G24" s="32" t="s">
+        <v>2957</v>
+      </c>
+      <c r="H24" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I24" t="s">
+        <v>2958</v>
+      </c>
+      <c r="J24" s="36" t="s">
+        <v>2959</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>2774</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>2877</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>2876</v>
+      </c>
+      <c r="N24" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="16" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="I15" r:id="rId1" xr:uid="{00000000-0004-0000-0A00-00000F000000}"/>
     <hyperlink ref="J15" r:id="rId2" xr:uid="{00000000-0004-0000-0A00-000010000000}"/>
@@ -14473,6 +14817,7 @@
     <hyperlink ref="J6" r:id="rId13" xr:uid="{00000000-0004-0000-0B00-000004000000}"/>
     <hyperlink ref="F7" r:id="rId14" xr:uid="{00000000-0004-0000-0B00-000005000000}"/>
     <hyperlink ref="I14" r:id="rId15" xr:uid="{BFE50862-7088-44B1-9DAF-F4C51270ACE8}"/>
+    <hyperlink ref="J24" r:id="rId16" xr:uid="{BA37FCF7-BBC9-434F-AC42-00AE241CF11E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -19936,7 +20281,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60E8291E-4293-4634-B9E9-80CB520CA181}">
-  <dimension ref="A1:N137"/>
+  <dimension ref="A1:N142"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="3" max="3" width="19.90625" customWidth="1"/>
@@ -25968,6 +26313,226 @@
         <v>57</v>
       </c>
       <c r="N137" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="138" spans="1:14">
+      <c r="A138" s="16" t="s">
+        <v>2925</v>
+      </c>
+      <c r="B138" s="7" t="s">
+        <v>2926</v>
+      </c>
+      <c r="C138" s="7" t="s">
+        <v>1185</v>
+      </c>
+      <c r="D138" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E138" s="7" t="s">
+        <v>1186</v>
+      </c>
+      <c r="F138" s="7" t="s">
+        <v>945</v>
+      </c>
+      <c r="G138" s="16" t="s">
+        <v>2927</v>
+      </c>
+      <c r="H138" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I138" s="7" t="s">
+        <v>2928</v>
+      </c>
+      <c r="J138" s="7" t="s">
+        <v>2929</v>
+      </c>
+      <c r="K138" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="L138" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M138" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="N138" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="139" spans="1:14">
+      <c r="A139" s="16" t="s">
+        <v>2930</v>
+      </c>
+      <c r="B139" s="33" t="s">
+        <v>2931</v>
+      </c>
+      <c r="C139" s="7" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D139" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E139" s="33" t="s">
+        <v>2932</v>
+      </c>
+      <c r="F139" s="7" t="s">
+        <v>945</v>
+      </c>
+      <c r="G139" s="34" t="s">
+        <v>2933</v>
+      </c>
+      <c r="H139" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I139" t="s">
+        <v>2934</v>
+      </c>
+      <c r="J139" t="s">
+        <v>2935</v>
+      </c>
+      <c r="K139" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="L139" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M139" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="N139" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="140" spans="1:14">
+      <c r="A140" s="16" t="s">
+        <v>2936</v>
+      </c>
+      <c r="B140" s="33" t="s">
+        <v>2937</v>
+      </c>
+      <c r="C140" s="7" t="s">
+        <v>2938</v>
+      </c>
+      <c r="D140" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E140" s="33" t="s">
+        <v>2939</v>
+      </c>
+      <c r="F140" s="33" t="s">
+        <v>60</v>
+      </c>
+      <c r="G140" s="34" t="s">
+        <v>2940</v>
+      </c>
+      <c r="H140" s="34" t="s">
+        <v>21</v>
+      </c>
+      <c r="I140" s="27" t="s">
+        <v>2941</v>
+      </c>
+      <c r="J140" s="27" t="s">
+        <v>2942</v>
+      </c>
+      <c r="K140" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="L140" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M140" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="N140" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="141" spans="1:14">
+      <c r="A141" s="16" t="s">
+        <v>2943</v>
+      </c>
+      <c r="B141" s="17" t="s">
+        <v>2944</v>
+      </c>
+      <c r="C141" s="3" t="s">
+        <v>2945</v>
+      </c>
+      <c r="D141" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E141" s="17" t="s">
+        <v>1566</v>
+      </c>
+      <c r="F141" s="17" t="s">
+        <v>1567</v>
+      </c>
+      <c r="G141" s="17" t="s">
+        <v>2946</v>
+      </c>
+      <c r="H141" s="34" t="s">
+        <v>21</v>
+      </c>
+      <c r="I141" s="18" t="s">
+        <v>2947</v>
+      </c>
+      <c r="J141" s="3" t="s">
+        <v>2948</v>
+      </c>
+      <c r="K141" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L141" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M141" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="N141" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="142" spans="1:14">
+      <c r="A142" s="16" t="s">
+        <v>2949</v>
+      </c>
+      <c r="B142" s="35" t="s">
+        <v>2950</v>
+      </c>
+      <c r="C142" s="17" t="s">
+        <v>1588</v>
+      </c>
+      <c r="D142" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E142" s="35" t="s">
+        <v>2954</v>
+      </c>
+      <c r="F142" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="G142" s="35" t="s">
+        <v>2953</v>
+      </c>
+      <c r="H142" s="34" t="s">
+        <v>21</v>
+      </c>
+      <c r="I142" t="s">
+        <v>2951</v>
+      </c>
+      <c r="J142" t="s">
+        <v>2952</v>
+      </c>
+      <c r="K142" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L142" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M142" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="N142" t="s">
         <v>25</v>
       </c>
     </row>
@@ -26064,15 +26629,17 @@
     <hyperlink ref="I127" r:id="rId88" xr:uid="{445CA2DB-DCDC-4D49-B3FC-95650287197F}"/>
     <hyperlink ref="I136" r:id="rId89" xr:uid="{4FA7D577-C2BC-4C3D-92A8-50A98BB0C15F}"/>
     <hyperlink ref="J137" r:id="rId90" xr:uid="{270FAB0D-B47D-4805-A699-C4BB16679313}"/>
+    <hyperlink ref="I140" r:id="rId91" xr:uid="{AF66F37C-DEF2-4C02-B09E-78216E8A0857}"/>
+    <hyperlink ref="J140" r:id="rId92" xr:uid="{5C7EACC9-1558-4F25-8631-38E695251F20}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId91"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId93"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81F9848D-6D60-47C0-9F84-A561FE4F106E}">
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="20.26953125" customWidth="1"/>
@@ -26210,11 +26777,58 @@
         <v>25</v>
       </c>
     </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>2970</v>
+      </c>
+      <c r="B4" t="s">
+        <v>2971</v>
+      </c>
+      <c r="C4" t="s">
+        <v>2972</v>
+      </c>
+      <c r="D4" t="s">
+        <v>2973</v>
+      </c>
+      <c r="E4" t="s">
+        <v>2974</v>
+      </c>
+      <c r="F4" t="s">
+        <v>2975</v>
+      </c>
+      <c r="G4" t="s">
+        <v>2976</v>
+      </c>
+      <c r="H4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>2977</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>2978</v>
+      </c>
+      <c r="K4" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M4" t="s">
+        <v>2979</v>
+      </c>
+      <c r="N4" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="16" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1" xr:uid="{9FEE5192-80A9-4D8D-B0ED-453C4A95B2F9}"/>
     <hyperlink ref="J2" r:id="rId2" xr:uid="{40967CA2-E6AE-4524-9EF5-66E92DD6A7B6}"/>
     <hyperlink ref="I3" r:id="rId3" xr:uid="{EDE33321-C187-4A8F-8366-9AEDB9FF4C7B}"/>
+    <hyperlink ref="I4" r:id="rId4" xr:uid="{DA619253-40A2-482C-A99F-F72A13182916}"/>
+    <hyperlink ref="J4" r:id="rId5" xr:uid="{65BF95D6-EB54-41F9-8886-7DFC774FFE44}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39849982-C04A-4265-AA5E-5CD885176695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FE21810-E363-458A-A80D-8A0528CE74F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" firstSheet="9" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -9185,7 +9185,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -9236,10 +9236,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
@@ -13592,10 +13588,10 @@
       <c r="A93" s="4" t="s">
         <v>2980</v>
       </c>
-      <c r="B93" s="32" t="s">
+      <c r="B93" s="3" t="s">
         <v>2981</v>
       </c>
-      <c r="C93" s="35" t="s">
+      <c r="C93" s="17" t="s">
         <v>2982</v>
       </c>
       <c r="D93" s="7" t="s">
@@ -13607,10 +13603,10 @@
       <c r="F93" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="G93" s="32" t="s">
+      <c r="G93" s="3" t="s">
         <v>2983</v>
       </c>
-      <c r="H93" s="34" t="s">
+      <c r="H93" s="16" t="s">
         <v>21</v>
       </c>
       <c r="I93" s="27" t="s">
@@ -13636,31 +13632,31 @@
       <c r="A94" s="4" t="s">
         <v>2986</v>
       </c>
-      <c r="B94" s="32" t="s">
+      <c r="B94" s="3" t="s">
         <v>2987</v>
       </c>
-      <c r="C94" s="35" t="s">
+      <c r="C94" s="17" t="s">
         <v>2988</v>
       </c>
       <c r="D94" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="E94" s="34" t="s">
+      <c r="E94" s="16" t="s">
         <v>2989</v>
       </c>
       <c r="F94" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="G94" s="32" t="s">
+      <c r="G94" s="3" t="s">
         <v>2990</v>
       </c>
-      <c r="H94" s="34" t="s">
+      <c r="H94" s="16" t="s">
         <v>21</v>
       </c>
       <c r="I94" s="27" t="s">
         <v>2984</v>
       </c>
-      <c r="J94" s="36" t="s">
+      <c r="J94" s="32" t="s">
         <v>2991</v>
       </c>
       <c r="K94" s="7" t="s">
@@ -14759,22 +14755,22 @@
       <c r="A24" s="7" t="s">
         <v>2969</v>
       </c>
-      <c r="B24" s="32" t="s">
+      <c r="B24" s="3" t="s">
         <v>2955</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>2793</v>
       </c>
-      <c r="D24" s="34" t="s">
+      <c r="D24" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="E24" s="32" t="s">
+      <c r="E24" s="3" t="s">
         <v>2956</v>
       </c>
-      <c r="F24" s="32" t="s">
+      <c r="F24" s="3" t="s">
         <v>1957</v>
       </c>
-      <c r="G24" s="32" t="s">
+      <c r="G24" s="3" t="s">
         <v>2957</v>
       </c>
       <c r="H24" s="16" t="s">
@@ -14783,7 +14779,7 @@
       <c r="I24" t="s">
         <v>2958</v>
       </c>
-      <c r="J24" s="36" t="s">
+      <c r="J24" s="32" t="s">
         <v>2959</v>
       </c>
       <c r="K24" s="7" t="s">
@@ -15890,7 +15886,7 @@
         <v>26</v>
       </c>
       <c r="M2" t="s">
-        <v>17</v>
+        <v>1651</v>
       </c>
       <c r="N2" t="s">
         <v>25</v>
@@ -26364,7 +26360,7 @@
       <c r="A139" s="16" t="s">
         <v>2930</v>
       </c>
-      <c r="B139" s="33" t="s">
+      <c r="B139" s="7" t="s">
         <v>2931</v>
       </c>
       <c r="C139" s="7" t="s">
@@ -26373,13 +26369,13 @@
       <c r="D139" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="E139" s="33" t="s">
+      <c r="E139" s="7" t="s">
         <v>2932</v>
       </c>
       <c r="F139" s="7" t="s">
         <v>945</v>
       </c>
-      <c r="G139" s="34" t="s">
+      <c r="G139" s="16" t="s">
         <v>2933</v>
       </c>
       <c r="H139" s="16" t="s">
@@ -26408,7 +26404,7 @@
       <c r="A140" s="16" t="s">
         <v>2936</v>
       </c>
-      <c r="B140" s="33" t="s">
+      <c r="B140" s="7" t="s">
         <v>2937</v>
       </c>
       <c r="C140" s="7" t="s">
@@ -26417,16 +26413,16 @@
       <c r="D140" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="E140" s="33" t="s">
+      <c r="E140" s="7" t="s">
         <v>2939</v>
       </c>
-      <c r="F140" s="33" t="s">
+      <c r="F140" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G140" s="34" t="s">
+      <c r="G140" s="16" t="s">
         <v>2940</v>
       </c>
-      <c r="H140" s="34" t="s">
+      <c r="H140" s="16" t="s">
         <v>21</v>
       </c>
       <c r="I140" s="27" t="s">
@@ -26470,7 +26466,7 @@
       <c r="G141" s="17" t="s">
         <v>2946</v>
       </c>
-      <c r="H141" s="34" t="s">
+      <c r="H141" s="16" t="s">
         <v>21</v>
       </c>
       <c r="I141" s="18" t="s">
@@ -26496,7 +26492,7 @@
       <c r="A142" s="16" t="s">
         <v>2949</v>
       </c>
-      <c r="B142" s="35" t="s">
+      <c r="B142" s="17" t="s">
         <v>2950</v>
       </c>
       <c r="C142" s="17" t="s">
@@ -26505,16 +26501,16 @@
       <c r="D142" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="E142" s="35" t="s">
+      <c r="E142" s="17" t="s">
         <v>2954</v>
       </c>
-      <c r="F142" s="35" t="s">
+      <c r="F142" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="G142" s="35" t="s">
+      <c r="G142" s="17" t="s">
         <v>2953</v>
       </c>
-      <c r="H142" s="34" t="s">
+      <c r="H142" s="16" t="s">
         <v>21</v>
       </c>
       <c r="I142" t="s">

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FE21810-E363-458A-A80D-8A0528CE74F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E00982A-7A9B-43D1-9B5B-4F76D30F1C8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" firstSheet="9" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5968" uniqueCount="2992">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5982" uniqueCount="3000">
   <si>
     <t>ID</t>
   </si>
@@ -9016,6 +9016,30 @@
   </si>
   <si>
     <t>https://www.mouser.es/ProductDetail/YAGEO/CC0603KRX7R7BB105?qs=Z5EW3TBnpq2UUKiQ6CZTSQ%3D%3D</t>
+  </si>
+  <si>
+    <t>https://www.vishay.com/docs/98847/ss20ph102.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Vishay-Semiconductors/SS20PH102HM3-I?qs=G4MbTVxgV4H1JubFDv9ZpA%3D%3D</t>
+  </si>
+  <si>
+    <t>031-0012</t>
+  </si>
+  <si>
+    <t>Diodos y rectificadores Schottky 20A,100VG2PSKYSMPCRect.</t>
+  </si>
+  <si>
+    <t>100V 20A</t>
+  </si>
+  <si>
+    <t>TO-277A-2</t>
+  </si>
+  <si>
+    <t>SS20PH102HM3/I</t>
+  </si>
+  <si>
+    <t>78-SS20PH102HM3/I</t>
   </si>
 </sst>
 </file>
@@ -9185,7 +9209,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -9237,6 +9261,9 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -27399,7 +27426,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FE2008B-4BF4-4C9A-883A-FEE5873AEAF4}">
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:14" ht="16" customHeight="1">
@@ -27930,7 +27957,52 @@
         <v>25</v>
       </c>
     </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="16" t="s">
+        <v>2994</v>
+      </c>
+      <c r="B13" s="33" t="s">
+        <v>2995</v>
+      </c>
+      <c r="C13" s="34" t="s">
+        <v>2996</v>
+      </c>
+      <c r="D13" s="33" t="s">
+        <v>2997</v>
+      </c>
+      <c r="E13" s="35" t="s">
+        <v>2998</v>
+      </c>
+      <c r="F13" s="17" t="s">
+        <v>1957</v>
+      </c>
+      <c r="G13" s="35" t="s">
+        <v>2999</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I13" t="s">
+        <v>2993</v>
+      </c>
+      <c r="J13" s="27" t="s">
+        <v>2992</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>1943</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>1994</v>
+      </c>
+      <c r="N13" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="16" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="I3" r:id="rId1" xr:uid="{00000000-0004-0000-0900-000000000000}"/>
     <hyperlink ref="I5" r:id="rId2" xr:uid="{00000000-0004-0000-0900-000001000000}"/>
@@ -27943,6 +28015,7 @@
     <hyperlink ref="I10" r:id="rId9" xr:uid="{43EA2952-ABB5-4F52-94F7-A96F82DE8560}"/>
     <hyperlink ref="I11" r:id="rId10" xr:uid="{E8167B89-7FBA-4877-BC25-3D4C05ED8AA6}"/>
     <hyperlink ref="I12" r:id="rId11" xr:uid="{C4B46D5B-BD3F-4DBC-A61E-40C494B3D177}"/>
+    <hyperlink ref="J13" r:id="rId12" xr:uid="{0C7D58F5-DE06-4F14-BC9F-F6688DDA76B4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E00982A-7A9B-43D1-9B5B-4F76D30F1C8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23C7232B-EA9B-4151-B2E2-AE258260E822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5982" uniqueCount="3000">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6024" uniqueCount="3019">
   <si>
     <t>ID</t>
   </si>
@@ -9040,6 +9040,63 @@
   </si>
   <si>
     <t>78-SS20PH102HM3/I</t>
+  </si>
+  <si>
+    <t>001-0094</t>
+  </si>
+  <si>
+    <t>001-0095</t>
+  </si>
+  <si>
+    <t>001-0096</t>
+  </si>
+  <si>
+    <t>Condensadores de cerámica multicapa (MLCC- SMD/SMT) Automotive MLCC 1uF, 10%, X7R, 50VDC</t>
+  </si>
+  <si>
+    <t>KAM21KR71H105KL</t>
+  </si>
+  <si>
+    <t>KYOCERA AVX</t>
+  </si>
+  <si>
+    <t>https://ele.kyocera.com/assets/products/capacitor/KGM_Series_e.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/KYOCERA-AVX/KAM21KR71H105KL?qs=Jm2GQyTW%2FbhahfzttUK9QA%3D%3D</t>
+  </si>
+  <si>
+    <t>Condensadores de cerámica multicapa (MLCC- SMD/SMT) 50V 10uF X7R 1210 10 % AEC-Q200</t>
+  </si>
+  <si>
+    <t>50V 10uF X7R</t>
+  </si>
+  <si>
+    <t>KAM32LR71H106KL</t>
+  </si>
+  <si>
+    <t>581-KAM32LR71H106KL</t>
+  </si>
+  <si>
+    <t>581-KAM21KR71H105KL</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/KYOCERA-AVX/KAM32LR71H106KL?qs=sGAEpiMZZMuMW9TJLBQkXqLYvz3DzaXf%2FdVWcOcJzto%3D</t>
+  </si>
+  <si>
+    <t>KAM21BR71H104JM</t>
+  </si>
+  <si>
+    <t>Condensadores de cerámica multicapa (MLCC- SMD/SMT) 50V 0.1uF X7R 0805 5% AEC-Q200</t>
+  </si>
+  <si>
+    <t>50V 0.1uF X7R</t>
+  </si>
+  <si>
+    <t>581-KAM21BR71H104JM</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/KYOCERA-AVX/KAM21BR71H104JM?qs=sGAEpiMZZMuMW9TJLBQkXqLYvz3DzaXfcS9olcxY6vM%3D</t>
   </si>
 </sst>
 </file>
@@ -9209,7 +9266,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -9262,8 +9319,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -9547,7 +9605,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N94"/>
+  <dimension ref="A1:N97"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="11.1796875" customWidth="1"/>
@@ -13696,6 +13754,138 @@
         <v>62</v>
       </c>
       <c r="N94" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14">
+      <c r="A95" s="4" t="s">
+        <v>3000</v>
+      </c>
+      <c r="B95" t="s">
+        <v>3003</v>
+      </c>
+      <c r="C95" s="34" t="s">
+        <v>443</v>
+      </c>
+      <c r="D95" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="E95" s="35" t="s">
+        <v>3004</v>
+      </c>
+      <c r="F95" s="36" t="s">
+        <v>3005</v>
+      </c>
+      <c r="G95" s="33" t="s">
+        <v>3012</v>
+      </c>
+      <c r="H95" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I95" s="27" t="s">
+        <v>3006</v>
+      </c>
+      <c r="J95" s="32" t="s">
+        <v>3007</v>
+      </c>
+      <c r="K95" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="L95" t="s">
+        <v>61</v>
+      </c>
+      <c r="M95" s="7" t="s">
+        <v>700</v>
+      </c>
+      <c r="N95" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14">
+      <c r="A96" s="4" t="s">
+        <v>3001</v>
+      </c>
+      <c r="B96" t="s">
+        <v>3008</v>
+      </c>
+      <c r="C96" s="34" t="s">
+        <v>3009</v>
+      </c>
+      <c r="D96" s="13" t="s">
+        <v>520</v>
+      </c>
+      <c r="E96" s="35" t="s">
+        <v>3010</v>
+      </c>
+      <c r="F96" s="33" t="s">
+        <v>3005</v>
+      </c>
+      <c r="G96" s="33" t="s">
+        <v>3011</v>
+      </c>
+      <c r="H96" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I96" s="27" t="s">
+        <v>3006</v>
+      </c>
+      <c r="J96" s="32" t="s">
+        <v>3013</v>
+      </c>
+      <c r="K96" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="L96" t="s">
+        <v>61</v>
+      </c>
+      <c r="M96" s="7" t="s">
+        <v>702</v>
+      </c>
+      <c r="N96" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14">
+      <c r="A97" s="4" t="s">
+        <v>3002</v>
+      </c>
+      <c r="B97" t="s">
+        <v>3015</v>
+      </c>
+      <c r="C97" s="34" t="s">
+        <v>3016</v>
+      </c>
+      <c r="D97" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="E97" s="35" t="s">
+        <v>3014</v>
+      </c>
+      <c r="F97" s="33" t="s">
+        <v>3005</v>
+      </c>
+      <c r="G97" s="33" t="s">
+        <v>3017</v>
+      </c>
+      <c r="H97" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I97" s="27" t="s">
+        <v>3006</v>
+      </c>
+      <c r="J97" t="s">
+        <v>3018</v>
+      </c>
+      <c r="K97" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="L97" t="s">
+        <v>61</v>
+      </c>
+      <c r="M97" s="7" t="s">
+        <v>700</v>
+      </c>
+      <c r="N97" t="s">
         <v>25</v>
       </c>
     </row>
@@ -13756,6 +13946,11 @@
     <hyperlink ref="J93" r:id="rId52" xr:uid="{02ABAA1D-5CBA-4945-9449-F11890AA00C1}"/>
     <hyperlink ref="I94" r:id="rId53" xr:uid="{CD066ABD-A9CF-4B23-B64F-6EFECB0682A9}"/>
     <hyperlink ref="J94" r:id="rId54" xr:uid="{DE191AC8-7CDC-47D8-8778-80293EDB2FDD}"/>
+    <hyperlink ref="I95" r:id="rId55" xr:uid="{CCA8EE89-F6B4-4DE6-8266-D2E2C7A801D9}"/>
+    <hyperlink ref="J95" r:id="rId56" xr:uid="{3EA9C5B0-8F07-472C-B534-F158D1D13832}"/>
+    <hyperlink ref="I96" r:id="rId57" xr:uid="{84DAD3FB-EB5D-446A-B122-0A99A60B6E95}"/>
+    <hyperlink ref="J96" r:id="rId58" xr:uid="{44B094DB-343C-49F4-A023-566CEE808AE0}"/>
+    <hyperlink ref="I97" r:id="rId59" xr:uid="{890D1BEC-53E9-4E41-AB45-508A74C3ACB5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -27961,22 +28156,22 @@
       <c r="A13" s="16" t="s">
         <v>2994</v>
       </c>
-      <c r="B13" s="33" t="s">
+      <c r="B13" s="3" t="s">
         <v>2995</v>
       </c>
-      <c r="C13" s="34" t="s">
+      <c r="C13" s="7" t="s">
         <v>2996</v>
       </c>
-      <c r="D13" s="33" t="s">
+      <c r="D13" s="3" t="s">
         <v>2997</v>
       </c>
-      <c r="E13" s="35" t="s">
+      <c r="E13" s="17" t="s">
         <v>2998</v>
       </c>
       <c r="F13" s="17" t="s">
         <v>1957</v>
       </c>
-      <c r="G13" s="35" t="s">
+      <c r="G13" s="17" t="s">
         <v>2999</v>
       </c>
       <c r="H13" s="7" t="s">

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23C7232B-EA9B-4151-B2E2-AE258260E822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA048F51-603F-42CB-A2A5-5560BB4F2097}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32280" yWindow="2235" windowWidth="29040" windowHeight="15720" firstSheet="9" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,9 @@
     <sheet name="050 - ICs - Analog" sheetId="2" r:id="rId12"/>
     <sheet name="060 - ICs - Digital" sheetId="3" r:id="rId13"/>
     <sheet name="070 - Power Supply - DCDC" sheetId="8" r:id="rId14"/>
-    <sheet name="100 - Electromechanicals" sheetId="15" r:id="rId15"/>
-    <sheet name="110 - Connectors" sheetId="13" r:id="rId16"/>
+    <sheet name="90 - Processor" sheetId="18" r:id="rId15"/>
+    <sheet name="100 - Electromechanicals" sheetId="15" r:id="rId16"/>
+    <sheet name="110 - Connectors" sheetId="13" r:id="rId17"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6024" uniqueCount="3019">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6053" uniqueCount="3028">
   <si>
     <t>ID</t>
   </si>
@@ -9097,6 +9098,33 @@
   </si>
   <si>
     <t>https://www.mouser.es/ProductDetail/KYOCERA-AVX/KAM21BR71H104JM?qs=sGAEpiMZZMuMW9TJLBQkXqLYvz3DzaXfcS9olcxY6vM%3D</t>
+  </si>
+  <si>
+    <t>Part</t>
+  </si>
+  <si>
+    <t>090-0001</t>
+  </si>
+  <si>
+    <t>Microcontroladores ARM (MCU) Mainstream Arm Cortex-M4 MCU 170 MHz 128 Kbytes of Flash Math Accel, HR Timer, H</t>
+  </si>
+  <si>
+    <t>LQFP-64</t>
+  </si>
+  <si>
+    <t>STM32G474RBT3</t>
+  </si>
+  <si>
+    <t>511-STM32G474RBT3</t>
+  </si>
+  <si>
+    <t>https://www.st.com/resource/en/datasheet/stm32g474cb.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/STMicroelectronics/STM32G474RBT3?qs=uwxL4vQweFM8LrM8Y%252BrfIg%3D%3D</t>
+  </si>
+  <si>
+    <t>eUSR_SchLibrary/eUSR_SchLibrary - Procesor.SchLib</t>
   </si>
 </sst>
 </file>
@@ -9266,7 +9294,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -9318,10 +9346,9 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -13764,19 +13791,19 @@
       <c r="B95" t="s">
         <v>3003</v>
       </c>
-      <c r="C95" s="34" t="s">
+      <c r="C95" s="17" t="s">
         <v>443</v>
       </c>
       <c r="D95" s="13" t="s">
         <v>240</v>
       </c>
-      <c r="E95" s="35" t="s">
+      <c r="E95" s="16" t="s">
         <v>3004</v>
       </c>
-      <c r="F95" s="36" t="s">
+      <c r="F95" s="31" t="s">
         <v>3005</v>
       </c>
-      <c r="G95" s="33" t="s">
+      <c r="G95" s="3" t="s">
         <v>3012</v>
       </c>
       <c r="H95" s="16" t="s">
@@ -13808,19 +13835,19 @@
       <c r="B96" t="s">
         <v>3008</v>
       </c>
-      <c r="C96" s="34" t="s">
+      <c r="C96" s="17" t="s">
         <v>3009</v>
       </c>
       <c r="D96" s="13" t="s">
         <v>520</v>
       </c>
-      <c r="E96" s="35" t="s">
+      <c r="E96" s="16" t="s">
         <v>3010</v>
       </c>
-      <c r="F96" s="33" t="s">
+      <c r="F96" s="3" t="s">
         <v>3005</v>
       </c>
-      <c r="G96" s="33" t="s">
+      <c r="G96" s="3" t="s">
         <v>3011</v>
       </c>
       <c r="H96" s="16" t="s">
@@ -13852,19 +13879,19 @@
       <c r="B97" t="s">
         <v>3015</v>
       </c>
-      <c r="C97" s="34" t="s">
+      <c r="C97" s="17" t="s">
         <v>3016</v>
       </c>
       <c r="D97" s="13" t="s">
         <v>240</v>
       </c>
-      <c r="E97" s="35" t="s">
+      <c r="E97" s="16" t="s">
         <v>3014</v>
       </c>
-      <c r="F97" s="33" t="s">
+      <c r="F97" s="3" t="s">
         <v>3005</v>
       </c>
-      <c r="G97" s="33" t="s">
+      <c r="G97" s="3" t="s">
         <v>3017</v>
       </c>
       <c r="H97" s="16" t="s">
@@ -16509,6 +16536,114 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E9EB2F5-2977-493B-BFA2-5CD20F8A3BC4}">
+  <dimension ref="A1:O2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetData>
+    <row r="1" spans="1:15">
+      <c r="A1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="33" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="33" t="s">
+        <v>3019</v>
+      </c>
+      <c r="I1" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="33" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2" t="s">
+        <v>3020</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3021</v>
+      </c>
+      <c r="C2">
+        <v>64</v>
+      </c>
+      <c r="D2" t="s">
+        <v>3022</v>
+      </c>
+      <c r="E2" t="s">
+        <v>3023</v>
+      </c>
+      <c r="F2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2" t="s">
+        <v>3024</v>
+      </c>
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>3023</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>3025</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>3026</v>
+      </c>
+      <c r="L2" t="s">
+        <v>3023</v>
+      </c>
+      <c r="M2" t="s">
+        <v>3027</v>
+      </c>
+      <c r="N2" t="s">
+        <v>3022</v>
+      </c>
+      <c r="O2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="J2" r:id="rId1" xr:uid="{F8A04A1C-92B7-4CCD-8C95-726A110347D5}"/>
+    <hyperlink ref="K2" r:id="rId2" xr:uid="{2F912663-1CD4-41BE-AE9B-6D2CA04D31B2}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69A1C46E-DEF3-467B-A5BD-162AB66E6A86}">
   <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -17591,7 +17726,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE14AD29-8DB0-4C42-AB91-A73B867AE121}">
   <dimension ref="A1:N62"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA048F51-603F-42CB-A2A5-5560BB4F2097}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A16833DF-A976-4E90-A359-833F84CE823C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32280" yWindow="2235" windowWidth="29040" windowHeight="15720" firstSheet="9" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3600" yWindow="4060" windowWidth="16200" windowHeight="9980" firstSheet="14" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
     <sheet name="050 - ICs - Analog" sheetId="2" r:id="rId12"/>
     <sheet name="060 - ICs - Digital" sheetId="3" r:id="rId13"/>
     <sheet name="070 - Power Supply - DCDC" sheetId="8" r:id="rId14"/>
-    <sheet name="90 - Processor" sheetId="18" r:id="rId15"/>
+    <sheet name="090 - Processor" sheetId="18" r:id="rId15"/>
     <sheet name="100 - Electromechanicals" sheetId="15" r:id="rId16"/>
     <sheet name="110 - Connectors" sheetId="13" r:id="rId17"/>
   </sheets>
@@ -9124,7 +9124,7 @@
     <t>https://www.mouser.es/ProductDetail/STMicroelectronics/STM32G474RBT3?qs=uwxL4vQweFM8LrM8Y%252BrfIg%3D%3D</t>
   </si>
   <si>
-    <t>eUSR_SchLibrary/eUSR_SchLibrary - Procesor.SchLib</t>
+    <t>eUSR_SchLibrary/eUSR_SchLibrary - Processor.SchLib</t>
   </si>
 </sst>
 </file>
@@ -16613,7 +16613,7 @@
         <v>16</v>
       </c>
       <c r="I2" t="s">
-        <v>3023</v>
+        <v>21</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>3025</v>

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A16833DF-A976-4E90-A359-833F84CE823C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AE5D07E-7296-4042-807A-7E55C6420D31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3600" yWindow="4060" windowWidth="16200" windowHeight="9980" firstSheet="14" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" firstSheet="10" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -24,12 +24,13 @@
     <sheet name="032 - Diode - TVS" sheetId="14" r:id="rId9"/>
     <sheet name="033 - Diode - LED" sheetId="12" r:id="rId10"/>
     <sheet name="040 - Fuses" sheetId="10" r:id="rId11"/>
-    <sheet name="050 - ICs - Analog" sheetId="2" r:id="rId12"/>
-    <sheet name="060 - ICs - Digital" sheetId="3" r:id="rId13"/>
-    <sheet name="070 - Power Supply - DCDC" sheetId="8" r:id="rId14"/>
-    <sheet name="090 - Processor" sheetId="18" r:id="rId15"/>
-    <sheet name="100 - Electromechanicals" sheetId="15" r:id="rId16"/>
-    <sheet name="110 - Connectors" sheetId="13" r:id="rId17"/>
+    <sheet name="045 - Crystal" sheetId="19" r:id="rId12"/>
+    <sheet name="050 - ICs - Analog" sheetId="2" r:id="rId13"/>
+    <sheet name="060 - ICs - Digital" sheetId="3" r:id="rId14"/>
+    <sheet name="070 - Power Supply - DCDC" sheetId="8" r:id="rId15"/>
+    <sheet name="090 - Processor" sheetId="18" r:id="rId16"/>
+    <sheet name="100 - Electromechanicals" sheetId="15" r:id="rId17"/>
+    <sheet name="110 - Connectors" sheetId="13" r:id="rId18"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6053" uniqueCount="3028">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6081" uniqueCount="3039">
   <si>
     <t>ID</t>
   </si>
@@ -9125,6 +9126,39 @@
   </si>
   <si>
     <t>eUSR_SchLibrary/eUSR_SchLibrary - Processor.SchLib</t>
+  </si>
+  <si>
+    <t>eUSR_SchLibrary/eUSR_SchLibrary - Crystal.SchLib</t>
+  </si>
+  <si>
+    <t>XTAL</t>
+  </si>
+  <si>
+    <t>045-0001</t>
+  </si>
+  <si>
+    <t>Cristales CRYSTAL 32.768KHZ 12.5PF SMD</t>
+  </si>
+  <si>
+    <t>32.768K</t>
+  </si>
+  <si>
+    <t>SMD3215-2P</t>
+  </si>
+  <si>
+    <t>STDMUA8-32.768K</t>
+  </si>
+  <si>
+    <t>NDK</t>
+  </si>
+  <si>
+    <t>344-NX3215SA32768K8</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/datasheet/3/1591/1/c_NX3215SA_e.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/NDK/STDMUA8-32.768K?qs=Tc%252BHE9vUsnvUQACJk1V1jw%3D%3D</t>
   </si>
 </sst>
 </file>
@@ -9294,7 +9328,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -9349,6 +9383,7 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -16038,6 +16073,108 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E5535EA-E186-4751-BC7F-9B3A0221302E}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="33" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="33" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
+        <v>3030</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3031</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3032</v>
+      </c>
+      <c r="D2" t="s">
+        <v>3033</v>
+      </c>
+      <c r="E2" t="s">
+        <v>3034</v>
+      </c>
+      <c r="F2" t="s">
+        <v>3035</v>
+      </c>
+      <c r="G2" t="s">
+        <v>3036</v>
+      </c>
+      <c r="H2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>3037</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>3038</v>
+      </c>
+      <c r="K2" s="34" t="s">
+        <v>3029</v>
+      </c>
+      <c r="L2" s="34" t="s">
+        <v>3028</v>
+      </c>
+      <c r="M2" t="s">
+        <v>3033</v>
+      </c>
+      <c r="N2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="I2" r:id="rId1" xr:uid="{337695E5-83C1-4E9C-B69D-3A199335F765}"/>
+    <hyperlink ref="J2" r:id="rId2" xr:uid="{F85761B8-F34F-4D64-BCF0-0EBE497625FF}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C98E1A12-072F-4773-8CB5-47FFE077E85B}">
   <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -16287,7 +16424,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59BC8B2E-A067-463D-937A-30E88D8BECD0}">
   <dimension ref="A1:N1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -16341,7 +16478,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4BBBCF5-BAC9-459C-ABE9-2526B85FD81E}">
   <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -16535,7 +16672,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E9EB2F5-2977-493B-BFA2-5CD20F8A3BC4}">
   <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -16643,7 +16780,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69A1C46E-DEF3-467B-A5BD-162AB66E6A86}">
   <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -17726,7 +17863,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE14AD29-8DB0-4C42-AB91-A73B867AE121}">
   <dimension ref="A1:N62"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AE5D07E-7296-4042-807A-7E55C6420D31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F22F469-B048-42F6-8D06-3B2211C6DD2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" firstSheet="10" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10710" yWindow="0" windowWidth="10980" windowHeight="13770" firstSheet="10" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6081" uniqueCount="3039">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6095" uniqueCount="3050">
   <si>
     <t>ID</t>
   </si>
@@ -9159,6 +9159,39 @@
   </si>
   <si>
     <t>https://www.mouser.es/ProductDetail/NDK/STDMUA8-32.768K?qs=Tc%252BHE9vUsnvUQACJk1V1jw%3D%3D</t>
+  </si>
+  <si>
+    <t>045-0002</t>
+  </si>
+  <si>
+    <t>Cristales CRYSTAL 8.0000MHZ 10PF SMD,ECX-32,10ppm,25ppm,400 Ohm,Fundamental,-40C - 85C,4-SMD, No Lead (DFN, LCC),0.126" L x 0.098" W (3.20mm x 2.50mm),0.031" (0.80mm)</t>
+  </si>
+  <si>
+    <t>8M</t>
+  </si>
+  <si>
+    <t>SMD3225</t>
+  </si>
+  <si>
+    <t>ECS-80-10-33-CHN-TR</t>
+  </si>
+  <si>
+    <t>ECS</t>
+  </si>
+  <si>
+    <t>520-ECS-80-1033CHNTR</t>
+  </si>
+  <si>
+    <t>https://www.ecsxtal.com/store/pdf/ecx-32.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/ECS/ECS-80-10-33-CHN-TR?qs=W%2FMpXkg%252BdQ6xEmLXccABKw%3D%3D</t>
+  </si>
+  <si>
+    <t>XTAL-4</t>
+  </si>
+  <si>
+    <t>SMD3225-4P</t>
   </si>
 </sst>
 </file>
@@ -9328,7 +9361,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -9384,6 +9417,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -16074,7 +16108,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E5535EA-E186-4751-BC7F-9B3A0221302E}">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:14">
@@ -16165,10 +16199,57 @@
         <v>25</v>
       </c>
     </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>3039</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3040</v>
+      </c>
+      <c r="C3" t="s">
+        <v>3041</v>
+      </c>
+      <c r="D3" t="s">
+        <v>3042</v>
+      </c>
+      <c r="E3" t="s">
+        <v>3043</v>
+      </c>
+      <c r="F3" t="s">
+        <v>3044</v>
+      </c>
+      <c r="G3" t="s">
+        <v>3045</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>3046</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>3047</v>
+      </c>
+      <c r="K3" s="35" t="s">
+        <v>3048</v>
+      </c>
+      <c r="L3" s="34" t="s">
+        <v>3028</v>
+      </c>
+      <c r="M3" s="35" t="s">
+        <v>3049</v>
+      </c>
+      <c r="N3" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="16" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1" xr:uid="{337695E5-83C1-4E9C-B69D-3A199335F765}"/>
     <hyperlink ref="J2" r:id="rId2" xr:uid="{F85761B8-F34F-4D64-BCF0-0EBE497625FF}"/>
+    <hyperlink ref="I3" r:id="rId3" xr:uid="{EFA9B72D-AA85-4A7F-BEAB-0C32D0D7AFB6}"/>
+    <hyperlink ref="J3" r:id="rId4" xr:uid="{9AAC4BF1-BF42-49D3-8F54-7A0BC590848A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F22F469-B048-42F6-8D06-3B2211C6DD2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{774D670F-F1D6-4AB3-A5EB-F0ABEB79F458}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10710" yWindow="0" windowWidth="10980" windowHeight="13770" firstSheet="10" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32295" yWindow="2355" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6095" uniqueCount="3050">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6207" uniqueCount="3102">
   <si>
     <t>ID</t>
   </si>
@@ -9192,6 +9192,162 @@
   </si>
   <si>
     <t>SMD3225-4P</t>
+  </si>
+  <si>
+    <t>001-0097</t>
+  </si>
+  <si>
+    <t>Condensadores de cerámica multicapa (MLCC- SMD/SMT) WCAP-CSGP 1.5pF 0402 0.5pF TOL 16V</t>
+  </si>
+  <si>
+    <t>16V 1.5pF C0G</t>
+  </si>
+  <si>
+    <t>710-885012005020</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/885012005020.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/885012005020?qs=0KOYDY2FL2%2FpnGt3CBSzcg%3D%3D</t>
+  </si>
+  <si>
+    <t>001-0098</t>
+  </si>
+  <si>
+    <t>001-0099</t>
+  </si>
+  <si>
+    <t>001-0100</t>
+  </si>
+  <si>
+    <t>001-0101</t>
+  </si>
+  <si>
+    <t>Condensadores de cerámica multicapa (MLCC- SMD/SMT) WCAP-CSGP 10pF 0402 5% 16V MLCC</t>
+  </si>
+  <si>
+    <t>16V 10pF C0G</t>
+  </si>
+  <si>
+    <t>710-885012005025</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/885012005025.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/885012005025?qs=0KOYDY2FL2%2F1u5tcR38OjQ%3D%3D</t>
+  </si>
+  <si>
+    <t>Condensadores de cerámica multicapa (MLCC- SMD/SMT) WCAP-CSGP 0.1uF 0402 20% 16V MLCC</t>
+  </si>
+  <si>
+    <t>16V 0.1uF X5R</t>
+  </si>
+  <si>
+    <t>710-885012105016</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/885012105016.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/885012105016?qs=0KOYDY2FL2%2FPbpf70bBQeA%3D%3D</t>
+  </si>
+  <si>
+    <t>Condensadores de cerámica multicapa (MLCC- SMD/SMT) WCAP-CSGP 0.1uF 0805 10% 50V MLCC</t>
+  </si>
+  <si>
+    <t>710-885012207098</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/885012207098?qs=0KOYDY2FL29sZCNyRsrK9g%3D%3D</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/885012207098.pdf</t>
+  </si>
+  <si>
+    <t>Condensadores de cerámica multicapa (MLCC- SMD/SMT) WCAP-CSGP 0.01uF 0402 10% 16V MLCC</t>
+  </si>
+  <si>
+    <t>001-0102</t>
+  </si>
+  <si>
+    <t>16V 10nF X5R</t>
+  </si>
+  <si>
+    <t>710-885012205031</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/885012205031.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/885012205031?qs=0KOYDY2FL28GOkIyNosgaQ%3D%3D</t>
+  </si>
+  <si>
+    <t>Condensadores de cerámica multicapa (MLCC- SMD/SMT) WCAP-CSGP 1uF 50 Vol 10%</t>
+  </si>
+  <si>
+    <t>885012005020</t>
+  </si>
+  <si>
+    <t>885012105016</t>
+  </si>
+  <si>
+    <t>885012005025</t>
+  </si>
+  <si>
+    <t>885012207098</t>
+  </si>
+  <si>
+    <t>885012205031</t>
+  </si>
+  <si>
+    <t>885012206126</t>
+  </si>
+  <si>
+    <t>710-885012206126</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/885012206126.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/885012206126?qs=amGC7iS6iy%2F%252BJOLb%2FSuwig%3D%3D</t>
+  </si>
+  <si>
+    <t>Condensadores de cerámica multicapa (MLCC- SMD/SMT) WCAP-CSGP 1uF 0402 20% 10V MLCC</t>
+  </si>
+  <si>
+    <t>001-0103</t>
+  </si>
+  <si>
+    <t>885012105012</t>
+  </si>
+  <si>
+    <t>710-885012105012</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/885012105012.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/885012105012?qs=0KOYDY2FL28qr2YJ9j3qRw%3D%3D</t>
+  </si>
+  <si>
+    <t>001-0104</t>
+  </si>
+  <si>
+    <t>Condensadores de cerámica multicapa (MLCC- SMD/SMT) WCAP-CSGP 10uF 50Vol 0.1</t>
+  </si>
+  <si>
+    <t>885012209073</t>
+  </si>
+  <si>
+    <t>710-885012209073</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/885012209073.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/885012209073?qs=sPbYRqrBIVm8PsM2ljQIMg%3D%3D</t>
   </si>
 </sst>
 </file>
@@ -9361,7 +9517,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -9418,6 +9574,10 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -9701,13 +9861,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N97"/>
+  <dimension ref="A1:N105"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="11.1796875" customWidth="1"/>
     <col min="2" max="2" width="29.6328125" customWidth="1"/>
     <col min="3" max="3" width="14.90625" customWidth="1"/>
     <col min="4" max="4" width="8.81640625" customWidth="1"/>
+    <col min="5" max="5" width="12.453125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.6328125" customWidth="1"/>
     <col min="7" max="7" width="15.453125" customWidth="1"/>
     <col min="8" max="8" width="12.453125" customWidth="1"/>
@@ -13982,6 +14143,358 @@
         <v>700</v>
       </c>
       <c r="N97" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14">
+      <c r="A98" s="4" t="s">
+        <v>3050</v>
+      </c>
+      <c r="B98" t="s">
+        <v>3051</v>
+      </c>
+      <c r="C98" s="37" t="s">
+        <v>3052</v>
+      </c>
+      <c r="D98" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="E98" s="38" t="s">
+        <v>3081</v>
+      </c>
+      <c r="F98" s="36" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G98" s="36" t="s">
+        <v>3053</v>
+      </c>
+      <c r="H98" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I98" s="27" t="s">
+        <v>3054</v>
+      </c>
+      <c r="J98" t="s">
+        <v>3055</v>
+      </c>
+      <c r="K98" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="L98" t="s">
+        <v>61</v>
+      </c>
+      <c r="M98" s="7" t="s">
+        <v>698</v>
+      </c>
+      <c r="N98" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14">
+      <c r="A99" s="4" t="s">
+        <v>3056</v>
+      </c>
+      <c r="B99" t="s">
+        <v>3060</v>
+      </c>
+      <c r="C99" s="37" t="s">
+        <v>3061</v>
+      </c>
+      <c r="D99" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="E99" s="38" t="s">
+        <v>3083</v>
+      </c>
+      <c r="F99" s="36" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G99" s="36" t="s">
+        <v>3062</v>
+      </c>
+      <c r="H99" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I99" s="27" t="s">
+        <v>3063</v>
+      </c>
+      <c r="J99" s="27" t="s">
+        <v>3064</v>
+      </c>
+      <c r="K99" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="L99" t="s">
+        <v>61</v>
+      </c>
+      <c r="M99" s="7" t="s">
+        <v>698</v>
+      </c>
+      <c r="N99" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14">
+      <c r="A100" s="4" t="s">
+        <v>3057</v>
+      </c>
+      <c r="B100" t="s">
+        <v>3065</v>
+      </c>
+      <c r="C100" s="37" t="s">
+        <v>3066</v>
+      </c>
+      <c r="D100" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="E100" s="38" t="s">
+        <v>3082</v>
+      </c>
+      <c r="F100" s="36" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G100" t="s">
+        <v>3067</v>
+      </c>
+      <c r="H100" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I100" t="s">
+        <v>3068</v>
+      </c>
+      <c r="J100" s="2" t="s">
+        <v>3069</v>
+      </c>
+      <c r="K100" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="L100" t="s">
+        <v>61</v>
+      </c>
+      <c r="M100" s="7" t="s">
+        <v>698</v>
+      </c>
+      <c r="N100" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14">
+      <c r="A101" s="4" t="s">
+        <v>3058</v>
+      </c>
+      <c r="B101" t="s">
+        <v>3070</v>
+      </c>
+      <c r="C101" s="37" t="s">
+        <v>3016</v>
+      </c>
+      <c r="D101" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="E101" s="38" t="s">
+        <v>3084</v>
+      </c>
+      <c r="F101" s="36" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G101" s="36" t="s">
+        <v>3071</v>
+      </c>
+      <c r="H101" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I101" t="s">
+        <v>3073</v>
+      </c>
+      <c r="J101" s="2" t="s">
+        <v>3072</v>
+      </c>
+      <c r="K101" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="L101" t="s">
+        <v>61</v>
+      </c>
+      <c r="M101" s="7" t="s">
+        <v>700</v>
+      </c>
+      <c r="N101" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14">
+      <c r="A102" s="4" t="s">
+        <v>3059</v>
+      </c>
+      <c r="B102" t="s">
+        <v>3074</v>
+      </c>
+      <c r="C102" s="37" t="s">
+        <v>3076</v>
+      </c>
+      <c r="D102" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="E102" s="38" t="s">
+        <v>3085</v>
+      </c>
+      <c r="F102" s="36" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G102" s="36" t="s">
+        <v>3077</v>
+      </c>
+      <c r="H102" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I102" s="27" t="s">
+        <v>3078</v>
+      </c>
+      <c r="J102" s="32" t="s">
+        <v>3079</v>
+      </c>
+      <c r="K102" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="L102" t="s">
+        <v>61</v>
+      </c>
+      <c r="M102" s="7" t="s">
+        <v>698</v>
+      </c>
+      <c r="N102" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="103" spans="1:14">
+      <c r="A103" s="4" t="s">
+        <v>3075</v>
+      </c>
+      <c r="B103" t="s">
+        <v>3080</v>
+      </c>
+      <c r="C103" s="17" t="s">
+        <v>443</v>
+      </c>
+      <c r="D103" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E103" s="38" t="s">
+        <v>3086</v>
+      </c>
+      <c r="F103" s="36" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G103" s="36" t="s">
+        <v>3087</v>
+      </c>
+      <c r="H103" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I103" s="2" t="s">
+        <v>3088</v>
+      </c>
+      <c r="J103" s="32" t="s">
+        <v>3089</v>
+      </c>
+      <c r="K103" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="L103" t="s">
+        <v>61</v>
+      </c>
+      <c r="M103" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="N103" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="104" spans="1:14">
+      <c r="A104" s="4" t="s">
+        <v>3091</v>
+      </c>
+      <c r="B104" t="s">
+        <v>3090</v>
+      </c>
+      <c r="C104" s="37" t="s">
+        <v>277</v>
+      </c>
+      <c r="D104" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="E104" s="38" t="s">
+        <v>3092</v>
+      </c>
+      <c r="F104" s="36" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G104" s="39" t="s">
+        <v>3093</v>
+      </c>
+      <c r="H104" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I104" s="27" t="s">
+        <v>3094</v>
+      </c>
+      <c r="J104" s="32" t="s">
+        <v>3095</v>
+      </c>
+      <c r="K104" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="L104" t="s">
+        <v>61</v>
+      </c>
+      <c r="M104" s="7" t="s">
+        <v>698</v>
+      </c>
+      <c r="N104" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="105" spans="1:14">
+      <c r="A105" s="4" t="s">
+        <v>3096</v>
+      </c>
+      <c r="B105" t="s">
+        <v>3097</v>
+      </c>
+      <c r="C105" s="17" t="s">
+        <v>3009</v>
+      </c>
+      <c r="D105" s="13" t="s">
+        <v>520</v>
+      </c>
+      <c r="E105" s="38" t="s">
+        <v>3098</v>
+      </c>
+      <c r="F105" s="36" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G105" s="39" t="s">
+        <v>3099</v>
+      </c>
+      <c r="H105" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I105" s="27" t="s">
+        <v>3100</v>
+      </c>
+      <c r="J105" s="32" t="s">
+        <v>3101</v>
+      </c>
+      <c r="K105" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="L105" t="s">
+        <v>61</v>
+      </c>
+      <c r="M105" s="7" t="s">
+        <v>702</v>
+      </c>
+      <c r="N105" t="s">
         <v>25</v>
       </c>
     </row>
@@ -14006,47 +14519,60 @@
     <hyperlink ref="I40" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
     <hyperlink ref="I41" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
     <hyperlink ref="I45" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="I58" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="J58" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="I59" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="J59" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="I60" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="J60" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="I61" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="J61" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="I62" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="J62" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="I67" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="J67" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="I68" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="J68" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="I69" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="J69" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="I70" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="J70" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="I71" r:id="rId37" xr:uid="{0B8C1C0C-47FA-451D-B2FE-12EFD0A111BF}"/>
-    <hyperlink ref="J71" r:id="rId38" xr:uid="{9FB12FE9-A0EE-496D-AFE6-FE36229B3E21}"/>
-    <hyperlink ref="J75" r:id="rId39" xr:uid="{4EB3F8F5-9523-4D51-98B0-69BB17DD7F5A}"/>
-    <hyperlink ref="J77" r:id="rId40" xr:uid="{3B031A79-4CEE-45C4-9A1F-B1D002630AFA}"/>
-    <hyperlink ref="I78" r:id="rId41" xr:uid="{93FF4324-911A-4833-81A9-4734C97681F3}"/>
-    <hyperlink ref="J78" r:id="rId42" xr:uid="{561B3DE3-61D1-42B0-B848-CBE9B1AFA9D1}"/>
-    <hyperlink ref="I79" r:id="rId43" xr:uid="{BE9E8745-188B-43B1-9452-32BEBE2AC112}"/>
-    <hyperlink ref="I87" r:id="rId44" xr:uid="{BBCF047A-9283-4540-8F64-F6AAC18C42BB}"/>
-    <hyperlink ref="J87" r:id="rId45" xr:uid="{85495087-0B60-4C63-9EAD-8FAFC16FDA87}"/>
-    <hyperlink ref="I88" r:id="rId46" xr:uid="{9D36823A-5DFC-4E8F-91FB-61378533EFF4}"/>
-    <hyperlink ref="J88" r:id="rId47" xr:uid="{56E53176-85EA-482A-8107-B53BC4B5A56E}"/>
-    <hyperlink ref="I89" r:id="rId48" xr:uid="{54C8C95D-2C8A-4B14-B3F8-1B69A2587372}"/>
-    <hyperlink ref="I82" r:id="rId49" xr:uid="{B234FDA3-9881-49C7-9757-E6B50F09E652}"/>
-    <hyperlink ref="I92" r:id="rId50" xr:uid="{629DD39D-5539-4595-B551-7C70898E50E5}"/>
-    <hyperlink ref="I93" r:id="rId51" xr:uid="{C9324AD1-D443-4B4A-88F6-7342BEEBC444}"/>
-    <hyperlink ref="J93" r:id="rId52" xr:uid="{02ABAA1D-5CBA-4945-9449-F11890AA00C1}"/>
-    <hyperlink ref="I94" r:id="rId53" xr:uid="{CD066ABD-A9CF-4B23-B64F-6EFECB0682A9}"/>
-    <hyperlink ref="J94" r:id="rId54" xr:uid="{DE191AC8-7CDC-47D8-8778-80293EDB2FDD}"/>
-    <hyperlink ref="I95" r:id="rId55" xr:uid="{CCA8EE89-F6B4-4DE6-8266-D2E2C7A801D9}"/>
-    <hyperlink ref="J95" r:id="rId56" xr:uid="{3EA9C5B0-8F07-472C-B534-F158D1D13832}"/>
-    <hyperlink ref="I96" r:id="rId57" xr:uid="{84DAD3FB-EB5D-446A-B122-0A99A60B6E95}"/>
-    <hyperlink ref="J96" r:id="rId58" xr:uid="{44B094DB-343C-49F4-A023-566CEE808AE0}"/>
-    <hyperlink ref="I97" r:id="rId59" xr:uid="{890D1BEC-53E9-4E41-AB45-508A74C3ACB5}"/>
+    <hyperlink ref="J58" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="I59" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="J59" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="I60" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="J60" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="I61" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="J61" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="I62" r:id="rId26" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="J62" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="I67" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="J67" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="I68" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="J68" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="I69" r:id="rId32" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="J69" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="I70" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="J70" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="I71" r:id="rId36" xr:uid="{0B8C1C0C-47FA-451D-B2FE-12EFD0A111BF}"/>
+    <hyperlink ref="J71" r:id="rId37" xr:uid="{9FB12FE9-A0EE-496D-AFE6-FE36229B3E21}"/>
+    <hyperlink ref="J75" r:id="rId38" xr:uid="{4EB3F8F5-9523-4D51-98B0-69BB17DD7F5A}"/>
+    <hyperlink ref="J77" r:id="rId39" xr:uid="{3B031A79-4CEE-45C4-9A1F-B1D002630AFA}"/>
+    <hyperlink ref="I78" r:id="rId40" xr:uid="{93FF4324-911A-4833-81A9-4734C97681F3}"/>
+    <hyperlink ref="J78" r:id="rId41" xr:uid="{561B3DE3-61D1-42B0-B848-CBE9B1AFA9D1}"/>
+    <hyperlink ref="I79" r:id="rId42" xr:uid="{BE9E8745-188B-43B1-9452-32BEBE2AC112}"/>
+    <hyperlink ref="I87" r:id="rId43" xr:uid="{BBCF047A-9283-4540-8F64-F6AAC18C42BB}"/>
+    <hyperlink ref="J87" r:id="rId44" xr:uid="{85495087-0B60-4C63-9EAD-8FAFC16FDA87}"/>
+    <hyperlink ref="I88" r:id="rId45" xr:uid="{9D36823A-5DFC-4E8F-91FB-61378533EFF4}"/>
+    <hyperlink ref="J88" r:id="rId46" xr:uid="{56E53176-85EA-482A-8107-B53BC4B5A56E}"/>
+    <hyperlink ref="I89" r:id="rId47" xr:uid="{54C8C95D-2C8A-4B14-B3F8-1B69A2587372}"/>
+    <hyperlink ref="I82" r:id="rId48" xr:uid="{B234FDA3-9881-49C7-9757-E6B50F09E652}"/>
+    <hyperlink ref="I92" r:id="rId49" xr:uid="{629DD39D-5539-4595-B551-7C70898E50E5}"/>
+    <hyperlink ref="I93" r:id="rId50" xr:uid="{C9324AD1-D443-4B4A-88F6-7342BEEBC444}"/>
+    <hyperlink ref="J93" r:id="rId51" xr:uid="{02ABAA1D-5CBA-4945-9449-F11890AA00C1}"/>
+    <hyperlink ref="I94" r:id="rId52" xr:uid="{CD066ABD-A9CF-4B23-B64F-6EFECB0682A9}"/>
+    <hyperlink ref="J94" r:id="rId53" xr:uid="{DE191AC8-7CDC-47D8-8778-80293EDB2FDD}"/>
+    <hyperlink ref="I95" r:id="rId54" xr:uid="{CCA8EE89-F6B4-4DE6-8266-D2E2C7A801D9}"/>
+    <hyperlink ref="J95" r:id="rId55" xr:uid="{3EA9C5B0-8F07-472C-B534-F158D1D13832}"/>
+    <hyperlink ref="I96" r:id="rId56" xr:uid="{84DAD3FB-EB5D-446A-B122-0A99A60B6E95}"/>
+    <hyperlink ref="J96" r:id="rId57" xr:uid="{44B094DB-343C-49F4-A023-566CEE808AE0}"/>
+    <hyperlink ref="I97" r:id="rId58" xr:uid="{890D1BEC-53E9-4E41-AB45-508A74C3ACB5}"/>
+    <hyperlink ref="I98" r:id="rId59" xr:uid="{02959CD1-6C86-4D79-AEAF-97CB61B96D25}"/>
+    <hyperlink ref="I99" r:id="rId60" xr:uid="{3688B733-FC93-4BD4-BD33-E91280D03ADE}"/>
+    <hyperlink ref="J99" r:id="rId61" xr:uid="{8F40B277-7A81-44F0-8336-1DAD2949332A}"/>
+    <hyperlink ref="J100" r:id="rId62" xr:uid="{DE00D900-0F4C-4258-946C-9BE0F3013002}"/>
+    <hyperlink ref="J101" r:id="rId63" xr:uid="{34919784-5679-4717-9885-2A1A0C412CE4}"/>
+    <hyperlink ref="I102" r:id="rId64" xr:uid="{470193F3-D16D-4EAC-841E-3D81FB5774A9}"/>
+    <hyperlink ref="J102" r:id="rId65" xr:uid="{2ED12714-63A2-41C3-AB62-1774DD1F70BA}"/>
+    <hyperlink ref="I58" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="I103" r:id="rId67" xr:uid="{4D721F85-2836-4ADB-B264-71CBD8B98BD8}"/>
+    <hyperlink ref="J103" r:id="rId68" xr:uid="{3925AD24-90B0-4A5C-A46D-F80F8E61579F}"/>
+    <hyperlink ref="I104" r:id="rId69" xr:uid="{478CCF2E-AB97-48E1-A38C-995964394AC8}"/>
+    <hyperlink ref="J104" r:id="rId70" xr:uid="{F9BBE179-DB54-4835-A14E-4454CA18A6AE}"/>
+    <hyperlink ref="I105" r:id="rId71" xr:uid="{ABB87B28-8AD2-4BF8-B4D7-500E78A25472}"/>
+    <hyperlink ref="J105" r:id="rId72" xr:uid="{F543587D-0A3E-429A-8125-C651D94CA2A5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{774D670F-F1D6-4AB3-A5EB-F0ABEB79F458}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DBCA921-DBC1-4B06-9069-00F4B7B41B87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32295" yWindow="2355" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32295" yWindow="2355" windowWidth="14610" windowHeight="15585" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6207" uniqueCount="3102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6333" uniqueCount="3162">
   <si>
     <t>ID</t>
   </si>
@@ -9348,6 +9348,186 @@
   </si>
   <si>
     <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/885012209073?qs=sPbYRqrBIVm8PsM2ljQIMg%3D%3D</t>
+  </si>
+  <si>
+    <t>010-0142</t>
+  </si>
+  <si>
+    <t>010-0143</t>
+  </si>
+  <si>
+    <t>010-0144</t>
+  </si>
+  <si>
+    <t>Resistores de película gruesa - SMD WRIS-RSKS &lt;0.05 Ohms 0.1 W Jumper 0603 AEC-Q200</t>
+  </si>
+  <si>
+    <t>560112116001</t>
+  </si>
+  <si>
+    <t>710-560112116001</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/560112116001.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/560112116001?qs=mELouGlnn3dlnHYj7TecuA%3D%3D</t>
+  </si>
+  <si>
+    <t>Resistores de película gruesa - SMD WRIS-RSKS 5.1 kOhms 5 % 0.25 W 0805 AEC-Q200</t>
+  </si>
+  <si>
+    <t>5.1kΩ 250mW  ±5%</t>
+  </si>
+  <si>
+    <t>560112120019</t>
+  </si>
+  <si>
+    <t>710-560112120019</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/560112120019.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/560112120019?qs=mELouGlnn3d1l%252BnKb9nSgA%3D%3D</t>
+  </si>
+  <si>
+    <t>Resistores de película gruesa - SMD WRIS-RSKS 330 Ohms 1 % 0.1 W 0603 AEC-Q200</t>
+  </si>
+  <si>
+    <t>330Ω 100mW ±1%</t>
+  </si>
+  <si>
+    <t>560112116020</t>
+  </si>
+  <si>
+    <t>710-560112116020</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/560112116020.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/560112116020?qs=mELouGlnn3dXlpeR%252Bp7gkg%3D%3D</t>
+  </si>
+  <si>
+    <t>010-0145</t>
+  </si>
+  <si>
+    <t>Resistores de película gruesa - SMD WRIS-RSKS 10 kOhms 1 % 0.1 W 0603 AEC-Q200</t>
+  </si>
+  <si>
+    <t>560112116005</t>
+  </si>
+  <si>
+    <t>710-560112116005</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/560112116005.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/560112116005?qs=mELouGlnn3dMVSPHwBGouA%3D%3D</t>
+  </si>
+  <si>
+    <t>010-0146</t>
+  </si>
+  <si>
+    <t>010-0147</t>
+  </si>
+  <si>
+    <t>010-0148</t>
+  </si>
+  <si>
+    <t>010-0149</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/560112116032?qs=mELouGlnn3dPZZEXKb4zAQ%3D%3D</t>
+  </si>
+  <si>
+    <t>Resistores de película gruesa - SMD WRIS-RSKS 1.8 kOhms 1 % 0.1 W 0603 AEC-Q200</t>
+  </si>
+  <si>
+    <t>1.8kΩ 100mW ±1%</t>
+  </si>
+  <si>
+    <t>560112116032</t>
+  </si>
+  <si>
+    <t>710-560112116032</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/560112116032.pdf</t>
+  </si>
+  <si>
+    <t>Resistores de película gruesa - SMD WRIS-RSKS 49.9 Ohms 1 % 0.1 W 0603 AEC-Q200</t>
+  </si>
+  <si>
+    <t>49.9Ω 100mW ±1%</t>
+  </si>
+  <si>
+    <t>560112116133</t>
+  </si>
+  <si>
+    <t>710-560112116133</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/560112116133.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/560112116133?qs=mELouGlnn3fu%2F7K9tg3bDw%3D%3D</t>
+  </si>
+  <si>
+    <t>Resistores de película gruesa - SMD WRIS-RSKS 4.02 kOhms 1 % 0.1 W 0603 AEC-Q200</t>
+  </si>
+  <si>
+    <t>560112116093</t>
+  </si>
+  <si>
+    <t>710-560112116093</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/560112116093.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/560112116093?qs=mELouGlnn3dikxUEmUbjog%3D%3D</t>
+  </si>
+  <si>
+    <t>Resistores de película gruesa - SMD WRIS-RSKS 10 Ohms 1 % 0.1 W 0603 AEC-Q200</t>
+  </si>
+  <si>
+    <t>10Ω 100mW ±1%</t>
+  </si>
+  <si>
+    <t>560112116013</t>
+  </si>
+  <si>
+    <t>710-560112116013</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/560112116013.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/560112116013?qs=mELouGlnn3f7quibYlpocQ%3D%3D</t>
+  </si>
+  <si>
+    <t>015-0004</t>
+  </si>
+  <si>
+    <t>Resistores de detección de corriente - SMD WRIS-PSMC 10mOhms 1% 2512 2W 100ppm/C</t>
+  </si>
+  <si>
+    <t>10mΩ 2W ±1%</t>
+  </si>
+  <si>
+    <t>580070763010</t>
+  </si>
+  <si>
+    <t>710-580070763010</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/580070763010.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/580070763010?qs=amGC7iS6iy%2FEZvIQbPzDXw%3D%3D</t>
   </si>
 </sst>
 </file>
@@ -9574,10 +9754,10 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -14153,19 +14333,19 @@
       <c r="B98" t="s">
         <v>3051</v>
       </c>
-      <c r="C98" s="37" t="s">
+      <c r="C98" s="17" t="s">
         <v>3052</v>
       </c>
       <c r="D98" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="E98" s="38" t="s">
+      <c r="E98" s="36" t="s">
         <v>3081</v>
       </c>
-      <c r="F98" s="36" t="s">
+      <c r="F98" s="3" t="s">
         <v>2100</v>
       </c>
-      <c r="G98" s="36" t="s">
+      <c r="G98" s="3" t="s">
         <v>3053</v>
       </c>
       <c r="H98" s="16" t="s">
@@ -14197,19 +14377,19 @@
       <c r="B99" t="s">
         <v>3060</v>
       </c>
-      <c r="C99" s="37" t="s">
+      <c r="C99" s="17" t="s">
         <v>3061</v>
       </c>
       <c r="D99" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="E99" s="38" t="s">
+      <c r="E99" s="36" t="s">
         <v>3083</v>
       </c>
-      <c r="F99" s="36" t="s">
+      <c r="F99" s="3" t="s">
         <v>2100</v>
       </c>
-      <c r="G99" s="36" t="s">
+      <c r="G99" s="3" t="s">
         <v>3062</v>
       </c>
       <c r="H99" s="16" t="s">
@@ -14241,16 +14421,16 @@
       <c r="B100" t="s">
         <v>3065</v>
       </c>
-      <c r="C100" s="37" t="s">
+      <c r="C100" s="17" t="s">
         <v>3066</v>
       </c>
       <c r="D100" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="E100" s="38" t="s">
+      <c r="E100" s="36" t="s">
         <v>3082</v>
       </c>
-      <c r="F100" s="36" t="s">
+      <c r="F100" s="3" t="s">
         <v>2100</v>
       </c>
       <c r="G100" t="s">
@@ -14285,19 +14465,19 @@
       <c r="B101" t="s">
         <v>3070</v>
       </c>
-      <c r="C101" s="37" t="s">
+      <c r="C101" s="17" t="s">
         <v>3016</v>
       </c>
       <c r="D101" s="13" t="s">
         <v>240</v>
       </c>
-      <c r="E101" s="38" t="s">
+      <c r="E101" s="36" t="s">
         <v>3084</v>
       </c>
-      <c r="F101" s="36" t="s">
+      <c r="F101" s="3" t="s">
         <v>2100</v>
       </c>
-      <c r="G101" s="36" t="s">
+      <c r="G101" s="3" t="s">
         <v>3071</v>
       </c>
       <c r="H101" s="16" t="s">
@@ -14329,19 +14509,19 @@
       <c r="B102" t="s">
         <v>3074</v>
       </c>
-      <c r="C102" s="37" t="s">
+      <c r="C102" s="17" t="s">
         <v>3076</v>
       </c>
       <c r="D102" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="E102" s="38" t="s">
+      <c r="E102" s="36" t="s">
         <v>3085</v>
       </c>
-      <c r="F102" s="36" t="s">
+      <c r="F102" s="3" t="s">
         <v>2100</v>
       </c>
-      <c r="G102" s="36" t="s">
+      <c r="G102" s="3" t="s">
         <v>3077</v>
       </c>
       <c r="H102" s="16" t="s">
@@ -14379,13 +14559,13 @@
       <c r="D103" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="E103" s="38" t="s">
+      <c r="E103" s="36" t="s">
         <v>3086</v>
       </c>
-      <c r="F103" s="36" t="s">
+      <c r="F103" s="3" t="s">
         <v>2100</v>
       </c>
-      <c r="G103" s="36" t="s">
+      <c r="G103" s="3" t="s">
         <v>3087</v>
       </c>
       <c r="H103" s="16" t="s">
@@ -14417,19 +14597,19 @@
       <c r="B104" t="s">
         <v>3090</v>
       </c>
-      <c r="C104" s="37" t="s">
+      <c r="C104" s="17" t="s">
         <v>277</v>
       </c>
       <c r="D104" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="E104" s="38" t="s">
+      <c r="E104" s="36" t="s">
         <v>3092</v>
       </c>
-      <c r="F104" s="36" t="s">
+      <c r="F104" s="3" t="s">
         <v>2100</v>
       </c>
-      <c r="G104" s="39" t="s">
+      <c r="G104" s="31" t="s">
         <v>3093</v>
       </c>
       <c r="H104" s="16" t="s">
@@ -14467,13 +14647,13 @@
       <c r="D105" s="13" t="s">
         <v>520</v>
       </c>
-      <c r="E105" s="38" t="s">
+      <c r="E105" s="36" t="s">
         <v>3098</v>
       </c>
-      <c r="F105" s="36" t="s">
+      <c r="F105" s="3" t="s">
         <v>2100</v>
       </c>
-      <c r="G105" s="39" t="s">
+      <c r="G105" s="31" t="s">
         <v>3099</v>
       </c>
       <c r="H105" s="16" t="s">
@@ -21378,10 +21558,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60E8291E-4293-4634-B9E9-80CB520CA181}">
-  <dimension ref="A1:N142"/>
+  <dimension ref="A1:N151"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="3" max="3" width="19.90625" customWidth="1"/>
+    <col min="5" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13.453125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -27632,6 +27813,361 @@
       <c r="N142" t="s">
         <v>25</v>
       </c>
+    </row>
+    <row r="143" spans="1:14">
+      <c r="A143" s="16" t="s">
+        <v>3102</v>
+      </c>
+      <c r="B143" s="37" t="s">
+        <v>3105</v>
+      </c>
+      <c r="C143" s="17" t="s">
+        <v>893</v>
+      </c>
+      <c r="D143" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E143" s="38" t="s">
+        <v>3106</v>
+      </c>
+      <c r="F143" s="37" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G143" s="37" t="s">
+        <v>3107</v>
+      </c>
+      <c r="H143" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I143" s="27" t="s">
+        <v>3108</v>
+      </c>
+      <c r="J143" s="27" t="s">
+        <v>3109</v>
+      </c>
+      <c r="K143" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L143" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M143" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="N143" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="144" spans="1:14">
+      <c r="A144" s="16" t="s">
+        <v>3103</v>
+      </c>
+      <c r="B144" s="37" t="s">
+        <v>3110</v>
+      </c>
+      <c r="C144" s="37" t="s">
+        <v>3111</v>
+      </c>
+      <c r="D144" s="20" t="s">
+        <v>240</v>
+      </c>
+      <c r="E144" s="38" t="s">
+        <v>3112</v>
+      </c>
+      <c r="F144" s="37" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G144" s="37" t="s">
+        <v>3113</v>
+      </c>
+      <c r="H144" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I144" s="27" t="s">
+        <v>3114</v>
+      </c>
+      <c r="J144" s="32" t="s">
+        <v>3115</v>
+      </c>
+      <c r="K144" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L144" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M144" s="17" t="s">
+        <v>1646</v>
+      </c>
+      <c r="N144" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="145" spans="1:14">
+      <c r="A145" s="16" t="s">
+        <v>3104</v>
+      </c>
+      <c r="B145" s="37" t="s">
+        <v>3116</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>3117</v>
+      </c>
+      <c r="D145" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E145" s="38" t="s">
+        <v>3118</v>
+      </c>
+      <c r="F145" s="37" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G145" s="37" t="s">
+        <v>3119</v>
+      </c>
+      <c r="H145" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I145" s="27" t="s">
+        <v>3120</v>
+      </c>
+      <c r="J145" s="32" t="s">
+        <v>3121</v>
+      </c>
+      <c r="K145" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L145" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M145" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="N145" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="146" spans="1:14">
+      <c r="A146" s="16" t="s">
+        <v>3122</v>
+      </c>
+      <c r="B146" s="37" t="s">
+        <v>3123</v>
+      </c>
+      <c r="C146" s="7" t="s">
+        <v>1149</v>
+      </c>
+      <c r="D146" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E146" s="38" t="s">
+        <v>3124</v>
+      </c>
+      <c r="F146" s="37" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G146" s="37" t="s">
+        <v>3125</v>
+      </c>
+      <c r="H146" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I146" s="27" t="s">
+        <v>3126</v>
+      </c>
+      <c r="J146" t="s">
+        <v>3127</v>
+      </c>
+      <c r="K146" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L146" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M146" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="N146" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="147" spans="1:14">
+      <c r="A147" s="16" t="s">
+        <v>3128</v>
+      </c>
+      <c r="B147" s="37" t="s">
+        <v>3133</v>
+      </c>
+      <c r="C147" s="17" t="s">
+        <v>3134</v>
+      </c>
+      <c r="D147" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E147" s="38" t="s">
+        <v>3135</v>
+      </c>
+      <c r="F147" s="37" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G147" s="37" t="s">
+        <v>3136</v>
+      </c>
+      <c r="H147" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I147" s="27" t="s">
+        <v>3137</v>
+      </c>
+      <c r="J147" s="27" t="s">
+        <v>3132</v>
+      </c>
+      <c r="K147" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L147" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M147" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="N147" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="148" spans="1:14">
+      <c r="A148" s="16" t="s">
+        <v>3129</v>
+      </c>
+      <c r="B148" s="37" t="s">
+        <v>3138</v>
+      </c>
+      <c r="C148" s="7" t="s">
+        <v>3139</v>
+      </c>
+      <c r="D148" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E148" s="36" t="s">
+        <v>3140</v>
+      </c>
+      <c r="F148" s="37" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G148" t="s">
+        <v>3141</v>
+      </c>
+      <c r="H148" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I148" s="27" t="s">
+        <v>3142</v>
+      </c>
+      <c r="J148" s="32" t="s">
+        <v>3143</v>
+      </c>
+      <c r="K148" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L148" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M148" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="N148" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="149" spans="1:14">
+      <c r="A149" s="16" t="s">
+        <v>3130</v>
+      </c>
+      <c r="B149" s="37" t="s">
+        <v>3144</v>
+      </c>
+      <c r="C149" s="16" t="s">
+        <v>1610</v>
+      </c>
+      <c r="D149" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E149" s="39" t="s">
+        <v>3145</v>
+      </c>
+      <c r="F149" s="37" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G149" s="37" t="s">
+        <v>3146</v>
+      </c>
+      <c r="H149" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I149" s="27" t="s">
+        <v>3147</v>
+      </c>
+      <c r="J149" s="32" t="s">
+        <v>3148</v>
+      </c>
+      <c r="K149" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L149" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M149" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="N149" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="150" spans="1:14">
+      <c r="A150" s="16" t="s">
+        <v>3131</v>
+      </c>
+      <c r="B150" s="37" t="s">
+        <v>3149</v>
+      </c>
+      <c r="C150" s="16" t="s">
+        <v>3150</v>
+      </c>
+      <c r="D150" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E150" s="39" t="s">
+        <v>3151</v>
+      </c>
+      <c r="F150" s="37" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G150" s="37" t="s">
+        <v>3152</v>
+      </c>
+      <c r="H150" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I150" s="27" t="s">
+        <v>3153</v>
+      </c>
+      <c r="J150" s="32" t="s">
+        <v>3154</v>
+      </c>
+      <c r="K150" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L150" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M150" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="N150" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="151" spans="1:14">
+      <c r="A151" s="16"/>
     </row>
   </sheetData>
   <phoneticPr fontId="16" type="noConversion"/>
@@ -27728,15 +28264,30 @@
     <hyperlink ref="J137" r:id="rId90" xr:uid="{270FAB0D-B47D-4805-A699-C4BB16679313}"/>
     <hyperlink ref="I140" r:id="rId91" xr:uid="{AF66F37C-DEF2-4C02-B09E-78216E8A0857}"/>
     <hyperlink ref="J140" r:id="rId92" xr:uid="{5C7EACC9-1558-4F25-8631-38E695251F20}"/>
+    <hyperlink ref="I143" r:id="rId93" xr:uid="{C01DAE4E-F612-4FC5-8D22-5944A3E92FB0}"/>
+    <hyperlink ref="J143" r:id="rId94" xr:uid="{06184D44-AC67-4E67-A84F-AA99CD34AEB6}"/>
+    <hyperlink ref="I144" r:id="rId95" xr:uid="{0BA127CF-9F17-46D3-8575-41BD9AD2CDB0}"/>
+    <hyperlink ref="J144" r:id="rId96" xr:uid="{4E510238-24C1-436C-B1B1-DC4BBBD46327}"/>
+    <hyperlink ref="I145" r:id="rId97" xr:uid="{4DAB6FCC-DE9F-47EE-8889-AF483417A869}"/>
+    <hyperlink ref="J145" r:id="rId98" xr:uid="{5B1AE306-EC71-4D08-9387-CBEBC35C11D8}"/>
+    <hyperlink ref="I146" r:id="rId99" xr:uid="{4917BA3D-010B-4FC0-897E-454B864E1931}"/>
+    <hyperlink ref="I147" r:id="rId100" xr:uid="{CA0F4A3B-5CA6-4B60-95A8-D5832F92DB0C}"/>
+    <hyperlink ref="J147" r:id="rId101" xr:uid="{E9DB0A36-8554-4D76-81C9-42407166BE48}"/>
+    <hyperlink ref="I148" r:id="rId102" xr:uid="{243AD2D2-4D58-4692-93A4-89A4B3090386}"/>
+    <hyperlink ref="J148" r:id="rId103" xr:uid="{081B7EBC-5724-44C6-B7A8-0F110E0A5EB2}"/>
+    <hyperlink ref="I149" r:id="rId104" xr:uid="{66E45401-3B0B-41F7-9778-7BDA8C0C1404}"/>
+    <hyperlink ref="J149" r:id="rId105" xr:uid="{1A42DE35-CA7D-4B83-ACC4-F85A80B83C4C}"/>
+    <hyperlink ref="I150" r:id="rId106" xr:uid="{866C2F71-4468-4B2A-8F29-42D5363F2AE6}"/>
+    <hyperlink ref="J150" r:id="rId107" xr:uid="{D030A4B2-39C9-4251-A1F3-D75C066D2B9B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId93"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId108"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81F9848D-6D60-47C0-9F84-A561FE4F106E}">
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="20.26953125" customWidth="1"/>
@@ -27918,6 +28469,50 @@
         <v>25</v>
       </c>
     </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>3155</v>
+      </c>
+      <c r="B5" t="s">
+        <v>3156</v>
+      </c>
+      <c r="C5" t="s">
+        <v>3157</v>
+      </c>
+      <c r="D5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" s="36" t="s">
+        <v>3158</v>
+      </c>
+      <c r="F5" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G5" t="s">
+        <v>3159</v>
+      </c>
+      <c r="H5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>3160</v>
+      </c>
+      <c r="J5" t="s">
+        <v>3161</v>
+      </c>
+      <c r="K5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M5" s="17" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N5" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="16" type="noConversion"/>
   <hyperlinks>
@@ -27926,6 +28521,7 @@
     <hyperlink ref="I3" r:id="rId3" xr:uid="{EDE33321-C187-4A8F-8366-9AEDB9FF4C7B}"/>
     <hyperlink ref="I4" r:id="rId4" xr:uid="{DA619253-40A2-482C-A99F-F72A13182916}"/>
     <hyperlink ref="J4" r:id="rId5" xr:uid="{65BF95D6-EB54-41F9-8886-7DFC774FFE44}"/>
+    <hyperlink ref="I5" r:id="rId6" xr:uid="{E9BE5DD3-9340-403D-9879-EBA54F1D68BE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DBCA921-DBC1-4B06-9069-00F4B7B41B87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B16B84C-A795-4F12-9527-5B4F35DED38B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32295" yWindow="2355" windowWidth="14610" windowHeight="15585" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="760" yWindow="760" windowWidth="16200" windowHeight="9970" firstSheet="14" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6333" uniqueCount="3162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6333" uniqueCount="3163">
   <si>
     <t>ID</t>
   </si>
@@ -9528,6 +9528,9 @@
   </si>
   <si>
     <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/580070763010?qs=amGC7iS6iy%2FEZvIQbPzDXw%3D%3D</t>
+  </si>
+  <si>
+    <t>A</t>
   </si>
 </sst>
 </file>
@@ -9697,7 +9700,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -9755,9 +9758,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -17534,7 +17534,7 @@
         <v>3024</v>
       </c>
       <c r="H2" t="s">
-        <v>16</v>
+        <v>3162</v>
       </c>
       <c r="I2" t="s">
         <v>21</v>
@@ -27818,7 +27818,7 @@
       <c r="A143" s="16" t="s">
         <v>3102</v>
       </c>
-      <c r="B143" s="37" t="s">
+      <c r="B143" s="17" t="s">
         <v>3105</v>
       </c>
       <c r="C143" s="17" t="s">
@@ -27827,13 +27827,13 @@
       <c r="D143" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="E143" s="38" t="s">
+      <c r="E143" s="29" t="s">
         <v>3106</v>
       </c>
-      <c r="F143" s="37" t="s">
+      <c r="F143" s="17" t="s">
         <v>2100</v>
       </c>
-      <c r="G143" s="37" t="s">
+      <c r="G143" s="17" t="s">
         <v>3107</v>
       </c>
       <c r="H143" s="16" t="s">
@@ -27862,22 +27862,22 @@
       <c r="A144" s="16" t="s">
         <v>3103</v>
       </c>
-      <c r="B144" s="37" t="s">
+      <c r="B144" s="17" t="s">
         <v>3110</v>
       </c>
-      <c r="C144" s="37" t="s">
+      <c r="C144" s="17" t="s">
         <v>3111</v>
       </c>
       <c r="D144" s="20" t="s">
         <v>240</v>
       </c>
-      <c r="E144" s="38" t="s">
+      <c r="E144" s="29" t="s">
         <v>3112</v>
       </c>
-      <c r="F144" s="37" t="s">
+      <c r="F144" s="17" t="s">
         <v>2100</v>
       </c>
-      <c r="G144" s="37" t="s">
+      <c r="G144" s="17" t="s">
         <v>3113</v>
       </c>
       <c r="H144" s="16" t="s">
@@ -27906,7 +27906,7 @@
       <c r="A145" s="16" t="s">
         <v>3104</v>
       </c>
-      <c r="B145" s="37" t="s">
+      <c r="B145" s="17" t="s">
         <v>3116</v>
       </c>
       <c r="C145" s="3" t="s">
@@ -27915,13 +27915,13 @@
       <c r="D145" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="E145" s="38" t="s">
+      <c r="E145" s="29" t="s">
         <v>3118</v>
       </c>
-      <c r="F145" s="37" t="s">
+      <c r="F145" s="17" t="s">
         <v>2100</v>
       </c>
-      <c r="G145" s="37" t="s">
+      <c r="G145" s="17" t="s">
         <v>3119</v>
       </c>
       <c r="H145" s="16" t="s">
@@ -27950,7 +27950,7 @@
       <c r="A146" s="16" t="s">
         <v>3122</v>
       </c>
-      <c r="B146" s="37" t="s">
+      <c r="B146" s="17" t="s">
         <v>3123</v>
       </c>
       <c r="C146" s="7" t="s">
@@ -27959,13 +27959,13 @@
       <c r="D146" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="E146" s="38" t="s">
+      <c r="E146" s="29" t="s">
         <v>3124</v>
       </c>
-      <c r="F146" s="37" t="s">
+      <c r="F146" s="17" t="s">
         <v>2100</v>
       </c>
-      <c r="G146" s="37" t="s">
+      <c r="G146" s="17" t="s">
         <v>3125</v>
       </c>
       <c r="H146" s="16" t="s">
@@ -27994,7 +27994,7 @@
       <c r="A147" s="16" t="s">
         <v>3128</v>
       </c>
-      <c r="B147" s="37" t="s">
+      <c r="B147" s="17" t="s">
         <v>3133</v>
       </c>
       <c r="C147" s="17" t="s">
@@ -28003,13 +28003,13 @@
       <c r="D147" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="E147" s="38" t="s">
+      <c r="E147" s="29" t="s">
         <v>3135</v>
       </c>
-      <c r="F147" s="37" t="s">
+      <c r="F147" s="17" t="s">
         <v>2100</v>
       </c>
-      <c r="G147" s="37" t="s">
+      <c r="G147" s="17" t="s">
         <v>3136</v>
       </c>
       <c r="H147" s="16" t="s">
@@ -28038,7 +28038,7 @@
       <c r="A148" s="16" t="s">
         <v>3129</v>
       </c>
-      <c r="B148" s="37" t="s">
+      <c r="B148" s="17" t="s">
         <v>3138</v>
       </c>
       <c r="C148" s="7" t="s">
@@ -28050,7 +28050,7 @@
       <c r="E148" s="36" t="s">
         <v>3140</v>
       </c>
-      <c r="F148" s="37" t="s">
+      <c r="F148" s="17" t="s">
         <v>2100</v>
       </c>
       <c r="G148" t="s">
@@ -28082,7 +28082,7 @@
       <c r="A149" s="16" t="s">
         <v>3130</v>
       </c>
-      <c r="B149" s="37" t="s">
+      <c r="B149" s="17" t="s">
         <v>3144</v>
       </c>
       <c r="C149" s="16" t="s">
@@ -28091,13 +28091,13 @@
       <c r="D149" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="E149" s="39" t="s">
+      <c r="E149" s="20" t="s">
         <v>3145</v>
       </c>
-      <c r="F149" s="37" t="s">
+      <c r="F149" s="17" t="s">
         <v>2100</v>
       </c>
-      <c r="G149" s="37" t="s">
+      <c r="G149" s="17" t="s">
         <v>3146</v>
       </c>
       <c r="H149" s="16" t="s">
@@ -28126,7 +28126,7 @@
       <c r="A150" s="16" t="s">
         <v>3131</v>
       </c>
-      <c r="B150" s="37" t="s">
+      <c r="B150" s="17" t="s">
         <v>3149</v>
       </c>
       <c r="C150" s="16" t="s">
@@ -28135,13 +28135,13 @@
       <c r="D150" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="E150" s="39" t="s">
+      <c r="E150" s="20" t="s">
         <v>3151</v>
       </c>
-      <c r="F150" s="37" t="s">
+      <c r="F150" s="17" t="s">
         <v>2100</v>
       </c>
-      <c r="G150" s="37" t="s">
+      <c r="G150" s="17" t="s">
         <v>3152</v>
       </c>
       <c r="H150" s="16" t="s">

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B16B84C-A795-4F12-9527-5B4F35DED38B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72E7BE8E-5349-4841-9AC6-E1B10AAFD1F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="760" windowWidth="16200" windowHeight="9970" firstSheet="14" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32280" yWindow="2235" windowWidth="29040" windowHeight="15720" firstSheet="10" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -24,13 +24,15 @@
     <sheet name="032 - Diode - TVS" sheetId="14" r:id="rId9"/>
     <sheet name="033 - Diode - LED" sheetId="12" r:id="rId10"/>
     <sheet name="040 - Fuses" sheetId="10" r:id="rId11"/>
-    <sheet name="045 - Crystal" sheetId="19" r:id="rId12"/>
-    <sheet name="050 - ICs - Analog" sheetId="2" r:id="rId13"/>
-    <sheet name="060 - ICs - Digital" sheetId="3" r:id="rId14"/>
-    <sheet name="070 - Power Supply - DCDC" sheetId="8" r:id="rId15"/>
-    <sheet name="090 - Processor" sheetId="18" r:id="rId16"/>
-    <sheet name="100 - Electromechanicals" sheetId="15" r:id="rId17"/>
-    <sheet name="110 - Connectors" sheetId="13" r:id="rId18"/>
+    <sheet name="043 - Transistors" sheetId="21" r:id="rId12"/>
+    <sheet name="045 - Crystal" sheetId="19" r:id="rId13"/>
+    <sheet name="050 - ICs - Analog" sheetId="2" r:id="rId14"/>
+    <sheet name="055 - Drivers" sheetId="20" r:id="rId15"/>
+    <sheet name="060 - ICs - Digital" sheetId="3" r:id="rId16"/>
+    <sheet name="070 - Power Supply - DCDC" sheetId="8" r:id="rId17"/>
+    <sheet name="090 - Processor" sheetId="18" r:id="rId18"/>
+    <sheet name="100 - Electromechanicals" sheetId="15" r:id="rId19"/>
+    <sheet name="110 - Connectors" sheetId="13" r:id="rId20"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -42,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6333" uniqueCount="3163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6417" uniqueCount="3201">
   <si>
     <t>ID</t>
   </si>
@@ -9531,6 +9533,120 @@
   </si>
   <si>
     <t>A</t>
+  </si>
+  <si>
+    <t>055-0001</t>
+  </si>
+  <si>
+    <t>Controladores de puerta con aislamiento galvánico Automotive 5.7kVrms 10A single-channel i A 595-UCC21710QDWQ1</t>
+  </si>
+  <si>
+    <t>SOIC-16</t>
+  </si>
+  <si>
+    <t>eUSR_SchLibrary/eUSR_SchLibrary - Drivers.SchLib</t>
+  </si>
+  <si>
+    <t>UCC21710QDWRQ1</t>
+  </si>
+  <si>
+    <t>595-UCC21710QDWRQ1</t>
+  </si>
+  <si>
+    <t>https://www.ti.com/lit/ds/symlink/ucc21710-q1.pdf?ts=1780997053821&amp;ref_url=https%253A%252F%252Fwww.ti.com%252Fproduct%252FUCC21710-Q1</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Texas-Instruments/UCC21710QDWRQ1?qs=9r4v7xj2LnlqS59tMWgtnw%3D%3D</t>
+  </si>
+  <si>
+    <t>UCC21710</t>
+  </si>
+  <si>
+    <t>043-0001</t>
+  </si>
+  <si>
+    <t>MOSFET 150 V, N-Ch, 3.8 mOhms max, Automotive MOSFET, TOLT (10x15)</t>
+  </si>
+  <si>
+    <t>PG-HSOG-8-1</t>
+  </si>
+  <si>
+    <t>IAUTN15S6N025GATMA1</t>
+  </si>
+  <si>
+    <t>726-IAUTN15S6N025GAT</t>
+  </si>
+  <si>
+    <t>Infineon Technologies</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/datasheet/3/70/1/Infineon_IAUTN15S6N025G_DataSheet_v01_00_EN.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Infineon-Technologies/IAUTN15S6N025GATMA1?qs=lxPAlgZqN%2Fyxd40SMd9ESg%3D%3D</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>IAUTN15S6N025</t>
+  </si>
+  <si>
+    <t>eUSR_SchLibrary/eUSR_SchLibrary - Transistors.SchLib</t>
+  </si>
+  <si>
+    <t>070-0004</t>
+  </si>
+  <si>
+    <t>Convertidores DC/DC para montaje pasante 10W DC/DC Converter isolated, regulated in a PCB Mount Plastic Case</t>
+  </si>
+  <si>
+    <t>110V-24V</t>
+  </si>
+  <si>
+    <t>31.8x20.3x10.6mm</t>
+  </si>
+  <si>
+    <t>TEN 10-11015WIRH</t>
+  </si>
+  <si>
+    <t>495-TEN10-11015WIRH</t>
+  </si>
+  <si>
+    <t>https://www.tracopower.com/ten10wirh-datasheet</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/TRACO-Power/TEN-10-11015WIRH?qs=A6eO%252BMLsxmQM8M6%2FnJVPNg%3D%3D</t>
+  </si>
+  <si>
+    <t>TEN 10-110</t>
+  </si>
+  <si>
+    <t>070-0005</t>
+  </si>
+  <si>
+    <t>Convertidores DC/DC para montaje pasante 2W 24-15VIN 5VOUT DC/DC</t>
+  </si>
+  <si>
+    <t>24V-(15,-5)V</t>
+  </si>
+  <si>
+    <t>19.5x9.8x12.5mm</t>
+  </si>
+  <si>
+    <t>MGJ2D241505SC</t>
+  </si>
+  <si>
+    <t>580-MGJ2D241505SC</t>
+  </si>
+  <si>
+    <t>Murata Power Solutions</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/datasheet/3/76/1/kdc-mgj2.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Murata-Power-Solutions/MGJ2D241505SC?qs=xLDY6iXSiQZSXeU7bFDLTA%3D%3D</t>
   </si>
 </sst>
 </file>
@@ -16813,6 +16929,108 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FAFF3B6-AF11-4BFB-8078-829FF6F2F366}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="33" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="33" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
+        <v>3172</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3173</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3180</v>
+      </c>
+      <c r="D2" t="s">
+        <v>3174</v>
+      </c>
+      <c r="E2" t="s">
+        <v>3175</v>
+      </c>
+      <c r="F2" t="s">
+        <v>3177</v>
+      </c>
+      <c r="G2" t="s">
+        <v>3176</v>
+      </c>
+      <c r="H2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>3178</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>3179</v>
+      </c>
+      <c r="K2" t="s">
+        <v>3181</v>
+      </c>
+      <c r="L2" s="34" t="s">
+        <v>3182</v>
+      </c>
+      <c r="M2" t="s">
+        <v>3174</v>
+      </c>
+      <c r="N2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="I2" r:id="rId1" xr:uid="{71BC0DAF-9651-41D4-BC90-0CA5C5CA063D}"/>
+    <hyperlink ref="J2" r:id="rId2" xr:uid="{B8956BA2-569B-4007-9354-F99A76E81F8D}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E5535EA-E186-4751-BC7F-9B3A0221302E}">
   <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -16961,7 +17179,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C98E1A12-072F-4773-8CB5-47FFE077E85B}">
   <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -17211,7 +17429,109 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{201D74E2-3547-4E9B-8216-09A22645AC2A}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="33" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="33" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
+        <v>3163</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3164</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>3165</v>
+      </c>
+      <c r="E2" t="s">
+        <v>3167</v>
+      </c>
+      <c r="F2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" t="s">
+        <v>3168</v>
+      </c>
+      <c r="H2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>3169</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>3170</v>
+      </c>
+      <c r="K2" t="s">
+        <v>3171</v>
+      </c>
+      <c r="L2" t="s">
+        <v>3166</v>
+      </c>
+      <c r="M2" t="s">
+        <v>3165</v>
+      </c>
+      <c r="N2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="I2" r:id="rId1" xr:uid="{8F7A6184-A0A3-4957-BEC8-F3E55B833A4E}"/>
+    <hyperlink ref="J2" r:id="rId2" xr:uid="{EFC059D7-FF37-4BE0-B7C4-41524A59BFAA}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59BC8B2E-A067-463D-937A-30E88D8BECD0}">
   <dimension ref="A1:N1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -17265,9 +17585,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4BBBCF5-BAC9-459C-ABE9-2526B85FD81E}">
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="4" max="4" width="17.54296875" customWidth="1"/>
@@ -17449,17 +17769,109 @@
         <v>25</v>
       </c>
     </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>3183</v>
+      </c>
+      <c r="B5" t="s">
+        <v>3184</v>
+      </c>
+      <c r="C5" t="s">
+        <v>3185</v>
+      </c>
+      <c r="D5" t="s">
+        <v>3186</v>
+      </c>
+      <c r="E5" t="s">
+        <v>3187</v>
+      </c>
+      <c r="F5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G5" t="s">
+        <v>3188</v>
+      </c>
+      <c r="H5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>3189</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>3190</v>
+      </c>
+      <c r="K5" t="s">
+        <v>3191</v>
+      </c>
+      <c r="L5" t="s">
+        <v>1689</v>
+      </c>
+      <c r="M5" t="s">
+        <v>3191</v>
+      </c>
+      <c r="N5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>3192</v>
+      </c>
+      <c r="B6" t="s">
+        <v>3193</v>
+      </c>
+      <c r="C6" t="s">
+        <v>3194</v>
+      </c>
+      <c r="D6" t="s">
+        <v>3195</v>
+      </c>
+      <c r="E6" t="s">
+        <v>3196</v>
+      </c>
+      <c r="F6" t="s">
+        <v>3198</v>
+      </c>
+      <c r="G6" t="s">
+        <v>3197</v>
+      </c>
+      <c r="H6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>3199</v>
+      </c>
+      <c r="J6" t="s">
+        <v>3200</v>
+      </c>
+      <c r="K6" t="s">
+        <v>3196</v>
+      </c>
+      <c r="L6" t="s">
+        <v>1689</v>
+      </c>
+      <c r="M6" t="s">
+        <v>3196</v>
+      </c>
+      <c r="N6" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="16" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1" xr:uid="{08280A44-0F58-4FDE-B5FD-3A95A0F423CB}"/>
     <hyperlink ref="J2" r:id="rId2" xr:uid="{85F326FF-BAE0-4072-815D-1EE4E7995C53}"/>
+    <hyperlink ref="I5" r:id="rId3" xr:uid="{38CEA448-03C1-4130-9D22-378144C1B83E}"/>
+    <hyperlink ref="J5" r:id="rId4" xr:uid="{178AE8D2-EC1F-4144-807A-F49730BDAEE7}"/>
+    <hyperlink ref="I6" r:id="rId5" xr:uid="{C6B22468-8A2D-4CA0-8E30-C5E1C054C475}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E9EB2F5-2977-493B-BFA2-5CD20F8A3BC4}">
   <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -17567,7 +17979,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69A1C46E-DEF3-467B-A5BD-162AB66E6A86}">
   <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -18650,7 +19062,114 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E05CC479-3669-40F7-BE22-BA5CFBFF29E9}">
+  <dimension ref="A1:N3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="5" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
+        <v>2906</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2907</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2908</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2909</v>
+      </c>
+      <c r="E2">
+        <v>860020675022</v>
+      </c>
+      <c r="F2" t="s">
+        <v>2910</v>
+      </c>
+      <c r="G2" t="s">
+        <v>2911</v>
+      </c>
+      <c r="H2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>2912</v>
+      </c>
+      <c r="J2" t="s">
+        <v>2913</v>
+      </c>
+      <c r="K2" t="s">
+        <v>2914</v>
+      </c>
+      <c r="L2" t="s">
+        <v>61</v>
+      </c>
+      <c r="M2" t="s">
+        <v>2915</v>
+      </c>
+      <c r="N2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="M3" s="7"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="I2" r:id="rId1" xr:uid="{BB2EDAB8-75EB-46D2-BA14-384BF06E1A6E}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE14AD29-8DB0-4C42-AB91-A73B867AE121}">
   <dimension ref="A1:N62"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -21444,113 +21963,6 @@
     <hyperlink ref="I56" r:id="rId51" xr:uid="{CE941FB5-1D41-41B6-9CFD-C1256871C52E}"/>
     <hyperlink ref="J57" r:id="rId52" xr:uid="{72ED46D3-1227-48FD-9800-7E78EA501F81}"/>
     <hyperlink ref="I57" r:id="rId53" xr:uid="{30F29B76-2559-4C1E-A762-9F9E7C2882A4}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E05CC479-3669-40F7-BE22-BA5CFBFF29E9}">
-  <dimension ref="A1:N3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
-  <cols>
-    <col min="5" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" t="s">
-        <v>2906</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2907</v>
-      </c>
-      <c r="C2" t="s">
-        <v>2908</v>
-      </c>
-      <c r="D2" t="s">
-        <v>2909</v>
-      </c>
-      <c r="E2">
-        <v>860020675022</v>
-      </c>
-      <c r="F2" t="s">
-        <v>2910</v>
-      </c>
-      <c r="G2" t="s">
-        <v>2911</v>
-      </c>
-      <c r="H2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>2912</v>
-      </c>
-      <c r="J2" t="s">
-        <v>2913</v>
-      </c>
-      <c r="K2" t="s">
-        <v>2914</v>
-      </c>
-      <c r="L2" t="s">
-        <v>61</v>
-      </c>
-      <c r="M2" t="s">
-        <v>2915</v>
-      </c>
-      <c r="N2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="M3" s="7"/>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="I2" r:id="rId1" xr:uid="{BB2EDAB8-75EB-46D2-BA14-384BF06E1A6E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,31 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72E7BE8E-5349-4841-9AC6-E1B10AAFD1F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{944AA604-5C9C-4A07-B4A8-289EF1B0937A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32280" yWindow="2235" windowWidth="29040" windowHeight="15720" firstSheet="10" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
     <sheet name="003 - Capacitors - THT Electrol" sheetId="17" r:id="rId2"/>
-    <sheet name="010 - Resistors - SMD" sheetId="4" r:id="rId3"/>
-    <sheet name="015 - Resistors - Shunt" sheetId="7" r:id="rId4"/>
-    <sheet name="020 - Inductor" sheetId="5" r:id="rId5"/>
-    <sheet name="023 - Inductor - CMM" sheetId="16" r:id="rId6"/>
-    <sheet name="030 - Diode - Rectifier" sheetId="9" r:id="rId7"/>
-    <sheet name="031 - Diode - Schottky" sheetId="11" r:id="rId8"/>
-    <sheet name="032 - Diode - TVS" sheetId="14" r:id="rId9"/>
-    <sheet name="033 - Diode - LED" sheetId="12" r:id="rId10"/>
-    <sheet name="040 - Fuses" sheetId="10" r:id="rId11"/>
-    <sheet name="043 - Transistors" sheetId="21" r:id="rId12"/>
-    <sheet name="045 - Crystal" sheetId="19" r:id="rId13"/>
-    <sheet name="050 - ICs - Analog" sheetId="2" r:id="rId14"/>
-    <sheet name="055 - Drivers" sheetId="20" r:id="rId15"/>
-    <sheet name="060 - ICs - Digital" sheetId="3" r:id="rId16"/>
-    <sheet name="070 - Power Supply - DCDC" sheetId="8" r:id="rId17"/>
-    <sheet name="090 - Processor" sheetId="18" r:id="rId18"/>
-    <sheet name="100 - Electromechanicals" sheetId="15" r:id="rId19"/>
-    <sheet name="110 - Connectors" sheetId="13" r:id="rId20"/>
+    <sheet name="004 - Capacitors - Film" sheetId="22" r:id="rId3"/>
+    <sheet name="010 - Resistors - SMD" sheetId="4" r:id="rId4"/>
+    <sheet name="015 - Resistors - Shunt" sheetId="7" r:id="rId5"/>
+    <sheet name="020 - Inductor" sheetId="5" r:id="rId6"/>
+    <sheet name="023 - Inductor - CMM" sheetId="16" r:id="rId7"/>
+    <sheet name="030 - Diode - Rectifier" sheetId="9" r:id="rId8"/>
+    <sheet name="031 - Diode - Schottky" sheetId="11" r:id="rId9"/>
+    <sheet name="032 - Diode - TVS" sheetId="14" r:id="rId10"/>
+    <sheet name="033 - Diode - LED" sheetId="12" r:id="rId11"/>
+    <sheet name="040 - Fuses" sheetId="10" r:id="rId12"/>
+    <sheet name="043 - Transistors" sheetId="21" r:id="rId13"/>
+    <sheet name="045 - Crystal" sheetId="19" r:id="rId14"/>
+    <sheet name="050 - ICs - Analog" sheetId="2" r:id="rId15"/>
+    <sheet name="055 - Drivers" sheetId="20" r:id="rId16"/>
+    <sheet name="060 - ICs - Digital" sheetId="3" r:id="rId17"/>
+    <sheet name="070 - Power Supply - DCDC" sheetId="8" r:id="rId18"/>
+    <sheet name="090 - Processor" sheetId="18" r:id="rId19"/>
+    <sheet name="100 - Electromechanicals" sheetId="15" r:id="rId20"/>
+    <sheet name="110 - Connectors" sheetId="13" r:id="rId21"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6417" uniqueCount="3201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6472" uniqueCount="3228">
   <si>
     <t>ID</t>
   </si>
@@ -9647,6 +9648,87 @@
   </si>
   <si>
     <t>https://www.mouser.es/ProductDetail/Murata-Power-Solutions/MGJ2D241505SC?qs=xLDY6iXSiQZSXeU7bFDLTA%3D%3D</t>
+  </si>
+  <si>
+    <t>003-0002</t>
+  </si>
+  <si>
+    <t>Condensadores electrolíticos de aluminio (con terminales radiales) WCAP-AT1H 330uF 200V 20%</t>
+  </si>
+  <si>
+    <t>330uF 200V ±20%</t>
+  </si>
+  <si>
+    <t>THT;D18xL35.5</t>
+  </si>
+  <si>
+    <t>860020675022</t>
+  </si>
+  <si>
+    <t>860241081001</t>
+  </si>
+  <si>
+    <t>710-860241081001</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/860241081001.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/860241081001?qs=amGC7iS6iy9AqvQPw6fWxw%3D%3D</t>
+  </si>
+  <si>
+    <t>CAP_18Dx35.5L</t>
+  </si>
+  <si>
+    <t>004-0001</t>
+  </si>
+  <si>
+    <t>Condensadores de película WCAP-FTXH 2.2 uF 10% 310V (AC)</t>
+  </si>
+  <si>
+    <t>2.2uF 630V 10%</t>
+  </si>
+  <si>
+    <t>THT;W16xL32</t>
+  </si>
+  <si>
+    <t>890414027011CS</t>
+  </si>
+  <si>
+    <t>710-890414027011CS</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/890414027011CS.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/890414027011CS?qs=a2MtRaTmNOQJkBZwIJ39Ww%3D%3D</t>
+  </si>
+  <si>
+    <t>001-0105</t>
+  </si>
+  <si>
+    <t>Condensadores de cerámica multicapa (MLCC- SMD/SMT) WCAP-CSMH 200V 0.1uF 1812 10%</t>
+  </si>
+  <si>
+    <t>200V 0.1uF X7R</t>
+  </si>
+  <si>
+    <t>1812</t>
+  </si>
+  <si>
+    <t>885342211002</t>
+  </si>
+  <si>
+    <t>710-885342211002</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/885342211002.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/885342211002?qs=MLItCLRbWsw2aK2K95e6Og%3D%3D</t>
+  </si>
+  <si>
+    <t>CAP SMD 1812</t>
   </si>
 </sst>
 </file>
@@ -9816,7 +9898,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -9874,6 +9956,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -10157,7 +10243,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N105"/>
+  <dimension ref="A1:N106"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="11.1796875" customWidth="1"/>
@@ -14791,6 +14877,50 @@
         <v>702</v>
       </c>
       <c r="N105" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="106" spans="1:14">
+      <c r="A106" s="4" t="s">
+        <v>3219</v>
+      </c>
+      <c r="B106" t="s">
+        <v>3220</v>
+      </c>
+      <c r="C106" s="37" t="s">
+        <v>3221</v>
+      </c>
+      <c r="D106" s="38" t="s">
+        <v>3222</v>
+      </c>
+      <c r="E106" s="36" t="s">
+        <v>3223</v>
+      </c>
+      <c r="F106" s="3" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G106" s="39" t="s">
+        <v>3224</v>
+      </c>
+      <c r="H106" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I106" s="27" t="s">
+        <v>3225</v>
+      </c>
+      <c r="J106" s="32" t="s">
+        <v>3226</v>
+      </c>
+      <c r="K106" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="L106" t="s">
+        <v>61</v>
+      </c>
+      <c r="M106" s="40" t="s">
+        <v>3227</v>
+      </c>
+      <c r="N106" s="40" t="s">
         <v>25</v>
       </c>
     </row>
@@ -14869,12 +14999,1036 @@
     <hyperlink ref="J104" r:id="rId70" xr:uid="{F9BBE179-DB54-4835-A14E-4454CA18A6AE}"/>
     <hyperlink ref="I105" r:id="rId71" xr:uid="{ABB87B28-8AD2-4BF8-B4D7-500E78A25472}"/>
     <hyperlink ref="J105" r:id="rId72" xr:uid="{F543587D-0A3E-429A-8125-C651D94CA2A5}"/>
+    <hyperlink ref="I106" r:id="rId73" xr:uid="{BD618E63-4947-48D9-B209-8DCC58D284A8}"/>
+    <hyperlink ref="J106" r:id="rId74" xr:uid="{C6D1135A-ABDE-44F6-88F2-FD4FF685F9BD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79E65951-BFD2-4888-A0A6-19D5130CB4A6}">
+  <dimension ref="A1:N23"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="2" max="2" width="41.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="25" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
+        <v>2003</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2004</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2005</v>
+      </c>
+      <c r="E2" t="s">
+        <v>2006</v>
+      </c>
+      <c r="F2" t="s">
+        <v>2007</v>
+      </c>
+      <c r="G2" t="s">
+        <v>2008</v>
+      </c>
+      <c r="H2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I2" t="s">
+        <v>2009</v>
+      </c>
+      <c r="J2" t="s">
+        <v>2010</v>
+      </c>
+      <c r="K2" t="s">
+        <v>2011</v>
+      </c>
+      <c r="L2" t="s">
+        <v>1910</v>
+      </c>
+      <c r="N2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>2012</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2013</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>2014</v>
+      </c>
+      <c r="E3" t="s">
+        <v>2015</v>
+      </c>
+      <c r="F3" t="s">
+        <v>2016</v>
+      </c>
+      <c r="G3" t="s">
+        <v>2017</v>
+      </c>
+      <c r="H3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I3" t="s">
+        <v>2018</v>
+      </c>
+      <c r="J3" t="s">
+        <v>2019</v>
+      </c>
+      <c r="K3" t="s">
+        <v>2011</v>
+      </c>
+      <c r="L3" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M3" t="s">
+        <v>2014</v>
+      </c>
+      <c r="N3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>2020</v>
+      </c>
+      <c r="B4" t="s">
+        <v>2021</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4">
+        <v>402</v>
+      </c>
+      <c r="E4" t="s">
+        <v>2022</v>
+      </c>
+      <c r="F4" t="s">
+        <v>2023</v>
+      </c>
+      <c r="G4" t="s">
+        <v>2024</v>
+      </c>
+      <c r="H4" t="s">
+        <v>69</v>
+      </c>
+      <c r="I4" t="s">
+        <v>2025</v>
+      </c>
+      <c r="J4" t="s">
+        <v>2026</v>
+      </c>
+      <c r="K4" t="s">
+        <v>2011</v>
+      </c>
+      <c r="L4" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M4" t="s">
+        <v>2027</v>
+      </c>
+      <c r="N4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>2028</v>
+      </c>
+      <c r="B5" t="s">
+        <v>2029</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s">
+        <v>2030</v>
+      </c>
+      <c r="E5" t="s">
+        <v>2031</v>
+      </c>
+      <c r="F5" t="s">
+        <v>1858</v>
+      </c>
+      <c r="G5" t="s">
+        <v>2032</v>
+      </c>
+      <c r="H5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I5" t="s">
+        <v>2033</v>
+      </c>
+      <c r="J5" t="s">
+        <v>2034</v>
+      </c>
+      <c r="K5" t="s">
+        <v>1918</v>
+      </c>
+      <c r="L5" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M5" t="s">
+        <v>2030</v>
+      </c>
+      <c r="N5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>2035</v>
+      </c>
+      <c r="B6" t="s">
+        <v>2036</v>
+      </c>
+      <c r="C6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" t="s">
+        <v>2037</v>
+      </c>
+      <c r="E6" t="s">
+        <v>2038</v>
+      </c>
+      <c r="F6" t="s">
+        <v>2039</v>
+      </c>
+      <c r="G6" t="s">
+        <v>2040</v>
+      </c>
+      <c r="H6" t="s">
+        <v>69</v>
+      </c>
+      <c r="I6" t="s">
+        <v>2041</v>
+      </c>
+      <c r="J6" t="s">
+        <v>2042</v>
+      </c>
+      <c r="K6" t="s">
+        <v>2043</v>
+      </c>
+      <c r="L6" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M6" t="s">
+        <v>2044</v>
+      </c>
+      <c r="N6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B7" t="s">
+        <v>2046</v>
+      </c>
+      <c r="C7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E7" t="s">
+        <v>2048</v>
+      </c>
+      <c r="F7" t="s">
+        <v>1696</v>
+      </c>
+      <c r="G7" t="s">
+        <v>2049</v>
+      </c>
+      <c r="H7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I7" t="s">
+        <v>2050</v>
+      </c>
+      <c r="J7" t="s">
+        <v>2051</v>
+      </c>
+      <c r="K7" t="s">
+        <v>2052</v>
+      </c>
+      <c r="L7" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M7" t="s">
+        <v>2047</v>
+      </c>
+      <c r="N7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>2053</v>
+      </c>
+      <c r="B8" t="s">
+        <v>2054</v>
+      </c>
+      <c r="C8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1947</v>
+      </c>
+      <c r="E8" t="s">
+        <v>2055</v>
+      </c>
+      <c r="F8" t="s">
+        <v>2056</v>
+      </c>
+      <c r="G8" t="s">
+        <v>2057</v>
+      </c>
+      <c r="H8" t="s">
+        <v>69</v>
+      </c>
+      <c r="I8" t="s">
+        <v>2058</v>
+      </c>
+      <c r="J8" t="s">
+        <v>2059</v>
+      </c>
+      <c r="K8" t="s">
+        <v>2052</v>
+      </c>
+      <c r="L8" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M8" t="s">
+        <v>2060</v>
+      </c>
+      <c r="N8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>2061</v>
+      </c>
+      <c r="B9" t="s">
+        <v>2062</v>
+      </c>
+      <c r="C9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1947</v>
+      </c>
+      <c r="E9" t="s">
+        <v>2063</v>
+      </c>
+      <c r="F9" t="s">
+        <v>2064</v>
+      </c>
+      <c r="G9" t="s">
+        <v>2065</v>
+      </c>
+      <c r="H9" t="s">
+        <v>69</v>
+      </c>
+      <c r="I9" t="s">
+        <v>2066</v>
+      </c>
+      <c r="J9" t="s">
+        <v>2067</v>
+      </c>
+      <c r="K9" t="s">
+        <v>2052</v>
+      </c>
+      <c r="L9" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M9" t="s">
+        <v>1947</v>
+      </c>
+      <c r="N9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B10" t="s">
+        <v>2069</v>
+      </c>
+      <c r="C10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" t="s">
+        <v>2070</v>
+      </c>
+      <c r="E10" t="s">
+        <v>2070</v>
+      </c>
+      <c r="F10" t="s">
+        <v>1981</v>
+      </c>
+      <c r="G10" t="s">
+        <v>2071</v>
+      </c>
+      <c r="H10" t="s">
+        <v>69</v>
+      </c>
+      <c r="I10" t="s">
+        <v>2072</v>
+      </c>
+      <c r="J10" t="s">
+        <v>2073</v>
+      </c>
+      <c r="K10" t="s">
+        <v>2074</v>
+      </c>
+      <c r="L10" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M10" t="s">
+        <v>1856</v>
+      </c>
+      <c r="N10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" t="s">
+        <v>2075</v>
+      </c>
+      <c r="B11" t="s">
+        <v>2076</v>
+      </c>
+      <c r="C11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" t="s">
+        <v>1856</v>
+      </c>
+      <c r="E11" t="s">
+        <v>2077</v>
+      </c>
+      <c r="F11" t="s">
+        <v>945</v>
+      </c>
+      <c r="G11" t="s">
+        <v>2078</v>
+      </c>
+      <c r="H11" t="s">
+        <v>69</v>
+      </c>
+      <c r="I11" t="s">
+        <v>2079</v>
+      </c>
+      <c r="J11" t="s">
+        <v>2080</v>
+      </c>
+      <c r="K11" t="s">
+        <v>2081</v>
+      </c>
+      <c r="L11" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M11" t="s">
+        <v>1856</v>
+      </c>
+      <c r="N11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" t="s">
+        <v>2082</v>
+      </c>
+      <c r="B12" t="s">
+        <v>2083</v>
+      </c>
+      <c r="C12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1856</v>
+      </c>
+      <c r="E12" t="s">
+        <v>2084</v>
+      </c>
+      <c r="F12" t="s">
+        <v>2085</v>
+      </c>
+      <c r="G12" t="s">
+        <v>2086</v>
+      </c>
+      <c r="H12" t="s">
+        <v>69</v>
+      </c>
+      <c r="I12" t="s">
+        <v>2087</v>
+      </c>
+      <c r="J12" t="s">
+        <v>2088</v>
+      </c>
+      <c r="K12" t="s">
+        <v>2074</v>
+      </c>
+      <c r="L12" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M12" t="s">
+        <v>1856</v>
+      </c>
+      <c r="N12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B13" t="s">
+        <v>2090</v>
+      </c>
+      <c r="C13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E13" t="s">
+        <v>2092</v>
+      </c>
+      <c r="F13" t="s">
+        <v>2007</v>
+      </c>
+      <c r="G13" t="s">
+        <v>2093</v>
+      </c>
+      <c r="H13" t="s">
+        <v>69</v>
+      </c>
+      <c r="I13" t="s">
+        <v>2094</v>
+      </c>
+      <c r="J13" t="s">
+        <v>2095</v>
+      </c>
+      <c r="K13" t="s">
+        <v>2096</v>
+      </c>
+      <c r="L13" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M13" t="s">
+        <v>2091</v>
+      </c>
+      <c r="N13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" t="s">
+        <v>2097</v>
+      </c>
+      <c r="B14" t="s">
+        <v>2098</v>
+      </c>
+      <c r="C14" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" t="s">
+        <v>2099</v>
+      </c>
+      <c r="E14">
+        <v>824012823</v>
+      </c>
+      <c r="F14" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G14" t="s">
+        <v>2101</v>
+      </c>
+      <c r="H14" t="s">
+        <v>2102</v>
+      </c>
+      <c r="I14" t="s">
+        <v>2103</v>
+      </c>
+      <c r="J14" t="s">
+        <v>2104</v>
+      </c>
+      <c r="K14">
+        <v>824012823</v>
+      </c>
+      <c r="L14" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M14" t="s">
+        <v>2105</v>
+      </c>
+      <c r="N14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" t="s">
+        <v>2106</v>
+      </c>
+      <c r="B15" t="s">
+        <v>2107</v>
+      </c>
+      <c r="C15" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" t="s">
+        <v>1856</v>
+      </c>
+      <c r="E15" t="s">
+        <v>2108</v>
+      </c>
+      <c r="F15" t="s">
+        <v>2085</v>
+      </c>
+      <c r="G15" t="s">
+        <v>2109</v>
+      </c>
+      <c r="H15" t="s">
+        <v>69</v>
+      </c>
+      <c r="I15" t="s">
+        <v>2110</v>
+      </c>
+      <c r="J15" t="s">
+        <v>2111</v>
+      </c>
+      <c r="K15" t="s">
+        <v>1943</v>
+      </c>
+      <c r="L15" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M15" t="s">
+        <v>1856</v>
+      </c>
+      <c r="N15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" t="s">
+        <v>2112</v>
+      </c>
+      <c r="B16" t="s">
+        <v>2113</v>
+      </c>
+      <c r="C16" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" t="s">
+        <v>1856</v>
+      </c>
+      <c r="E16" t="s">
+        <v>2114</v>
+      </c>
+      <c r="F16" t="s">
+        <v>2023</v>
+      </c>
+      <c r="G16" t="s">
+        <v>2115</v>
+      </c>
+      <c r="H16" t="s">
+        <v>69</v>
+      </c>
+      <c r="I16" t="s">
+        <v>2116</v>
+      </c>
+      <c r="J16" t="s">
+        <v>2116</v>
+      </c>
+      <c r="K16" t="s">
+        <v>2117</v>
+      </c>
+      <c r="L16" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M16" t="s">
+        <v>1856</v>
+      </c>
+      <c r="N16" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" t="s">
+        <v>2118</v>
+      </c>
+      <c r="B17" t="s">
+        <v>2119</v>
+      </c>
+      <c r="C17" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" t="s">
+        <v>2120</v>
+      </c>
+      <c r="E17" t="s">
+        <v>2121</v>
+      </c>
+      <c r="F17" t="s">
+        <v>1877</v>
+      </c>
+      <c r="G17" t="s">
+        <v>2122</v>
+      </c>
+      <c r="H17" t="s">
+        <v>69</v>
+      </c>
+      <c r="I17" t="s">
+        <v>2123</v>
+      </c>
+      <c r="J17" t="s">
+        <v>2124</v>
+      </c>
+      <c r="K17" t="s">
+        <v>2125</v>
+      </c>
+      <c r="L17" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M17" t="s">
+        <v>2120</v>
+      </c>
+      <c r="N17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" t="s">
+        <v>2126</v>
+      </c>
+      <c r="B18" t="s">
+        <v>2127</v>
+      </c>
+      <c r="C18" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" t="s">
+        <v>1856</v>
+      </c>
+      <c r="E18" t="s">
+        <v>2128</v>
+      </c>
+      <c r="F18" t="s">
+        <v>2129</v>
+      </c>
+      <c r="G18" t="s">
+        <v>2130</v>
+      </c>
+      <c r="H18" t="s">
+        <v>69</v>
+      </c>
+      <c r="I18" t="s">
+        <v>2131</v>
+      </c>
+      <c r="J18" t="s">
+        <v>2132</v>
+      </c>
+      <c r="K18" t="s">
+        <v>1943</v>
+      </c>
+      <c r="L18" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M18" t="s">
+        <v>1856</v>
+      </c>
+      <c r="N18" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" t="s">
+        <v>2133</v>
+      </c>
+      <c r="B19" t="s">
+        <v>2134</v>
+      </c>
+      <c r="C19" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" t="s">
+        <v>2135</v>
+      </c>
+      <c r="E19" t="s">
+        <v>2136</v>
+      </c>
+      <c r="F19" t="s">
+        <v>20</v>
+      </c>
+      <c r="G19" t="s">
+        <v>2137</v>
+      </c>
+      <c r="H19" t="s">
+        <v>69</v>
+      </c>
+      <c r="I19" t="s">
+        <v>2138</v>
+      </c>
+      <c r="J19" t="s">
+        <v>2139</v>
+      </c>
+      <c r="K19" t="s">
+        <v>2136</v>
+      </c>
+      <c r="L19" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M19" t="s">
+        <v>2136</v>
+      </c>
+      <c r="N19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" t="s">
+        <v>2140</v>
+      </c>
+      <c r="B20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" t="s">
+        <v>2142</v>
+      </c>
+      <c r="E20" t="s">
+        <v>2143</v>
+      </c>
+      <c r="F20" t="s">
+        <v>1658</v>
+      </c>
+      <c r="G20" t="s">
+        <v>2144</v>
+      </c>
+      <c r="H20" t="s">
+        <v>69</v>
+      </c>
+      <c r="I20" t="s">
+        <v>2145</v>
+      </c>
+      <c r="J20" t="s">
+        <v>2146</v>
+      </c>
+      <c r="K20" t="s">
+        <v>2143</v>
+      </c>
+      <c r="L20" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M20" t="s">
+        <v>2147</v>
+      </c>
+      <c r="N20" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" t="s">
+        <v>2148</v>
+      </c>
+      <c r="B21" t="s">
+        <v>2149</v>
+      </c>
+      <c r="C21" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" t="s">
+        <v>1856</v>
+      </c>
+      <c r="E21" t="s">
+        <v>2150</v>
+      </c>
+      <c r="F21" t="s">
+        <v>1858</v>
+      </c>
+      <c r="G21" t="s">
+        <v>2151</v>
+      </c>
+      <c r="H21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I21" t="s">
+        <v>2152</v>
+      </c>
+      <c r="J21" t="s">
+        <v>2153</v>
+      </c>
+      <c r="K21" t="s">
+        <v>2154</v>
+      </c>
+      <c r="L21" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M21" t="s">
+        <v>1856</v>
+      </c>
+      <c r="N21" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" t="s">
+        <v>2155</v>
+      </c>
+      <c r="B22" t="s">
+        <v>2156</v>
+      </c>
+      <c r="C22" t="s">
+        <v>16</v>
+      </c>
+      <c r="D22" t="s">
+        <v>2157</v>
+      </c>
+      <c r="E22" t="s">
+        <v>2158</v>
+      </c>
+      <c r="F22" t="s">
+        <v>1696</v>
+      </c>
+      <c r="G22" t="s">
+        <v>2159</v>
+      </c>
+      <c r="H22" t="s">
+        <v>69</v>
+      </c>
+      <c r="I22" t="s">
+        <v>2160</v>
+      </c>
+      <c r="J22" t="s">
+        <v>2161</v>
+      </c>
+      <c r="K22" t="s">
+        <v>2052</v>
+      </c>
+      <c r="L22" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M22" t="s">
+        <v>1904</v>
+      </c>
+      <c r="N22" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" t="s">
+        <v>2162</v>
+      </c>
+      <c r="B23" t="s">
+        <v>2163</v>
+      </c>
+      <c r="C23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" t="s">
+        <v>1947</v>
+      </c>
+      <c r="E23" t="s">
+        <v>2164</v>
+      </c>
+      <c r="F23" t="s">
+        <v>1696</v>
+      </c>
+      <c r="G23" t="s">
+        <v>2165</v>
+      </c>
+      <c r="H23" t="s">
+        <v>69</v>
+      </c>
+      <c r="I23" t="s">
+        <v>2166</v>
+      </c>
+      <c r="J23" t="s">
+        <v>2167</v>
+      </c>
+      <c r="K23" t="s">
+        <v>2052</v>
+      </c>
+      <c r="L23" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M23" t="s">
+        <v>2060</v>
+      </c>
+      <c r="N23" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89BFA1EF-29B2-41E4-A9D1-F8E90A663FA1}">
   <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -15959,7 +17113,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B6F0D32-9CE2-4DF7-927E-42E7BA331F12}">
   <dimension ref="A1:O21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -16928,7 +18082,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FAFF3B6-AF11-4BFB-8078-829FF6F2F366}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -17030,7 +18184,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E5535EA-E186-4751-BC7F-9B3A0221302E}">
   <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -17179,7 +18333,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C98E1A12-072F-4773-8CB5-47FFE077E85B}">
   <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -17429,7 +18583,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{201D74E2-3547-4E9B-8216-09A22645AC2A}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -17531,7 +18685,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59BC8B2E-A067-463D-937A-30E88D8BECD0}">
   <dimension ref="A1:N1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -17585,7 +18739,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4BBBCF5-BAC9-459C-ABE9-2526B85FD81E}">
   <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -17871,7 +19025,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E9EB2F5-2977-493B-BFA2-5CD20F8A3BC4}">
   <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -17979,7 +19133,158 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E05CC479-3669-40F7-BE22-BA5CFBFF29E9}">
+  <dimension ref="A1:N3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="5" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
+        <v>2906</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2907</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2908</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2909</v>
+      </c>
+      <c r="E2" s="36" t="s">
+        <v>3205</v>
+      </c>
+      <c r="F2" t="s">
+        <v>2910</v>
+      </c>
+      <c r="G2" t="s">
+        <v>2911</v>
+      </c>
+      <c r="H2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>2912</v>
+      </c>
+      <c r="J2" t="s">
+        <v>2913</v>
+      </c>
+      <c r="K2" t="s">
+        <v>2914</v>
+      </c>
+      <c r="L2" t="s">
+        <v>61</v>
+      </c>
+      <c r="M2" t="s">
+        <v>2915</v>
+      </c>
+      <c r="N2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>3201</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3202</v>
+      </c>
+      <c r="C3" t="s">
+        <v>3203</v>
+      </c>
+      <c r="D3" t="s">
+        <v>3204</v>
+      </c>
+      <c r="E3" s="36" t="s">
+        <v>3206</v>
+      </c>
+      <c r="F3" t="s">
+        <v>2910</v>
+      </c>
+      <c r="G3" t="s">
+        <v>3207</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>3208</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>3209</v>
+      </c>
+      <c r="K3" t="s">
+        <v>2914</v>
+      </c>
+      <c r="L3" t="s">
+        <v>61</v>
+      </c>
+      <c r="M3" t="s">
+        <v>3210</v>
+      </c>
+      <c r="N3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="16" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="I2" r:id="rId1" xr:uid="{BB2EDAB8-75EB-46D2-BA14-384BF06E1A6E}"/>
+    <hyperlink ref="I3" r:id="rId2" xr:uid="{8F6B3EB5-F217-4353-ABA9-F461982FB5ED}"/>
+    <hyperlink ref="J3" r:id="rId3" xr:uid="{E90B210E-79B4-494B-B985-7D11C4705F7B}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69A1C46E-DEF3-467B-A5BD-162AB66E6A86}">
   <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -19062,114 +20367,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E05CC479-3669-40F7-BE22-BA5CFBFF29E9}">
-  <dimension ref="A1:N3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
-  <cols>
-    <col min="5" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" t="s">
-        <v>2906</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2907</v>
-      </c>
-      <c r="C2" t="s">
-        <v>2908</v>
-      </c>
-      <c r="D2" t="s">
-        <v>2909</v>
-      </c>
-      <c r="E2">
-        <v>860020675022</v>
-      </c>
-      <c r="F2" t="s">
-        <v>2910</v>
-      </c>
-      <c r="G2" t="s">
-        <v>2911</v>
-      </c>
-      <c r="H2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>2912</v>
-      </c>
-      <c r="J2" t="s">
-        <v>2913</v>
-      </c>
-      <c r="K2" t="s">
-        <v>2914</v>
-      </c>
-      <c r="L2" t="s">
-        <v>61</v>
-      </c>
-      <c r="M2" t="s">
-        <v>2915</v>
-      </c>
-      <c r="N2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="M3" s="7"/>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="I2" r:id="rId1" xr:uid="{BB2EDAB8-75EB-46D2-BA14-384BF06E1A6E}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE14AD29-8DB0-4C42-AB91-A73B867AE121}">
   <dimension ref="A1:N62"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -21969,6 +23167,110 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E940ACE-72CF-4504-B730-2719484575BC}">
+  <dimension ref="A1:N3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="5" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
+        <v>3211</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3212</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3213</v>
+      </c>
+      <c r="D2" t="s">
+        <v>3214</v>
+      </c>
+      <c r="E2" s="36" t="s">
+        <v>3215</v>
+      </c>
+      <c r="F2" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G2" t="s">
+        <v>3216</v>
+      </c>
+      <c r="H2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>3217</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>3218</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="L2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="E3" s="36"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="I2" r:id="rId1" xr:uid="{A3195937-552B-4025-8C26-81ADB44BFFC2}"/>
+    <hyperlink ref="J2" r:id="rId2" xr:uid="{52A98722-6674-4772-ABA0-DFA6125FAC08}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60E8291E-4293-4634-B9E9-80CB520CA181}">
   <dimension ref="A1:N151"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -28697,7 +29999,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81F9848D-6D60-47C0-9F84-A561FE4F106E}">
   <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -28939,7 +30241,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01C6B0FD-D8A3-44EC-9532-03DDA232F922}">
   <dimension ref="A1:N1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -28993,7 +30295,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D956EFE-E955-4E62-8478-2294E6413DC1}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -29094,7 +30396,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{652841DA-3619-42EE-A536-61B58BE1B457}">
   <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -29506,7 +30808,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FE2008B-4BF4-4C9A-883A-FEE5873AEAF4}">
   <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -30101,1026 +31403,4 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79E65951-BFD2-4888-A0A6-19D5130CB4A6}">
-  <dimension ref="A1:N23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
-  <cols>
-    <col min="2" max="2" width="41.1796875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="25" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="25" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" t="s">
-        <v>2003</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2004</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>2005</v>
-      </c>
-      <c r="E2" t="s">
-        <v>2006</v>
-      </c>
-      <c r="F2" t="s">
-        <v>2007</v>
-      </c>
-      <c r="G2" t="s">
-        <v>2008</v>
-      </c>
-      <c r="H2" t="s">
-        <v>69</v>
-      </c>
-      <c r="I2" t="s">
-        <v>2009</v>
-      </c>
-      <c r="J2" t="s">
-        <v>2010</v>
-      </c>
-      <c r="K2" t="s">
-        <v>2011</v>
-      </c>
-      <c r="L2" t="s">
-        <v>1910</v>
-      </c>
-      <c r="N2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
-        <v>2012</v>
-      </c>
-      <c r="B3" t="s">
-        <v>2013</v>
-      </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" t="s">
-        <v>2014</v>
-      </c>
-      <c r="E3" t="s">
-        <v>2015</v>
-      </c>
-      <c r="F3" t="s">
-        <v>2016</v>
-      </c>
-      <c r="G3" t="s">
-        <v>2017</v>
-      </c>
-      <c r="H3" t="s">
-        <v>69</v>
-      </c>
-      <c r="I3" t="s">
-        <v>2018</v>
-      </c>
-      <c r="J3" t="s">
-        <v>2019</v>
-      </c>
-      <c r="K3" t="s">
-        <v>2011</v>
-      </c>
-      <c r="L3" t="s">
-        <v>1910</v>
-      </c>
-      <c r="M3" t="s">
-        <v>2014</v>
-      </c>
-      <c r="N3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" t="s">
-        <v>2020</v>
-      </c>
-      <c r="B4" t="s">
-        <v>2021</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4">
-        <v>402</v>
-      </c>
-      <c r="E4" t="s">
-        <v>2022</v>
-      </c>
-      <c r="F4" t="s">
-        <v>2023</v>
-      </c>
-      <c r="G4" t="s">
-        <v>2024</v>
-      </c>
-      <c r="H4" t="s">
-        <v>69</v>
-      </c>
-      <c r="I4" t="s">
-        <v>2025</v>
-      </c>
-      <c r="J4" t="s">
-        <v>2026</v>
-      </c>
-      <c r="K4" t="s">
-        <v>2011</v>
-      </c>
-      <c r="L4" t="s">
-        <v>1910</v>
-      </c>
-      <c r="M4" t="s">
-        <v>2027</v>
-      </c>
-      <c r="N4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" t="s">
-        <v>2028</v>
-      </c>
-      <c r="B5" t="s">
-        <v>2029</v>
-      </c>
-      <c r="C5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" t="s">
-        <v>2030</v>
-      </c>
-      <c r="E5" t="s">
-        <v>2031</v>
-      </c>
-      <c r="F5" t="s">
-        <v>1858</v>
-      </c>
-      <c r="G5" t="s">
-        <v>2032</v>
-      </c>
-      <c r="H5" t="s">
-        <v>69</v>
-      </c>
-      <c r="I5" t="s">
-        <v>2033</v>
-      </c>
-      <c r="J5" t="s">
-        <v>2034</v>
-      </c>
-      <c r="K5" t="s">
-        <v>1918</v>
-      </c>
-      <c r="L5" t="s">
-        <v>1910</v>
-      </c>
-      <c r="M5" t="s">
-        <v>2030</v>
-      </c>
-      <c r="N5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" t="s">
-        <v>2035</v>
-      </c>
-      <c r="B6" t="s">
-        <v>2036</v>
-      </c>
-      <c r="C6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" t="s">
-        <v>2037</v>
-      </c>
-      <c r="E6" t="s">
-        <v>2038</v>
-      </c>
-      <c r="F6" t="s">
-        <v>2039</v>
-      </c>
-      <c r="G6" t="s">
-        <v>2040</v>
-      </c>
-      <c r="H6" t="s">
-        <v>69</v>
-      </c>
-      <c r="I6" t="s">
-        <v>2041</v>
-      </c>
-      <c r="J6" t="s">
-        <v>2042</v>
-      </c>
-      <c r="K6" t="s">
-        <v>2043</v>
-      </c>
-      <c r="L6" t="s">
-        <v>1910</v>
-      </c>
-      <c r="M6" t="s">
-        <v>2044</v>
-      </c>
-      <c r="N6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" t="s">
-        <v>2045</v>
-      </c>
-      <c r="B7" t="s">
-        <v>2046</v>
-      </c>
-      <c r="C7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E7" t="s">
-        <v>2048</v>
-      </c>
-      <c r="F7" t="s">
-        <v>1696</v>
-      </c>
-      <c r="G7" t="s">
-        <v>2049</v>
-      </c>
-      <c r="H7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I7" t="s">
-        <v>2050</v>
-      </c>
-      <c r="J7" t="s">
-        <v>2051</v>
-      </c>
-      <c r="K7" t="s">
-        <v>2052</v>
-      </c>
-      <c r="L7" t="s">
-        <v>1910</v>
-      </c>
-      <c r="M7" t="s">
-        <v>2047</v>
-      </c>
-      <c r="N7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" t="s">
-        <v>2053</v>
-      </c>
-      <c r="B8" t="s">
-        <v>2054</v>
-      </c>
-      <c r="C8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" t="s">
-        <v>1947</v>
-      </c>
-      <c r="E8" t="s">
-        <v>2055</v>
-      </c>
-      <c r="F8" t="s">
-        <v>2056</v>
-      </c>
-      <c r="G8" t="s">
-        <v>2057</v>
-      </c>
-      <c r="H8" t="s">
-        <v>69</v>
-      </c>
-      <c r="I8" t="s">
-        <v>2058</v>
-      </c>
-      <c r="J8" t="s">
-        <v>2059</v>
-      </c>
-      <c r="K8" t="s">
-        <v>2052</v>
-      </c>
-      <c r="L8" t="s">
-        <v>1910</v>
-      </c>
-      <c r="M8" t="s">
-        <v>2060</v>
-      </c>
-      <c r="N8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" t="s">
-        <v>2061</v>
-      </c>
-      <c r="B9" t="s">
-        <v>2062</v>
-      </c>
-      <c r="C9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" t="s">
-        <v>1947</v>
-      </c>
-      <c r="E9" t="s">
-        <v>2063</v>
-      </c>
-      <c r="F9" t="s">
-        <v>2064</v>
-      </c>
-      <c r="G9" t="s">
-        <v>2065</v>
-      </c>
-      <c r="H9" t="s">
-        <v>69</v>
-      </c>
-      <c r="I9" t="s">
-        <v>2066</v>
-      </c>
-      <c r="J9" t="s">
-        <v>2067</v>
-      </c>
-      <c r="K9" t="s">
-        <v>2052</v>
-      </c>
-      <c r="L9" t="s">
-        <v>1910</v>
-      </c>
-      <c r="M9" t="s">
-        <v>1947</v>
-      </c>
-      <c r="N9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" t="s">
-        <v>2068</v>
-      </c>
-      <c r="B10" t="s">
-        <v>2069</v>
-      </c>
-      <c r="C10" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" t="s">
-        <v>2070</v>
-      </c>
-      <c r="E10" t="s">
-        <v>2070</v>
-      </c>
-      <c r="F10" t="s">
-        <v>1981</v>
-      </c>
-      <c r="G10" t="s">
-        <v>2071</v>
-      </c>
-      <c r="H10" t="s">
-        <v>69</v>
-      </c>
-      <c r="I10" t="s">
-        <v>2072</v>
-      </c>
-      <c r="J10" t="s">
-        <v>2073</v>
-      </c>
-      <c r="K10" t="s">
-        <v>2074</v>
-      </c>
-      <c r="L10" t="s">
-        <v>1910</v>
-      </c>
-      <c r="M10" t="s">
-        <v>1856</v>
-      </c>
-      <c r="N10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" t="s">
-        <v>2075</v>
-      </c>
-      <c r="B11" t="s">
-        <v>2076</v>
-      </c>
-      <c r="C11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" t="s">
-        <v>1856</v>
-      </c>
-      <c r="E11" t="s">
-        <v>2077</v>
-      </c>
-      <c r="F11" t="s">
-        <v>945</v>
-      </c>
-      <c r="G11" t="s">
-        <v>2078</v>
-      </c>
-      <c r="H11" t="s">
-        <v>69</v>
-      </c>
-      <c r="I11" t="s">
-        <v>2079</v>
-      </c>
-      <c r="J11" t="s">
-        <v>2080</v>
-      </c>
-      <c r="K11" t="s">
-        <v>2081</v>
-      </c>
-      <c r="L11" t="s">
-        <v>1910</v>
-      </c>
-      <c r="M11" t="s">
-        <v>1856</v>
-      </c>
-      <c r="N11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" t="s">
-        <v>2082</v>
-      </c>
-      <c r="B12" t="s">
-        <v>2083</v>
-      </c>
-      <c r="C12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" t="s">
-        <v>1856</v>
-      </c>
-      <c r="E12" t="s">
-        <v>2084</v>
-      </c>
-      <c r="F12" t="s">
-        <v>2085</v>
-      </c>
-      <c r="G12" t="s">
-        <v>2086</v>
-      </c>
-      <c r="H12" t="s">
-        <v>69</v>
-      </c>
-      <c r="I12" t="s">
-        <v>2087</v>
-      </c>
-      <c r="J12" t="s">
-        <v>2088</v>
-      </c>
-      <c r="K12" t="s">
-        <v>2074</v>
-      </c>
-      <c r="L12" t="s">
-        <v>1910</v>
-      </c>
-      <c r="M12" t="s">
-        <v>1856</v>
-      </c>
-      <c r="N12" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" t="s">
-        <v>2089</v>
-      </c>
-      <c r="B13" t="s">
-        <v>2090</v>
-      </c>
-      <c r="C13" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" t="s">
-        <v>2091</v>
-      </c>
-      <c r="E13" t="s">
-        <v>2092</v>
-      </c>
-      <c r="F13" t="s">
-        <v>2007</v>
-      </c>
-      <c r="G13" t="s">
-        <v>2093</v>
-      </c>
-      <c r="H13" t="s">
-        <v>69</v>
-      </c>
-      <c r="I13" t="s">
-        <v>2094</v>
-      </c>
-      <c r="J13" t="s">
-        <v>2095</v>
-      </c>
-      <c r="K13" t="s">
-        <v>2096</v>
-      </c>
-      <c r="L13" t="s">
-        <v>1910</v>
-      </c>
-      <c r="M13" t="s">
-        <v>2091</v>
-      </c>
-      <c r="N13" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" t="s">
-        <v>2097</v>
-      </c>
-      <c r="B14" t="s">
-        <v>2098</v>
-      </c>
-      <c r="C14" t="s">
-        <v>16</v>
-      </c>
-      <c r="D14" t="s">
-        <v>2099</v>
-      </c>
-      <c r="E14">
-        <v>824012823</v>
-      </c>
-      <c r="F14" t="s">
-        <v>2100</v>
-      </c>
-      <c r="G14" t="s">
-        <v>2101</v>
-      </c>
-      <c r="H14" t="s">
-        <v>2102</v>
-      </c>
-      <c r="I14" t="s">
-        <v>2103</v>
-      </c>
-      <c r="J14" t="s">
-        <v>2104</v>
-      </c>
-      <c r="K14">
-        <v>824012823</v>
-      </c>
-      <c r="L14" t="s">
-        <v>1910</v>
-      </c>
-      <c r="M14" t="s">
-        <v>2105</v>
-      </c>
-      <c r="N14" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="A15" t="s">
-        <v>2106</v>
-      </c>
-      <c r="B15" t="s">
-        <v>2107</v>
-      </c>
-      <c r="C15" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15" t="s">
-        <v>1856</v>
-      </c>
-      <c r="E15" t="s">
-        <v>2108</v>
-      </c>
-      <c r="F15" t="s">
-        <v>2085</v>
-      </c>
-      <c r="G15" t="s">
-        <v>2109</v>
-      </c>
-      <c r="H15" t="s">
-        <v>69</v>
-      </c>
-      <c r="I15" t="s">
-        <v>2110</v>
-      </c>
-      <c r="J15" t="s">
-        <v>2111</v>
-      </c>
-      <c r="K15" t="s">
-        <v>1943</v>
-      </c>
-      <c r="L15" t="s">
-        <v>1910</v>
-      </c>
-      <c r="M15" t="s">
-        <v>1856</v>
-      </c>
-      <c r="N15" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="A16" t="s">
-        <v>2112</v>
-      </c>
-      <c r="B16" t="s">
-        <v>2113</v>
-      </c>
-      <c r="C16" t="s">
-        <v>16</v>
-      </c>
-      <c r="D16" t="s">
-        <v>1856</v>
-      </c>
-      <c r="E16" t="s">
-        <v>2114</v>
-      </c>
-      <c r="F16" t="s">
-        <v>2023</v>
-      </c>
-      <c r="G16" t="s">
-        <v>2115</v>
-      </c>
-      <c r="H16" t="s">
-        <v>69</v>
-      </c>
-      <c r="I16" t="s">
-        <v>2116</v>
-      </c>
-      <c r="J16" t="s">
-        <v>2116</v>
-      </c>
-      <c r="K16" t="s">
-        <v>2117</v>
-      </c>
-      <c r="L16" t="s">
-        <v>1910</v>
-      </c>
-      <c r="M16" t="s">
-        <v>1856</v>
-      </c>
-      <c r="N16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
-      <c r="A17" t="s">
-        <v>2118</v>
-      </c>
-      <c r="B17" t="s">
-        <v>2119</v>
-      </c>
-      <c r="C17" t="s">
-        <v>16</v>
-      </c>
-      <c r="D17" t="s">
-        <v>2120</v>
-      </c>
-      <c r="E17" t="s">
-        <v>2121</v>
-      </c>
-      <c r="F17" t="s">
-        <v>1877</v>
-      </c>
-      <c r="G17" t="s">
-        <v>2122</v>
-      </c>
-      <c r="H17" t="s">
-        <v>69</v>
-      </c>
-      <c r="I17" t="s">
-        <v>2123</v>
-      </c>
-      <c r="J17" t="s">
-        <v>2124</v>
-      </c>
-      <c r="K17" t="s">
-        <v>2125</v>
-      </c>
-      <c r="L17" t="s">
-        <v>1910</v>
-      </c>
-      <c r="M17" t="s">
-        <v>2120</v>
-      </c>
-      <c r="N17" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
-      <c r="A18" t="s">
-        <v>2126</v>
-      </c>
-      <c r="B18" t="s">
-        <v>2127</v>
-      </c>
-      <c r="C18" t="s">
-        <v>16</v>
-      </c>
-      <c r="D18" t="s">
-        <v>1856</v>
-      </c>
-      <c r="E18" t="s">
-        <v>2128</v>
-      </c>
-      <c r="F18" t="s">
-        <v>2129</v>
-      </c>
-      <c r="G18" t="s">
-        <v>2130</v>
-      </c>
-      <c r="H18" t="s">
-        <v>69</v>
-      </c>
-      <c r="I18" t="s">
-        <v>2131</v>
-      </c>
-      <c r="J18" t="s">
-        <v>2132</v>
-      </c>
-      <c r="K18" t="s">
-        <v>1943</v>
-      </c>
-      <c r="L18" t="s">
-        <v>1910</v>
-      </c>
-      <c r="M18" t="s">
-        <v>1856</v>
-      </c>
-      <c r="N18" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
-      <c r="A19" t="s">
-        <v>2133</v>
-      </c>
-      <c r="B19" t="s">
-        <v>2134</v>
-      </c>
-      <c r="C19" t="s">
-        <v>16</v>
-      </c>
-      <c r="D19" t="s">
-        <v>2135</v>
-      </c>
-      <c r="E19" t="s">
-        <v>2136</v>
-      </c>
-      <c r="F19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G19" t="s">
-        <v>2137</v>
-      </c>
-      <c r="H19" t="s">
-        <v>69</v>
-      </c>
-      <c r="I19" t="s">
-        <v>2138</v>
-      </c>
-      <c r="J19" t="s">
-        <v>2139</v>
-      </c>
-      <c r="K19" t="s">
-        <v>2136</v>
-      </c>
-      <c r="L19" t="s">
-        <v>1910</v>
-      </c>
-      <c r="M19" t="s">
-        <v>2136</v>
-      </c>
-      <c r="N19" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
-      <c r="A20" t="s">
-        <v>2140</v>
-      </c>
-      <c r="B20" t="s">
-        <v>2141</v>
-      </c>
-      <c r="C20" t="s">
-        <v>16</v>
-      </c>
-      <c r="D20" t="s">
-        <v>2142</v>
-      </c>
-      <c r="E20" t="s">
-        <v>2143</v>
-      </c>
-      <c r="F20" t="s">
-        <v>1658</v>
-      </c>
-      <c r="G20" t="s">
-        <v>2144</v>
-      </c>
-      <c r="H20" t="s">
-        <v>69</v>
-      </c>
-      <c r="I20" t="s">
-        <v>2145</v>
-      </c>
-      <c r="J20" t="s">
-        <v>2146</v>
-      </c>
-      <c r="K20" t="s">
-        <v>2143</v>
-      </c>
-      <c r="L20" t="s">
-        <v>1910</v>
-      </c>
-      <c r="M20" t="s">
-        <v>2147</v>
-      </c>
-      <c r="N20" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14">
-      <c r="A21" t="s">
-        <v>2148</v>
-      </c>
-      <c r="B21" t="s">
-        <v>2149</v>
-      </c>
-      <c r="C21" t="s">
-        <v>16</v>
-      </c>
-      <c r="D21" t="s">
-        <v>1856</v>
-      </c>
-      <c r="E21" t="s">
-        <v>2150</v>
-      </c>
-      <c r="F21" t="s">
-        <v>1858</v>
-      </c>
-      <c r="G21" t="s">
-        <v>2151</v>
-      </c>
-      <c r="H21" t="s">
-        <v>69</v>
-      </c>
-      <c r="I21" t="s">
-        <v>2152</v>
-      </c>
-      <c r="J21" t="s">
-        <v>2153</v>
-      </c>
-      <c r="K21" t="s">
-        <v>2154</v>
-      </c>
-      <c r="L21" t="s">
-        <v>1910</v>
-      </c>
-      <c r="M21" t="s">
-        <v>1856</v>
-      </c>
-      <c r="N21" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14">
-      <c r="A22" t="s">
-        <v>2155</v>
-      </c>
-      <c r="B22" t="s">
-        <v>2156</v>
-      </c>
-      <c r="C22" t="s">
-        <v>16</v>
-      </c>
-      <c r="D22" t="s">
-        <v>2157</v>
-      </c>
-      <c r="E22" t="s">
-        <v>2158</v>
-      </c>
-      <c r="F22" t="s">
-        <v>1696</v>
-      </c>
-      <c r="G22" t="s">
-        <v>2159</v>
-      </c>
-      <c r="H22" t="s">
-        <v>69</v>
-      </c>
-      <c r="I22" t="s">
-        <v>2160</v>
-      </c>
-      <c r="J22" t="s">
-        <v>2161</v>
-      </c>
-      <c r="K22" t="s">
-        <v>2052</v>
-      </c>
-      <c r="L22" t="s">
-        <v>1910</v>
-      </c>
-      <c r="M22" t="s">
-        <v>1904</v>
-      </c>
-      <c r="N22" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14">
-      <c r="A23" t="s">
-        <v>2162</v>
-      </c>
-      <c r="B23" t="s">
-        <v>2163</v>
-      </c>
-      <c r="C23" t="s">
-        <v>16</v>
-      </c>
-      <c r="D23" t="s">
-        <v>1947</v>
-      </c>
-      <c r="E23" t="s">
-        <v>2164</v>
-      </c>
-      <c r="F23" t="s">
-        <v>1696</v>
-      </c>
-      <c r="G23" t="s">
-        <v>2165</v>
-      </c>
-      <c r="H23" t="s">
-        <v>69</v>
-      </c>
-      <c r="I23" t="s">
-        <v>2166</v>
-      </c>
-      <c r="J23" t="s">
-        <v>2167</v>
-      </c>
-      <c r="K23" t="s">
-        <v>2052</v>
-      </c>
-      <c r="L23" t="s">
-        <v>1910</v>
-      </c>
-      <c r="M23" t="s">
-        <v>2060</v>
-      </c>
-      <c r="N23" t="s">
-        <v>25</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{944AA604-5C9C-4A07-B4A8-289EF1B0937A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECDDD5F2-53E9-4AE3-BB92-BF21129E6B67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32280" yWindow="2235" windowWidth="29040" windowHeight="15720" firstSheet="16" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -25,15 +25,16 @@
     <sheet name="032 - Diode - TVS" sheetId="14" r:id="rId10"/>
     <sheet name="033 - Diode - LED" sheetId="12" r:id="rId11"/>
     <sheet name="040 - Fuses" sheetId="10" r:id="rId12"/>
-    <sheet name="043 - Transistors" sheetId="21" r:id="rId13"/>
-    <sheet name="045 - Crystal" sheetId="19" r:id="rId14"/>
-    <sheet name="050 - ICs - Analog" sheetId="2" r:id="rId15"/>
-    <sheet name="055 - Drivers" sheetId="20" r:id="rId16"/>
-    <sheet name="060 - ICs - Digital" sheetId="3" r:id="rId17"/>
-    <sheet name="070 - Power Supply - DCDC" sheetId="8" r:id="rId18"/>
-    <sheet name="090 - Processor" sheetId="18" r:id="rId19"/>
-    <sheet name="100 - Electromechanicals" sheetId="15" r:id="rId20"/>
-    <sheet name="110 - Connectors" sheetId="13" r:id="rId21"/>
+    <sheet name="042 - NTC" sheetId="23" r:id="rId13"/>
+    <sheet name="043 - Transistors" sheetId="21" r:id="rId14"/>
+    <sheet name="045 - Crystal" sheetId="19" r:id="rId15"/>
+    <sheet name="050 - ICs - Analog" sheetId="2" r:id="rId16"/>
+    <sheet name="055 - Drivers" sheetId="20" r:id="rId17"/>
+    <sheet name="060 - ICs - Digital" sheetId="3" r:id="rId18"/>
+    <sheet name="070 - Power Supply - DCDC" sheetId="8" r:id="rId19"/>
+    <sheet name="090 - Processor" sheetId="18" r:id="rId20"/>
+    <sheet name="100 - Electromechanicals" sheetId="15" r:id="rId21"/>
+    <sheet name="110 - Connectors" sheetId="13" r:id="rId22"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6472" uniqueCount="3228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6557" uniqueCount="3263">
   <si>
     <t>ID</t>
   </si>
@@ -9729,6 +9730,111 @@
   </si>
   <si>
     <t>CAP SMD 1812</t>
+  </si>
+  <si>
+    <t>010-0150</t>
+  </si>
+  <si>
+    <t>Resistores de película gruesa - SMD CRGP 2512 15R 1% SMD Resistor</t>
+  </si>
+  <si>
+    <t>15Ω 2W ±1%</t>
+  </si>
+  <si>
+    <t>2512</t>
+  </si>
+  <si>
+    <t>CRGP2512F15R</t>
+  </si>
+  <si>
+    <t>279-CRGP2512F15R</t>
+  </si>
+  <si>
+    <t>https://www.te.com/commerce/DocumentDelivery/DDEController?Action=srchrtrv&amp;DocNm=9-1773463-9&amp;DocType=Data%20Sheet&amp;DocLang=English&amp;PartCntxt=2176331-3&amp;DocFormat=pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/TE-Connectivity-Holsworthy/CRGP2512F15R?qs=sGAEpiMZZMtlubZbdhIBIOInyB5Ysv8smEFBCggATNk%3D</t>
+  </si>
+  <si>
+    <t>010-0151</t>
+  </si>
+  <si>
+    <t>010-0152</t>
+  </si>
+  <si>
+    <t>Resistores de película gruesa - SMD 0.75W 6.8ohms 1% High Power AEC-Q200</t>
+  </si>
+  <si>
+    <t>6.8Ω 750mW ±1%</t>
+  </si>
+  <si>
+    <t>CRCW06036R80FKEAHP</t>
+  </si>
+  <si>
+    <t>71-CRCW06036R80FKEAH</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Vishay/CRCW06036R80FKEAHP?qs=KWN%252BoghGvh0VLghfFgThPw%3D%3D</t>
+  </si>
+  <si>
+    <t>Resistores de película gruesa - SMD 0.75W 8.2ohms 1% High Power AEC-Q200</t>
+  </si>
+  <si>
+    <t>8.2Ω 750mW ±1%</t>
+  </si>
+  <si>
+    <t>CRCW06038R20FKEAHP</t>
+  </si>
+  <si>
+    <t>71-CRCW06038R20FKEAH</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Vishay/CRCW06038R20FKEAHP?qs=40TFAHZMFveezrMfyoByGQ%3D%3D</t>
+  </si>
+  <si>
+    <t>090-0002</t>
+  </si>
+  <si>
+    <t>Equipos y placas de desarrollo - TMS320 C2000 F28379D DELFIN O LAUNCHPAD</t>
+  </si>
+  <si>
+    <t>LAUNCHXL-F28379D</t>
+  </si>
+  <si>
+    <t>595-LAUNCHXL-F28379D</t>
+  </si>
+  <si>
+    <t>https://www.ti.com/lit/ug/sprui77c/sprui77c.pdf?ts=1639427205104&amp;ref_url=https%253A%252F%252Fwww.google.com%252F</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Texas-Instruments/LAUNCHXL-F28379D?qs=8%252Br4Hz5Xir%252BwQNYYjOfeVA%3D%3D</t>
+  </si>
+  <si>
+    <t>110-0062</t>
+  </si>
+  <si>
+    <t>SSK03-MPH-254-B20</t>
+  </si>
+  <si>
+    <t>Same Sky</t>
+  </si>
+  <si>
+    <t>179-SSK03MPH254B20</t>
+  </si>
+  <si>
+    <t>20P</t>
+  </si>
+  <si>
+    <t>Alojamientos de cables y cabecera 2.54mm Male Header, 2X20pin, Straight, PA6T, Gold Flash</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/datasheet/3/6118/1/ssk03_mph_254.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Same-Sky/SSK03-MPH-254-B20?qs=G4MbTVxgV4GvjhUhLLGrSQ%3D%3D</t>
+  </si>
+  <si>
+    <t>CONN 20P</t>
   </si>
 </sst>
 </file>
@@ -9779,12 +9885,14 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -9796,24 +9904,28 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -9829,17 +9941,20 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0563C1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
@@ -9957,9 +10072,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -14887,10 +15002,10 @@
       <c r="B106" t="s">
         <v>3220</v>
       </c>
-      <c r="C106" s="37" t="s">
+      <c r="C106" s="17" t="s">
         <v>3221</v>
       </c>
-      <c r="D106" s="38" t="s">
+      <c r="D106" s="13" t="s">
         <v>3222</v>
       </c>
       <c r="E106" s="36" t="s">
@@ -14899,7 +15014,7 @@
       <c r="F106" s="3" t="s">
         <v>2100</v>
       </c>
-      <c r="G106" s="39" t="s">
+      <c r="G106" s="31" t="s">
         <v>3224</v>
       </c>
       <c r="H106" s="16" t="s">
@@ -14917,10 +15032,10 @@
       <c r="L106" t="s">
         <v>61</v>
       </c>
-      <c r="M106" s="40" t="s">
+      <c r="M106" s="7" t="s">
         <v>3227</v>
       </c>
-      <c r="N106" s="40" t="s">
+      <c r="N106" s="7" t="s">
         <v>25</v>
       </c>
     </row>
@@ -18083,6 +18198,60 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB954362-0CE9-4363-A149-F8AA1E8DAAF4}">
+  <dimension ref="A1:N1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FAFF3B6-AF11-4BFB-8078-829FF6F2F366}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -18184,7 +18353,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E5535EA-E186-4751-BC7F-9B3A0221302E}">
   <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -18333,7 +18502,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C98E1A12-072F-4773-8CB5-47FFE077E85B}">
   <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -18583,7 +18752,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{201D74E2-3547-4E9B-8216-09A22645AC2A}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -18685,7 +18854,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59BC8B2E-A067-463D-937A-30E88D8BECD0}">
   <dimension ref="A1:N1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -18739,7 +18908,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4BBBCF5-BAC9-459C-ABE9-2526B85FD81E}">
   <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -19025,114 +19194,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E9EB2F5-2977-493B-BFA2-5CD20F8A3BC4}">
-  <dimension ref="A1:O2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
-  <sheetData>
-    <row r="1" spans="1:15">
-      <c r="A1" s="33" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="33" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="33" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="33" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="33" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="33" t="s">
-        <v>3019</v>
-      </c>
-      <c r="I1" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="33" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" s="33" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="33" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" t="s">
-        <v>3020</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3021</v>
-      </c>
-      <c r="C2">
-        <v>64</v>
-      </c>
-      <c r="D2" t="s">
-        <v>3022</v>
-      </c>
-      <c r="E2" t="s">
-        <v>3023</v>
-      </c>
-      <c r="F2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G2" t="s">
-        <v>3024</v>
-      </c>
-      <c r="H2" t="s">
-        <v>3162</v>
-      </c>
-      <c r="I2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>3025</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>3026</v>
-      </c>
-      <c r="L2" t="s">
-        <v>3023</v>
-      </c>
-      <c r="M2" t="s">
-        <v>3027</v>
-      </c>
-      <c r="N2" t="s">
-        <v>3022</v>
-      </c>
-      <c r="O2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="J2" r:id="rId1" xr:uid="{F8A04A1C-92B7-4CCD-8C95-726A110347D5}"/>
-    <hyperlink ref="K2" r:id="rId2" xr:uid="{2F912663-1CD4-41BE-AE9B-6D2CA04D31B2}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E05CC479-3669-40F7-BE22-BA5CFBFF29E9}">
   <dimension ref="A1:N3"/>
@@ -19285,6 +19346,164 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E9EB2F5-2977-493B-BFA2-5CD20F8A3BC4}">
+  <dimension ref="A1:O3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetData>
+    <row r="1" spans="1:15">
+      <c r="A1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="33" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="33" t="s">
+        <v>3019</v>
+      </c>
+      <c r="I1" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="33" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2" t="s">
+        <v>3020</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3021</v>
+      </c>
+      <c r="C2">
+        <v>64</v>
+      </c>
+      <c r="D2" t="s">
+        <v>3022</v>
+      </c>
+      <c r="E2" t="s">
+        <v>3023</v>
+      </c>
+      <c r="F2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2" t="s">
+        <v>3024</v>
+      </c>
+      <c r="H2" t="s">
+        <v>3162</v>
+      </c>
+      <c r="I2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>3025</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>3026</v>
+      </c>
+      <c r="L2" t="s">
+        <v>3023</v>
+      </c>
+      <c r="M2" t="s">
+        <v>3027</v>
+      </c>
+      <c r="N2" t="s">
+        <v>3022</v>
+      </c>
+      <c r="O2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" t="s">
+        <v>3248</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3249</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>3250</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" t="s">
+        <v>3251</v>
+      </c>
+      <c r="H3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>3252</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>3253</v>
+      </c>
+      <c r="L3" t="s">
+        <v>3250</v>
+      </c>
+      <c r="M3" t="s">
+        <v>3027</v>
+      </c>
+      <c r="N3" t="s">
+        <v>3250</v>
+      </c>
+      <c r="O3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="16" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="J2" r:id="rId1" xr:uid="{F8A04A1C-92B7-4CCD-8C95-726A110347D5}"/>
+    <hyperlink ref="K2" r:id="rId2" xr:uid="{2F912663-1CD4-41BE-AE9B-6D2CA04D31B2}"/>
+    <hyperlink ref="J3" r:id="rId3" xr:uid="{5A7F225D-EAAF-407C-A3F5-CF931A93B345}"/>
+    <hyperlink ref="K3" r:id="rId4" xr:uid="{A443CB7E-9DAC-4B30-B6D7-ABE633033E6D}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69A1C46E-DEF3-467B-A5BD-162AB66E6A86}">
   <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -20367,9 +20586,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE14AD29-8DB0-4C42-AB91-A73B867AE121}">
-  <dimension ref="A1:N62"/>
+  <dimension ref="A1:N63"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="5" max="5" width="16.36328125" bestFit="1" customWidth="1"/>
@@ -23102,6 +23321,47 @@
         <v>2322</v>
       </c>
       <c r="N62" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14">
+      <c r="A63" s="16" t="s">
+        <v>3254</v>
+      </c>
+      <c r="B63" t="s">
+        <v>3259</v>
+      </c>
+      <c r="C63" s="39" t="s">
+        <v>3258</v>
+      </c>
+      <c r="D63" s="16" t="s">
+        <v>2543</v>
+      </c>
+      <c r="E63" t="s">
+        <v>3255</v>
+      </c>
+      <c r="F63" t="s">
+        <v>3256</v>
+      </c>
+      <c r="G63" t="s">
+        <v>3257</v>
+      </c>
+      <c r="H63" t="s">
+        <v>21</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>3260</v>
+      </c>
+      <c r="J63" s="2" t="s">
+        <v>3261</v>
+      </c>
+      <c r="K63" s="17" t="s">
+        <v>3262</v>
+      </c>
+      <c r="L63" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="N63" s="7" t="s">
         <v>25</v>
       </c>
     </row>
@@ -23161,6 +23421,8 @@
     <hyperlink ref="I56" r:id="rId51" xr:uid="{CE941FB5-1D41-41B6-9CFD-C1256871C52E}"/>
     <hyperlink ref="J57" r:id="rId52" xr:uid="{72ED46D3-1227-48FD-9800-7E78EA501F81}"/>
     <hyperlink ref="I57" r:id="rId53" xr:uid="{30F29B76-2559-4C1E-A762-9F9E7C2882A4}"/>
+    <hyperlink ref="I63" r:id="rId54" xr:uid="{6A963C34-C9E4-46D1-9088-09C203C63186}"/>
+    <hyperlink ref="J63" r:id="rId55" xr:uid="{29B6CE96-A331-4903-A5B6-DD5273C7B49A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -23272,7 +23534,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60E8291E-4293-4634-B9E9-80CB520CA181}">
-  <dimension ref="A1:N151"/>
+  <dimension ref="A1:N154"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="3" max="3" width="19.90625" customWidth="1"/>
@@ -28746,8 +29008,8 @@
       <c r="C125" s="17" t="s">
         <v>1559</v>
       </c>
-      <c r="D125" s="3">
-        <v>2512</v>
+      <c r="D125" s="40" t="s">
+        <v>3231</v>
       </c>
       <c r="E125" s="17" t="s">
         <v>1560</v>
@@ -29881,7 +30143,139 @@
       </c>
     </row>
     <row r="151" spans="1:14">
-      <c r="A151" s="16"/>
+      <c r="A151" s="16" t="s">
+        <v>3228</v>
+      </c>
+      <c r="B151" s="37" t="s">
+        <v>3229</v>
+      </c>
+      <c r="C151" s="16" t="s">
+        <v>3230</v>
+      </c>
+      <c r="D151" s="38" t="s">
+        <v>3231</v>
+      </c>
+      <c r="E151" s="39" t="s">
+        <v>3232</v>
+      </c>
+      <c r="F151" s="37" t="s">
+        <v>1524</v>
+      </c>
+      <c r="G151" s="37" t="s">
+        <v>3233</v>
+      </c>
+      <c r="H151" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="I151" s="27" t="s">
+        <v>3234</v>
+      </c>
+      <c r="J151" s="32" t="s">
+        <v>3235</v>
+      </c>
+      <c r="K151" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L151" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M151" s="17" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N151" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="152" spans="1:14">
+      <c r="A152" s="16" t="s">
+        <v>3236</v>
+      </c>
+      <c r="B152" s="37" t="s">
+        <v>3238</v>
+      </c>
+      <c r="C152" s="16" t="s">
+        <v>3239</v>
+      </c>
+      <c r="D152" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E152" s="39" t="s">
+        <v>3240</v>
+      </c>
+      <c r="F152" s="37" t="s">
+        <v>945</v>
+      </c>
+      <c r="G152" s="37" t="s">
+        <v>3241</v>
+      </c>
+      <c r="H152" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="I152" s="27" t="s">
+        <v>2928</v>
+      </c>
+      <c r="J152" t="s">
+        <v>3242</v>
+      </c>
+      <c r="K152" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="L152" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M152" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="N152" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="153" spans="1:14">
+      <c r="A153" s="16" t="s">
+        <v>3237</v>
+      </c>
+      <c r="B153" s="37" t="s">
+        <v>3243</v>
+      </c>
+      <c r="C153" s="16" t="s">
+        <v>3244</v>
+      </c>
+      <c r="D153" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E153" s="39" t="s">
+        <v>3245</v>
+      </c>
+      <c r="F153" s="37" t="s">
+        <v>945</v>
+      </c>
+      <c r="G153" s="37" t="s">
+        <v>3246</v>
+      </c>
+      <c r="H153" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="I153" s="27" t="s">
+        <v>2928</v>
+      </c>
+      <c r="J153" s="27" t="s">
+        <v>3247</v>
+      </c>
+      <c r="K153" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="L153" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M153" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="N153" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="154" spans="1:14">
+      <c r="A154" s="16"/>
     </row>
   </sheetData>
   <phoneticPr fontId="16" type="noConversion"/>
@@ -29993,9 +30387,14 @@
     <hyperlink ref="J149" r:id="rId105" xr:uid="{1A42DE35-CA7D-4B83-ACC4-F85A80B83C4C}"/>
     <hyperlink ref="I150" r:id="rId106" xr:uid="{866C2F71-4468-4B2A-8F29-42D5363F2AE6}"/>
     <hyperlink ref="J150" r:id="rId107" xr:uid="{D030A4B2-39C9-4251-A1F3-D75C066D2B9B}"/>
+    <hyperlink ref="I151" r:id="rId108" xr:uid="{3CCC961A-FF6C-4434-BC16-DDC86909A33F}"/>
+    <hyperlink ref="J151" r:id="rId109" xr:uid="{C97E27C0-F3AB-4B5F-8915-58EC85F19F0D}"/>
+    <hyperlink ref="I152" r:id="rId110" xr:uid="{6971B994-F382-4D08-B0E3-89DECACB1BB6}"/>
+    <hyperlink ref="I153" r:id="rId111" xr:uid="{C3A39571-7B63-4B1B-8B0B-6C12C2D3193F}"/>
+    <hyperlink ref="J153" r:id="rId112" xr:uid="{53C0A29A-1A44-4CAA-BD58-4A236F43C0F3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId108"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId113"/>
 </worksheet>
 </file>
 

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECDDD5F2-53E9-4AE3-BB92-BF21129E6B67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93DA7B63-08BF-4C8C-A251-DF34670A7E64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32280" yWindow="2235" windowWidth="29040" windowHeight="15720" firstSheet="16" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32280" yWindow="2235" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6557" uniqueCount="3263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6571" uniqueCount="3270">
   <si>
     <t>ID</t>
   </si>
@@ -9835,6 +9835,27 @@
   </si>
   <si>
     <t>CONN 20P</t>
+  </si>
+  <si>
+    <t>001-0106</t>
+  </si>
+  <si>
+    <t>885342211007</t>
+  </si>
+  <si>
+    <t>710-885342211007</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/885342211007.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/885342211007?qs=MLItCLRbWswJ3Lv4KQFFUA%3D%3D</t>
+  </si>
+  <si>
+    <t>Condensadores de cerámica multicapa (MLCC- SMD/SMT) WCAP-CSMH 2000V 2200pF 1812 10%</t>
+  </si>
+  <si>
+    <t>2000V 2.2nF X7R</t>
   </si>
 </sst>
 </file>
@@ -10013,7 +10034,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -10071,10 +10092,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -10358,7 +10377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N106"/>
+  <dimension ref="A1:N107"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="11.1796875" customWidth="1"/>
@@ -15036,6 +15055,50 @@
         <v>3227</v>
       </c>
       <c r="N106" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="107" spans="1:14">
+      <c r="A107" s="4" t="s">
+        <v>3263</v>
+      </c>
+      <c r="B107" t="s">
+        <v>3268</v>
+      </c>
+      <c r="C107" s="38" t="s">
+        <v>3269</v>
+      </c>
+      <c r="D107" s="13" t="s">
+        <v>3222</v>
+      </c>
+      <c r="E107" s="36" t="s">
+        <v>3264</v>
+      </c>
+      <c r="F107" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G107" t="s">
+        <v>3265</v>
+      </c>
+      <c r="H107" t="s">
+        <v>21</v>
+      </c>
+      <c r="I107" s="2" t="s">
+        <v>3266</v>
+      </c>
+      <c r="J107" s="2" t="s">
+        <v>3267</v>
+      </c>
+      <c r="K107" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="L107" t="s">
+        <v>61</v>
+      </c>
+      <c r="M107" s="7" t="s">
+        <v>3227</v>
+      </c>
+      <c r="N107" s="7" t="s">
         <v>25</v>
       </c>
     </row>
@@ -15116,6 +15179,7 @@
     <hyperlink ref="J105" r:id="rId72" xr:uid="{F543587D-0A3E-429A-8125-C651D94CA2A5}"/>
     <hyperlink ref="I106" r:id="rId73" xr:uid="{BD618E63-4947-48D9-B209-8DCC58D284A8}"/>
     <hyperlink ref="J106" r:id="rId74" xr:uid="{C6D1135A-ABDE-44F6-88F2-FD4FF685F9BD}"/>
+    <hyperlink ref="J107" r:id="rId75" xr:uid="{1FF336D1-9AD9-43B7-B5A0-A1ECC5C35A05}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -23331,7 +23395,7 @@
       <c r="B63" t="s">
         <v>3259</v>
       </c>
-      <c r="C63" s="39" t="s">
+      <c r="C63" s="16" t="s">
         <v>3258</v>
       </c>
       <c r="D63" s="16" t="s">
@@ -29008,7 +29072,7 @@
       <c r="C125" s="17" t="s">
         <v>1559</v>
       </c>
-      <c r="D125" s="40" t="s">
+      <c r="D125" s="37" t="s">
         <v>3231</v>
       </c>
       <c r="E125" s="17" t="s">
@@ -30146,25 +30210,25 @@
       <c r="A151" s="16" t="s">
         <v>3228</v>
       </c>
-      <c r="B151" s="37" t="s">
+      <c r="B151" s="17" t="s">
         <v>3229</v>
       </c>
       <c r="C151" s="16" t="s">
         <v>3230</v>
       </c>
-      <c r="D151" s="38" t="s">
+      <c r="D151" s="20" t="s">
         <v>3231</v>
       </c>
-      <c r="E151" s="39" t="s">
+      <c r="E151" s="16" t="s">
         <v>3232</v>
       </c>
-      <c r="F151" s="37" t="s">
+      <c r="F151" s="17" t="s">
         <v>1524</v>
       </c>
-      <c r="G151" s="37" t="s">
+      <c r="G151" s="17" t="s">
         <v>3233</v>
       </c>
-      <c r="H151" s="39" t="s">
+      <c r="H151" s="16" t="s">
         <v>21</v>
       </c>
       <c r="I151" s="27" t="s">
@@ -30190,7 +30254,7 @@
       <c r="A152" s="16" t="s">
         <v>3236</v>
       </c>
-      <c r="B152" s="37" t="s">
+      <c r="B152" s="17" t="s">
         <v>3238</v>
       </c>
       <c r="C152" s="16" t="s">
@@ -30199,16 +30263,16 @@
       <c r="D152" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="E152" s="39" t="s">
+      <c r="E152" s="16" t="s">
         <v>3240</v>
       </c>
-      <c r="F152" s="37" t="s">
+      <c r="F152" s="17" t="s">
         <v>945</v>
       </c>
-      <c r="G152" s="37" t="s">
+      <c r="G152" s="17" t="s">
         <v>3241</v>
       </c>
-      <c r="H152" s="39" t="s">
+      <c r="H152" s="16" t="s">
         <v>21</v>
       </c>
       <c r="I152" s="27" t="s">
@@ -30217,7 +30281,7 @@
       <c r="J152" t="s">
         <v>3242</v>
       </c>
-      <c r="K152" s="37" t="s">
+      <c r="K152" s="17" t="s">
         <v>34</v>
       </c>
       <c r="L152" t="s">
@@ -30234,7 +30298,7 @@
       <c r="A153" s="16" t="s">
         <v>3237</v>
       </c>
-      <c r="B153" s="37" t="s">
+      <c r="B153" s="17" t="s">
         <v>3243</v>
       </c>
       <c r="C153" s="16" t="s">
@@ -30243,16 +30307,16 @@
       <c r="D153" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="E153" s="39" t="s">
+      <c r="E153" s="16" t="s">
         <v>3245</v>
       </c>
-      <c r="F153" s="37" t="s">
+      <c r="F153" s="17" t="s">
         <v>945</v>
       </c>
-      <c r="G153" s="37" t="s">
+      <c r="G153" s="17" t="s">
         <v>3246</v>
       </c>
-      <c r="H153" s="39" t="s">
+      <c r="H153" s="16" t="s">
         <v>21</v>
       </c>
       <c r="I153" s="27" t="s">
@@ -30261,7 +30325,7 @@
       <c r="J153" s="27" t="s">
         <v>3247</v>
       </c>
-      <c r="K153" s="37" t="s">
+      <c r="K153" s="17" t="s">
         <v>34</v>
       </c>
       <c r="L153" t="s">

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93DA7B63-08BF-4C8C-A251-DF34670A7E64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57427EF6-83D2-4D33-A6A2-07490B83ADDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32280" yWindow="2235" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32280" yWindow="2235" windowWidth="29040" windowHeight="15720" firstSheet="12" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -25,12 +25,12 @@
     <sheet name="032 - Diode - TVS" sheetId="14" r:id="rId10"/>
     <sheet name="033 - Diode - LED" sheetId="12" r:id="rId11"/>
     <sheet name="040 - Fuses" sheetId="10" r:id="rId12"/>
-    <sheet name="042 - NTC" sheetId="23" r:id="rId13"/>
-    <sheet name="043 - Transistors" sheetId="21" r:id="rId14"/>
-    <sheet name="045 - Crystal" sheetId="19" r:id="rId15"/>
-    <sheet name="050 - ICs - Analog" sheetId="2" r:id="rId16"/>
+    <sheet name="043 - Transistors" sheetId="21" r:id="rId13"/>
+    <sheet name="045 - Crystal" sheetId="19" r:id="rId14"/>
+    <sheet name="050 - ICs - Analog" sheetId="2" r:id="rId15"/>
+    <sheet name="051 - ICs - Digital" sheetId="24" r:id="rId16"/>
     <sheet name="055 - Drivers" sheetId="20" r:id="rId17"/>
-    <sheet name="060 - ICs - Digital" sheetId="3" r:id="rId18"/>
+    <sheet name="060 - Sensor" sheetId="3" r:id="rId18"/>
     <sheet name="070 - Power Supply - DCDC" sheetId="8" r:id="rId19"/>
     <sheet name="090 - Processor" sheetId="18" r:id="rId20"/>
     <sheet name="100 - Electromechanicals" sheetId="15" r:id="rId21"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6571" uniqueCount="3270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6585" uniqueCount="3280">
   <si>
     <t>ID</t>
   </si>
@@ -9856,6 +9856,36 @@
   </si>
   <si>
     <t>2000V 2.2nF X7R</t>
+  </si>
+  <si>
+    <t>LF 510-S</t>
+  </si>
+  <si>
+    <t>LEM</t>
+  </si>
+  <si>
+    <t>61-LF510-S</t>
+  </si>
+  <si>
+    <t>https://www.lem.com/sites/default/files/products_datasheets/lf_510-s.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/LEM/LF-510-S?qs=Vi0JKjFBtYlrxHjwN8JfEg%3D%3D</t>
+  </si>
+  <si>
+    <t>70x70x30mm</t>
+  </si>
+  <si>
+    <t>500A</t>
+  </si>
+  <si>
+    <t>Sensores de corriente industriales Current Transducer LF 510-S. For the electronic measurement of current: DC, AC, pulsed, with galvanic separation between the primary and secondary circuit.</t>
+  </si>
+  <si>
+    <t>060-0001</t>
+  </si>
+  <si>
+    <t>eUSR_SchLibrary/eUSR_SchLibrary - Sensors.SchLib</t>
   </si>
 </sst>
 </file>
@@ -10034,7 +10064,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -10093,7 +10123,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -15065,7 +15094,7 @@
       <c r="B107" t="s">
         <v>3268</v>
       </c>
-      <c r="C107" s="38" t="s">
+      <c r="C107" s="17" t="s">
         <v>3269</v>
       </c>
       <c r="D107" s="13" t="s">
@@ -18262,60 +18291,6 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB954362-0CE9-4363-A149-F8AA1E8DAAF4}">
-  <dimension ref="A1:N1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
-  <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FAFF3B6-AF11-4BFB-8078-829FF6F2F366}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -18417,7 +18392,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E5535EA-E186-4751-BC7F-9B3A0221302E}">
   <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -18566,7 +18541,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C98E1A12-072F-4773-8CB5-47FFE077E85B}">
   <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -18816,6 +18791,60 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{316C64E0-14FB-467C-956A-E132FAFB0232}">
+  <dimension ref="A1:N1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{201D74E2-3547-4E9B-8216-09A22645AC2A}">
   <dimension ref="A1:N2"/>
@@ -18920,7 +18949,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59BC8B2E-A067-463D-937A-30E88D8BECD0}">
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:14">
@@ -18967,7 +18996,55 @@
         <v>13</v>
       </c>
     </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
+        <v>3278</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3277</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3276</v>
+      </c>
+      <c r="D2" t="s">
+        <v>3275</v>
+      </c>
+      <c r="E2" t="s">
+        <v>3270</v>
+      </c>
+      <c r="F2" t="s">
+        <v>3271</v>
+      </c>
+      <c r="G2" t="s">
+        <v>3272</v>
+      </c>
+      <c r="H2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>3273</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>3274</v>
+      </c>
+      <c r="K2" t="s">
+        <v>3270</v>
+      </c>
+      <c r="L2" t="s">
+        <v>3279</v>
+      </c>
+      <c r="M2" t="s">
+        <v>3270</v>
+      </c>
+      <c r="N2" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="I2" r:id="rId1" xr:uid="{BFD1D0BA-D934-44C0-B127-7693B6B8FCF4}"/>
+    <hyperlink ref="J2" r:id="rId2" xr:uid="{72343140-B075-45AB-91DC-7B87E10B2AD1}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57427EF6-83D2-4D33-A6A2-07490B83ADDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89776970-5449-4C7B-9D0A-673F790E488F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32280" yWindow="2235" windowWidth="29040" windowHeight="15720" firstSheet="12" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32280" yWindow="2235" windowWidth="29040" windowHeight="15720" firstSheet="16" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6585" uniqueCount="3280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6586" uniqueCount="3281">
   <si>
     <t>ID</t>
   </si>
@@ -9813,15 +9813,9 @@
     <t>110-0062</t>
   </si>
   <si>
-    <t>SSK03-MPH-254-B20</t>
-  </si>
-  <si>
     <t>Same Sky</t>
   </si>
   <si>
-    <t>179-SSK03MPH254B20</t>
-  </si>
-  <si>
     <t>20P</t>
   </si>
   <si>
@@ -9831,9 +9825,6 @@
     <t>https://www.mouser.es/datasheet/3/6118/1/ssk03_mph_254.pdf</t>
   </si>
   <si>
-    <t>https://www.mouser.es/ProductDetail/Same-Sky/SSK03-MPH-254-B20?qs=G4MbTVxgV4GvjhUhLLGrSQ%3D%3D</t>
-  </si>
-  <si>
     <t>CONN 20P</t>
   </si>
   <si>
@@ -9886,6 +9877,18 @@
   </si>
   <si>
     <t>eUSR_SchLibrary/eUSR_SchLibrary - Sensors.SchLib</t>
+  </si>
+  <si>
+    <t>PIN_HEADER_THT_20P</t>
+  </si>
+  <si>
+    <t>SSK03-MPH-254-B10</t>
+  </si>
+  <si>
+    <t>179-SSK03MPH254B10</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Same-Sky/SSK03-MPH-254-B10?qs=G4MbTVxgV4GMuEeZX4ESdA%3D%3D</t>
   </si>
 </sst>
 </file>
@@ -15089,34 +15092,34 @@
     </row>
     <row r="107" spans="1:14">
       <c r="A107" s="4" t="s">
-        <v>3263</v>
+        <v>3260</v>
       </c>
       <c r="B107" t="s">
-        <v>3268</v>
+        <v>3265</v>
       </c>
       <c r="C107" s="17" t="s">
-        <v>3269</v>
+        <v>3266</v>
       </c>
       <c r="D107" s="13" t="s">
         <v>3222</v>
       </c>
       <c r="E107" s="36" t="s">
-        <v>3264</v>
+        <v>3261</v>
       </c>
       <c r="F107" t="s">
         <v>2100</v>
       </c>
       <c r="G107" t="s">
-        <v>3265</v>
+        <v>3262</v>
       </c>
       <c r="H107" t="s">
         <v>21</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>3266</v>
+        <v>3263</v>
       </c>
       <c r="J107" s="2" t="s">
-        <v>3267</v>
+        <v>3264</v>
       </c>
       <c r="K107" s="7" t="s">
         <v>72</v>
@@ -18998,43 +19001,43 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>3278</v>
+        <v>3275</v>
       </c>
       <c r="B2" t="s">
-        <v>3277</v>
+        <v>3274</v>
       </c>
       <c r="C2" t="s">
-        <v>3276</v>
+        <v>3273</v>
       </c>
       <c r="D2" t="s">
-        <v>3275</v>
+        <v>3272</v>
       </c>
       <c r="E2" t="s">
-        <v>3270</v>
+        <v>3267</v>
       </c>
       <c r="F2" t="s">
-        <v>3271</v>
+        <v>3268</v>
       </c>
       <c r="G2" t="s">
-        <v>3272</v>
+        <v>3269</v>
       </c>
       <c r="H2" t="s">
         <v>21</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>3273</v>
+        <v>3270</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>3274</v>
+        <v>3271</v>
       </c>
       <c r="K2" t="s">
-        <v>3270</v>
+        <v>3267</v>
       </c>
       <c r="L2" t="s">
-        <v>3279</v>
+        <v>3276</v>
       </c>
       <c r="M2" t="s">
-        <v>3270</v>
+        <v>3267</v>
       </c>
       <c r="N2" t="s">
         <v>25</v>
@@ -23470,37 +23473,40 @@
         <v>3254</v>
       </c>
       <c r="B63" t="s">
-        <v>3259</v>
+        <v>3257</v>
       </c>
       <c r="C63" s="16" t="s">
-        <v>3258</v>
+        <v>3256</v>
       </c>
       <c r="D63" s="16" t="s">
         <v>2543</v>
       </c>
       <c r="E63" t="s">
+        <v>3278</v>
+      </c>
+      <c r="F63" t="s">
         <v>3255</v>
       </c>
-      <c r="F63" t="s">
-        <v>3256</v>
-      </c>
       <c r="G63" t="s">
-        <v>3257</v>
+        <v>3279</v>
       </c>
       <c r="H63" t="s">
         <v>21</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>3260</v>
+        <v>3258</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>3261</v>
+        <v>3280</v>
       </c>
       <c r="K63" s="17" t="s">
-        <v>3262</v>
+        <v>3259</v>
       </c>
       <c r="L63" s="7" t="s">
         <v>2572</v>
+      </c>
+      <c r="M63" t="s">
+        <v>3277</v>
       </c>
       <c r="N63" s="7" t="s">
         <v>25</v>
@@ -23562,8 +23568,7 @@
     <hyperlink ref="I56" r:id="rId51" xr:uid="{CE941FB5-1D41-41B6-9CFD-C1256871C52E}"/>
     <hyperlink ref="J57" r:id="rId52" xr:uid="{72ED46D3-1227-48FD-9800-7E78EA501F81}"/>
     <hyperlink ref="I57" r:id="rId53" xr:uid="{30F29B76-2559-4C1E-A762-9F9E7C2882A4}"/>
-    <hyperlink ref="I63" r:id="rId54" xr:uid="{6A963C34-C9E4-46D1-9088-09C203C63186}"/>
-    <hyperlink ref="J63" r:id="rId55" xr:uid="{29B6CE96-A331-4903-A5B6-DD5273C7B49A}"/>
+    <hyperlink ref="J63" r:id="rId54" xr:uid="{29B6CE96-A331-4903-A5B6-DD5273C7B49A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89776970-5449-4C7B-9D0A-673F790E488F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93C11AAF-FD6F-46BD-BB28-734C9B614313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32280" yWindow="2235" windowWidth="29040" windowHeight="15720" firstSheet="16" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32280" yWindow="2235" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6586" uniqueCount="3281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6588" uniqueCount="3282">
   <si>
     <t>ID</t>
   </si>
@@ -9889,6 +9889,9 @@
   </si>
   <si>
     <t>https://www.mouser.es/ProductDetail/Same-Sky/SSK03-MPH-254-B10?qs=G4MbTVxgV4GMuEeZX4ESdA%3D%3D</t>
+  </si>
+  <si>
+    <t>CAP_27.5Px30H</t>
   </si>
 </sst>
 </file>
@@ -23663,6 +23666,12 @@
       <c r="L2" t="s">
         <v>61</v>
       </c>
+      <c r="M2" t="s">
+        <v>3281</v>
+      </c>
+      <c r="N2" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="3" spans="1:14">
       <c r="E3" s="36"/>

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93C11AAF-FD6F-46BD-BB28-734C9B614313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14F13589-66E7-4F6B-A953-78148688FE83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32280" yWindow="2235" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32280" yWindow="2235" windowWidth="29040" windowHeight="15720" firstSheet="16" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6588" uniqueCount="3282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6601" uniqueCount="3289">
   <si>
     <t>ID</t>
   </si>
@@ -9892,6 +9892,27 @@
   </si>
   <si>
     <t>CAP_27.5Px30H</t>
+  </si>
+  <si>
+    <t>110-0063</t>
+  </si>
+  <si>
+    <t>Terminales WR-BUCF Pin-Plate 20Pin Circm M8 350A</t>
+  </si>
+  <si>
+    <t>M8</t>
+  </si>
+  <si>
+    <t>7461090</t>
+  </si>
+  <si>
+    <t>710-7461090</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/7461090.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/7461090?qs=sGAEpiMZZMvlX3nhDDO4AGfuriVUnyWatNc5gc2eHA0%3D</t>
   </si>
 </sst>
 </file>
@@ -10070,7 +10091,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -10129,6 +10150,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -20735,7 +20760,7 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE14AD29-8DB0-4C42-AB91-A73B867AE121}">
-  <dimension ref="A1:N63"/>
+  <dimension ref="A1:N64"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="5" max="5" width="16.36328125" bestFit="1" customWidth="1"/>
@@ -23467,7 +23492,7 @@
       <c r="M62" s="16" t="s">
         <v>2322</v>
       </c>
-      <c r="N62" s="7" t="s">
+      <c r="N62" s="16" t="s">
         <v>25</v>
       </c>
     </row>
@@ -23512,6 +23537,50 @@
         <v>3277</v>
       </c>
       <c r="N63" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14">
+      <c r="A64" s="16" t="s">
+        <v>3282</v>
+      </c>
+      <c r="B64" t="s">
+        <v>3283</v>
+      </c>
+      <c r="C64" s="39" t="s">
+        <v>2488</v>
+      </c>
+      <c r="D64" s="16" t="s">
+        <v>3284</v>
+      </c>
+      <c r="E64" s="40" t="s">
+        <v>3285</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G64" s="38" t="s">
+        <v>3286</v>
+      </c>
+      <c r="H64" t="s">
+        <v>21</v>
+      </c>
+      <c r="I64" s="27" t="s">
+        <v>3287</v>
+      </c>
+      <c r="J64" s="2" t="s">
+        <v>3288</v>
+      </c>
+      <c r="K64" s="41" t="s">
+        <v>2429</v>
+      </c>
+      <c r="L64" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M64" s="30">
+        <v>7461090</v>
+      </c>
+      <c r="N64" s="7" t="s">
         <v>25</v>
       </c>
     </row>
@@ -23572,6 +23641,8 @@
     <hyperlink ref="J57" r:id="rId52" xr:uid="{72ED46D3-1227-48FD-9800-7E78EA501F81}"/>
     <hyperlink ref="I57" r:id="rId53" xr:uid="{30F29B76-2559-4C1E-A762-9F9E7C2882A4}"/>
     <hyperlink ref="J63" r:id="rId54" xr:uid="{29B6CE96-A331-4903-A5B6-DD5273C7B49A}"/>
+    <hyperlink ref="I64" r:id="rId55" xr:uid="{5CA52475-6941-42F8-9AA3-C5156AF91DB1}"/>
+    <hyperlink ref="J64" r:id="rId56" xr:uid="{0176710A-1D50-48A9-9ACC-C0E8F9C09246}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14F13589-66E7-4F6B-A953-78148688FE83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AF7DBB5-03D0-475B-B814-DAAE6467A581}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32280" yWindow="2235" windowWidth="29040" windowHeight="15720" firstSheet="16" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -31,10 +31,11 @@
     <sheet name="051 - ICs - Digital" sheetId="24" r:id="rId16"/>
     <sheet name="055 - Drivers" sheetId="20" r:id="rId17"/>
     <sheet name="060 - Sensor" sheetId="3" r:id="rId18"/>
-    <sheet name="070 - Power Supply - DCDC" sheetId="8" r:id="rId19"/>
-    <sheet name="090 - Processor" sheetId="18" r:id="rId20"/>
-    <sheet name="100 - Electromechanicals" sheetId="15" r:id="rId21"/>
-    <sheet name="110 - Connectors" sheetId="13" r:id="rId22"/>
+    <sheet name="062 - Amplifiers" sheetId="25" r:id="rId19"/>
+    <sheet name="070 - Power Supply - DCDC" sheetId="8" r:id="rId20"/>
+    <sheet name="090 - Processor" sheetId="18" r:id="rId21"/>
+    <sheet name="100 - Electromechanicals" sheetId="15" r:id="rId22"/>
+    <sheet name="110 - Connectors" sheetId="13" r:id="rId23"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6601" uniqueCount="3289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6685" uniqueCount="3329">
   <si>
     <t>ID</t>
   </si>
@@ -9913,6 +9914,126 @@
   </si>
   <si>
     <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/7461090?qs=sGAEpiMZZMvlX3nhDDO4AGfuriVUnyWatNc5gc2eHA0%3D</t>
+  </si>
+  <si>
+    <t>062-0001</t>
+  </si>
+  <si>
+    <t>AMC1200BDUBR</t>
+  </si>
+  <si>
+    <t>595-AMC1200BDUBR</t>
+  </si>
+  <si>
+    <t>https://www.ti.com/lit/ds/symlink/amc1200.pdf?ts=1781612882045&amp;ref_url=https%253A%252F%252Fwww.ti.com%252Fproduct%252FAMC1200%253FkeyMatch%253DAMC1200%2526tisearch%253Duniversal_search%2526usecase%253DGPN-ALT</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Texas-Instruments/AMC1200BDUBR?qs=4whTb%2F0XQMjhZwrxk0lf%2FQ%3D%3D</t>
+  </si>
+  <si>
+    <t>TLV6001UIDBVR</t>
+  </si>
+  <si>
+    <t>595-TLV6001UIDBVR</t>
+  </si>
+  <si>
+    <t>https://www.ti.com/lit/ds/symlink/tlv6001.pdf?ts=1781607824916&amp;ref_url=https%253A%252F%252Fcz.mouser.com%252F</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Texas-Instruments/TLV6001UIDBVR?qs=8N88piwwHEgntIgM8jjJ5Q%3D%3D</t>
+  </si>
+  <si>
+    <t>SOP-8</t>
+  </si>
+  <si>
+    <t>Amplificadores de aislamiento 4kV peak Iso Amp A 5 95-AMC1200BDUB A 59 A 595-AMC1200BDUB</t>
+  </si>
+  <si>
+    <t>eUSR_SchLibrary/eUSR_SchLibrary - Amplifiers.SchLib</t>
+  </si>
+  <si>
+    <t>AMC1200B</t>
+  </si>
+  <si>
+    <t>TLV6001</t>
+  </si>
+  <si>
+    <t>SOT-23-5</t>
+  </si>
+  <si>
+    <t>062-0002</t>
+  </si>
+  <si>
+    <t>Amplificadores operacionales - Op Amps Single 5.5-V 1-MHz R RIO operational a A A 595-TLV6001UIDBVT</t>
+  </si>
+  <si>
+    <t>GRT1885C1E103FA02D</t>
+  </si>
+  <si>
+    <t>81-GRT1885C1E103FA2D</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/datasheet/3/76/2/GRT1885C1E103FA02_01A.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Murata-Electronics/GRT1885C1E103FA02D?qs=xZ%2FP%252Ba9zWqaqiXqJj78%252Bmg%3D%3D</t>
+  </si>
+  <si>
+    <t>VJ0603D471KCXAJ</t>
+  </si>
+  <si>
+    <t>Vishay</t>
+  </si>
+  <si>
+    <t>77-VJ0603D471KCXAJ</t>
+  </si>
+  <si>
+    <t>https://www.vishay.com/docs/45258/vjhifreqseries.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Vishay-Vitramon/VJ0603D471KCXAJ?qs=oomPkbqnLXekRyIlVWaYLQ%3D%3D</t>
+  </si>
+  <si>
+    <t>C0603C512F5GACTU</t>
+  </si>
+  <si>
+    <t>KEMET</t>
+  </si>
+  <si>
+    <t>80-C0603C512F5G</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/datasheet/3/72/1/C0603C512F5GACTU.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/KEMET/C0603C512F5GACTU?qs=Fn3VdHBzkcmgqbeAGPfrXg%3D%3D</t>
+  </si>
+  <si>
+    <t>Condensadores de cerámica multicapa (MLCC- SMD/SMT) 0.01 uF 25 VDC 1% 0603 C0G (NP0) AEC-Q200</t>
+  </si>
+  <si>
+    <t>Condensadores de cerámica multicapa (MLCC- SMD/SMT) VJ0603 HIFREQ 471 0.1 non-magnetic copper non-magnetic copper 25V unmarked 7" reel</t>
+  </si>
+  <si>
+    <t>Condensadores de cerámica multicapa (MLCC- SMD/SMT) 50V 5100pF 0603 C0G 1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 25V 10nF NP0</t>
+  </si>
+  <si>
+    <t>25V 470pF NP0</t>
+  </si>
+  <si>
+    <t>25V 10nF NP0</t>
+  </si>
+  <si>
+    <t>001-0107</t>
+  </si>
+  <si>
+    <t>001-0108</t>
+  </si>
+  <si>
+    <t>001-0109</t>
   </si>
 </sst>
 </file>
@@ -10091,7 +10212,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -10150,10 +10271,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -10437,7 +10555,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N107"/>
+  <dimension ref="A1:N110"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="11.1796875" customWidth="1"/>
@@ -15159,6 +15277,138 @@
         <v>3227</v>
       </c>
       <c r="N107" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="108" spans="1:14">
+      <c r="A108" s="4" t="s">
+        <v>3326</v>
+      </c>
+      <c r="B108" t="s">
+        <v>3320</v>
+      </c>
+      <c r="C108" t="s">
+        <v>3323</v>
+      </c>
+      <c r="D108" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E108" t="s">
+        <v>3306</v>
+      </c>
+      <c r="F108" t="s">
+        <v>585</v>
+      </c>
+      <c r="G108" t="s">
+        <v>3307</v>
+      </c>
+      <c r="H108" t="s">
+        <v>21</v>
+      </c>
+      <c r="I108" s="2" t="s">
+        <v>3308</v>
+      </c>
+      <c r="J108" s="2" t="s">
+        <v>3309</v>
+      </c>
+      <c r="K108" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="L108" t="s">
+        <v>61</v>
+      </c>
+      <c r="M108" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="N108" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="109" spans="1:14">
+      <c r="A109" s="4" t="s">
+        <v>3327</v>
+      </c>
+      <c r="B109" t="s">
+        <v>3321</v>
+      </c>
+      <c r="C109" t="s">
+        <v>3324</v>
+      </c>
+      <c r="D109" s="38" t="s">
+        <v>59</v>
+      </c>
+      <c r="E109" t="s">
+        <v>3310</v>
+      </c>
+      <c r="F109" t="s">
+        <v>3311</v>
+      </c>
+      <c r="G109" t="s">
+        <v>3312</v>
+      </c>
+      <c r="H109" t="s">
+        <v>21</v>
+      </c>
+      <c r="I109" s="2" t="s">
+        <v>3313</v>
+      </c>
+      <c r="J109" s="2" t="s">
+        <v>3314</v>
+      </c>
+      <c r="K109" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="L109" t="s">
+        <v>61</v>
+      </c>
+      <c r="M109" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="N109" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="110" spans="1:14">
+      <c r="A110" s="4" t="s">
+        <v>3328</v>
+      </c>
+      <c r="B110" t="s">
+        <v>3322</v>
+      </c>
+      <c r="C110" t="s">
+        <v>3325</v>
+      </c>
+      <c r="D110" s="38" t="s">
+        <v>59</v>
+      </c>
+      <c r="E110" t="s">
+        <v>3315</v>
+      </c>
+      <c r="F110" t="s">
+        <v>3316</v>
+      </c>
+      <c r="G110" t="s">
+        <v>3317</v>
+      </c>
+      <c r="H110" t="s">
+        <v>21</v>
+      </c>
+      <c r="I110" s="2" t="s">
+        <v>3318</v>
+      </c>
+      <c r="J110" s="2" t="s">
+        <v>3319</v>
+      </c>
+      <c r="K110" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="L110" t="s">
+        <v>61</v>
+      </c>
+      <c r="M110" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="N110" t="s">
         <v>25</v>
       </c>
     </row>
@@ -15240,6 +15490,12 @@
     <hyperlink ref="I106" r:id="rId73" xr:uid="{BD618E63-4947-48D9-B209-8DCC58D284A8}"/>
     <hyperlink ref="J106" r:id="rId74" xr:uid="{C6D1135A-ABDE-44F6-88F2-FD4FF685F9BD}"/>
     <hyperlink ref="J107" r:id="rId75" xr:uid="{1FF336D1-9AD9-43B7-B5A0-A1ECC5C35A05}"/>
+    <hyperlink ref="I108" r:id="rId76" xr:uid="{46D4B59D-8E89-4DFA-8C9B-D3898FC3F9F3}"/>
+    <hyperlink ref="J108" r:id="rId77" xr:uid="{16223393-80B2-4745-8EA0-0A4239D2EC41}"/>
+    <hyperlink ref="I109" r:id="rId78" xr:uid="{55DEE86C-7DBE-4CD7-A07A-510E08868177}"/>
+    <hyperlink ref="J109" r:id="rId79" xr:uid="{0CE792E4-F174-4E91-B551-7288414F4023}"/>
+    <hyperlink ref="I110" r:id="rId80" xr:uid="{D7BF0419-A302-4F7D-9852-5D8A83AABBD7}"/>
+    <hyperlink ref="J110" r:id="rId81" xr:uid="{DA72DF56-54CF-4031-AB23-9AEE808CCA42}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -19081,6 +19337,306 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4185B0A-D162-4EBC-935B-7159E365DD54}">
+  <dimension ref="A1:N3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
+        <v>3289</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3299</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>3298</v>
+      </c>
+      <c r="E2" t="s">
+        <v>3290</v>
+      </c>
+      <c r="F2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" t="s">
+        <v>3291</v>
+      </c>
+      <c r="H2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>3292</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>3293</v>
+      </c>
+      <c r="K2" t="s">
+        <v>3301</v>
+      </c>
+      <c r="L2" t="s">
+        <v>3300</v>
+      </c>
+      <c r="M2" t="s">
+        <v>3301</v>
+      </c>
+      <c r="N2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>3304</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3305</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>3303</v>
+      </c>
+      <c r="E3" t="s">
+        <v>3294</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" t="s">
+        <v>3295</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>3296</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>3297</v>
+      </c>
+      <c r="K3" t="s">
+        <v>3302</v>
+      </c>
+      <c r="L3" t="s">
+        <v>3300</v>
+      </c>
+      <c r="M3" t="s">
+        <v>3303</v>
+      </c>
+      <c r="N3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="16" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="I2" r:id="rId1" xr:uid="{0AE24270-4D5D-4E12-981B-AA2533208AEE}"/>
+    <hyperlink ref="J2" r:id="rId2" xr:uid="{339478FA-7B81-4702-B5E2-22F306F57121}"/>
+    <hyperlink ref="I3" r:id="rId3" xr:uid="{28D99F1F-302C-4204-9911-77A7F0CFE035}"/>
+    <hyperlink ref="J3" r:id="rId4" xr:uid="{BCBD2BA5-6C89-4F65-A990-3E3D7A05A9E7}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E05CC479-3669-40F7-BE22-BA5CFBFF29E9}">
+  <dimension ref="A1:N3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="5" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
+        <v>2906</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2907</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2908</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2909</v>
+      </c>
+      <c r="E2" s="36" t="s">
+        <v>3205</v>
+      </c>
+      <c r="F2" t="s">
+        <v>2910</v>
+      </c>
+      <c r="G2" t="s">
+        <v>2911</v>
+      </c>
+      <c r="H2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>2912</v>
+      </c>
+      <c r="J2" t="s">
+        <v>2913</v>
+      </c>
+      <c r="K2" t="s">
+        <v>2914</v>
+      </c>
+      <c r="L2" t="s">
+        <v>61</v>
+      </c>
+      <c r="M2" t="s">
+        <v>2915</v>
+      </c>
+      <c r="N2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>3201</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3202</v>
+      </c>
+      <c r="C3" t="s">
+        <v>3203</v>
+      </c>
+      <c r="D3" t="s">
+        <v>3204</v>
+      </c>
+      <c r="E3" s="36" t="s">
+        <v>3206</v>
+      </c>
+      <c r="F3" t="s">
+        <v>2910</v>
+      </c>
+      <c r="G3" t="s">
+        <v>3207</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>3208</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>3209</v>
+      </c>
+      <c r="K3" t="s">
+        <v>2914</v>
+      </c>
+      <c r="L3" t="s">
+        <v>61</v>
+      </c>
+      <c r="M3" t="s">
+        <v>3210</v>
+      </c>
+      <c r="N3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="16" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="I2" r:id="rId1" xr:uid="{BB2EDAB8-75EB-46D2-BA14-384BF06E1A6E}"/>
+    <hyperlink ref="I3" r:id="rId2" xr:uid="{8F6B3EB5-F217-4353-ABA9-F461982FB5ED}"/>
+    <hyperlink ref="J3" r:id="rId3" xr:uid="{E90B210E-79B4-494B-B985-7D11C4705F7B}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4BBBCF5-BAC9-459C-ABE9-2526B85FD81E}">
   <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -19366,158 +19922,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E05CC479-3669-40F7-BE22-BA5CFBFF29E9}">
-  <dimension ref="A1:N3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
-  <cols>
-    <col min="5" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" t="s">
-        <v>2906</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2907</v>
-      </c>
-      <c r="C2" t="s">
-        <v>2908</v>
-      </c>
-      <c r="D2" t="s">
-        <v>2909</v>
-      </c>
-      <c r="E2" s="36" t="s">
-        <v>3205</v>
-      </c>
-      <c r="F2" t="s">
-        <v>2910</v>
-      </c>
-      <c r="G2" t="s">
-        <v>2911</v>
-      </c>
-      <c r="H2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>2912</v>
-      </c>
-      <c r="J2" t="s">
-        <v>2913</v>
-      </c>
-      <c r="K2" t="s">
-        <v>2914</v>
-      </c>
-      <c r="L2" t="s">
-        <v>61</v>
-      </c>
-      <c r="M2" t="s">
-        <v>2915</v>
-      </c>
-      <c r="N2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
-        <v>3201</v>
-      </c>
-      <c r="B3" t="s">
-        <v>3202</v>
-      </c>
-      <c r="C3" t="s">
-        <v>3203</v>
-      </c>
-      <c r="D3" t="s">
-        <v>3204</v>
-      </c>
-      <c r="E3" s="36" t="s">
-        <v>3206</v>
-      </c>
-      <c r="F3" t="s">
-        <v>2910</v>
-      </c>
-      <c r="G3" t="s">
-        <v>3207</v>
-      </c>
-      <c r="H3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>3208</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>3209</v>
-      </c>
-      <c r="K3" t="s">
-        <v>2914</v>
-      </c>
-      <c r="L3" t="s">
-        <v>61</v>
-      </c>
-      <c r="M3" t="s">
-        <v>3210</v>
-      </c>
-      <c r="N3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="16" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="I2" r:id="rId1" xr:uid="{BB2EDAB8-75EB-46D2-BA14-384BF06E1A6E}"/>
-    <hyperlink ref="I3" r:id="rId2" xr:uid="{8F6B3EB5-F217-4353-ABA9-F461982FB5ED}"/>
-    <hyperlink ref="J3" r:id="rId3" xr:uid="{E90B210E-79B4-494B-B985-7D11C4705F7B}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E9EB2F5-2977-493B-BFA2-5CD20F8A3BC4}">
   <dimension ref="A1:O3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -19675,7 +20080,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69A1C46E-DEF3-467B-A5BD-162AB66E6A86}">
   <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -20758,7 +21163,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE14AD29-8DB0-4C42-AB91-A73B867AE121}">
   <dimension ref="A1:N64"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -23547,19 +23952,19 @@
       <c r="B64" t="s">
         <v>3283</v>
       </c>
-      <c r="C64" s="39" t="s">
+      <c r="C64" s="16" t="s">
         <v>2488</v>
       </c>
       <c r="D64" s="16" t="s">
         <v>3284</v>
       </c>
-      <c r="E64" s="40" t="s">
+      <c r="E64" s="20" t="s">
         <v>3285</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>2100</v>
       </c>
-      <c r="G64" s="38" t="s">
+      <c r="G64" s="3" t="s">
         <v>3286</v>
       </c>
       <c r="H64" t="s">
@@ -23571,7 +23976,7 @@
       <c r="J64" s="2" t="s">
         <v>3288</v>
       </c>
-      <c r="K64" s="41" t="s">
+      <c r="K64" s="17" t="s">
         <v>2429</v>
       </c>
       <c r="L64" s="7" t="s">

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AF7DBB5-03D0-475B-B814-DAAE6467A581}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{580C0203-3800-43DF-8E8C-CB21C43739CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6685" uniqueCount="3329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6727" uniqueCount="3352">
   <si>
     <t>ID</t>
   </si>
@@ -10034,6 +10034,75 @@
   </si>
   <si>
     <t>001-0109</t>
+  </si>
+  <si>
+    <t>010-0153</t>
+  </si>
+  <si>
+    <t>010-0154</t>
+  </si>
+  <si>
+    <t>010-0155</t>
+  </si>
+  <si>
+    <t>Thin Film Resistors MCU 0805-15 0.1% P1 1K65</t>
+  </si>
+  <si>
+    <t>Thin Film Resistors 0805 3.3Kohm 0.1% 15ppm AEC-Q200</t>
+  </si>
+  <si>
+    <t>RES SMD 12 OHM 0.25% 1/4W 1206</t>
+  </si>
+  <si>
+    <t>1.65kΩ 125mW ±0.1%</t>
+  </si>
+  <si>
+    <t>3.3kΩ 125mW ±0.1%</t>
+  </si>
+  <si>
+    <t>12Ω 250mW  0.25%</t>
+  </si>
+  <si>
+    <t>MCU08050E1651BP100</t>
+  </si>
+  <si>
+    <t>594-MCU08050E1651BP1</t>
+  </si>
+  <si>
+    <t>https://www.vishay.com/docs/28700/mcx0x0xpre.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Vishay-Beyschlag/MCU08050E1651BP100?qs=sGAEpiMZZMvdGkrng054t2c0lhweLxbk6HRvs42FTBI%3D</t>
+  </si>
+  <si>
+    <t>ERA-6APB332V</t>
+  </si>
+  <si>
+    <t>Panasonic</t>
+  </si>
+  <si>
+    <t>667-ERA-6APB332V</t>
+  </si>
+  <si>
+    <t>https://industrial.panasonic.com/cdbs/www-data/pdf/RDM0000/AOA0000C307.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Panasonic/ERA-6APB332V?qs=sGAEpiMZZMvdGkrng054t7Q%2FBjLwFmgicQi9zKDLbrs%3D</t>
+  </si>
+  <si>
+    <t>RT1206CRC0712RL</t>
+  </si>
+  <si>
+    <t>RT1206CRC0712RL-ND</t>
+  </si>
+  <si>
+    <t>Digikey</t>
+  </si>
+  <si>
+    <t>https://www.digikey.es/es/models/5937613?tab=null</t>
+  </si>
+  <si>
+    <t>https://www.digikey.es/es/products/detail/yageo/RT1206CRC0712RL/5937613</t>
   </si>
 </sst>
 </file>
@@ -10212,7 +10281,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -10271,7 +10340,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -15334,7 +15402,7 @@
       <c r="C109" t="s">
         <v>3324</v>
       </c>
-      <c r="D109" s="38" t="s">
+      <c r="D109" s="16" t="s">
         <v>59</v>
       </c>
       <c r="E109" t="s">
@@ -15378,7 +15446,7 @@
       <c r="C110" t="s">
         <v>3325</v>
       </c>
-      <c r="D110" s="38" t="s">
+      <c r="D110" s="16" t="s">
         <v>59</v>
       </c>
       <c r="E110" t="s">
@@ -24165,7 +24233,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60E8291E-4293-4634-B9E9-80CB520CA181}">
-  <dimension ref="A1:N154"/>
+  <dimension ref="A1:N159"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="3" max="3" width="19.90625" customWidth="1"/>
@@ -30906,7 +30974,139 @@
       </c>
     </row>
     <row r="154" spans="1:14">
-      <c r="A154" s="16"/>
+      <c r="A154" s="16" t="s">
+        <v>3329</v>
+      </c>
+      <c r="B154" t="s">
+        <v>3332</v>
+      </c>
+      <c r="C154" t="s">
+        <v>3335</v>
+      </c>
+      <c r="D154" s="20" t="s">
+        <v>240</v>
+      </c>
+      <c r="E154" t="s">
+        <v>3338</v>
+      </c>
+      <c r="F154" t="s">
+        <v>3311</v>
+      </c>
+      <c r="G154" t="s">
+        <v>3339</v>
+      </c>
+      <c r="H154" t="s">
+        <v>21</v>
+      </c>
+      <c r="I154" s="2" t="s">
+        <v>3340</v>
+      </c>
+      <c r="J154" s="2" t="s">
+        <v>3341</v>
+      </c>
+      <c r="K154" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L154" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M154" s="17" t="s">
+        <v>1646</v>
+      </c>
+      <c r="N154" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="155" spans="1:14">
+      <c r="A155" s="16" t="s">
+        <v>3330</v>
+      </c>
+      <c r="B155" t="s">
+        <v>3333</v>
+      </c>
+      <c r="C155" t="s">
+        <v>3336</v>
+      </c>
+      <c r="D155" s="20" t="s">
+        <v>240</v>
+      </c>
+      <c r="E155" t="s">
+        <v>3342</v>
+      </c>
+      <c r="F155" t="s">
+        <v>3343</v>
+      </c>
+      <c r="G155" t="s">
+        <v>3344</v>
+      </c>
+      <c r="H155" t="s">
+        <v>21</v>
+      </c>
+      <c r="I155" s="2" t="s">
+        <v>3345</v>
+      </c>
+      <c r="J155" s="2" t="s">
+        <v>3346</v>
+      </c>
+      <c r="K155" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L155" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M155" s="17" t="s">
+        <v>1646</v>
+      </c>
+      <c r="N155" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="156" spans="1:14">
+      <c r="A156" s="16" t="s">
+        <v>3331</v>
+      </c>
+      <c r="B156" t="s">
+        <v>3334</v>
+      </c>
+      <c r="C156" t="s">
+        <v>3337</v>
+      </c>
+      <c r="D156" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="E156" t="s">
+        <v>3347</v>
+      </c>
+      <c r="F156" t="s">
+        <v>60</v>
+      </c>
+      <c r="G156" t="s">
+        <v>3348</v>
+      </c>
+      <c r="H156" t="s">
+        <v>3349</v>
+      </c>
+      <c r="I156" t="s">
+        <v>3350</v>
+      </c>
+      <c r="J156" s="2" t="s">
+        <v>3351</v>
+      </c>
+      <c r="K156" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L156" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M156" s="7" t="s">
+        <v>1645</v>
+      </c>
+      <c r="N156" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="159" spans="1:14">
+      <c r="F159" s="21"/>
     </row>
   </sheetData>
   <phoneticPr fontId="16" type="noConversion"/>
@@ -31023,9 +31223,14 @@
     <hyperlink ref="I152" r:id="rId110" xr:uid="{6971B994-F382-4D08-B0E3-89DECACB1BB6}"/>
     <hyperlink ref="I153" r:id="rId111" xr:uid="{C3A39571-7B63-4B1B-8B0B-6C12C2D3193F}"/>
     <hyperlink ref="J153" r:id="rId112" xr:uid="{53C0A29A-1A44-4CAA-BD58-4A236F43C0F3}"/>
+    <hyperlink ref="I154" r:id="rId113" xr:uid="{EC84B0AF-9E78-4228-A4D8-C52EEB67EF3E}"/>
+    <hyperlink ref="J154" r:id="rId114" xr:uid="{293A3F3E-9607-4CA6-999A-FBB3D073E270}"/>
+    <hyperlink ref="I155" r:id="rId115" xr:uid="{819E07D4-A0E4-475C-ACC0-622501017E74}"/>
+    <hyperlink ref="J155" r:id="rId116" xr:uid="{9D7A02D8-02AB-40F9-A4C3-999EDC72ED54}"/>
+    <hyperlink ref="J156" r:id="rId117" xr:uid="{C7F72D9E-B22F-4AFF-9CFB-3A851699B586}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId113"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId118"/>
 </worksheet>
 </file>
 

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{580C0203-3800-43DF-8E8C-CB21C43739CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{400EDE90-C96D-4FA7-A343-F0BE4401D0AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -10024,9 +10024,6 @@
     <t>25V 470pF NP0</t>
   </si>
   <si>
-    <t>25V 10nF NP0</t>
-  </si>
-  <si>
     <t>001-0107</t>
   </si>
   <si>
@@ -10103,6 +10100,9 @@
   </si>
   <si>
     <t>https://www.digikey.es/es/products/detail/yageo/RT1206CRC0712RL/5937613</t>
+  </si>
+  <si>
+    <t>50V 5.1nF NP0</t>
   </si>
 </sst>
 </file>
@@ -15350,7 +15350,7 @@
     </row>
     <row r="108" spans="1:14">
       <c r="A108" s="4" t="s">
-        <v>3326</v>
+        <v>3325</v>
       </c>
       <c r="B108" t="s">
         <v>3320</v>
@@ -15394,7 +15394,7 @@
     </row>
     <row r="109" spans="1:14">
       <c r="A109" s="4" t="s">
-        <v>3327</v>
+        <v>3326</v>
       </c>
       <c r="B109" t="s">
         <v>3321</v>
@@ -15438,13 +15438,13 @@
     </row>
     <row r="110" spans="1:14">
       <c r="A110" s="4" t="s">
-        <v>3328</v>
+        <v>3327</v>
       </c>
       <c r="B110" t="s">
         <v>3322</v>
       </c>
       <c r="C110" t="s">
-        <v>3325</v>
+        <v>3351</v>
       </c>
       <c r="D110" s="16" t="s">
         <v>59</v>
@@ -30975,34 +30975,34 @@
     </row>
     <row r="154" spans="1:14">
       <c r="A154" s="16" t="s">
-        <v>3329</v>
+        <v>3328</v>
       </c>
       <c r="B154" t="s">
-        <v>3332</v>
+        <v>3331</v>
       </c>
       <c r="C154" t="s">
-        <v>3335</v>
+        <v>3334</v>
       </c>
       <c r="D154" s="20" t="s">
         <v>240</v>
       </c>
       <c r="E154" t="s">
-        <v>3338</v>
+        <v>3337</v>
       </c>
       <c r="F154" t="s">
         <v>3311</v>
       </c>
       <c r="G154" t="s">
-        <v>3339</v>
+        <v>3338</v>
       </c>
       <c r="H154" t="s">
         <v>21</v>
       </c>
       <c r="I154" s="2" t="s">
+        <v>3339</v>
+      </c>
+      <c r="J154" s="2" t="s">
         <v>3340</v>
-      </c>
-      <c r="J154" s="2" t="s">
-        <v>3341</v>
       </c>
       <c r="K154" s="17" t="s">
         <v>34</v>
@@ -31019,34 +31019,34 @@
     </row>
     <row r="155" spans="1:14">
       <c r="A155" s="16" t="s">
-        <v>3330</v>
+        <v>3329</v>
       </c>
       <c r="B155" t="s">
-        <v>3333</v>
+        <v>3332</v>
       </c>
       <c r="C155" t="s">
-        <v>3336</v>
+        <v>3335</v>
       </c>
       <c r="D155" s="20" t="s">
         <v>240</v>
       </c>
       <c r="E155" t="s">
+        <v>3341</v>
+      </c>
+      <c r="F155" t="s">
         <v>3342</v>
       </c>
-      <c r="F155" t="s">
+      <c r="G155" t="s">
         <v>3343</v>
-      </c>
-      <c r="G155" t="s">
-        <v>3344</v>
       </c>
       <c r="H155" t="s">
         <v>21</v>
       </c>
       <c r="I155" s="2" t="s">
+        <v>3344</v>
+      </c>
+      <c r="J155" s="2" t="s">
         <v>3345</v>
-      </c>
-      <c r="J155" s="2" t="s">
-        <v>3346</v>
       </c>
       <c r="K155" s="17" t="s">
         <v>34</v>
@@ -31063,34 +31063,34 @@
     </row>
     <row r="156" spans="1:14">
       <c r="A156" s="16" t="s">
-        <v>3331</v>
+        <v>3330</v>
       </c>
       <c r="B156" t="s">
-        <v>3334</v>
+        <v>3333</v>
       </c>
       <c r="C156" t="s">
-        <v>3337</v>
+        <v>3336</v>
       </c>
       <c r="D156" s="13" t="s">
         <v>249</v>
       </c>
       <c r="E156" t="s">
-        <v>3347</v>
+        <v>3346</v>
       </c>
       <c r="F156" t="s">
         <v>60</v>
       </c>
       <c r="G156" t="s">
+        <v>3347</v>
+      </c>
+      <c r="H156" t="s">
         <v>3348</v>
       </c>
-      <c r="H156" t="s">
+      <c r="I156" t="s">
         <v>3349</v>
       </c>
-      <c r="I156" t="s">
+      <c r="J156" s="2" t="s">
         <v>3350</v>
-      </c>
-      <c r="J156" s="2" t="s">
-        <v>3351</v>
       </c>
       <c r="K156" s="17" t="s">
         <v>34</v>

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{400EDE90-C96D-4FA7-A343-F0BE4401D0AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5FD5C94-E2A0-464E-ABDF-65CDE4E48212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32280" yWindow="2235" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
     <sheet name="055 - Drivers" sheetId="20" r:id="rId17"/>
     <sheet name="060 - Sensor" sheetId="3" r:id="rId18"/>
     <sheet name="062 - Amplifiers" sheetId="25" r:id="rId19"/>
-    <sheet name="070 - Power Supply - DCDC" sheetId="8" r:id="rId20"/>
+    <sheet name="070 - Power Supply" sheetId="8" r:id="rId20"/>
     <sheet name="090 - Processor" sheetId="18" r:id="rId21"/>
     <sheet name="100 - Electromechanicals" sheetId="15" r:id="rId22"/>
     <sheet name="110 - Connectors" sheetId="13" r:id="rId23"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6727" uniqueCount="3352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6909" uniqueCount="3448">
   <si>
     <t>ID</t>
   </si>
@@ -10103,6 +10103,294 @@
   </si>
   <si>
     <t>50V 5.1nF NP0</t>
+  </si>
+  <si>
+    <t>885012206052</t>
+  </si>
+  <si>
+    <t>710-885012206052</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/885012206052.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/885012206052?qs=0KOYDY2FL2%2F2JKabApojcQ%3D%3D</t>
+  </si>
+  <si>
+    <t>885012107014</t>
+  </si>
+  <si>
+    <t>710-885012107014</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/885012107014.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/885012107014?qs=0KOYDY2FL28i0pwNdARIlg%3D%3D</t>
+  </si>
+  <si>
+    <t>885012206046</t>
+  </si>
+  <si>
+    <t>710-885012206046</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/885012206046.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/885012206046?qs=0KOYDY2FL2%252B89gr6HvTBXA%3D%3D</t>
+  </si>
+  <si>
+    <t>885012106029</t>
+  </si>
+  <si>
+    <t>710-885012106029</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/885012106029.pdf</t>
+  </si>
+  <si>
+    <t>001-0110</t>
+  </si>
+  <si>
+    <t>001-0111</t>
+  </si>
+  <si>
+    <t>001-0112</t>
+  </si>
+  <si>
+    <t>001-0113</t>
+  </si>
+  <si>
+    <t>Condensadores de cerámica multicapa (MLCC- SMD/SMT) WCAP-CSGP 1uF 0603 10% 16V MLCC</t>
+  </si>
+  <si>
+    <t>Condensadores de cerámica multicapa (MLCC- SMD/SMT) WCAP-CSGP 10uF 0805 20% 16V MLCC</t>
+  </si>
+  <si>
+    <t>16V 10uF X5R</t>
+  </si>
+  <si>
+    <t>Condensadores de cerámica multicapa (MLCC- SMD/SMT) WCAP-CSGP 0.1uF 0603 10% 16V MLCC</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/885012106029?qs=amGC7iS6iy%252BgG3I4L92Nqg%3D%3D</t>
+  </si>
+  <si>
+    <t>Condensadores de cerámica multicapa (MLCC- SMD/SMT) WCAP-CSGP 2.2uF 16V 10%</t>
+  </si>
+  <si>
+    <t>560112110142</t>
+  </si>
+  <si>
+    <t>710-560112110142</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/560112110142.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/560112110142?qs=mELouGlnn3daEwPMtfpdeg%3D%3D</t>
+  </si>
+  <si>
+    <t>Resistores de película gruesa - SMD WRIS-RSKS 118 kOhms 1 % 0.1 W 0402 AEC-Q200</t>
+  </si>
+  <si>
+    <t>560112110099</t>
+  </si>
+  <si>
+    <t>710-560112110099</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/560112110099.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/560112110099?qs=mELouGlnn3eF8MLEVMJrCw%3D%3D</t>
+  </si>
+  <si>
+    <t>Resistores de película gruesa - SMD WRIS-RSKS 22.1 kOhms 1 % 0.1 W 0402 AEC-Q200</t>
+  </si>
+  <si>
+    <t>CRCW040269K8FKED</t>
+  </si>
+  <si>
+    <t>71-CRCW0402-69.8K-E3</t>
+  </si>
+  <si>
+    <t>https://www.vishay.com/docs/20035/dcrcwe3.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Vishay/CRCW040269K8FKED?qs=sGAEpiMZZMtlubZbdhIBICni6BQV4SfY1e7wNtp2Znw%3D</t>
+  </si>
+  <si>
+    <t>Resistores de película gruesa - SMD 1/10 Watt 69.8Kohms 1%</t>
+  </si>
+  <si>
+    <t>118kΩ 100mW ±1%</t>
+  </si>
+  <si>
+    <t>010-0156</t>
+  </si>
+  <si>
+    <t>010-0157</t>
+  </si>
+  <si>
+    <t>010-0158</t>
+  </si>
+  <si>
+    <t>22.1kΩ 100mW ±1%</t>
+  </si>
+  <si>
+    <t>69.8kΩ 100mW ±1%</t>
+  </si>
+  <si>
+    <t>74438336100</t>
+  </si>
+  <si>
+    <t>710-74438336100</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/74438336100.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/74438336100?qs=iC14BvcgY%2F3tj5fn6qP7Hg%3D%3D</t>
+  </si>
+  <si>
+    <t>74438357082</t>
+  </si>
+  <si>
+    <t>710-74438357082</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/74438357082.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/74438357082?qs=AQlKX63v8RvaY%2FvJVfZzHA%3D%3D</t>
+  </si>
+  <si>
+    <t>IND</t>
+  </si>
+  <si>
+    <t>Inductores de potencia (SMD) WE-MAPI 10uH 1.2A DCR=322mOhms AEC-Q200</t>
+  </si>
+  <si>
+    <t>10uH 1.65A 322mOhm</t>
+  </si>
+  <si>
+    <t>SMD;3x3mm</t>
+  </si>
+  <si>
+    <t>IND SMD 3x3</t>
+  </si>
+  <si>
+    <t>020-0001</t>
+  </si>
+  <si>
+    <t>020-0002</t>
+  </si>
+  <si>
+    <t>8.2uH 2.8A 86mOhm</t>
+  </si>
+  <si>
+    <t>SMD;4.1x4.1mm</t>
+  </si>
+  <si>
+    <t>IND SMD 4.1x4.1</t>
+  </si>
+  <si>
+    <t>Inductores de potencia (SMD) WE-MAPI 8.2uH 2.8A DCR=86mOhms AEC-Q200</t>
+  </si>
+  <si>
+    <t>070-0006</t>
+  </si>
+  <si>
+    <t>070-0007</t>
+  </si>
+  <si>
+    <t>070-0008</t>
+  </si>
+  <si>
+    <t>TLV705165YFPR</t>
+  </si>
+  <si>
+    <t>595-TLV705165YFPR</t>
+  </si>
+  <si>
+    <t>https://www.ti.com/lit/ds/symlink/tlv705.pdf?ts=1781649192737&amp;ref_url=https%253A%252F%252Fwww.ti.com</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Texas-Instruments/TLV705165YFPR?qs=rrS6PyfT74d8bhzeUZaAoA%3D%3D</t>
+  </si>
+  <si>
+    <t>LMR51410YFDBVR</t>
+  </si>
+  <si>
+    <t>595-LMR51410YFDBVR</t>
+  </si>
+  <si>
+    <t>https://www.ti.com/lit/ds/symlink/lmr51410.pdf?ts=1781684561920&amp;ref_url=https%253A%252F%252Fwww.mouser.de%252F</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Texas-Instruments/LMR51410YFDBVR?qs=i8QVZAFTkqTUiBodeYrDsw%3D%3D</t>
+  </si>
+  <si>
+    <t>LM2776DBVT</t>
+  </si>
+  <si>
+    <t>595-LM2776DBVT</t>
+  </si>
+  <si>
+    <t>https://www.ti.com/lit/ds/symlink/lm2776.pdf?ts=1781716279536&amp;ref_url=https%253A%252F%252Fwww.mouser.es%252F</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Texas-Instruments/LM2776DBVT?qs=GJ%2F2ZGcr5uMLAYYW9ugYkg%3D%3D</t>
+  </si>
+  <si>
+    <t>(4/42)V-(0.8/28)V</t>
+  </si>
+  <si>
+    <t>Reguladores de tensión de conmutación SIMPLE SWITCHER 4V t o 42V 1A synchronou</t>
+  </si>
+  <si>
+    <t>Reguladores de voltaje LDO 200-mA high-PSRR l o w-IQ low-dropout v A 595-TLV705165YFPT</t>
+  </si>
+  <si>
+    <t>(2/5.5)V-1.65V</t>
+  </si>
+  <si>
+    <t>DSBGA-4</t>
+  </si>
+  <si>
+    <t>TLV705165</t>
+  </si>
+  <si>
+    <t>LMR51410</t>
+  </si>
+  <si>
+    <t>(2.7/5.5)V-(-2.7/-5.5)V</t>
+  </si>
+  <si>
+    <t>Reguladores de tensión de conmutación Switched Capacitor I nverter A 595-LM277 A 595-LM2776DBVR</t>
+  </si>
+  <si>
+    <t>LM2776</t>
+  </si>
+  <si>
+    <t>010-0159</t>
+  </si>
+  <si>
+    <t>Resistores de película gruesa - SMD WRIS-RSKS 100 kOhms 1 % 0.1 W 0402 AEC-Q200</t>
+  </si>
+  <si>
+    <t>560112110019</t>
+  </si>
+  <si>
+    <t>710-560112110019</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/560112110019.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/560112110019?qs=mELouGlnn3eOtqJeFyZVpA%3D%3D</t>
   </si>
 </sst>
 </file>
@@ -10623,7 +10911,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N110"/>
+  <dimension ref="A1:N114"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="11.1796875" customWidth="1"/>
@@ -15477,6 +15765,182 @@
         <v>62</v>
       </c>
       <c r="N110" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="111" spans="1:14">
+      <c r="A111" s="4" t="s">
+        <v>3367</v>
+      </c>
+      <c r="B111" t="s">
+        <v>3371</v>
+      </c>
+      <c r="C111" t="s">
+        <v>2988</v>
+      </c>
+      <c r="D111" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="E111" s="36" t="s">
+        <v>3352</v>
+      </c>
+      <c r="F111" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G111" t="s">
+        <v>3353</v>
+      </c>
+      <c r="H111" t="s">
+        <v>21</v>
+      </c>
+      <c r="I111" s="2" t="s">
+        <v>3354</v>
+      </c>
+      <c r="J111" s="2" t="s">
+        <v>3355</v>
+      </c>
+      <c r="K111" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="L111" t="s">
+        <v>61</v>
+      </c>
+      <c r="M111" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="N111" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="112" spans="1:14">
+      <c r="A112" s="4" t="s">
+        <v>3368</v>
+      </c>
+      <c r="B112" t="s">
+        <v>3372</v>
+      </c>
+      <c r="C112" t="s">
+        <v>3373</v>
+      </c>
+      <c r="D112" s="20" t="s">
+        <v>240</v>
+      </c>
+      <c r="E112" s="36" t="s">
+        <v>3356</v>
+      </c>
+      <c r="F112" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G112" t="s">
+        <v>3357</v>
+      </c>
+      <c r="H112" t="s">
+        <v>21</v>
+      </c>
+      <c r="I112" s="2" t="s">
+        <v>3358</v>
+      </c>
+      <c r="J112" s="2" t="s">
+        <v>3359</v>
+      </c>
+      <c r="K112" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="L112" t="s">
+        <v>61</v>
+      </c>
+      <c r="M112" s="7" t="s">
+        <v>700</v>
+      </c>
+      <c r="N112" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="113" spans="1:14">
+      <c r="A113" s="4" t="s">
+        <v>3369</v>
+      </c>
+      <c r="B113" t="s">
+        <v>3374</v>
+      </c>
+      <c r="C113" t="s">
+        <v>2982</v>
+      </c>
+      <c r="D113" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="E113" s="36" t="s">
+        <v>3360</v>
+      </c>
+      <c r="F113" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G113" t="s">
+        <v>3361</v>
+      </c>
+      <c r="H113" t="s">
+        <v>21</v>
+      </c>
+      <c r="I113" s="2" t="s">
+        <v>3362</v>
+      </c>
+      <c r="J113" s="2" t="s">
+        <v>3363</v>
+      </c>
+      <c r="K113" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="L113" t="s">
+        <v>61</v>
+      </c>
+      <c r="M113" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="N113" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="114" spans="1:14">
+      <c r="A114" s="4" t="s">
+        <v>3370</v>
+      </c>
+      <c r="B114" t="s">
+        <v>3376</v>
+      </c>
+      <c r="C114" t="s">
+        <v>155</v>
+      </c>
+      <c r="D114" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="E114" s="36" t="s">
+        <v>3364</v>
+      </c>
+      <c r="F114" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G114" t="s">
+        <v>3365</v>
+      </c>
+      <c r="H114" t="s">
+        <v>21</v>
+      </c>
+      <c r="I114" s="2" t="s">
+        <v>3366</v>
+      </c>
+      <c r="J114" s="2" t="s">
+        <v>3375</v>
+      </c>
+      <c r="K114" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="L114" t="s">
+        <v>61</v>
+      </c>
+      <c r="M114" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="N114" t="s">
         <v>25</v>
       </c>
     </row>
@@ -15564,8 +16028,17 @@
     <hyperlink ref="J109" r:id="rId79" xr:uid="{0CE792E4-F174-4E91-B551-7288414F4023}"/>
     <hyperlink ref="I110" r:id="rId80" xr:uid="{D7BF0419-A302-4F7D-9852-5D8A83AABBD7}"/>
     <hyperlink ref="J110" r:id="rId81" xr:uid="{DA72DF56-54CF-4031-AB23-9AEE808CCA42}"/>
+    <hyperlink ref="I111" r:id="rId82" xr:uid="{AD5C5368-A948-45EC-8368-303EF16B76C4}"/>
+    <hyperlink ref="J111" r:id="rId83" xr:uid="{12677E4F-CC0C-474A-AF70-3FA3FD23CCC8}"/>
+    <hyperlink ref="I112" r:id="rId84" xr:uid="{6738B4F6-C20E-4F28-A5E0-DA4B845CD87C}"/>
+    <hyperlink ref="J112" r:id="rId85" xr:uid="{203E6C20-5030-4C57-A692-AE145EF9A648}"/>
+    <hyperlink ref="I113" r:id="rId86" xr:uid="{6BF8DD46-F79B-4225-A5CE-0178FA8E1FD1}"/>
+    <hyperlink ref="J113" r:id="rId87" xr:uid="{888ED7A4-81F2-44BF-ACB2-1634B14D367A}"/>
+    <hyperlink ref="I114" r:id="rId88" xr:uid="{4DE3B0C7-2537-4971-98DE-9A56EF44C421}"/>
+    <hyperlink ref="J114" r:id="rId89" xr:uid="{FB1B8B94-45EA-4535-BE3A-72D28A8B6781}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId90"/>
 </worksheet>
 </file>
 
@@ -19706,7 +20179,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4BBBCF5-BAC9-459C-ABE9-2526B85FD81E}">
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="4" max="4" width="17.54296875" customWidth="1"/>
@@ -19976,6 +20449,138 @@
         <v>25</v>
       </c>
     </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>3417</v>
+      </c>
+      <c r="B7" t="s">
+        <v>3434</v>
+      </c>
+      <c r="C7" t="s">
+        <v>3435</v>
+      </c>
+      <c r="D7" t="s">
+        <v>3436</v>
+      </c>
+      <c r="E7" t="s">
+        <v>3420</v>
+      </c>
+      <c r="F7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" t="s">
+        <v>3421</v>
+      </c>
+      <c r="H7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>3422</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>3423</v>
+      </c>
+      <c r="K7" t="s">
+        <v>3437</v>
+      </c>
+      <c r="L7" t="s">
+        <v>1689</v>
+      </c>
+      <c r="M7" t="s">
+        <v>3436</v>
+      </c>
+      <c r="N7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>3418</v>
+      </c>
+      <c r="B8" t="s">
+        <v>3433</v>
+      </c>
+      <c r="C8" t="s">
+        <v>3432</v>
+      </c>
+      <c r="D8" t="s">
+        <v>2120</v>
+      </c>
+      <c r="E8" t="s">
+        <v>3424</v>
+      </c>
+      <c r="F8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" t="s">
+        <v>3425</v>
+      </c>
+      <c r="H8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>3426</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>3427</v>
+      </c>
+      <c r="K8" t="s">
+        <v>3438</v>
+      </c>
+      <c r="L8" t="s">
+        <v>1689</v>
+      </c>
+      <c r="M8" t="s">
+        <v>2120</v>
+      </c>
+      <c r="N8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>3419</v>
+      </c>
+      <c r="B9" t="s">
+        <v>3440</v>
+      </c>
+      <c r="C9" t="s">
+        <v>3439</v>
+      </c>
+      <c r="D9" t="s">
+        <v>2120</v>
+      </c>
+      <c r="E9" t="s">
+        <v>3428</v>
+      </c>
+      <c r="F9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" t="s">
+        <v>3429</v>
+      </c>
+      <c r="H9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" t="s">
+        <v>3430</v>
+      </c>
+      <c r="J9" t="s">
+        <v>3431</v>
+      </c>
+      <c r="K9" t="s">
+        <v>3441</v>
+      </c>
+      <c r="L9" t="s">
+        <v>1689</v>
+      </c>
+      <c r="M9" t="s">
+        <v>2120</v>
+      </c>
+      <c r="N9" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="16" type="noConversion"/>
   <hyperlinks>
@@ -19984,9 +20589,13 @@
     <hyperlink ref="I5" r:id="rId3" xr:uid="{38CEA448-03C1-4130-9D22-378144C1B83E}"/>
     <hyperlink ref="J5" r:id="rId4" xr:uid="{178AE8D2-EC1F-4144-807A-F49730BDAEE7}"/>
     <hyperlink ref="I6" r:id="rId5" xr:uid="{C6B22468-8A2D-4CA0-8E30-C5E1C054C475}"/>
+    <hyperlink ref="I7" r:id="rId6" xr:uid="{46E13713-695D-493D-96DD-70A916E207CE}"/>
+    <hyperlink ref="J7" r:id="rId7" xr:uid="{CE7C033B-E1D3-4982-B98D-45472DE55249}"/>
+    <hyperlink ref="J8" r:id="rId8" xr:uid="{EA27946F-BAF3-48A3-B1E1-735BC730E575}"/>
+    <hyperlink ref="I8" r:id="rId9" xr:uid="{E0BD2FA6-2C87-41A3-AA17-DD7C10DA47E6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId10"/>
 </worksheet>
 </file>
 
@@ -24233,7 +24842,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60E8291E-4293-4634-B9E9-80CB520CA181}">
-  <dimension ref="A1:N159"/>
+  <dimension ref="A1:N160"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="3" max="3" width="19.90625" customWidth="1"/>
@@ -31105,8 +31714,181 @@
         <v>25</v>
       </c>
     </row>
+    <row r="157" spans="1:14">
+      <c r="A157" s="16" t="s">
+        <v>3393</v>
+      </c>
+      <c r="B157" t="s">
+        <v>3381</v>
+      </c>
+      <c r="C157" s="16" t="s">
+        <v>3392</v>
+      </c>
+      <c r="D157" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="E157" s="36" t="s">
+        <v>3377</v>
+      </c>
+      <c r="F157" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G157" t="s">
+        <v>3378</v>
+      </c>
+      <c r="H157" t="s">
+        <v>21</v>
+      </c>
+      <c r="I157" s="2" t="s">
+        <v>3379</v>
+      </c>
+      <c r="J157" t="s">
+        <v>3380</v>
+      </c>
+      <c r="K157" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L157" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M157" s="7" t="s">
+        <v>1644</v>
+      </c>
+      <c r="N157" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="158" spans="1:14">
+      <c r="A158" s="16" t="s">
+        <v>3394</v>
+      </c>
+      <c r="B158" t="s">
+        <v>3386</v>
+      </c>
+      <c r="C158" s="16" t="s">
+        <v>3396</v>
+      </c>
+      <c r="D158" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="E158" s="36" t="s">
+        <v>3382</v>
+      </c>
+      <c r="F158" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G158" t="s">
+        <v>3383</v>
+      </c>
+      <c r="H158" t="s">
+        <v>21</v>
+      </c>
+      <c r="I158" s="2" t="s">
+        <v>3384</v>
+      </c>
+      <c r="J158" t="s">
+        <v>3385</v>
+      </c>
+      <c r="K158" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L158" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M158" s="7" t="s">
+        <v>1644</v>
+      </c>
+      <c r="N158" t="s">
+        <v>25</v>
+      </c>
+    </row>
     <row r="159" spans="1:14">
-      <c r="F159" s="21"/>
+      <c r="A159" s="16" t="s">
+        <v>3395</v>
+      </c>
+      <c r="B159" t="s">
+        <v>3391</v>
+      </c>
+      <c r="C159" s="16" t="s">
+        <v>3397</v>
+      </c>
+      <c r="D159" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="E159" t="s">
+        <v>3387</v>
+      </c>
+      <c r="F159" t="s">
+        <v>3311</v>
+      </c>
+      <c r="G159" t="s">
+        <v>3388</v>
+      </c>
+      <c r="H159" t="s">
+        <v>21</v>
+      </c>
+      <c r="I159" s="2" t="s">
+        <v>3389</v>
+      </c>
+      <c r="J159" s="2" t="s">
+        <v>3390</v>
+      </c>
+      <c r="K159" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L159" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M159" s="7" t="s">
+        <v>1644</v>
+      </c>
+      <c r="N159" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="160" spans="1:14">
+      <c r="A160" s="16" t="s">
+        <v>3442</v>
+      </c>
+      <c r="B160" t="s">
+        <v>3443</v>
+      </c>
+      <c r="C160" s="16" t="s">
+        <v>929</v>
+      </c>
+      <c r="D160" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="E160" s="20" t="s">
+        <v>3444</v>
+      </c>
+      <c r="F160" s="16" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G160" s="16" t="s">
+        <v>3445</v>
+      </c>
+      <c r="H160" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I160" s="27" t="s">
+        <v>3446</v>
+      </c>
+      <c r="J160" t="s">
+        <v>3447</v>
+      </c>
+      <c r="K160" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L160" s="17" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M160" s="7" t="s">
+        <v>1644</v>
+      </c>
+      <c r="N160" t="s">
+        <v>25</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="16" type="noConversion"/>
@@ -31228,9 +32010,13 @@
     <hyperlink ref="I155" r:id="rId115" xr:uid="{819E07D4-A0E4-475C-ACC0-622501017E74}"/>
     <hyperlink ref="J155" r:id="rId116" xr:uid="{9D7A02D8-02AB-40F9-A4C3-999EDC72ED54}"/>
     <hyperlink ref="J156" r:id="rId117" xr:uid="{C7F72D9E-B22F-4AFF-9CFB-3A851699B586}"/>
+    <hyperlink ref="I158" r:id="rId118" xr:uid="{A3CABA41-1EF9-4C9F-AE07-C02EA7FCF75E}"/>
+    <hyperlink ref="I159" r:id="rId119" xr:uid="{D5889C02-ED09-4327-9DFB-0BBF24BA4AA7}"/>
+    <hyperlink ref="J159" r:id="rId120" xr:uid="{5E88809D-3319-44CA-AC1F-18CC618C3A0A}"/>
+    <hyperlink ref="I160" r:id="rId121" xr:uid="{38247BF1-5599-4165-BFEC-26629D789AC3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId118"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId122"/>
 </worksheet>
 </file>
 
@@ -31478,7 +32264,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01C6B0FD-D8A3-44EC-9532-03DDA232F922}">
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:14">
@@ -31525,8 +32311,103 @@
         <v>13</v>
       </c>
     </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
+        <v>3411</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3407</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3408</v>
+      </c>
+      <c r="D2" t="s">
+        <v>3409</v>
+      </c>
+      <c r="E2" s="36" t="s">
+        <v>3398</v>
+      </c>
+      <c r="F2" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G2" t="s">
+        <v>3399</v>
+      </c>
+      <c r="H2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>3400</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>3401</v>
+      </c>
+      <c r="K2" t="s">
+        <v>3406</v>
+      </c>
+      <c r="L2" t="s">
+        <v>2904</v>
+      </c>
+      <c r="M2" s="17" t="s">
+        <v>3410</v>
+      </c>
+      <c r="N2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>3412</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3416</v>
+      </c>
+      <c r="C3" t="s">
+        <v>3413</v>
+      </c>
+      <c r="D3" t="s">
+        <v>3414</v>
+      </c>
+      <c r="E3" s="36" t="s">
+        <v>3402</v>
+      </c>
+      <c r="F3" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G3" t="s">
+        <v>3403</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>3404</v>
+      </c>
+      <c r="J3" t="s">
+        <v>3405</v>
+      </c>
+      <c r="K3" t="s">
+        <v>3406</v>
+      </c>
+      <c r="L3" t="s">
+        <v>2904</v>
+      </c>
+      <c r="M3" s="17" t="s">
+        <v>3415</v>
+      </c>
+      <c r="N3" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="16" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="I2" r:id="rId1" xr:uid="{07883802-B058-47F9-BBB3-C06E82952829}"/>
+    <hyperlink ref="J2" r:id="rId2" xr:uid="{62DD0F89-540D-4537-B7A5-4B172FA10C23}"/>
+    <hyperlink ref="I3" r:id="rId3" xr:uid="{A45B5B86-5ADB-44B4-BF96-CFB1161AF6C6}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>
 

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5FD5C94-E2A0-464E-ABDF-65CDE4E48212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30C5A904-14E0-40B9-B0A1-5757D9C583FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="32280" yWindow="2235" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6909" uniqueCount="3448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6922" uniqueCount="3450">
   <si>
     <t>ID</t>
   </si>
@@ -10391,6 +10391,12 @@
   </si>
   <si>
     <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/560112110019?qs=mELouGlnn3eOtqJeFyZVpA%3D%3D</t>
+  </si>
+  <si>
+    <t>010-0160</t>
+  </si>
+  <si>
+    <t>0Ω 100mW ±1%</t>
   </si>
 </sst>
 </file>
@@ -10569,7 +10575,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -10628,6 +10634,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -24842,7 +24850,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60E8291E-4293-4634-B9E9-80CB520CA181}">
-  <dimension ref="A1:N160"/>
+  <dimension ref="A1:N161"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="3" max="3" width="19.90625" customWidth="1"/>
@@ -31887,6 +31895,50 @@
         <v>1644</v>
       </c>
       <c r="N160" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="161" spans="1:14">
+      <c r="A161" s="16" t="s">
+        <v>3448</v>
+      </c>
+      <c r="B161" t="s">
+        <v>3105</v>
+      </c>
+      <c r="C161" s="16" t="s">
+        <v>3449</v>
+      </c>
+      <c r="D161" s="38" t="s">
+        <v>59</v>
+      </c>
+      <c r="E161">
+        <v>560112116001</v>
+      </c>
+      <c r="F161" s="16" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G161" s="39" t="s">
+        <v>3107</v>
+      </c>
+      <c r="H161" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="I161" s="27" t="s">
+        <v>3108</v>
+      </c>
+      <c r="J161" s="27" t="s">
+        <v>3109</v>
+      </c>
+      <c r="K161" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L161" s="17" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M161" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="N161" t="s">
         <v>25</v>
       </c>
     </row>
@@ -32014,9 +32066,11 @@
     <hyperlink ref="I159" r:id="rId119" xr:uid="{D5889C02-ED09-4327-9DFB-0BBF24BA4AA7}"/>
     <hyperlink ref="J159" r:id="rId120" xr:uid="{5E88809D-3319-44CA-AC1F-18CC618C3A0A}"/>
     <hyperlink ref="I160" r:id="rId121" xr:uid="{38247BF1-5599-4165-BFEC-26629D789AC3}"/>
+    <hyperlink ref="I161" r:id="rId122" xr:uid="{7C28565D-C222-4AEC-81A3-9D2C8C79A1A1}"/>
+    <hyperlink ref="J161" r:id="rId123" xr:uid="{3A2D1BFE-71D6-460D-8752-1790B0BCD8EB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId122"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId124"/>
 </worksheet>
 </file>
 

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30C5A904-14E0-40B9-B0A1-5757D9C583FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE01584E-F2A1-4EBB-B809-BEEF27A38C26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32280" yWindow="2235" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32280" yWindow="2235" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6922" uniqueCount="3450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6950" uniqueCount="3463">
   <si>
     <t>ID</t>
   </si>
@@ -10397,6 +10397,45 @@
   </si>
   <si>
     <t>0Ω 100mW ±1%</t>
+  </si>
+  <si>
+    <t>ZRB18AR61E106KE01L</t>
+  </si>
+  <si>
+    <t>81-ZRB18AR61E106KE1L</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Murata-Electronics/ZRB18AR61E106KE01L?qs=sGAEpiMZZMsh%252B1woXyUXj%2Fze%252BJJ8bUKCZuLWV6qOmdQ%3D</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/datasheet/3/76/2/ZRB18AR61E106KE01_02A.pdf</t>
+  </si>
+  <si>
+    <t>885012206071</t>
+  </si>
+  <si>
+    <t>710-885012206071</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/885012206071.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/885012206071?qs=0KOYDY2FL2%2FEBQkuHgvarg%3D%3D</t>
+  </si>
+  <si>
+    <t>25V 0.1uF X7R</t>
+  </si>
+  <si>
+    <t>Condensadores de cerámica multicapa (MLCC- SMD/SMT) 0603 25VDC 10uF 10% X5R</t>
+  </si>
+  <si>
+    <t>Condensadores de cerámica multicapa (MLCC- SMD/SMT) WCAP-CSGP 0.1uF 0603 10% 25V MLCC</t>
+  </si>
+  <si>
+    <t>001-0114</t>
+  </si>
+  <si>
+    <t>001-0115</t>
   </si>
 </sst>
 </file>
@@ -10575,7 +10614,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -10634,8 +10673,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -10919,7 +10956,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N114"/>
+  <dimension ref="A1:N116"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="11.1796875" customWidth="1"/>
@@ -15949,6 +15986,94 @@
         <v>62</v>
       </c>
       <c r="N114" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="115" spans="1:14">
+      <c r="A115" s="4" t="s">
+        <v>3461</v>
+      </c>
+      <c r="B115" t="s">
+        <v>3459</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="D115" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>3450</v>
+      </c>
+      <c r="F115" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="G115" s="3" t="s">
+        <v>3451</v>
+      </c>
+      <c r="H115" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I115" s="2" t="s">
+        <v>3452</v>
+      </c>
+      <c r="J115" s="2" t="s">
+        <v>3453</v>
+      </c>
+      <c r="K115" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="L115" t="s">
+        <v>61</v>
+      </c>
+      <c r="M115" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="N115" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="116" spans="1:14">
+      <c r="A116" s="4" t="s">
+        <v>3462</v>
+      </c>
+      <c r="B116" t="s">
+        <v>3460</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>3458</v>
+      </c>
+      <c r="D116" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="E116" s="36" t="s">
+        <v>3454</v>
+      </c>
+      <c r="F116" s="3" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G116" t="s">
+        <v>3455</v>
+      </c>
+      <c r="H116" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I116" s="2" t="s">
+        <v>3456</v>
+      </c>
+      <c r="J116" s="2" t="s">
+        <v>3457</v>
+      </c>
+      <c r="K116" s="3" t="s">
+        <v>3458</v>
+      </c>
+      <c r="L116" t="s">
+        <v>61</v>
+      </c>
+      <c r="M116" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="N116" t="s">
         <v>25</v>
       </c>
     </row>
@@ -16044,9 +16169,11 @@
     <hyperlink ref="J113" r:id="rId87" xr:uid="{888ED7A4-81F2-44BF-ACB2-1634B14D367A}"/>
     <hyperlink ref="I114" r:id="rId88" xr:uid="{4DE3B0C7-2537-4971-98DE-9A56EF44C421}"/>
     <hyperlink ref="J114" r:id="rId89" xr:uid="{FB1B8B94-45EA-4535-BE3A-72D28A8B6781}"/>
+    <hyperlink ref="J115" r:id="rId90" xr:uid="{88671F05-A2EE-487E-BF71-2F48DB15577D}"/>
+    <hyperlink ref="I115" r:id="rId91" xr:uid="{42FBB82F-FA0A-49B4-BEC5-E4E89D6CB366}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId90"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId92"/>
 </worksheet>
 </file>
 
@@ -31908,7 +32035,7 @@
       <c r="C161" s="16" t="s">
         <v>3449</v>
       </c>
-      <c r="D161" s="38" t="s">
+      <c r="D161" s="20" t="s">
         <v>59</v>
       </c>
       <c r="E161">
@@ -31917,10 +32044,10 @@
       <c r="F161" s="16" t="s">
         <v>2100</v>
       </c>
-      <c r="G161" s="39" t="s">
+      <c r="G161" s="16" t="s">
         <v>3107</v>
       </c>
-      <c r="H161" s="39" t="s">
+      <c r="H161" s="16" t="s">
         <v>21</v>
       </c>
       <c r="I161" s="27" t="s">

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE01584E-F2A1-4EBB-B809-BEEF27A38C26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52E71095-319C-402F-87FB-E1C8317109D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="32280" yWindow="2235" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16020,8 +16020,8 @@
       <c r="J115" s="2" t="s">
         <v>3453</v>
       </c>
-      <c r="K115" s="3" t="s">
-        <v>469</v>
+      <c r="K115" s="7" t="s">
+        <v>72</v>
       </c>
       <c r="L115" t="s">
         <v>61</v>
@@ -16064,8 +16064,8 @@
       <c r="J116" s="2" t="s">
         <v>3457</v>
       </c>
-      <c r="K116" s="3" t="s">
-        <v>3458</v>
+      <c r="K116" s="7" t="s">
+        <v>72</v>
       </c>
       <c r="L116" t="s">
         <v>61</v>

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52E71095-319C-402F-87FB-E1C8317109D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BE23959-6875-40F2-AEF9-9D4DBB8E573D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="32280" yWindow="2235" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6950" uniqueCount="3463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6964" uniqueCount="3470">
   <si>
     <t>ID</t>
   </si>
@@ -10436,6 +10436,27 @@
   </si>
   <si>
     <t>001-0115</t>
+  </si>
+  <si>
+    <t>885012005031</t>
+  </si>
+  <si>
+    <t>710-885012005031</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/885012005031.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/885012005031?qs=0KOYDY2FL2%2FUQDbf4TYx%2Fw%3D%3D</t>
+  </si>
+  <si>
+    <t>16V 100pF NP0</t>
+  </si>
+  <si>
+    <t>001-0116</t>
+  </si>
+  <si>
+    <t>Condensadores de cerámica multicapa (MLCC- SMD/SMT) WCAP-CSGP 100pF 0402 5% 16V MLCC</t>
   </si>
 </sst>
 </file>
@@ -10956,7 +10977,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N116"/>
+  <dimension ref="A1:N117"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="11.1796875" customWidth="1"/>
@@ -16074,6 +16095,50 @@
         <v>62</v>
       </c>
       <c r="N116" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="117" spans="1:14">
+      <c r="A117" s="4" t="s">
+        <v>3468</v>
+      </c>
+      <c r="B117" t="s">
+        <v>3469</v>
+      </c>
+      <c r="C117" t="s">
+        <v>3467</v>
+      </c>
+      <c r="D117" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="E117" s="36" t="s">
+        <v>3463</v>
+      </c>
+      <c r="F117" s="3" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G117" t="s">
+        <v>3464</v>
+      </c>
+      <c r="H117" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I117" s="27" t="s">
+        <v>3465</v>
+      </c>
+      <c r="J117" s="27" t="s">
+        <v>3466</v>
+      </c>
+      <c r="K117" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="L117" t="s">
+        <v>61</v>
+      </c>
+      <c r="M117" s="7" t="s">
+        <v>698</v>
+      </c>
+      <c r="N117" t="s">
         <v>25</v>
       </c>
     </row>
@@ -16171,9 +16236,11 @@
     <hyperlink ref="J114" r:id="rId89" xr:uid="{FB1B8B94-45EA-4535-BE3A-72D28A8B6781}"/>
     <hyperlink ref="J115" r:id="rId90" xr:uid="{88671F05-A2EE-487E-BF71-2F48DB15577D}"/>
     <hyperlink ref="I115" r:id="rId91" xr:uid="{42FBB82F-FA0A-49B4-BEC5-E4E89D6CB366}"/>
+    <hyperlink ref="I117" r:id="rId92" xr:uid="{23D714D4-7CC4-4BAB-A4CC-6A79467AD22E}"/>
+    <hyperlink ref="J117" r:id="rId93" xr:uid="{0C0CFB93-4989-4142-A8A1-5426DCB29DF6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId92"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId94"/>
 </worksheet>
 </file>
 

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BE23959-6875-40F2-AEF9-9D4DBB8E573D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7643704E-0F7D-4704-8899-B926297121C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32280" yWindow="2235" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="46695" yWindow="2355" windowWidth="14610" windowHeight="15585" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6964" uniqueCount="3470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7020" uniqueCount="3502">
   <si>
     <t>ID</t>
   </si>
@@ -10457,6 +10457,102 @@
   </si>
   <si>
     <t>Condensadores de cerámica multicapa (MLCC- SMD/SMT) WCAP-CSGP 100pF 0402 5% 16V MLCC</t>
+  </si>
+  <si>
+    <t>1812VC105KAT2A</t>
+  </si>
+  <si>
+    <t>581-1812VC105KAT2A</t>
+  </si>
+  <si>
+    <t>https://datasheets.kyocera-avx.com/AVX-HV_MLCC.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/KYOCERA-AVX/1812VC105KAT2A?qs=sGAEpiMZZMvsSlwiRhF8qtsBU8Zhqm2RiX3yQof58UA8TRVHqLE0IA%3D%3D</t>
+  </si>
+  <si>
+    <t>C4532X7T2E684M160KA</t>
+  </si>
+  <si>
+    <t>810-C4532X7T2E684M6K</t>
+  </si>
+  <si>
+    <t>https://product.tdk.com/system/files/dam/doc/product/capacitor/ceramic/mlcc/catalog/mlcc_commercial_highvoltage_en.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/TDK/C4532X7T2E684M160KA?qs=sGAEpiMZZMvsSlwiRhF8qtKev7nvVKumgcECMxBqJildLuXsoVBqzA%3D%3D</t>
+  </si>
+  <si>
+    <t>Condensadores de cerámica multicapa (MLCC- SMD/SMT) 250V 1uF X7R 1812 10 %</t>
+  </si>
+  <si>
+    <t>250V 1uF X7R</t>
+  </si>
+  <si>
+    <t>250V 680nF X7T</t>
+  </si>
+  <si>
+    <t>Condensadores de cerámica multicapa (MLCC- SMD/SMT) 1812 250V 0.68uF X7T 20% T: 1.6mm</t>
+  </si>
+  <si>
+    <t>001-0117</t>
+  </si>
+  <si>
+    <t>001-0118</t>
+  </si>
+  <si>
+    <t>004-0002</t>
+  </si>
+  <si>
+    <t>Condensadores de seguridad 500volts 680pF 20% LS=15mm</t>
+  </si>
+  <si>
+    <t>1.5kV 680pF Y1</t>
+  </si>
+  <si>
+    <t>THT;W5.5xL18mm</t>
+  </si>
+  <si>
+    <t>P295BE681M500A</t>
+  </si>
+  <si>
+    <t>80-P295BE681M500A</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/datasheet/3/72/1/KEM_F3088_P295_Y1_500.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/KEMET/P295BE681M500A?qs=zoGAYOF739DgwL35ue4hHg%3D%3D</t>
+  </si>
+  <si>
+    <t>CAP_15Px12.5H</t>
+  </si>
+  <si>
+    <t>023-0002</t>
+  </si>
+  <si>
+    <t>Cebadores / filtros de modo común Filter Component</t>
+  </si>
+  <si>
+    <t>325uH 3.3A 35 %</t>
+  </si>
+  <si>
+    <t>11x11x8.8</t>
+  </si>
+  <si>
+    <t>TCK-050</t>
+  </si>
+  <si>
+    <t>495-TCK-050</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/datasheet/3/1230/1/tck_050_datasheet.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/TRACO-Power/TCK-050?qs=ckJk83FOD0VjpXDswRrv6g%3D%3D</t>
+  </si>
+  <si>
+    <t>IND_CMM_THT_11x11mm</t>
   </si>
 </sst>
 </file>
@@ -10635,7 +10731,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -10694,6 +10790,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -10977,7 +11075,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N117"/>
+  <dimension ref="A1:N119"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="11.1796875" customWidth="1"/>
@@ -16139,6 +16237,94 @@
         <v>698</v>
       </c>
       <c r="N117" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="118" spans="1:14">
+      <c r="A118" s="4" t="s">
+        <v>3482</v>
+      </c>
+      <c r="B118" t="s">
+        <v>3478</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>3479</v>
+      </c>
+      <c r="D118" s="13" t="s">
+        <v>3222</v>
+      </c>
+      <c r="E118" t="s">
+        <v>3470</v>
+      </c>
+      <c r="F118" s="3" t="s">
+        <v>3005</v>
+      </c>
+      <c r="G118" s="3" t="s">
+        <v>3471</v>
+      </c>
+      <c r="H118" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I118" s="27" t="s">
+        <v>3472</v>
+      </c>
+      <c r="J118" s="32" t="s">
+        <v>3473</v>
+      </c>
+      <c r="K118" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="L118" t="s">
+        <v>61</v>
+      </c>
+      <c r="M118" s="7" t="s">
+        <v>3227</v>
+      </c>
+      <c r="N118" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="119" spans="1:14">
+      <c r="A119" s="4" t="s">
+        <v>3483</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>3481</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>3480</v>
+      </c>
+      <c r="D119" s="13" t="s">
+        <v>3222</v>
+      </c>
+      <c r="E119" t="s">
+        <v>3474</v>
+      </c>
+      <c r="F119" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="G119" s="3" t="s">
+        <v>3475</v>
+      </c>
+      <c r="H119" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I119" s="27" t="s">
+        <v>3476</v>
+      </c>
+      <c r="J119" s="32" t="s">
+        <v>3477</v>
+      </c>
+      <c r="K119" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="L119" t="s">
+        <v>61</v>
+      </c>
+      <c r="M119" s="7" t="s">
+        <v>3227</v>
+      </c>
+      <c r="N119" t="s">
         <v>25</v>
       </c>
     </row>
@@ -16238,9 +16424,13 @@
     <hyperlink ref="I115" r:id="rId91" xr:uid="{42FBB82F-FA0A-49B4-BEC5-E4E89D6CB366}"/>
     <hyperlink ref="I117" r:id="rId92" xr:uid="{23D714D4-7CC4-4BAB-A4CC-6A79467AD22E}"/>
     <hyperlink ref="J117" r:id="rId93" xr:uid="{0C0CFB93-4989-4142-A8A1-5426DCB29DF6}"/>
+    <hyperlink ref="I118" r:id="rId94" xr:uid="{E8F66462-23F8-4357-86E4-F00E1DDD00BD}"/>
+    <hyperlink ref="J118" r:id="rId95" xr:uid="{0DDD8FD6-EB7C-4099-AC8D-546E7FFB975A}"/>
+    <hyperlink ref="I119" r:id="rId96" xr:uid="{3E85D3AE-5734-420B-B08C-558D7D7AE59C}"/>
+    <hyperlink ref="J119" r:id="rId97" xr:uid="{4F7D3F8C-8C44-41BA-BBA8-939E653CA2D5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId94"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId98"/>
 </worksheet>
 </file>
 
@@ -25029,14 +25219,56 @@
       </c>
     </row>
     <row r="3" spans="1:14">
-      <c r="E3" s="36"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
+      <c r="A3" t="s">
+        <v>3484</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>3485</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>3486</v>
+      </c>
+      <c r="D3" s="38" t="s">
+        <v>3487</v>
+      </c>
+      <c r="E3" t="s">
+        <v>3488</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>3316</v>
+      </c>
+      <c r="G3" t="s">
+        <v>3489</v>
+      </c>
+      <c r="H3" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="27" t="s">
+        <v>3490</v>
+      </c>
+      <c r="J3" s="27" t="s">
+        <v>3491</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="L3" t="s">
+        <v>61</v>
+      </c>
+      <c r="M3" t="s">
+        <v>3492</v>
+      </c>
+      <c r="N3" t="s">
+        <v>25</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="16" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1" xr:uid="{A3195937-552B-4025-8C26-81ADB44BFFC2}"/>
     <hyperlink ref="J2" r:id="rId2" xr:uid="{52A98722-6674-4772-ABA0-DFA6125FAC08}"/>
+    <hyperlink ref="I3" r:id="rId3" xr:uid="{349067E1-E702-4B84-8148-B4C1A22F177F}"/>
+    <hyperlink ref="J3" r:id="rId4" xr:uid="{C828D96D-14A3-4C4F-A35B-A9CD2A9F5BC8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -32661,7 +32893,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D956EFE-E955-4E62-8478-2294E6413DC1}">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:14">
@@ -32752,9 +32984,56 @@
         <v>25</v>
       </c>
     </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>3493</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>3494</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>3495</v>
+      </c>
+      <c r="D3" s="39" t="s">
+        <v>3496</v>
+      </c>
+      <c r="E3" t="s">
+        <v>3497</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>3498</v>
+      </c>
+      <c r="H3" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="27" t="s">
+        <v>3499</v>
+      </c>
+      <c r="J3" s="32" t="s">
+        <v>3500</v>
+      </c>
+      <c r="K3" t="s">
+        <v>2903</v>
+      </c>
+      <c r="L3" t="s">
+        <v>2904</v>
+      </c>
+      <c r="M3" t="s">
+        <v>3501</v>
+      </c>
+      <c r="N3" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="16" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1" xr:uid="{1A9E4CB0-A8E7-4FC1-A9A7-FA5E28311F4C}"/>
+    <hyperlink ref="I3" r:id="rId2" xr:uid="{56FF5CE4-5A16-43B7-A444-8540568671A8}"/>
+    <hyperlink ref="J3" r:id="rId3" xr:uid="{5A2C53EE-4AA9-4D60-B6B6-16BED3AC487F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7643704E-0F7D-4704-8899-B926297121C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE71E387-20A1-4B98-8AE0-E7021B06AE43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="46695" yWindow="2355" windowWidth="14610" windowHeight="15585" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="46695" yWindow="2355" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7020" uniqueCount="3502">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7105" uniqueCount="3543">
   <si>
     <t>ID</t>
   </si>
@@ -10553,6 +10553,129 @@
   </si>
   <si>
     <t>IND_CMM_THT_11x11mm</t>
+  </si>
+  <si>
+    <t>010-0161</t>
+  </si>
+  <si>
+    <t>010-0162</t>
+  </si>
+  <si>
+    <t>010-0163</t>
+  </si>
+  <si>
+    <t>010-0164</t>
+  </si>
+  <si>
+    <t>Thin Film Resistors CHIP RESISTOR Precision</t>
+  </si>
+  <si>
+    <t>Thin Film Resistors 0805 1.8Kohm 0.1% 10ppm AEC-Q200</t>
+  </si>
+  <si>
+    <t>Thin Film Resistors RP 2A 20R 0.1% 15PPM CUT LENGTH</t>
+  </si>
+  <si>
+    <t>Thin Film Resistors 0805 2.2Kohm 0.1% 15ppm AEC-Q200</t>
+  </si>
+  <si>
+    <t>1MΩ 125mW ±0.1%</t>
+  </si>
+  <si>
+    <t>1.8kΩ 125mW ±0.1%</t>
+  </si>
+  <si>
+    <t>20Ω 125mW ±0.1%</t>
+  </si>
+  <si>
+    <t>2.2kΩ 125mW ±0.1%</t>
+  </si>
+  <si>
+    <t>CRT1206-BW-1004ELF</t>
+  </si>
+  <si>
+    <t>652-CRT1206BW1004ELF</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/datasheet/3/40/1/CRT.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Bourns/CRT1206-BW-1004ELF?qs=sGAEpiMZZMvdGkrng054t9uZ12tsVZVXUwFPKPuMiMw%3D</t>
+  </si>
+  <si>
+    <t>ERA-6ARB182V</t>
+  </si>
+  <si>
+    <t>667-ERA-6ARB182V</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Panasonic/ERA-6ARB182V?qs=sGAEpiMZZMvdGkrng054t7Q%2FBjLwFmgiTwW2qqIgdzU%3D</t>
+  </si>
+  <si>
+    <t>RP73D2A20RBTG</t>
+  </si>
+  <si>
+    <t>TE</t>
+  </si>
+  <si>
+    <t>279-RP73D2A20RBTG</t>
+  </si>
+  <si>
+    <t>https://www.te.com/commerce/DocumentDelivery/DDEController?Action=showdoc&amp;DocId=Data+Sheet%7F1773272%7FL%7Fpdf%7FEnglish%7FENG_DS_1773272_L.pdf%7F</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/TE-Connectivity-Holsworthy/RP73D2A20RBTG?qs=sGAEpiMZZMvdGkrng054t9WFtWtrbdtG%2F6%2Fjgh8ECZ8%3D</t>
+  </si>
+  <si>
+    <t>ERA-6APB222V</t>
+  </si>
+  <si>
+    <t>667-ERA-6APB222V</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Panasonic/ERA-6APB222V?qs=sGAEpiMZZMvdGkrng054t7Q%2FBjLwFmgixWLzItBYhMc%3D</t>
+  </si>
+  <si>
+    <t>001-0119</t>
+  </si>
+  <si>
+    <t>001-0120</t>
+  </si>
+  <si>
+    <t>Condensadores de cerámica multicapa (MLCC- SMD/SMT) 25V 10pF C0G 0402 0. 1pF</t>
+  </si>
+  <si>
+    <t>Condensadores de cerámica multicapa (MLCC- SMD/SMT) 0603 330pF 25volts C0G 1%</t>
+  </si>
+  <si>
+    <t>25V 10pF NP0</t>
+  </si>
+  <si>
+    <t>25V 330pF NP0</t>
+  </si>
+  <si>
+    <t>04023A100BAT2A</t>
+  </si>
+  <si>
+    <t>581-04023A100BAT2A</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/datasheet/3/5926/1/C0GNP0_Dielectric.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/KYOCERA-AVX/04023A100BAT2A?qs=Op3aA%252BNiUY5yU4vAZ7xiKg%3D%3D</t>
+  </si>
+  <si>
+    <t>VJ0603A331FXXCW1BC</t>
+  </si>
+  <si>
+    <t>77-VJ0603A331FXXCBC</t>
+  </si>
+  <si>
+    <t>https://www.vishay.com/docs/28548/vjw1bcbascomseries.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Vishay-Vitramon/VJ0603A331FXXCW1BC?qs=%2Fh0R4aLiLgPLKHvkP5P%252BKw%3D%3D</t>
   </si>
 </sst>
 </file>
@@ -10731,7 +10854,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -10790,8 +10913,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -11075,7 +11197,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N119"/>
+  <dimension ref="A1:N121"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="11.1796875" customWidth="1"/>
@@ -16325,6 +16447,94 @@
         <v>3227</v>
       </c>
       <c r="N119" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="120" spans="1:14">
+      <c r="A120" s="4" t="s">
+        <v>3529</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>3531</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>3533</v>
+      </c>
+      <c r="D120" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="E120" t="s">
+        <v>3535</v>
+      </c>
+      <c r="F120" t="s">
+        <v>3005</v>
+      </c>
+      <c r="G120" t="s">
+        <v>3536</v>
+      </c>
+      <c r="H120" t="s">
+        <v>21</v>
+      </c>
+      <c r="I120" s="2" t="s">
+        <v>3537</v>
+      </c>
+      <c r="J120" s="2" t="s">
+        <v>3538</v>
+      </c>
+      <c r="K120" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="L120" t="s">
+        <v>61</v>
+      </c>
+      <c r="M120" s="7" t="s">
+        <v>698</v>
+      </c>
+      <c r="N120" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="121" spans="1:14">
+      <c r="A121" s="4" t="s">
+        <v>3530</v>
+      </c>
+      <c r="B121" t="s">
+        <v>3532</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>3534</v>
+      </c>
+      <c r="D121" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="E121" t="s">
+        <v>3539</v>
+      </c>
+      <c r="F121" t="s">
+        <v>3311</v>
+      </c>
+      <c r="G121" t="s">
+        <v>3540</v>
+      </c>
+      <c r="H121" t="s">
+        <v>21</v>
+      </c>
+      <c r="I121" t="s">
+        <v>3541</v>
+      </c>
+      <c r="J121" s="2" t="s">
+        <v>3542</v>
+      </c>
+      <c r="K121" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="L121" t="s">
+        <v>61</v>
+      </c>
+      <c r="M121" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="N121" t="s">
         <v>25</v>
       </c>
     </row>
@@ -16428,9 +16638,12 @@
     <hyperlink ref="J118" r:id="rId95" xr:uid="{0DDD8FD6-EB7C-4099-AC8D-546E7FFB975A}"/>
     <hyperlink ref="I119" r:id="rId96" xr:uid="{3E85D3AE-5734-420B-B08C-558D7D7AE59C}"/>
     <hyperlink ref="J119" r:id="rId97" xr:uid="{4F7D3F8C-8C44-41BA-BBA8-939E653CA2D5}"/>
+    <hyperlink ref="I120" r:id="rId98" xr:uid="{C96C48DA-EDC8-49C8-AF84-EC04D1CADF1F}"/>
+    <hyperlink ref="J120" r:id="rId99" xr:uid="{82BD7645-36AC-4B87-A6AC-DC24E52B487C}"/>
+    <hyperlink ref="J121" r:id="rId100" xr:uid="{8D158E67-4FC0-4FA4-904D-A0664134DB5C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId98"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId101"/>
 </worksheet>
 </file>
 
@@ -25228,7 +25441,7 @@
       <c r="C3" s="3" t="s">
         <v>3486</v>
       </c>
-      <c r="D3" s="38" t="s">
+      <c r="D3" s="3" t="s">
         <v>3487</v>
       </c>
       <c r="E3" t="s">
@@ -25276,7 +25489,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60E8291E-4293-4634-B9E9-80CB520CA181}">
-  <dimension ref="A1:N161"/>
+  <dimension ref="A1:N165"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="3" max="3" width="19.90625" customWidth="1"/>
@@ -32337,8 +32550,8 @@
       <c r="D161" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="E161">
-        <v>560112116001</v>
+      <c r="E161" s="36" t="s">
+        <v>3106</v>
       </c>
       <c r="F161" s="16" t="s">
         <v>2100</v>
@@ -32365,6 +32578,182 @@
         <v>57</v>
       </c>
       <c r="N161" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="162" spans="1:14">
+      <c r="A162" s="16" t="s">
+        <v>3502</v>
+      </c>
+      <c r="B162" s="3" t="s">
+        <v>3506</v>
+      </c>
+      <c r="C162" s="16" t="s">
+        <v>3510</v>
+      </c>
+      <c r="D162" s="38" t="s">
+        <v>249</v>
+      </c>
+      <c r="E162" t="s">
+        <v>3514</v>
+      </c>
+      <c r="F162" s="3" t="s">
+        <v>1516</v>
+      </c>
+      <c r="G162" s="3" t="s">
+        <v>3515</v>
+      </c>
+      <c r="H162" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I162" s="27" t="s">
+        <v>3516</v>
+      </c>
+      <c r="J162" s="32" t="s">
+        <v>3517</v>
+      </c>
+      <c r="K162" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L162" s="17" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M162" s="7" t="s">
+        <v>1645</v>
+      </c>
+      <c r="N162" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="163" spans="1:14">
+      <c r="A163" s="16" t="s">
+        <v>3503</v>
+      </c>
+      <c r="B163" s="3" t="s">
+        <v>3507</v>
+      </c>
+      <c r="C163" s="16" t="s">
+        <v>3511</v>
+      </c>
+      <c r="D163" s="20" t="s">
+        <v>240</v>
+      </c>
+      <c r="E163" t="s">
+        <v>3518</v>
+      </c>
+      <c r="F163" s="3" t="s">
+        <v>3342</v>
+      </c>
+      <c r="G163" s="3" t="s">
+        <v>3519</v>
+      </c>
+      <c r="H163" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I163" s="27" t="s">
+        <v>3344</v>
+      </c>
+      <c r="J163" s="32" t="s">
+        <v>3520</v>
+      </c>
+      <c r="K163" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L163" s="17" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M163" s="17" t="s">
+        <v>1646</v>
+      </c>
+      <c r="N163" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="164" spans="1:14">
+      <c r="A164" s="16" t="s">
+        <v>3504</v>
+      </c>
+      <c r="B164" s="3" t="s">
+        <v>3508</v>
+      </c>
+      <c r="C164" s="16" t="s">
+        <v>3512</v>
+      </c>
+      <c r="D164" s="20" t="s">
+        <v>240</v>
+      </c>
+      <c r="E164" t="s">
+        <v>3521</v>
+      </c>
+      <c r="F164" s="3" t="s">
+        <v>3522</v>
+      </c>
+      <c r="G164" s="3" t="s">
+        <v>3523</v>
+      </c>
+      <c r="H164" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I164" s="27" t="s">
+        <v>3524</v>
+      </c>
+      <c r="J164" s="32" t="s">
+        <v>3525</v>
+      </c>
+      <c r="K164" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L164" s="17" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M164" s="17" t="s">
+        <v>1646</v>
+      </c>
+      <c r="N164" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="165" spans="1:14">
+      <c r="A165" s="16" t="s">
+        <v>3505</v>
+      </c>
+      <c r="B165" t="s">
+        <v>3509</v>
+      </c>
+      <c r="C165" s="16" t="s">
+        <v>3513</v>
+      </c>
+      <c r="D165" s="20" t="s">
+        <v>240</v>
+      </c>
+      <c r="E165" t="s">
+        <v>3526</v>
+      </c>
+      <c r="F165" s="3" t="s">
+        <v>3342</v>
+      </c>
+      <c r="G165" s="3" t="s">
+        <v>3527</v>
+      </c>
+      <c r="H165" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I165" t="s">
+        <v>3344</v>
+      </c>
+      <c r="J165" t="s">
+        <v>3528</v>
+      </c>
+      <c r="K165" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L165" s="17" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M165" s="17" t="s">
+        <v>1646</v>
+      </c>
+      <c r="N165" t="s">
         <v>25</v>
       </c>
     </row>
@@ -32494,9 +32883,15 @@
     <hyperlink ref="I160" r:id="rId121" xr:uid="{38247BF1-5599-4165-BFEC-26629D789AC3}"/>
     <hyperlink ref="I161" r:id="rId122" xr:uid="{7C28565D-C222-4AEC-81A3-9D2C8C79A1A1}"/>
     <hyperlink ref="J161" r:id="rId123" xr:uid="{3A2D1BFE-71D6-460D-8752-1790B0BCD8EB}"/>
+    <hyperlink ref="I162" r:id="rId124" xr:uid="{4463DBEE-380B-4841-92E5-B0899C1AD050}"/>
+    <hyperlink ref="J162" r:id="rId125" xr:uid="{62FCC9B6-C758-4F6B-B770-33EEFB677F26}"/>
+    <hyperlink ref="I163" r:id="rId126" xr:uid="{B69945C4-5E62-46A4-B52C-B5FBF9EDB912}"/>
+    <hyperlink ref="J163" r:id="rId127" xr:uid="{E16CCBB4-7842-4D7A-96FB-5BD6FA1E6421}"/>
+    <hyperlink ref="I164" r:id="rId128" xr:uid="{7CE4EE78-4CA5-4B21-8D4B-AA08BC8B3267}"/>
+    <hyperlink ref="J164" r:id="rId129" xr:uid="{4DF264B3-7BEB-4A01-9BB8-A7BE1607E581}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId124"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId130"/>
 </worksheet>
 </file>
 
@@ -32994,7 +33389,7 @@
       <c r="C3" s="31" t="s">
         <v>3495</v>
       </c>
-      <c r="D3" s="39" t="s">
+      <c r="D3" s="31" t="s">
         <v>3496</v>
       </c>
       <c r="E3" t="s">

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE71E387-20A1-4B98-8AE0-E7021B06AE43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84CCC42B-63C5-43DB-A86D-E386789B4664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="46695" yWindow="2355" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="46695" yWindow="2355" windowWidth="14610" windowHeight="15585" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7105" uniqueCount="3543">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7119" uniqueCount="3551">
   <si>
     <t>ID</t>
   </si>
@@ -10676,6 +10676,30 @@
   </si>
   <si>
     <t>https://www.mouser.es/ProductDetail/Vishay-Vitramon/VJ0603A331FXXCW1BC?qs=%2Fh0R4aLiLgPLKHvkP5P%252BKw%3D%3D</t>
+  </si>
+  <si>
+    <t>010-0165</t>
+  </si>
+  <si>
+    <t>Thin Film Resistors 2.5K OHM .1% 25PPM 1/4W</t>
+  </si>
+  <si>
+    <t>2.5kΩ 250mW ±0.1%</t>
+  </si>
+  <si>
+    <t>RN73R2ATTD2501B25</t>
+  </si>
+  <si>
+    <t>KOA Speer</t>
+  </si>
+  <si>
+    <t>660-RN73R2ATTD2501B2</t>
+  </si>
+  <si>
+    <t>https://www.mouser.com/catalog/specsheets/KOA_Speer_RN73R__8_20_24.pdf?_gl=1*23gnzt*_gcl_aw*R0NMLjE3ODA5NDM2MTUuQ2owS0NRancwSm5SQmhESkFSSXNBTG9iblhiTVZmV3NWb0pqSGVpNWRkTXk2SzRuNEhwRGVRWXYxa0dMT0s1N0VWSjRWQlE1eFhBYUoxd2FBa3NuRUFMd193Y0I.*_gcl_au*MjAyMjI4MzgwOS4xNzc1NDk0ODAwLjEzNzM0NjYwNTMuMTc4MTk0MzEyNS4xNzgxOTQ0MDMw*_ga*Nzg3Njk5NTY0LjE3NDY2Mzg0MjI.*_ga_15W4STQT4T*czE3ODE5NDMwOTckbzk3JGcxJHQxNzgxOTQ0MDQwJGo0MCRsMCRoMA..</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/KOA-Speer/RN73R2ATTD2501B25?qs=sGAEpiMZZMvdGkrng054tz3%252BeNFGeSG0078E0Mg5MLJLGvMlGbhAYw%3D%3D</t>
   </si>
 </sst>
 </file>
@@ -10854,7 +10878,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -10913,7 +10937,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -25489,7 +25512,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60E8291E-4293-4634-B9E9-80CB520CA181}">
-  <dimension ref="A1:N165"/>
+  <dimension ref="A1:N166"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="3" max="3" width="19.90625" customWidth="1"/>
@@ -32591,7 +32614,7 @@
       <c r="C162" s="16" t="s">
         <v>3510</v>
       </c>
-      <c r="D162" s="38" t="s">
+      <c r="D162" s="20" t="s">
         <v>249</v>
       </c>
       <c r="E162" t="s">
@@ -32754,6 +32777,50 @@
         <v>1646</v>
       </c>
       <c r="N165" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="166" spans="1:14">
+      <c r="A166" s="16" t="s">
+        <v>3543</v>
+      </c>
+      <c r="B166" s="16" t="s">
+        <v>3544</v>
+      </c>
+      <c r="C166" s="16" t="s">
+        <v>3545</v>
+      </c>
+      <c r="D166" s="20" t="s">
+        <v>240</v>
+      </c>
+      <c r="E166" t="s">
+        <v>3546</v>
+      </c>
+      <c r="F166" s="3" t="s">
+        <v>3547</v>
+      </c>
+      <c r="G166" t="s">
+        <v>3548</v>
+      </c>
+      <c r="H166" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I166" s="27" t="s">
+        <v>3549</v>
+      </c>
+      <c r="J166" s="32" t="s">
+        <v>3550</v>
+      </c>
+      <c r="K166" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L166" s="17" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M166" s="17" t="s">
+        <v>1646</v>
+      </c>
+      <c r="N166" t="s">
         <v>25</v>
       </c>
     </row>
@@ -32889,9 +32956,11 @@
     <hyperlink ref="J163" r:id="rId127" xr:uid="{E16CCBB4-7842-4D7A-96FB-5BD6FA1E6421}"/>
     <hyperlink ref="I164" r:id="rId128" xr:uid="{7CE4EE78-4CA5-4B21-8D4B-AA08BC8B3267}"/>
     <hyperlink ref="J164" r:id="rId129" xr:uid="{4DF264B3-7BEB-4A01-9BB8-A7BE1607E581}"/>
+    <hyperlink ref="I166" r:id="rId130" display="https://www.mouser.com/catalog/specsheets/KOA_Speer_RN73R__8_20_24.pdf?_gl=1*23gnzt*_gcl_aw*R0NMLjE3ODA5NDM2MTUuQ2owS0NRancwSm5SQmhESkFSSXNBTG9iblhiTVZmV3NWb0pqSGVpNWRkTXk2SzRuNEhwRGVRWXYxa0dMT0s1N0VWSjRWQlE1eFhBYUoxd2FBa3NuRUFMd193Y0I.*_gcl_au*MjAyMjI4MzgwOS4xNzc1NDk0ODAwLjEzNzM0NjYwNTMuMTc4MTk0MzEyNS4xNzgxOTQ0MDMw*_ga*Nzg3Njk5NTY0LjE3NDY2Mzg0MjI.*_ga_15W4STQT4T*czE3ODE5NDMwOTckbzk3JGcxJHQxNzgxOTQ0MDQwJGo0MCRsMCRoMA.." xr:uid="{637208B5-2C9A-4EEB-9CE7-9AEB37AC38F3}"/>
+    <hyperlink ref="J166" r:id="rId131" xr:uid="{C0A169AF-232E-42CF-80E5-11600433186C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId130"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId132"/>
 </worksheet>
 </file>
 

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84CCC42B-63C5-43DB-A86D-E386789B4664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAE49C5F-8453-40D1-9455-8A9AA12F7A5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="46695" yWindow="2355" windowWidth="14610" windowHeight="15585" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="46695" yWindow="2355" windowWidth="14610" windowHeight="15585" firstSheet="21" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7119" uniqueCount="3551">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7132" uniqueCount="3559">
   <si>
     <t>ID</t>
   </si>
@@ -10700,6 +10700,30 @@
   </si>
   <si>
     <t>https://www.mouser.es/ProductDetail/KOA-Speer/RN73R2ATTD2501B25?qs=sGAEpiMZZMvdGkrng054tz3%252BeNFGeSG0078E0Mg5MLJLGvMlGbhAYw%3D%3D</t>
+  </si>
+  <si>
+    <t>110-0064</t>
+  </si>
+  <si>
+    <t>Wurth Elektronik Latón Terminal roscado Ángulo de 90° 340A</t>
+  </si>
+  <si>
+    <t>M10</t>
+  </si>
+  <si>
+    <t>7461117</t>
+  </si>
+  <si>
+    <t>122-4987</t>
+  </si>
+  <si>
+    <t>RS Components</t>
+  </si>
+  <si>
+    <t>https://docs.rs-online.com/2b0b/0900766b814ffbea.pdf</t>
+  </si>
+  <si>
+    <t>https://es.rs-online.com/web/p/terminales-roscados/1224987</t>
   </si>
 </sst>
 </file>
@@ -10878,7 +10902,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -10937,6 +10961,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -22470,7 +22495,7 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE14AD29-8DB0-4C42-AB91-A73B867AE121}">
-  <dimension ref="A1:N64"/>
+  <dimension ref="A1:N65"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="5" max="5" width="16.36328125" bestFit="1" customWidth="1"/>
@@ -25291,6 +25316,50 @@
         <v>7461090</v>
       </c>
       <c r="N64" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14">
+      <c r="A65" s="16" t="s">
+        <v>3551</v>
+      </c>
+      <c r="B65" t="s">
+        <v>3552</v>
+      </c>
+      <c r="C65" s="16" t="s">
+        <v>2488</v>
+      </c>
+      <c r="D65" s="38" t="s">
+        <v>3553</v>
+      </c>
+      <c r="E65" s="36" t="s">
+        <v>3554</v>
+      </c>
+      <c r="F65" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G65" t="s">
+        <v>3555</v>
+      </c>
+      <c r="H65" t="s">
+        <v>3556</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>3557</v>
+      </c>
+      <c r="J65" s="2" t="s">
+        <v>3558</v>
+      </c>
+      <c r="K65" s="17" t="s">
+        <v>2429</v>
+      </c>
+      <c r="L65" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M65" s="36">
+        <v>7461117</v>
+      </c>
+      <c r="N65" s="7" t="s">
         <v>25</v>
       </c>
     </row>

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAE49C5F-8453-40D1-9455-8A9AA12F7A5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1969BA44-1E51-4A0E-BA04-CB57746DC593}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="46695" yWindow="2355" windowWidth="14610" windowHeight="15585" firstSheet="21" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="46695" yWindow="2355" windowWidth="14610" windowHeight="15585" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7132" uniqueCount="3559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7146" uniqueCount="3566">
   <si>
     <t>ID</t>
   </si>
@@ -10724,6 +10724,27 @@
   </si>
   <si>
     <t>https://es.rs-online.com/web/p/terminales-roscados/1224987</t>
+  </si>
+  <si>
+    <t>CRT1206ABY-1003ELF</t>
+  </si>
+  <si>
+    <t>652-CRT1206ABY-1003E</t>
+  </si>
+  <si>
+    <t>https://www.mouser.com/catalog/specsheets/Bourns_08052024_CRT-A_Datasheet.pdf?_gl=1*1yxig20*_gcl_aw*R0NMLjE3ODA5NDM2MTUuQ2owS0NRancwSm5SQmhESkFSSXNBTG9iblhiTVZmV3NWb0pqSGVpNWRkTXk2SzRuNEhwRGVRWXYxa0dMT0s1N0VWSjRWQlE1eFhBYUoxd2FBa3NuRUFMd193Y0I.*_gcl_au*MjAyMjI4MzgwOS4xNzc1NDk0ODAwLjIwNTEzODM1NjYuMTc4MTk3NjAxMC4xNzgxOTc2MzUx*_ga*Nzg3Njk5NTY0LjE3NDY2Mzg0MjI.*_ga_15W4STQT4T*czE3ODE5NzU4ODEkbzEwMSRnMSR0MTc4MTk3NjM2NyRqMTIkbDAkaDA.</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Bourns/CRT1206ABY-1003ELF?qs=IKkN%2F947nfBi3pROFgBLfA%3D%3D</t>
+  </si>
+  <si>
+    <t>100kΩ 250mW ±0.1%</t>
+  </si>
+  <si>
+    <t>Resistores de película fina - SMD ResThinFilm 1206 100kR 0.1% 250mW TC25</t>
+  </si>
+  <si>
+    <t>010-0166</t>
   </si>
 </sst>
 </file>
@@ -10902,7 +10923,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -10961,7 +10982,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -25329,7 +25349,7 @@
       <c r="C65" s="16" t="s">
         <v>2488</v>
       </c>
-      <c r="D65" s="38" t="s">
+      <c r="D65" s="16" t="s">
         <v>3553</v>
       </c>
       <c r="E65" s="36" t="s">
@@ -25581,7 +25601,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60E8291E-4293-4634-B9E9-80CB520CA181}">
-  <dimension ref="A1:N166"/>
+  <dimension ref="A1:N167"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="3" max="3" width="19.90625" customWidth="1"/>
@@ -32890,6 +32910,50 @@
         <v>1646</v>
       </c>
       <c r="N166" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="167" spans="1:14">
+      <c r="A167" s="16" t="s">
+        <v>3565</v>
+      </c>
+      <c r="B167" s="16" t="s">
+        <v>3564</v>
+      </c>
+      <c r="C167" s="16" t="s">
+        <v>3563</v>
+      </c>
+      <c r="D167" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="E167" t="s">
+        <v>3559</v>
+      </c>
+      <c r="F167" s="3" t="s">
+        <v>1516</v>
+      </c>
+      <c r="G167" s="3" t="s">
+        <v>3560</v>
+      </c>
+      <c r="H167" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I167" t="s">
+        <v>3561</v>
+      </c>
+      <c r="J167" s="2" t="s">
+        <v>3562</v>
+      </c>
+      <c r="K167" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L167" s="17" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M167" s="7" t="s">
+        <v>1645</v>
+      </c>
+      <c r="N167" t="s">
         <v>25</v>
       </c>
     </row>
@@ -33027,9 +33091,10 @@
     <hyperlink ref="J164" r:id="rId129" xr:uid="{4DF264B3-7BEB-4A01-9BB8-A7BE1607E581}"/>
     <hyperlink ref="I166" r:id="rId130" display="https://www.mouser.com/catalog/specsheets/KOA_Speer_RN73R__8_20_24.pdf?_gl=1*23gnzt*_gcl_aw*R0NMLjE3ODA5NDM2MTUuQ2owS0NRancwSm5SQmhESkFSSXNBTG9iblhiTVZmV3NWb0pqSGVpNWRkTXk2SzRuNEhwRGVRWXYxa0dMT0s1N0VWSjRWQlE1eFhBYUoxd2FBa3NuRUFMd193Y0I.*_gcl_au*MjAyMjI4MzgwOS4xNzc1NDk0ODAwLjEzNzM0NjYwNTMuMTc4MTk0MzEyNS4xNzgxOTQ0MDMw*_ga*Nzg3Njk5NTY0LjE3NDY2Mzg0MjI.*_ga_15W4STQT4T*czE3ODE5NDMwOTckbzk3JGcxJHQxNzgxOTQ0MDQwJGo0MCRsMCRoMA.." xr:uid="{637208B5-2C9A-4EEB-9CE7-9AEB37AC38F3}"/>
     <hyperlink ref="J166" r:id="rId131" xr:uid="{C0A169AF-232E-42CF-80E5-11600433186C}"/>
+    <hyperlink ref="J167" r:id="rId132" xr:uid="{42A48B33-700F-4889-AE6E-DC32FECC2541}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId132"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId133"/>
 </worksheet>
 </file>
 

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1969BA44-1E51-4A0E-BA04-CB57746DC593}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBE110CB-2630-4579-9C13-EC515E231E35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="46695" yWindow="2355" windowWidth="14610" windowHeight="15585" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32280" yWindow="2235" windowWidth="29040" windowHeight="15720" firstSheet="13" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBE110CB-2630-4579-9C13-EC515E231E35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FA4BEBE-085A-4A84-AC25-2280EFC350FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32280" yWindow="2235" windowWidth="29040" windowHeight="15720" firstSheet="13" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32280" yWindow="2235" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7146" uniqueCount="3566">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7202" uniqueCount="3591">
   <si>
     <t>ID</t>
   </si>
@@ -10745,6 +10745,81 @@
   </si>
   <si>
     <t>010-0166</t>
+  </si>
+  <si>
+    <t>010-0167</t>
+  </si>
+  <si>
+    <t>010-0168</t>
+  </si>
+  <si>
+    <t>010-0169</t>
+  </si>
+  <si>
+    <t>Thin Film Resistors 0805 Thin film chip resistor</t>
+  </si>
+  <si>
+    <t>Thin Film Resistors 0805 3Kohm 0.1% 15ppm AEC-Q200</t>
+  </si>
+  <si>
+    <t>Thin Film Resistors 0805 33Kohm 0.1% 15ppm AEC-Q200</t>
+  </si>
+  <si>
+    <t>16.5kΩ 125mW ±0.1%</t>
+  </si>
+  <si>
+    <t>3kΩ 125mW ±0.1%</t>
+  </si>
+  <si>
+    <t>33kΩ 125mW ±0.1%</t>
+  </si>
+  <si>
+    <t>ERA-6ARB1652V</t>
+  </si>
+  <si>
+    <t>667-ERA-6ARB1652V</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Panasonic/ERA-6ARB1652V?qs=sGAEpiMZZMvdGkrng054t%2FDNinWxsEFqx8wKlfWZmnLEWdfrAdOy9w%3D%3D</t>
+  </si>
+  <si>
+    <t>ERA-6APB302V</t>
+  </si>
+  <si>
+    <t>667-ERA-6APB302V</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Panasonic/ERA-6APB302V?qs=sGAEpiMZZMvdGkrng054t7Q%2FBjLwFmgiNXNWyxy63ps%3D</t>
+  </si>
+  <si>
+    <t>ERA-6APB333V</t>
+  </si>
+  <si>
+    <t>667-ERA-6APB333V</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Panasonic/ERA-6APB333V?qs=sGAEpiMZZMvdGkrng054t7Q%2FBjLwFmgi3idxPYTcWw0%3D</t>
+  </si>
+  <si>
+    <t>001-0121</t>
+  </si>
+  <si>
+    <t>Condensadores de cerámica multicapa (MLCC- SMD/SMT) 25V 1500pF C0G 0603 1%</t>
+  </si>
+  <si>
+    <t>16V 1.5nF NP0</t>
+  </si>
+  <si>
+    <t>C0603C152F3GECTU</t>
+  </si>
+  <si>
+    <t>80-C0603C152F3GEC</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/datasheet/3/508/1/KEM_C1091_C0G_ESD.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/KEMET/C0603C152F3GECTU?qs=Mv7BduZupUh%252Bk5D8ZWarTg%3D%3D</t>
   </si>
 </sst>
 </file>
@@ -11265,7 +11340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N121"/>
+  <dimension ref="A1:N122"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="11.1796875" customWidth="1"/>
@@ -16603,6 +16678,50 @@
         <v>62</v>
       </c>
       <c r="N121" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="122" spans="1:14">
+      <c r="A122" s="4" t="s">
+        <v>3584</v>
+      </c>
+      <c r="B122" t="s">
+        <v>3585</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>3586</v>
+      </c>
+      <c r="D122" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="E122" t="s">
+        <v>3587</v>
+      </c>
+      <c r="F122" s="3" t="s">
+        <v>3316</v>
+      </c>
+      <c r="G122" s="3" t="s">
+        <v>3588</v>
+      </c>
+      <c r="H122" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I122" s="27" t="s">
+        <v>3589</v>
+      </c>
+      <c r="J122" s="27" t="s">
+        <v>3590</v>
+      </c>
+      <c r="K122" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="L122" t="s">
+        <v>61</v>
+      </c>
+      <c r="M122" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="N122" t="s">
         <v>25</v>
       </c>
     </row>
@@ -16709,9 +16828,11 @@
     <hyperlink ref="I120" r:id="rId98" xr:uid="{C96C48DA-EDC8-49C8-AF84-EC04D1CADF1F}"/>
     <hyperlink ref="J120" r:id="rId99" xr:uid="{82BD7645-36AC-4B87-A6AC-DC24E52B487C}"/>
     <hyperlink ref="J121" r:id="rId100" xr:uid="{8D158E67-4FC0-4FA4-904D-A0664134DB5C}"/>
+    <hyperlink ref="I122" r:id="rId101" xr:uid="{5646A60C-F082-4812-AAFF-C09F7BC184F6}"/>
+    <hyperlink ref="J122" r:id="rId102" xr:uid="{E13F1BFA-1BC5-4864-9D2F-0D97B5F47657}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId101"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId103"/>
 </worksheet>
 </file>
 
@@ -25601,7 +25722,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60E8291E-4293-4634-B9E9-80CB520CA181}">
-  <dimension ref="A1:N167"/>
+  <dimension ref="A1:N170"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="3" max="3" width="19.90625" customWidth="1"/>
@@ -32954,6 +33075,138 @@
         <v>1645</v>
       </c>
       <c r="N167" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="168" spans="1:14">
+      <c r="A168" s="16" t="s">
+        <v>3566</v>
+      </c>
+      <c r="B168" s="16" t="s">
+        <v>3569</v>
+      </c>
+      <c r="C168" s="16" t="s">
+        <v>3572</v>
+      </c>
+      <c r="D168" s="20" t="s">
+        <v>240</v>
+      </c>
+      <c r="E168" t="s">
+        <v>3575</v>
+      </c>
+      <c r="F168" s="3" t="s">
+        <v>3342</v>
+      </c>
+      <c r="G168" s="3" t="s">
+        <v>3576</v>
+      </c>
+      <c r="H168" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I168" s="27" t="s">
+        <v>3344</v>
+      </c>
+      <c r="J168" s="27" t="s">
+        <v>3577</v>
+      </c>
+      <c r="K168" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L168" s="17" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M168" s="17" t="s">
+        <v>1646</v>
+      </c>
+      <c r="N168" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="169" spans="1:14">
+      <c r="A169" s="16" t="s">
+        <v>3567</v>
+      </c>
+      <c r="B169" s="16" t="s">
+        <v>3570</v>
+      </c>
+      <c r="C169" s="16" t="s">
+        <v>3573</v>
+      </c>
+      <c r="D169" s="20" t="s">
+        <v>240</v>
+      </c>
+      <c r="E169" t="s">
+        <v>3578</v>
+      </c>
+      <c r="F169" s="3" t="s">
+        <v>3342</v>
+      </c>
+      <c r="G169" s="3" t="s">
+        <v>3579</v>
+      </c>
+      <c r="H169" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I169" s="27" t="s">
+        <v>3344</v>
+      </c>
+      <c r="J169" t="s">
+        <v>3580</v>
+      </c>
+      <c r="K169" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L169" s="17" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M169" s="17" t="s">
+        <v>1646</v>
+      </c>
+      <c r="N169" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="170" spans="1:14">
+      <c r="A170" s="16" t="s">
+        <v>3568</v>
+      </c>
+      <c r="B170" t="s">
+        <v>3571</v>
+      </c>
+      <c r="C170" s="16" t="s">
+        <v>3574</v>
+      </c>
+      <c r="D170" s="20" t="s">
+        <v>240</v>
+      </c>
+      <c r="E170" t="s">
+        <v>3581</v>
+      </c>
+      <c r="F170" s="3" t="s">
+        <v>3342</v>
+      </c>
+      <c r="G170" s="3" t="s">
+        <v>3582</v>
+      </c>
+      <c r="H170" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I170" t="s">
+        <v>3344</v>
+      </c>
+      <c r="J170" t="s">
+        <v>3583</v>
+      </c>
+      <c r="K170" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L170" s="17" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M170" s="17" t="s">
+        <v>1646</v>
+      </c>
+      <c r="N170" t="s">
         <v>25</v>
       </c>
     </row>
@@ -33092,9 +33345,12 @@
     <hyperlink ref="I166" r:id="rId130" display="https://www.mouser.com/catalog/specsheets/KOA_Speer_RN73R__8_20_24.pdf?_gl=1*23gnzt*_gcl_aw*R0NMLjE3ODA5NDM2MTUuQ2owS0NRancwSm5SQmhESkFSSXNBTG9iblhiTVZmV3NWb0pqSGVpNWRkTXk2SzRuNEhwRGVRWXYxa0dMT0s1N0VWSjRWQlE1eFhBYUoxd2FBa3NuRUFMd193Y0I.*_gcl_au*MjAyMjI4MzgwOS4xNzc1NDk0ODAwLjEzNzM0NjYwNTMuMTc4MTk0MzEyNS4xNzgxOTQ0MDMw*_ga*Nzg3Njk5NTY0LjE3NDY2Mzg0MjI.*_ga_15W4STQT4T*czE3ODE5NDMwOTckbzk3JGcxJHQxNzgxOTQ0MDQwJGo0MCRsMCRoMA.." xr:uid="{637208B5-2C9A-4EEB-9CE7-9AEB37AC38F3}"/>
     <hyperlink ref="J166" r:id="rId131" xr:uid="{C0A169AF-232E-42CF-80E5-11600433186C}"/>
     <hyperlink ref="J167" r:id="rId132" xr:uid="{42A48B33-700F-4889-AE6E-DC32FECC2541}"/>
+    <hyperlink ref="I168" r:id="rId133" xr:uid="{5017C3EA-65D9-46AF-AF8E-218938D0A3B7}"/>
+    <hyperlink ref="J168" r:id="rId134" xr:uid="{18E306B2-279B-447D-8479-574435B55633}"/>
+    <hyperlink ref="I169" r:id="rId135" xr:uid="{0DCBF918-6691-4999-BB88-8B4F9C447EAB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId133"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId136"/>
 </worksheet>
 </file>
 

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FA4BEBE-085A-4A84-AC25-2280EFC350FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4F02F2F-84B1-4490-AC16-5CF383DE7186}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32280" yWindow="2235" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" firstSheet="9" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7202" uniqueCount="3591">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7244" uniqueCount="3613">
   <si>
     <t>ID</t>
   </si>
@@ -10820,6 +10820,72 @@
   </si>
   <si>
     <t>https://www.mouser.es/ProductDetail/KEMET/C0603C152F3GECTU?qs=Mv7BduZupUh%252Bk5D8ZWarTg%3D%3D</t>
+  </si>
+  <si>
+    <t>010-0170</t>
+  </si>
+  <si>
+    <t>010-0171</t>
+  </si>
+  <si>
+    <t>Thick Film Resistors WRIS-RSKS 1 kOhms 1 % 0.1 W 0603 AEC-Q200</t>
+  </si>
+  <si>
+    <t>Resistores de película gruesa - SMD WRIS-RSKS 28 kOhms 1 % 0.1 W 0402 AEC-Q200</t>
+  </si>
+  <si>
+    <t>1kΩ 100mW ±1%</t>
+  </si>
+  <si>
+    <t>2.8kΩ 100mW ±1%</t>
+  </si>
+  <si>
+    <t>560112116014</t>
+  </si>
+  <si>
+    <t>710-560112116014</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/560112116014.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/560112116014?qs=sGAEpiMZZMvdGkrng054txLI%2FDB4oIKD92viHLDiYpSVemZawWv4yQ%3D%3D</t>
+  </si>
+  <si>
+    <t>560112110228</t>
+  </si>
+  <si>
+    <t>710-560112110228</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/560112110228.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/560112110228?qs=mELouGlnn3ckGB3GQT9Puw%3D%3D</t>
+  </si>
+  <si>
+    <t>050-0005</t>
+  </si>
+  <si>
+    <t>Comparadores analógicos Dual Differential A 595-TLC372CPW A 595- A 595-TLC372CPW</t>
+  </si>
+  <si>
+    <t>TSSOP-8</t>
+  </si>
+  <si>
+    <t>TLC372CPWR</t>
+  </si>
+  <si>
+    <t>595-TLC372CPWR</t>
+  </si>
+  <si>
+    <t>https://www.ti.com/lit/ds/symlink/tlc372.pdf?ts=1782158413305&amp;ref_url=https%253A%252F%252Fwww.mouser.es%252F</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Texas-Instruments/TLC372CPWR?qs=Zu35EjizYSQJQcLjIiS2wQ%3D%3D</t>
+  </si>
+  <si>
+    <t>TLC372C</t>
   </si>
 </sst>
 </file>
@@ -20168,7 +20234,7 @@
   <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="93.81640625" customWidth="1"/>
+    <col min="2" max="2" width="43.7265625" customWidth="1"/>
     <col min="5" max="5" width="16.1796875" customWidth="1"/>
     <col min="6" max="6" width="17.81640625" customWidth="1"/>
     <col min="7" max="7" width="16.7265625" customWidth="1"/>
@@ -20240,10 +20306,10 @@
         <v>18</v>
       </c>
       <c r="F2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" t="s">
         <v>19</v>
-      </c>
-      <c r="G2" t="s">
-        <v>20</v>
       </c>
       <c r="H2" t="s">
         <v>21</v>
@@ -20284,10 +20350,10 @@
         <v>39</v>
       </c>
       <c r="F3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G3" t="s">
         <v>40</v>
-      </c>
-      <c r="G3" t="s">
-        <v>41</v>
       </c>
       <c r="H3" t="s">
         <v>21</v>
@@ -20328,10 +20394,10 @@
         <v>18</v>
       </c>
       <c r="F4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" t="s">
         <v>1652</v>
-      </c>
-      <c r="G4" t="s">
-        <v>20</v>
       </c>
       <c r="H4" t="s">
         <v>69</v>
@@ -20372,10 +20438,10 @@
         <v>39</v>
       </c>
       <c r="F5" t="s">
+        <v>1658</v>
+      </c>
+      <c r="G5" t="s">
         <v>1657</v>
-      </c>
-      <c r="G5" t="s">
-        <v>1658</v>
       </c>
       <c r="H5" t="s">
         <v>69</v>
@@ -20399,17 +20465,64 @@
         <v>25</v>
       </c>
     </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>3605</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>3606</v>
+      </c>
+      <c r="C6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" t="s">
+        <v>3607</v>
+      </c>
+      <c r="E6" t="s">
+        <v>3608</v>
+      </c>
+      <c r="F6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" t="s">
+        <v>3609</v>
+      </c>
+      <c r="H6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>3610</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>3611</v>
+      </c>
+      <c r="K6" t="s">
+        <v>3612</v>
+      </c>
+      <c r="L6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M6" t="s">
+        <v>3607</v>
+      </c>
+      <c r="N6" t="s">
+        <v>25</v>
+      </c>
+    </row>
     <row r="9" spans="1:14">
       <c r="L9" s="21"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="16" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="J2" r:id="rId1" xr:uid="{78125F11-BE4E-4312-8E61-0550889BB81F}"/>
     <hyperlink ref="I2" r:id="rId2" xr:uid="{1CFCC581-B5E5-4159-8EE1-35A941FCD4DF}"/>
     <hyperlink ref="J4" r:id="rId3" xr:uid="{BD7BCD4B-25F3-483F-8F98-D146F94F5AAF}"/>
+    <hyperlink ref="I6" r:id="rId4" xr:uid="{9E4B6332-A551-48B7-BFF0-45B7D65C08A2}"/>
+    <hyperlink ref="J6" r:id="rId5" xr:uid="{2277AFAF-7670-400C-9F4A-5D96406C91FF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
 </worksheet>
 </file>
 
@@ -25722,7 +25835,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60E8291E-4293-4634-B9E9-80CB520CA181}">
-  <dimension ref="A1:N170"/>
+  <dimension ref="A1:N172"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="3" max="3" width="19.90625" customWidth="1"/>
@@ -33207,6 +33320,94 @@
         <v>1646</v>
       </c>
       <c r="N170" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="171" spans="1:14">
+      <c r="A171" s="16" t="s">
+        <v>3591</v>
+      </c>
+      <c r="B171" s="16" t="s">
+        <v>3593</v>
+      </c>
+      <c r="C171" s="16" t="s">
+        <v>3595</v>
+      </c>
+      <c r="D171" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E171" s="36" t="s">
+        <v>3597</v>
+      </c>
+      <c r="F171" s="3" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G171" t="s">
+        <v>3598</v>
+      </c>
+      <c r="H171" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I171" t="s">
+        <v>3599</v>
+      </c>
+      <c r="J171" s="2" t="s">
+        <v>3600</v>
+      </c>
+      <c r="K171" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L171" s="17" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M171" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="N171" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="172" spans="1:14">
+      <c r="A172" s="16" t="s">
+        <v>3592</v>
+      </c>
+      <c r="B172" t="s">
+        <v>3594</v>
+      </c>
+      <c r="C172" s="16" t="s">
+        <v>3596</v>
+      </c>
+      <c r="D172" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="E172" s="36" t="s">
+        <v>3601</v>
+      </c>
+      <c r="F172" s="3" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G172" t="s">
+        <v>3602</v>
+      </c>
+      <c r="H172" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I172" s="27" t="s">
+        <v>3603</v>
+      </c>
+      <c r="J172" s="2" t="s">
+        <v>3604</v>
+      </c>
+      <c r="K172" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L172" s="17" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M172" s="7" t="s">
+        <v>1644</v>
+      </c>
+      <c r="N172" t="s">
         <v>25</v>
       </c>
     </row>
@@ -33348,9 +33549,12 @@
     <hyperlink ref="I168" r:id="rId133" xr:uid="{5017C3EA-65D9-46AF-AF8E-218938D0A3B7}"/>
     <hyperlink ref="J168" r:id="rId134" xr:uid="{18E306B2-279B-447D-8479-574435B55633}"/>
     <hyperlink ref="I169" r:id="rId135" xr:uid="{0DCBF918-6691-4999-BB88-8B4F9C447EAB}"/>
+    <hyperlink ref="J171" r:id="rId136" xr:uid="{DCF772DB-BDD0-4B1A-9FFA-545D6848BA75}"/>
+    <hyperlink ref="I172" r:id="rId137" xr:uid="{FA50CF1F-CE1E-48C4-AFFC-FEFE4E08F6BD}"/>
+    <hyperlink ref="J172" r:id="rId138" xr:uid="{B2371745-8711-4172-950E-289F49877CF4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId136"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId139"/>
 </worksheet>
 </file>
 

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4F02F2F-84B1-4490-AC16-5CF383DE7186}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6286F60-DE9F-4D2F-AACF-1202290F46B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" firstSheet="9" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32280" yWindow="2235" windowWidth="29040" windowHeight="15720" firstSheet="11" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7244" uniqueCount="3613">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7286" uniqueCount="3633">
   <si>
     <t>ID</t>
   </si>
@@ -10886,6 +10886,66 @@
   </si>
   <si>
     <t>TLC372C</t>
+  </si>
+  <si>
+    <t>560112116009</t>
+  </si>
+  <si>
+    <t>710-560112116009</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/560112116009.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/560112116009?qs=sGAEpiMZZMvdGkrng054txLI%2FDB4oIKDTCqaE%2Fpesdwv2JWXHdCmlQ%3D%3D</t>
+  </si>
+  <si>
+    <t>TNPW060317K6BEEA</t>
+  </si>
+  <si>
+    <t>71-TNPW060317K6BEEA</t>
+  </si>
+  <si>
+    <t>https://www.vishay.com/docs/28758/tnpw_e3.pdf</t>
+  </si>
+  <si>
+    <t>17.6kΩ 210mW ±1%</t>
+  </si>
+  <si>
+    <t>Thick Film Resistors WRIS-RSKS 100 Ohms 1 % 0.1 W 0603 AEC-Q200</t>
+  </si>
+  <si>
+    <t>Thin Film Resistors 17.6Kohms .1% 25ppm</t>
+  </si>
+  <si>
+    <t>010-0172</t>
+  </si>
+  <si>
+    <t>010-0173</t>
+  </si>
+  <si>
+    <t>050-0006</t>
+  </si>
+  <si>
+    <t>https://www.ti.com/lit/ds/symlink/sn74act10-q1.pdf?ts=1755166715768&amp;ref_url=https%253A%252F%252Fwww.ti.com%252Fsitesearch%252Fen-us%252Fdocs%252Funiversalsearch.tsp%253FlangPref%253Den-US%2526nr%253D2%2526searchTerm%253DSN74ACT10WBQARQ1</t>
+  </si>
+  <si>
+    <t>Puertas lógicas Automotive 3-ch 3- i nput 1.5V to 6V 24</t>
+  </si>
+  <si>
+    <t>SN74ACT10QPWRG4Q1</t>
+  </si>
+  <si>
+    <t>595-N74ACT10QPWRG4Q1</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Texas-Instruments/SN74ACT10QPWRG4Q1?qs=sGAEpiMZZMutXGli8Ay4kFDTtzDUNYkmI6wEEhUY5cY%3D</t>
+  </si>
+  <si>
+    <t>SN74ACT10-Q1</t>
+  </si>
+  <si>
+    <t>TSSOP-14</t>
   </si>
 </sst>
 </file>
@@ -20509,6 +20569,50 @@
         <v>25</v>
       </c>
     </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>3625</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>3627</v>
+      </c>
+      <c r="C7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" t="s">
+        <v>3632</v>
+      </c>
+      <c r="E7" t="s">
+        <v>3628</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>3629</v>
+      </c>
+      <c r="H7" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="27" t="s">
+        <v>3626</v>
+      </c>
+      <c r="J7" s="27" t="s">
+        <v>3630</v>
+      </c>
+      <c r="K7" t="s">
+        <v>3631</v>
+      </c>
+      <c r="L7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M7" t="s">
+        <v>3632</v>
+      </c>
+      <c r="N7" t="s">
+        <v>25</v>
+      </c>
+    </row>
     <row r="9" spans="1:14">
       <c r="L9" s="21"/>
     </row>
@@ -20520,9 +20624,10 @@
     <hyperlink ref="J4" r:id="rId3" xr:uid="{BD7BCD4B-25F3-483F-8F98-D146F94F5AAF}"/>
     <hyperlink ref="I6" r:id="rId4" xr:uid="{9E4B6332-A551-48B7-BFF0-45B7D65C08A2}"/>
     <hyperlink ref="J6" r:id="rId5" xr:uid="{2277AFAF-7670-400C-9F4A-5D96406C91FF}"/>
+    <hyperlink ref="I7" r:id="rId6" xr:uid="{4EE7BCCF-17ED-4BF0-90C6-97AD9B6D2A45}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId7"/>
 </worksheet>
 </file>
 
@@ -25835,7 +25940,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60E8291E-4293-4634-B9E9-80CB520CA181}">
-  <dimension ref="A1:N172"/>
+  <dimension ref="A1:N174"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="3" max="3" width="19.90625" customWidth="1"/>
@@ -33408,6 +33513,94 @@
         <v>1644</v>
       </c>
       <c r="N172" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="173" spans="1:14">
+      <c r="A173" s="16" t="s">
+        <v>3623</v>
+      </c>
+      <c r="B173" s="16" t="s">
+        <v>3621</v>
+      </c>
+      <c r="C173" s="16" t="s">
+        <v>1334</v>
+      </c>
+      <c r="D173" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E173" s="36" t="s">
+        <v>3613</v>
+      </c>
+      <c r="F173" s="3" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G173" t="s">
+        <v>3614</v>
+      </c>
+      <c r="H173" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I173" t="s">
+        <v>3615</v>
+      </c>
+      <c r="J173" s="2" t="s">
+        <v>3616</v>
+      </c>
+      <c r="K173" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L173" s="17" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M173" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="N173" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="174" spans="1:14">
+      <c r="A174" s="16" t="s">
+        <v>3624</v>
+      </c>
+      <c r="B174" s="16" t="s">
+        <v>3622</v>
+      </c>
+      <c r="C174" s="16" t="s">
+        <v>3620</v>
+      </c>
+      <c r="D174" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E174" t="s">
+        <v>3617</v>
+      </c>
+      <c r="F174" s="3" t="s">
+        <v>3311</v>
+      </c>
+      <c r="G174" s="3" t="s">
+        <v>3618</v>
+      </c>
+      <c r="H174" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I174" t="s">
+        <v>3619</v>
+      </c>
+      <c r="J174" t="s">
+        <v>3619</v>
+      </c>
+      <c r="K174" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L174" s="17" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M174" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="N174" t="s">
         <v>25</v>
       </c>
     </row>
@@ -33552,9 +33745,10 @@
     <hyperlink ref="J171" r:id="rId136" xr:uid="{DCF772DB-BDD0-4B1A-9FFA-545D6848BA75}"/>
     <hyperlink ref="I172" r:id="rId137" xr:uid="{FA50CF1F-CE1E-48C4-AFFC-FEFE4E08F6BD}"/>
     <hyperlink ref="J172" r:id="rId138" xr:uid="{B2371745-8711-4172-950E-289F49877CF4}"/>
+    <hyperlink ref="J173" r:id="rId139" xr:uid="{3A21D11A-C4F5-4700-844C-E488B5091D30}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId139"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId140"/>
 </worksheet>
 </file>
 

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6286F60-DE9F-4D2F-AACF-1202290F46B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7EBF044-90D7-4B5E-99D5-3A5989AD0C29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32280" yWindow="2235" windowWidth="29040" windowHeight="15720" firstSheet="11" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32280" yWindow="2235" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7286" uniqueCount="3633">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7314" uniqueCount="3646">
   <si>
     <t>ID</t>
   </si>
@@ -10946,6 +10946,45 @@
   </si>
   <si>
     <t>TSSOP-14</t>
+  </si>
+  <si>
+    <t>010-0174</t>
+  </si>
+  <si>
+    <t>010-0175</t>
+  </si>
+  <si>
+    <t>Thin Film Resistors 40kOhm 1/10W 0603 .1 %</t>
+  </si>
+  <si>
+    <t>Thin Film Resistors .1W 3Kohm 1% 0603 50ppm Auto</t>
+  </si>
+  <si>
+    <t>40kΩ 100mW ±1%</t>
+  </si>
+  <si>
+    <t>3kΩ 100mW ±1%</t>
+  </si>
+  <si>
+    <t>RT0603BRD0740KL</t>
+  </si>
+  <si>
+    <t>603-RT0603BRD0740KL</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/YAGEO/RT0603BRD0740KL?qs=sGAEpiMZZMvdGkrng054tz3%252BeNFGeSG0GkyUjI%2FdHogYz0a%2FQgLP3Q%3D%3D</t>
+  </si>
+  <si>
+    <t>MCT06030C3001FP500</t>
+  </si>
+  <si>
+    <t>594-MCT06030C3001FP5</t>
+  </si>
+  <si>
+    <t>https://www.vishay.com/docs/28705/mcx0x0xpro.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Vishay-Beyschlag/MCT06030C3001FP500?qs=sGAEpiMZZMvdGkrng054txcf3av6vnC8jqPtP2Mvtkc%3D</t>
   </si>
 </sst>
 </file>
@@ -25940,7 +25979,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60E8291E-4293-4634-B9E9-80CB520CA181}">
-  <dimension ref="A1:N174"/>
+  <dimension ref="A1:N176"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="3" max="3" width="19.90625" customWidth="1"/>
@@ -33601,6 +33640,94 @@
         <v>57</v>
       </c>
       <c r="N174" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="175" spans="1:14">
+      <c r="A175" s="16" t="s">
+        <v>3633</v>
+      </c>
+      <c r="B175" s="16" t="s">
+        <v>3635</v>
+      </c>
+      <c r="C175" s="16" t="s">
+        <v>3637</v>
+      </c>
+      <c r="D175" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E175" t="s">
+        <v>3639</v>
+      </c>
+      <c r="F175" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G175" t="s">
+        <v>3640</v>
+      </c>
+      <c r="H175" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I175" s="27" t="s">
+        <v>2941</v>
+      </c>
+      <c r="J175" s="27" t="s">
+        <v>3641</v>
+      </c>
+      <c r="K175" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L175" s="17" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M175" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="N175" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="176" spans="1:14">
+      <c r="A176" s="16" t="s">
+        <v>3634</v>
+      </c>
+      <c r="B176" s="16" t="s">
+        <v>3636</v>
+      </c>
+      <c r="C176" s="16" t="s">
+        <v>3638</v>
+      </c>
+      <c r="D176" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E176" t="s">
+        <v>3642</v>
+      </c>
+      <c r="F176" s="3" t="s">
+        <v>3311</v>
+      </c>
+      <c r="G176" s="3" t="s">
+        <v>3643</v>
+      </c>
+      <c r="H176" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I176" s="2" t="s">
+        <v>3644</v>
+      </c>
+      <c r="J176" s="2" t="s">
+        <v>3645</v>
+      </c>
+      <c r="K176" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L176" s="17" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M176" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="N176" t="s">
         <v>25</v>
       </c>
     </row>
@@ -33746,9 +33873,13 @@
     <hyperlink ref="I172" r:id="rId137" xr:uid="{FA50CF1F-CE1E-48C4-AFFC-FEFE4E08F6BD}"/>
     <hyperlink ref="J172" r:id="rId138" xr:uid="{B2371745-8711-4172-950E-289F49877CF4}"/>
     <hyperlink ref="J173" r:id="rId139" xr:uid="{3A21D11A-C4F5-4700-844C-E488B5091D30}"/>
+    <hyperlink ref="I175" r:id="rId140" xr:uid="{0ACAE8CB-C675-42FE-A879-5CFFD5F81486}"/>
+    <hyperlink ref="J175" r:id="rId141" xr:uid="{66445A72-7098-4D8D-B976-582E289253DB}"/>
+    <hyperlink ref="I176" r:id="rId142" xr:uid="{169D9C30-30AB-4C8F-8A4D-E3B4AF0FB7C6}"/>
+    <hyperlink ref="J176" r:id="rId143" xr:uid="{888F1817-76F7-4A94-A2F6-101494CA1688}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId140"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId144"/>
 </worksheet>
 </file>
 

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7EBF044-90D7-4B5E-99D5-3A5989AD0C29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0091A8B9-CF2A-4DF4-B706-79CD73BE187A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32280" yWindow="2235" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32280" yWindow="2235" windowWidth="29040" windowHeight="15720" firstSheet="7" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -25,17 +25,18 @@
     <sheet name="032 - Diode - TVS" sheetId="14" r:id="rId10"/>
     <sheet name="033 - Diode - LED" sheetId="12" r:id="rId11"/>
     <sheet name="040 - Fuses" sheetId="10" r:id="rId12"/>
-    <sheet name="043 - Transistors" sheetId="21" r:id="rId13"/>
-    <sheet name="045 - Crystal" sheetId="19" r:id="rId14"/>
-    <sheet name="050 - ICs - Analog" sheetId="2" r:id="rId15"/>
-    <sheet name="051 - ICs - Digital" sheetId="24" r:id="rId16"/>
-    <sheet name="055 - Drivers" sheetId="20" r:id="rId17"/>
-    <sheet name="060 - Sensor" sheetId="3" r:id="rId18"/>
-    <sheet name="062 - Amplifiers" sheetId="25" r:id="rId19"/>
-    <sheet name="070 - Power Supply" sheetId="8" r:id="rId20"/>
-    <sheet name="090 - Processor" sheetId="18" r:id="rId21"/>
-    <sheet name="100 - Electromechanicals" sheetId="15" r:id="rId22"/>
-    <sheet name="110 - Connectors" sheetId="13" r:id="rId23"/>
+    <sheet name="041 - Optoisolators" sheetId="26" r:id="rId13"/>
+    <sheet name="043 - Transistors" sheetId="21" r:id="rId14"/>
+    <sheet name="045 - Crystal" sheetId="19" r:id="rId15"/>
+    <sheet name="050 - ICs - Analog" sheetId="2" r:id="rId16"/>
+    <sheet name="051 - ICs - Digital" sheetId="24" r:id="rId17"/>
+    <sheet name="055 - Drivers" sheetId="20" r:id="rId18"/>
+    <sheet name="060 - Sensor" sheetId="3" r:id="rId19"/>
+    <sheet name="062 - Amplifiers" sheetId="25" r:id="rId20"/>
+    <sheet name="070 - Power Supply" sheetId="8" r:id="rId21"/>
+    <sheet name="090 - Processor" sheetId="18" r:id="rId22"/>
+    <sheet name="100 - Electromechanicals" sheetId="15" r:id="rId23"/>
+    <sheet name="110 - Connectors" sheetId="13" r:id="rId24"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7314" uniqueCount="3646">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7342" uniqueCount="3655">
   <si>
     <t>ID</t>
   </si>
@@ -10985,6 +10986,33 @@
   </si>
   <si>
     <t>https://www.mouser.es/ProductDetail/Vishay-Beyschlag/MCT06030C3001FP500?qs=sGAEpiMZZMvdGkrng054txcf3av6vnC8jqPtP2Mvtkc%3D</t>
+  </si>
+  <si>
+    <t>041-0001</t>
+  </si>
+  <si>
+    <t>OPTO 1 CHANNEL</t>
+  </si>
+  <si>
+    <t>eUSR_SchLibrary/eUSR_SchLibrary - Optoisolators.SchLib</t>
+  </si>
+  <si>
+    <t>SOIC-4</t>
+  </si>
+  <si>
+    <t>Optoacopladores para salidas de transistores Automotive DC-input transistor-output s</t>
+  </si>
+  <si>
+    <t>ISOM8110DFHRQ1</t>
+  </si>
+  <si>
+    <t>595-ISOM8110DFHRQ1</t>
+  </si>
+  <si>
+    <t>https://www.ti.com/lit/ds/symlink/isom8118-q1.pdf?ts=1782232586415&amp;ref_url=https%253A%252F%252Fwww.mouser.es%252F</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Texas-Instruments/ISOM8110DFHRQ1?qs=7%2F6SraaimPTj7eqPn2eA2w%3D%3D</t>
   </si>
 </sst>
 </file>
@@ -10994,7 +11022,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -11112,6 +11140,11 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -11163,7 +11196,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -11222,6 +11255,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -20078,6 +20112,108 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA7E41C9-E62B-4149-A5B5-E7986E8877E6}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
+        <v>3646</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3650</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="E2" t="s">
+        <v>3651</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>3652</v>
+      </c>
+      <c r="H2" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="27" t="s">
+        <v>3653</v>
+      </c>
+      <c r="J2" s="32" t="s">
+        <v>3654</v>
+      </c>
+      <c r="K2" s="38" t="s">
+        <v>3647</v>
+      </c>
+      <c r="L2" t="s">
+        <v>3648</v>
+      </c>
+      <c r="M2" s="16" t="s">
+        <v>3649</v>
+      </c>
+      <c r="N2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="I2" r:id="rId1" xr:uid="{C0196A92-FFC7-4B23-8894-B6344B4B2643}"/>
+    <hyperlink ref="J2" r:id="rId2" xr:uid="{0B83CD2F-6571-479E-AB7A-FA77C6040D49}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FAFF3B6-AF11-4BFB-8078-829FF6F2F366}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -20179,7 +20315,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E5535EA-E186-4751-BC7F-9B3A0221302E}">
   <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -20328,7 +20464,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C98E1A12-072F-4773-8CB5-47FFE077E85B}">
   <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -20670,7 +20806,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{316C64E0-14FB-467C-956A-E132FAFB0232}">
   <dimension ref="A1:N1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -20724,7 +20860,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{201D74E2-3547-4E9B-8216-09A22645AC2A}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -20826,7 +20962,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59BC8B2E-A067-463D-937A-30E88D8BECD0}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -20923,155 +21059,6 @@
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1" xr:uid="{BFD1D0BA-D934-44C0-B127-7693B6B8FCF4}"/>
     <hyperlink ref="J2" r:id="rId2" xr:uid="{72343140-B075-45AB-91DC-7B87E10B2AD1}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4185B0A-D162-4EBC-935B-7159E365DD54}">
-  <dimension ref="A1:N3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
-  <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" t="s">
-        <v>3289</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3299</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>3298</v>
-      </c>
-      <c r="E2" t="s">
-        <v>3290</v>
-      </c>
-      <c r="F2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" t="s">
-        <v>3291</v>
-      </c>
-      <c r="H2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>3292</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>3293</v>
-      </c>
-      <c r="K2" t="s">
-        <v>3301</v>
-      </c>
-      <c r="L2" t="s">
-        <v>3300</v>
-      </c>
-      <c r="M2" t="s">
-        <v>3301</v>
-      </c>
-      <c r="N2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
-        <v>3304</v>
-      </c>
-      <c r="B3" t="s">
-        <v>3305</v>
-      </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" t="s">
-        <v>3303</v>
-      </c>
-      <c r="E3" t="s">
-        <v>3294</v>
-      </c>
-      <c r="F3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3" t="s">
-        <v>3295</v>
-      </c>
-      <c r="H3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>3296</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>3297</v>
-      </c>
-      <c r="K3" t="s">
-        <v>3302</v>
-      </c>
-      <c r="L3" t="s">
-        <v>3300</v>
-      </c>
-      <c r="M3" t="s">
-        <v>3303</v>
-      </c>
-      <c r="N3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="16" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="I2" r:id="rId1" xr:uid="{0AE24270-4D5D-4E12-981B-AA2533208AEE}"/>
-    <hyperlink ref="J2" r:id="rId2" xr:uid="{339478FA-7B81-4702-B5E2-22F306F57121}"/>
-    <hyperlink ref="I3" r:id="rId3" xr:uid="{28D99F1F-302C-4204-9911-77A7F0CFE035}"/>
-    <hyperlink ref="J3" r:id="rId4" xr:uid="{BCBD2BA5-6C89-4F65-A990-3E3D7A05A9E7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -21229,6 +21216,155 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4185B0A-D162-4EBC-935B-7159E365DD54}">
+  <dimension ref="A1:N3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
+        <v>3289</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3299</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>3298</v>
+      </c>
+      <c r="E2" t="s">
+        <v>3290</v>
+      </c>
+      <c r="F2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" t="s">
+        <v>3291</v>
+      </c>
+      <c r="H2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>3292</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>3293</v>
+      </c>
+      <c r="K2" t="s">
+        <v>3301</v>
+      </c>
+      <c r="L2" t="s">
+        <v>3300</v>
+      </c>
+      <c r="M2" t="s">
+        <v>3301</v>
+      </c>
+      <c r="N2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>3304</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3305</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>3303</v>
+      </c>
+      <c r="E3" t="s">
+        <v>3294</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" t="s">
+        <v>3295</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>3296</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>3297</v>
+      </c>
+      <c r="K3" t="s">
+        <v>3302</v>
+      </c>
+      <c r="L3" t="s">
+        <v>3300</v>
+      </c>
+      <c r="M3" t="s">
+        <v>3303</v>
+      </c>
+      <c r="N3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="16" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="I2" r:id="rId1" xr:uid="{0AE24270-4D5D-4E12-981B-AA2533208AEE}"/>
+    <hyperlink ref="J2" r:id="rId2" xr:uid="{339478FA-7B81-4702-B5E2-22F306F57121}"/>
+    <hyperlink ref="I3" r:id="rId3" xr:uid="{28D99F1F-302C-4204-9911-77A7F0CFE035}"/>
+    <hyperlink ref="J3" r:id="rId4" xr:uid="{BCBD2BA5-6C89-4F65-A990-3E3D7A05A9E7}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4BBBCF5-BAC9-459C-ABE9-2526B85FD81E}">
   <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -21650,7 +21786,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E9EB2F5-2977-493B-BFA2-5CD20F8A3BC4}">
   <dimension ref="A1:O3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -21808,7 +21944,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69A1C46E-DEF3-467B-A5BD-162AB66E6A86}">
   <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -22891,7 +23027,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE14AD29-8DB0-4C42-AB91-A73B867AE121}">
   <dimension ref="A1:N65"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0091A8B9-CF2A-4DF4-B706-79CD73BE187A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B0A5B2E-9CFA-4038-961C-362650F3B567}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32280" yWindow="2235" windowWidth="29040" windowHeight="15720" firstSheet="7" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="45105" yWindow="6885" windowWidth="16200" windowHeight="9975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7342" uniqueCount="3655">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7356" uniqueCount="3662">
   <si>
     <t>ID</t>
   </si>
@@ -11013,6 +11013,27 @@
   </si>
   <si>
     <t>https://www.mouser.es/ProductDetail/Texas-Instruments/ISOM8110DFHRQ1?qs=7%2F6SraaimPTj7eqPn2eA2w%3D%3D</t>
+  </si>
+  <si>
+    <t>001-0122</t>
+  </si>
+  <si>
+    <t>Condensadores de cerámica multicapa (MLCC- SMD/SMT) WCAP-CSGP 2.2uF 1812 10% 50V MLCC</t>
+  </si>
+  <si>
+    <t>50V 2.2uF X7R</t>
+  </si>
+  <si>
+    <t>885012210032</t>
+  </si>
+  <si>
+    <t>710-885012210032</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/885012210032.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/885012210032?qs=0KOYDY2FL28JFhdrfHzb7w%3D%3D</t>
   </si>
 </sst>
 </file>
@@ -11144,6 +11165,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -11196,7 +11218,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -11256,6 +11278,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -11539,7 +11564,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N122"/>
+  <dimension ref="A1:N123"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="11.1796875" customWidth="1"/>
@@ -16921,6 +16946,50 @@
         <v>62</v>
       </c>
       <c r="N122" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="123" spans="1:14">
+      <c r="A123" s="39" t="s">
+        <v>3655</v>
+      </c>
+      <c r="B123" t="s">
+        <v>3656</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>3657</v>
+      </c>
+      <c r="D123" s="13" t="s">
+        <v>3222</v>
+      </c>
+      <c r="E123" s="36" t="s">
+        <v>3658</v>
+      </c>
+      <c r="F123" s="3" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G123" s="3" t="s">
+        <v>3659</v>
+      </c>
+      <c r="H123" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I123" s="27" t="s">
+        <v>3660</v>
+      </c>
+      <c r="J123" s="32" t="s">
+        <v>3661</v>
+      </c>
+      <c r="K123" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="L123" t="s">
+        <v>61</v>
+      </c>
+      <c r="M123" s="7" t="s">
+        <v>3227</v>
+      </c>
+      <c r="N123" t="s">
         <v>25</v>
       </c>
     </row>
@@ -17029,9 +17098,11 @@
     <hyperlink ref="J121" r:id="rId100" xr:uid="{8D158E67-4FC0-4FA4-904D-A0664134DB5C}"/>
     <hyperlink ref="I122" r:id="rId101" xr:uid="{5646A60C-F082-4812-AAFF-C09F7BC184F6}"/>
     <hyperlink ref="J122" r:id="rId102" xr:uid="{E13F1BFA-1BC5-4864-9D2F-0D97B5F47657}"/>
+    <hyperlink ref="I123" r:id="rId103" xr:uid="{958FF4C4-BE0E-4556-B03B-7C4DCD6D04F9}"/>
+    <hyperlink ref="J123" r:id="rId104" xr:uid="{FF54A4A3-2741-4A5A-9D1A-3F5746177EAD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId103"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId105"/>
 </worksheet>
 </file>
 

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B0A5B2E-9CFA-4038-961C-362650F3B567}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45105" yWindow="6885" windowWidth="16200" windowHeight="9975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1900" yWindow="1900" windowWidth="16200" windowHeight="9970" firstSheet="17" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B0A5B2E-9CFA-4038-961C-362650F3B567}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DC4E5B3-EA43-4F56-ACD4-6BA91B21325F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1900" windowWidth="16200" windowHeight="9970" firstSheet="17" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32295" yWindow="2355" windowWidth="14610" windowHeight="15585" firstSheet="18" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7356" uniqueCount="3662">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7384" uniqueCount="3675">
   <si>
     <t>ID</t>
   </si>
@@ -11034,6 +11034,45 @@
   </si>
   <si>
     <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/885012210032?qs=0KOYDY2FL28JFhdrfHzb7w%3D%3D</t>
+  </si>
+  <si>
+    <t>060-0002</t>
+  </si>
+  <si>
+    <t>Thin Film Resistors 5.1Kohms 0.1% 10ppm</t>
+  </si>
+  <si>
+    <t>Termistores NTC 10Kohms 1% SMD</t>
+  </si>
+  <si>
+    <t>NTCS0603E3103FLT</t>
+  </si>
+  <si>
+    <t>594-NTCS0603E3103FLT</t>
+  </si>
+  <si>
+    <t>https://www.vishay.com/docs/29056/ntcs0603e3t.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Vishay-BC-Components/NTCS0603E3103FLT?qs=%2FWiulJ9oly66lfIcr%252B1Bpw%3D%3D</t>
+  </si>
+  <si>
+    <t>NTC</t>
+  </si>
+  <si>
+    <t>010-0176</t>
+  </si>
+  <si>
+    <t>5.1kΩ 210mW ±0.1%</t>
+  </si>
+  <si>
+    <t>TNPW06035K10BYEN</t>
+  </si>
+  <si>
+    <t>71-TNPW06035K10BYEN</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Vishay/TNPW06035K10BYEN?qs=sGAEpiMZZMvdGkrng054t1oDJztsiizWD%252B5sENOdKiv4hhjUJDCTXQ%3D%3D</t>
   </si>
 </sst>
 </file>
@@ -11218,7 +11257,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -11281,6 +11320,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -21035,7 +21076,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59BC8B2E-A067-463D-937A-30E88D8BECD0}">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:14">
@@ -21126,10 +21167,56 @@
         <v>25</v>
       </c>
     </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>3662</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3664</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>900</v>
+      </c>
+      <c r="D3" s="40" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" t="s">
+        <v>3665</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>3311</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>3666</v>
+      </c>
+      <c r="H3" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>3667</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>3668</v>
+      </c>
+      <c r="K3" s="41" t="s">
+        <v>3669</v>
+      </c>
+      <c r="L3" t="s">
+        <v>3276</v>
+      </c>
+      <c r="M3" t="s">
+        <v>57</v>
+      </c>
+      <c r="N3" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1" xr:uid="{BFD1D0BA-D934-44C0-B127-7693B6B8FCF4}"/>
     <hyperlink ref="J2" r:id="rId2" xr:uid="{72343140-B075-45AB-91DC-7B87E10B2AD1}"/>
+    <hyperlink ref="I3" r:id="rId3" xr:uid="{D9F4A33B-2595-4DA0-8363-A69F15E2B303}"/>
+    <hyperlink ref="J3" r:id="rId4" xr:uid="{1ABB114B-1F85-4103-ABE2-AA0C257EB7B1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -26186,7 +26273,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60E8291E-4293-4634-B9E9-80CB520CA181}">
-  <dimension ref="A1:N176"/>
+  <dimension ref="A1:N177"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="3" max="3" width="19.90625" customWidth="1"/>
@@ -33935,6 +34022,50 @@
         <v>57</v>
       </c>
       <c r="N176" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="177" spans="1:14">
+      <c r="A177" s="16" t="s">
+        <v>3670</v>
+      </c>
+      <c r="B177" s="16" t="s">
+        <v>3663</v>
+      </c>
+      <c r="C177" s="16" t="s">
+        <v>3671</v>
+      </c>
+      <c r="D177" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E177" t="s">
+        <v>3672</v>
+      </c>
+      <c r="F177" s="3" t="s">
+        <v>3311</v>
+      </c>
+      <c r="G177" s="3" t="s">
+        <v>3673</v>
+      </c>
+      <c r="H177" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I177" s="27" t="s">
+        <v>3619</v>
+      </c>
+      <c r="J177" s="32" t="s">
+        <v>3674</v>
+      </c>
+      <c r="K177" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L177" s="17" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M177" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="N177" t="s">
         <v>25</v>
       </c>
     </row>
@@ -34084,9 +34215,11 @@
     <hyperlink ref="J175" r:id="rId141" xr:uid="{66445A72-7098-4D8D-B976-582E289253DB}"/>
     <hyperlink ref="I176" r:id="rId142" xr:uid="{169D9C30-30AB-4C8F-8A4D-E3B4AF0FB7C6}"/>
     <hyperlink ref="J176" r:id="rId143" xr:uid="{888F1817-76F7-4A94-A2F6-101494CA1688}"/>
+    <hyperlink ref="I177" r:id="rId144" xr:uid="{D768CC27-0F4F-4814-BD5B-A0D920CDA8FB}"/>
+    <hyperlink ref="J177" r:id="rId145" xr:uid="{18CDD4BD-07CE-40B1-A25E-51C6A46E6A26}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId144"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId146"/>
 </worksheet>
 </file>
 

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DC4E5B3-EA43-4F56-ACD4-6BA91B21325F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25A36233-08C0-4E66-9885-4DBBF9911E15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32295" yWindow="2355" windowWidth="14610" windowHeight="15585" firstSheet="18" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="40305" yWindow="3975" windowWidth="16200" windowHeight="9975" firstSheet="19" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7384" uniqueCount="3675">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7398" uniqueCount="3683">
   <si>
     <t>ID</t>
   </si>
@@ -11073,6 +11073,30 @@
   </si>
   <si>
     <t>https://www.mouser.es/ProductDetail/Vishay/TNPW06035K10BYEN?qs=sGAEpiMZZMvdGkrng054t1oDJztsiizWD%252B5sENOdKiv4hhjUJDCTXQ%3D%3D</t>
+  </si>
+  <si>
+    <t>070-0009</t>
+  </si>
+  <si>
+    <t>Reguladores de voltaje LDO 300 MA CMOS LDO, AD OPTIO</t>
+  </si>
+  <si>
+    <t>(1.7/5.5)V-1.65V</t>
+  </si>
+  <si>
+    <t>NCV8114ASN165T1G</t>
+  </si>
+  <si>
+    <t>863-NCV8114ASN165T1G</t>
+  </si>
+  <si>
+    <t>https://www.onsemi.com/pdf/datasheet/ncv8114-d.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/onsemi/NCV8114ASN165T1G?qs=PqoDHHvF64%252BWMsY7A2HF3Q%3D%3D</t>
+  </si>
+  <si>
+    <t>NCV8114</t>
   </si>
 </sst>
 </file>
@@ -11257,7 +11281,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -11320,8 +11344,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -21177,7 +21199,7 @@
       <c r="C3" s="16" t="s">
         <v>900</v>
       </c>
-      <c r="D3" s="40" t="s">
+      <c r="D3" s="20" t="s">
         <v>59</v>
       </c>
       <c r="E3" t="s">
@@ -21198,7 +21220,7 @@
       <c r="J3" s="2" t="s">
         <v>3668</v>
       </c>
-      <c r="K3" s="41" t="s">
+      <c r="K3" s="16" t="s">
         <v>3669</v>
       </c>
       <c r="L3" t="s">
@@ -21524,7 +21546,7 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4BBBCF5-BAC9-459C-ABE9-2526B85FD81E}">
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="4" max="4" width="17.54296875" customWidth="1"/>
@@ -21923,6 +21945,50 @@
         <v>2120</v>
       </c>
       <c r="N9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
+        <v>3675</v>
+      </c>
+      <c r="B10" t="s">
+        <v>3676</v>
+      </c>
+      <c r="C10" t="s">
+        <v>3677</v>
+      </c>
+      <c r="D10" t="s">
+        <v>3303</v>
+      </c>
+      <c r="E10" t="s">
+        <v>3678</v>
+      </c>
+      <c r="F10" t="s">
+        <v>1858</v>
+      </c>
+      <c r="G10" t="s">
+        <v>3679</v>
+      </c>
+      <c r="H10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>3680</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>3681</v>
+      </c>
+      <c r="K10" t="s">
+        <v>3682</v>
+      </c>
+      <c r="L10" t="s">
+        <v>1689</v>
+      </c>
+      <c r="M10" t="s">
+        <v>3303</v>
+      </c>
+      <c r="N10" t="s">
         <v>25</v>
       </c>
     </row>
@@ -21938,9 +22004,11 @@
     <hyperlink ref="J7" r:id="rId7" xr:uid="{CE7C033B-E1D3-4982-B98D-45472DE55249}"/>
     <hyperlink ref="J8" r:id="rId8" xr:uid="{EA27946F-BAF3-48A3-B1E1-735BC730E575}"/>
     <hyperlink ref="I8" r:id="rId9" xr:uid="{E0BD2FA6-2C87-41A3-AA17-DD7C10DA47E6}"/>
+    <hyperlink ref="I10" r:id="rId10" xr:uid="{5A295B9B-C058-4576-ACE5-C276BDFAEEE4}"/>
+    <hyperlink ref="J10" r:id="rId11" xr:uid="{4B965264-88E4-4839-92CE-367CACEF3C9F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId10"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId12"/>
 </worksheet>
 </file>
 

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25A36233-08C0-4E66-9885-4DBBF9911E15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D470915-6B92-45F6-8D0F-A398B9E7A2D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40305" yWindow="3975" windowWidth="16200" windowHeight="9975" firstSheet="19" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32280" yWindow="2235" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7398" uniqueCount="3683">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7467" uniqueCount="3720">
   <si>
     <t>ID</t>
   </si>
@@ -11097,6 +11097,117 @@
   </si>
   <si>
     <t>NCV8114</t>
+  </si>
+  <si>
+    <t>110-0065</t>
+  </si>
+  <si>
+    <t>Conectores para automoción 35P HEADER AMPSEAL ASSEMBLY</t>
+  </si>
+  <si>
+    <t>35P</t>
+  </si>
+  <si>
+    <t>THT 4mm</t>
+  </si>
+  <si>
+    <t>1-776163-1</t>
+  </si>
+  <si>
+    <t>571-1-776163-1</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/datasheet/3/80/26/ENG_CD_776163_K1.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/TE-Connectivity-AMP/1-776163-1?qs=VKrXD49J9EqcsUPRwW8PqQ%3D%3D</t>
+  </si>
+  <si>
+    <t>CONN 1-776163-1</t>
+  </si>
+  <si>
+    <t>Diodos y rectificadores Schottky 3A 60V</t>
+  </si>
+  <si>
+    <t>031-0013</t>
+  </si>
+  <si>
+    <t>MBRS360T3G</t>
+  </si>
+  <si>
+    <t>863-MBRS360T3G</t>
+  </si>
+  <si>
+    <t>https://www.onsemi.com/pdf/datasheet/mbrs360t3-d.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/onsemi/MBRS360T3G?qs=3JMERSakebpuPnGIg0cvPA%3D%3D</t>
+  </si>
+  <si>
+    <t>001-0123</t>
+  </si>
+  <si>
+    <t>Condensadores de cerámica multicapa (MLCC- SMD/SMT) 10 uF 50 VDC 10% 0805 X5R</t>
+  </si>
+  <si>
+    <t>GRM21BR61H106KE43K</t>
+  </si>
+  <si>
+    <t>81-GRM21BR61H106KE3K</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/datasheet/3/76/1/GRM21BR61H106KE43_01A.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Murata-Electronics/GRM21BR61H106KE43K?qs=xZ%2FP%252Ba9zWqbh3%252B96jyTKxw%3D%3D</t>
+  </si>
+  <si>
+    <t>020-0003</t>
+  </si>
+  <si>
+    <t>Inductores de potencia (SMD) WE-LHMI Powr SMD7030 10uH 3.0A 85mOhm</t>
+  </si>
+  <si>
+    <t>10uH 3A ±20%</t>
+  </si>
+  <si>
+    <t>SMD;7.3x6.6mm</t>
+  </si>
+  <si>
+    <t>IND SMD 7.3x6.6</t>
+  </si>
+  <si>
+    <t>74437346100</t>
+  </si>
+  <si>
+    <t>710-74437346100</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/74437346100.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/74437346100?qs=cFlH0mFHHFqNHncV%252BuVFvQ%3D%3D</t>
+  </si>
+  <si>
+    <t>040-0021</t>
+  </si>
+  <si>
+    <t>Fusibles de montaje en superficie 2.5A Fast Acting 1206 SinglFuse</t>
+  </si>
+  <si>
+    <t>2.5A</t>
+  </si>
+  <si>
+    <t>SF-1206F250-2</t>
+  </si>
+  <si>
+    <t>652-SF-1206F250-2</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/datasheet/3/40/1/sf_1206f48eb4f2c90e165f58a72ff000066632f.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Bourns/SF-1206F250-2?qs=GIQXYiEeHGDcWHFyUr2UTQ%3D%3D</t>
   </si>
 </sst>
 </file>
@@ -11281,7 +11392,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -11344,6 +11455,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -11627,7 +11739,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N123"/>
+  <dimension ref="A1:N124"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="11.1796875" customWidth="1"/>
@@ -17053,6 +17165,50 @@
         <v>3227</v>
       </c>
       <c r="N123" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="124" spans="1:14">
+      <c r="A124" s="39" t="s">
+        <v>3698</v>
+      </c>
+      <c r="B124" s="16" t="s">
+        <v>3699</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="D124" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="E124" t="s">
+        <v>3700</v>
+      </c>
+      <c r="F124" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="G124" s="3" t="s">
+        <v>3701</v>
+      </c>
+      <c r="H124" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I124" s="27" t="s">
+        <v>3702</v>
+      </c>
+      <c r="J124" s="32" t="s">
+        <v>3703</v>
+      </c>
+      <c r="K124" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="L124" t="s">
+        <v>61</v>
+      </c>
+      <c r="M124" s="7" t="s">
+        <v>700</v>
+      </c>
+      <c r="N124" t="s">
         <v>25</v>
       </c>
     </row>
@@ -17163,9 +17319,11 @@
     <hyperlink ref="J122" r:id="rId102" xr:uid="{E13F1BFA-1BC5-4864-9D2F-0D97B5F47657}"/>
     <hyperlink ref="I123" r:id="rId103" xr:uid="{958FF4C4-BE0E-4556-B03B-7C4DCD6D04F9}"/>
     <hyperlink ref="J123" r:id="rId104" xr:uid="{FF54A4A3-2741-4A5A-9D1A-3F5746177EAD}"/>
+    <hyperlink ref="I124" r:id="rId105" xr:uid="{3BC617E5-C20D-4B7A-B6F8-6DE6572A7AA0}"/>
+    <hyperlink ref="J124" r:id="rId106" xr:uid="{69468929-3CB4-4434-AED4-E3828EC8E37D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId105"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId107"/>
 </worksheet>
 </file>
 
@@ -19278,7 +19436,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B6F0D32-9CE2-4DF7-927E-42E7BA331F12}">
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="13" max="13" width="13.36328125" customWidth="1"/>
@@ -20218,6 +20376,50 @@
         <v>1746</v>
       </c>
       <c r="N21" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" t="s">
+        <v>3713</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>3714</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>3715</v>
+      </c>
+      <c r="D22" s="7">
+        <v>1206</v>
+      </c>
+      <c r="E22" t="s">
+        <v>3716</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>1516</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3717</v>
+      </c>
+      <c r="H22" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I22" s="27" t="s">
+        <v>3718</v>
+      </c>
+      <c r="J22" s="32" t="s">
+        <v>3719</v>
+      </c>
+      <c r="K22" s="17" t="s">
+        <v>1700</v>
+      </c>
+      <c r="L22" t="s">
+        <v>55</v>
+      </c>
+      <c r="M22" s="7" t="s">
+        <v>1701</v>
+      </c>
+      <c r="N22" t="s">
         <v>25</v>
       </c>
     </row>
@@ -20240,6 +20442,8 @@
     <hyperlink ref="I20" r:id="rId14" xr:uid="{6C9DFF48-0956-4B25-8972-EC0656F1483E}"/>
     <hyperlink ref="J20" r:id="rId15" xr:uid="{6EF40273-C6D8-4BC3-9EF6-1B4C76903848}"/>
     <hyperlink ref="J21" r:id="rId16" xr:uid="{FFB17F08-401F-47B0-899B-612CD8B9FB6B}"/>
+    <hyperlink ref="I22" r:id="rId17" xr:uid="{1372C46B-1234-4FDC-9A5A-49F3F36A3112}"/>
+    <hyperlink ref="J22" r:id="rId18" xr:uid="{5B608490-0175-4BFB-8CEB-749053C4E8DA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -23255,7 +23459,7 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE14AD29-8DB0-4C42-AB91-A73B867AE121}">
-  <dimension ref="A1:N65"/>
+  <dimension ref="A1:N66"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="5" max="5" width="16.36328125" bestFit="1" customWidth="1"/>
@@ -26120,6 +26324,50 @@
         <v>7461117</v>
       </c>
       <c r="N65" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14">
+      <c r="A66" s="16" t="s">
+        <v>3683</v>
+      </c>
+      <c r="B66" s="16" t="s">
+        <v>3684</v>
+      </c>
+      <c r="C66" s="16" t="s">
+        <v>3685</v>
+      </c>
+      <c r="D66" s="16" t="s">
+        <v>3686</v>
+      </c>
+      <c r="E66" t="s">
+        <v>3687</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>2192</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>3688</v>
+      </c>
+      <c r="H66" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I66" s="27" t="s">
+        <v>3689</v>
+      </c>
+      <c r="J66" s="32" t="s">
+        <v>3690</v>
+      </c>
+      <c r="K66" s="17" t="s">
+        <v>3691</v>
+      </c>
+      <c r="L66" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M66" t="s">
+        <v>3687</v>
+      </c>
+      <c r="N66" s="7" t="s">
         <v>25</v>
       </c>
     </row>
@@ -26182,6 +26430,8 @@
     <hyperlink ref="J63" r:id="rId54" xr:uid="{29B6CE96-A331-4903-A5B6-DD5273C7B49A}"/>
     <hyperlink ref="I64" r:id="rId55" xr:uid="{5CA52475-6941-42F8-9AA3-C5156AF91DB1}"/>
     <hyperlink ref="J64" r:id="rId56" xr:uid="{0176710A-1D50-48A9-9ACC-C0E8F9C09246}"/>
+    <hyperlink ref="I66" r:id="rId57" xr:uid="{F4FD0F61-138E-4DBE-8F6A-3A26376F772A}"/>
+    <hyperlink ref="J66" r:id="rId58" xr:uid="{F9BBC9A3-5DDE-4132-B9F9-18EE393B61F2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -34535,7 +34785,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01C6B0FD-D8A3-44EC-9532-03DDA232F922}">
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:14">
@@ -34667,6 +34917,50 @@
         <v>3415</v>
       </c>
       <c r="N3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>3704</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>3705</v>
+      </c>
+      <c r="C4" t="s">
+        <v>3706</v>
+      </c>
+      <c r="D4" t="s">
+        <v>3707</v>
+      </c>
+      <c r="E4" s="36" t="s">
+        <v>3709</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>3710</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="27" t="s">
+        <v>3711</v>
+      </c>
+      <c r="J4" s="32" t="s">
+        <v>3712</v>
+      </c>
+      <c r="K4" t="s">
+        <v>3406</v>
+      </c>
+      <c r="L4" t="s">
+        <v>2904</v>
+      </c>
+      <c r="M4" s="17" t="s">
+        <v>3708</v>
+      </c>
+      <c r="N4" t="s">
         <v>25</v>
       </c>
     </row>
@@ -34676,9 +34970,11 @@
     <hyperlink ref="I2" r:id="rId1" xr:uid="{07883802-B058-47F9-BBB3-C06E82952829}"/>
     <hyperlink ref="J2" r:id="rId2" xr:uid="{62DD0F89-540D-4537-B7A5-4B172FA10C23}"/>
     <hyperlink ref="I3" r:id="rId3" xr:uid="{A45B5B86-5ADB-44B4-BF96-CFB1161AF6C6}"/>
+    <hyperlink ref="I4" r:id="rId4" xr:uid="{172DE15B-CE66-4479-BB47-E78881F87955}"/>
+    <hyperlink ref="J4" r:id="rId5" xr:uid="{554E337A-6092-4CB5-BAAD-9E740E529981}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
 </worksheet>
 </file>
 
@@ -35244,7 +35540,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FE2008B-4BF4-4C9A-883A-FEE5873AEAF4}">
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:14" ht="16" customHeight="1">
@@ -35816,6 +36112,50 @@
         <v>1994</v>
       </c>
       <c r="N13" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="16" t="s">
+        <v>3693</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>3692</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>1997</v>
+      </c>
+      <c r="D14" s="40" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E14" t="s">
+        <v>3694</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>1858</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3695</v>
+      </c>
+      <c r="H14" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I14" s="27" t="s">
+        <v>3696</v>
+      </c>
+      <c r="J14" s="32" t="s">
+        <v>3697</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>1918</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M14" t="s">
+        <v>2047</v>
+      </c>
+      <c r="N14" s="7" t="s">
         <v>25</v>
       </c>
     </row>
@@ -35834,6 +36174,8 @@
     <hyperlink ref="I11" r:id="rId10" xr:uid="{E8167B89-7FBA-4877-BC25-3D4C05ED8AA6}"/>
     <hyperlink ref="I12" r:id="rId11" xr:uid="{C4B46D5B-BD3F-4DBC-A61E-40C494B3D177}"/>
     <hyperlink ref="J13" r:id="rId12" xr:uid="{0C7D58F5-DE06-4F14-BC9F-F6688DDA76B4}"/>
+    <hyperlink ref="I14" r:id="rId13" xr:uid="{69D5D5EE-78C1-424D-8FB6-5CEE6BF86BEE}"/>
+    <hyperlink ref="J14" r:id="rId14" xr:uid="{E4E8D2D8-B131-437F-A58D-DE6AA7E926D6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D470915-6B92-45F6-8D0F-A398B9E7A2D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A1163EA-8E62-4F34-AC84-F68F818BB4C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32280" yWindow="2235" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38205" yWindow="5070" windowWidth="16200" windowHeight="9975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7467" uniqueCount="3720">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7479" uniqueCount="3727">
   <si>
     <t>ID</t>
   </si>
@@ -11208,6 +11208,27 @@
   </si>
   <si>
     <t>https://www.mouser.es/ProductDetail/Bourns/SF-1206F250-2?qs=GIQXYiEeHGDcWHFyUr2UTQ%3D%3D</t>
+  </si>
+  <si>
+    <t>001-0124</t>
+  </si>
+  <si>
+    <t>06033C821KAT2A</t>
+  </si>
+  <si>
+    <t>581-06033C821KAT2A</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/datasheet/3/5926/1/X7RDielectric.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/KYOCERA-AVX/06033C821KAT2A?qs=L7ztplQO5PEEKgzJp4fVEA%3D%3D</t>
+  </si>
+  <si>
+    <t>Condensadores de cerámica multicapa (MLCC- SMD/SMT) 25V 820pF X7R 0603 1 0% Tol</t>
+  </si>
+  <si>
+    <t>25V 820pF X7R</t>
   </si>
 </sst>
 </file>
@@ -11392,7 +11413,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -11455,7 +11476,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -11739,7 +11759,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N124"/>
+  <dimension ref="A1:N125"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="11.1796875" customWidth="1"/>
@@ -17210,6 +17230,44 @@
       </c>
       <c r="N124" t="s">
         <v>25</v>
+      </c>
+    </row>
+    <row r="125" spans="1:14">
+      <c r="A125" s="39" t="s">
+        <v>3720</v>
+      </c>
+      <c r="B125" s="16" t="s">
+        <v>3725</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>3726</v>
+      </c>
+      <c r="D125" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="E125" t="s">
+        <v>3721</v>
+      </c>
+      <c r="F125" s="3" t="s">
+        <v>3005</v>
+      </c>
+      <c r="G125" s="3" t="s">
+        <v>3722</v>
+      </c>
+      <c r="H125" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I125" s="27" t="s">
+        <v>3723</v>
+      </c>
+      <c r="J125" s="32" t="s">
+        <v>3724</v>
+      </c>
+      <c r="K125" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="L125" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -17321,9 +17379,11 @@
     <hyperlink ref="J123" r:id="rId104" xr:uid="{FF54A4A3-2741-4A5A-9D1A-3F5746177EAD}"/>
     <hyperlink ref="I124" r:id="rId105" xr:uid="{3BC617E5-C20D-4B7A-B6F8-6DE6572A7AA0}"/>
     <hyperlink ref="J124" r:id="rId106" xr:uid="{69468929-3CB4-4434-AED4-E3828EC8E37D}"/>
+    <hyperlink ref="I125" r:id="rId107" xr:uid="{3751854E-FBCB-466E-9A3F-E9FA67863B07}"/>
+    <hyperlink ref="J125" r:id="rId108" xr:uid="{9182F2C7-A992-4E11-BE40-90109E613496}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId107"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId109"/>
 </worksheet>
 </file>
 
@@ -36125,7 +36185,7 @@
       <c r="C14" s="16" t="s">
         <v>1997</v>
       </c>
-      <c r="D14" s="40" t="s">
+      <c r="D14" s="3" t="s">
         <v>2047</v>
       </c>
       <c r="E14" t="s">

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A1163EA-8E62-4F34-AC84-F68F818BB4C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45188B53-EC23-4051-AED2-71F3F63D48E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38205" yWindow="5070" windowWidth="16200" windowHeight="9975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="970" yWindow="2880" windowWidth="16200" windowHeight="9980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7479" uniqueCount="3727">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7481" uniqueCount="3727">
   <si>
     <t>ID</t>
   </si>
@@ -17269,6 +17269,12 @@
       <c r="L125" t="s">
         <v>61</v>
       </c>
+      <c r="M125" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="N125" t="s">
+        <v>25</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="16" type="noConversion"/>

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45188B53-EC23-4051-AED2-71F3F63D48E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{483B9C45-A4C5-46C1-B133-402A95888440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="970" yWindow="2880" windowWidth="16200" windowHeight="9980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10710" yWindow="0" windowWidth="10980" windowHeight="13770" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7481" uniqueCount="3727">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7621" uniqueCount="3794">
   <si>
     <t>ID</t>
   </si>
@@ -11229,6 +11229,207 @@
   </si>
   <si>
     <t>25V 820pF X7R</t>
+  </si>
+  <si>
+    <t>110-0066</t>
+  </si>
+  <si>
+    <t>110-0067</t>
+  </si>
+  <si>
+    <t>Alojamientos de cables y cabecera 2.54mm Male Header, 2X4pin, Straight, PA6T, Gold Flash</t>
+  </si>
+  <si>
+    <t>Alojamientos de cables y cabecera 2.54mm Male Header, 1x3pin, Straight, PA6T, Gold Flash</t>
+  </si>
+  <si>
+    <t>SSK03-MPH-254-B4</t>
+  </si>
+  <si>
+    <t>179-SSK03MPH254B4</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Same-Sky/SSK03-MPH-254-B4?qs=G4MbTVxgV4Ers0DmO9LUxQ%3D%3D</t>
+  </si>
+  <si>
+    <t>PIN_HEADER_THT_2x4P</t>
+  </si>
+  <si>
+    <t>SSK01-MPH-254-A3</t>
+  </si>
+  <si>
+    <t>179-SSK01MPH254A3</t>
+  </si>
+  <si>
+    <t>https://www.sameskydevices.com/product/resource/ssk01-mph-254.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Same-Sky/SSK01-MPH-254-A3?qs=G4MbTVxgV4Fn9I88dZHrEw%3D%3D</t>
+  </si>
+  <si>
+    <t>001-0125</t>
+  </si>
+  <si>
+    <t>001-0126</t>
+  </si>
+  <si>
+    <t>Condensadores de cerámica multicapa (MLCC- SMD/SMT) WCAP-CSGP 4700pF 0603 10% 25V MLCC</t>
+  </si>
+  <si>
+    <t>Condensadores de cerámica multicapa (MLCC- SMD/SMT) WCAP-CSGP 50VDC 22pF 0201 5%</t>
+  </si>
+  <si>
+    <t>25V 4.7nF X7R</t>
+  </si>
+  <si>
+    <t>50V 22pF X7R</t>
+  </si>
+  <si>
+    <t>885012206063</t>
+  </si>
+  <si>
+    <t>710-885012206063</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/885012206063.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/885012206063?qs=0KOYDY2FL285eK3hQulgUw%3D%3D</t>
+  </si>
+  <si>
+    <t>885012004012</t>
+  </si>
+  <si>
+    <t>710-885012004012</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/885012004012.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/885012004012?qs=rQFj71Wb1eXV%2FFwrY5Shkg%3D%3D</t>
+  </si>
+  <si>
+    <t>010-0177</t>
+  </si>
+  <si>
+    <t>Resistores de película gruesa - SMD WRIS-RSKS 120 Ohms 1 % 0.1 W 0603 AEC-Q200</t>
+  </si>
+  <si>
+    <t>560112116119</t>
+  </si>
+  <si>
+    <t>710-560112116119</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/560112116119.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/560112116119?qs=mELouGlnn3eT%2F22oIMY8Ng%3D%3D</t>
+  </si>
+  <si>
+    <t>032-0023</t>
+  </si>
+  <si>
+    <t>ESD2CAN24DBZRQ1</t>
+  </si>
+  <si>
+    <t>595-ESD2CAN24DBZRQ1</t>
+  </si>
+  <si>
+    <t>https://www.ti.com/lit/ds/symlink/esd2canxl24-q1.pdf?ts=1782719399037&amp;ref_url=https%253A%252F%252Fwww.mouser.it%252F</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Texas-Instruments/ESD2CAN24DBZRQ1?qs=Y0Uzf4wQF3knJz9mU6BNuw%3D%3D</t>
+  </si>
+  <si>
+    <t>SOT-23-3</t>
+  </si>
+  <si>
+    <t>Diodos de Protección contra ESD / Diodos TVS Automotive dual 3- p F +/-24-V +/-30-k</t>
+  </si>
+  <si>
+    <t>050-0007</t>
+  </si>
+  <si>
+    <t>Sensores de corriente montados en placa</t>
+  </si>
+  <si>
+    <t>SOIC-8</t>
+  </si>
+  <si>
+    <t>SN65HVD23</t>
+  </si>
+  <si>
+    <t>SN65HVD230DR</t>
+  </si>
+  <si>
+    <t>595-SN65HVD230DR</t>
+  </si>
+  <si>
+    <t>https://www.ti.com/lit/ds/symlink/sn65hvd232.pdf?ts=1782719100047&amp;ref_url=https%253A%252F%252Fwww.mouser.tw%252F</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Texas-Instruments/SN65HVD230DR?qs=QViXGNcIEAtifeQR3pYVUQ%3D%3D</t>
+  </si>
+  <si>
+    <t>060-0003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HASS 500-S </t>
+  </si>
+  <si>
+    <t>61-HASS500-S</t>
+  </si>
+  <si>
+    <t>https://www.lem.com/sites/default/files/products_datasheets/hass-50_600-s-v22.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/LEM/HASS-500-S?qs=Vi0JKjFBtYkICNHwIPcpdw%3D%3D</t>
+  </si>
+  <si>
+    <t>HASS 500-S</t>
+  </si>
+  <si>
+    <t>010-0178</t>
+  </si>
+  <si>
+    <t>010-0179</t>
+  </si>
+  <si>
+    <t>Resistores de película fina - SMD 0.2W 500ohm 0.1% 10ppm</t>
+  </si>
+  <si>
+    <t>500Ω 200mW ±0.1%</t>
+  </si>
+  <si>
+    <t>PTN0805Y5000BST1</t>
+  </si>
+  <si>
+    <t>71-PTN0805Y5000BST1</t>
+  </si>
+  <si>
+    <t>https://www.vishay.com/docs/60026/ptn.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Vishay-Thin-Film/PTN0805Y5000BST1?qs=zW32dvEIR3sKd%2FnwncGe3A%3D%3D</t>
+  </si>
+  <si>
+    <t>Resistores de película fina - SMD 1/8W 510 Ohms 0.05% 0805 10ppm</t>
+  </si>
+  <si>
+    <t>510Ω 125mW ±0.05%</t>
+  </si>
+  <si>
+    <t>RG2012N-511-W-T1</t>
+  </si>
+  <si>
+    <t>754-RG2012N-511-W-T1</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/datasheet/3/826/1/n_catalog_partition01_en.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Susumu/RG2012N-511-W-T1?qs=juJhw1yPxAFbuvw1oDA4sg%3D%3D</t>
   </si>
 </sst>
 </file>
@@ -11238,7 +11439,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -11413,7 +11614,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -11476,6 +11677,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -11759,8 +11962,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N125"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <dimension ref="A1:N128"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.1796875" customWidth="1"/>
     <col min="2" max="2" width="29.6328125" customWidth="1"/>
@@ -11778,7 +11981,7 @@
     <col min="14" max="14" width="17.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="13.5" customHeight="1">
+    <row r="1" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -11822,7 +12025,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="14" customHeight="1">
+    <row r="2" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>58</v>
       </c>
@@ -11866,7 +12069,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="14" customHeight="1">
+    <row r="3" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>73</v>
       </c>
@@ -11910,7 +12113,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="14" customHeight="1">
+    <row r="4" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>81</v>
       </c>
@@ -11954,7 +12157,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="14" customHeight="1">
+    <row r="5" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>88</v>
       </c>
@@ -11998,7 +12201,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="14" customHeight="1">
+    <row r="6" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>95</v>
       </c>
@@ -12042,7 +12245,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="14" customHeight="1">
+    <row r="7" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>103</v>
       </c>
@@ -12086,7 +12289,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="14" customHeight="1">
+    <row r="8" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>110</v>
       </c>
@@ -12130,7 +12333,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="14" customHeight="1">
+    <row r="9" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>117</v>
       </c>
@@ -12174,7 +12377,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="14" customHeight="1">
+    <row r="10" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>124</v>
       </c>
@@ -12218,7 +12421,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="14" customHeight="1">
+    <row r="11" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>131</v>
       </c>
@@ -12262,7 +12465,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="14" customHeight="1">
+    <row r="12" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>138</v>
       </c>
@@ -12306,7 +12509,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="14" customHeight="1">
+    <row r="13" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>145</v>
       </c>
@@ -12350,7 +12553,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="14" customHeight="1">
+    <row r="14" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>153</v>
       </c>
@@ -12394,7 +12597,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="14" customHeight="1">
+    <row r="15" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>160</v>
       </c>
@@ -12438,7 +12641,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="14" customHeight="1">
+    <row r="16" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>167</v>
       </c>
@@ -12482,7 +12685,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="14" customHeight="1">
+    <row r="17" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>174</v>
       </c>
@@ -12526,7 +12729,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="14" customHeight="1">
+    <row r="18" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
         <v>180</v>
       </c>
@@ -12570,7 +12773,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="14" customHeight="1">
+    <row r="19" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>187</v>
       </c>
@@ -12614,7 +12817,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="14" customHeight="1">
+    <row r="20" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
         <v>194</v>
       </c>
@@ -12658,7 +12861,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="14" customHeight="1">
+    <row r="21" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
         <v>201</v>
       </c>
@@ -12702,7 +12905,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="14" customHeight="1">
+    <row r="22" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
         <v>208</v>
       </c>
@@ -12746,7 +12949,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="14" customHeight="1">
+    <row r="23" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>216</v>
       </c>
@@ -12790,7 +12993,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="14" customHeight="1">
+    <row r="24" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
         <v>223</v>
       </c>
@@ -12834,7 +13037,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="14" customHeight="1">
+    <row r="25" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>230</v>
       </c>
@@ -12878,7 +13081,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="14" customHeight="1">
+    <row r="26" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
         <v>237</v>
       </c>
@@ -12922,7 +13125,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="14" customHeight="1">
+    <row r="27" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
         <v>246</v>
       </c>
@@ -12966,7 +13169,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="14" customHeight="1">
+    <row r="28" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
         <v>254</v>
       </c>
@@ -13010,7 +13213,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="14" customHeight="1">
+    <row r="29" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
         <v>261</v>
       </c>
@@ -13054,7 +13257,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="14" customHeight="1">
+    <row r="30" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
         <v>268</v>
       </c>
@@ -13098,7 +13301,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="14" customHeight="1">
+    <row r="31" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
         <v>275</v>
       </c>
@@ -13142,7 +13345,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="14" customHeight="1">
+    <row r="32" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
         <v>282</v>
       </c>
@@ -13186,7 +13389,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="14" customHeight="1">
+    <row r="33" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
         <v>288</v>
       </c>
@@ -13230,7 +13433,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="1:14" ht="14" customHeight="1">
+    <row r="34" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
         <v>295</v>
       </c>
@@ -13274,7 +13477,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="1:14" ht="14" customHeight="1">
+    <row r="35" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
         <v>302</v>
       </c>
@@ -13318,7 +13521,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:14" ht="14" customHeight="1">
+    <row r="36" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="s">
         <v>308</v>
       </c>
@@ -13362,7 +13565,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:14" ht="14" customHeight="1">
+    <row r="37" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
         <v>315</v>
       </c>
@@ -13406,7 +13609,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:14" ht="14" customHeight="1">
+    <row r="38" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="s">
         <v>322</v>
       </c>
@@ -13450,7 +13653,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:14" ht="14" customHeight="1">
+    <row r="39" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
         <v>329</v>
       </c>
@@ -13494,7 +13697,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="40" spans="1:14" ht="14" customHeight="1">
+    <row r="40" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
         <v>336</v>
       </c>
@@ -13538,7 +13741,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="41" spans="1:14" ht="14" customHeight="1">
+    <row r="41" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
         <v>343</v>
       </c>
@@ -13582,7 +13785,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="42" spans="1:14" ht="14" customHeight="1">
+    <row r="42" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
         <v>350</v>
       </c>
@@ -13626,7 +13829,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="43" spans="1:14" ht="14" customHeight="1">
+    <row r="43" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
         <v>357</v>
       </c>
@@ -13670,7 +13873,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="44" spans="1:14" ht="14" customHeight="1">
+    <row r="44" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
         <v>364</v>
       </c>
@@ -13714,7 +13917,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="45" spans="1:14" ht="14" customHeight="1">
+    <row r="45" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
         <v>371</v>
       </c>
@@ -13758,7 +13961,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="1:14" ht="14" customHeight="1">
+    <row r="46" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
         <v>378</v>
       </c>
@@ -13802,7 +14005,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="47" spans="1:14" ht="14" customHeight="1">
+    <row r="47" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
         <v>384</v>
       </c>
@@ -13846,7 +14049,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="48" spans="1:14" ht="14" customHeight="1">
+    <row r="48" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
         <v>391</v>
       </c>
@@ -13890,7 +14093,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="49" spans="1:14" ht="14" customHeight="1">
+    <row r="49" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
         <v>398</v>
       </c>
@@ -13934,7 +14137,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="50" spans="1:14" ht="14" customHeight="1">
+    <row r="50" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
         <v>405</v>
       </c>
@@ -13978,7 +14181,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="51" spans="1:14" ht="14" customHeight="1">
+    <row r="51" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
         <v>413</v>
       </c>
@@ -14022,7 +14225,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="52" spans="1:14" ht="14" customHeight="1">
+    <row r="52" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
         <v>420</v>
       </c>
@@ -14066,7 +14269,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="53" spans="1:14" ht="14" customHeight="1">
+    <row r="53" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
         <v>427</v>
       </c>
@@ -14110,7 +14313,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="54" spans="1:14" ht="14" customHeight="1">
+    <row r="54" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="s">
         <v>434</v>
       </c>
@@ -14154,7 +14357,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="55" spans="1:14" ht="14" customHeight="1">
+    <row r="55" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
         <v>441</v>
       </c>
@@ -14198,7 +14401,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="56" spans="1:14" ht="14" customHeight="1">
+    <row r="56" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
         <v>448</v>
       </c>
@@ -14242,7 +14445,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="57" spans="1:14" ht="14" customHeight="1">
+    <row r="57" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
         <v>455</v>
       </c>
@@ -14284,7 +14487,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="58" spans="1:14" ht="14" customHeight="1">
+    <row r="58" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
         <v>461</v>
       </c>
@@ -14328,7 +14531,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="59" spans="1:14" ht="14" customHeight="1">
+    <row r="59" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
         <v>467</v>
       </c>
@@ -14372,7 +14575,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="1:14" ht="14" customHeight="1">
+    <row r="60" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
         <v>474</v>
       </c>
@@ -14416,7 +14619,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="61" spans="1:14" ht="14" customHeight="1">
+    <row r="61" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
         <v>482</v>
       </c>
@@ -14460,7 +14663,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="62" spans="1:14" ht="14" customHeight="1">
+    <row r="62" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="4" t="s">
         <v>490</v>
       </c>
@@ -14504,7 +14707,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="63" spans="1:14" ht="14" customHeight="1">
+    <row r="63" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="4" t="s">
         <v>497</v>
       </c>
@@ -14548,7 +14751,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="64" spans="1:14" ht="14" customHeight="1">
+    <row r="64" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="4" t="s">
         <v>504</v>
       </c>
@@ -14592,7 +14795,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="65" spans="1:14" ht="14" customHeight="1">
+    <row r="65" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
         <v>511</v>
       </c>
@@ -14636,7 +14839,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="66" spans="1:14" ht="14" customHeight="1">
+    <row r="66" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
         <v>517</v>
       </c>
@@ -14680,7 +14883,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="67" spans="1:14" ht="14" customHeight="1">
+    <row r="67" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="4" t="s">
         <v>525</v>
       </c>
@@ -14724,7 +14927,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="68" spans="1:14" ht="14" customHeight="1">
+    <row r="68" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="4" t="s">
         <v>531</v>
       </c>
@@ -14768,7 +14971,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="69" spans="1:14" ht="14" customHeight="1">
+    <row r="69" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="4" t="s">
         <v>538</v>
       </c>
@@ -14812,7 +15015,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="70" spans="1:14" ht="14" customHeight="1">
+    <row r="70" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="4" t="s">
         <v>545</v>
       </c>
@@ -14856,7 +15059,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="71" spans="1:14" ht="14" customHeight="1">
+    <row r="71" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="4" t="s">
         <v>552</v>
       </c>
@@ -14900,7 +15103,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="72" spans="1:14" ht="14" customHeight="1">
+    <row r="72" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="4" t="s">
         <v>560</v>
       </c>
@@ -14944,7 +15147,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="73" spans="1:14" ht="14" customHeight="1">
+    <row r="73" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="4" t="s">
         <v>567</v>
       </c>
@@ -14988,7 +15191,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="74" spans="1:14" ht="14" customHeight="1">
+    <row r="74" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="4" t="s">
         <v>574</v>
       </c>
@@ -15032,7 +15235,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="75" spans="1:14" ht="14" customHeight="1">
+    <row r="75" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="4" t="s">
         <v>582</v>
       </c>
@@ -15076,7 +15279,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="76" spans="1:14" ht="14" customHeight="1">
+    <row r="76" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="4" t="s">
         <v>589</v>
       </c>
@@ -15120,7 +15323,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="77" spans="1:14" ht="14" customHeight="1">
+    <row r="77" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="4" t="s">
         <v>595</v>
       </c>
@@ -15164,7 +15367,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="78" spans="1:14" ht="14" customHeight="1">
+    <row r="78" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="4" t="s">
         <v>602</v>
       </c>
@@ -15208,7 +15411,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="79" spans="1:14" ht="14" customHeight="1">
+    <row r="79" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="4" t="s">
         <v>608</v>
       </c>
@@ -15252,7 +15455,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="80" spans="1:14" ht="14" customHeight="1">
+    <row r="80" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="4" t="s">
         <v>615</v>
       </c>
@@ -15296,7 +15499,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="81" spans="1:14" ht="14" customHeight="1">
+    <row r="81" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="4" t="s">
         <v>622</v>
       </c>
@@ -15340,7 +15543,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="82" spans="1:14" ht="14" customHeight="1">
+    <row r="82" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="4" t="s">
         <v>628</v>
       </c>
@@ -15384,7 +15587,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="83" spans="1:14" ht="14" customHeight="1">
+    <row r="83" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="4" t="s">
         <v>635</v>
       </c>
@@ -15428,7 +15631,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="84" spans="1:14" ht="14" customHeight="1">
+    <row r="84" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="4" t="s">
         <v>642</v>
       </c>
@@ -15472,7 +15675,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="85" spans="1:14" ht="14" customHeight="1">
+    <row r="85" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="4" t="s">
         <v>643</v>
       </c>
@@ -15516,7 +15719,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="86" spans="1:14" ht="14" customHeight="1">
+    <row r="86" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="4" t="s">
         <v>650</v>
       </c>
@@ -15560,7 +15763,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="87" spans="1:14" ht="14" customHeight="1">
+    <row r="87" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="4" t="s">
         <v>656</v>
       </c>
@@ -15604,7 +15807,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="88" spans="1:14" ht="14" customHeight="1">
+    <row r="88" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="4" t="s">
         <v>663</v>
       </c>
@@ -15648,7 +15851,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="89" spans="1:14" ht="14" customHeight="1">
+    <row r="89" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="4" t="s">
         <v>670</v>
       </c>
@@ -15692,7 +15895,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="90" spans="1:14" ht="14" customHeight="1">
+    <row r="90" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="4" t="s">
         <v>677</v>
       </c>
@@ -15736,7 +15939,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="91" spans="1:14" ht="14" customHeight="1">
+    <row r="91" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="4" t="s">
         <v>684</v>
       </c>
@@ -15780,7 +15983,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="92" spans="1:14" ht="14" customHeight="1">
+    <row r="92" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="4" t="s">
         <v>691</v>
       </c>
@@ -15824,7 +16027,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="93" spans="1:14">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A93" s="4" t="s">
         <v>2980</v>
       </c>
@@ -15868,7 +16071,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="94" spans="1:14">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A94" s="4" t="s">
         <v>2986</v>
       </c>
@@ -15912,7 +16115,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="95" spans="1:14">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A95" s="4" t="s">
         <v>3000</v>
       </c>
@@ -15956,7 +16159,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="96" spans="1:14">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A96" s="4" t="s">
         <v>3001</v>
       </c>
@@ -16000,7 +16203,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="97" spans="1:14">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A97" s="4" t="s">
         <v>3002</v>
       </c>
@@ -16044,7 +16247,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="98" spans="1:14">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A98" s="4" t="s">
         <v>3050</v>
       </c>
@@ -16088,7 +16291,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="99" spans="1:14">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A99" s="4" t="s">
         <v>3056</v>
       </c>
@@ -16132,7 +16335,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="100" spans="1:14">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A100" s="4" t="s">
         <v>3057</v>
       </c>
@@ -16176,7 +16379,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="101" spans="1:14">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A101" s="4" t="s">
         <v>3058</v>
       </c>
@@ -16220,7 +16423,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="102" spans="1:14">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A102" s="4" t="s">
         <v>3059</v>
       </c>
@@ -16264,7 +16467,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="103" spans="1:14">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A103" s="4" t="s">
         <v>3075</v>
       </c>
@@ -16308,7 +16511,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="104" spans="1:14">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A104" s="4" t="s">
         <v>3091</v>
       </c>
@@ -16352,7 +16555,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="105" spans="1:14">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A105" s="4" t="s">
         <v>3096</v>
       </c>
@@ -16396,7 +16599,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="106" spans="1:14">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A106" s="4" t="s">
         <v>3219</v>
       </c>
@@ -16440,7 +16643,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="107" spans="1:14">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A107" s="4" t="s">
         <v>3260</v>
       </c>
@@ -16484,7 +16687,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="108" spans="1:14">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A108" s="4" t="s">
         <v>3325</v>
       </c>
@@ -16528,7 +16731,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="109" spans="1:14">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A109" s="4" t="s">
         <v>3326</v>
       </c>
@@ -16572,7 +16775,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="110" spans="1:14">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A110" s="4" t="s">
         <v>3327</v>
       </c>
@@ -16616,7 +16819,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="111" spans="1:14">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A111" s="4" t="s">
         <v>3367</v>
       </c>
@@ -16660,7 +16863,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="112" spans="1:14">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A112" s="4" t="s">
         <v>3368</v>
       </c>
@@ -16704,7 +16907,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="113" spans="1:14">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A113" s="4" t="s">
         <v>3369</v>
       </c>
@@ -16748,7 +16951,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="114" spans="1:14">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A114" s="4" t="s">
         <v>3370</v>
       </c>
@@ -16792,7 +16995,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="115" spans="1:14">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A115" s="4" t="s">
         <v>3461</v>
       </c>
@@ -16836,7 +17039,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="116" spans="1:14">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A116" s="4" t="s">
         <v>3462</v>
       </c>
@@ -16880,7 +17083,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="117" spans="1:14">
+    <row r="117" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A117" s="4" t="s">
         <v>3468</v>
       </c>
@@ -16924,7 +17127,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="118" spans="1:14">
+    <row r="118" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A118" s="4" t="s">
         <v>3482</v>
       </c>
@@ -16968,7 +17171,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="119" spans="1:14">
+    <row r="119" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A119" s="4" t="s">
         <v>3483</v>
       </c>
@@ -17012,7 +17215,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="120" spans="1:14">
+    <row r="120" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A120" s="4" t="s">
         <v>3529</v>
       </c>
@@ -17056,7 +17259,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="121" spans="1:14">
+    <row r="121" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A121" s="4" t="s">
         <v>3530</v>
       </c>
@@ -17100,7 +17303,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="122" spans="1:14">
+    <row r="122" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A122" s="4" t="s">
         <v>3584</v>
       </c>
@@ -17144,7 +17347,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="123" spans="1:14">
+    <row r="123" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A123" s="39" t="s">
         <v>3655</v>
       </c>
@@ -17188,7 +17391,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="124" spans="1:14">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A124" s="39" t="s">
         <v>3698</v>
       </c>
@@ -17232,7 +17435,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="125" spans="1:14">
+    <row r="125" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A125" s="39" t="s">
         <v>3720</v>
       </c>
@@ -17275,6 +17478,97 @@
       <c r="N125" t="s">
         <v>25</v>
       </c>
+    </row>
+    <row r="126" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A126" s="39" t="s">
+        <v>3739</v>
+      </c>
+      <c r="B126" s="16" t="s">
+        <v>3741</v>
+      </c>
+      <c r="C126" s="16" t="s">
+        <v>3743</v>
+      </c>
+      <c r="D126" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="E126" s="36" t="s">
+        <v>3745</v>
+      </c>
+      <c r="F126" s="3" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G126" s="3" t="s">
+        <v>3746</v>
+      </c>
+      <c r="H126" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I126" s="27" t="s">
+        <v>3747</v>
+      </c>
+      <c r="J126" s="27" t="s">
+        <v>3748</v>
+      </c>
+      <c r="K126" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="L126" t="s">
+        <v>61</v>
+      </c>
+      <c r="M126" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N126" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="127" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A127" s="39" t="s">
+        <v>3740</v>
+      </c>
+      <c r="B127" s="16" t="s">
+        <v>3742</v>
+      </c>
+      <c r="C127" s="16" t="s">
+        <v>3744</v>
+      </c>
+      <c r="D127" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E127" s="36" t="s">
+        <v>3749</v>
+      </c>
+      <c r="F127" s="3" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G127" s="3" t="s">
+        <v>3750</v>
+      </c>
+      <c r="H127" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I127" s="27" t="s">
+        <v>3751</v>
+      </c>
+      <c r="J127" s="27" t="s">
+        <v>3752</v>
+      </c>
+      <c r="K127" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="L127" t="s">
+        <v>61</v>
+      </c>
+      <c r="M127" s="7" t="s">
+        <v>699</v>
+      </c>
+      <c r="N127" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="128" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A128" s="39"/>
     </row>
   </sheetData>
   <phoneticPr fontId="16" type="noConversion"/>
@@ -17387,21 +17681,24 @@
     <hyperlink ref="J124" r:id="rId106" xr:uid="{69468929-3CB4-4434-AED4-E3828EC8E37D}"/>
     <hyperlink ref="I125" r:id="rId107" xr:uid="{3751854E-FBCB-466E-9A3F-E9FA67863B07}"/>
     <hyperlink ref="J125" r:id="rId108" xr:uid="{9182F2C7-A992-4E11-BE40-90109E613496}"/>
+    <hyperlink ref="I127" r:id="rId109" xr:uid="{8B613FFC-245E-4018-8618-7ADD2AFEA0F4}"/>
+    <hyperlink ref="J127" r:id="rId110" xr:uid="{A4DE3241-74D8-49E9-8179-47E56B1F9994}"/>
+    <hyperlink ref="J126" r:id="rId111" xr:uid="{348E15E9-2492-4FC3-9ADB-2287FB61453A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId109"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId112"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79E65951-BFD2-4888-A0A6-19D5130CB4A6}">
-  <dimension ref="A1:N23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <dimension ref="A1:N24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="41.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
@@ -17445,7 +17742,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2003</v>
       </c>
@@ -17486,7 +17783,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2012</v>
       </c>
@@ -17530,7 +17827,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>2020</v>
       </c>
@@ -17574,7 +17871,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>2028</v>
       </c>
@@ -17618,7 +17915,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>2035</v>
       </c>
@@ -17662,7 +17959,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>2045</v>
       </c>
@@ -17706,7 +18003,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>2053</v>
       </c>
@@ -17750,7 +18047,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>2061</v>
       </c>
@@ -17794,7 +18091,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>2068</v>
       </c>
@@ -17838,7 +18135,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>2075</v>
       </c>
@@ -17882,7 +18179,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>2082</v>
       </c>
@@ -17926,7 +18223,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>2089</v>
       </c>
@@ -17970,7 +18267,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>2097</v>
       </c>
@@ -18014,7 +18311,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>2106</v>
       </c>
@@ -18058,7 +18355,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>2112</v>
       </c>
@@ -18102,7 +18399,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:14">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>2118</v>
       </c>
@@ -18146,7 +18443,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:14">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>2126</v>
       </c>
@@ -18190,7 +18487,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:14">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>2133</v>
       </c>
@@ -18234,7 +18531,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:14">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>2140</v>
       </c>
@@ -18278,7 +18575,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:14">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>2148</v>
       </c>
@@ -18322,7 +18619,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:14">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>2155</v>
       </c>
@@ -18366,7 +18663,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:14">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>2162</v>
       </c>
@@ -18410,7 +18707,56 @@
         <v>25</v>
       </c>
     </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>3759</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>3765</v>
+      </c>
+      <c r="C24" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24" t="s">
+        <v>3764</v>
+      </c>
+      <c r="E24" t="s">
+        <v>3760</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3761</v>
+      </c>
+      <c r="H24" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I24" s="27" t="s">
+        <v>3762</v>
+      </c>
+      <c r="J24" s="32" t="s">
+        <v>3763</v>
+      </c>
+      <c r="K24" t="s">
+        <v>2074</v>
+      </c>
+      <c r="L24" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M24" t="s">
+        <v>1856</v>
+      </c>
+      <c r="N24" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="16" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="I24" r:id="rId1" xr:uid="{78311E40-7EC4-416F-9EC0-8BD29F412DF9}"/>
+    <hyperlink ref="J24" r:id="rId2" xr:uid="{44368450-35A2-41A5-87EC-FE66FDA78B0D}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -18418,9 +18764,9 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89BFA1EF-29B2-41E4-A9D1-F8E90A663FA1}">
   <dimension ref="A1:N24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="14.5" customHeight="1">
+    <row r="1" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
@@ -18464,7 +18810,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
         <v>2766</v>
       </c>
@@ -18508,7 +18854,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
         <v>2776</v>
       </c>
@@ -18552,7 +18898,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>2784</v>
       </c>
@@ -18596,7 +18942,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
         <v>2791</v>
       </c>
@@ -18640,7 +18986,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
         <v>2799</v>
       </c>
@@ -18684,7 +19030,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
         <v>2806</v>
       </c>
@@ -18728,7 +19074,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
         <v>2817</v>
       </c>
@@ -18772,7 +19118,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="14.5" customHeight="1">
+    <row r="9" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
         <v>2827</v>
       </c>
@@ -18816,7 +19162,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
         <v>2836</v>
       </c>
@@ -18860,7 +19206,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
         <v>2844</v>
       </c>
@@ -18904,7 +19250,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
         <v>2852</v>
       </c>
@@ -18948,7 +19294,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="13.5" customHeight="1">
+    <row r="13" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
         <v>2860</v>
       </c>
@@ -18992,7 +19338,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="15" customHeight="1">
+    <row r="14" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="7" t="s">
         <v>2870</v>
       </c>
@@ -19036,7 +19382,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="7" t="s">
         <v>2960</v>
       </c>
@@ -19080,7 +19426,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
         <v>2961</v>
       </c>
@@ -19124,7 +19470,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:14">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="7" t="s">
         <v>2962</v>
       </c>
@@ -19168,7 +19514,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:14">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" s="7" t="s">
         <v>2963</v>
       </c>
@@ -19212,7 +19558,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:14">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" s="7" t="s">
         <v>2964</v>
       </c>
@@ -19256,7 +19602,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:14">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" s="7" t="s">
         <v>2965</v>
       </c>
@@ -19300,7 +19646,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:14">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" s="7" t="s">
         <v>2966</v>
       </c>
@@ -19344,7 +19690,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:14">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" s="7" t="s">
         <v>2967</v>
       </c>
@@ -19388,7 +19734,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:14">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" s="7" t="s">
         <v>2968</v>
       </c>
@@ -19432,7 +19778,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:14">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" s="7" t="s">
         <v>2969</v>
       </c>
@@ -19503,13 +19849,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B6F0D32-9CE2-4DF7-927E-42E7BA331F12}">
   <dimension ref="A1:O22"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="13" max="13" width="13.36328125" customWidth="1"/>
     <col min="14" max="14" width="16.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -19553,7 +19899,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -19597,7 +19943,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1813</v>
       </c>
@@ -19642,7 +19988,7 @@
       </c>
       <c r="O3" s="7"/>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>1814</v>
       </c>
@@ -19687,7 +20033,7 @@
       </c>
       <c r="O4" s="7"/>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>1815</v>
       </c>
@@ -19732,7 +20078,7 @@
       </c>
       <c r="O5" s="3"/>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>1816</v>
       </c>
@@ -19777,7 +20123,7 @@
       </c>
       <c r="O6" s="3"/>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>1817</v>
       </c>
@@ -19822,7 +20168,7 @@
       </c>
       <c r="O7" s="3"/>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>1818</v>
       </c>
@@ -19867,7 +20213,7 @@
       </c>
       <c r="O8" s="3"/>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>1819</v>
       </c>
@@ -19912,7 +20258,7 @@
       </c>
       <c r="O9" s="3"/>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>1820</v>
       </c>
@@ -19957,7 +20303,7 @@
       </c>
       <c r="O10" s="3"/>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>1821</v>
       </c>
@@ -20002,7 +20348,7 @@
       </c>
       <c r="O11" s="3"/>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>1822</v>
       </c>
@@ -20047,7 +20393,7 @@
       </c>
       <c r="O12" s="3"/>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>1823</v>
       </c>
@@ -20092,7 +20438,7 @@
       </c>
       <c r="O13" s="3"/>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>1824</v>
       </c>
@@ -20137,7 +20483,7 @@
       </c>
       <c r="O14" s="3"/>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>1825</v>
       </c>
@@ -20181,7 +20527,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>1826</v>
       </c>
@@ -20225,7 +20571,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:14">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>1827</v>
       </c>
@@ -20269,7 +20615,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:14">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>1828</v>
       </c>
@@ -20313,7 +20659,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:14">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>1829</v>
       </c>
@@ -20357,7 +20703,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:14">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>1830</v>
       </c>
@@ -20401,7 +20747,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:14">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>1831</v>
       </c>
@@ -20445,7 +20791,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:14">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>3713</v>
       </c>
@@ -20518,9 +20864,9 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA7E41C9-E62B-4149-A5B5-E7986E8877E6}">
   <dimension ref="A1:N2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -20564,7 +20910,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3646</v>
       </c>
@@ -20620,9 +20966,9 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FAFF3B6-AF11-4BFB-8078-829FF6F2F366}">
   <dimension ref="A1:N2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
@@ -20666,7 +21012,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3172</v>
       </c>
@@ -20722,9 +21068,9 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E5535EA-E186-4751-BC7F-9B3A0221302E}">
   <dimension ref="A1:N3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
@@ -20768,7 +21114,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3030</v>
       </c>
@@ -20812,7 +21158,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3039</v>
       </c>
@@ -20871,7 +21217,7 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C98E1A12-072F-4773-8CB5-47FFE077E85B}">
   <dimension ref="A1:N9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="43.7265625" customWidth="1"/>
     <col min="5" max="5" width="16.1796875" customWidth="1"/>
@@ -20884,7 +21230,7 @@
     <col min="14" max="14" width="21.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -20928,7 +21274,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -20972,7 +21318,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>42</v>
       </c>
@@ -21016,7 +21362,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>1649</v>
       </c>
@@ -21060,7 +21406,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>1655</v>
       </c>
@@ -21104,7 +21450,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3605</v>
       </c>
@@ -21148,7 +21494,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3625</v>
       </c>
@@ -21192,7 +21538,51 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>3766</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>3767</v>
+      </c>
+      <c r="C8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" t="s">
+        <v>3768</v>
+      </c>
+      <c r="E8" t="s">
+        <v>3770</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>3771</v>
+      </c>
+      <c r="H8" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" s="27" t="s">
+        <v>3772</v>
+      </c>
+      <c r="J8" s="32" t="s">
+        <v>3773</v>
+      </c>
+      <c r="K8" t="s">
+        <v>3769</v>
+      </c>
+      <c r="L8" t="s">
+        <v>26</v>
+      </c>
+      <c r="M8" t="s">
+        <v>3768</v>
+      </c>
+      <c r="N8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="L9" s="21"/>
     </row>
   </sheetData>
@@ -21204,18 +21594,20 @@
     <hyperlink ref="I6" r:id="rId4" xr:uid="{9E4B6332-A551-48B7-BFF0-45B7D65C08A2}"/>
     <hyperlink ref="J6" r:id="rId5" xr:uid="{2277AFAF-7670-400C-9F4A-5D96406C91FF}"/>
     <hyperlink ref="I7" r:id="rId6" xr:uid="{4EE7BCCF-17ED-4BF0-90C6-97AD9B6D2A45}"/>
+    <hyperlink ref="I8" r:id="rId7" xr:uid="{5DA62FDE-E136-4C6E-84DA-50C789567BAA}"/>
+    <hyperlink ref="J8" r:id="rId8" xr:uid="{802F32D1-101A-4CE0-9BF6-8EBCFB56FF87}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId7"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{316C64E0-14FB-467C-956A-E132FAFB0232}">
   <dimension ref="A1:N1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -21267,9 +21659,9 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{201D74E2-3547-4E9B-8216-09A22645AC2A}">
   <dimension ref="A1:N2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
@@ -21313,7 +21705,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3163</v>
       </c>
@@ -21368,10 +21760,10 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59BC8B2E-A067-463D-937A-30E88D8BECD0}">
-  <dimension ref="A1:N3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <dimension ref="A1:N4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -21415,7 +21807,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3275</v>
       </c>
@@ -21459,7 +21851,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3662</v>
       </c>
@@ -21503,12 +21895,59 @@
         <v>25</v>
       </c>
     </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>3774</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>3767</v>
+      </c>
+      <c r="C4" t="s">
+        <v>3273</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="36" t="s">
+        <v>3775</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>3268</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>3776</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>3777</v>
+      </c>
+      <c r="J4" s="32" t="s">
+        <v>3778</v>
+      </c>
+      <c r="K4" s="36" t="s">
+        <v>3779</v>
+      </c>
+      <c r="L4" t="s">
+        <v>3276</v>
+      </c>
+      <c r="M4" s="36" t="s">
+        <v>3779</v>
+      </c>
+      <c r="N4" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="16" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1" xr:uid="{BFD1D0BA-D934-44C0-B127-7693B6B8FCF4}"/>
     <hyperlink ref="J2" r:id="rId2" xr:uid="{72343140-B075-45AB-91DC-7B87E10B2AD1}"/>
     <hyperlink ref="I3" r:id="rId3" xr:uid="{D9F4A33B-2595-4DA0-8363-A69F15E2B303}"/>
     <hyperlink ref="J3" r:id="rId4" xr:uid="{1ABB114B-1F85-4103-ABE2-AA0C257EB7B1}"/>
+    <hyperlink ref="I4" r:id="rId5" xr:uid="{23F5B451-07F8-40FF-B8FF-09319797C4C9}"/>
+    <hyperlink ref="J4" r:id="rId6" xr:uid="{AB96B204-6A61-49B4-8F27-F35BA2651662}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -21517,12 +21956,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E05CC479-3669-40F7-BE22-BA5CFBFF29E9}">
   <dimension ref="A1:N3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="5" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -21566,7 +22005,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2906</v>
       </c>
@@ -21610,7 +22049,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3201</v>
       </c>
@@ -21668,9 +22107,9 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4185B0A-D162-4EBC-935B-7159E365DD54}">
   <dimension ref="A1:N3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -21714,7 +22153,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3289</v>
       </c>
@@ -21758,7 +22197,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3304</v>
       </c>
@@ -21817,12 +22256,12 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4BBBCF5-BAC9-459C-ABE9-2526B85FD81E}">
   <dimension ref="A1:N10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="4" max="4" width="17.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -21866,7 +22305,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>45</v>
       </c>
@@ -21910,7 +22349,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1677</v>
       </c>
@@ -21954,7 +22393,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>1683</v>
       </c>
@@ -21998,7 +22437,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3183</v>
       </c>
@@ -22042,7 +22481,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3192</v>
       </c>
@@ -22086,7 +22525,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3417</v>
       </c>
@@ -22130,7 +22569,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>3418</v>
       </c>
@@ -22174,7 +22613,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>3419</v>
       </c>
@@ -22218,7 +22657,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>3675</v>
       </c>
@@ -22285,9 +22724,9 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E9EB2F5-2977-493B-BFA2-5CD20F8A3BC4}">
   <dimension ref="A1:O3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
@@ -22334,7 +22773,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3020</v>
       </c>
@@ -22381,7 +22820,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3248</v>
       </c>
@@ -22443,9 +22882,9 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69A1C46E-DEF3-467B-A5BD-162AB66E6A86}">
   <dimension ref="A1:N24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -22489,7 +22928,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
         <v>2595</v>
       </c>
@@ -22533,7 +22972,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
         <v>2604</v>
       </c>
@@ -22577,7 +23016,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>2608</v>
       </c>
@@ -22621,7 +23060,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
         <v>2617</v>
       </c>
@@ -22663,7 +23102,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
         <v>2625</v>
       </c>
@@ -22707,7 +23146,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
         <v>2633</v>
       </c>
@@ -22751,7 +23190,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
         <v>2641</v>
       </c>
@@ -22795,7 +23234,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
         <v>2648</v>
       </c>
@@ -22839,7 +23278,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
         <v>2654</v>
       </c>
@@ -22883,7 +23322,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
         <v>2662</v>
       </c>
@@ -22927,7 +23366,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
         <v>2669</v>
       </c>
@@ -22971,7 +23410,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
         <v>2675</v>
       </c>
@@ -23015,7 +23454,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="7" t="s">
         <v>2681</v>
       </c>
@@ -23059,7 +23498,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="7" t="s">
         <v>2688</v>
       </c>
@@ -23103,7 +23542,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
         <v>2692</v>
       </c>
@@ -23147,7 +23586,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:14">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="7" t="s">
         <v>2701</v>
       </c>
@@ -23191,7 +23630,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:14">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" s="7" t="s">
         <v>2712</v>
       </c>
@@ -23235,7 +23674,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:14">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" s="7" t="s">
         <v>2716</v>
       </c>
@@ -23279,7 +23718,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:14">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" s="7" t="s">
         <v>2723</v>
       </c>
@@ -23323,7 +23762,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:14">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" s="7" t="s">
         <v>2733</v>
       </c>
@@ -23367,7 +23806,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:14">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" s="16" t="s">
         <v>2742</v>
       </c>
@@ -23411,7 +23850,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:14">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" s="16" t="s">
         <v>2751</v>
       </c>
@@ -23455,7 +23894,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:14">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" s="16" t="s">
         <v>2759</v>
       </c>
@@ -23525,15 +23964,15 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE14AD29-8DB0-4C42-AB91-A73B867AE121}">
-  <dimension ref="A1:N66"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <dimension ref="A1:N68"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="5" max="5" width="16.36328125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.26953125" customWidth="1"/>
     <col min="13" max="13" width="14.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
@@ -23577,7 +24016,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
         <v>2168</v>
       </c>
@@ -23621,7 +24060,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
         <v>2178</v>
       </c>
@@ -23665,7 +24104,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>2188</v>
       </c>
@@ -23709,7 +24148,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
         <v>2196</v>
       </c>
@@ -23753,7 +24192,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
         <v>2206</v>
       </c>
@@ -23797,7 +24236,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
         <v>2213</v>
       </c>
@@ -23841,7 +24280,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
         <v>2223</v>
       </c>
@@ -23885,7 +24324,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
         <v>2227</v>
       </c>
@@ -23929,7 +24368,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
         <v>2236</v>
       </c>
@@ -23973,7 +24412,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
         <v>2245</v>
       </c>
@@ -24017,7 +24456,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
         <v>2252</v>
       </c>
@@ -24061,7 +24500,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
         <v>2259</v>
       </c>
@@ -24105,7 +24544,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="7" t="s">
         <v>2267</v>
       </c>
@@ -24149,7 +24588,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="7" t="s">
         <v>2277</v>
       </c>
@@ -24193,7 +24632,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
         <v>2286</v>
       </c>
@@ -24237,7 +24676,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:14">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="7" t="s">
         <v>2287</v>
       </c>
@@ -24281,7 +24720,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:14">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" s="7" t="s">
         <v>2296</v>
       </c>
@@ -24325,7 +24764,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:14">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" s="7" t="s">
         <v>2303</v>
       </c>
@@ -24369,7 +24808,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:14">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" s="7" t="s">
         <v>2313</v>
       </c>
@@ -24413,7 +24852,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:14">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" s="7" t="s">
         <v>2323</v>
       </c>
@@ -24457,7 +24896,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:14">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" s="7" t="s">
         <v>2332</v>
       </c>
@@ -24501,7 +24940,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:14">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" s="7" t="s">
         <v>2340</v>
       </c>
@@ -24545,7 +24984,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:14">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" s="7" t="s">
         <v>2348</v>
       </c>
@@ -24589,7 +25028,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:14">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" s="7" t="s">
         <v>2356</v>
       </c>
@@ -24633,7 +25072,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:14">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" s="7" t="s">
         <v>2365</v>
       </c>
@@ -24677,7 +25116,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:14">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" s="7" t="s">
         <v>2373</v>
       </c>
@@ -24721,7 +25160,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:14">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" s="7" t="s">
         <v>2380</v>
       </c>
@@ -24765,7 +25204,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="1:14">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" s="7" t="s">
         <v>2390</v>
       </c>
@@ -24809,7 +25248,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="30" spans="1:14">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" s="7" t="s">
         <v>2398</v>
       </c>
@@ -24853,7 +25292,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:14">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" s="7" t="s">
         <v>2409</v>
       </c>
@@ -24897,7 +25336,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:14">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" s="7" t="s">
         <v>2418</v>
       </c>
@@ -24941,7 +25380,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:14">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A33" s="7" t="s">
         <v>2424</v>
       </c>
@@ -24985,7 +25424,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="1:14">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A34" s="7" t="s">
         <v>2430</v>
       </c>
@@ -25029,7 +25468,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="1:14">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A35" s="7" t="s">
         <v>2435</v>
       </c>
@@ -25073,7 +25512,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:14">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36" s="7" t="s">
         <v>2442</v>
       </c>
@@ -25117,7 +25556,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:14">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A37" s="7" t="s">
         <v>2450</v>
       </c>
@@ -25161,7 +25600,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:14">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A38" s="7" t="s">
         <v>2457</v>
       </c>
@@ -25205,7 +25644,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:14">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A39" s="7" t="s">
         <v>2465</v>
       </c>
@@ -25249,7 +25688,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="40" spans="1:14">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A40" s="7" t="s">
         <v>2473</v>
       </c>
@@ -25293,7 +25732,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="41" spans="1:14">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A41" s="7" t="s">
         <v>2478</v>
       </c>
@@ -25337,7 +25776,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="42" spans="1:14">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A42" s="7" t="s">
         <v>2482</v>
       </c>
@@ -25381,7 +25820,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="43" spans="1:14">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A43" s="7" t="s">
         <v>2484</v>
       </c>
@@ -25425,7 +25864,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="44" spans="1:14">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A44" s="7" t="s">
         <v>2486</v>
       </c>
@@ -25469,7 +25908,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="45" spans="1:14">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A45" s="7" t="s">
         <v>2495</v>
       </c>
@@ -25513,7 +25952,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="1:14">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A46" s="7" t="s">
         <v>2501</v>
       </c>
@@ -25557,7 +25996,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="47" spans="1:14">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A47" s="7" t="s">
         <v>2511</v>
       </c>
@@ -25601,7 +26040,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="48" spans="1:14">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A48" s="7" t="s">
         <v>2520</v>
       </c>
@@ -25645,7 +26084,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="49" spans="1:14">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A49" s="7" t="s">
         <v>2527</v>
       </c>
@@ -25689,7 +26128,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="50" spans="1:14">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A50" s="7" t="s">
         <v>2534</v>
       </c>
@@ -25733,7 +26172,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="51" spans="1:14">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A51" s="7" t="s">
         <v>2541</v>
       </c>
@@ -25777,7 +26216,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="52" spans="1:14">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A52" s="7" t="s">
         <v>2549</v>
       </c>
@@ -25821,7 +26260,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="53" spans="1:14">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A53" s="7" t="s">
         <v>2557</v>
       </c>
@@ -25865,7 +26304,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="54" spans="1:14">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A54" s="7" t="s">
         <v>2565</v>
       </c>
@@ -25909,7 +26348,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="55" spans="1:14">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A55" s="16" t="s">
         <v>2578</v>
       </c>
@@ -25953,7 +26392,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="56" spans="1:14">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A56" s="16" t="s">
         <v>2583</v>
       </c>
@@ -25997,7 +26436,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="57" spans="1:14">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A57" s="16" t="s">
         <v>2584</v>
       </c>
@@ -26041,7 +26480,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="58" spans="1:14">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A58" s="16" t="s">
         <v>2878</v>
       </c>
@@ -26085,7 +26524,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="59" spans="1:14">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A59" s="16" t="s">
         <v>2879</v>
       </c>
@@ -26129,7 +26568,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="1:14">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A60" s="16" t="s">
         <v>2880</v>
       </c>
@@ -26173,7 +26612,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="61" spans="1:14">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A61" s="16" t="s">
         <v>2881</v>
       </c>
@@ -26217,7 +26656,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="62" spans="1:14">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A62" s="16" t="s">
         <v>2916</v>
       </c>
@@ -26261,7 +26700,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="63" spans="1:14">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A63" s="16" t="s">
         <v>3254</v>
       </c>
@@ -26305,7 +26744,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="64" spans="1:14">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A64" s="16" t="s">
         <v>3282</v>
       </c>
@@ -26349,7 +26788,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="65" spans="1:14">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A65" s="16" t="s">
         <v>3551</v>
       </c>
@@ -26393,7 +26832,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="66" spans="1:14">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A66" s="16" t="s">
         <v>3683</v>
       </c>
@@ -26434,6 +26873,94 @@
         <v>3687</v>
       </c>
       <c r="N66" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A67" s="16" t="s">
+        <v>3727</v>
+      </c>
+      <c r="B67" s="16" t="s">
+        <v>3729</v>
+      </c>
+      <c r="C67" s="16" t="s">
+        <v>2411</v>
+      </c>
+      <c r="D67" s="16" t="s">
+        <v>2543</v>
+      </c>
+      <c r="E67" t="s">
+        <v>3731</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>3255</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>3732</v>
+      </c>
+      <c r="H67" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I67" s="27" t="s">
+        <v>3258</v>
+      </c>
+      <c r="J67" s="32" t="s">
+        <v>3733</v>
+      </c>
+      <c r="K67" s="31" t="s">
+        <v>2416</v>
+      </c>
+      <c r="L67" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M67" t="s">
+        <v>3734</v>
+      </c>
+      <c r="N67" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A68" s="16" t="s">
+        <v>3728</v>
+      </c>
+      <c r="B68" s="16" t="s">
+        <v>3730</v>
+      </c>
+      <c r="C68" s="16" t="s">
+        <v>2238</v>
+      </c>
+      <c r="D68" s="16" t="s">
+        <v>2543</v>
+      </c>
+      <c r="E68" t="s">
+        <v>3735</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>3255</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>3736</v>
+      </c>
+      <c r="H68" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I68" s="27" t="s">
+        <v>3737</v>
+      </c>
+      <c r="J68" s="32" t="s">
+        <v>3738</v>
+      </c>
+      <c r="K68" s="7" t="s">
+        <v>2243</v>
+      </c>
+      <c r="L68" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M68" t="s">
+        <v>2472</v>
+      </c>
+      <c r="N68" s="7" t="s">
         <v>25</v>
       </c>
     </row>
@@ -26498,6 +27025,9 @@
     <hyperlink ref="J64" r:id="rId56" xr:uid="{0176710A-1D50-48A9-9ACC-C0E8F9C09246}"/>
     <hyperlink ref="I66" r:id="rId57" xr:uid="{F4FD0F61-138E-4DBE-8F6A-3A26376F772A}"/>
     <hyperlink ref="J66" r:id="rId58" xr:uid="{F9BBC9A3-5DDE-4132-B9F9-18EE393B61F2}"/>
+    <hyperlink ref="I67" r:id="rId59" xr:uid="{D6DD9CAC-20BB-4706-BDE2-8C70E0ACB94A}"/>
+    <hyperlink ref="I68" r:id="rId60" xr:uid="{95FCBFB7-6612-4485-AC1E-1061EEA56343}"/>
+    <hyperlink ref="J68" r:id="rId61" xr:uid="{757626C9-CBA5-4F47-B647-04E7A7DD6CDF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -26506,12 +27036,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E940ACE-72CF-4504-B730-2719484575BC}">
   <dimension ref="A1:N3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="5" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -26555,7 +27085,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3211</v>
       </c>
@@ -26599,7 +27129,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3484</v>
       </c>
@@ -26657,15 +27187,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60E8291E-4293-4634-B9E9-80CB520CA181}">
-  <dimension ref="A1:N177"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <dimension ref="A1:N180"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="19.90625" customWidth="1"/>
     <col min="5" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -26709,7 +27239,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
         <v>35</v>
       </c>
@@ -26753,7 +27283,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
         <v>56</v>
       </c>
@@ -26797,7 +27327,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>716</v>
       </c>
@@ -26841,7 +27371,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
         <v>723</v>
       </c>
@@ -26885,7 +27415,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
         <v>730</v>
       </c>
@@ -26929,7 +27459,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
         <v>737</v>
       </c>
@@ -26973,7 +27503,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
         <v>744</v>
       </c>
@@ -27017,7 +27547,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
         <v>752</v>
       </c>
@@ -27061,7 +27591,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
         <v>759</v>
       </c>
@@ -27105,7 +27635,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
         <v>766</v>
       </c>
@@ -27149,7 +27679,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
         <v>773</v>
       </c>
@@ -27193,7 +27723,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
         <v>780</v>
       </c>
@@ -27237,7 +27767,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="7" t="s">
         <v>787</v>
       </c>
@@ -27281,7 +27811,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="7" t="s">
         <v>794</v>
       </c>
@@ -27325,7 +27855,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
         <v>801</v>
       </c>
@@ -27369,7 +27899,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:14">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="7" t="s">
         <v>808</v>
       </c>
@@ -27413,7 +27943,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:14">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" s="7" t="s">
         <v>815</v>
       </c>
@@ -27457,7 +27987,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:14">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" s="7" t="s">
         <v>822</v>
       </c>
@@ -27501,7 +28031,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:14">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" s="7" t="s">
         <v>829</v>
       </c>
@@ -27545,7 +28075,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:14">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" s="7" t="s">
         <v>834</v>
       </c>
@@ -27589,7 +28119,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:14">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" s="7" t="s">
         <v>841</v>
       </c>
@@ -27633,7 +28163,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:14">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" s="7" t="s">
         <v>849</v>
       </c>
@@ -27677,7 +28207,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:14">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" s="7" t="s">
         <v>856</v>
       </c>
@@ -27721,7 +28251,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:14">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" s="7" t="s">
         <v>863</v>
       </c>
@@ -27765,7 +28295,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:14">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" s="7" t="s">
         <v>870</v>
       </c>
@@ -27809,7 +28339,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:14">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" s="7" t="s">
         <v>877</v>
       </c>
@@ -27853,7 +28383,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:14">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" s="7" t="s">
         <v>884</v>
       </c>
@@ -27897,7 +28427,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="1:14">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" s="7" t="s">
         <v>891</v>
       </c>
@@ -27941,7 +28471,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="30" spans="1:14">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" s="7" t="s">
         <v>898</v>
       </c>
@@ -27985,7 +28515,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:14">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" s="7" t="s">
         <v>905</v>
       </c>
@@ -28029,7 +28559,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:14">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" s="7" t="s">
         <v>912</v>
       </c>
@@ -28073,7 +28603,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:14">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A33" s="7" t="s">
         <v>919</v>
       </c>
@@ -28117,7 +28647,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="1:14">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A34" s="7" t="s">
         <v>927</v>
       </c>
@@ -28161,7 +28691,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="1:14">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A35" s="7" t="s">
         <v>934</v>
       </c>
@@ -28205,7 +28735,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:14">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36" s="7" t="s">
         <v>941</v>
       </c>
@@ -28249,7 +28779,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:14">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A37" s="7" t="s">
         <v>949</v>
       </c>
@@ -28293,7 +28823,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:14">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A38" s="7" t="s">
         <v>956</v>
       </c>
@@ -28337,7 +28867,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:14">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A39" s="7" t="s">
         <v>963</v>
       </c>
@@ -28381,7 +28911,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="40" spans="1:14">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A40" s="7" t="s">
         <v>970</v>
       </c>
@@ -28425,7 +28955,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="41" spans="1:14">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A41" s="7" t="s">
         <v>976</v>
       </c>
@@ -28469,7 +28999,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="42" spans="1:14">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A42" s="7" t="s">
         <v>983</v>
       </c>
@@ -28513,7 +29043,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="43" spans="1:14">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A43" s="7" t="s">
         <v>990</v>
       </c>
@@ -28557,7 +29087,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="44" spans="1:14">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A44" s="7" t="s">
         <v>997</v>
       </c>
@@ -28601,7 +29131,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="45" spans="1:14">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A45" s="7" t="s">
         <v>1004</v>
       </c>
@@ -28645,7 +29175,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="1:14">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A46" s="7" t="s">
         <v>1011</v>
       </c>
@@ -28689,7 +29219,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="47" spans="1:14">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A47" s="7" t="s">
         <v>1018</v>
       </c>
@@ -28733,7 +29263,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="48" spans="1:14">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A48" s="7" t="s">
         <v>1025</v>
       </c>
@@ -28777,7 +29307,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="49" spans="1:14">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A49" s="7" t="s">
         <v>1032</v>
       </c>
@@ -28821,7 +29351,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="50" spans="1:14">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A50" s="7" t="s">
         <v>1040</v>
       </c>
@@ -28865,7 +29395,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="51" spans="1:14">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A51" s="7" t="s">
         <v>1047</v>
       </c>
@@ -28909,7 +29439,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="52" spans="1:14">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A52" s="7" t="s">
         <v>1054</v>
       </c>
@@ -28953,7 +29483,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="53" spans="1:14">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A53" s="7" t="s">
         <v>1061</v>
       </c>
@@ -28997,7 +29527,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="54" spans="1:14">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A54" s="7" t="s">
         <v>1068</v>
       </c>
@@ -29041,7 +29571,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="55" spans="1:14">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A55" s="7" t="s">
         <v>1075</v>
       </c>
@@ -29085,7 +29615,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="56" spans="1:14">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A56" s="7" t="s">
         <v>1082</v>
       </c>
@@ -29129,7 +29659,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="57" spans="1:14">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A57" s="7" t="s">
         <v>1089</v>
       </c>
@@ -29173,7 +29703,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="58" spans="1:14">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A58" s="7" t="s">
         <v>1096</v>
       </c>
@@ -29217,7 +29747,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="59" spans="1:14">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A59" s="7" t="s">
         <v>1103</v>
       </c>
@@ -29261,7 +29791,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="1:14">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A60" s="7" t="s">
         <v>1110</v>
       </c>
@@ -29305,7 +29835,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="61" spans="1:14">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A61" s="7" t="s">
         <v>1117</v>
       </c>
@@ -29349,7 +29879,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="62" spans="1:14">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A62" s="7" t="s">
         <v>1124</v>
       </c>
@@ -29393,7 +29923,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="63" spans="1:14">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A63" s="7" t="s">
         <v>1132</v>
       </c>
@@ -29437,7 +29967,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="64" spans="1:14">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A64" s="7" t="s">
         <v>1139</v>
       </c>
@@ -29481,7 +30011,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="65" spans="1:14">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A65" s="7" t="s">
         <v>1147</v>
       </c>
@@ -29525,7 +30055,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="66" spans="1:14">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A66" s="7" t="s">
         <v>1154</v>
       </c>
@@ -29569,7 +30099,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="67" spans="1:14">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A67" s="7" t="s">
         <v>1162</v>
       </c>
@@ -29613,7 +30143,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="68" spans="1:14">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A68" s="7" t="s">
         <v>1169</v>
       </c>
@@ -29657,7 +30187,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="69" spans="1:14">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A69" s="7" t="s">
         <v>1176</v>
       </c>
@@ -29701,7 +30231,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="70" spans="1:14">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A70" s="7" t="s">
         <v>1183</v>
       </c>
@@ -29745,7 +30275,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="71" spans="1:14">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A71" s="7" t="s">
         <v>1190</v>
       </c>
@@ -29789,7 +30319,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="72" spans="1:14">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A72" s="7" t="s">
         <v>1198</v>
       </c>
@@ -29833,7 +30363,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="73" spans="1:14">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A73" s="7" t="s">
         <v>1205</v>
       </c>
@@ -29877,7 +30407,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="74" spans="1:14">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A74" s="7" t="s">
         <v>1212</v>
       </c>
@@ -29921,7 +30451,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="75" spans="1:14">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A75" s="7" t="s">
         <v>1219</v>
       </c>
@@ -29965,7 +30495,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="76" spans="1:14">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A76" s="7" t="s">
         <v>1226</v>
       </c>
@@ -30009,7 +30539,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="77" spans="1:14">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A77" s="7" t="s">
         <v>1233</v>
       </c>
@@ -30053,7 +30583,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="78" spans="1:14">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A78" s="7" t="s">
         <v>1240</v>
       </c>
@@ -30097,7 +30627,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="79" spans="1:14">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A79" s="7" t="s">
         <v>1247</v>
       </c>
@@ -30141,7 +30671,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="80" spans="1:14">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A80" s="7" t="s">
         <v>1254</v>
       </c>
@@ -30185,7 +30715,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="81" spans="1:14">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A81" s="7" t="s">
         <v>1261</v>
       </c>
@@ -30229,7 +30759,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="82" spans="1:14">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A82" s="7" t="s">
         <v>1268</v>
       </c>
@@ -30273,7 +30803,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="83" spans="1:14">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A83" s="7" t="s">
         <v>1275</v>
       </c>
@@ -30317,7 +30847,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="84" spans="1:14">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A84" s="7" t="s">
         <v>1283</v>
       </c>
@@ -30361,7 +30891,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="85" spans="1:14">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A85" s="7" t="s">
         <v>1290</v>
       </c>
@@ -30405,7 +30935,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="86" spans="1:14">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A86" s="7" t="s">
         <v>1297</v>
       </c>
@@ -30449,7 +30979,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="87" spans="1:14">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A87" s="7" t="s">
         <v>1304</v>
       </c>
@@ -30493,7 +31023,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="88" spans="1:14">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A88" s="7" t="s">
         <v>1311</v>
       </c>
@@ -30537,7 +31067,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="89" spans="1:14">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A89" s="7" t="s">
         <v>1318</v>
       </c>
@@ -30581,7 +31111,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="90" spans="1:14">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A90" s="7" t="s">
         <v>1325</v>
       </c>
@@ -30625,7 +31155,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="91" spans="1:14">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A91" s="7" t="s">
         <v>1332</v>
       </c>
@@ -30669,7 +31199,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="92" spans="1:14">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A92" s="7" t="s">
         <v>1339</v>
       </c>
@@ -30713,7 +31243,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="93" spans="1:14">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A93" s="7" t="s">
         <v>1346</v>
       </c>
@@ -30757,7 +31287,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="94" spans="1:14">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A94" s="7" t="s">
         <v>1353</v>
       </c>
@@ -30801,7 +31331,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="95" spans="1:14">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A95" s="7" t="s">
         <v>1360</v>
       </c>
@@ -30845,7 +31375,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="96" spans="1:14">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A96" s="7" t="s">
         <v>1367</v>
       </c>
@@ -30889,7 +31419,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="97" spans="1:14">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A97" s="7" t="s">
         <v>1374</v>
       </c>
@@ -30933,7 +31463,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="98" spans="1:14">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A98" s="7" t="s">
         <v>1381</v>
       </c>
@@ -30977,7 +31507,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="99" spans="1:14">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A99" s="7" t="s">
         <v>1388</v>
       </c>
@@ -31021,7 +31551,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="100" spans="1:14">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A100" s="7" t="s">
         <v>1395</v>
       </c>
@@ -31065,7 +31595,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="101" spans="1:14">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A101" s="7" t="s">
         <v>1402</v>
       </c>
@@ -31109,7 +31639,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="102" spans="1:14">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A102" s="7" t="s">
         <v>1408</v>
       </c>
@@ -31153,7 +31683,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="103" spans="1:14">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A103" s="7" t="s">
         <v>1414</v>
       </c>
@@ -31197,7 +31727,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="104" spans="1:14">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A104" s="7" t="s">
         <v>1420</v>
       </c>
@@ -31241,7 +31771,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="105" spans="1:14">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A105" s="7" t="s">
         <v>1426</v>
       </c>
@@ -31285,7 +31815,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="106" spans="1:14">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A106" s="7" t="s">
         <v>1432</v>
       </c>
@@ -31329,7 +31859,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="107" spans="1:14">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A107" s="7" t="s">
         <v>1438</v>
       </c>
@@ -31373,7 +31903,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="108" spans="1:14">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A108" s="7" t="s">
         <v>1444</v>
       </c>
@@ -31417,7 +31947,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="109" spans="1:14">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A109" s="7" t="s">
         <v>1450</v>
       </c>
@@ -31461,7 +31991,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="110" spans="1:14">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A110" s="7" t="s">
         <v>1456</v>
       </c>
@@ -31505,7 +32035,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="111" spans="1:14">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A111" s="7" t="s">
         <v>1462</v>
       </c>
@@ -31549,7 +32079,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="112" spans="1:14">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A112" s="7" t="s">
         <v>1467</v>
       </c>
@@ -31593,7 +32123,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="113" spans="1:14">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A113" s="7" t="s">
         <v>1473</v>
       </c>
@@ -31637,7 +32167,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="114" spans="1:14">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A114" s="7" t="s">
         <v>1480</v>
       </c>
@@ -31681,7 +32211,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="115" spans="1:14">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A115" s="7" t="s">
         <v>1486</v>
       </c>
@@ -31725,7 +32255,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="116" spans="1:14">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A116" s="7" t="s">
         <v>1492</v>
       </c>
@@ -31769,7 +32299,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="117" spans="1:14">
+    <row r="117" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A117" s="7" t="s">
         <v>1498</v>
       </c>
@@ -31813,7 +32343,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="118" spans="1:14">
+    <row r="118" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A118" s="7" t="s">
         <v>1505</v>
       </c>
@@ -31857,7 +32387,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="119" spans="1:14">
+    <row r="119" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A119" s="7" t="s">
         <v>1512</v>
       </c>
@@ -31901,7 +32431,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="120" spans="1:14">
+    <row r="120" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A120" s="16" t="s">
         <v>1520</v>
       </c>
@@ -31945,7 +32475,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="121" spans="1:14">
+    <row r="121" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A121" s="16" t="s">
         <v>1528</v>
       </c>
@@ -31989,7 +32519,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="122" spans="1:14">
+    <row r="122" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A122" s="16" t="s">
         <v>1535</v>
       </c>
@@ -32033,7 +32563,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="123" spans="1:14">
+    <row r="123" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A123" s="16" t="s">
         <v>1542</v>
       </c>
@@ -32077,7 +32607,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="124" spans="1:14">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A124" s="16" t="s">
         <v>1550</v>
       </c>
@@ -32121,7 +32651,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="125" spans="1:14">
+    <row r="125" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A125" s="16" t="s">
         <v>1557</v>
       </c>
@@ -32165,7 +32695,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="126" spans="1:14">
+    <row r="126" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A126" s="16" t="s">
         <v>1563</v>
       </c>
@@ -32209,7 +32739,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="127" spans="1:14">
+    <row r="127" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A127" s="16" t="s">
         <v>1571</v>
       </c>
@@ -32253,7 +32783,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="128" spans="1:14">
+    <row r="128" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A128" s="16" t="s">
         <v>1578</v>
       </c>
@@ -32297,7 +32827,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="129" spans="1:14">
+    <row r="129" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A129" s="16" t="s">
         <v>1586</v>
       </c>
@@ -32341,7 +32871,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="130" spans="1:14">
+    <row r="130" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A130" s="16" t="s">
         <v>1593</v>
       </c>
@@ -32385,7 +32915,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="131" spans="1:14">
+    <row r="131" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A131" s="16" t="s">
         <v>1601</v>
       </c>
@@ -32429,7 +32959,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="132" spans="1:14">
+    <row r="132" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A132" s="16" t="s">
         <v>1608</v>
       </c>
@@ -32473,7 +33003,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="133" spans="1:14">
+    <row r="133" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A133" s="16" t="s">
         <v>1615</v>
       </c>
@@ -32517,7 +33047,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="134" spans="1:14">
+    <row r="134" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A134" s="16" t="s">
         <v>1621</v>
       </c>
@@ -32561,7 +33091,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="135" spans="1:14">
+    <row r="135" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A135" s="16" t="s">
         <v>1628</v>
       </c>
@@ -32605,7 +33135,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="136" spans="1:14">
+    <row r="136" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A136" s="16" t="s">
         <v>1635</v>
       </c>
@@ -32649,7 +33179,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="137" spans="1:14">
+    <row r="137" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A137" s="16" t="s">
         <v>2921</v>
       </c>
@@ -32693,7 +33223,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="138" spans="1:14">
+    <row r="138" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A138" s="16" t="s">
         <v>2925</v>
       </c>
@@ -32737,7 +33267,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="139" spans="1:14">
+    <row r="139" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A139" s="16" t="s">
         <v>2930</v>
       </c>
@@ -32781,7 +33311,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="140" spans="1:14">
+    <row r="140" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A140" s="16" t="s">
         <v>2936</v>
       </c>
@@ -32825,7 +33355,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="141" spans="1:14">
+    <row r="141" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A141" s="16" t="s">
         <v>2943</v>
       </c>
@@ -32869,7 +33399,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="142" spans="1:14">
+    <row r="142" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A142" s="16" t="s">
         <v>2949</v>
       </c>
@@ -32913,7 +33443,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="143" spans="1:14">
+    <row r="143" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A143" s="16" t="s">
         <v>3102</v>
       </c>
@@ -32957,7 +33487,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="144" spans="1:14">
+    <row r="144" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A144" s="16" t="s">
         <v>3103</v>
       </c>
@@ -33001,7 +33531,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="145" spans="1:14">
+    <row r="145" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A145" s="16" t="s">
         <v>3104</v>
       </c>
@@ -33045,7 +33575,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="146" spans="1:14">
+    <row r="146" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A146" s="16" t="s">
         <v>3122</v>
       </c>
@@ -33089,7 +33619,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="147" spans="1:14">
+    <row r="147" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A147" s="16" t="s">
         <v>3128</v>
       </c>
@@ -33133,7 +33663,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="148" spans="1:14">
+    <row r="148" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A148" s="16" t="s">
         <v>3129</v>
       </c>
@@ -33177,7 +33707,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="149" spans="1:14">
+    <row r="149" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A149" s="16" t="s">
         <v>3130</v>
       </c>
@@ -33221,7 +33751,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="150" spans="1:14">
+    <row r="150" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A150" s="16" t="s">
         <v>3131</v>
       </c>
@@ -33265,7 +33795,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="151" spans="1:14">
+    <row r="151" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A151" s="16" t="s">
         <v>3228</v>
       </c>
@@ -33309,7 +33839,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="152" spans="1:14">
+    <row r="152" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A152" s="16" t="s">
         <v>3236</v>
       </c>
@@ -33353,7 +33883,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="153" spans="1:14">
+    <row r="153" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A153" s="16" t="s">
         <v>3237</v>
       </c>
@@ -33397,7 +33927,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="154" spans="1:14">
+    <row r="154" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A154" s="16" t="s">
         <v>3328</v>
       </c>
@@ -33441,7 +33971,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="155" spans="1:14">
+    <row r="155" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A155" s="16" t="s">
         <v>3329</v>
       </c>
@@ -33485,7 +34015,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="156" spans="1:14">
+    <row r="156" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A156" s="16" t="s">
         <v>3330</v>
       </c>
@@ -33529,7 +34059,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="157" spans="1:14">
+    <row r="157" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A157" s="16" t="s">
         <v>3393</v>
       </c>
@@ -33573,7 +34103,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="158" spans="1:14">
+    <row r="158" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A158" s="16" t="s">
         <v>3394</v>
       </c>
@@ -33617,7 +34147,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="159" spans="1:14">
+    <row r="159" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A159" s="16" t="s">
         <v>3395</v>
       </c>
@@ -33661,7 +34191,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="160" spans="1:14">
+    <row r="160" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A160" s="16" t="s">
         <v>3442</v>
       </c>
@@ -33705,7 +34235,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="161" spans="1:14">
+    <row r="161" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A161" s="16" t="s">
         <v>3448</v>
       </c>
@@ -33749,7 +34279,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="162" spans="1:14">
+    <row r="162" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A162" s="16" t="s">
         <v>3502</v>
       </c>
@@ -33793,7 +34323,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="163" spans="1:14">
+    <row r="163" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A163" s="16" t="s">
         <v>3503</v>
       </c>
@@ -33837,7 +34367,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="164" spans="1:14">
+    <row r="164" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A164" s="16" t="s">
         <v>3504</v>
       </c>
@@ -33881,7 +34411,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="165" spans="1:14">
+    <row r="165" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A165" s="16" t="s">
         <v>3505</v>
       </c>
@@ -33925,7 +34455,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="166" spans="1:14">
+    <row r="166" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A166" s="16" t="s">
         <v>3543</v>
       </c>
@@ -33969,7 +34499,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="167" spans="1:14">
+    <row r="167" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A167" s="16" t="s">
         <v>3565</v>
       </c>
@@ -34013,7 +34543,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="168" spans="1:14">
+    <row r="168" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A168" s="16" t="s">
         <v>3566</v>
       </c>
@@ -34057,7 +34587,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="169" spans="1:14">
+    <row r="169" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A169" s="16" t="s">
         <v>3567</v>
       </c>
@@ -34101,7 +34631,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="170" spans="1:14">
+    <row r="170" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A170" s="16" t="s">
         <v>3568</v>
       </c>
@@ -34145,7 +34675,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="171" spans="1:14">
+    <row r="171" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A171" s="16" t="s">
         <v>3591</v>
       </c>
@@ -34189,7 +34719,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="172" spans="1:14">
+    <row r="172" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A172" s="16" t="s">
         <v>3592</v>
       </c>
@@ -34233,7 +34763,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="173" spans="1:14">
+    <row r="173" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A173" s="16" t="s">
         <v>3623</v>
       </c>
@@ -34277,7 +34807,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="174" spans="1:14">
+    <row r="174" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A174" s="16" t="s">
         <v>3624</v>
       </c>
@@ -34321,7 +34851,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="175" spans="1:14">
+    <row r="175" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A175" s="16" t="s">
         <v>3633</v>
       </c>
@@ -34365,7 +34895,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="176" spans="1:14">
+    <row r="176" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A176" s="16" t="s">
         <v>3634</v>
       </c>
@@ -34409,7 +34939,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="177" spans="1:14">
+    <row r="177" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A177" s="16" t="s">
         <v>3670</v>
       </c>
@@ -34450,6 +34980,138 @@
         <v>57</v>
       </c>
       <c r="N177" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="178" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A178" s="16" t="s">
+        <v>3753</v>
+      </c>
+      <c r="B178" s="16" t="s">
+        <v>3754</v>
+      </c>
+      <c r="C178" s="16" t="s">
+        <v>1178</v>
+      </c>
+      <c r="D178" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E178" s="36" t="s">
+        <v>3755</v>
+      </c>
+      <c r="F178" s="3" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G178" s="3" t="s">
+        <v>3756</v>
+      </c>
+      <c r="H178" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I178" s="27" t="s">
+        <v>3757</v>
+      </c>
+      <c r="J178" t="s">
+        <v>3758</v>
+      </c>
+      <c r="K178" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L178" s="17" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M178" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="N178" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="179" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A179" s="16" t="s">
+        <v>3780</v>
+      </c>
+      <c r="B179" s="41" t="s">
+        <v>3782</v>
+      </c>
+      <c r="C179" s="16" t="s">
+        <v>3783</v>
+      </c>
+      <c r="D179" s="20" t="s">
+        <v>240</v>
+      </c>
+      <c r="E179" s="41" t="s">
+        <v>3784</v>
+      </c>
+      <c r="F179" s="40" t="s">
+        <v>3311</v>
+      </c>
+      <c r="G179" s="40" t="s">
+        <v>3785</v>
+      </c>
+      <c r="H179" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I179" s="27" t="s">
+        <v>3786</v>
+      </c>
+      <c r="J179" s="2" t="s">
+        <v>3787</v>
+      </c>
+      <c r="K179" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L179" s="17" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M179" s="17" t="s">
+        <v>1646</v>
+      </c>
+      <c r="N179" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="180" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A180" s="16" t="s">
+        <v>3781</v>
+      </c>
+      <c r="B180" s="41" t="s">
+        <v>3788</v>
+      </c>
+      <c r="C180" s="16" t="s">
+        <v>3789</v>
+      </c>
+      <c r="D180" s="20" t="s">
+        <v>240</v>
+      </c>
+      <c r="E180" s="41" t="s">
+        <v>3790</v>
+      </c>
+      <c r="F180" s="40" t="s">
+        <v>2975</v>
+      </c>
+      <c r="G180" s="40" t="s">
+        <v>3791</v>
+      </c>
+      <c r="H180" s="41" t="s">
+        <v>21</v>
+      </c>
+      <c r="I180" s="27" t="s">
+        <v>3792</v>
+      </c>
+      <c r="J180" s="32" t="s">
+        <v>3793</v>
+      </c>
+      <c r="K180" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L180" s="17" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M180" s="17" t="s">
+        <v>1646</v>
+      </c>
+      <c r="N180" t="s">
         <v>25</v>
       </c>
     </row>
@@ -34601,21 +35263,26 @@
     <hyperlink ref="J176" r:id="rId143" xr:uid="{888F1817-76F7-4A94-A2F6-101494CA1688}"/>
     <hyperlink ref="I177" r:id="rId144" xr:uid="{D768CC27-0F4F-4814-BD5B-A0D920CDA8FB}"/>
     <hyperlink ref="J177" r:id="rId145" xr:uid="{18CDD4BD-07CE-40B1-A25E-51C6A46E6A26}"/>
+    <hyperlink ref="I178" r:id="rId146" xr:uid="{DA068430-3865-431C-B913-6E888ACA9570}"/>
+    <hyperlink ref="I179" r:id="rId147" xr:uid="{B4F8527A-A63F-4693-9D43-525080A46624}"/>
+    <hyperlink ref="J179" r:id="rId148" xr:uid="{59A00EB9-3C29-4E7E-9493-B5D23481D54F}"/>
+    <hyperlink ref="I180" r:id="rId149" xr:uid="{E7507415-6A06-429F-98FD-0C48D02CCF14}"/>
+    <hyperlink ref="J180" r:id="rId150" xr:uid="{940F6C26-625D-4CA2-BC87-6ED0B49D62C6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId146"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId151"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81F9848D-6D60-47C0-9F84-A561FE4F106E}">
   <dimension ref="A1:N5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="20.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -34659,7 +35326,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>28</v>
       </c>
@@ -34703,7 +35370,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1661</v>
       </c>
@@ -34747,7 +35414,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>2970</v>
       </c>
@@ -34791,7 +35458,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3155</v>
       </c>
@@ -34852,9 +35519,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01C6B0FD-D8A3-44EC-9532-03DDA232F922}">
   <dimension ref="A1:N4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -34898,7 +35565,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3411</v>
       </c>
@@ -34942,7 +35609,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3412</v>
       </c>
@@ -34986,7 +35653,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3704</v>
       </c>
@@ -35047,9 +35714,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D956EFE-E955-4E62-8478-2294E6413DC1}">
   <dimension ref="A1:N3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -35093,7 +35760,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2896</v>
       </c>
@@ -35137,7 +35804,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3493</v>
       </c>
@@ -35195,9 +35862,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{652841DA-3619-42EE-A536-61B58BE1B457}">
   <dimension ref="A1:N9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -35241,7 +35908,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
         <v>1832</v>
       </c>
@@ -35285,7 +35952,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
         <v>1843</v>
       </c>
@@ -35329,7 +35996,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>1853</v>
       </c>
@@ -35373,7 +36040,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
         <v>1864</v>
       </c>
@@ -35417,7 +36084,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
         <v>1872</v>
       </c>
@@ -35461,7 +36128,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
         <v>1882</v>
       </c>
@@ -35505,7 +36172,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="16" t="s">
         <v>1892</v>
       </c>
@@ -35549,7 +36216,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="16" t="s">
         <v>1901</v>
       </c>
@@ -35607,9 +36274,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FE2008B-4BF4-4C9A-883A-FEE5873AEAF4}">
   <dimension ref="A1:N14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="16" customHeight="1">
+    <row r="1" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
@@ -35653,7 +36320,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="16" customHeight="1">
+    <row r="2" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
         <v>1911</v>
       </c>
@@ -35697,7 +36364,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="16" customHeight="1">
+    <row r="3" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
         <v>1920</v>
       </c>
@@ -35741,7 +36408,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="16" customHeight="1">
+    <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>1928</v>
       </c>
@@ -35785,7 +36452,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="16" customHeight="1">
+    <row r="5" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
         <v>1936</v>
       </c>
@@ -35829,7 +36496,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="16" customHeight="1">
+    <row r="6" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
         <v>1944</v>
       </c>
@@ -35873,7 +36540,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="16" customHeight="1">
+    <row r="7" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
         <v>1952</v>
       </c>
@@ -35917,7 +36584,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="16" customHeight="1">
+    <row r="8" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
         <v>1961</v>
       </c>
@@ -35961,7 +36628,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="16" customHeight="1">
+    <row r="9" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
         <v>1969</v>
       </c>
@@ -36005,7 +36672,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="16" customHeight="1">
+    <row r="10" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="16" t="s">
         <v>1977</v>
       </c>
@@ -36049,7 +36716,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="16" customHeight="1">
+    <row r="11" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="16" t="s">
         <v>1986</v>
       </c>
@@ -36093,7 +36760,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="16" customHeight="1">
+    <row r="12" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="16" t="s">
         <v>1995</v>
       </c>
@@ -36137,7 +36804,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="16" t="s">
         <v>2994</v>
       </c>
@@ -36181,7 +36848,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="16" t="s">
         <v>3693</v>
       </c>

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{483B9C45-A4C5-46C1-B133-402A95888440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C3BCFAE-D526-4DC3-84A5-BB09569D115B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10710" yWindow="0" windowWidth="10980" windowHeight="13770" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10710" yWindow="0" windowWidth="10980" windowHeight="13770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7621" uniqueCount="3794">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7676" uniqueCount="3819">
   <si>
     <t>ID</t>
   </si>
@@ -11430,6 +11430,81 @@
   </si>
   <si>
     <t>https://www.mouser.es/ProductDetail/Susumu/RG2012N-511-W-T1?qs=juJhw1yPxAFbuvw1oDA4sg%3D%3D</t>
+  </si>
+  <si>
+    <t>010-0180</t>
+  </si>
+  <si>
+    <t>Resistores de película fina - SMD 1/10W 32K Ohms 0.1%</t>
+  </si>
+  <si>
+    <t>32kΩ 100mW ±0.1%</t>
+  </si>
+  <si>
+    <t>RT0603BRD0732KL</t>
+  </si>
+  <si>
+    <t>603-RT0603BRD0732KL</t>
+  </si>
+  <si>
+    <t>010-0181</t>
+  </si>
+  <si>
+    <t>8.25kΩ 210mW ±0.1%</t>
+  </si>
+  <si>
+    <t>Resistores de película fina - SMD MCT 0603-25 0.1% AT P5 8K25</t>
+  </si>
+  <si>
+    <t>MCT0603MD8251BP500</t>
+  </si>
+  <si>
+    <t>594-MCT0603MD8251BP5</t>
+  </si>
+  <si>
+    <t>https://www.vishay.com/docs/28952/mcr0201at-mca1206at.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Vishay-Beyschlag/MCT0603MD8251BP500?qs=sGAEpiMZZMtlubZbdhIBIGdRHMDLYLBRFQ8bTeYTl3o%3D</t>
+  </si>
+  <si>
+    <t>010-0182</t>
+  </si>
+  <si>
+    <t>Resistores de película fina - SMD MCT 0603-25 0.5% P5 8K2</t>
+  </si>
+  <si>
+    <t>8.2kΩ 100mW ±0.1%</t>
+  </si>
+  <si>
+    <t>MCT06030D8201DP500</t>
+  </si>
+  <si>
+    <t>594-MCT06030D8201DP5</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Vishay-Beyschlag/MCT06030D8201DP500?qs=sGAEpiMZZMtlubZbdhIBIHIEm3drdiPafgRM58oNK1g%3D</t>
+  </si>
+  <si>
+    <t>001-0127</t>
+  </si>
+  <si>
+    <t>Condensadores de cerámica multicapa (MLCC- SMD/SMT) WCAP-CSGP 1000pF 0603 5% 50V MLCC</t>
+  </si>
+  <si>
+    <t>50V 1nF NP0</t>
+  </si>
+  <si>
+    <t>885012006063</t>
+  </si>
+  <si>
+    <t>710-885012006063</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/885012006063.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/885012006063?qs=0KOYDY2FL29yUmMQmcJrdA%3D%3D</t>
   </si>
 </sst>
 </file>
@@ -11439,7 +11514,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -11614,7 +11689,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -11679,6 +11754,8 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -11963,7 +12040,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N128"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="11.1796875" customWidth="1"/>
     <col min="2" max="2" width="29.6328125" customWidth="1"/>
@@ -11981,7 +12058,7 @@
     <col min="14" max="14" width="17.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" ht="13.5" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -12025,7 +12102,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" ht="14" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>58</v>
       </c>
@@ -12069,7 +12146,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" ht="14" customHeight="1">
       <c r="A3" s="4" t="s">
         <v>73</v>
       </c>
@@ -12113,7 +12190,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" ht="14" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>81</v>
       </c>
@@ -12157,7 +12234,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" ht="14" customHeight="1">
       <c r="A5" s="4" t="s">
         <v>88</v>
       </c>
@@ -12201,7 +12278,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" ht="14" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>95</v>
       </c>
@@ -12245,7 +12322,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" ht="14" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>103</v>
       </c>
@@ -12289,7 +12366,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" ht="14" customHeight="1">
       <c r="A8" s="4" t="s">
         <v>110</v>
       </c>
@@ -12333,7 +12410,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" ht="14" customHeight="1">
       <c r="A9" s="4" t="s">
         <v>117</v>
       </c>
@@ -12377,7 +12454,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" ht="14" customHeight="1">
       <c r="A10" s="4" t="s">
         <v>124</v>
       </c>
@@ -12421,7 +12498,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" ht="14" customHeight="1">
       <c r="A11" s="4" t="s">
         <v>131</v>
       </c>
@@ -12465,7 +12542,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" ht="14" customHeight="1">
       <c r="A12" s="4" t="s">
         <v>138</v>
       </c>
@@ -12509,7 +12586,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" ht="14" customHeight="1">
       <c r="A13" s="4" t="s">
         <v>145</v>
       </c>
@@ -12553,7 +12630,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" ht="14" customHeight="1">
       <c r="A14" s="4" t="s">
         <v>153</v>
       </c>
@@ -12597,7 +12674,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" ht="14" customHeight="1">
       <c r="A15" s="4" t="s">
         <v>160</v>
       </c>
@@ -12641,7 +12718,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" ht="14" customHeight="1">
       <c r="A16" s="4" t="s">
         <v>167</v>
       </c>
@@ -12685,7 +12762,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:14" ht="14" customHeight="1">
       <c r="A17" s="4" t="s">
         <v>174</v>
       </c>
@@ -12729,7 +12806,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:14" ht="14" customHeight="1">
       <c r="A18" s="4" t="s">
         <v>180</v>
       </c>
@@ -12773,7 +12850,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:14" ht="14" customHeight="1">
       <c r="A19" s="4" t="s">
         <v>187</v>
       </c>
@@ -12817,7 +12894,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:14" ht="14" customHeight="1">
       <c r="A20" s="4" t="s">
         <v>194</v>
       </c>
@@ -12861,7 +12938,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:14" ht="14" customHeight="1">
       <c r="A21" s="4" t="s">
         <v>201</v>
       </c>
@@ -12905,7 +12982,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:14" ht="14" customHeight="1">
       <c r="A22" s="4" t="s">
         <v>208</v>
       </c>
@@ -12949,7 +13026,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:14" ht="14" customHeight="1">
       <c r="A23" s="4" t="s">
         <v>216</v>
       </c>
@@ -12993,7 +13070,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:14" ht="14" customHeight="1">
       <c r="A24" s="4" t="s">
         <v>223</v>
       </c>
@@ -13037,7 +13114,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:14" ht="14" customHeight="1">
       <c r="A25" s="4" t="s">
         <v>230</v>
       </c>
@@ -13081,7 +13158,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:14" ht="14" customHeight="1">
       <c r="A26" s="4" t="s">
         <v>237</v>
       </c>
@@ -13125,7 +13202,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:14" ht="14" customHeight="1">
       <c r="A27" s="4" t="s">
         <v>246</v>
       </c>
@@ -13169,7 +13246,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:14" ht="14" customHeight="1">
       <c r="A28" s="4" t="s">
         <v>254</v>
       </c>
@@ -13213,7 +13290,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:14" ht="14" customHeight="1">
       <c r="A29" s="4" t="s">
         <v>261</v>
       </c>
@@ -13257,7 +13334,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:14" ht="14" customHeight="1">
       <c r="A30" s="4" t="s">
         <v>268</v>
       </c>
@@ -13301,7 +13378,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:14" ht="14" customHeight="1">
       <c r="A31" s="4" t="s">
         <v>275</v>
       </c>
@@ -13345,7 +13422,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:14" ht="14" customHeight="1">
       <c r="A32" s="4" t="s">
         <v>282</v>
       </c>
@@ -13389,7 +13466,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:14" ht="14" customHeight="1">
       <c r="A33" s="4" t="s">
         <v>288</v>
       </c>
@@ -13433,7 +13510,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:14" ht="14" customHeight="1">
       <c r="A34" s="4" t="s">
         <v>295</v>
       </c>
@@ -13477,7 +13554,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:14" ht="14" customHeight="1">
       <c r="A35" s="4" t="s">
         <v>302</v>
       </c>
@@ -13521,7 +13598,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:14" ht="14" customHeight="1">
       <c r="A36" s="4" t="s">
         <v>308</v>
       </c>
@@ -13565,7 +13642,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:14" ht="14" customHeight="1">
       <c r="A37" s="4" t="s">
         <v>315</v>
       </c>
@@ -13609,7 +13686,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:14" ht="14" customHeight="1">
       <c r="A38" s="4" t="s">
         <v>322</v>
       </c>
@@ -13653,7 +13730,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:14" ht="14" customHeight="1">
       <c r="A39" s="4" t="s">
         <v>329</v>
       </c>
@@ -13697,7 +13774,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="40" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:14" ht="14" customHeight="1">
       <c r="A40" s="4" t="s">
         <v>336</v>
       </c>
@@ -13741,7 +13818,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="41" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:14" ht="14" customHeight="1">
       <c r="A41" s="4" t="s">
         <v>343</v>
       </c>
@@ -13785,7 +13862,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="42" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:14" ht="14" customHeight="1">
       <c r="A42" s="4" t="s">
         <v>350</v>
       </c>
@@ -13829,7 +13906,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="43" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:14" ht="14" customHeight="1">
       <c r="A43" s="4" t="s">
         <v>357</v>
       </c>
@@ -13873,7 +13950,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="44" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:14" ht="14" customHeight="1">
       <c r="A44" s="4" t="s">
         <v>364</v>
       </c>
@@ -13917,7 +13994,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="45" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:14" ht="14" customHeight="1">
       <c r="A45" s="4" t="s">
         <v>371</v>
       </c>
@@ -13961,7 +14038,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:14" ht="14" customHeight="1">
       <c r="A46" s="4" t="s">
         <v>378</v>
       </c>
@@ -14005,7 +14082,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="47" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:14" ht="14" customHeight="1">
       <c r="A47" s="4" t="s">
         <v>384</v>
       </c>
@@ -14049,7 +14126,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="48" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:14" ht="14" customHeight="1">
       <c r="A48" s="4" t="s">
         <v>391</v>
       </c>
@@ -14093,7 +14170,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="49" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:14" ht="14" customHeight="1">
       <c r="A49" s="4" t="s">
         <v>398</v>
       </c>
@@ -14137,7 +14214,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="50" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:14" ht="14" customHeight="1">
       <c r="A50" s="4" t="s">
         <v>405</v>
       </c>
@@ -14181,7 +14258,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="51" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:14" ht="14" customHeight="1">
       <c r="A51" s="4" t="s">
         <v>413</v>
       </c>
@@ -14225,7 +14302,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="52" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:14" ht="14" customHeight="1">
       <c r="A52" s="4" t="s">
         <v>420</v>
       </c>
@@ -14269,7 +14346,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="53" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:14" ht="14" customHeight="1">
       <c r="A53" s="4" t="s">
         <v>427</v>
       </c>
@@ -14313,7 +14390,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="54" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:14" ht="14" customHeight="1">
       <c r="A54" s="4" t="s">
         <v>434</v>
       </c>
@@ -14357,7 +14434,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="55" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:14" ht="14" customHeight="1">
       <c r="A55" s="4" t="s">
         <v>441</v>
       </c>
@@ -14401,7 +14478,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="56" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:14" ht="14" customHeight="1">
       <c r="A56" s="4" t="s">
         <v>448</v>
       </c>
@@ -14445,7 +14522,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="57" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:14" ht="14" customHeight="1">
       <c r="A57" s="4" t="s">
         <v>455</v>
       </c>
@@ -14487,7 +14564,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="58" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:14" ht="14" customHeight="1">
       <c r="A58" s="4" t="s">
         <v>461</v>
       </c>
@@ -14531,7 +14608,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="59" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:14" ht="14" customHeight="1">
       <c r="A59" s="4" t="s">
         <v>467</v>
       </c>
@@ -14575,7 +14652,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:14" ht="14" customHeight="1">
       <c r="A60" s="4" t="s">
         <v>474</v>
       </c>
@@ -14619,7 +14696,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="61" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:14" ht="14" customHeight="1">
       <c r="A61" s="4" t="s">
         <v>482</v>
       </c>
@@ -14663,7 +14740,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="62" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:14" ht="14" customHeight="1">
       <c r="A62" s="4" t="s">
         <v>490</v>
       </c>
@@ -14707,7 +14784,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="63" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:14" ht="14" customHeight="1">
       <c r="A63" s="4" t="s">
         <v>497</v>
       </c>
@@ -14751,7 +14828,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="64" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:14" ht="14" customHeight="1">
       <c r="A64" s="4" t="s">
         <v>504</v>
       </c>
@@ -14795,7 +14872,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="65" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:14" ht="14" customHeight="1">
       <c r="A65" s="4" t="s">
         <v>511</v>
       </c>
@@ -14839,7 +14916,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="66" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:14" ht="14" customHeight="1">
       <c r="A66" s="4" t="s">
         <v>517</v>
       </c>
@@ -14883,7 +14960,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="67" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:14" ht="14" customHeight="1">
       <c r="A67" s="4" t="s">
         <v>525</v>
       </c>
@@ -14927,7 +15004,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="68" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:14" ht="14" customHeight="1">
       <c r="A68" s="4" t="s">
         <v>531</v>
       </c>
@@ -14971,7 +15048,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="69" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:14" ht="14" customHeight="1">
       <c r="A69" s="4" t="s">
         <v>538</v>
       </c>
@@ -15015,7 +15092,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="70" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:14" ht="14" customHeight="1">
       <c r="A70" s="4" t="s">
         <v>545</v>
       </c>
@@ -15059,7 +15136,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="71" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:14" ht="14" customHeight="1">
       <c r="A71" s="4" t="s">
         <v>552</v>
       </c>
@@ -15103,7 +15180,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="72" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:14" ht="14" customHeight="1">
       <c r="A72" s="4" t="s">
         <v>560</v>
       </c>
@@ -15147,7 +15224,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="73" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:14" ht="14" customHeight="1">
       <c r="A73" s="4" t="s">
         <v>567</v>
       </c>
@@ -15191,7 +15268,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="74" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:14" ht="14" customHeight="1">
       <c r="A74" s="4" t="s">
         <v>574</v>
       </c>
@@ -15235,7 +15312,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="75" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:14" ht="14" customHeight="1">
       <c r="A75" s="4" t="s">
         <v>582</v>
       </c>
@@ -15279,7 +15356,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="76" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:14" ht="14" customHeight="1">
       <c r="A76" s="4" t="s">
         <v>589</v>
       </c>
@@ -15323,7 +15400,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="77" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:14" ht="14" customHeight="1">
       <c r="A77" s="4" t="s">
         <v>595</v>
       </c>
@@ -15367,7 +15444,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="78" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:14" ht="14" customHeight="1">
       <c r="A78" s="4" t="s">
         <v>602</v>
       </c>
@@ -15411,7 +15488,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="79" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:14" ht="14" customHeight="1">
       <c r="A79" s="4" t="s">
         <v>608</v>
       </c>
@@ -15455,7 +15532,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="80" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:14" ht="14" customHeight="1">
       <c r="A80" s="4" t="s">
         <v>615</v>
       </c>
@@ -15499,7 +15576,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="81" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:14" ht="14" customHeight="1">
       <c r="A81" s="4" t="s">
         <v>622</v>
       </c>
@@ -15543,7 +15620,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="82" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:14" ht="14" customHeight="1">
       <c r="A82" s="4" t="s">
         <v>628</v>
       </c>
@@ -15587,7 +15664,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="83" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:14" ht="14" customHeight="1">
       <c r="A83" s="4" t="s">
         <v>635</v>
       </c>
@@ -15631,7 +15708,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="84" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:14" ht="14" customHeight="1">
       <c r="A84" s="4" t="s">
         <v>642</v>
       </c>
@@ -15675,7 +15752,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="85" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:14" ht="14" customHeight="1">
       <c r="A85" s="4" t="s">
         <v>643</v>
       </c>
@@ -15719,7 +15796,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="86" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:14" ht="14" customHeight="1">
       <c r="A86" s="4" t="s">
         <v>650</v>
       </c>
@@ -15763,7 +15840,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="87" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:14" ht="14" customHeight="1">
       <c r="A87" s="4" t="s">
         <v>656</v>
       </c>
@@ -15807,7 +15884,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="88" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:14" ht="14" customHeight="1">
       <c r="A88" s="4" t="s">
         <v>663</v>
       </c>
@@ -15851,7 +15928,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="89" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:14" ht="14" customHeight="1">
       <c r="A89" s="4" t="s">
         <v>670</v>
       </c>
@@ -15895,7 +15972,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="90" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:14" ht="14" customHeight="1">
       <c r="A90" s="4" t="s">
         <v>677</v>
       </c>
@@ -15939,7 +16016,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="91" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:14" ht="14" customHeight="1">
       <c r="A91" s="4" t="s">
         <v>684</v>
       </c>
@@ -15983,7 +16060,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="92" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:14" ht="14" customHeight="1">
       <c r="A92" s="4" t="s">
         <v>691</v>
       </c>
@@ -16027,7 +16104,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:14">
       <c r="A93" s="4" t="s">
         <v>2980</v>
       </c>
@@ -16071,7 +16148,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:14">
       <c r="A94" s="4" t="s">
         <v>2986</v>
       </c>
@@ -16115,7 +16192,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:14">
       <c r="A95" s="4" t="s">
         <v>3000</v>
       </c>
@@ -16159,7 +16236,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:14">
       <c r="A96" s="4" t="s">
         <v>3001</v>
       </c>
@@ -16203,7 +16280,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:14">
       <c r="A97" s="4" t="s">
         <v>3002</v>
       </c>
@@ -16247,7 +16324,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:14">
       <c r="A98" s="4" t="s">
         <v>3050</v>
       </c>
@@ -16291,7 +16368,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:14">
       <c r="A99" s="4" t="s">
         <v>3056</v>
       </c>
@@ -16335,7 +16412,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:14">
       <c r="A100" s="4" t="s">
         <v>3057</v>
       </c>
@@ -16379,7 +16456,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:14">
       <c r="A101" s="4" t="s">
         <v>3058</v>
       </c>
@@ -16423,7 +16500,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:14">
       <c r="A102" s="4" t="s">
         <v>3059</v>
       </c>
@@ -16467,7 +16544,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:14">
       <c r="A103" s="4" t="s">
         <v>3075</v>
       </c>
@@ -16511,7 +16588,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:14">
       <c r="A104" s="4" t="s">
         <v>3091</v>
       </c>
@@ -16555,7 +16632,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:14">
       <c r="A105" s="4" t="s">
         <v>3096</v>
       </c>
@@ -16599,7 +16676,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:14">
       <c r="A106" s="4" t="s">
         <v>3219</v>
       </c>
@@ -16643,7 +16720,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:14">
       <c r="A107" s="4" t="s">
         <v>3260</v>
       </c>
@@ -16687,7 +16764,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:14">
       <c r="A108" s="4" t="s">
         <v>3325</v>
       </c>
@@ -16731,7 +16808,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:14">
       <c r="A109" s="4" t="s">
         <v>3326</v>
       </c>
@@ -16775,7 +16852,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:14">
       <c r="A110" s="4" t="s">
         <v>3327</v>
       </c>
@@ -16819,7 +16896,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:14">
       <c r="A111" s="4" t="s">
         <v>3367</v>
       </c>
@@ -16863,7 +16940,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:14">
       <c r="A112" s="4" t="s">
         <v>3368</v>
       </c>
@@ -16907,7 +16984,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:14">
       <c r="A113" s="4" t="s">
         <v>3369</v>
       </c>
@@ -16951,7 +17028,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:14">
       <c r="A114" s="4" t="s">
         <v>3370</v>
       </c>
@@ -16995,7 +17072,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:14">
       <c r="A115" s="4" t="s">
         <v>3461</v>
       </c>
@@ -17039,7 +17116,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:14">
       <c r="A116" s="4" t="s">
         <v>3462</v>
       </c>
@@ -17083,7 +17160,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:14">
       <c r="A117" s="4" t="s">
         <v>3468</v>
       </c>
@@ -17127,7 +17204,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:14">
       <c r="A118" s="4" t="s">
         <v>3482</v>
       </c>
@@ -17171,7 +17248,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:14">
       <c r="A119" s="4" t="s">
         <v>3483</v>
       </c>
@@ -17215,7 +17292,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:14">
       <c r="A120" s="4" t="s">
         <v>3529</v>
       </c>
@@ -17259,7 +17336,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:14">
       <c r="A121" s="4" t="s">
         <v>3530</v>
       </c>
@@ -17303,7 +17380,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:14">
       <c r="A122" s="4" t="s">
         <v>3584</v>
       </c>
@@ -17347,7 +17424,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:14">
       <c r="A123" s="39" t="s">
         <v>3655</v>
       </c>
@@ -17391,7 +17468,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:14">
       <c r="A124" s="39" t="s">
         <v>3698</v>
       </c>
@@ -17435,7 +17512,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:14">
       <c r="A125" s="39" t="s">
         <v>3720</v>
       </c>
@@ -17479,7 +17556,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:14">
       <c r="A126" s="39" t="s">
         <v>3739</v>
       </c>
@@ -17523,7 +17600,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:14">
       <c r="A127" s="39" t="s">
         <v>3740</v>
       </c>
@@ -17567,8 +17644,49 @@
         <v>25</v>
       </c>
     </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A128" s="39"/>
+    <row r="128" spans="1:14">
+      <c r="A128" s="39" t="s">
+        <v>3812</v>
+      </c>
+      <c r="B128" s="41" t="s">
+        <v>3813</v>
+      </c>
+      <c r="C128" s="16" t="s">
+        <v>3814</v>
+      </c>
+      <c r="D128" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="E128" s="36" t="s">
+        <v>3815</v>
+      </c>
+      <c r="F128" s="3" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G128" s="43" t="s">
+        <v>3816</v>
+      </c>
+      <c r="H128" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I128" s="27" t="s">
+        <v>3817</v>
+      </c>
+      <c r="J128" s="2" t="s">
+        <v>3818</v>
+      </c>
+      <c r="K128" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="L128" t="s">
+        <v>61</v>
+      </c>
+      <c r="M128" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N128" t="s">
+        <v>25</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="16" type="noConversion"/>
@@ -17684,21 +17802,23 @@
     <hyperlink ref="I127" r:id="rId109" xr:uid="{8B613FFC-245E-4018-8618-7ADD2AFEA0F4}"/>
     <hyperlink ref="J127" r:id="rId110" xr:uid="{A4DE3241-74D8-49E9-8179-47E56B1F9994}"/>
     <hyperlink ref="J126" r:id="rId111" xr:uid="{348E15E9-2492-4FC3-9ADB-2287FB61453A}"/>
+    <hyperlink ref="I128" r:id="rId112" xr:uid="{7E9F6B16-E367-4F43-A463-251B6118FB6C}"/>
+    <hyperlink ref="J128" r:id="rId113" xr:uid="{6D13DE09-35E1-44E8-A161-CF565B19ADED}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId112"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId114"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79E65951-BFD2-4888-A0A6-19D5130CB4A6}">
   <dimension ref="A1:N24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="41.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14">
       <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
@@ -17742,7 +17862,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>2003</v>
       </c>
@@ -17783,7 +17903,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>2012</v>
       </c>
@@ -17827,7 +17947,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
         <v>2020</v>
       </c>
@@ -17871,7 +17991,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
         <v>2028</v>
       </c>
@@ -17915,7 +18035,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
         <v>2035</v>
       </c>
@@ -17959,7 +18079,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
         <v>2045</v>
       </c>
@@ -18003,7 +18123,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
         <v>2053</v>
       </c>
@@ -18047,7 +18167,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
         <v>2061</v>
       </c>
@@ -18091,7 +18211,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
         <v>2068</v>
       </c>
@@ -18135,7 +18255,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
         <v>2075</v>
       </c>
@@ -18179,7 +18299,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
         <v>2082</v>
       </c>
@@ -18223,7 +18343,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
         <v>2089</v>
       </c>
@@ -18267,7 +18387,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
         <v>2097</v>
       </c>
@@ -18311,7 +18431,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14">
       <c r="A15" t="s">
         <v>2106</v>
       </c>
@@ -18355,7 +18475,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14">
       <c r="A16" t="s">
         <v>2112</v>
       </c>
@@ -18399,7 +18519,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:14">
       <c r="A17" t="s">
         <v>2118</v>
       </c>
@@ -18443,7 +18563,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:14">
       <c r="A18" t="s">
         <v>2126</v>
       </c>
@@ -18487,7 +18607,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:14">
       <c r="A19" t="s">
         <v>2133</v>
       </c>
@@ -18531,7 +18651,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:14">
       <c r="A20" t="s">
         <v>2140</v>
       </c>
@@ -18575,7 +18695,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:14">
       <c r="A21" t="s">
         <v>2148</v>
       </c>
@@ -18619,7 +18739,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:14">
       <c r="A22" t="s">
         <v>2155</v>
       </c>
@@ -18663,7 +18783,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:14">
       <c r="A23" t="s">
         <v>2162</v>
       </c>
@@ -18707,7 +18827,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:14">
       <c r="A24" t="s">
         <v>3759</v>
       </c>
@@ -18764,9 +18884,9 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89BFA1EF-29B2-41E4-A9D1-F8E90A663FA1}">
   <dimension ref="A1:N24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" ht="14.5" customHeight="1">
       <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
@@ -18810,7 +18930,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14">
       <c r="A2" s="7" t="s">
         <v>2766</v>
       </c>
@@ -18854,7 +18974,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14">
       <c r="A3" s="7" t="s">
         <v>2776</v>
       </c>
@@ -18898,7 +19018,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14">
       <c r="A4" s="7" t="s">
         <v>2784</v>
       </c>
@@ -18942,7 +19062,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14">
       <c r="A5" s="7" t="s">
         <v>2791</v>
       </c>
@@ -18986,7 +19106,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14">
       <c r="A6" s="7" t="s">
         <v>2799</v>
       </c>
@@ -19030,7 +19150,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14">
       <c r="A7" s="7" t="s">
         <v>2806</v>
       </c>
@@ -19074,7 +19194,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14">
       <c r="A8" s="7" t="s">
         <v>2817</v>
       </c>
@@ -19118,7 +19238,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" ht="14.5" customHeight="1">
       <c r="A9" s="7" t="s">
         <v>2827</v>
       </c>
@@ -19162,7 +19282,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14">
       <c r="A10" s="7" t="s">
         <v>2836</v>
       </c>
@@ -19206,7 +19326,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14">
       <c r="A11" s="7" t="s">
         <v>2844</v>
       </c>
@@ -19250,7 +19370,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14">
       <c r="A12" s="7" t="s">
         <v>2852</v>
       </c>
@@ -19294,7 +19414,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" ht="13.5" customHeight="1">
       <c r="A13" s="7" t="s">
         <v>2860</v>
       </c>
@@ -19338,7 +19458,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" ht="15" customHeight="1">
       <c r="A14" s="7" t="s">
         <v>2870</v>
       </c>
@@ -19382,7 +19502,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14">
       <c r="A15" s="7" t="s">
         <v>2960</v>
       </c>
@@ -19426,7 +19546,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14">
       <c r="A16" s="7" t="s">
         <v>2961</v>
       </c>
@@ -19470,7 +19590,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:14">
       <c r="A17" s="7" t="s">
         <v>2962</v>
       </c>
@@ -19514,7 +19634,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:14">
       <c r="A18" s="7" t="s">
         <v>2963</v>
       </c>
@@ -19558,7 +19678,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:14">
       <c r="A19" s="7" t="s">
         <v>2964</v>
       </c>
@@ -19602,7 +19722,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:14">
       <c r="A20" s="7" t="s">
         <v>2965</v>
       </c>
@@ -19646,7 +19766,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:14">
       <c r="A21" s="7" t="s">
         <v>2966</v>
       </c>
@@ -19690,7 +19810,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:14">
       <c r="A22" s="7" t="s">
         <v>2967</v>
       </c>
@@ -19734,7 +19854,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:14">
       <c r="A23" s="7" t="s">
         <v>2968</v>
       </c>
@@ -19778,7 +19898,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:14">
       <c r="A24" s="7" t="s">
         <v>2969</v>
       </c>
@@ -19849,13 +19969,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B6F0D32-9CE2-4DF7-927E-42E7BA331F12}">
   <dimension ref="A1:O22"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="13" max="13" width="13.36328125" customWidth="1"/>
     <col min="14" max="14" width="16.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -19899,7 +20019,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -19943,7 +20063,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15">
       <c r="A3" t="s">
         <v>1813</v>
       </c>
@@ -19988,7 +20108,7 @@
       </c>
       <c r="O3" s="7"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15">
       <c r="A4" t="s">
         <v>1814</v>
       </c>
@@ -20033,7 +20153,7 @@
       </c>
       <c r="O4" s="7"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15">
       <c r="A5" t="s">
         <v>1815</v>
       </c>
@@ -20078,7 +20198,7 @@
       </c>
       <c r="O5" s="3"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15">
       <c r="A6" t="s">
         <v>1816</v>
       </c>
@@ -20123,7 +20243,7 @@
       </c>
       <c r="O6" s="3"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15">
       <c r="A7" t="s">
         <v>1817</v>
       </c>
@@ -20168,7 +20288,7 @@
       </c>
       <c r="O7" s="3"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15">
       <c r="A8" t="s">
         <v>1818</v>
       </c>
@@ -20213,7 +20333,7 @@
       </c>
       <c r="O8" s="3"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15">
       <c r="A9" t="s">
         <v>1819</v>
       </c>
@@ -20258,7 +20378,7 @@
       </c>
       <c r="O9" s="3"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15">
       <c r="A10" t="s">
         <v>1820</v>
       </c>
@@ -20303,7 +20423,7 @@
       </c>
       <c r="O10" s="3"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15">
       <c r="A11" t="s">
         <v>1821</v>
       </c>
@@ -20348,7 +20468,7 @@
       </c>
       <c r="O11" s="3"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15">
       <c r="A12" t="s">
         <v>1822</v>
       </c>
@@ -20393,7 +20513,7 @@
       </c>
       <c r="O12" s="3"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15">
       <c r="A13" t="s">
         <v>1823</v>
       </c>
@@ -20438,7 +20558,7 @@
       </c>
       <c r="O13" s="3"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15">
       <c r="A14" t="s">
         <v>1824</v>
       </c>
@@ -20483,7 +20603,7 @@
       </c>
       <c r="O14" s="3"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15">
       <c r="A15" t="s">
         <v>1825</v>
       </c>
@@ -20527,7 +20647,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15">
       <c r="A16" t="s">
         <v>1826</v>
       </c>
@@ -20571,7 +20691,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:14">
       <c r="A17" t="s">
         <v>1827</v>
       </c>
@@ -20615,7 +20735,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:14">
       <c r="A18" t="s">
         <v>1828</v>
       </c>
@@ -20659,7 +20779,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:14">
       <c r="A19" t="s">
         <v>1829</v>
       </c>
@@ -20703,7 +20823,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:14">
       <c r="A20" t="s">
         <v>1830</v>
       </c>
@@ -20747,7 +20867,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:14">
       <c r="A21" t="s">
         <v>1831</v>
       </c>
@@ -20791,7 +20911,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:14">
       <c r="A22" t="s">
         <v>3713</v>
       </c>
@@ -20864,9 +20984,9 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA7E41C9-E62B-4149-A5B5-E7986E8877E6}">
   <dimension ref="A1:N2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -20910,7 +21030,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>3646</v>
       </c>
@@ -20966,9 +21086,9 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FAFF3B6-AF11-4BFB-8078-829FF6F2F366}">
   <dimension ref="A1:N2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14">
       <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
@@ -21012,7 +21132,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>3172</v>
       </c>
@@ -21068,9 +21188,9 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E5535EA-E186-4751-BC7F-9B3A0221302E}">
   <dimension ref="A1:N3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14">
       <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
@@ -21114,7 +21234,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>3030</v>
       </c>
@@ -21158,7 +21278,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>3039</v>
       </c>
@@ -21217,7 +21337,7 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C98E1A12-072F-4773-8CB5-47FFE077E85B}">
   <dimension ref="A1:N9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="43.7265625" customWidth="1"/>
     <col min="5" max="5" width="16.1796875" customWidth="1"/>
@@ -21230,7 +21350,7 @@
     <col min="14" max="14" width="21.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -21274,7 +21394,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -21318,7 +21438,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>42</v>
       </c>
@@ -21362,7 +21482,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
         <v>1649</v>
       </c>
@@ -21406,7 +21526,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
         <v>1655</v>
       </c>
@@ -21450,7 +21570,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
         <v>3605</v>
       </c>
@@ -21494,7 +21614,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
         <v>3625</v>
       </c>
@@ -21538,7 +21658,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
         <v>3766</v>
       </c>
@@ -21582,7 +21702,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14">
       <c r="L9" s="21"/>
     </row>
   </sheetData>
@@ -21605,9 +21725,9 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{316C64E0-14FB-467C-956A-E132FAFB0232}">
   <dimension ref="A1:N1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -21659,9 +21779,9 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{201D74E2-3547-4E9B-8216-09A22645AC2A}">
   <dimension ref="A1:N2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14">
       <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
@@ -21705,7 +21825,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>3163</v>
       </c>
@@ -21761,9 +21881,9 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59BC8B2E-A067-463D-937A-30E88D8BECD0}">
   <dimension ref="A1:N4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -21807,7 +21927,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>3275</v>
       </c>
@@ -21851,7 +21971,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>3662</v>
       </c>
@@ -21895,7 +22015,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
         <v>3774</v>
       </c>
@@ -21956,12 +22076,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E05CC479-3669-40F7-BE22-BA5CFBFF29E9}">
   <dimension ref="A1:N3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="5" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -22005,7 +22125,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>2906</v>
       </c>
@@ -22049,7 +22169,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>3201</v>
       </c>
@@ -22107,9 +22227,9 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4185B0A-D162-4EBC-935B-7159E365DD54}">
   <dimension ref="A1:N3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -22153,7 +22273,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>3289</v>
       </c>
@@ -22197,7 +22317,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>3304</v>
       </c>
@@ -22256,12 +22376,12 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4BBBCF5-BAC9-459C-ABE9-2526B85FD81E}">
   <dimension ref="A1:N10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="4" max="4" width="17.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -22305,7 +22425,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>45</v>
       </c>
@@ -22349,7 +22469,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>1677</v>
       </c>
@@ -22393,7 +22513,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
         <v>1683</v>
       </c>
@@ -22437,7 +22557,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
         <v>3183</v>
       </c>
@@ -22481,7 +22601,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
         <v>3192</v>
       </c>
@@ -22525,7 +22645,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
         <v>3417</v>
       </c>
@@ -22569,7 +22689,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
         <v>3418</v>
       </c>
@@ -22613,7 +22733,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
         <v>3419</v>
       </c>
@@ -22657,7 +22777,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
         <v>3675</v>
       </c>
@@ -22724,9 +22844,9 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E9EB2F5-2977-493B-BFA2-5CD20F8A3BC4}">
   <dimension ref="A1:O3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15">
       <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
@@ -22773,7 +22893,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
         <v>3020</v>
       </c>
@@ -22820,7 +22940,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15">
       <c r="A3" t="s">
         <v>3248</v>
       </c>
@@ -22882,9 +23002,9 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69A1C46E-DEF3-467B-A5BD-162AB66E6A86}">
   <dimension ref="A1:N24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -22928,7 +23048,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14">
       <c r="A2" s="7" t="s">
         <v>2595</v>
       </c>
@@ -22972,7 +23092,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14">
       <c r="A3" s="7" t="s">
         <v>2604</v>
       </c>
@@ -23016,7 +23136,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14">
       <c r="A4" s="7" t="s">
         <v>2608</v>
       </c>
@@ -23060,7 +23180,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14">
       <c r="A5" s="7" t="s">
         <v>2617</v>
       </c>
@@ -23102,7 +23222,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14">
       <c r="A6" s="7" t="s">
         <v>2625</v>
       </c>
@@ -23146,7 +23266,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14">
       <c r="A7" s="7" t="s">
         <v>2633</v>
       </c>
@@ -23190,7 +23310,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14">
       <c r="A8" s="7" t="s">
         <v>2641</v>
       </c>
@@ -23234,7 +23354,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14">
       <c r="A9" s="7" t="s">
         <v>2648</v>
       </c>
@@ -23278,7 +23398,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14">
       <c r="A10" s="7" t="s">
         <v>2654</v>
       </c>
@@ -23322,7 +23442,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14">
       <c r="A11" s="7" t="s">
         <v>2662</v>
       </c>
@@ -23366,7 +23486,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14">
       <c r="A12" s="7" t="s">
         <v>2669</v>
       </c>
@@ -23410,7 +23530,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14">
       <c r="A13" s="7" t="s">
         <v>2675</v>
       </c>
@@ -23454,7 +23574,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14">
       <c r="A14" s="7" t="s">
         <v>2681</v>
       </c>
@@ -23498,7 +23618,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14">
       <c r="A15" s="7" t="s">
         <v>2688</v>
       </c>
@@ -23542,7 +23662,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14">
       <c r="A16" s="7" t="s">
         <v>2692</v>
       </c>
@@ -23586,7 +23706,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:14">
       <c r="A17" s="7" t="s">
         <v>2701</v>
       </c>
@@ -23630,7 +23750,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:14">
       <c r="A18" s="7" t="s">
         <v>2712</v>
       </c>
@@ -23674,7 +23794,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:14">
       <c r="A19" s="7" t="s">
         <v>2716</v>
       </c>
@@ -23718,7 +23838,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:14">
       <c r="A20" s="7" t="s">
         <v>2723</v>
       </c>
@@ -23762,7 +23882,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:14">
       <c r="A21" s="7" t="s">
         <v>2733</v>
       </c>
@@ -23806,7 +23926,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:14">
       <c r="A22" s="16" t="s">
         <v>2742</v>
       </c>
@@ -23850,7 +23970,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:14">
       <c r="A23" s="16" t="s">
         <v>2751</v>
       </c>
@@ -23894,7 +24014,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:14">
       <c r="A24" s="16" t="s">
         <v>2759</v>
       </c>
@@ -23965,14 +24085,14 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE14AD29-8DB0-4C42-AB91-A73B867AE121}">
   <dimension ref="A1:N68"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="5" max="5" width="16.36328125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.26953125" customWidth="1"/>
     <col min="13" max="13" width="14.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14">
       <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
@@ -24016,7 +24136,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14">
       <c r="A2" s="7" t="s">
         <v>2168</v>
       </c>
@@ -24060,7 +24180,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14">
       <c r="A3" s="7" t="s">
         <v>2178</v>
       </c>
@@ -24104,7 +24224,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14">
       <c r="A4" s="7" t="s">
         <v>2188</v>
       </c>
@@ -24148,7 +24268,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14">
       <c r="A5" s="7" t="s">
         <v>2196</v>
       </c>
@@ -24192,7 +24312,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14">
       <c r="A6" s="7" t="s">
         <v>2206</v>
       </c>
@@ -24236,7 +24356,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14">
       <c r="A7" s="7" t="s">
         <v>2213</v>
       </c>
@@ -24280,7 +24400,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14">
       <c r="A8" s="7" t="s">
         <v>2223</v>
       </c>
@@ -24324,7 +24444,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14">
       <c r="A9" s="7" t="s">
         <v>2227</v>
       </c>
@@ -24368,7 +24488,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14">
       <c r="A10" s="7" t="s">
         <v>2236</v>
       </c>
@@ -24412,7 +24532,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14">
       <c r="A11" s="7" t="s">
         <v>2245</v>
       </c>
@@ -24456,7 +24576,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14">
       <c r="A12" s="7" t="s">
         <v>2252</v>
       </c>
@@ -24500,7 +24620,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14">
       <c r="A13" s="7" t="s">
         <v>2259</v>
       </c>
@@ -24544,7 +24664,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14">
       <c r="A14" s="7" t="s">
         <v>2267</v>
       </c>
@@ -24588,7 +24708,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14">
       <c r="A15" s="7" t="s">
         <v>2277</v>
       </c>
@@ -24632,7 +24752,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14">
       <c r="A16" s="7" t="s">
         <v>2286</v>
       </c>
@@ -24676,7 +24796,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:14">
       <c r="A17" s="7" t="s">
         <v>2287</v>
       </c>
@@ -24720,7 +24840,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:14">
       <c r="A18" s="7" t="s">
         <v>2296</v>
       </c>
@@ -24764,7 +24884,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:14">
       <c r="A19" s="7" t="s">
         <v>2303</v>
       </c>
@@ -24808,7 +24928,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:14">
       <c r="A20" s="7" t="s">
         <v>2313</v>
       </c>
@@ -24852,7 +24972,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:14">
       <c r="A21" s="7" t="s">
         <v>2323</v>
       </c>
@@ -24896,7 +25016,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:14">
       <c r="A22" s="7" t="s">
         <v>2332</v>
       </c>
@@ -24940,7 +25060,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:14">
       <c r="A23" s="7" t="s">
         <v>2340</v>
       </c>
@@ -24984,7 +25104,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:14">
       <c r="A24" s="7" t="s">
         <v>2348</v>
       </c>
@@ -25028,7 +25148,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:14">
       <c r="A25" s="7" t="s">
         <v>2356</v>
       </c>
@@ -25072,7 +25192,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:14">
       <c r="A26" s="7" t="s">
         <v>2365</v>
       </c>
@@ -25116,7 +25236,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:14">
       <c r="A27" s="7" t="s">
         <v>2373</v>
       </c>
@@ -25160,7 +25280,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:14">
       <c r="A28" s="7" t="s">
         <v>2380</v>
       </c>
@@ -25204,7 +25324,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:14">
       <c r="A29" s="7" t="s">
         <v>2390</v>
       </c>
@@ -25248,7 +25368,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:14">
       <c r="A30" s="7" t="s">
         <v>2398</v>
       </c>
@@ -25292,7 +25412,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:14">
       <c r="A31" s="7" t="s">
         <v>2409</v>
       </c>
@@ -25336,7 +25456,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:14">
       <c r="A32" s="7" t="s">
         <v>2418</v>
       </c>
@@ -25380,7 +25500,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:14">
       <c r="A33" s="7" t="s">
         <v>2424</v>
       </c>
@@ -25424,7 +25544,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:14">
       <c r="A34" s="7" t="s">
         <v>2430</v>
       </c>
@@ -25468,7 +25588,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:14">
       <c r="A35" s="7" t="s">
         <v>2435</v>
       </c>
@@ -25512,7 +25632,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:14">
       <c r="A36" s="7" t="s">
         <v>2442</v>
       </c>
@@ -25556,7 +25676,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:14">
       <c r="A37" s="7" t="s">
         <v>2450</v>
       </c>
@@ -25600,7 +25720,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:14">
       <c r="A38" s="7" t="s">
         <v>2457</v>
       </c>
@@ -25644,7 +25764,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:14">
       <c r="A39" s="7" t="s">
         <v>2465</v>
       </c>
@@ -25688,7 +25808,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:14">
       <c r="A40" s="7" t="s">
         <v>2473</v>
       </c>
@@ -25732,7 +25852,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:14">
       <c r="A41" s="7" t="s">
         <v>2478</v>
       </c>
@@ -25776,7 +25896,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:14">
       <c r="A42" s="7" t="s">
         <v>2482</v>
       </c>
@@ -25820,7 +25940,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:14">
       <c r="A43" s="7" t="s">
         <v>2484</v>
       </c>
@@ -25864,7 +25984,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:14">
       <c r="A44" s="7" t="s">
         <v>2486</v>
       </c>
@@ -25908,7 +26028,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:14">
       <c r="A45" s="7" t="s">
         <v>2495</v>
       </c>
@@ -25952,7 +26072,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:14">
       <c r="A46" s="7" t="s">
         <v>2501</v>
       </c>
@@ -25996,7 +26116,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:14">
       <c r="A47" s="7" t="s">
         <v>2511</v>
       </c>
@@ -26040,7 +26160,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:14">
       <c r="A48" s="7" t="s">
         <v>2520</v>
       </c>
@@ -26084,7 +26204,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:14">
       <c r="A49" s="7" t="s">
         <v>2527</v>
       </c>
@@ -26128,7 +26248,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:14">
       <c r="A50" s="7" t="s">
         <v>2534</v>
       </c>
@@ -26172,7 +26292,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:14">
       <c r="A51" s="7" t="s">
         <v>2541</v>
       </c>
@@ -26216,7 +26336,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:14">
       <c r="A52" s="7" t="s">
         <v>2549</v>
       </c>
@@ -26260,7 +26380,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:14">
       <c r="A53" s="7" t="s">
         <v>2557</v>
       </c>
@@ -26304,7 +26424,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:14">
       <c r="A54" s="7" t="s">
         <v>2565</v>
       </c>
@@ -26348,7 +26468,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:14">
       <c r="A55" s="16" t="s">
         <v>2578</v>
       </c>
@@ -26392,7 +26512,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:14">
       <c r="A56" s="16" t="s">
         <v>2583</v>
       </c>
@@ -26436,7 +26556,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:14">
       <c r="A57" s="16" t="s">
         <v>2584</v>
       </c>
@@ -26480,7 +26600,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:14">
       <c r="A58" s="16" t="s">
         <v>2878</v>
       </c>
@@ -26524,7 +26644,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:14">
       <c r="A59" s="16" t="s">
         <v>2879</v>
       </c>
@@ -26568,7 +26688,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:14">
       <c r="A60" s="16" t="s">
         <v>2880</v>
       </c>
@@ -26612,7 +26732,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:14">
       <c r="A61" s="16" t="s">
         <v>2881</v>
       </c>
@@ -26656,7 +26776,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:14">
       <c r="A62" s="16" t="s">
         <v>2916</v>
       </c>
@@ -26700,7 +26820,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:14">
       <c r="A63" s="16" t="s">
         <v>3254</v>
       </c>
@@ -26744,7 +26864,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:14">
       <c r="A64" s="16" t="s">
         <v>3282</v>
       </c>
@@ -26788,7 +26908,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:14">
       <c r="A65" s="16" t="s">
         <v>3551</v>
       </c>
@@ -26832,7 +26952,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:14">
       <c r="A66" s="16" t="s">
         <v>3683</v>
       </c>
@@ -26876,7 +26996,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:14">
       <c r="A67" s="16" t="s">
         <v>3727</v>
       </c>
@@ -26920,7 +27040,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:14">
       <c r="A68" s="16" t="s">
         <v>3728</v>
       </c>
@@ -27036,12 +27156,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E940ACE-72CF-4504-B730-2719484575BC}">
   <dimension ref="A1:N3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="5" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -27085,7 +27205,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>3211</v>
       </c>
@@ -27129,7 +27249,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>3484</v>
       </c>
@@ -27187,15 +27307,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60E8291E-4293-4634-B9E9-80CB520CA181}">
-  <dimension ref="A1:N180"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:N184"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="3" max="3" width="19.90625" customWidth="1"/>
     <col min="5" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -27239,7 +27359,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14">
       <c r="A2" s="7" t="s">
         <v>35</v>
       </c>
@@ -27283,7 +27403,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14">
       <c r="A3" s="7" t="s">
         <v>56</v>
       </c>
@@ -27327,7 +27447,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14">
       <c r="A4" s="7" t="s">
         <v>716</v>
       </c>
@@ -27371,7 +27491,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14">
       <c r="A5" s="7" t="s">
         <v>723</v>
       </c>
@@ -27415,7 +27535,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14">
       <c r="A6" s="7" t="s">
         <v>730</v>
       </c>
@@ -27459,7 +27579,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14">
       <c r="A7" s="7" t="s">
         <v>737</v>
       </c>
@@ -27503,7 +27623,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14">
       <c r="A8" s="7" t="s">
         <v>744</v>
       </c>
@@ -27547,7 +27667,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14">
       <c r="A9" s="7" t="s">
         <v>752</v>
       </c>
@@ -27591,7 +27711,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14">
       <c r="A10" s="7" t="s">
         <v>759</v>
       </c>
@@ -27635,7 +27755,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14">
       <c r="A11" s="7" t="s">
         <v>766</v>
       </c>
@@ -27679,7 +27799,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14">
       <c r="A12" s="7" t="s">
         <v>773</v>
       </c>
@@ -27723,7 +27843,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14">
       <c r="A13" s="7" t="s">
         <v>780</v>
       </c>
@@ -27767,7 +27887,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14">
       <c r="A14" s="7" t="s">
         <v>787</v>
       </c>
@@ -27811,7 +27931,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14">
       <c r="A15" s="7" t="s">
         <v>794</v>
       </c>
@@ -27855,7 +27975,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14">
       <c r="A16" s="7" t="s">
         <v>801</v>
       </c>
@@ -27899,7 +28019,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:14">
       <c r="A17" s="7" t="s">
         <v>808</v>
       </c>
@@ -27943,7 +28063,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:14">
       <c r="A18" s="7" t="s">
         <v>815</v>
       </c>
@@ -27987,7 +28107,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:14">
       <c r="A19" s="7" t="s">
         <v>822</v>
       </c>
@@ -28031,7 +28151,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:14">
       <c r="A20" s="7" t="s">
         <v>829</v>
       </c>
@@ -28075,7 +28195,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:14">
       <c r="A21" s="7" t="s">
         <v>834</v>
       </c>
@@ -28119,7 +28239,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:14">
       <c r="A22" s="7" t="s">
         <v>841</v>
       </c>
@@ -28163,7 +28283,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:14">
       <c r="A23" s="7" t="s">
         <v>849</v>
       </c>
@@ -28207,7 +28327,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:14">
       <c r="A24" s="7" t="s">
         <v>856</v>
       </c>
@@ -28251,7 +28371,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:14">
       <c r="A25" s="7" t="s">
         <v>863</v>
       </c>
@@ -28295,7 +28415,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:14">
       <c r="A26" s="7" t="s">
         <v>870</v>
       </c>
@@ -28339,7 +28459,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:14">
       <c r="A27" s="7" t="s">
         <v>877</v>
       </c>
@@ -28383,7 +28503,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:14">
       <c r="A28" s="7" t="s">
         <v>884</v>
       </c>
@@ -28427,7 +28547,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:14">
       <c r="A29" s="7" t="s">
         <v>891</v>
       </c>
@@ -28471,7 +28591,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:14">
       <c r="A30" s="7" t="s">
         <v>898</v>
       </c>
@@ -28515,7 +28635,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:14">
       <c r="A31" s="7" t="s">
         <v>905</v>
       </c>
@@ -28559,7 +28679,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:14">
       <c r="A32" s="7" t="s">
         <v>912</v>
       </c>
@@ -28603,7 +28723,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:14">
       <c r="A33" s="7" t="s">
         <v>919</v>
       </c>
@@ -28647,7 +28767,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:14">
       <c r="A34" s="7" t="s">
         <v>927</v>
       </c>
@@ -28691,7 +28811,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:14">
       <c r="A35" s="7" t="s">
         <v>934</v>
       </c>
@@ -28735,7 +28855,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:14">
       <c r="A36" s="7" t="s">
         <v>941</v>
       </c>
@@ -28779,7 +28899,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:14">
       <c r="A37" s="7" t="s">
         <v>949</v>
       </c>
@@ -28823,7 +28943,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:14">
       <c r="A38" s="7" t="s">
         <v>956</v>
       </c>
@@ -28867,7 +28987,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:14">
       <c r="A39" s="7" t="s">
         <v>963</v>
       </c>
@@ -28911,7 +29031,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:14">
       <c r="A40" s="7" t="s">
         <v>970</v>
       </c>
@@ -28955,7 +29075,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:14">
       <c r="A41" s="7" t="s">
         <v>976</v>
       </c>
@@ -28999,7 +29119,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:14">
       <c r="A42" s="7" t="s">
         <v>983</v>
       </c>
@@ -29043,7 +29163,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:14">
       <c r="A43" s="7" t="s">
         <v>990</v>
       </c>
@@ -29087,7 +29207,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:14">
       <c r="A44" s="7" t="s">
         <v>997</v>
       </c>
@@ -29131,7 +29251,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:14">
       <c r="A45" s="7" t="s">
         <v>1004</v>
       </c>
@@ -29175,7 +29295,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:14">
       <c r="A46" s="7" t="s">
         <v>1011</v>
       </c>
@@ -29219,7 +29339,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:14">
       <c r="A47" s="7" t="s">
         <v>1018</v>
       </c>
@@ -29263,7 +29383,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:14">
       <c r="A48" s="7" t="s">
         <v>1025</v>
       </c>
@@ -29307,7 +29427,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:14">
       <c r="A49" s="7" t="s">
         <v>1032</v>
       </c>
@@ -29351,7 +29471,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:14">
       <c r="A50" s="7" t="s">
         <v>1040</v>
       </c>
@@ -29395,7 +29515,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:14">
       <c r="A51" s="7" t="s">
         <v>1047</v>
       </c>
@@ -29439,7 +29559,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:14">
       <c r="A52" s="7" t="s">
         <v>1054</v>
       </c>
@@ -29483,7 +29603,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:14">
       <c r="A53" s="7" t="s">
         <v>1061</v>
       </c>
@@ -29527,7 +29647,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:14">
       <c r="A54" s="7" t="s">
         <v>1068</v>
       </c>
@@ -29571,7 +29691,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:14">
       <c r="A55" s="7" t="s">
         <v>1075</v>
       </c>
@@ -29615,7 +29735,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:14">
       <c r="A56" s="7" t="s">
         <v>1082</v>
       </c>
@@ -29659,7 +29779,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:14">
       <c r="A57" s="7" t="s">
         <v>1089</v>
       </c>
@@ -29703,7 +29823,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:14">
       <c r="A58" s="7" t="s">
         <v>1096</v>
       </c>
@@ -29747,7 +29867,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:14">
       <c r="A59" s="7" t="s">
         <v>1103</v>
       </c>
@@ -29791,7 +29911,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:14">
       <c r="A60" s="7" t="s">
         <v>1110</v>
       </c>
@@ -29835,7 +29955,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:14">
       <c r="A61" s="7" t="s">
         <v>1117</v>
       </c>
@@ -29879,7 +29999,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:14">
       <c r="A62" s="7" t="s">
         <v>1124</v>
       </c>
@@ -29923,7 +30043,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:14">
       <c r="A63" s="7" t="s">
         <v>1132</v>
       </c>
@@ -29967,7 +30087,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:14">
       <c r="A64" s="7" t="s">
         <v>1139</v>
       </c>
@@ -30011,7 +30131,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:14">
       <c r="A65" s="7" t="s">
         <v>1147</v>
       </c>
@@ -30055,7 +30175,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:14">
       <c r="A66" s="7" t="s">
         <v>1154</v>
       </c>
@@ -30099,7 +30219,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:14">
       <c r="A67" s="7" t="s">
         <v>1162</v>
       </c>
@@ -30143,7 +30263,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:14">
       <c r="A68" s="7" t="s">
         <v>1169</v>
       </c>
@@ -30187,7 +30307,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:14">
       <c r="A69" s="7" t="s">
         <v>1176</v>
       </c>
@@ -30231,7 +30351,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:14">
       <c r="A70" s="7" t="s">
         <v>1183</v>
       </c>
@@ -30275,7 +30395,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:14">
       <c r="A71" s="7" t="s">
         <v>1190</v>
       </c>
@@ -30319,7 +30439,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:14">
       <c r="A72" s="7" t="s">
         <v>1198</v>
       </c>
@@ -30363,7 +30483,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:14">
       <c r="A73" s="7" t="s">
         <v>1205</v>
       </c>
@@ -30407,7 +30527,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:14">
       <c r="A74" s="7" t="s">
         <v>1212</v>
       </c>
@@ -30451,7 +30571,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:14">
       <c r="A75" s="7" t="s">
         <v>1219</v>
       </c>
@@ -30495,7 +30615,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:14">
       <c r="A76" s="7" t="s">
         <v>1226</v>
       </c>
@@ -30539,7 +30659,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:14">
       <c r="A77" s="7" t="s">
         <v>1233</v>
       </c>
@@ -30583,7 +30703,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:14">
       <c r="A78" s="7" t="s">
         <v>1240</v>
       </c>
@@ -30627,7 +30747,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:14">
       <c r="A79" s="7" t="s">
         <v>1247</v>
       </c>
@@ -30671,7 +30791,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:14">
       <c r="A80" s="7" t="s">
         <v>1254</v>
       </c>
@@ -30715,7 +30835,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:14">
       <c r="A81" s="7" t="s">
         <v>1261</v>
       </c>
@@ -30759,7 +30879,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:14">
       <c r="A82" s="7" t="s">
         <v>1268</v>
       </c>
@@ -30803,7 +30923,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:14">
       <c r="A83" s="7" t="s">
         <v>1275</v>
       </c>
@@ -30847,7 +30967,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:14">
       <c r="A84" s="7" t="s">
         <v>1283</v>
       </c>
@@ -30891,7 +31011,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:14">
       <c r="A85" s="7" t="s">
         <v>1290</v>
       </c>
@@ -30935,7 +31055,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:14">
       <c r="A86" s="7" t="s">
         <v>1297</v>
       </c>
@@ -30979,7 +31099,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:14">
       <c r="A87" s="7" t="s">
         <v>1304</v>
       </c>
@@ -31023,7 +31143,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:14">
       <c r="A88" s="7" t="s">
         <v>1311</v>
       </c>
@@ -31067,7 +31187,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:14">
       <c r="A89" s="7" t="s">
         <v>1318</v>
       </c>
@@ -31111,7 +31231,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:14">
       <c r="A90" s="7" t="s">
         <v>1325</v>
       </c>
@@ -31155,7 +31275,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:14">
       <c r="A91" s="7" t="s">
         <v>1332</v>
       </c>
@@ -31199,7 +31319,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:14">
       <c r="A92" s="7" t="s">
         <v>1339</v>
       </c>
@@ -31243,7 +31363,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:14">
       <c r="A93" s="7" t="s">
         <v>1346</v>
       </c>
@@ -31287,7 +31407,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:14">
       <c r="A94" s="7" t="s">
         <v>1353</v>
       </c>
@@ -31331,7 +31451,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:14">
       <c r="A95" s="7" t="s">
         <v>1360</v>
       </c>
@@ -31375,7 +31495,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:14">
       <c r="A96" s="7" t="s">
         <v>1367</v>
       </c>
@@ -31419,7 +31539,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:14">
       <c r="A97" s="7" t="s">
         <v>1374</v>
       </c>
@@ -31463,7 +31583,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:14">
       <c r="A98" s="7" t="s">
         <v>1381</v>
       </c>
@@ -31507,7 +31627,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:14">
       <c r="A99" s="7" t="s">
         <v>1388</v>
       </c>
@@ -31551,7 +31671,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:14">
       <c r="A100" s="7" t="s">
         <v>1395</v>
       </c>
@@ -31595,7 +31715,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:14">
       <c r="A101" s="7" t="s">
         <v>1402</v>
       </c>
@@ -31639,7 +31759,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:14">
       <c r="A102" s="7" t="s">
         <v>1408</v>
       </c>
@@ -31683,7 +31803,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:14">
       <c r="A103" s="7" t="s">
         <v>1414</v>
       </c>
@@ -31727,7 +31847,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:14">
       <c r="A104" s="7" t="s">
         <v>1420</v>
       </c>
@@ -31771,7 +31891,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:14">
       <c r="A105" s="7" t="s">
         <v>1426</v>
       </c>
@@ -31815,7 +31935,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:14">
       <c r="A106" s="7" t="s">
         <v>1432</v>
       </c>
@@ -31859,7 +31979,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:14">
       <c r="A107" s="7" t="s">
         <v>1438</v>
       </c>
@@ -31903,7 +32023,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:14">
       <c r="A108" s="7" t="s">
         <v>1444</v>
       </c>
@@ -31947,7 +32067,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:14">
       <c r="A109" s="7" t="s">
         <v>1450</v>
       </c>
@@ -31991,7 +32111,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:14">
       <c r="A110" s="7" t="s">
         <v>1456</v>
       </c>
@@ -32035,7 +32155,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:14">
       <c r="A111" s="7" t="s">
         <v>1462</v>
       </c>
@@ -32079,7 +32199,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:14">
       <c r="A112" s="7" t="s">
         <v>1467</v>
       </c>
@@ -32123,7 +32243,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:14">
       <c r="A113" s="7" t="s">
         <v>1473</v>
       </c>
@@ -32167,7 +32287,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:14">
       <c r="A114" s="7" t="s">
         <v>1480</v>
       </c>
@@ -32211,7 +32331,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:14">
       <c r="A115" s="7" t="s">
         <v>1486</v>
       </c>
@@ -32255,7 +32375,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:14">
       <c r="A116" s="7" t="s">
         <v>1492</v>
       </c>
@@ -32299,7 +32419,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:14">
       <c r="A117" s="7" t="s">
         <v>1498</v>
       </c>
@@ -32343,7 +32463,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:14">
       <c r="A118" s="7" t="s">
         <v>1505</v>
       </c>
@@ -32387,7 +32507,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:14">
       <c r="A119" s="7" t="s">
         <v>1512</v>
       </c>
@@ -32431,7 +32551,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:14">
       <c r="A120" s="16" t="s">
         <v>1520</v>
       </c>
@@ -32475,7 +32595,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:14">
       <c r="A121" s="16" t="s">
         <v>1528</v>
       </c>
@@ -32519,7 +32639,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:14">
       <c r="A122" s="16" t="s">
         <v>1535</v>
       </c>
@@ -32563,7 +32683,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:14">
       <c r="A123" s="16" t="s">
         <v>1542</v>
       </c>
@@ -32607,7 +32727,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:14">
       <c r="A124" s="16" t="s">
         <v>1550</v>
       </c>
@@ -32651,7 +32771,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:14">
       <c r="A125" s="16" t="s">
         <v>1557</v>
       </c>
@@ -32695,7 +32815,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:14">
       <c r="A126" s="16" t="s">
         <v>1563</v>
       </c>
@@ -32739,7 +32859,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:14">
       <c r="A127" s="16" t="s">
         <v>1571</v>
       </c>
@@ -32783,7 +32903,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:14">
       <c r="A128" s="16" t="s">
         <v>1578</v>
       </c>
@@ -32827,7 +32947,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:14">
       <c r="A129" s="16" t="s">
         <v>1586</v>
       </c>
@@ -32871,7 +32991,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:14">
       <c r="A130" s="16" t="s">
         <v>1593</v>
       </c>
@@ -32915,7 +33035,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:14">
       <c r="A131" s="16" t="s">
         <v>1601</v>
       </c>
@@ -32959,7 +33079,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:14">
       <c r="A132" s="16" t="s">
         <v>1608</v>
       </c>
@@ -33003,7 +33123,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:14">
       <c r="A133" s="16" t="s">
         <v>1615</v>
       </c>
@@ -33047,7 +33167,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:14">
       <c r="A134" s="16" t="s">
         <v>1621</v>
       </c>
@@ -33091,7 +33211,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:14">
       <c r="A135" s="16" t="s">
         <v>1628</v>
       </c>
@@ -33135,7 +33255,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:14">
       <c r="A136" s="16" t="s">
         <v>1635</v>
       </c>
@@ -33179,7 +33299,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:14">
       <c r="A137" s="16" t="s">
         <v>2921</v>
       </c>
@@ -33223,7 +33343,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:14">
       <c r="A138" s="16" t="s">
         <v>2925</v>
       </c>
@@ -33267,7 +33387,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:14">
       <c r="A139" s="16" t="s">
         <v>2930</v>
       </c>
@@ -33311,7 +33431,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:14">
       <c r="A140" s="16" t="s">
         <v>2936</v>
       </c>
@@ -33355,7 +33475,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:14">
       <c r="A141" s="16" t="s">
         <v>2943</v>
       </c>
@@ -33399,7 +33519,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:14">
       <c r="A142" s="16" t="s">
         <v>2949</v>
       </c>
@@ -33443,7 +33563,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:14">
       <c r="A143" s="16" t="s">
         <v>3102</v>
       </c>
@@ -33487,7 +33607,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:14">
       <c r="A144" s="16" t="s">
         <v>3103</v>
       </c>
@@ -33531,7 +33651,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:14">
       <c r="A145" s="16" t="s">
         <v>3104</v>
       </c>
@@ -33575,7 +33695,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:14">
       <c r="A146" s="16" t="s">
         <v>3122</v>
       </c>
@@ -33619,7 +33739,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:14">
       <c r="A147" s="16" t="s">
         <v>3128</v>
       </c>
@@ -33663,7 +33783,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:14">
       <c r="A148" s="16" t="s">
         <v>3129</v>
       </c>
@@ -33707,7 +33827,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:14">
       <c r="A149" s="16" t="s">
         <v>3130</v>
       </c>
@@ -33751,7 +33871,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:14">
       <c r="A150" s="16" t="s">
         <v>3131</v>
       </c>
@@ -33795,7 +33915,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:14">
       <c r="A151" s="16" t="s">
         <v>3228</v>
       </c>
@@ -33839,7 +33959,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:14">
       <c r="A152" s="16" t="s">
         <v>3236</v>
       </c>
@@ -33883,7 +34003,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:14">
       <c r="A153" s="16" t="s">
         <v>3237</v>
       </c>
@@ -33927,7 +34047,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:14">
       <c r="A154" s="16" t="s">
         <v>3328</v>
       </c>
@@ -33971,7 +34091,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:14">
       <c r="A155" s="16" t="s">
         <v>3329</v>
       </c>
@@ -34015,7 +34135,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:14">
       <c r="A156" s="16" t="s">
         <v>3330</v>
       </c>
@@ -34059,7 +34179,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:14">
       <c r="A157" s="16" t="s">
         <v>3393</v>
       </c>
@@ -34103,7 +34223,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:14">
       <c r="A158" s="16" t="s">
         <v>3394</v>
       </c>
@@ -34147,7 +34267,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:14">
       <c r="A159" s="16" t="s">
         <v>3395</v>
       </c>
@@ -34191,7 +34311,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:14">
       <c r="A160" s="16" t="s">
         <v>3442</v>
       </c>
@@ -34235,7 +34355,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:14">
       <c r="A161" s="16" t="s">
         <v>3448</v>
       </c>
@@ -34279,7 +34399,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:14">
       <c r="A162" s="16" t="s">
         <v>3502</v>
       </c>
@@ -34323,7 +34443,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:14">
       <c r="A163" s="16" t="s">
         <v>3503</v>
       </c>
@@ -34367,7 +34487,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:14">
       <c r="A164" s="16" t="s">
         <v>3504</v>
       </c>
@@ -34411,7 +34531,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:14">
       <c r="A165" s="16" t="s">
         <v>3505</v>
       </c>
@@ -34455,7 +34575,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:14">
       <c r="A166" s="16" t="s">
         <v>3543</v>
       </c>
@@ -34499,7 +34619,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:14">
       <c r="A167" s="16" t="s">
         <v>3565</v>
       </c>
@@ -34543,7 +34663,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:14">
       <c r="A168" s="16" t="s">
         <v>3566</v>
       </c>
@@ -34587,7 +34707,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:14">
       <c r="A169" s="16" t="s">
         <v>3567</v>
       </c>
@@ -34631,7 +34751,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:14">
       <c r="A170" s="16" t="s">
         <v>3568</v>
       </c>
@@ -34675,7 +34795,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:14">
       <c r="A171" s="16" t="s">
         <v>3591</v>
       </c>
@@ -34719,7 +34839,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:14">
       <c r="A172" s="16" t="s">
         <v>3592</v>
       </c>
@@ -34763,7 +34883,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:14">
       <c r="A173" s="16" t="s">
         <v>3623</v>
       </c>
@@ -34807,7 +34927,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:14">
       <c r="A174" s="16" t="s">
         <v>3624</v>
       </c>
@@ -34851,7 +34971,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:14">
       <c r="A175" s="16" t="s">
         <v>3633</v>
       </c>
@@ -34895,7 +35015,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:14">
       <c r="A176" s="16" t="s">
         <v>3634</v>
       </c>
@@ -34939,7 +35059,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:14">
       <c r="A177" s="16" t="s">
         <v>3670</v>
       </c>
@@ -34983,7 +35103,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:14">
       <c r="A178" s="16" t="s">
         <v>3753</v>
       </c>
@@ -35027,11 +35147,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:14">
       <c r="A179" s="16" t="s">
         <v>3780</v>
       </c>
-      <c r="B179" s="41" t="s">
+      <c r="B179" s="16" t="s">
         <v>3782</v>
       </c>
       <c r="C179" s="16" t="s">
@@ -35040,13 +35160,13 @@
       <c r="D179" s="20" t="s">
         <v>240</v>
       </c>
-      <c r="E179" s="41" t="s">
+      <c r="E179" s="16" t="s">
         <v>3784</v>
       </c>
-      <c r="F179" s="40" t="s">
+      <c r="F179" s="3" t="s">
         <v>3311</v>
       </c>
-      <c r="G179" s="40" t="s">
+      <c r="G179" s="3" t="s">
         <v>3785</v>
       </c>
       <c r="H179" s="16" t="s">
@@ -35071,11 +35191,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:14">
       <c r="A180" s="16" t="s">
         <v>3781</v>
       </c>
-      <c r="B180" s="41" t="s">
+      <c r="B180" s="16" t="s">
         <v>3788</v>
       </c>
       <c r="C180" s="16" t="s">
@@ -35084,16 +35204,16 @@
       <c r="D180" s="20" t="s">
         <v>240</v>
       </c>
-      <c r="E180" s="41" t="s">
+      <c r="E180" s="16" t="s">
         <v>3790</v>
       </c>
-      <c r="F180" s="40" t="s">
+      <c r="F180" s="3" t="s">
         <v>2975</v>
       </c>
-      <c r="G180" s="40" t="s">
+      <c r="G180" s="3" t="s">
         <v>3791</v>
       </c>
-      <c r="H180" s="41" t="s">
+      <c r="H180" s="16" t="s">
         <v>21</v>
       </c>
       <c r="I180" s="27" t="s">
@@ -35114,6 +35234,138 @@
       <c r="N180" t="s">
         <v>25</v>
       </c>
+    </row>
+    <row r="181" spans="1:14">
+      <c r="A181" s="16" t="s">
+        <v>3794</v>
+      </c>
+      <c r="B181" s="16" t="s">
+        <v>3795</v>
+      </c>
+      <c r="C181" s="16" t="s">
+        <v>3796</v>
+      </c>
+      <c r="D181" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="E181" t="s">
+        <v>3797</v>
+      </c>
+      <c r="F181" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="G181" s="40" t="s">
+        <v>3798</v>
+      </c>
+      <c r="H181" s="41" t="s">
+        <v>21</v>
+      </c>
+      <c r="I181" s="27" t="s">
+        <v>2941</v>
+      </c>
+      <c r="K181" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L181" s="17" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M181" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="N181" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="182" spans="1:14">
+      <c r="A182" s="16" t="s">
+        <v>3799</v>
+      </c>
+      <c r="B182" s="41" t="s">
+        <v>3801</v>
+      </c>
+      <c r="C182" s="16" t="s">
+        <v>3800</v>
+      </c>
+      <c r="D182" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="E182" s="41" t="s">
+        <v>3802</v>
+      </c>
+      <c r="F182" s="42" t="s">
+        <v>3311</v>
+      </c>
+      <c r="G182" s="42" t="s">
+        <v>3803</v>
+      </c>
+      <c r="H182" s="41" t="s">
+        <v>21</v>
+      </c>
+      <c r="I182" s="27" t="s">
+        <v>3804</v>
+      </c>
+      <c r="J182" s="27" t="s">
+        <v>3805</v>
+      </c>
+      <c r="K182" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L182" s="17" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M182" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="N182" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="183" spans="1:14">
+      <c r="A183" s="16" t="s">
+        <v>3806</v>
+      </c>
+      <c r="B183" s="41" t="s">
+        <v>3807</v>
+      </c>
+      <c r="C183" s="16" t="s">
+        <v>3808</v>
+      </c>
+      <c r="D183" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="E183" s="41" t="s">
+        <v>3809</v>
+      </c>
+      <c r="F183" s="42" t="s">
+        <v>3311</v>
+      </c>
+      <c r="G183" s="42" t="s">
+        <v>3810</v>
+      </c>
+      <c r="H183" s="41" t="s">
+        <v>21</v>
+      </c>
+      <c r="I183" s="27" t="s">
+        <v>3644</v>
+      </c>
+      <c r="J183" s="32" t="s">
+        <v>3811</v>
+      </c>
+      <c r="K183" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L183" s="17" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M183" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="N183" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="184" spans="1:14">
+      <c r="A184" s="16"/>
     </row>
   </sheetData>
   <phoneticPr fontId="16" type="noConversion"/>
@@ -35268,21 +35520,26 @@
     <hyperlink ref="J179" r:id="rId148" xr:uid="{59A00EB9-3C29-4E7E-9493-B5D23481D54F}"/>
     <hyperlink ref="I180" r:id="rId149" xr:uid="{E7507415-6A06-429F-98FD-0C48D02CCF14}"/>
     <hyperlink ref="J180" r:id="rId150" xr:uid="{940F6C26-625D-4CA2-BC87-6ED0B49D62C6}"/>
+    <hyperlink ref="I181" r:id="rId151" xr:uid="{5C03D7D7-EFC4-40DE-B06F-47A8465A62B8}"/>
+    <hyperlink ref="I182" r:id="rId152" xr:uid="{2A557AB7-8F4A-4DCD-B566-7FE02B85736C}"/>
+    <hyperlink ref="J182" r:id="rId153" xr:uid="{2B26D6AA-C539-4788-90B0-829083988502}"/>
+    <hyperlink ref="I183" r:id="rId154" xr:uid="{17AE4450-0CA6-491F-AEB3-46674CC00EEE}"/>
+    <hyperlink ref="J183" r:id="rId155" xr:uid="{3A9AF27C-EAA3-4F8D-B05D-139594372A97}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId151"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId156"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81F9848D-6D60-47C0-9F84-A561FE4F106E}">
   <dimension ref="A1:N5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="20.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -35326,7 +35583,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>28</v>
       </c>
@@ -35370,7 +35627,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>1661</v>
       </c>
@@ -35414,7 +35671,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
         <v>2970</v>
       </c>
@@ -35458,7 +35715,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
         <v>3155</v>
       </c>
@@ -35519,9 +35776,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01C6B0FD-D8A3-44EC-9532-03DDA232F922}">
   <dimension ref="A1:N4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -35565,7 +35822,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>3411</v>
       </c>
@@ -35609,7 +35866,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>3412</v>
       </c>
@@ -35653,7 +35910,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
         <v>3704</v>
       </c>
@@ -35714,9 +35971,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D956EFE-E955-4E62-8478-2294E6413DC1}">
   <dimension ref="A1:N3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -35760,7 +36017,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>2896</v>
       </c>
@@ -35804,7 +36061,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>3493</v>
       </c>
@@ -35862,9 +36119,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{652841DA-3619-42EE-A536-61B58BE1B457}">
   <dimension ref="A1:N9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -35908,7 +36165,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14">
       <c r="A2" s="7" t="s">
         <v>1832</v>
       </c>
@@ -35952,7 +36209,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14">
       <c r="A3" s="7" t="s">
         <v>1843</v>
       </c>
@@ -35996,7 +36253,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14">
       <c r="A4" s="7" t="s">
         <v>1853</v>
       </c>
@@ -36040,7 +36297,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14">
       <c r="A5" s="7" t="s">
         <v>1864</v>
       </c>
@@ -36084,7 +36341,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14">
       <c r="A6" s="7" t="s">
         <v>1872</v>
       </c>
@@ -36128,7 +36385,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14">
       <c r="A7" s="7" t="s">
         <v>1882</v>
       </c>
@@ -36172,7 +36429,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14">
       <c r="A8" s="16" t="s">
         <v>1892</v>
       </c>
@@ -36216,7 +36473,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14">
       <c r="A9" s="16" t="s">
         <v>1901</v>
       </c>
@@ -36274,9 +36531,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FE2008B-4BF4-4C9A-883A-FEE5873AEAF4}">
   <dimension ref="A1:N14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" ht="16" customHeight="1">
       <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
@@ -36320,7 +36577,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" ht="16" customHeight="1">
       <c r="A2" s="7" t="s">
         <v>1911</v>
       </c>
@@ -36364,7 +36621,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" ht="16" customHeight="1">
       <c r="A3" s="7" t="s">
         <v>1920</v>
       </c>
@@ -36408,7 +36665,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" ht="16" customHeight="1">
       <c r="A4" s="7" t="s">
         <v>1928</v>
       </c>
@@ -36452,7 +36709,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" ht="16" customHeight="1">
       <c r="A5" s="7" t="s">
         <v>1936</v>
       </c>
@@ -36496,7 +36753,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" ht="16" customHeight="1">
       <c r="A6" s="7" t="s">
         <v>1944</v>
       </c>
@@ -36540,7 +36797,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" ht="16" customHeight="1">
       <c r="A7" s="7" t="s">
         <v>1952</v>
       </c>
@@ -36584,7 +36841,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" ht="16" customHeight="1">
       <c r="A8" s="7" t="s">
         <v>1961</v>
       </c>
@@ -36628,7 +36885,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" ht="16" customHeight="1">
       <c r="A9" s="7" t="s">
         <v>1969</v>
       </c>
@@ -36672,7 +36929,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" ht="16" customHeight="1">
       <c r="A10" s="16" t="s">
         <v>1977</v>
       </c>
@@ -36716,7 +36973,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" ht="16" customHeight="1">
       <c r="A11" s="16" t="s">
         <v>1986</v>
       </c>
@@ -36760,7 +37017,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" ht="16" customHeight="1">
       <c r="A12" s="16" t="s">
         <v>1995</v>
       </c>
@@ -36804,7 +37061,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14">
       <c r="A13" s="16" t="s">
         <v>2994</v>
       </c>
@@ -36848,7 +37105,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14">
       <c r="A14" s="16" t="s">
         <v>3693</v>
       </c>

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C3BCFAE-D526-4DC3-84A5-BB09569D115B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F25D5F6-3FD0-477A-BD8D-51CA3D725368}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10710" yWindow="0" windowWidth="10980" windowHeight="13770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="26532" yWindow="2268" windowWidth="16200" windowHeight="9972" firstSheet="14" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7676" uniqueCount="3819">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7690" uniqueCount="3826">
   <si>
     <t>ID</t>
   </si>
@@ -11505,6 +11505,27 @@
   </si>
   <si>
     <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/885012006063?qs=0KOYDY2FL29yUmMQmcJrdA%3D%3D</t>
+  </si>
+  <si>
+    <t>ADS1015</t>
+  </si>
+  <si>
+    <t>050-0008</t>
+  </si>
+  <si>
+    <t>Conversores de analógico a digital (ADC) 12-Bit ADC I2C-Comp atible 3.3kSPS Wit A A 595-ADS1015IDGST</t>
+  </si>
+  <si>
+    <t>ADS1015IDGSR</t>
+  </si>
+  <si>
+    <t>595-ADS1015IDGSR</t>
+  </si>
+  <si>
+    <t>https://www.ti.com/lit/ds/symlink/ads1013.pdf?ts=1782833806674&amp;ref_url=https%253A%252F%252Fwww.mouser.com%252F</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Texas-Instruments/ADS1015IDGSR?qs=IK5e5L0zOXhCrFZ0pftZqw%3D%3D</t>
   </si>
 </sst>
 </file>
@@ -11514,7 +11535,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -11594,14 +11615,6 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -11689,7 +11702,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -11723,16 +11736,15 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -11741,21 +11753,19 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -16129,10 +16139,10 @@
       <c r="H93" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I93" s="27" t="s">
+      <c r="I93" s="26" t="s">
         <v>2984</v>
       </c>
-      <c r="J93" s="27" t="s">
+      <c r="J93" s="26" t="s">
         <v>2985</v>
       </c>
       <c r="K93" s="7" t="s">
@@ -16164,7 +16174,7 @@
       <c r="E94" s="16" t="s">
         <v>2989</v>
       </c>
-      <c r="F94" s="31" t="s">
+      <c r="F94" s="30" t="s">
         <v>60</v>
       </c>
       <c r="G94" s="3" t="s">
@@ -16173,10 +16183,10 @@
       <c r="H94" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I94" s="27" t="s">
+      <c r="I94" s="26" t="s">
         <v>2984</v>
       </c>
-      <c r="J94" s="32" t="s">
+      <c r="J94" s="31" t="s">
         <v>2991</v>
       </c>
       <c r="K94" s="7" t="s">
@@ -16208,7 +16218,7 @@
       <c r="E95" s="16" t="s">
         <v>3004</v>
       </c>
-      <c r="F95" s="31" t="s">
+      <c r="F95" s="30" t="s">
         <v>3005</v>
       </c>
       <c r="G95" s="3" t="s">
@@ -16217,10 +16227,10 @@
       <c r="H95" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I95" s="27" t="s">
+      <c r="I95" s="26" t="s">
         <v>3006</v>
       </c>
-      <c r="J95" s="32" t="s">
+      <c r="J95" s="31" t="s">
         <v>3007</v>
       </c>
       <c r="K95" s="7" t="s">
@@ -16261,10 +16271,10 @@
       <c r="H96" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I96" s="27" t="s">
+      <c r="I96" s="26" t="s">
         <v>3006</v>
       </c>
-      <c r="J96" s="32" t="s">
+      <c r="J96" s="31" t="s">
         <v>3013</v>
       </c>
       <c r="K96" s="7" t="s">
@@ -16305,7 +16315,7 @@
       <c r="H97" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I97" s="27" t="s">
+      <c r="I97" s="26" t="s">
         <v>3006</v>
       </c>
       <c r="J97" t="s">
@@ -16337,7 +16347,7 @@
       <c r="D98" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="E98" s="36" t="s">
+      <c r="E98" s="35" t="s">
         <v>3081</v>
       </c>
       <c r="F98" s="3" t="s">
@@ -16349,7 +16359,7 @@
       <c r="H98" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I98" s="27" t="s">
+      <c r="I98" s="26" t="s">
         <v>3054</v>
       </c>
       <c r="J98" t="s">
@@ -16381,7 +16391,7 @@
       <c r="D99" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="E99" s="36" t="s">
+      <c r="E99" s="35" t="s">
         <v>3083</v>
       </c>
       <c r="F99" s="3" t="s">
@@ -16393,10 +16403,10 @@
       <c r="H99" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I99" s="27" t="s">
+      <c r="I99" s="26" t="s">
         <v>3063</v>
       </c>
-      <c r="J99" s="27" t="s">
+      <c r="J99" s="26" t="s">
         <v>3064</v>
       </c>
       <c r="K99" s="7" t="s">
@@ -16425,7 +16435,7 @@
       <c r="D100" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="E100" s="36" t="s">
+      <c r="E100" s="35" t="s">
         <v>3082</v>
       </c>
       <c r="F100" s="3" t="s">
@@ -16469,7 +16479,7 @@
       <c r="D101" s="13" t="s">
         <v>240</v>
       </c>
-      <c r="E101" s="36" t="s">
+      <c r="E101" s="35" t="s">
         <v>3084</v>
       </c>
       <c r="F101" s="3" t="s">
@@ -16513,7 +16523,7 @@
       <c r="D102" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="E102" s="36" t="s">
+      <c r="E102" s="35" t="s">
         <v>3085</v>
       </c>
       <c r="F102" s="3" t="s">
@@ -16525,10 +16535,10 @@
       <c r="H102" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I102" s="27" t="s">
+      <c r="I102" s="26" t="s">
         <v>3078</v>
       </c>
-      <c r="J102" s="32" t="s">
+      <c r="J102" s="31" t="s">
         <v>3079</v>
       </c>
       <c r="K102" s="7" t="s">
@@ -16557,7 +16567,7 @@
       <c r="D103" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="E103" s="36" t="s">
+      <c r="E103" s="35" t="s">
         <v>3086</v>
       </c>
       <c r="F103" s="3" t="s">
@@ -16572,7 +16582,7 @@
       <c r="I103" s="2" t="s">
         <v>3088</v>
       </c>
-      <c r="J103" s="32" t="s">
+      <c r="J103" s="31" t="s">
         <v>3089</v>
       </c>
       <c r="K103" s="7" t="s">
@@ -16601,22 +16611,22 @@
       <c r="D104" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="E104" s="36" t="s">
+      <c r="E104" s="35" t="s">
         <v>3092</v>
       </c>
       <c r="F104" s="3" t="s">
         <v>2100</v>
       </c>
-      <c r="G104" s="31" t="s">
+      <c r="G104" s="30" t="s">
         <v>3093</v>
       </c>
       <c r="H104" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I104" s="27" t="s">
+      <c r="I104" s="26" t="s">
         <v>3094</v>
       </c>
-      <c r="J104" s="32" t="s">
+      <c r="J104" s="31" t="s">
         <v>3095</v>
       </c>
       <c r="K104" s="7" t="s">
@@ -16645,22 +16655,22 @@
       <c r="D105" s="13" t="s">
         <v>520</v>
       </c>
-      <c r="E105" s="36" t="s">
+      <c r="E105" s="35" t="s">
         <v>3098</v>
       </c>
       <c r="F105" s="3" t="s">
         <v>2100</v>
       </c>
-      <c r="G105" s="31" t="s">
+      <c r="G105" s="30" t="s">
         <v>3099</v>
       </c>
       <c r="H105" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I105" s="27" t="s">
+      <c r="I105" s="26" t="s">
         <v>3100</v>
       </c>
-      <c r="J105" s="32" t="s">
+      <c r="J105" s="31" t="s">
         <v>3101</v>
       </c>
       <c r="K105" s="7" t="s">
@@ -16689,22 +16699,22 @@
       <c r="D106" s="13" t="s">
         <v>3222</v>
       </c>
-      <c r="E106" s="36" t="s">
+      <c r="E106" s="35" t="s">
         <v>3223</v>
       </c>
       <c r="F106" s="3" t="s">
         <v>2100</v>
       </c>
-      <c r="G106" s="31" t="s">
+      <c r="G106" s="30" t="s">
         <v>3224</v>
       </c>
       <c r="H106" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I106" s="27" t="s">
+      <c r="I106" s="26" t="s">
         <v>3225</v>
       </c>
-      <c r="J106" s="32" t="s">
+      <c r="J106" s="31" t="s">
         <v>3226</v>
       </c>
       <c r="K106" s="7" t="s">
@@ -16733,7 +16743,7 @@
       <c r="D107" s="13" t="s">
         <v>3222</v>
       </c>
-      <c r="E107" s="36" t="s">
+      <c r="E107" s="35" t="s">
         <v>3261</v>
       </c>
       <c r="F107" t="s">
@@ -16909,7 +16919,7 @@
       <c r="D111" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="E111" s="36" t="s">
+      <c r="E111" s="35" t="s">
         <v>3352</v>
       </c>
       <c r="F111" t="s">
@@ -16953,7 +16963,7 @@
       <c r="D112" s="20" t="s">
         <v>240</v>
       </c>
-      <c r="E112" s="36" t="s">
+      <c r="E112" s="35" t="s">
         <v>3356</v>
       </c>
       <c r="F112" t="s">
@@ -16997,7 +17007,7 @@
       <c r="D113" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="E113" s="36" t="s">
+      <c r="E113" s="35" t="s">
         <v>3360</v>
       </c>
       <c r="F113" t="s">
@@ -17041,7 +17051,7 @@
       <c r="D114" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="E114" s="36" t="s">
+      <c r="E114" s="35" t="s">
         <v>3364</v>
       </c>
       <c r="F114" t="s">
@@ -17129,7 +17139,7 @@
       <c r="D116" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="E116" s="36" t="s">
+      <c r="E116" s="35" t="s">
         <v>3454</v>
       </c>
       <c r="F116" s="3" t="s">
@@ -17173,7 +17183,7 @@
       <c r="D117" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="E117" s="36" t="s">
+      <c r="E117" s="35" t="s">
         <v>3463</v>
       </c>
       <c r="F117" s="3" t="s">
@@ -17185,10 +17195,10 @@
       <c r="H117" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I117" s="27" t="s">
+      <c r="I117" s="26" t="s">
         <v>3465</v>
       </c>
-      <c r="J117" s="27" t="s">
+      <c r="J117" s="26" t="s">
         <v>3466</v>
       </c>
       <c r="K117" s="7" t="s">
@@ -17229,10 +17239,10 @@
       <c r="H118" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I118" s="27" t="s">
+      <c r="I118" s="26" t="s">
         <v>3472</v>
       </c>
-      <c r="J118" s="32" t="s">
+      <c r="J118" s="31" t="s">
         <v>3473</v>
       </c>
       <c r="K118" s="7" t="s">
@@ -17273,10 +17283,10 @@
       <c r="H119" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I119" s="27" t="s">
+      <c r="I119" s="26" t="s">
         <v>3476</v>
       </c>
-      <c r="J119" s="32" t="s">
+      <c r="J119" s="31" t="s">
         <v>3477</v>
       </c>
       <c r="K119" s="7" t="s">
@@ -17405,10 +17415,10 @@
       <c r="H122" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I122" s="27" t="s">
+      <c r="I122" s="26" t="s">
         <v>3589</v>
       </c>
-      <c r="J122" s="27" t="s">
+      <c r="J122" s="26" t="s">
         <v>3590</v>
       </c>
       <c r="K122" s="7" t="s">
@@ -17425,7 +17435,7 @@
       </c>
     </row>
     <row r="123" spans="1:14">
-      <c r="A123" s="39" t="s">
+      <c r="A123" s="38" t="s">
         <v>3655</v>
       </c>
       <c r="B123" t="s">
@@ -17437,7 +17447,7 @@
       <c r="D123" s="13" t="s">
         <v>3222</v>
       </c>
-      <c r="E123" s="36" t="s">
+      <c r="E123" s="35" t="s">
         <v>3658</v>
       </c>
       <c r="F123" s="3" t="s">
@@ -17449,10 +17459,10 @@
       <c r="H123" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I123" s="27" t="s">
+      <c r="I123" s="26" t="s">
         <v>3660</v>
       </c>
-      <c r="J123" s="32" t="s">
+      <c r="J123" s="31" t="s">
         <v>3661</v>
       </c>
       <c r="K123" s="7" t="s">
@@ -17469,7 +17479,7 @@
       </c>
     </row>
     <row r="124" spans="1:14">
-      <c r="A124" s="39" t="s">
+      <c r="A124" s="38" t="s">
         <v>3698</v>
       </c>
       <c r="B124" s="16" t="s">
@@ -17493,10 +17503,10 @@
       <c r="H124" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I124" s="27" t="s">
+      <c r="I124" s="26" t="s">
         <v>3702</v>
       </c>
-      <c r="J124" s="32" t="s">
+      <c r="J124" s="31" t="s">
         <v>3703</v>
       </c>
       <c r="K124" s="7" t="s">
@@ -17513,7 +17523,7 @@
       </c>
     </row>
     <row r="125" spans="1:14">
-      <c r="A125" s="39" t="s">
+      <c r="A125" s="38" t="s">
         <v>3720</v>
       </c>
       <c r="B125" s="16" t="s">
@@ -17537,10 +17547,10 @@
       <c r="H125" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I125" s="27" t="s">
+      <c r="I125" s="26" t="s">
         <v>3723</v>
       </c>
-      <c r="J125" s="32" t="s">
+      <c r="J125" s="31" t="s">
         <v>3724</v>
       </c>
       <c r="K125" s="7" t="s">
@@ -17557,7 +17567,7 @@
       </c>
     </row>
     <row r="126" spans="1:14">
-      <c r="A126" s="39" t="s">
+      <c r="A126" s="38" t="s">
         <v>3739</v>
       </c>
       <c r="B126" s="16" t="s">
@@ -17569,7 +17579,7 @@
       <c r="D126" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="E126" s="36" t="s">
+      <c r="E126" s="35" t="s">
         <v>3745</v>
       </c>
       <c r="F126" s="3" t="s">
@@ -17581,10 +17591,10 @@
       <c r="H126" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I126" s="27" t="s">
+      <c r="I126" s="26" t="s">
         <v>3747</v>
       </c>
-      <c r="J126" s="27" t="s">
+      <c r="J126" s="26" t="s">
         <v>3748</v>
       </c>
       <c r="K126" s="7" t="s">
@@ -17601,7 +17611,7 @@
       </c>
     </row>
     <row r="127" spans="1:14">
-      <c r="A127" s="39" t="s">
+      <c r="A127" s="38" t="s">
         <v>3740</v>
       </c>
       <c r="B127" s="16" t="s">
@@ -17613,7 +17623,7 @@
       <c r="D127" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="E127" s="36" t="s">
+      <c r="E127" s="35" t="s">
         <v>3749</v>
       </c>
       <c r="F127" s="3" t="s">
@@ -17625,10 +17635,10 @@
       <c r="H127" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I127" s="27" t="s">
+      <c r="I127" s="26" t="s">
         <v>3751</v>
       </c>
-      <c r="J127" s="27" t="s">
+      <c r="J127" s="26" t="s">
         <v>3752</v>
       </c>
       <c r="K127" s="7" t="s">
@@ -17645,10 +17655,10 @@
       </c>
     </row>
     <row r="128" spans="1:14">
-      <c r="A128" s="39" t="s">
+      <c r="A128" s="38" t="s">
         <v>3812</v>
       </c>
-      <c r="B128" s="41" t="s">
+      <c r="B128" s="16" t="s">
         <v>3813</v>
       </c>
       <c r="C128" s="16" t="s">
@@ -17657,19 +17667,19 @@
       <c r="D128" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="E128" s="36" t="s">
+      <c r="E128" s="35" t="s">
         <v>3815</v>
       </c>
       <c r="F128" s="3" t="s">
         <v>2100</v>
       </c>
-      <c r="G128" s="43" t="s">
+      <c r="G128" s="36" t="s">
         <v>3816</v>
       </c>
       <c r="H128" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I128" s="27" t="s">
+      <c r="I128" s="26" t="s">
         <v>3817</v>
       </c>
       <c r="J128" s="2" t="s">
@@ -17689,7 +17699,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="16" type="noConversion"/>
+  <phoneticPr fontId="15" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="I22" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="I23" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
@@ -17819,46 +17829,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="D1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="E1" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="25" t="s">
+      <c r="F1" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="25" t="s">
+      <c r="G1" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="25" t="s">
+      <c r="H1" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="25" t="s">
+      <c r="I1" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="25" t="s">
+      <c r="J1" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="25" t="s">
+      <c r="K1" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="25" t="s">
+      <c r="L1" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="25" t="s">
+      <c r="M1" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="25" t="s">
+      <c r="N1" s="24" t="s">
         <v>13</v>
       </c>
     </row>
@@ -18852,10 +18862,10 @@
       <c r="H24" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I24" s="27" t="s">
+      <c r="I24" s="26" t="s">
         <v>3762</v>
       </c>
-      <c r="J24" s="32" t="s">
+      <c r="J24" s="31" t="s">
         <v>3763</v>
       </c>
       <c r="K24" t="s">
@@ -18872,7 +18882,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="16" type="noConversion"/>
+  <phoneticPr fontId="15" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="I24" r:id="rId1" xr:uid="{78311E40-7EC4-416F-9EC0-8BD29F412DF9}"/>
     <hyperlink ref="J24" r:id="rId2" xr:uid="{44368450-35A2-41A5-87EC-FE66FDA78B0D}"/>
@@ -18887,46 +18897,46 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:14" ht="14.5" customHeight="1">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="D1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="E1" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="25" t="s">
+      <c r="F1" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="25" t="s">
+      <c r="G1" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="25" t="s">
+      <c r="H1" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="25" t="s">
+      <c r="I1" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="25" t="s">
+      <c r="J1" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="25" t="s">
+      <c r="K1" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="25" t="s">
+      <c r="L1" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="25" t="s">
+      <c r="M1" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="25" t="s">
+      <c r="N1" s="24" t="s">
         <v>13</v>
       </c>
     </row>
@@ -19251,7 +19261,7 @@
       <c r="D9" s="3" t="s">
         <v>2829</v>
       </c>
-      <c r="E9" s="28" t="s">
+      <c r="E9" s="27" t="s">
         <v>2830</v>
       </c>
       <c r="F9" s="16" t="s">
@@ -19292,7 +19302,7 @@
       <c r="C10" s="16" t="s">
         <v>2786</v>
       </c>
-      <c r="D10" s="29" t="s">
+      <c r="D10" s="28" t="s">
         <v>249</v>
       </c>
       <c r="E10" s="3" t="s">
@@ -19336,7 +19346,7 @@
       <c r="C11" s="16" t="s">
         <v>2846</v>
       </c>
-      <c r="D11" s="29" t="s">
+      <c r="D11" s="28" t="s">
         <v>249</v>
       </c>
       <c r="E11" s="3" t="s">
@@ -19468,7 +19478,7 @@
       <c r="C14" s="3" t="s">
         <v>2793</v>
       </c>
-      <c r="D14" s="23" t="s">
+      <c r="D14" s="22" t="s">
         <v>59</v>
       </c>
       <c r="E14" s="3" t="s">
@@ -19926,7 +19936,7 @@
       <c r="I24" t="s">
         <v>2958</v>
       </c>
-      <c r="J24" s="32" t="s">
+      <c r="J24" s="31" t="s">
         <v>2959</v>
       </c>
       <c r="K24" s="7" t="s">
@@ -19943,7 +19953,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="16" type="noConversion"/>
+  <phoneticPr fontId="15" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="I15" r:id="rId1" xr:uid="{00000000-0004-0000-0A00-00000F000000}"/>
     <hyperlink ref="J15" r:id="rId2" xr:uid="{00000000-0004-0000-0A00-000010000000}"/>
@@ -20073,7 +20083,7 @@
       <c r="C3" s="7" t="s">
         <v>1694</v>
       </c>
-      <c r="D3" s="22">
+      <c r="D3" s="21">
         <v>1206</v>
       </c>
       <c r="E3" s="7" t="s">
@@ -20833,7 +20843,7 @@
       <c r="C20" s="16" t="s">
         <v>1692</v>
       </c>
-      <c r="D20" s="23" t="s">
+      <c r="D20" s="22" t="s">
         <v>1802</v>
       </c>
       <c r="E20" s="3" t="s">
@@ -20936,10 +20946,10 @@
       <c r="H22" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I22" s="27" t="s">
+      <c r="I22" s="26" t="s">
         <v>3718</v>
       </c>
-      <c r="J22" s="32" t="s">
+      <c r="J22" s="31" t="s">
         <v>3719</v>
       </c>
       <c r="K22" s="17" t="s">
@@ -20956,7 +20966,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="16" type="noConversion"/>
+  <phoneticPr fontId="15" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1" xr:uid="{3DE7E9B7-7F71-48BD-A43F-56652EF48515}"/>
     <hyperlink ref="I5" r:id="rId2" xr:uid="{00000000-0004-0000-0C00-000001000000}"/>
@@ -21055,13 +21065,13 @@
       <c r="H2" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I2" s="27" t="s">
+      <c r="I2" s="26" t="s">
         <v>3653</v>
       </c>
-      <c r="J2" s="32" t="s">
+      <c r="J2" s="31" t="s">
         <v>3654</v>
       </c>
-      <c r="K2" s="38" t="s">
+      <c r="K2" s="37" t="s">
         <v>3647</v>
       </c>
       <c r="L2" t="s">
@@ -21089,46 +21099,46 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="33" t="s">
+      <c r="C1" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="33" t="s">
+      <c r="D1" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="33" t="s">
+      <c r="E1" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="33" t="s">
+      <c r="F1" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="33" t="s">
+      <c r="G1" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="33" t="s">
+      <c r="H1" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="33" t="s">
+      <c r="I1" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="33" t="s">
+      <c r="J1" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="33" t="s">
+      <c r="K1" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="33" t="s">
+      <c r="L1" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="33" t="s">
+      <c r="M1" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="33" t="s">
+      <c r="N1" s="32" t="s">
         <v>13</v>
       </c>
     </row>
@@ -21166,7 +21176,7 @@
       <c r="K2" t="s">
         <v>3181</v>
       </c>
-      <c r="L2" s="34" t="s">
+      <c r="L2" s="33" t="s">
         <v>3182</v>
       </c>
       <c r="M2" t="s">
@@ -21191,46 +21201,46 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="33" t="s">
+      <c r="C1" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="33" t="s">
+      <c r="D1" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="33" t="s">
+      <c r="E1" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="33" t="s">
+      <c r="F1" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="33" t="s">
+      <c r="G1" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="33" t="s">
+      <c r="H1" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="33" t="s">
+      <c r="I1" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="33" t="s">
+      <c r="J1" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="33" t="s">
+      <c r="K1" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="33" t="s">
+      <c r="L1" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="33" t="s">
+      <c r="M1" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="33" t="s">
+      <c r="N1" s="32" t="s">
         <v>13</v>
       </c>
     </row>
@@ -21265,10 +21275,10 @@
       <c r="J2" s="2" t="s">
         <v>3038</v>
       </c>
-      <c r="K2" s="34" t="s">
+      <c r="K2" s="33" t="s">
         <v>3029</v>
       </c>
-      <c r="L2" s="34" t="s">
+      <c r="L2" s="33" t="s">
         <v>3028</v>
       </c>
       <c r="M2" t="s">
@@ -21309,13 +21319,13 @@
       <c r="J3" s="2" t="s">
         <v>3047</v>
       </c>
-      <c r="K3" s="35" t="s">
+      <c r="K3" s="34" t="s">
         <v>3048</v>
       </c>
-      <c r="L3" s="34" t="s">
+      <c r="L3" s="33" t="s">
         <v>3028</v>
       </c>
-      <c r="M3" s="35" t="s">
+      <c r="M3" s="34" t="s">
         <v>3049</v>
       </c>
       <c r="N3" t="s">
@@ -21323,7 +21333,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="16" type="noConversion"/>
+  <phoneticPr fontId="15" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1" xr:uid="{337695E5-83C1-4E9C-B69D-3A199335F765}"/>
     <hyperlink ref="J2" r:id="rId2" xr:uid="{F85761B8-F34F-4D64-BCF0-0EBE497625FF}"/>
@@ -21639,10 +21649,10 @@
       <c r="H7" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I7" s="27" t="s">
+      <c r="I7" s="26" t="s">
         <v>3626</v>
       </c>
-      <c r="J7" s="27" t="s">
+      <c r="J7" s="26" t="s">
         <v>3630</v>
       </c>
       <c r="K7" t="s">
@@ -21683,10 +21693,10 @@
       <c r="H8" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I8" s="27" t="s">
+      <c r="I8" s="26" t="s">
         <v>3772</v>
       </c>
-      <c r="J8" s="32" t="s">
+      <c r="J8" s="31" t="s">
         <v>3773</v>
       </c>
       <c r="K8" t="s">
@@ -21703,10 +21713,51 @@
       </c>
     </row>
     <row r="9" spans="1:14">
-      <c r="L9" s="21"/>
+      <c r="A9" t="s">
+        <v>3820</v>
+      </c>
+      <c r="B9" s="40" t="s">
+        <v>3821</v>
+      </c>
+      <c r="C9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1651</v>
+      </c>
+      <c r="E9" t="s">
+        <v>3822</v>
+      </c>
+      <c r="F9" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" s="39" t="s">
+        <v>3823</v>
+      </c>
+      <c r="H9" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" s="26" t="s">
+        <v>3824</v>
+      </c>
+      <c r="J9" s="31" t="s">
+        <v>3825</v>
+      </c>
+      <c r="K9" t="s">
+        <v>3819</v>
+      </c>
+      <c r="L9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M9" t="s">
+        <v>1651</v>
+      </c>
+      <c r="N9" t="s">
+        <v>25</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="16" type="noConversion"/>
+  <phoneticPr fontId="15" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="J2" r:id="rId1" xr:uid="{78125F11-BE4E-4312-8E61-0550889BB81F}"/>
     <hyperlink ref="I2" r:id="rId2" xr:uid="{1CFCC581-B5E5-4159-8EE1-35A941FCD4DF}"/>
@@ -21716,9 +21767,11 @@
     <hyperlink ref="I7" r:id="rId6" xr:uid="{4EE7BCCF-17ED-4BF0-90C6-97AD9B6D2A45}"/>
     <hyperlink ref="I8" r:id="rId7" xr:uid="{5DA62FDE-E136-4C6E-84DA-50C789567BAA}"/>
     <hyperlink ref="J8" r:id="rId8" xr:uid="{802F32D1-101A-4CE0-9BF6-8EBCFB56FF87}"/>
+    <hyperlink ref="I9" r:id="rId9" xr:uid="{964E2DD8-5B7E-493E-BED7-E37B35A0CC86}"/>
+    <hyperlink ref="J9" r:id="rId10" xr:uid="{15D18AE1-0363-41F6-90C3-E5A099B4FCCB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId9"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId11"/>
 </worksheet>
 </file>
 
@@ -21782,46 +21835,46 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="33" t="s">
+      <c r="C1" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="33" t="s">
+      <c r="D1" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="33" t="s">
+      <c r="E1" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="33" t="s">
+      <c r="F1" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="33" t="s">
+      <c r="G1" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="33" t="s">
+      <c r="H1" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="33" t="s">
+      <c r="I1" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="33" t="s">
+      <c r="J1" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="33" t="s">
+      <c r="K1" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="33" t="s">
+      <c r="L1" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="33" t="s">
+      <c r="M1" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="33" t="s">
+      <c r="N1" s="32" t="s">
         <v>13</v>
       </c>
     </row>
@@ -22028,7 +22081,7 @@
       <c r="D4" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="36" t="s">
+      <c r="E4" s="35" t="s">
         <v>3775</v>
       </c>
       <c r="F4" s="3" t="s">
@@ -22043,16 +22096,16 @@
       <c r="I4" s="2" t="s">
         <v>3777</v>
       </c>
-      <c r="J4" s="32" t="s">
+      <c r="J4" s="31" t="s">
         <v>3778</v>
       </c>
-      <c r="K4" s="36" t="s">
+      <c r="K4" s="35" t="s">
         <v>3779</v>
       </c>
       <c r="L4" t="s">
         <v>3276</v>
       </c>
-      <c r="M4" s="36" t="s">
+      <c r="M4" s="35" t="s">
         <v>3779</v>
       </c>
       <c r="N4" t="s">
@@ -22060,7 +22113,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="16" type="noConversion"/>
+  <phoneticPr fontId="15" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1" xr:uid="{BFD1D0BA-D934-44C0-B127-7693B6B8FCF4}"/>
     <hyperlink ref="J2" r:id="rId2" xr:uid="{72343140-B075-45AB-91DC-7B87E10B2AD1}"/>
@@ -22138,7 +22191,7 @@
       <c r="D2" t="s">
         <v>2909</v>
       </c>
-      <c r="E2" s="36" t="s">
+      <c r="E2" s="35" t="s">
         <v>3205</v>
       </c>
       <c r="F2" t="s">
@@ -22182,7 +22235,7 @@
       <c r="D3" t="s">
         <v>3204</v>
       </c>
-      <c r="E3" s="36" t="s">
+      <c r="E3" s="35" t="s">
         <v>3206</v>
       </c>
       <c r="F3" t="s">
@@ -22214,7 +22267,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="16" type="noConversion"/>
+  <phoneticPr fontId="15" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1" xr:uid="{BB2EDAB8-75EB-46D2-BA14-384BF06E1A6E}"/>
     <hyperlink ref="I3" r:id="rId2" xr:uid="{8F6B3EB5-F217-4353-ABA9-F461982FB5ED}"/>
@@ -22362,7 +22415,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="16" type="noConversion"/>
+  <phoneticPr fontId="15" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1" xr:uid="{0AE24270-4D5D-4E12-981B-AA2533208AEE}"/>
     <hyperlink ref="J2" r:id="rId2" xr:uid="{339478FA-7B81-4702-B5E2-22F306F57121}"/>
@@ -22822,7 +22875,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="16" type="noConversion"/>
+  <phoneticPr fontId="15" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1" xr:uid="{08280A44-0F58-4FDE-B5FD-3A95A0F423CB}"/>
     <hyperlink ref="J2" r:id="rId2" xr:uid="{85F326FF-BAE0-4072-815D-1EE4E7995C53}"/>
@@ -22847,49 +22900,49 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:15">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="33" t="s">
+      <c r="C1" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="33" t="s">
+      <c r="D1" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="33" t="s">
+      <c r="E1" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="33" t="s">
+      <c r="F1" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="33" t="s">
+      <c r="G1" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="33" t="s">
+      <c r="H1" s="32" t="s">
         <v>3019</v>
       </c>
-      <c r="I1" s="33" t="s">
+      <c r="I1" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="33" t="s">
+      <c r="J1" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="33" t="s">
+      <c r="K1" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="33" t="s">
+      <c r="L1" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="33" t="s">
+      <c r="M1" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="33" t="s">
+      <c r="N1" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="33" t="s">
+      <c r="O1" s="32" t="s">
         <v>13</v>
       </c>
     </row>
@@ -22988,7 +23041,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="16" type="noConversion"/>
+  <phoneticPr fontId="15" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="J2" r:id="rId1" xr:uid="{F8A04A1C-92B7-4CCD-8C95-726A110347D5}"/>
     <hyperlink ref="K2" r:id="rId2" xr:uid="{2F912663-1CD4-41BE-AE9B-6D2CA04D31B2}"/>
@@ -24093,46 +24146,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="D1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="E1" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="25" t="s">
+      <c r="F1" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="25" t="s">
+      <c r="G1" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="25" t="s">
+      <c r="H1" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="25" t="s">
+      <c r="I1" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="25" t="s">
+      <c r="J1" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="25" t="s">
+      <c r="K1" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="25" t="s">
+      <c r="L1" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="25" t="s">
+      <c r="M1" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="25" t="s">
+      <c r="N1" s="24" t="s">
         <v>13</v>
       </c>
     </row>
@@ -24513,10 +24566,10 @@
       <c r="H10" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="I10" s="26" t="s">
+      <c r="I10" s="25" t="s">
         <v>2241</v>
       </c>
-      <c r="J10" s="26" t="s">
+      <c r="J10" s="25" t="s">
         <v>2242</v>
       </c>
       <c r="K10" s="7" t="s">
@@ -25877,10 +25930,10 @@
       <c r="H41" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="I41" s="26" t="s">
+      <c r="I41" s="25" t="s">
         <v>2241</v>
       </c>
-      <c r="J41" s="26" t="s">
+      <c r="J41" s="25" t="s">
         <v>2242</v>
       </c>
       <c r="K41" s="7" t="s">
@@ -26493,7 +26546,7 @@
       <c r="H55" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I55" s="27" t="s">
+      <c r="I55" s="26" t="s">
         <v>2581</v>
       </c>
       <c r="J55" t="s">
@@ -26537,7 +26590,7 @@
       <c r="H56" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I56" s="27" t="s">
+      <c r="I56" s="26" t="s">
         <v>2592</v>
       </c>
       <c r="J56" s="2" t="s">
@@ -26581,7 +26634,7 @@
       <c r="H57" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I57" s="27" t="s">
+      <c r="I57" s="26" t="s">
         <v>2594</v>
       </c>
       <c r="J57" s="2" t="s">
@@ -26613,13 +26666,13 @@
       <c r="D58" s="16" t="s">
         <v>2883</v>
       </c>
-      <c r="E58" s="30">
+      <c r="E58" s="29">
         <v>657012240101</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>2100</v>
       </c>
-      <c r="G58" s="30">
+      <c r="G58" s="29">
         <v>657012240101</v>
       </c>
       <c r="H58" s="3" t="s">
@@ -26631,13 +26684,13 @@
       <c r="J58" t="s">
         <v>2885</v>
       </c>
-      <c r="K58" s="31" t="s">
+      <c r="K58" s="30" t="s">
         <v>2895</v>
       </c>
       <c r="L58" s="7" t="s">
         <v>2572</v>
       </c>
-      <c r="M58" s="30">
+      <c r="M58" s="29">
         <v>657012240101</v>
       </c>
       <c r="N58" s="7" t="s">
@@ -26657,13 +26710,13 @@
       <c r="D59" s="16" t="s">
         <v>2883</v>
       </c>
-      <c r="E59" s="30">
+      <c r="E59" s="29">
         <v>657012250201</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>2100</v>
       </c>
-      <c r="G59" s="30">
+      <c r="G59" s="29">
         <v>657012250201</v>
       </c>
       <c r="H59" s="3" t="s">
@@ -26681,7 +26734,7 @@
       <c r="L59" s="7" t="s">
         <v>2572</v>
       </c>
-      <c r="M59" s="30">
+      <c r="M59" s="29">
         <v>657012250201</v>
       </c>
       <c r="N59" s="7" t="s">
@@ -26701,13 +26754,13 @@
       <c r="D60" s="16" t="s">
         <v>2883</v>
       </c>
-      <c r="E60" s="30">
+      <c r="E60" s="29">
         <v>657004140101</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>2100</v>
       </c>
-      <c r="G60" s="30">
+      <c r="G60" s="29">
         <v>657004140101</v>
       </c>
       <c r="H60" s="3" t="s">
@@ -26719,13 +26772,13 @@
       <c r="J60" t="s">
         <v>2889</v>
       </c>
-      <c r="K60" s="31" t="s">
+      <c r="K60" s="30" t="s">
         <v>2416</v>
       </c>
       <c r="L60" s="7" t="s">
         <v>2572</v>
       </c>
-      <c r="M60" s="30">
+      <c r="M60" s="29">
         <v>657004140101</v>
       </c>
       <c r="N60" s="7" t="s">
@@ -26745,13 +26798,13 @@
       <c r="D61" s="16" t="s">
         <v>2883</v>
       </c>
-      <c r="E61" s="30">
+      <c r="E61" s="29">
         <v>657004150201</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>2100</v>
       </c>
-      <c r="G61" s="30">
+      <c r="G61" s="29">
         <v>657004150201</v>
       </c>
       <c r="H61" s="3" t="s">
@@ -26769,7 +26822,7 @@
       <c r="L61" s="7" t="s">
         <v>2572</v>
       </c>
-      <c r="M61" s="30">
+      <c r="M61" s="29">
         <v>657004150201</v>
       </c>
       <c r="N61" s="7" t="s">
@@ -26889,7 +26942,7 @@
       <c r="H64" t="s">
         <v>21</v>
       </c>
-      <c r="I64" s="27" t="s">
+      <c r="I64" s="26" t="s">
         <v>3287</v>
       </c>
       <c r="J64" s="2" t="s">
@@ -26901,7 +26954,7 @@
       <c r="L64" s="7" t="s">
         <v>2572</v>
       </c>
-      <c r="M64" s="30">
+      <c r="M64" s="29">
         <v>7461090</v>
       </c>
       <c r="N64" s="7" t="s">
@@ -26921,7 +26974,7 @@
       <c r="D65" s="16" t="s">
         <v>3553</v>
       </c>
-      <c r="E65" s="36" t="s">
+      <c r="E65" s="35" t="s">
         <v>3554</v>
       </c>
       <c r="F65" t="s">
@@ -26945,7 +26998,7 @@
       <c r="L65" s="7" t="s">
         <v>2572</v>
       </c>
-      <c r="M65" s="36">
+      <c r="M65" s="35">
         <v>7461117</v>
       </c>
       <c r="N65" s="7" t="s">
@@ -26977,10 +27030,10 @@
       <c r="H66" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I66" s="27" t="s">
+      <c r="I66" s="26" t="s">
         <v>3689</v>
       </c>
-      <c r="J66" s="32" t="s">
+      <c r="J66" s="31" t="s">
         <v>3690</v>
       </c>
       <c r="K66" s="17" t="s">
@@ -27021,13 +27074,13 @@
       <c r="H67" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I67" s="27" t="s">
+      <c r="I67" s="26" t="s">
         <v>3258</v>
       </c>
-      <c r="J67" s="32" t="s">
+      <c r="J67" s="31" t="s">
         <v>3733</v>
       </c>
-      <c r="K67" s="31" t="s">
+      <c r="K67" s="30" t="s">
         <v>2416</v>
       </c>
       <c r="L67" s="7" t="s">
@@ -27065,10 +27118,10 @@
       <c r="H68" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I68" s="27" t="s">
+      <c r="I68" s="26" t="s">
         <v>3737</v>
       </c>
-      <c r="J68" s="32" t="s">
+      <c r="J68" s="31" t="s">
         <v>3738</v>
       </c>
       <c r="K68" s="7" t="s">
@@ -27085,7 +27138,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="16" type="noConversion"/>
+  <phoneticPr fontId="15" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="J3" r:id="rId1" xr:uid="{00000000-0004-0000-1D00-000000000000}"/>
     <hyperlink ref="I7" r:id="rId2" xr:uid="{00000000-0004-0000-1D00-000001000000}"/>
@@ -27218,7 +27271,7 @@
       <c r="D2" t="s">
         <v>3214</v>
       </c>
-      <c r="E2" s="36" t="s">
+      <c r="E2" s="35" t="s">
         <v>3215</v>
       </c>
       <c r="F2" t="s">
@@ -27274,10 +27327,10 @@
       <c r="H3" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="27" t="s">
+      <c r="I3" s="26" t="s">
         <v>3490</v>
       </c>
-      <c r="J3" s="27" t="s">
+      <c r="J3" s="26" t="s">
         <v>3491</v>
       </c>
       <c r="K3" s="7" t="s">
@@ -27294,7 +27347,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="16" type="noConversion"/>
+  <phoneticPr fontId="15" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1" xr:uid="{A3195937-552B-4025-8C26-81ADB44BFFC2}"/>
     <hyperlink ref="J2" r:id="rId2" xr:uid="{52A98722-6674-4772-ABA0-DFA6125FAC08}"/>
@@ -32781,7 +32834,7 @@
       <c r="C125" s="17" t="s">
         <v>1559</v>
       </c>
-      <c r="D125" s="37" t="s">
+      <c r="D125" s="36" t="s">
         <v>3231</v>
       </c>
       <c r="E125" s="17" t="s">
@@ -33456,10 +33509,10 @@
       <c r="H140" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I140" s="27" t="s">
+      <c r="I140" s="26" t="s">
         <v>2941</v>
       </c>
-      <c r="J140" s="27" t="s">
+      <c r="J140" s="26" t="s">
         <v>2942</v>
       </c>
       <c r="K140" s="7" t="s">
@@ -33576,7 +33629,7 @@
       <c r="D143" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="E143" s="29" t="s">
+      <c r="E143" s="28" t="s">
         <v>3106</v>
       </c>
       <c r="F143" s="17" t="s">
@@ -33588,10 +33641,10 @@
       <c r="H143" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I143" s="27" t="s">
+      <c r="I143" s="26" t="s">
         <v>3108</v>
       </c>
-      <c r="J143" s="27" t="s">
+      <c r="J143" s="26" t="s">
         <v>3109</v>
       </c>
       <c r="K143" s="17" t="s">
@@ -33620,7 +33673,7 @@
       <c r="D144" s="20" t="s">
         <v>240</v>
       </c>
-      <c r="E144" s="29" t="s">
+      <c r="E144" s="28" t="s">
         <v>3112</v>
       </c>
       <c r="F144" s="17" t="s">
@@ -33632,10 +33685,10 @@
       <c r="H144" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I144" s="27" t="s">
+      <c r="I144" s="26" t="s">
         <v>3114</v>
       </c>
-      <c r="J144" s="32" t="s">
+      <c r="J144" s="31" t="s">
         <v>3115</v>
       </c>
       <c r="K144" s="17" t="s">
@@ -33664,7 +33717,7 @@
       <c r="D145" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="E145" s="29" t="s">
+      <c r="E145" s="28" t="s">
         <v>3118</v>
       </c>
       <c r="F145" s="17" t="s">
@@ -33676,10 +33729,10 @@
       <c r="H145" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I145" s="27" t="s">
+      <c r="I145" s="26" t="s">
         <v>3120</v>
       </c>
-      <c r="J145" s="32" t="s">
+      <c r="J145" s="31" t="s">
         <v>3121</v>
       </c>
       <c r="K145" s="17" t="s">
@@ -33708,7 +33761,7 @@
       <c r="D146" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="E146" s="29" t="s">
+      <c r="E146" s="28" t="s">
         <v>3124</v>
       </c>
       <c r="F146" s="17" t="s">
@@ -33720,7 +33773,7 @@
       <c r="H146" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I146" s="27" t="s">
+      <c r="I146" s="26" t="s">
         <v>3126</v>
       </c>
       <c r="J146" t="s">
@@ -33752,7 +33805,7 @@
       <c r="D147" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="E147" s="29" t="s">
+      <c r="E147" s="28" t="s">
         <v>3135</v>
       </c>
       <c r="F147" s="17" t="s">
@@ -33764,10 +33817,10 @@
       <c r="H147" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I147" s="27" t="s">
+      <c r="I147" s="26" t="s">
         <v>3137</v>
       </c>
-      <c r="J147" s="27" t="s">
+      <c r="J147" s="26" t="s">
         <v>3132</v>
       </c>
       <c r="K147" s="17" t="s">
@@ -33796,7 +33849,7 @@
       <c r="D148" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="E148" s="36" t="s">
+      <c r="E148" s="35" t="s">
         <v>3140</v>
       </c>
       <c r="F148" s="17" t="s">
@@ -33808,10 +33861,10 @@
       <c r="H148" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I148" s="27" t="s">
+      <c r="I148" s="26" t="s">
         <v>3142</v>
       </c>
-      <c r="J148" s="32" t="s">
+      <c r="J148" s="31" t="s">
         <v>3143</v>
       </c>
       <c r="K148" s="17" t="s">
@@ -33852,10 +33905,10 @@
       <c r="H149" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I149" s="27" t="s">
+      <c r="I149" s="26" t="s">
         <v>3147</v>
       </c>
-      <c r="J149" s="32" t="s">
+      <c r="J149" s="31" t="s">
         <v>3148</v>
       </c>
       <c r="K149" s="17" t="s">
@@ -33896,10 +33949,10 @@
       <c r="H150" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I150" s="27" t="s">
+      <c r="I150" s="26" t="s">
         <v>3153</v>
       </c>
-      <c r="J150" s="32" t="s">
+      <c r="J150" s="31" t="s">
         <v>3154</v>
       </c>
       <c r="K150" s="17" t="s">
@@ -33940,10 +33993,10 @@
       <c r="H151" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I151" s="27" t="s">
+      <c r="I151" s="26" t="s">
         <v>3234</v>
       </c>
-      <c r="J151" s="32" t="s">
+      <c r="J151" s="31" t="s">
         <v>3235</v>
       </c>
       <c r="K151" s="17" t="s">
@@ -33984,7 +34037,7 @@
       <c r="H152" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I152" s="27" t="s">
+      <c r="I152" s="26" t="s">
         <v>2928</v>
       </c>
       <c r="J152" t="s">
@@ -34028,10 +34081,10 @@
       <c r="H153" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I153" s="27" t="s">
+      <c r="I153" s="26" t="s">
         <v>2928</v>
       </c>
-      <c r="J153" s="27" t="s">
+      <c r="J153" s="26" t="s">
         <v>3247</v>
       </c>
       <c r="K153" s="17" t="s">
@@ -34192,7 +34245,7 @@
       <c r="D157" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="E157" s="36" t="s">
+      <c r="E157" s="35" t="s">
         <v>3377</v>
       </c>
       <c r="F157" t="s">
@@ -34236,7 +34289,7 @@
       <c r="D158" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="E158" s="36" t="s">
+      <c r="E158" s="35" t="s">
         <v>3382</v>
       </c>
       <c r="F158" t="s">
@@ -34336,7 +34389,7 @@
       <c r="H160" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I160" s="27" t="s">
+      <c r="I160" s="26" t="s">
         <v>3446</v>
       </c>
       <c r="J160" t="s">
@@ -34368,7 +34421,7 @@
       <c r="D161" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="E161" s="36" t="s">
+      <c r="E161" s="35" t="s">
         <v>3106</v>
       </c>
       <c r="F161" s="16" t="s">
@@ -34380,10 +34433,10 @@
       <c r="H161" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I161" s="27" t="s">
+      <c r="I161" s="26" t="s">
         <v>3108</v>
       </c>
-      <c r="J161" s="27" t="s">
+      <c r="J161" s="26" t="s">
         <v>3109</v>
       </c>
       <c r="K161" s="17" t="s">
@@ -34424,10 +34477,10 @@
       <c r="H162" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I162" s="27" t="s">
+      <c r="I162" s="26" t="s">
         <v>3516</v>
       </c>
-      <c r="J162" s="32" t="s">
+      <c r="J162" s="31" t="s">
         <v>3517</v>
       </c>
       <c r="K162" s="17" t="s">
@@ -34468,10 +34521,10 @@
       <c r="H163" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I163" s="27" t="s">
+      <c r="I163" s="26" t="s">
         <v>3344</v>
       </c>
-      <c r="J163" s="32" t="s">
+      <c r="J163" s="31" t="s">
         <v>3520</v>
       </c>
       <c r="K163" s="17" t="s">
@@ -34512,10 +34565,10 @@
       <c r="H164" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I164" s="27" t="s">
+      <c r="I164" s="26" t="s">
         <v>3524</v>
       </c>
-      <c r="J164" s="32" t="s">
+      <c r="J164" s="31" t="s">
         <v>3525</v>
       </c>
       <c r="K164" s="17" t="s">
@@ -34600,10 +34653,10 @@
       <c r="H166" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I166" s="27" t="s">
+      <c r="I166" s="26" t="s">
         <v>3549</v>
       </c>
-      <c r="J166" s="32" t="s">
+      <c r="J166" s="31" t="s">
         <v>3550</v>
       </c>
       <c r="K166" s="17" t="s">
@@ -34688,10 +34741,10 @@
       <c r="H168" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I168" s="27" t="s">
+      <c r="I168" s="26" t="s">
         <v>3344</v>
       </c>
-      <c r="J168" s="27" t="s">
+      <c r="J168" s="26" t="s">
         <v>3577</v>
       </c>
       <c r="K168" s="17" t="s">
@@ -34732,7 +34785,7 @@
       <c r="H169" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I169" s="27" t="s">
+      <c r="I169" s="26" t="s">
         <v>3344</v>
       </c>
       <c r="J169" t="s">
@@ -34808,7 +34861,7 @@
       <c r="D171" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="E171" s="36" t="s">
+      <c r="E171" s="35" t="s">
         <v>3597</v>
       </c>
       <c r="F171" s="3" t="s">
@@ -34852,7 +34905,7 @@
       <c r="D172" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="E172" s="36" t="s">
+      <c r="E172" s="35" t="s">
         <v>3601</v>
       </c>
       <c r="F172" s="3" t="s">
@@ -34864,7 +34917,7 @@
       <c r="H172" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I172" s="27" t="s">
+      <c r="I172" s="26" t="s">
         <v>3603</v>
       </c>
       <c r="J172" s="2" t="s">
@@ -34896,7 +34949,7 @@
       <c r="D173" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="E173" s="36" t="s">
+      <c r="E173" s="35" t="s">
         <v>3613</v>
       </c>
       <c r="F173" s="3" t="s">
@@ -34996,10 +35049,10 @@
       <c r="H175" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I175" s="27" t="s">
+      <c r="I175" s="26" t="s">
         <v>2941</v>
       </c>
-      <c r="J175" s="27" t="s">
+      <c r="J175" s="26" t="s">
         <v>3641</v>
       </c>
       <c r="K175" s="17" t="s">
@@ -35084,10 +35137,10 @@
       <c r="H177" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I177" s="27" t="s">
+      <c r="I177" s="26" t="s">
         <v>3619</v>
       </c>
-      <c r="J177" s="32" t="s">
+      <c r="J177" s="31" t="s">
         <v>3674</v>
       </c>
       <c r="K177" s="17" t="s">
@@ -35116,7 +35169,7 @@
       <c r="D178" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="E178" s="36" t="s">
+      <c r="E178" s="35" t="s">
         <v>3755</v>
       </c>
       <c r="F178" s="3" t="s">
@@ -35128,7 +35181,7 @@
       <c r="H178" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I178" s="27" t="s">
+      <c r="I178" s="26" t="s">
         <v>3757</v>
       </c>
       <c r="J178" t="s">
@@ -35172,7 +35225,7 @@
       <c r="H179" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I179" s="27" t="s">
+      <c r="I179" s="26" t="s">
         <v>3786</v>
       </c>
       <c r="J179" s="2" t="s">
@@ -35216,10 +35269,10 @@
       <c r="H180" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I180" s="27" t="s">
+      <c r="I180" s="26" t="s">
         <v>3792</v>
       </c>
-      <c r="J180" s="32" t="s">
+      <c r="J180" s="31" t="s">
         <v>3793</v>
       </c>
       <c r="K180" s="17" t="s">
@@ -35251,16 +35304,16 @@
       <c r="E181" t="s">
         <v>3797</v>
       </c>
-      <c r="F181" s="40" t="s">
+      <c r="F181" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="G181" s="40" t="s">
+      <c r="G181" s="3" t="s">
         <v>3798</v>
       </c>
-      <c r="H181" s="41" t="s">
+      <c r="H181" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I181" s="27" t="s">
+      <c r="I181" s="26" t="s">
         <v>2941</v>
       </c>
       <c r="K181" s="17" t="s">
@@ -35280,7 +35333,7 @@
       <c r="A182" s="16" t="s">
         <v>3799</v>
       </c>
-      <c r="B182" s="41" t="s">
+      <c r="B182" s="16" t="s">
         <v>3801</v>
       </c>
       <c r="C182" s="16" t="s">
@@ -35289,22 +35342,22 @@
       <c r="D182" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="E182" s="41" t="s">
+      <c r="E182" s="16" t="s">
         <v>3802</v>
       </c>
-      <c r="F182" s="42" t="s">
+      <c r="F182" s="30" t="s">
         <v>3311</v>
       </c>
-      <c r="G182" s="42" t="s">
+      <c r="G182" s="30" t="s">
         <v>3803</v>
       </c>
-      <c r="H182" s="41" t="s">
+      <c r="H182" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I182" s="27" t="s">
+      <c r="I182" s="26" t="s">
         <v>3804</v>
       </c>
-      <c r="J182" s="27" t="s">
+      <c r="J182" s="26" t="s">
         <v>3805</v>
       </c>
       <c r="K182" s="17" t="s">
@@ -35324,7 +35377,7 @@
       <c r="A183" s="16" t="s">
         <v>3806</v>
       </c>
-      <c r="B183" s="41" t="s">
+      <c r="B183" s="16" t="s">
         <v>3807</v>
       </c>
       <c r="C183" s="16" t="s">
@@ -35333,22 +35386,22 @@
       <c r="D183" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="E183" s="41" t="s">
+      <c r="E183" s="16" t="s">
         <v>3809</v>
       </c>
-      <c r="F183" s="42" t="s">
+      <c r="F183" s="30" t="s">
         <v>3311</v>
       </c>
-      <c r="G183" s="42" t="s">
+      <c r="G183" s="30" t="s">
         <v>3810</v>
       </c>
-      <c r="H183" s="41" t="s">
+      <c r="H183" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I183" s="27" t="s">
+      <c r="I183" s="26" t="s">
         <v>3644</v>
       </c>
-      <c r="J183" s="32" t="s">
+      <c r="J183" s="31" t="s">
         <v>3811</v>
       </c>
       <c r="K183" s="17" t="s">
@@ -35368,7 +35421,7 @@
       <c r="A184" s="16"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="16" type="noConversion"/>
+  <phoneticPr fontId="15" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="J5" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
     <hyperlink ref="I20" r:id="rId2" xr:uid="{00000000-0004-0000-0400-000001000000}"/>
@@ -35728,7 +35781,7 @@
       <c r="D5" t="s">
         <v>36</v>
       </c>
-      <c r="E5" s="36" t="s">
+      <c r="E5" s="35" t="s">
         <v>3158</v>
       </c>
       <c r="F5" t="s">
@@ -35760,7 +35813,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="16" type="noConversion"/>
+  <phoneticPr fontId="15" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1" xr:uid="{9FEE5192-80A9-4D8D-B0ED-453C4A95B2F9}"/>
     <hyperlink ref="J2" r:id="rId2" xr:uid="{40967CA2-E6AE-4524-9EF5-66E92DD6A7B6}"/>
@@ -35835,7 +35888,7 @@
       <c r="D2" t="s">
         <v>3409</v>
       </c>
-      <c r="E2" s="36" t="s">
+      <c r="E2" s="35" t="s">
         <v>3398</v>
       </c>
       <c r="F2" t="s">
@@ -35879,7 +35932,7 @@
       <c r="D3" t="s">
         <v>3414</v>
       </c>
-      <c r="E3" s="36" t="s">
+      <c r="E3" s="35" t="s">
         <v>3402</v>
       </c>
       <c r="F3" t="s">
@@ -35923,7 +35976,7 @@
       <c r="D4" t="s">
         <v>3707</v>
       </c>
-      <c r="E4" s="36" t="s">
+      <c r="E4" s="35" t="s">
         <v>3709</v>
       </c>
       <c r="F4" s="3" t="s">
@@ -35935,10 +35988,10 @@
       <c r="H4" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="27" t="s">
+      <c r="I4" s="26" t="s">
         <v>3711</v>
       </c>
-      <c r="J4" s="32" t="s">
+      <c r="J4" s="31" t="s">
         <v>3712</v>
       </c>
       <c r="K4" t="s">
@@ -35955,7 +36008,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="16" type="noConversion"/>
+  <phoneticPr fontId="15" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1" xr:uid="{07883802-B058-47F9-BBB3-C06E82952829}"/>
     <hyperlink ref="J2" r:id="rId2" xr:uid="{62DD0F89-540D-4537-B7A5-4B172FA10C23}"/>
@@ -36068,10 +36121,10 @@
       <c r="B3" s="3" t="s">
         <v>3494</v>
       </c>
-      <c r="C3" s="31" t="s">
+      <c r="C3" s="30" t="s">
         <v>3495</v>
       </c>
-      <c r="D3" s="31" t="s">
+      <c r="D3" s="30" t="s">
         <v>3496</v>
       </c>
       <c r="E3" t="s">
@@ -36086,10 +36139,10 @@
       <c r="H3" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="27" t="s">
+      <c r="I3" s="26" t="s">
         <v>3499</v>
       </c>
-      <c r="J3" s="32" t="s">
+      <c r="J3" s="31" t="s">
         <v>3500</v>
       </c>
       <c r="K3" t="s">
@@ -36106,7 +36159,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="16" type="noConversion"/>
+  <phoneticPr fontId="15" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1" xr:uid="{1A9E4CB0-A8E7-4FC1-A9A7-FA5E28311F4C}"/>
     <hyperlink ref="I3" r:id="rId2" xr:uid="{56FF5CE4-5A16-43B7-A444-8540568671A8}"/>
@@ -36172,7 +36225,7 @@
       <c r="B2" s="7" t="s">
         <v>1833</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="23" t="s">
         <v>1834</v>
       </c>
       <c r="D2" s="7" t="s">
@@ -36534,46 +36587,46 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:14" ht="16" customHeight="1">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="D1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="E1" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="25" t="s">
+      <c r="F1" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="25" t="s">
+      <c r="G1" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="25" t="s">
+      <c r="H1" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="25" t="s">
+      <c r="I1" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="25" t="s">
+      <c r="J1" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="25" t="s">
+      <c r="K1" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="25" t="s">
+      <c r="L1" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="25" t="s">
+      <c r="M1" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="25" t="s">
+      <c r="N1" s="24" t="s">
         <v>13</v>
       </c>
     </row>
@@ -36734,10 +36787,10 @@
       <c r="H5" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="I5" s="26" t="s">
+      <c r="I5" s="25" t="s">
         <v>1941</v>
       </c>
-      <c r="J5" s="26" t="s">
+      <c r="J5" s="25" t="s">
         <v>1942</v>
       </c>
       <c r="K5" s="7" t="s">
@@ -37089,7 +37142,7 @@
       <c r="I13" t="s">
         <v>2993</v>
       </c>
-      <c r="J13" s="27" t="s">
+      <c r="J13" s="26" t="s">
         <v>2992</v>
       </c>
       <c r="K13" s="7" t="s">
@@ -37130,10 +37183,10 @@
       <c r="H14" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I14" s="27" t="s">
+      <c r="I14" s="26" t="s">
         <v>3696</v>
       </c>
-      <c r="J14" s="32" t="s">
+      <c r="J14" s="31" t="s">
         <v>3697</v>
       </c>
       <c r="K14" s="7" t="s">
@@ -37150,7 +37203,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="16" type="noConversion"/>
+  <phoneticPr fontId="15" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="I3" r:id="rId1" xr:uid="{00000000-0004-0000-0900-000000000000}"/>
     <hyperlink ref="I5" r:id="rId2" xr:uid="{00000000-0004-0000-0900-000001000000}"/>

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F25D5F6-3FD0-477A-BD8D-51CA3D725368}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65CDDEA2-A327-4738-9EA6-12A5E0F91C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26532" yWindow="2268" windowWidth="16200" windowHeight="9972" firstSheet="14" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="1596" windowWidth="23256" windowHeight="12456" firstSheet="19" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7690" uniqueCount="3826">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7704" uniqueCount="3834">
   <si>
     <t>ID</t>
   </si>
@@ -11526,6 +11526,30 @@
   </si>
   <si>
     <t>https://www.mouser.es/ProductDetail/Texas-Instruments/ADS1015IDGSR?qs=IK5e5L0zOXhCrFZ0pftZqw%3D%3D</t>
+  </si>
+  <si>
+    <t>110-0068</t>
+  </si>
+  <si>
+    <t>Alojamientos de cables y cabecera XH HEADER (TOP)</t>
+  </si>
+  <si>
+    <t>4p</t>
+  </si>
+  <si>
+    <t>THT 2,5mm</t>
+  </si>
+  <si>
+    <t>B4B-XH-A-BK(LF)(SN)</t>
+  </si>
+  <si>
+    <t>306-B4BXHABKLFSN</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/datasheet/3/1070/1/eXH.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/JST-Commercial/B4B-XH-A-BKLFSN?qs=cIziFXvMxOXLG2L7xSRqLw%3D%3D</t>
   </si>
 </sst>
 </file>
@@ -21716,7 +21740,7 @@
       <c r="A9" t="s">
         <v>3820</v>
       </c>
-      <c r="B9" s="40" t="s">
+      <c r="B9" s="16" t="s">
         <v>3821</v>
       </c>
       <c r="C9" t="s">
@@ -21728,13 +21752,13 @@
       <c r="E9" t="s">
         <v>3822</v>
       </c>
-      <c r="F9" s="39" t="s">
+      <c r="F9" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G9" s="39" t="s">
+      <c r="G9" s="3" t="s">
         <v>3823</v>
       </c>
-      <c r="H9" s="40" t="s">
+      <c r="H9" s="16" t="s">
         <v>21</v>
       </c>
       <c r="I9" s="26" t="s">
@@ -24137,7 +24161,7 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE14AD29-8DB0-4C42-AB91-A73B867AE121}">
-  <dimension ref="A1:N68"/>
+  <dimension ref="A1:N69"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="5" max="5" width="16.36328125" bestFit="1" customWidth="1"/>
@@ -27134,6 +27158,50 @@
         <v>2472</v>
       </c>
       <c r="N68" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14">
+      <c r="A69" s="16" t="s">
+        <v>3826</v>
+      </c>
+      <c r="B69" s="40" t="s">
+        <v>3827</v>
+      </c>
+      <c r="C69" s="40" t="s">
+        <v>3828</v>
+      </c>
+      <c r="D69" s="16" t="s">
+        <v>3829</v>
+      </c>
+      <c r="E69" s="40" t="s">
+        <v>3830</v>
+      </c>
+      <c r="F69" s="39" t="s">
+        <v>2172</v>
+      </c>
+      <c r="G69" s="39" t="s">
+        <v>3831</v>
+      </c>
+      <c r="H69" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>3832</v>
+      </c>
+      <c r="J69" s="31" t="s">
+        <v>3833</v>
+      </c>
+      <c r="K69" s="17" t="s">
+        <v>2464</v>
+      </c>
+      <c r="L69" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M69" s="40" t="s">
+        <v>3830</v>
+      </c>
+      <c r="N69" s="7" t="s">
         <v>25</v>
       </c>
     </row>
@@ -27201,6 +27269,8 @@
     <hyperlink ref="I67" r:id="rId59" xr:uid="{D6DD9CAC-20BB-4706-BDE2-8C70E0ACB94A}"/>
     <hyperlink ref="I68" r:id="rId60" xr:uid="{95FCBFB7-6612-4485-AC1E-1061EEA56343}"/>
     <hyperlink ref="J68" r:id="rId61" xr:uid="{757626C9-CBA5-4F47-B647-04E7A7DD6CDF}"/>
+    <hyperlink ref="I69" r:id="rId62" xr:uid="{8544A61F-D856-4F2E-9F97-2DB4D2387AAF}"/>
+    <hyperlink ref="J69" r:id="rId63" xr:uid="{98081F45-A00E-45DE-9140-BA44372DDD97}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65CDDEA2-A327-4738-9EA6-12A5E0F91C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA813EBF-8389-4C81-B2ED-461B0C1711E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="1596" windowWidth="23256" windowHeight="12456" firstSheet="19" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="37332" yWindow="2100" windowWidth="11724" windowHeight="12336" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7704" uniqueCount="3834">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7718" uniqueCount="3841">
   <si>
     <t>ID</t>
   </si>
@@ -11550,6 +11550,27 @@
   </si>
   <si>
     <t>https://www.mouser.es/ProductDetail/JST-Commercial/B4B-XH-A-BKLFSN?qs=cIziFXvMxOXLG2L7xSRqLw%3D%3D</t>
+  </si>
+  <si>
+    <t>010-0183</t>
+  </si>
+  <si>
+    <t>Resistores de película fina - SMD RQ 0603 20K 0.1% 10PPM 5K RL</t>
+  </si>
+  <si>
+    <t>20kΩ 150mW ±0.1%</t>
+  </si>
+  <si>
+    <t>RQ73C1J20KBTD</t>
+  </si>
+  <si>
+    <t>279-RQ73C1J20KBTD</t>
+  </si>
+  <si>
+    <t>https://www.te.com/commerce/DocumentDelivery/DDEController?Action=showdoc&amp;DocId=Data+Sheet%7F1773270-2%7FA%7Fpdf%7FEnglish%7FENG_DS_1773270-2_A.pdf%7F2176380-2086</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/TE-Connectivity-Holsworthy/RQ73C1J20KBTD?qs=gZXFycFWdAPzh65iaC%2FK3A%3D%3D</t>
   </si>
 </sst>
 </file>
@@ -11788,8 +11809,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -27165,25 +27186,25 @@
       <c r="A69" s="16" t="s">
         <v>3826</v>
       </c>
-      <c r="B69" s="40" t="s">
+      <c r="B69" s="16" t="s">
         <v>3827</v>
       </c>
-      <c r="C69" s="40" t="s">
+      <c r="C69" s="16" t="s">
         <v>3828</v>
       </c>
       <c r="D69" s="16" t="s">
         <v>3829</v>
       </c>
-      <c r="E69" s="40" t="s">
+      <c r="E69" s="16" t="s">
         <v>3830</v>
       </c>
-      <c r="F69" s="39" t="s">
+      <c r="F69" s="3" t="s">
         <v>2172</v>
       </c>
-      <c r="G69" s="39" t="s">
+      <c r="G69" s="3" t="s">
         <v>3831</v>
       </c>
-      <c r="H69" s="40" t="s">
+      <c r="H69" s="16" t="s">
         <v>21</v>
       </c>
       <c r="I69" s="2" t="s">
@@ -27198,7 +27219,7 @@
       <c r="L69" s="7" t="s">
         <v>2572</v>
       </c>
-      <c r="M69" s="40" t="s">
+      <c r="M69" s="16" t="s">
         <v>3830</v>
       </c>
       <c r="N69" s="7" t="s">
@@ -35488,7 +35509,48 @@
       </c>
     </row>
     <row r="184" spans="1:14">
-      <c r="A184" s="16"/>
+      <c r="A184" s="16" t="s">
+        <v>3834</v>
+      </c>
+      <c r="B184" s="39" t="s">
+        <v>3835</v>
+      </c>
+      <c r="C184" s="16" t="s">
+        <v>3836</v>
+      </c>
+      <c r="D184" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="E184" s="39" t="s">
+        <v>3837</v>
+      </c>
+      <c r="F184" s="40" t="s">
+        <v>1524</v>
+      </c>
+      <c r="G184" s="40" t="s">
+        <v>3838</v>
+      </c>
+      <c r="H184" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="I184" s="26" t="s">
+        <v>3839</v>
+      </c>
+      <c r="J184" s="31" t="s">
+        <v>3840</v>
+      </c>
+      <c r="K184" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L184" s="17" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M184" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="N184" t="s">
+        <v>25</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="15" type="noConversion"/>
@@ -35648,9 +35710,11 @@
     <hyperlink ref="J182" r:id="rId153" xr:uid="{2B26D6AA-C539-4788-90B0-829083988502}"/>
     <hyperlink ref="I183" r:id="rId154" xr:uid="{17AE4450-0CA6-491F-AEB3-46674CC00EEE}"/>
     <hyperlink ref="J183" r:id="rId155" xr:uid="{3A9AF27C-EAA3-4F8D-B05D-139594372A97}"/>
+    <hyperlink ref="I184" r:id="rId156" xr:uid="{D00616E2-05E3-4C0D-936C-236760B22307}"/>
+    <hyperlink ref="J184" r:id="rId157" xr:uid="{7D0F9E12-2745-498A-B01D-8E33966F5A6D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId156"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId158"/>
 </worksheet>
 </file>
 

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA813EBF-8389-4C81-B2ED-461B0C1711E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5621C71C-6C41-47E7-A527-FED67CACD76C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="37332" yWindow="2100" windowWidth="11724" windowHeight="12336" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25812" yWindow="1992" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7718" uniqueCount="3841">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7774" uniqueCount="3867">
   <si>
     <t>ID</t>
   </si>
@@ -11571,6 +11571,84 @@
   </si>
   <si>
     <t>https://www.mouser.es/ProductDetail/TE-Connectivity-Holsworthy/RQ73C1J20KBTD?qs=gZXFycFWdAPzh65iaC%2FK3A%3D%3D</t>
+  </si>
+  <si>
+    <t>001-0128</t>
+  </si>
+  <si>
+    <t>Condensadores de cerámica multicapa (MLCC- SMD/SMT) 4300 pF 25 VDC 2% 0603 C0G (NP0)</t>
+  </si>
+  <si>
+    <t>25V 4.3nF NP0</t>
+  </si>
+  <si>
+    <t>GRM1885C1E432GA01J</t>
+  </si>
+  <si>
+    <t>81-GRM1885C1E432GA1J</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/datasheet/3/76/1/GRM1885C1E432GA01-01A.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Murata-Electronics/GRM1885C1E432GA01J?qs=QzBtWTOodeWyXLs1jqPc7Q%3D%3D</t>
+  </si>
+  <si>
+    <t>010-0184</t>
+  </si>
+  <si>
+    <t>Resistores de película fina - SMD 0805 16Kohm 0.1% 10ppm AEC-Q200</t>
+  </si>
+  <si>
+    <t>ERA-6ARB163V</t>
+  </si>
+  <si>
+    <t>667-ERA-6ARB163V</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Panasonic/ERA-6ARB163V?qs=sGAEpiMZZMtlubZbdhIBIJiMSTY83nT4nukUMCYb38k%3D</t>
+  </si>
+  <si>
+    <t>010-0185</t>
+  </si>
+  <si>
+    <t>Resistores de película fina - SMD 0805 24Kohm 0.1% 15ppm AEC-Q200</t>
+  </si>
+  <si>
+    <t>16kΩ 125mW ±0.1%</t>
+  </si>
+  <si>
+    <t>24kΩ 125mW ±0.1%</t>
+  </si>
+  <si>
+    <t>ERA-6APB243V</t>
+  </si>
+  <si>
+    <t>667-ERA-6APB243V</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Panasonic/ERA-6APB243V?qs=ob%252BdNz2%252BYEgwblk2D2VCQQ%3D%3D</t>
+  </si>
+  <si>
+    <t>010-0186</t>
+  </si>
+  <si>
+    <t>Resistores de película fina - SMD RQ 0805 12K1 0.1% 10PPM 5K RL</t>
+  </si>
+  <si>
+    <t>12kΩ 200mW ±0.1%</t>
+  </si>
+  <si>
+    <t>RQ73C2A12K1BTD</t>
+  </si>
+  <si>
+    <t>279-RQ73C2A12K1BTD</t>
+  </si>
+  <si>
+    <t>https://www.te.com/en/product-9-2176380-9.html</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/TE-Connectivity-Holsworthy/RQ73C2A12K1BTD?qs=gZXFycFWdAO8owZcKCpcmw%3D%3D</t>
   </si>
 </sst>
 </file>
@@ -12094,7 +12172,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N128"/>
+  <dimension ref="A1:N129"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="11.1796875" customWidth="1"/>
@@ -17740,6 +17818,50 @@
         <v>62</v>
       </c>
       <c r="N128" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="129" spans="1:14">
+      <c r="A129" s="38" t="s">
+        <v>3841</v>
+      </c>
+      <c r="B129" s="16" t="s">
+        <v>3842</v>
+      </c>
+      <c r="C129" s="16" t="s">
+        <v>3843</v>
+      </c>
+      <c r="D129" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="E129" t="s">
+        <v>3844</v>
+      </c>
+      <c r="F129" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="G129" s="3" t="s">
+        <v>3845</v>
+      </c>
+      <c r="H129" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I129" s="26" t="s">
+        <v>3846</v>
+      </c>
+      <c r="J129" s="31" t="s">
+        <v>3847</v>
+      </c>
+      <c r="K129" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="L129" t="s">
+        <v>61</v>
+      </c>
+      <c r="M129" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N129" t="s">
         <v>25</v>
       </c>
     </row>
@@ -17859,9 +17981,11 @@
     <hyperlink ref="J126" r:id="rId111" xr:uid="{348E15E9-2492-4FC3-9ADB-2287FB61453A}"/>
     <hyperlink ref="I128" r:id="rId112" xr:uid="{7E9F6B16-E367-4F43-A463-251B6118FB6C}"/>
     <hyperlink ref="J128" r:id="rId113" xr:uid="{6D13DE09-35E1-44E8-A161-CF565B19ADED}"/>
+    <hyperlink ref="I129" r:id="rId114" xr:uid="{FB710C94-A4D0-4FF6-A673-D2144CBFEE83}"/>
+    <hyperlink ref="J129" r:id="rId115" xr:uid="{9DCA9E08-FCEB-4C24-B9BD-2A4EB3937E26}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId114"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId116"/>
 </worksheet>
 </file>
 
@@ -27451,7 +27575,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60E8291E-4293-4634-B9E9-80CB520CA181}">
-  <dimension ref="A1:N184"/>
+  <dimension ref="A1:N187"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="3" max="3" width="19.90625" customWidth="1"/>
@@ -35512,7 +35636,7 @@
       <c r="A184" s="16" t="s">
         <v>3834</v>
       </c>
-      <c r="B184" s="39" t="s">
+      <c r="B184" s="16" t="s">
         <v>3835</v>
       </c>
       <c r="C184" s="16" t="s">
@@ -35521,16 +35645,16 @@
       <c r="D184" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="E184" s="39" t="s">
+      <c r="E184" s="16" t="s">
         <v>3837</v>
       </c>
-      <c r="F184" s="40" t="s">
+      <c r="F184" s="30" t="s">
         <v>1524</v>
       </c>
-      <c r="G184" s="40" t="s">
+      <c r="G184" s="30" t="s">
         <v>3838</v>
       </c>
-      <c r="H184" s="39" t="s">
+      <c r="H184" s="16" t="s">
         <v>21</v>
       </c>
       <c r="I184" s="26" t="s">
@@ -35549,6 +35673,138 @@
         <v>57</v>
       </c>
       <c r="N184" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="185" spans="1:14">
+      <c r="A185" s="16" t="s">
+        <v>3848</v>
+      </c>
+      <c r="B185" s="39" t="s">
+        <v>3849</v>
+      </c>
+      <c r="C185" s="16" t="s">
+        <v>3855</v>
+      </c>
+      <c r="D185" s="20" t="s">
+        <v>240</v>
+      </c>
+      <c r="E185" s="39" t="s">
+        <v>3850</v>
+      </c>
+      <c r="F185" s="40" t="s">
+        <v>3342</v>
+      </c>
+      <c r="G185" s="40" t="s">
+        <v>3851</v>
+      </c>
+      <c r="H185" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="I185" s="26" t="s">
+        <v>3344</v>
+      </c>
+      <c r="J185" s="31" t="s">
+        <v>3852</v>
+      </c>
+      <c r="K185" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L185" s="17" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M185" s="17" t="s">
+        <v>1646</v>
+      </c>
+      <c r="N185" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="186" spans="1:14">
+      <c r="A186" s="16" t="s">
+        <v>3853</v>
+      </c>
+      <c r="B186" s="39" t="s">
+        <v>3854</v>
+      </c>
+      <c r="C186" s="16" t="s">
+        <v>3856</v>
+      </c>
+      <c r="D186" s="20" t="s">
+        <v>240</v>
+      </c>
+      <c r="E186" s="39" t="s">
+        <v>3857</v>
+      </c>
+      <c r="F186" s="40" t="s">
+        <v>3342</v>
+      </c>
+      <c r="G186" s="40" t="s">
+        <v>3858</v>
+      </c>
+      <c r="H186" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="I186" s="26" t="s">
+        <v>3344</v>
+      </c>
+      <c r="J186" s="31" t="s">
+        <v>3859</v>
+      </c>
+      <c r="K186" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L186" s="17" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M186" s="17" t="s">
+        <v>1646</v>
+      </c>
+      <c r="N186" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="187" spans="1:14">
+      <c r="A187" s="16" t="s">
+        <v>3860</v>
+      </c>
+      <c r="B187" s="39" t="s">
+        <v>3861</v>
+      </c>
+      <c r="C187" s="16" t="s">
+        <v>3862</v>
+      </c>
+      <c r="D187" s="20" t="s">
+        <v>240</v>
+      </c>
+      <c r="E187" s="39" t="s">
+        <v>3863</v>
+      </c>
+      <c r="F187" s="40" t="s">
+        <v>1524</v>
+      </c>
+      <c r="G187" s="40" t="s">
+        <v>3864</v>
+      </c>
+      <c r="H187" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="I187" s="26" t="s">
+        <v>3865</v>
+      </c>
+      <c r="J187" s="31" t="s">
+        <v>3866</v>
+      </c>
+      <c r="K187" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L187" s="17" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M187" s="17" t="s">
+        <v>1646</v>
+      </c>
+      <c r="N187" t="s">
         <v>25</v>
       </c>
     </row>
@@ -35712,9 +35968,15 @@
     <hyperlink ref="J183" r:id="rId155" xr:uid="{3A9AF27C-EAA3-4F8D-B05D-139594372A97}"/>
     <hyperlink ref="I184" r:id="rId156" xr:uid="{D00616E2-05E3-4C0D-936C-236760B22307}"/>
     <hyperlink ref="J184" r:id="rId157" xr:uid="{7D0F9E12-2745-498A-B01D-8E33966F5A6D}"/>
+    <hyperlink ref="I185" r:id="rId158" xr:uid="{76F8280B-4CF8-4448-8C9A-3185533245A6}"/>
+    <hyperlink ref="J185" r:id="rId159" xr:uid="{F8240B68-10A9-44E1-9FC1-E1BCA6E4C641}"/>
+    <hyperlink ref="I186" r:id="rId160" xr:uid="{160C0D78-3243-4318-9D23-9CF9CA067F85}"/>
+    <hyperlink ref="J186" r:id="rId161" xr:uid="{6E7208C2-303A-4F5A-A973-294BBF656D01}"/>
+    <hyperlink ref="I187" r:id="rId162" xr:uid="{DEEBED7E-17D0-4EAC-BAFF-84DAFFF8847D}"/>
+    <hyperlink ref="J187" r:id="rId163" xr:uid="{4D207532-6F36-4B9E-ABE1-BC18363AB4D3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId158"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId164"/>
 </worksheet>
 </file>
 

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5621C71C-6C41-47E7-A527-FED67CACD76C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D26F753-56DD-4AAA-A5A3-CE78084B7F61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25812" yWindow="1992" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25812" yWindow="1992" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7774" uniqueCount="3867">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7830" uniqueCount="3893">
   <si>
     <t>ID</t>
   </si>
@@ -11649,6 +11649,84 @@
   </si>
   <si>
     <t>https://www.mouser.es/ProductDetail/TE-Connectivity-Holsworthy/RQ73C2A12K1BTD?qs=gZXFycFWdAO8owZcKCpcmw%3D%3D</t>
+  </si>
+  <si>
+    <t>010-0187</t>
+  </si>
+  <si>
+    <t>Thick Film Resistors WRIS-RSKS 470 Ohms 5 % 0.1 W 0603 AEC-Q200</t>
+  </si>
+  <si>
+    <t>470Ω 100mW ±5%</t>
+  </si>
+  <si>
+    <t>560112116031</t>
+  </si>
+  <si>
+    <t>710-560112116031</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/560112116031.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/560112116031?qs=sGAEpiMZZMvdGkrng054t2cqbZCzJY7Nc63jNcSJ2mNzAJgQFdfNBw%3D%3D</t>
+  </si>
+  <si>
+    <t>010-0188</t>
+  </si>
+  <si>
+    <t>Thick Film Resistors WRIS-RSKS 4.7 kOhms 5 % 0.1 W 0402 AEC-Q200</t>
+  </si>
+  <si>
+    <t>4.7kΩ 100mW ±5%</t>
+  </si>
+  <si>
+    <t>560112110018</t>
+  </si>
+  <si>
+    <t>710-560112110018</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/560112110018.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/560112110018?qs=sGAEpiMZZMvdGkrng054txLI%2FDB4oIKDXtogfAbE0Wc%252BspLjErwG3g%3D%3D</t>
+  </si>
+  <si>
+    <t>010-0189</t>
+  </si>
+  <si>
+    <t>Thick Film Resistors WRIS-RSKS 1 kOhms 1 % 0.25 W 1206 AEC-Q200</t>
+  </si>
+  <si>
+    <t>560112132038</t>
+  </si>
+  <si>
+    <t>710-560112132038</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/560112132038.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/560112132038?qs=sGAEpiMZZMvdGkrng054txLI%2FDB4oIKDY2lGR1OfVmrCt7nE4RR%2Faw%3D%3D</t>
+  </si>
+  <si>
+    <t>010-0190</t>
+  </si>
+  <si>
+    <t>Thick Film Resistors WRIS-RSKS 100 kOhms 1 % 0.1 W 0603 AEC-Q200</t>
+  </si>
+  <si>
+    <t>560112116004</t>
+  </si>
+  <si>
+    <t>710-560112116004</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/560112116004.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/560112116004?qs=sGAEpiMZZMvdGkrng054txLI%2FDB4oIKDB%252BmfBE1ySSGuQklCN21gzA%3D%3D</t>
   </si>
 </sst>
 </file>
@@ -11825,7 +11903,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -11887,8 +11965,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -27575,7 +27655,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60E8291E-4293-4634-B9E9-80CB520CA181}">
-  <dimension ref="A1:N187"/>
+  <dimension ref="A1:N191"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="3" max="3" width="19.90625" customWidth="1"/>
@@ -35680,7 +35760,7 @@
       <c r="A185" s="16" t="s">
         <v>3848</v>
       </c>
-      <c r="B185" s="39" t="s">
+      <c r="B185" s="16" t="s">
         <v>3849</v>
       </c>
       <c r="C185" s="16" t="s">
@@ -35689,16 +35769,16 @@
       <c r="D185" s="20" t="s">
         <v>240</v>
       </c>
-      <c r="E185" s="39" t="s">
+      <c r="E185" s="16" t="s">
         <v>3850</v>
       </c>
-      <c r="F185" s="40" t="s">
+      <c r="F185" s="30" t="s">
         <v>3342</v>
       </c>
-      <c r="G185" s="40" t="s">
+      <c r="G185" s="30" t="s">
         <v>3851</v>
       </c>
-      <c r="H185" s="39" t="s">
+      <c r="H185" s="16" t="s">
         <v>21</v>
       </c>
       <c r="I185" s="26" t="s">
@@ -35724,7 +35804,7 @@
       <c r="A186" s="16" t="s">
         <v>3853</v>
       </c>
-      <c r="B186" s="39" t="s">
+      <c r="B186" s="16" t="s">
         <v>3854</v>
       </c>
       <c r="C186" s="16" t="s">
@@ -35733,16 +35813,16 @@
       <c r="D186" s="20" t="s">
         <v>240</v>
       </c>
-      <c r="E186" s="39" t="s">
+      <c r="E186" s="16" t="s">
         <v>3857</v>
       </c>
-      <c r="F186" s="40" t="s">
+      <c r="F186" s="30" t="s">
         <v>3342</v>
       </c>
-      <c r="G186" s="40" t="s">
+      <c r="G186" s="30" t="s">
         <v>3858</v>
       </c>
-      <c r="H186" s="39" t="s">
+      <c r="H186" s="16" t="s">
         <v>21</v>
       </c>
       <c r="I186" s="26" t="s">
@@ -35768,7 +35848,7 @@
       <c r="A187" s="16" t="s">
         <v>3860</v>
       </c>
-      <c r="B187" s="39" t="s">
+      <c r="B187" s="16" t="s">
         <v>3861</v>
       </c>
       <c r="C187" s="16" t="s">
@@ -35777,16 +35857,16 @@
       <c r="D187" s="20" t="s">
         <v>240</v>
       </c>
-      <c r="E187" s="39" t="s">
+      <c r="E187" s="16" t="s">
         <v>3863</v>
       </c>
-      <c r="F187" s="40" t="s">
+      <c r="F187" s="30" t="s">
         <v>1524</v>
       </c>
-      <c r="G187" s="40" t="s">
+      <c r="G187" s="30" t="s">
         <v>3864</v>
       </c>
-      <c r="H187" s="39" t="s">
+      <c r="H187" s="16" t="s">
         <v>21</v>
       </c>
       <c r="I187" s="26" t="s">
@@ -35805,6 +35885,182 @@
         <v>1646</v>
       </c>
       <c r="N187" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="188" spans="1:14">
+      <c r="A188" s="16" t="s">
+        <v>3867</v>
+      </c>
+      <c r="B188" t="s">
+        <v>3868</v>
+      </c>
+      <c r="C188" s="16" t="s">
+        <v>3869</v>
+      </c>
+      <c r="D188" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="E188" s="39" t="s">
+        <v>3870</v>
+      </c>
+      <c r="F188" s="40" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G188" s="41" t="s">
+        <v>3871</v>
+      </c>
+      <c r="H188" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="I188" s="2" t="s">
+        <v>3872</v>
+      </c>
+      <c r="J188" s="2" t="s">
+        <v>3873</v>
+      </c>
+      <c r="K188" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L188" s="17" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M188" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="N188" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="189" spans="1:14">
+      <c r="A189" s="16" t="s">
+        <v>3874</v>
+      </c>
+      <c r="B189" t="s">
+        <v>3875</v>
+      </c>
+      <c r="C189" s="16" t="s">
+        <v>3876</v>
+      </c>
+      <c r="D189" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="E189" s="39" t="s">
+        <v>3877</v>
+      </c>
+      <c r="F189" s="40" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G189" s="40" t="s">
+        <v>3878</v>
+      </c>
+      <c r="H189" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="I189" s="26" t="s">
+        <v>3879</v>
+      </c>
+      <c r="J189" s="31" t="s">
+        <v>3880</v>
+      </c>
+      <c r="K189" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L189" s="17" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M189" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="N189" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="190" spans="1:14">
+      <c r="A190" s="16" t="s">
+        <v>3881</v>
+      </c>
+      <c r="B190" t="s">
+        <v>3882</v>
+      </c>
+      <c r="C190" s="16" t="s">
+        <v>921</v>
+      </c>
+      <c r="D190" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="E190" s="39" t="s">
+        <v>3883</v>
+      </c>
+      <c r="F190" s="40" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G190" s="40" t="s">
+        <v>3884</v>
+      </c>
+      <c r="H190" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="I190" s="26" t="s">
+        <v>3885</v>
+      </c>
+      <c r="J190" s="31" t="s">
+        <v>3886</v>
+      </c>
+      <c r="K190" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L190" s="17" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M190" s="7" t="s">
+        <v>1645</v>
+      </c>
+      <c r="N190" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="191" spans="1:14">
+      <c r="A191" s="16" t="s">
+        <v>3887</v>
+      </c>
+      <c r="B191" t="s">
+        <v>3888</v>
+      </c>
+      <c r="C191" s="16" t="s">
+        <v>929</v>
+      </c>
+      <c r="D191" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="E191" s="39" t="s">
+        <v>3889</v>
+      </c>
+      <c r="F191" s="40" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G191" s="40" t="s">
+        <v>3890</v>
+      </c>
+      <c r="H191" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="I191" s="26" t="s">
+        <v>3891</v>
+      </c>
+      <c r="J191" s="31" t="s">
+        <v>3892</v>
+      </c>
+      <c r="K191" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L191" s="17" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M191" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="N191" t="s">
         <v>25</v>
       </c>
     </row>
@@ -35974,9 +36230,17 @@
     <hyperlink ref="J186" r:id="rId161" xr:uid="{6E7208C2-303A-4F5A-A973-294BBF656D01}"/>
     <hyperlink ref="I187" r:id="rId162" xr:uid="{DEEBED7E-17D0-4EAC-BAFF-84DAFFF8847D}"/>
     <hyperlink ref="J187" r:id="rId163" xr:uid="{4D207532-6F36-4B9E-ABE1-BC18363AB4D3}"/>
+    <hyperlink ref="I188" r:id="rId164" xr:uid="{2870986C-1953-4DC5-9B89-873E713D299E}"/>
+    <hyperlink ref="J188" r:id="rId165" xr:uid="{A9897C76-A247-4FC9-9EB7-688C646664B8}"/>
+    <hyperlink ref="I189" r:id="rId166" xr:uid="{03119699-A4ED-41E9-802A-E01A41195490}"/>
+    <hyperlink ref="J189" r:id="rId167" xr:uid="{0B59B227-55EE-4290-A209-1475B1D01884}"/>
+    <hyperlink ref="I190" r:id="rId168" xr:uid="{066E29AC-27BD-48CF-96FC-427AF0B4A004}"/>
+    <hyperlink ref="J190" r:id="rId169" xr:uid="{0416598A-C30A-47A1-9871-D973FB462120}"/>
+    <hyperlink ref="I191" r:id="rId170" xr:uid="{1A8D28AA-426F-4991-A638-E362EF62E8B7}"/>
+    <hyperlink ref="J191" r:id="rId171" xr:uid="{0D368A4C-5099-4A8A-AFA4-4A14478071B4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId164"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId172"/>
 </worksheet>
 </file>
 

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D26F753-56DD-4AAA-A5A3-CE78084B7F61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F727296F-CB30-45AB-BA47-6B0C293B0C49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25812" yWindow="1992" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" firstSheet="9" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -24,19 +24,20 @@
     <sheet name="031 - Diode - Schottky" sheetId="11" r:id="rId9"/>
     <sheet name="032 - Diode - TVS" sheetId="14" r:id="rId10"/>
     <sheet name="033 - Diode - LED" sheetId="12" r:id="rId11"/>
-    <sheet name="040 - Fuses" sheetId="10" r:id="rId12"/>
-    <sheet name="041 - Optoisolators" sheetId="26" r:id="rId13"/>
-    <sheet name="043 - Transistors" sheetId="21" r:id="rId14"/>
-    <sheet name="045 - Crystal" sheetId="19" r:id="rId15"/>
-    <sheet name="050 - ICs - Analog" sheetId="2" r:id="rId16"/>
-    <sheet name="051 - ICs - Digital" sheetId="24" r:id="rId17"/>
-    <sheet name="055 - Drivers" sheetId="20" r:id="rId18"/>
-    <sheet name="060 - Sensor" sheetId="3" r:id="rId19"/>
-    <sheet name="062 - Amplifiers" sheetId="25" r:id="rId20"/>
-    <sheet name="070 - Power Supply" sheetId="8" r:id="rId21"/>
-    <sheet name="090 - Processor" sheetId="18" r:id="rId22"/>
-    <sheet name="100 - Electromechanicals" sheetId="15" r:id="rId23"/>
-    <sheet name="110 - Connectors" sheetId="13" r:id="rId24"/>
+    <sheet name="035 - Varistor " sheetId="27" r:id="rId12"/>
+    <sheet name="040 - Fuses" sheetId="10" r:id="rId13"/>
+    <sheet name="041 - Optoisolators" sheetId="26" r:id="rId14"/>
+    <sheet name="043 - Transistors" sheetId="21" r:id="rId15"/>
+    <sheet name="045 - Crystal" sheetId="19" r:id="rId16"/>
+    <sheet name="050 - ICs - Analog" sheetId="2" r:id="rId17"/>
+    <sheet name="051 - ICs - Digital" sheetId="24" r:id="rId18"/>
+    <sheet name="055 - Drivers" sheetId="20" r:id="rId19"/>
+    <sheet name="060 - Sensor" sheetId="3" r:id="rId20"/>
+    <sheet name="062 - Amplifiers" sheetId="25" r:id="rId21"/>
+    <sheet name="070 - Power Supply" sheetId="8" r:id="rId22"/>
+    <sheet name="090 - Processor" sheetId="18" r:id="rId23"/>
+    <sheet name="100 - Electromechanicals" sheetId="15" r:id="rId24"/>
+    <sheet name="110 - Connectors" sheetId="13" r:id="rId25"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -48,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7830" uniqueCount="3893">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7858" uniqueCount="3904">
   <si>
     <t>ID</t>
   </si>
@@ -11727,6 +11728,39 @@
   </si>
   <si>
     <t>https://www.mouser.es/ProductDetail/Wurth-Elektronik/560112116004?qs=sGAEpiMZZMvdGkrng054txLI%2FDB4oIKDB%252BmfBE1ySSGuQklCN21gzA%3D%3D</t>
+  </si>
+  <si>
+    <t>036-0001</t>
+  </si>
+  <si>
+    <t>Varistores 5.5V 150A 3500pF</t>
+  </si>
+  <si>
+    <t>V5.5MLA1206NH</t>
+  </si>
+  <si>
+    <t>5.5V 150A 3500pF</t>
+  </si>
+  <si>
+    <t>Littlefuse</t>
+  </si>
+  <si>
+    <t>576-V5.5MLA1206NH</t>
+  </si>
+  <si>
+    <t>https://www.littelfuse.com/assetdocs/littelfuse_varistor_mla_datasheet.pdf?assetguid=7092c93f-7453-48dd-8345-d10368b54a20</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Littelfuse/V5.5MLA1206NH?qs=slssyL07VvN8GgKT7I2llw%3D%3D</t>
+  </si>
+  <si>
+    <t>eUSR_SchLibrary/eUSR_SchLibrary - Varistors.SchLib</t>
+  </si>
+  <si>
+    <t>VAR</t>
+  </si>
+  <si>
+    <t>VAR SMD 1206</t>
   </si>
 </sst>
 </file>
@@ -11903,7 +11937,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -11965,10 +11999,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -20226,6 +20256,108 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ED8913B-580D-466F-B6D1-947424810FAF}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" s="34" t="s">
+        <v>3893</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3894</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3896</v>
+      </c>
+      <c r="D2" s="35" t="s">
+        <v>249</v>
+      </c>
+      <c r="E2" t="s">
+        <v>3895</v>
+      </c>
+      <c r="F2" t="s">
+        <v>3897</v>
+      </c>
+      <c r="G2" t="s">
+        <v>3898</v>
+      </c>
+      <c r="H2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>3899</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>3900</v>
+      </c>
+      <c r="K2" s="34" t="s">
+        <v>3902</v>
+      </c>
+      <c r="L2" t="s">
+        <v>3901</v>
+      </c>
+      <c r="M2" s="7" t="s">
+        <v>3903</v>
+      </c>
+      <c r="N2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="I2" r:id="rId1" xr:uid="{5F5F3BE2-5F72-475E-AFB5-D9F96DAF6C1C}"/>
+    <hyperlink ref="J2" r:id="rId2" xr:uid="{E7947B33-F3FB-4060-B8E3-89D65F1F489E}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B6F0D32-9CE2-4DF7-927E-42E7BA331F12}">
   <dimension ref="A1:O22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -21240,7 +21372,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA7E41C9-E62B-4149-A5B5-E7986E8877E6}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -21342,7 +21474,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FAFF3B6-AF11-4BFB-8078-829FF6F2F366}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -21444,7 +21576,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E5535EA-E186-4751-BC7F-9B3A0221302E}">
   <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -21593,7 +21725,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C98E1A12-072F-4773-8CB5-47FFE077E85B}">
   <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -22024,7 +22156,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{316C64E0-14FB-467C-956A-E132FAFB0232}">
   <dimension ref="A1:N1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -22078,7 +22210,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{201D74E2-3547-4E9B-8216-09A22645AC2A}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -22175,201 +22307,6 @@
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1" xr:uid="{8F7A6184-A0A3-4957-BEC8-F3E55B833A4E}"/>
     <hyperlink ref="J2" r:id="rId2" xr:uid="{EFC059D7-FF37-4BE0-B7C4-41524A59BFAA}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59BC8B2E-A067-463D-937A-30E88D8BECD0}">
-  <dimension ref="A1:N4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
-  <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" t="s">
-        <v>3275</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3274</v>
-      </c>
-      <c r="C2" t="s">
-        <v>3273</v>
-      </c>
-      <c r="D2" t="s">
-        <v>3272</v>
-      </c>
-      <c r="E2" t="s">
-        <v>3267</v>
-      </c>
-      <c r="F2" t="s">
-        <v>3268</v>
-      </c>
-      <c r="G2" t="s">
-        <v>3269</v>
-      </c>
-      <c r="H2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>3270</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>3271</v>
-      </c>
-      <c r="K2" t="s">
-        <v>3267</v>
-      </c>
-      <c r="L2" t="s">
-        <v>3276</v>
-      </c>
-      <c r="M2" t="s">
-        <v>3267</v>
-      </c>
-      <c r="N2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
-        <v>3662</v>
-      </c>
-      <c r="B3" t="s">
-        <v>3664</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>900</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="E3" t="s">
-        <v>3665</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>3311</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>3666</v>
-      </c>
-      <c r="H3" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>3667</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>3668</v>
-      </c>
-      <c r="K3" s="16" t="s">
-        <v>3669</v>
-      </c>
-      <c r="L3" t="s">
-        <v>3276</v>
-      </c>
-      <c r="M3" t="s">
-        <v>57</v>
-      </c>
-      <c r="N3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" t="s">
-        <v>3774</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>3767</v>
-      </c>
-      <c r="C4" t="s">
-        <v>3273</v>
-      </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="35" t="s">
-        <v>3775</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>3268</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>3776</v>
-      </c>
-      <c r="H4" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>3777</v>
-      </c>
-      <c r="J4" s="31" t="s">
-        <v>3778</v>
-      </c>
-      <c r="K4" s="35" t="s">
-        <v>3779</v>
-      </c>
-      <c r="L4" t="s">
-        <v>3276</v>
-      </c>
-      <c r="M4" s="35" t="s">
-        <v>3779</v>
-      </c>
-      <c r="N4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="15" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="I2" r:id="rId1" xr:uid="{BFD1D0BA-D934-44C0-B127-7693B6B8FCF4}"/>
-    <hyperlink ref="J2" r:id="rId2" xr:uid="{72343140-B075-45AB-91DC-7B87E10B2AD1}"/>
-    <hyperlink ref="I3" r:id="rId3" xr:uid="{D9F4A33B-2595-4DA0-8363-A69F15E2B303}"/>
-    <hyperlink ref="J3" r:id="rId4" xr:uid="{1ABB114B-1F85-4103-ABE2-AA0C257EB7B1}"/>
-    <hyperlink ref="I4" r:id="rId5" xr:uid="{23F5B451-07F8-40FF-B8FF-09319797C4C9}"/>
-    <hyperlink ref="J4" r:id="rId6" xr:uid="{AB96B204-6A61-49B4-8F27-F35BA2651662}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -22527,6 +22464,201 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59BC8B2E-A067-463D-937A-30E88D8BECD0}">
+  <dimension ref="A1:N4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
+        <v>3275</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3274</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3273</v>
+      </c>
+      <c r="D2" t="s">
+        <v>3272</v>
+      </c>
+      <c r="E2" t="s">
+        <v>3267</v>
+      </c>
+      <c r="F2" t="s">
+        <v>3268</v>
+      </c>
+      <c r="G2" t="s">
+        <v>3269</v>
+      </c>
+      <c r="H2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>3270</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>3271</v>
+      </c>
+      <c r="K2" t="s">
+        <v>3267</v>
+      </c>
+      <c r="L2" t="s">
+        <v>3276</v>
+      </c>
+      <c r="M2" t="s">
+        <v>3267</v>
+      </c>
+      <c r="N2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>3662</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3664</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>900</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" t="s">
+        <v>3665</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>3311</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>3666</v>
+      </c>
+      <c r="H3" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>3667</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>3668</v>
+      </c>
+      <c r="K3" s="16" t="s">
+        <v>3669</v>
+      </c>
+      <c r="L3" t="s">
+        <v>3276</v>
+      </c>
+      <c r="M3" t="s">
+        <v>57</v>
+      </c>
+      <c r="N3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>3774</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>3767</v>
+      </c>
+      <c r="C4" t="s">
+        <v>3273</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="35" t="s">
+        <v>3775</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>3268</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>3776</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>3777</v>
+      </c>
+      <c r="J4" s="31" t="s">
+        <v>3778</v>
+      </c>
+      <c r="K4" s="35" t="s">
+        <v>3779</v>
+      </c>
+      <c r="L4" t="s">
+        <v>3276</v>
+      </c>
+      <c r="M4" s="35" t="s">
+        <v>3779</v>
+      </c>
+      <c r="N4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="15" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="I2" r:id="rId1" xr:uid="{BFD1D0BA-D934-44C0-B127-7693B6B8FCF4}"/>
+    <hyperlink ref="J2" r:id="rId2" xr:uid="{72343140-B075-45AB-91DC-7B87E10B2AD1}"/>
+    <hyperlink ref="I3" r:id="rId3" xr:uid="{D9F4A33B-2595-4DA0-8363-A69F15E2B303}"/>
+    <hyperlink ref="J3" r:id="rId4" xr:uid="{1ABB114B-1F85-4103-ABE2-AA0C257EB7B1}"/>
+    <hyperlink ref="I4" r:id="rId5" xr:uid="{23F5B451-07F8-40FF-B8FF-09319797C4C9}"/>
+    <hyperlink ref="J4" r:id="rId6" xr:uid="{AB96B204-6A61-49B4-8F27-F35BA2651662}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4185B0A-D162-4EBC-935B-7159E365DD54}">
   <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -22675,7 +22807,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4BBBCF5-BAC9-459C-ABE9-2526B85FD81E}">
   <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -23143,7 +23275,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E9EB2F5-2977-493B-BFA2-5CD20F8A3BC4}">
   <dimension ref="A1:O3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -23301,7 +23433,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69A1C46E-DEF3-467B-A5BD-162AB66E6A86}">
   <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -24384,7 +24516,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE14AD29-8DB0-4C42-AB91-A73B867AE121}">
   <dimension ref="A1:N69"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -35901,16 +36033,16 @@
       <c r="D188" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="E188" s="39" t="s">
+      <c r="E188" s="20" t="s">
         <v>3870</v>
       </c>
-      <c r="F188" s="40" t="s">
+      <c r="F188" s="30" t="s">
         <v>2100</v>
       </c>
-      <c r="G188" s="41" t="s">
+      <c r="G188" s="36" t="s">
         <v>3871</v>
       </c>
-      <c r="H188" s="42" t="s">
+      <c r="H188" s="16" t="s">
         <v>21</v>
       </c>
       <c r="I188" s="2" t="s">
@@ -35945,16 +36077,16 @@
       <c r="D189" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="E189" s="39" t="s">
+      <c r="E189" s="20" t="s">
         <v>3877</v>
       </c>
-      <c r="F189" s="40" t="s">
+      <c r="F189" s="30" t="s">
         <v>2100</v>
       </c>
-      <c r="G189" s="40" t="s">
+      <c r="G189" s="30" t="s">
         <v>3878</v>
       </c>
-      <c r="H189" s="42" t="s">
+      <c r="H189" s="16" t="s">
         <v>21</v>
       </c>
       <c r="I189" s="26" t="s">
@@ -35989,16 +36121,16 @@
       <c r="D190" s="20" t="s">
         <v>249</v>
       </c>
-      <c r="E190" s="39" t="s">
+      <c r="E190" s="20" t="s">
         <v>3883</v>
       </c>
-      <c r="F190" s="40" t="s">
+      <c r="F190" s="30" t="s">
         <v>2100</v>
       </c>
-      <c r="G190" s="40" t="s">
+      <c r="G190" s="30" t="s">
         <v>3884</v>
       </c>
-      <c r="H190" s="42" t="s">
+      <c r="H190" s="16" t="s">
         <v>21</v>
       </c>
       <c r="I190" s="26" t="s">
@@ -36033,16 +36165,16 @@
       <c r="D191" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="E191" s="39" t="s">
+      <c r="E191" s="20" t="s">
         <v>3889</v>
       </c>
-      <c r="F191" s="40" t="s">
+      <c r="F191" s="30" t="s">
         <v>2100</v>
       </c>
-      <c r="G191" s="40" t="s">
+      <c r="G191" s="30" t="s">
         <v>3890</v>
       </c>
-      <c r="H191" s="42" t="s">
+      <c r="H191" s="16" t="s">
         <v>21</v>
       </c>
       <c r="I191" s="26" t="s">

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F727296F-CB30-45AB-BA47-6B0C293B0C49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DAB7F5D-6061-446B-84BA-07CEACF1C04C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" firstSheet="9" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25812" yWindow="1992" windowWidth="23256" windowHeight="12456" firstSheet="10" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7858" uniqueCount="3904">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7924" uniqueCount="3937">
   <si>
     <t>ID</t>
   </si>
@@ -11761,6 +11761,105 @@
   </si>
   <si>
     <t>VAR SMD 1206</t>
+  </si>
+  <si>
+    <t>043-0002</t>
+  </si>
+  <si>
+    <t>MOSFET P</t>
+  </si>
+  <si>
+    <t>MOSFET -30V Vds 20V Vgs SOT-23</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>SI2303CDS-T1-GE3</t>
+  </si>
+  <si>
+    <t>781-SI2303CDS-T1-GE3</t>
+  </si>
+  <si>
+    <t>https://www.vishay.com/docs/69991/si2303cd.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Vishay-Semiconductors/SI2303CDS-T1-GE3?qs=IRuQNBqMOckJHxNXLRBkmw%3D%3D</t>
+  </si>
+  <si>
+    <t>010-0191</t>
+  </si>
+  <si>
+    <t>Resistores de película gruesa - SMD WRIS-RSKS 220 Ohms 1 % 0.1 W 0603 AEC-Q200</t>
+  </si>
+  <si>
+    <t>220Ω 100mW ±1%</t>
+  </si>
+  <si>
+    <t>560112116126</t>
+  </si>
+  <si>
+    <t>710-560112116126</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/560112116126.pdf</t>
+  </si>
+  <si>
+    <t>040-0022</t>
+  </si>
+  <si>
+    <t>Fusibles de montaje en superficie 1206 0.2AMPS SMD</t>
+  </si>
+  <si>
+    <t>200mA</t>
+  </si>
+  <si>
+    <t>https://datasheets.kyocera-avx.com/AccuGuard2.pdf</t>
+  </si>
+  <si>
+    <t>F1206B0R20FSTR</t>
+  </si>
+  <si>
+    <t>581-F1206B0R20FSTR</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/KYOCERA-AVX/F1206B0R20FSTR?qs=qfFDQzOiitCIvTCyICvztA%3D%3D</t>
+  </si>
+  <si>
+    <t>040-0023</t>
+  </si>
+  <si>
+    <t>Fusibles de montaje en superficie 63V 1A FA HALIDE FREE SLIM</t>
+  </si>
+  <si>
+    <t>0466001.NRHF</t>
+  </si>
+  <si>
+    <t>576-0466001.NRHF</t>
+  </si>
+  <si>
+    <t>https://www.littelfuse.com/assetdocs/littelfuse_fuse_466_datasheet?assetguid=dbe9bcd7-6072-4adf-bf5b-d33e52a6b90f</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/Littelfuse/0466001.NRHF?qs=n5MbhIql%252BRl7ALFy%2FbHisA%3D%3D</t>
+  </si>
+  <si>
+    <t>040-0024</t>
+  </si>
+  <si>
+    <t>Fusibles de montaje en superficie 1206 0.5AMPS SMD</t>
+  </si>
+  <si>
+    <t>500mA</t>
+  </si>
+  <si>
+    <t>F1206B0R50FSTR</t>
+  </si>
+  <si>
+    <t>581-F1206B0R50FSTR</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/KYOCERA-AVX/F1206B0R50FSTR?qs=hZPoALHhU4OC%2FuvTP6tvGA%3D%3D</t>
   </si>
 </sst>
 </file>
@@ -11937,7 +12036,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -11999,6 +12098,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -20359,7 +20462,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B6F0D32-9CE2-4DF7-927E-42E7BA331F12}">
-  <dimension ref="A1:O22"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="13" max="13" width="13.36328125" customWidth="1"/>
@@ -21343,6 +21446,138 @@
         <v>1701</v>
       </c>
       <c r="N22" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" t="s">
+        <v>3918</v>
+      </c>
+      <c r="B23" s="42" t="s">
+        <v>3919</v>
+      </c>
+      <c r="C23" s="42" t="s">
+        <v>3920</v>
+      </c>
+      <c r="D23" s="7">
+        <v>1206</v>
+      </c>
+      <c r="E23" s="42" t="s">
+        <v>3922</v>
+      </c>
+      <c r="F23" s="40" t="s">
+        <v>3005</v>
+      </c>
+      <c r="G23" s="40" t="s">
+        <v>3923</v>
+      </c>
+      <c r="H23" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="I23" t="s">
+        <v>3921</v>
+      </c>
+      <c r="J23" t="s">
+        <v>3924</v>
+      </c>
+      <c r="K23" s="17" t="s">
+        <v>1700</v>
+      </c>
+      <c r="L23" t="s">
+        <v>55</v>
+      </c>
+      <c r="M23" s="7" t="s">
+        <v>1701</v>
+      </c>
+      <c r="N23" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" t="s">
+        <v>3925</v>
+      </c>
+      <c r="B24" s="42" t="s">
+        <v>3926</v>
+      </c>
+      <c r="C24" s="42" t="s">
+        <v>1711</v>
+      </c>
+      <c r="D24" s="7">
+        <v>1206</v>
+      </c>
+      <c r="E24" s="42" t="s">
+        <v>3927</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>1696</v>
+      </c>
+      <c r="G24" s="40" t="s">
+        <v>3928</v>
+      </c>
+      <c r="H24" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="I24" s="26" t="s">
+        <v>3929</v>
+      </c>
+      <c r="J24" s="26" t="s">
+        <v>3930</v>
+      </c>
+      <c r="K24" s="17" t="s">
+        <v>1700</v>
+      </c>
+      <c r="L24" t="s">
+        <v>55</v>
+      </c>
+      <c r="M24" s="7" t="s">
+        <v>1701</v>
+      </c>
+      <c r="N24" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" t="s">
+        <v>3931</v>
+      </c>
+      <c r="B25" s="42" t="s">
+        <v>3932</v>
+      </c>
+      <c r="C25" s="42" t="s">
+        <v>3933</v>
+      </c>
+      <c r="D25" s="7">
+        <v>1206</v>
+      </c>
+      <c r="E25" s="42" t="s">
+        <v>3934</v>
+      </c>
+      <c r="F25" s="16" t="s">
+        <v>1696</v>
+      </c>
+      <c r="G25" s="40" t="s">
+        <v>3935</v>
+      </c>
+      <c r="H25" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="I25" s="26" t="s">
+        <v>3921</v>
+      </c>
+      <c r="J25" s="31" t="s">
+        <v>3936</v>
+      </c>
+      <c r="K25" s="17" t="s">
+        <v>1700</v>
+      </c>
+      <c r="L25" t="s">
+        <v>55</v>
+      </c>
+      <c r="M25" s="7" t="s">
+        <v>1701</v>
+      </c>
+      <c r="N25" t="s">
         <v>25</v>
       </c>
     </row>
@@ -21367,6 +21602,10 @@
     <hyperlink ref="J21" r:id="rId16" xr:uid="{FFB17F08-401F-47B0-899B-612CD8B9FB6B}"/>
     <hyperlink ref="I22" r:id="rId17" xr:uid="{1372C46B-1234-4FDC-9A5A-49F3F36A3112}"/>
     <hyperlink ref="J22" r:id="rId18" xr:uid="{5B608490-0175-4BFB-8CEB-749053C4E8DA}"/>
+    <hyperlink ref="I24" r:id="rId19" xr:uid="{8860E270-1EA1-413E-81F7-FE643E5ACB08}"/>
+    <hyperlink ref="J24" r:id="rId20" xr:uid="{0EEBF3D2-D854-4F60-9074-0417D1F60860}"/>
+    <hyperlink ref="I25" r:id="rId21" xr:uid="{C43E42B6-8EB7-4520-ABCA-F6BA4656E176}"/>
+    <hyperlink ref="J25" r:id="rId22" xr:uid="{69E1134F-3116-4058-838E-440309247FBB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -21476,7 +21715,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FAFF3B6-AF11-4BFB-8078-829FF6F2F366}">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:14">
@@ -21567,10 +21806,57 @@
         <v>25</v>
       </c>
     </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>3904</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3906</v>
+      </c>
+      <c r="C3" t="s">
+        <v>3907</v>
+      </c>
+      <c r="D3" t="s">
+        <v>3764</v>
+      </c>
+      <c r="E3" t="s">
+        <v>3908</v>
+      </c>
+      <c r="F3" t="s">
+        <v>1957</v>
+      </c>
+      <c r="G3" t="s">
+        <v>3909</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>3910</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>3911</v>
+      </c>
+      <c r="K3" t="s">
+        <v>3905</v>
+      </c>
+      <c r="L3" s="33" t="s">
+        <v>3182</v>
+      </c>
+      <c r="M3" s="34" t="s">
+        <v>1856</v>
+      </c>
+      <c r="N3" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="15" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1" xr:uid="{71BC0DAF-9651-41D4-BC90-0CA5C5CA063D}"/>
     <hyperlink ref="J2" r:id="rId2" xr:uid="{B8956BA2-569B-4007-9354-F99A76E81F8D}"/>
+    <hyperlink ref="I3" r:id="rId3" xr:uid="{360B4179-45EE-4DEA-AE1A-A9A674637B6A}"/>
+    <hyperlink ref="J3" r:id="rId4" xr:uid="{9FAEC919-51DF-4619-9BEF-284521DA0E38}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -27787,7 +28073,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60E8291E-4293-4634-B9E9-80CB520CA181}">
-  <dimension ref="A1:N191"/>
+  <dimension ref="A1:N192"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="3" max="3" width="19.90625" customWidth="1"/>
@@ -36193,6 +36479,47 @@
         <v>57</v>
       </c>
       <c r="N191" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="192" spans="1:14">
+      <c r="A192" s="16" t="s">
+        <v>3912</v>
+      </c>
+      <c r="B192" t="s">
+        <v>3913</v>
+      </c>
+      <c r="C192" s="16" t="s">
+        <v>3914</v>
+      </c>
+      <c r="D192" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="E192" s="39" t="s">
+        <v>3915</v>
+      </c>
+      <c r="F192" s="30" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G192" s="41" t="s">
+        <v>3916</v>
+      </c>
+      <c r="H192" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="I192" s="26" t="s">
+        <v>3917</v>
+      </c>
+      <c r="K192" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L192" s="17" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M192" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="N192" t="s">
         <v>25</v>
       </c>
     </row>
@@ -36370,9 +36697,10 @@
     <hyperlink ref="J190" r:id="rId169" xr:uid="{0416598A-C30A-47A1-9871-D973FB462120}"/>
     <hyperlink ref="I191" r:id="rId170" xr:uid="{1A8D28AA-426F-4991-A638-E362EF62E8B7}"/>
     <hyperlink ref="J191" r:id="rId171" xr:uid="{0D368A4C-5099-4A8A-AFA4-4A14478071B4}"/>
+    <hyperlink ref="I192" r:id="rId172" xr:uid="{22F61D15-F86A-45C4-8028-A72154D709C5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId172"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId173"/>
 </worksheet>
 </file>
 

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DAB7F5D-6061-446B-84BA-07CEACF1C04C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FEA2133-7BD5-4026-9DC2-D10F1ACCD3DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25812" yWindow="1992" windowWidth="23256" windowHeight="12456" firstSheet="10" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25812" yWindow="1992" windowWidth="23256" windowHeight="12456" firstSheet="10" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7924" uniqueCount="3937">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7938" uniqueCount="3947">
   <si>
     <t>ID</t>
   </si>
@@ -11860,6 +11860,36 @@
   </si>
   <si>
     <t>https://www.mouser.es/ProductDetail/KYOCERA-AVX/F1206B0R50FSTR?qs=hZPoALHhU4OC%2FuvTP6tvGA%3D%3D</t>
+  </si>
+  <si>
+    <t>041-0002</t>
+  </si>
+  <si>
+    <t>LTV-247</t>
+  </si>
+  <si>
+    <t>Pleeda_SchLibrary/Pleeda_SchLibrary - Optoisolators.SchLib</t>
+  </si>
+  <si>
+    <t>SOP-16</t>
+  </si>
+  <si>
+    <t>Pleeda_PcbLibrary/Pleeda_PcbLibrary.PcbLib</t>
+  </si>
+  <si>
+    <t>https://www.mouser.com/catalog/specsheets/Lite-On-07-31-2018-LTV-2X7%20sereis%20Apr18.pdf?_gl=1*hv8h7o*_gcl_aw*R0NMLjE3ODA5NDM2MTUuQ2owS0NRancwSm5SQmhESkFSSXNBTG9iblhiTVZmV3NWb0pqSGVpNWRkTXk2SzRuNEhwRGVRWXYxa0dMT0s1N0VWSjRWQlE1eFhBYUoxd2FBa3NuRUFMd193Y0I.*_gcl_au*MjAyMjI4MzgwOS4xNzc1NDk0ODAwLjEzNjA3ODI2NzguMTc4MzExMDAxNi4xNzgzMTEwMDE2*_ga*Nzg3Njk5NTY0LjE3NDY2Mzg0MjI.*_ga_15W4STQT4T*czE3ODMxMTAwMTYkbzEzNyRnMSR0MTc4MzExMDAxOSRqNTckbDAkaDA.</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/ProductDetail/LITEON/LTV-247?qs=9ayhpukWNmvWpoxQBzWkFA%3D%3D</t>
+  </si>
+  <si>
+    <t>Optoacopladores para salidas de transistores PTR 50% 5KV 16 PIN 4CH Optocoupler</t>
+  </si>
+  <si>
+    <t>LITEON</t>
+  </si>
+  <si>
+    <t>859-LTV-247</t>
   </si>
 </sst>
 </file>
@@ -11869,7 +11899,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -11985,6 +12015,11 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -12036,7 +12071,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -12098,10 +12133,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -21453,25 +21485,25 @@
       <c r="A23" t="s">
         <v>3918</v>
       </c>
-      <c r="B23" s="42" t="s">
+      <c r="B23" s="16" t="s">
         <v>3919</v>
       </c>
-      <c r="C23" s="42" t="s">
+      <c r="C23" s="16" t="s">
         <v>3920</v>
       </c>
       <c r="D23" s="7">
         <v>1206</v>
       </c>
-      <c r="E23" s="42" t="s">
+      <c r="E23" s="16" t="s">
         <v>3922</v>
       </c>
-      <c r="F23" s="40" t="s">
+      <c r="F23" s="3" t="s">
         <v>3005</v>
       </c>
-      <c r="G23" s="40" t="s">
+      <c r="G23" s="3" t="s">
         <v>3923</v>
       </c>
-      <c r="H23" s="42" t="s">
+      <c r="H23" s="16" t="s">
         <v>21</v>
       </c>
       <c r="I23" t="s">
@@ -21497,25 +21529,25 @@
       <c r="A24" t="s">
         <v>3925</v>
       </c>
-      <c r="B24" s="42" t="s">
+      <c r="B24" s="16" t="s">
         <v>3926</v>
       </c>
-      <c r="C24" s="42" t="s">
+      <c r="C24" s="16" t="s">
         <v>1711</v>
       </c>
       <c r="D24" s="7">
         <v>1206</v>
       </c>
-      <c r="E24" s="42" t="s">
+      <c r="E24" s="16" t="s">
         <v>3927</v>
       </c>
       <c r="F24" s="16" t="s">
         <v>1696</v>
       </c>
-      <c r="G24" s="40" t="s">
+      <c r="G24" s="3" t="s">
         <v>3928</v>
       </c>
-      <c r="H24" s="42" t="s">
+      <c r="H24" s="16" t="s">
         <v>21</v>
       </c>
       <c r="I24" s="26" t="s">
@@ -21541,25 +21573,25 @@
       <c r="A25" t="s">
         <v>3931</v>
       </c>
-      <c r="B25" s="42" t="s">
+      <c r="B25" s="16" t="s">
         <v>3932</v>
       </c>
-      <c r="C25" s="42" t="s">
+      <c r="C25" s="16" t="s">
         <v>3933</v>
       </c>
       <c r="D25" s="7">
         <v>1206</v>
       </c>
-      <c r="E25" s="42" t="s">
+      <c r="E25" s="16" t="s">
         <v>3934</v>
       </c>
       <c r="F25" s="16" t="s">
         <v>1696</v>
       </c>
-      <c r="G25" s="40" t="s">
+      <c r="G25" s="3" t="s">
         <v>3935</v>
       </c>
-      <c r="H25" s="42" t="s">
+      <c r="H25" s="16" t="s">
         <v>21</v>
       </c>
       <c r="I25" s="26" t="s">
@@ -21613,7 +21645,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA7E41C9-E62B-4149-A5B5-E7986E8877E6}">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:14">
@@ -21704,10 +21736,56 @@
         <v>25</v>
       </c>
     </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>3937</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3944</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>3940</v>
+      </c>
+      <c r="E3" t="s">
+        <v>3938</v>
+      </c>
+      <c r="F3" t="s">
+        <v>3945</v>
+      </c>
+      <c r="G3" t="s">
+        <v>3946</v>
+      </c>
+      <c r="H3" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" t="s">
+        <v>3942</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>3943</v>
+      </c>
+      <c r="K3" s="39" t="s">
+        <v>3938</v>
+      </c>
+      <c r="L3" s="39" t="s">
+        <v>3939</v>
+      </c>
+      <c r="M3" s="39" t="s">
+        <v>3940</v>
+      </c>
+      <c r="N3" s="39" t="s">
+        <v>3941</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="15" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1" xr:uid="{C0196A92-FFC7-4B23-8894-B6344B4B2643}"/>
     <hyperlink ref="J2" r:id="rId2" xr:uid="{0B83CD2F-6571-479E-AB7A-FA77C6040D49}"/>
+    <hyperlink ref="J3" r:id="rId3" xr:uid="{6CF2E8FA-2871-441E-B367-030778224566}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -36495,16 +36573,16 @@
       <c r="D192" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="E192" s="39" t="s">
+      <c r="E192" s="20" t="s">
         <v>3915</v>
       </c>
       <c r="F192" s="30" t="s">
         <v>2100</v>
       </c>
-      <c r="G192" s="41" t="s">
+      <c r="G192" s="30" t="s">
         <v>3916</v>
       </c>
-      <c r="H192" s="42" t="s">
+      <c r="H192" s="16" t="s">
         <v>21</v>
       </c>
       <c r="I192" s="26" t="s">

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FEA2133-7BD5-4026-9DC2-D10F1ACCD3DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C396918A-09A1-420F-AA63-8CC2D778B579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25812" yWindow="1992" windowWidth="23256" windowHeight="12456" firstSheet="10" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7938" uniqueCount="3947">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7938" uniqueCount="3945">
   <si>
     <t>ID</t>
   </si>
@@ -11868,13 +11868,7 @@
     <t>LTV-247</t>
   </si>
   <si>
-    <t>Pleeda_SchLibrary/Pleeda_SchLibrary - Optoisolators.SchLib</t>
-  </si>
-  <si>
     <t>SOP-16</t>
-  </si>
-  <si>
-    <t>Pleeda_PcbLibrary/Pleeda_PcbLibrary.PcbLib</t>
   </si>
   <si>
     <t>https://www.mouser.com/catalog/specsheets/Lite-On-07-31-2018-LTV-2X7%20sereis%20Apr18.pdf?_gl=1*hv8h7o*_gcl_aw*R0NMLjE3ODA5NDM2MTUuQ2owS0NRancwSm5SQmhESkFSSXNBTG9iblhiTVZmV3NWb0pqSGVpNWRkTXk2SzRuNEhwRGVRWXYxa0dMT0s1N0VWSjRWQlE1eFhBYUoxd2FBa3NuRUFMd193Y0I.*_gcl_au*MjAyMjI4MzgwOS4xNzc1NDk0ODAwLjEzNjA3ODI2NzguMTc4MzExMDAxNi4xNzgzMTEwMDE2*_ga*Nzg3Njk5NTY0LjE3NDY2Mzg0MjI.*_ga_15W4STQT4T*czE3ODMxMTAwMTYkbzEzNyRnMSR0MTc4MzExMDAxOSRqNTckbDAkaDA.</t>
@@ -21741,43 +21735,43 @@
         <v>3937</v>
       </c>
       <c r="B3" t="s">
-        <v>3944</v>
+        <v>3942</v>
       </c>
       <c r="C3" t="s">
         <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>3940</v>
+        <v>3939</v>
       </c>
       <c r="E3" t="s">
         <v>3938</v>
       </c>
       <c r="F3" t="s">
-        <v>3945</v>
+        <v>3943</v>
       </c>
       <c r="G3" t="s">
-        <v>3946</v>
+        <v>3944</v>
       </c>
       <c r="H3" s="16" t="s">
         <v>21</v>
       </c>
       <c r="I3" t="s">
-        <v>3942</v>
+        <v>3940</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>3943</v>
+        <v>3941</v>
       </c>
       <c r="K3" s="39" t="s">
         <v>3938</v>
       </c>
-      <c r="L3" s="39" t="s">
+      <c r="L3" t="s">
+        <v>3648</v>
+      </c>
+      <c r="M3" s="39" t="s">
         <v>3939</v>
       </c>
-      <c r="M3" s="39" t="s">
-        <v>3940</v>
-      </c>
-      <c r="N3" s="39" t="s">
-        <v>3941</v>
+      <c r="N3" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C396918A-09A1-420F-AA63-8CC2D778B579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E964C66B-DF2E-4DF3-B8FB-D5D42E140EFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25812" yWindow="1992" windowWidth="23256" windowHeight="12456" firstSheet="10" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34500" yWindow="7176" windowWidth="13500" windowHeight="8316" firstSheet="10" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7938" uniqueCount="3945">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7952" uniqueCount="3952">
   <si>
     <t>ID</t>
   </si>
@@ -11884,6 +11884,27 @@
   </si>
   <si>
     <t>859-LTV-247</t>
+  </si>
+  <si>
+    <t>036-0002</t>
+  </si>
+  <si>
+    <t>VAR SMD 0805</t>
+  </si>
+  <si>
+    <t>Varistores 18 VDC .3J 44V-CL 120A PK</t>
+  </si>
+  <si>
+    <t>V18MLA0805NH</t>
+  </si>
+  <si>
+    <t>576-V18MLA0805NH</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/es/ProductDetail/Littelfuse/V18MLA0805NH?qs=slssyL07VvNBxGr5IH4W1g%3D%3D</t>
+  </si>
+  <si>
+    <t>18V 120A 520pF</t>
   </si>
 </sst>
 </file>
@@ -20386,7 +20407,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ED8913B-580D-466F-B6D1-947424810FAF}">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:14">
@@ -20477,10 +20498,57 @@
         <v>25</v>
       </c>
     </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="34" t="s">
+        <v>3945</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3947</v>
+      </c>
+      <c r="C3" t="s">
+        <v>3951</v>
+      </c>
+      <c r="D3" s="35" t="s">
+        <v>240</v>
+      </c>
+      <c r="E3" t="s">
+        <v>3948</v>
+      </c>
+      <c r="F3" t="s">
+        <v>3897</v>
+      </c>
+      <c r="G3" t="s">
+        <v>3949</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>3899</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>3950</v>
+      </c>
+      <c r="K3" s="34" t="s">
+        <v>3902</v>
+      </c>
+      <c r="L3" t="s">
+        <v>3901</v>
+      </c>
+      <c r="M3" s="16" t="s">
+        <v>3946</v>
+      </c>
+      <c r="N3" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="15" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1" xr:uid="{5F5F3BE2-5F72-475E-AFB5-D9F96DAF6C1C}"/>
     <hyperlink ref="J2" r:id="rId2" xr:uid="{E7947B33-F3FB-4060-B8E3-89D65F1F489E}"/>
+    <hyperlink ref="I3" r:id="rId3" xr:uid="{CDF34A71-8D79-4140-915F-6D067879A14A}"/>
+    <hyperlink ref="J3" r:id="rId4" xr:uid="{577274DA-1852-4AF5-9BDC-AE557DC87043}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E964C66B-DF2E-4DF3-B8FB-D5D42E140EFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6BE3DB0-1C6A-4699-BB2F-341CF84106A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34500" yWindow="7176" windowWidth="13500" windowHeight="8316" firstSheet="10" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" firstSheet="21" activeTab="24" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7952" uniqueCount="3952">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7964" uniqueCount="3957">
   <si>
     <t>ID</t>
   </si>
@@ -11905,6 +11905,21 @@
   </si>
   <si>
     <t>18V 120A 520pF</t>
+  </si>
+  <si>
+    <t>110-0069</t>
+  </si>
+  <si>
+    <t>Headers &amp; Wire Housings WR-MPC5 THT Dual Row Male Header Right Angled with Snap-in Plastic Pegs Glow-Wire 10 Pins</t>
+  </si>
+  <si>
+    <t>710-657010240101</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/657010240101.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/en/ProductDetail/Wurth-Elektronik/657010240101?qs=Z%252BL2brAPG1L7pimSXLZIOg%3D%3D</t>
   </si>
 </sst>
 </file>
@@ -11914,7 +11929,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -12035,6 +12050,14 @@
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -12086,7 +12109,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -12149,6 +12172,8 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -24944,10 +24969,10 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE14AD29-8DB0-4C42-AB91-A73B867AE121}">
-  <dimension ref="A1:N69"/>
+  <dimension ref="A1:N77"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="5" max="5" width="16.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.36328125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.26953125" customWidth="1"/>
     <col min="13" max="13" width="14.453125" customWidth="1"/>
   </cols>
@@ -27987,6 +28012,56 @@
       <c r="N69" s="7" t="s">
         <v>25</v>
       </c>
+    </row>
+    <row r="70" spans="1:14">
+      <c r="A70" s="16" t="s">
+        <v>3952</v>
+      </c>
+      <c r="B70" s="16" t="s">
+        <v>3953</v>
+      </c>
+      <c r="C70" s="16" t="s">
+        <v>2513</v>
+      </c>
+      <c r="D70" s="16" t="s">
+        <v>2883</v>
+      </c>
+      <c r="E70" s="41">
+        <v>657010240101</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G70" t="s">
+        <v>3954</v>
+      </c>
+      <c r="H70" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I70" s="26" t="s">
+        <v>3955</v>
+      </c>
+      <c r="J70" s="26" t="s">
+        <v>3956</v>
+      </c>
+      <c r="K70" s="17" t="s">
+        <v>2533</v>
+      </c>
+      <c r="L70" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M70" s="41">
+        <v>657010240101</v>
+      </c>
+      <c r="N70" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14">
+      <c r="M73" s="40"/>
+    </row>
+    <row r="77" spans="1:14">
+      <c r="I77" s="40"/>
     </row>
   </sheetData>
   <phoneticPr fontId="15" type="noConversion"/>
@@ -28054,6 +28129,8 @@
     <hyperlink ref="J68" r:id="rId61" xr:uid="{757626C9-CBA5-4F47-B647-04E7A7DD6CDF}"/>
     <hyperlink ref="I69" r:id="rId62" xr:uid="{8544A61F-D856-4F2E-9F97-2DB4D2387AAF}"/>
     <hyperlink ref="J69" r:id="rId63" xr:uid="{98081F45-A00E-45DE-9140-BA44372DDD97}"/>
+    <hyperlink ref="I70" r:id="rId64" xr:uid="{6004C564-9134-4DE0-9E7A-993FD2CE9BF5}"/>
+    <hyperlink ref="J70" r:id="rId65" xr:uid="{03F14566-E754-46FF-B4A8-8273B9090065}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6BE3DB0-1C6A-4699-BB2F-341CF84106A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB11F223-71B0-4F8A-AEBA-8741A3B7B059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" firstSheet="21" activeTab="24" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25812" yWindow="1992" windowWidth="23256" windowHeight="12456" firstSheet="9" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7964" uniqueCount="3957">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7978" uniqueCount="3964">
   <si>
     <t>ID</t>
   </si>
@@ -11920,6 +11920,27 @@
   </si>
   <si>
     <t>https://www.mouser.es/en/ProductDetail/Wurth-Elektronik/657010240101?qs=Z%252BL2brAPG1L7pimSXLZIOg%3D%3D</t>
+  </si>
+  <si>
+    <t>040-0025</t>
+  </si>
+  <si>
+    <t>Surface Mount Fuses 3.15A Slow Blow 0603 SinglFuse</t>
+  </si>
+  <si>
+    <t>3.15A</t>
+  </si>
+  <si>
+    <t>SF-0603S315-2</t>
+  </si>
+  <si>
+    <t>652-SF-0603S315-2</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/datasheet/3/40/1/sf0603s.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/en/ProductDetail/Bourns/SF-0603S315-2?qs=GIQXYiEeHGBW8r%252BkbDjk9Q%3D%3D</t>
   </si>
 </sst>
 </file>
@@ -12109,7 +12130,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -12174,6 +12195,8 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -20581,7 +20604,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B6F0D32-9CE2-4DF7-927E-42E7BA331F12}">
-  <dimension ref="A1:O25"/>
+  <dimension ref="A1:O26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="13" max="13" width="13.36328125" customWidth="1"/>
@@ -21697,6 +21720,50 @@
         <v>1701</v>
       </c>
       <c r="N25" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" t="s">
+        <v>3957</v>
+      </c>
+      <c r="B26" s="43" t="s">
+        <v>3958</v>
+      </c>
+      <c r="C26" s="43" t="s">
+        <v>3959</v>
+      </c>
+      <c r="D26" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="E26" s="43" t="s">
+        <v>3960</v>
+      </c>
+      <c r="F26" s="43" t="s">
+        <v>1516</v>
+      </c>
+      <c r="G26" s="42" t="s">
+        <v>3961</v>
+      </c>
+      <c r="H26" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="I26" s="26" t="s">
+        <v>3962</v>
+      </c>
+      <c r="J26" s="26" t="s">
+        <v>3963</v>
+      </c>
+      <c r="K26" s="17" t="s">
+        <v>1700</v>
+      </c>
+      <c r="L26" t="s">
+        <v>55</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>1785</v>
+      </c>
+      <c r="N26" t="s">
         <v>25</v>
       </c>
     </row>
@@ -21725,6 +21792,8 @@
     <hyperlink ref="J24" r:id="rId20" xr:uid="{0EEBF3D2-D854-4F60-9074-0417D1F60860}"/>
     <hyperlink ref="I25" r:id="rId21" xr:uid="{C43E42B6-8EB7-4520-ABCA-F6BA4656E176}"/>
     <hyperlink ref="J25" r:id="rId22" xr:uid="{69E1134F-3116-4058-838E-440309247FBB}"/>
+    <hyperlink ref="I26" r:id="rId23" xr:uid="{0D32544C-35BB-4327-BB7D-AF104017BD04}"/>
+    <hyperlink ref="J26" r:id="rId24" xr:uid="{9793B0E3-2D69-4504-8B5D-26B0BECF5557}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB11F223-71B0-4F8A-AEBA-8741A3B7B059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50CD2317-854B-4B24-9F2B-A7513115859D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25812" yWindow="1992" windowWidth="23256" windowHeight="12456" firstSheet="9" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7978" uniqueCount="3964">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7991" uniqueCount="3971">
   <si>
     <t>ID</t>
   </si>
@@ -11941,6 +11941,27 @@
   </si>
   <si>
     <t>https://www.mouser.es/en/ProductDetail/Bourns/SF-0603S315-2?qs=GIQXYiEeHGBW8r%252BkbDjk9Q%3D%3D</t>
+  </si>
+  <si>
+    <t>040-0026</t>
+  </si>
+  <si>
+    <t>Surface Mount Fuses 12A 32V FAST ACTING</t>
+  </si>
+  <si>
+    <t>12A</t>
+  </si>
+  <si>
+    <t>0501012.WRA</t>
+  </si>
+  <si>
+    <t>576-0501012.WRA</t>
+  </si>
+  <si>
+    <t>https://www.littelfuse.com/assetdocs/littelfuse_fuse_501a_datasheet.pdf?assetguid=16e534f2-c7ad-421d-9fb1-2d7646704d65</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/en/ProductDetail/Littelfuse/0501012.WRA?qs=r5DSvlrkXmL6WmckR9m8eg%3D%3D</t>
   </si>
 </sst>
 </file>
@@ -20604,7 +20625,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B6F0D32-9CE2-4DF7-927E-42E7BA331F12}">
-  <dimension ref="A1:O26"/>
+  <dimension ref="A1:O27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="13" max="13" width="13.36328125" customWidth="1"/>
@@ -21727,25 +21748,25 @@
       <c r="A26" t="s">
         <v>3957</v>
       </c>
-      <c r="B26" s="43" t="s">
+      <c r="B26" s="16" t="s">
         <v>3958</v>
       </c>
-      <c r="C26" s="43" t="s">
+      <c r="C26" s="16" t="s">
         <v>3959</v>
       </c>
       <c r="D26" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="E26" s="43" t="s">
+      <c r="E26" s="16" t="s">
         <v>3960</v>
       </c>
-      <c r="F26" s="43" t="s">
+      <c r="F26" s="16" t="s">
         <v>1516</v>
       </c>
-      <c r="G26" s="42" t="s">
+      <c r="G26" s="3" t="s">
         <v>3961</v>
       </c>
-      <c r="H26" s="43" t="s">
+      <c r="H26" s="16" t="s">
         <v>21</v>
       </c>
       <c r="I26" s="26" t="s">
@@ -21764,6 +21785,50 @@
         <v>1785</v>
       </c>
       <c r="N26" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" t="s">
+        <v>3964</v>
+      </c>
+      <c r="B27" s="43" t="s">
+        <v>3965</v>
+      </c>
+      <c r="C27" s="43" t="s">
+        <v>3966</v>
+      </c>
+      <c r="D27" s="43">
+        <v>1206</v>
+      </c>
+      <c r="E27" s="43" t="s">
+        <v>3967</v>
+      </c>
+      <c r="F27" s="43" t="s">
+        <v>1696</v>
+      </c>
+      <c r="G27" s="42" t="s">
+        <v>3968</v>
+      </c>
+      <c r="H27" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="I27" s="26" t="s">
+        <v>3969</v>
+      </c>
+      <c r="J27" s="26" t="s">
+        <v>3970</v>
+      </c>
+      <c r="K27" s="17" t="s">
+        <v>1700</v>
+      </c>
+      <c r="L27" t="s">
+        <v>55</v>
+      </c>
+      <c r="M27" s="7" t="s">
+        <v>1701</v>
+      </c>
+      <c r="N27" t="s">
         <v>25</v>
       </c>
     </row>
@@ -21794,6 +21859,8 @@
     <hyperlink ref="J25" r:id="rId22" xr:uid="{69E1134F-3116-4058-838E-440309247FBB}"/>
     <hyperlink ref="I26" r:id="rId23" xr:uid="{0D32544C-35BB-4327-BB7D-AF104017BD04}"/>
     <hyperlink ref="J26" r:id="rId24" xr:uid="{9793B0E3-2D69-4504-8B5D-26B0BECF5557}"/>
+    <hyperlink ref="I27" r:id="rId25" xr:uid="{D5F6BA00-63BC-4E92-99CF-2B334D8D8AF0}"/>
+    <hyperlink ref="J27" r:id="rId26" xr:uid="{44FF3741-58F0-47A8-83F8-CCD057B318B1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50CD2317-854B-4B24-9F2B-A7513115859D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1D1E6CF-664F-49E7-AAF4-A6FF5EE364FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25812" yWindow="1992" windowWidth="23256" windowHeight="12456" firstSheet="9" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25812" yWindow="1992" windowWidth="23256" windowHeight="12456" firstSheet="20" activeTab="24" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7991" uniqueCount="3971">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8003" uniqueCount="3976">
   <si>
     <t>ID</t>
   </si>
@@ -11962,6 +11962,21 @@
   </si>
   <si>
     <t>https://www.mouser.es/en/ProductDetail/Littelfuse/0501012.WRA?qs=r5DSvlrkXmL6WmckR9m8eg%3D%3D</t>
+  </si>
+  <si>
+    <t>110-0070</t>
+  </si>
+  <si>
+    <t>Headers &amp; Wire Housings WR-MPC5 THT Dual Row Male Header Right Angled with Snap-in Plastic Pegs Glow-Wire 4 Pins</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/657004240101.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/en/ProductDetail/Wurth-Elektronik/657004240101?qs=Z%252BL2brAPG1IceqvpwioElw%3D%3D</t>
+  </si>
+  <si>
+    <t>710-657004240101</t>
   </si>
 </sst>
 </file>
@@ -12151,7 +12166,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -12216,7 +12231,6 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
@@ -21792,25 +21806,25 @@
       <c r="A27" t="s">
         <v>3964</v>
       </c>
-      <c r="B27" s="43" t="s">
+      <c r="B27" s="16" t="s">
         <v>3965</v>
       </c>
-      <c r="C27" s="43" t="s">
+      <c r="C27" s="16" t="s">
         <v>3966</v>
       </c>
-      <c r="D27" s="43">
+      <c r="D27" s="16">
         <v>1206</v>
       </c>
-      <c r="E27" s="43" t="s">
+      <c r="E27" s="16" t="s">
         <v>3967</v>
       </c>
-      <c r="F27" s="43" t="s">
+      <c r="F27" s="16" t="s">
         <v>1696</v>
       </c>
-      <c r="G27" s="42" t="s">
+      <c r="G27" s="3" t="s">
         <v>3968</v>
       </c>
-      <c r="H27" s="43" t="s">
+      <c r="H27" s="16" t="s">
         <v>21</v>
       </c>
       <c r="I27" s="26" t="s">
@@ -28190,6 +28204,50 @@
         <v>657010240101</v>
       </c>
       <c r="N70" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14">
+      <c r="A71" s="16" t="s">
+        <v>3971</v>
+      </c>
+      <c r="B71" s="42" t="s">
+        <v>3972</v>
+      </c>
+      <c r="C71" s="42" t="s">
+        <v>2452</v>
+      </c>
+      <c r="D71" s="16" t="s">
+        <v>2883</v>
+      </c>
+      <c r="E71" s="29">
+        <v>657004240101</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G71" t="s">
+        <v>3975</v>
+      </c>
+      <c r="H71" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I71" s="2" t="s">
+        <v>3973</v>
+      </c>
+      <c r="J71" s="2" t="s">
+        <v>3974</v>
+      </c>
+      <c r="K71" s="17" t="s">
+        <v>2464</v>
+      </c>
+      <c r="L71" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M71" s="29">
+        <v>657004240101</v>
+      </c>
+      <c r="N71" s="7" t="s">
         <v>25</v>
       </c>
     </row>
@@ -28267,6 +28325,8 @@
     <hyperlink ref="J69" r:id="rId63" xr:uid="{98081F45-A00E-45DE-9140-BA44372DDD97}"/>
     <hyperlink ref="I70" r:id="rId64" xr:uid="{6004C564-9134-4DE0-9E7A-993FD2CE9BF5}"/>
     <hyperlink ref="J70" r:id="rId65" xr:uid="{03F14566-E754-46FF-B4A8-8273B9090065}"/>
+    <hyperlink ref="I71" r:id="rId66" xr:uid="{96F2E17A-16DE-48A9-8D88-69602C1C2F6E}"/>
+    <hyperlink ref="J71" r:id="rId67" xr:uid="{F7B2F86A-80EA-4ECB-93DF-E8DCEAA063DF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1D1E6CF-664F-49E7-AAF4-A6FF5EE364FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7342A5A7-F98A-43CC-839B-CA2D7AA9867C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25812" yWindow="1992" windowWidth="23256" windowHeight="12456" firstSheet="20" activeTab="24" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25812" yWindow="2292" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8003" uniqueCount="3976">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8059" uniqueCount="4005">
   <si>
     <t>ID</t>
   </si>
@@ -11977,6 +11977,93 @@
   </si>
   <si>
     <t>710-657004240101</t>
+  </si>
+  <si>
+    <t>015-0005</t>
+  </si>
+  <si>
+    <t>015-0006</t>
+  </si>
+  <si>
+    <t>015-0007</t>
+  </si>
+  <si>
+    <t>015-0008</t>
+  </si>
+  <si>
+    <t>Current Sense Resistors - SMD WRIS-KWKH 0.62Ohms 1% 1W +200ppm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">620mΩ 1W ±1% </t>
+  </si>
+  <si>
+    <t>1206 (Reversed)</t>
+  </si>
+  <si>
+    <t>561070332081</t>
+  </si>
+  <si>
+    <t>710-561070332081</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/561070332081.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/en/ProductDetail/Wurth-Elektronik/561070332081?qs=unwgFEO1A6sUBr71YhIMeA%3D%3D</t>
+  </si>
+  <si>
+    <t>RES SMD 1206 Reversed</t>
+  </si>
+  <si>
+    <t>Current Sense Resistors - SMD WRIS-KWKH 0.15Ohms 1% 1W +350ppm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150mΩ 1W ±1% </t>
+  </si>
+  <si>
+    <t>561070332055</t>
+  </si>
+  <si>
+    <t>710-561070332055</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/561070332055.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/en/ProductDetail/Wurth-Elektronik/561070332055?qs=sGAEpiMZZMtlubZbdhIBIKUWFMOULdJiXOgwA76%2FMU4%3D</t>
+  </si>
+  <si>
+    <t>Current Sense Resistors - SMD RLW73 B2 1% R039 200ppm 1k RL</t>
+  </si>
+  <si>
+    <t>RLW73B2FR039TDF</t>
+  </si>
+  <si>
+    <t>279-RLW73B2FR039TDF</t>
+  </si>
+  <si>
+    <t>https://www.te.com/commerce/DocumentDelivery/DDEController?Action=showdoc&amp;DocId=Data+Sheet%7Fcgs-wide-terminal-rlw73%7F2211%7Fpdf%7FEnglish%7FENG_DS_cgs-wide-terminal-rlw73_2211.pdf%7F2176535-1</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/en/ProductDetail/TE-Connectivity-CGS/RLW73B2FR039TDF?qs=8Wlm6%252BaMh8Slhw8Q%252Bucv7g%3D%3D</t>
+  </si>
+  <si>
+    <t>Current Sense Resistors - SMD RLW73 B2 1% R068 200ppm 1k RL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39mΩ 750mW ±1% </t>
+  </si>
+  <si>
+    <t xml:space="preserve">68mΩ 750mW ±1% </t>
+  </si>
+  <si>
+    <t>RLW73B2FR068TDF</t>
+  </si>
+  <si>
+    <t>279-RLW73B2FR068TDF</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/en/ProductDetail/TE-Connectivity-CGS/RLW73B2FR068TDF?qs=8Wlm6%252BaMh8Q8YtMhJjj3hA%3D%3D</t>
   </si>
 </sst>
 </file>
@@ -12231,7 +12318,7 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -28211,10 +28298,10 @@
       <c r="A71" s="16" t="s">
         <v>3971</v>
       </c>
-      <c r="B71" s="42" t="s">
+      <c r="B71" s="16" t="s">
         <v>3972</v>
       </c>
-      <c r="C71" s="42" t="s">
+      <c r="C71" s="16" t="s">
         <v>2452</v>
       </c>
       <c r="D71" s="16" t="s">
@@ -37119,7 +37206,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81F9848D-6D60-47C0-9F84-A561FE4F106E}">
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="20.26953125" customWidth="1"/>
@@ -37342,6 +37429,182 @@
         <v>1647</v>
       </c>
       <c r="N5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>3976</v>
+      </c>
+      <c r="B6" t="s">
+        <v>3980</v>
+      </c>
+      <c r="C6" t="s">
+        <v>3981</v>
+      </c>
+      <c r="D6" t="s">
+        <v>3982</v>
+      </c>
+      <c r="E6" s="35" t="s">
+        <v>3983</v>
+      </c>
+      <c r="F6" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G6" t="s">
+        <v>3984</v>
+      </c>
+      <c r="H6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>3985</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>3986</v>
+      </c>
+      <c r="K6" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M6" s="42" t="s">
+        <v>3987</v>
+      </c>
+      <c r="N6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>3977</v>
+      </c>
+      <c r="B7" t="s">
+        <v>3988</v>
+      </c>
+      <c r="C7" t="s">
+        <v>3989</v>
+      </c>
+      <c r="D7" t="s">
+        <v>3982</v>
+      </c>
+      <c r="E7" s="35" t="s">
+        <v>3990</v>
+      </c>
+      <c r="F7" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G7" t="s">
+        <v>3991</v>
+      </c>
+      <c r="H7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>3992</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>3993</v>
+      </c>
+      <c r="K7" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M7" s="42" t="s">
+        <v>3987</v>
+      </c>
+      <c r="N7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>3978</v>
+      </c>
+      <c r="B8" t="s">
+        <v>3994</v>
+      </c>
+      <c r="C8" t="s">
+        <v>4000</v>
+      </c>
+      <c r="D8" t="s">
+        <v>3982</v>
+      </c>
+      <c r="E8" t="s">
+        <v>3995</v>
+      </c>
+      <c r="F8" t="s">
+        <v>2192</v>
+      </c>
+      <c r="G8" t="s">
+        <v>3996</v>
+      </c>
+      <c r="H8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>3997</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>3998</v>
+      </c>
+      <c r="K8" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M8" s="42" t="s">
+        <v>3987</v>
+      </c>
+      <c r="N8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>3979</v>
+      </c>
+      <c r="B9" t="s">
+        <v>3999</v>
+      </c>
+      <c r="C9" t="s">
+        <v>4001</v>
+      </c>
+      <c r="D9" t="s">
+        <v>3982</v>
+      </c>
+      <c r="E9" t="s">
+        <v>4002</v>
+      </c>
+      <c r="F9" t="s">
+        <v>2192</v>
+      </c>
+      <c r="G9" t="s">
+        <v>4003</v>
+      </c>
+      <c r="H9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>3997</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>4004</v>
+      </c>
+      <c r="K9" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M9" s="42" t="s">
+        <v>3987</v>
+      </c>
+      <c r="N9" t="s">
         <v>25</v>
       </c>
     </row>
@@ -37354,8 +37617,17 @@
     <hyperlink ref="I4" r:id="rId4" xr:uid="{DA619253-40A2-482C-A99F-F72A13182916}"/>
     <hyperlink ref="J4" r:id="rId5" xr:uid="{65BF95D6-EB54-41F9-8886-7DFC774FFE44}"/>
     <hyperlink ref="I5" r:id="rId6" xr:uid="{E9BE5DD3-9340-403D-9879-EBA54F1D68BE}"/>
+    <hyperlink ref="I6" r:id="rId7" xr:uid="{A0FEDAF8-B077-4E91-A533-0BF21B3850D4}"/>
+    <hyperlink ref="J6" r:id="rId8" xr:uid="{7E76CE16-8D3D-41D0-B66B-54075687FCB0}"/>
+    <hyperlink ref="I7" r:id="rId9" xr:uid="{588AF41D-5865-4683-B4AC-FFCE2EEF92A4}"/>
+    <hyperlink ref="J7" r:id="rId10" xr:uid="{BDBCF452-A59D-494E-A080-4E069519929D}"/>
+    <hyperlink ref="I8" r:id="rId11" xr:uid="{745537AE-849B-4D1C-9F73-038DE1A2228B}"/>
+    <hyperlink ref="J8" r:id="rId12" xr:uid="{2522A19B-C8CE-448A-B70B-CFD7C4AFEEF0}"/>
+    <hyperlink ref="I9" r:id="rId13" xr:uid="{6C0457D9-CE57-4F5A-8777-E39EA4F17352}"/>
+    <hyperlink ref="J9" r:id="rId14" xr:uid="{BA2A9F42-701A-48EA-BFA8-1B1F3BDDF2F6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId15"/>
 </worksheet>
 </file>
 

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7342A5A7-F98A-43CC-839B-CA2D7AA9867C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3181F104-9B17-402B-B1E8-80D6E0945166}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25812" yWindow="2292" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25812" yWindow="2292" windowWidth="23256" windowHeight="12456" firstSheet="8" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8059" uniqueCount="4005">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8098" uniqueCount="4023">
   <si>
     <t>ID</t>
   </si>
@@ -12064,6 +12064,60 @@
   </si>
   <si>
     <t>https://www.mouser.es/en/ProductDetail/TE-Connectivity-CGS/RLW73B2FR068TDF?qs=8Wlm6%252BaMh8Q8YtMhJjj3hA%3D%3D</t>
+  </si>
+  <si>
+    <t>040-0027</t>
+  </si>
+  <si>
+    <t>040-0028</t>
+  </si>
+  <si>
+    <t>040-0029</t>
+  </si>
+  <si>
+    <t>Surface Mount Fuses JB12S SMD Fuse 63V 0.75A Slow 1206 3.2mm X 1.6mm</t>
+  </si>
+  <si>
+    <t>JB12S7500R</t>
+  </si>
+  <si>
+    <t>603-JB12S7500R</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/datasheet/3/508/1/JB12S_1.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/en/ProductDetail/YAGEO/JB12S7500R?qs=iLKYxzqNS76J6pRfCpvQZQ%3D%3D</t>
+  </si>
+  <si>
+    <t>Surface Mount Fuses 1.5A 110V TIME DELAY</t>
+  </si>
+  <si>
+    <t>SF-1206SA150W-2</t>
+  </si>
+  <si>
+    <t>652-SF-1206SA150W-2</t>
+  </si>
+  <si>
+    <t>https://www.mouser.com/catalog/specsheets/Bourns_01272020SF-1206SA-W_datasheet.pdf?_gl=1*1pr3f9q*_gcl_au*MTA5NjM4MzM5OC4xNzgzMzUxNzE4LjMyNzA1MjgyNS4xNzg5MTI0MzkxLjE3ODkxMjQ1ODkuODc0OTk4MjIwLjE3ODkxMjQzOTEuMTc4OTEyNDU4OQ..*_ga*Nzg3Njk5NTY0LjE3NDY2Mzg0MjI.*_ga_15W4STQT4T*czE3ODkxMjQzOTAkbzE2NCRnMSR0MTc4OTEyNDU4OSRqNjAkbDAkaDA.</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/en/ProductDetail/Bourns/SF-1206SA150W-2?qs=GBLSl2AkiruWVvm1odQw6A%3D%3D</t>
+  </si>
+  <si>
+    <t>Surface Mount Fuses 3A 63V TIME DELAY</t>
+  </si>
+  <si>
+    <t>0407003.WR</t>
+  </si>
+  <si>
+    <t>576-0407003.WR</t>
+  </si>
+  <si>
+    <t>https://www.littelfuse.com/assetdocs/littelfuse-fuse-407-datasheet?assetguid=B3BB718B-1FDE-4CDC-9CB1-A6465C126EC4</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/en/ProductDetail/Littelfuse/0407003.WR?qs=sPbYRqrBIVmOJKm3qiJ6qQ%3D%3D</t>
   </si>
 </sst>
 </file>
@@ -12193,6 +12247,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
@@ -12253,7 +12308,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -12318,7 +12373,8 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -20726,7 +20782,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B6F0D32-9CE2-4DF7-927E-42E7BA331F12}">
-  <dimension ref="A1:O27"/>
+  <dimension ref="A1:O30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="13" max="13" width="13.36328125" customWidth="1"/>
@@ -21930,6 +21986,138 @@
         <v>1701</v>
       </c>
       <c r="N27" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" t="s">
+        <v>4005</v>
+      </c>
+      <c r="B28" s="43" t="s">
+        <v>4008</v>
+      </c>
+      <c r="C28" s="43" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D28" s="16">
+        <v>1206</v>
+      </c>
+      <c r="E28" s="43" t="s">
+        <v>4009</v>
+      </c>
+      <c r="F28" s="43" t="s">
+        <v>60</v>
+      </c>
+      <c r="G28" s="42" t="s">
+        <v>4010</v>
+      </c>
+      <c r="H28" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="I28" s="26" t="s">
+        <v>4011</v>
+      </c>
+      <c r="J28" s="26" t="s">
+        <v>4012</v>
+      </c>
+      <c r="K28" s="17" t="s">
+        <v>1700</v>
+      </c>
+      <c r="L28" t="s">
+        <v>55</v>
+      </c>
+      <c r="M28" s="7" t="s">
+        <v>1701</v>
+      </c>
+      <c r="N28" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29" t="s">
+        <v>4006</v>
+      </c>
+      <c r="B29" s="43" t="s">
+        <v>4013</v>
+      </c>
+      <c r="C29" s="43" t="s">
+        <v>1748</v>
+      </c>
+      <c r="D29" s="16">
+        <v>1206</v>
+      </c>
+      <c r="E29" s="43" t="s">
+        <v>4014</v>
+      </c>
+      <c r="F29" s="43" t="s">
+        <v>1516</v>
+      </c>
+      <c r="G29" s="42" t="s">
+        <v>4015</v>
+      </c>
+      <c r="H29" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="I29" s="26" t="s">
+        <v>4016</v>
+      </c>
+      <c r="J29" s="26" t="s">
+        <v>4017</v>
+      </c>
+      <c r="K29" s="17" t="s">
+        <v>1700</v>
+      </c>
+      <c r="L29" t="s">
+        <v>55</v>
+      </c>
+      <c r="M29" s="7" t="s">
+        <v>1701</v>
+      </c>
+      <c r="N29" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" t="s">
+        <v>4007</v>
+      </c>
+      <c r="B30" s="43" t="s">
+        <v>4018</v>
+      </c>
+      <c r="C30" s="43" t="s">
+        <v>1703</v>
+      </c>
+      <c r="D30" s="16">
+        <v>1206</v>
+      </c>
+      <c r="E30" s="43" t="s">
+        <v>4019</v>
+      </c>
+      <c r="F30" s="43" t="s">
+        <v>1696</v>
+      </c>
+      <c r="G30" s="42" t="s">
+        <v>4020</v>
+      </c>
+      <c r="H30" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="I30" s="26" t="s">
+        <v>4021</v>
+      </c>
+      <c r="J30" s="26" t="s">
+        <v>4022</v>
+      </c>
+      <c r="K30" s="17" t="s">
+        <v>1700</v>
+      </c>
+      <c r="L30" t="s">
+        <v>55</v>
+      </c>
+      <c r="M30" s="7" t="s">
+        <v>1701</v>
+      </c>
+      <c r="N30" t="s">
         <v>25</v>
       </c>
     </row>
@@ -21962,6 +22150,12 @@
     <hyperlink ref="J26" r:id="rId24" xr:uid="{9793B0E3-2D69-4504-8B5D-26B0BECF5557}"/>
     <hyperlink ref="I27" r:id="rId25" xr:uid="{D5F6BA00-63BC-4E92-99CF-2B334D8D8AF0}"/>
     <hyperlink ref="J27" r:id="rId26" xr:uid="{44FF3741-58F0-47A8-83F8-CCD057B318B1}"/>
+    <hyperlink ref="I28" r:id="rId27" xr:uid="{887925C6-2B06-478A-9434-9C2D43B4FDC0}"/>
+    <hyperlink ref="J28" r:id="rId28" xr:uid="{4BDB9D16-D89F-43B4-82E5-FD786FC52E76}"/>
+    <hyperlink ref="I29" r:id="rId29" display="https://www.mouser.com/catalog/specsheets/Bourns_01272020SF-1206SA-W_datasheet.pdf?_gl=1*1pr3f9q*_gcl_au*MTA5NjM4MzM5OC4xNzgzMzUxNzE4LjMyNzA1MjgyNS4xNzg5MTI0MzkxLjE3ODkxMjQ1ODkuODc0OTk4MjIwLjE3ODkxMjQzOTEuMTc4OTEyNDU4OQ..*_ga*Nzg3Njk5NTY0LjE3NDY2Mzg0MjI.*_ga_15W4STQT4T*czE3ODkxMjQzOTAkbzE2NCRnMSR0MTc4OTEyNDU4OSRqNjAkbDAkaDA." xr:uid="{83CB5175-217F-4050-97F4-B646F03C6622}"/>
+    <hyperlink ref="J29" r:id="rId30" xr:uid="{0F119F88-FF89-4B12-848E-7BBFE27299F5}"/>
+    <hyperlink ref="I30" r:id="rId31" xr:uid="{C229C9D4-3F37-4DBD-9352-BF5A898D0314}"/>
+    <hyperlink ref="J30" r:id="rId32" xr:uid="{B4F8AF74-EF6D-49F1-9CE8-29F632F7A754}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -37469,7 +37663,7 @@
       <c r="L6" t="s">
         <v>1648</v>
       </c>
-      <c r="M6" s="42" t="s">
+      <c r="M6" s="17" t="s">
         <v>3987</v>
       </c>
       <c r="N6" t="s">
@@ -37513,7 +37707,7 @@
       <c r="L7" t="s">
         <v>1648</v>
       </c>
-      <c r="M7" s="42" t="s">
+      <c r="M7" s="17" t="s">
         <v>3987</v>
       </c>
       <c r="N7" t="s">
@@ -37557,7 +37751,7 @@
       <c r="L8" t="s">
         <v>1648</v>
       </c>
-      <c r="M8" s="42" t="s">
+      <c r="M8" s="17" t="s">
         <v>3987</v>
       </c>
       <c r="N8" t="s">
@@ -37601,7 +37795,7 @@
       <c r="L9" t="s">
         <v>1648</v>
       </c>
-      <c r="M9" s="42" t="s">
+      <c r="M9" s="17" t="s">
         <v>3987</v>
       </c>
       <c r="N9" t="s">

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,36 +8,37 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3181F104-9B17-402B-B1E8-80D6E0945166}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14555C9A-C152-490F-833E-6CC2CC5B4082}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25812" yWindow="2292" windowWidth="23256" windowHeight="12456" firstSheet="8" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25812" yWindow="2292" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
-    <sheet name="003 - Capacitors - THT Electrol" sheetId="17" r:id="rId2"/>
-    <sheet name="004 - Capacitors - Film" sheetId="22" r:id="rId3"/>
-    <sheet name="010 - Resistors - SMD" sheetId="4" r:id="rId4"/>
-    <sheet name="015 - Resistors - Shunt" sheetId="7" r:id="rId5"/>
-    <sheet name="020 - Inductor" sheetId="5" r:id="rId6"/>
-    <sheet name="023 - Inductor - CMM" sheetId="16" r:id="rId7"/>
-    <sheet name="030 - Diode - Rectifier" sheetId="9" r:id="rId8"/>
-    <sheet name="031 - Diode - Schottky" sheetId="11" r:id="rId9"/>
-    <sheet name="032 - Diode - TVS" sheetId="14" r:id="rId10"/>
-    <sheet name="033 - Diode - LED" sheetId="12" r:id="rId11"/>
-    <sheet name="035 - Varistor " sheetId="27" r:id="rId12"/>
-    <sheet name="040 - Fuses" sheetId="10" r:id="rId13"/>
-    <sheet name="041 - Optoisolators" sheetId="26" r:id="rId14"/>
-    <sheet name="043 - Transistors" sheetId="21" r:id="rId15"/>
-    <sheet name="045 - Crystal" sheetId="19" r:id="rId16"/>
-    <sheet name="050 - ICs - Analog" sheetId="2" r:id="rId17"/>
-    <sheet name="051 - ICs - Digital" sheetId="24" r:id="rId18"/>
-    <sheet name="055 - Drivers" sheetId="20" r:id="rId19"/>
-    <sheet name="060 - Sensor" sheetId="3" r:id="rId20"/>
-    <sheet name="062 - Amplifiers" sheetId="25" r:id="rId21"/>
-    <sheet name="070 - Power Supply" sheetId="8" r:id="rId22"/>
-    <sheet name="090 - Processor" sheetId="18" r:id="rId23"/>
-    <sheet name="100 - Electromechanicals" sheetId="15" r:id="rId24"/>
-    <sheet name="110 - Connectors" sheetId="13" r:id="rId25"/>
+    <sheet name="002 - Capacitors - SMD Electrol" sheetId="28" r:id="rId2"/>
+    <sheet name="003 - Capacitors - THT Electrol" sheetId="17" r:id="rId3"/>
+    <sheet name="004 - Capacitors - Film" sheetId="22" r:id="rId4"/>
+    <sheet name="010 - Resistors - SMD" sheetId="4" r:id="rId5"/>
+    <sheet name="015 - Resistors - Shunt" sheetId="7" r:id="rId6"/>
+    <sheet name="020 - Inductor" sheetId="5" r:id="rId7"/>
+    <sheet name="023 - Inductor - CMM" sheetId="16" r:id="rId8"/>
+    <sheet name="030 - Diode - Rectifier" sheetId="9" r:id="rId9"/>
+    <sheet name="031 - Diode - Schottky" sheetId="11" r:id="rId10"/>
+    <sheet name="032 - Diode - TVS" sheetId="14" r:id="rId11"/>
+    <sheet name="033 - Diode - LED" sheetId="12" r:id="rId12"/>
+    <sheet name="035 - Varistor " sheetId="27" r:id="rId13"/>
+    <sheet name="040 - Fuses" sheetId="10" r:id="rId14"/>
+    <sheet name="041 - Optoisolators" sheetId="26" r:id="rId15"/>
+    <sheet name="043 - Transistors" sheetId="21" r:id="rId16"/>
+    <sheet name="045 - Crystal" sheetId="19" r:id="rId17"/>
+    <sheet name="050 - ICs - Analog" sheetId="2" r:id="rId18"/>
+    <sheet name="051 - ICs - Digital" sheetId="24" r:id="rId19"/>
+    <sheet name="055 - Drivers" sheetId="20" r:id="rId20"/>
+    <sheet name="060 - Sensor" sheetId="3" r:id="rId21"/>
+    <sheet name="062 - Amplifiers" sheetId="25" r:id="rId22"/>
+    <sheet name="070 - Power Supply" sheetId="8" r:id="rId23"/>
+    <sheet name="090 - Processor" sheetId="18" r:id="rId24"/>
+    <sheet name="100 - Electromechanicals" sheetId="15" r:id="rId25"/>
+    <sheet name="110 - Connectors" sheetId="13" r:id="rId26"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -49,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8098" uniqueCount="4023">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8126" uniqueCount="4032">
   <si>
     <t>ID</t>
   </si>
@@ -12118,6 +12119,33 @@
   </si>
   <si>
     <t>https://www.mouser.es/en/ProductDetail/Littelfuse/0407003.WR?qs=sPbYRqrBIVmOJKm3qiJ6qQ%3D%3D</t>
+  </si>
+  <si>
+    <t>002-0001</t>
+  </si>
+  <si>
+    <t>Aluminium Electrolytic Capacitors - SMD WCAP-ASLI 100uF 35V 20% SMD/SMT</t>
+  </si>
+  <si>
+    <t>100uF 35V 20%</t>
+  </si>
+  <si>
+    <t>SMD;D6.3xL7.7mm</t>
+  </si>
+  <si>
+    <t>865080545012</t>
+  </si>
+  <si>
+    <t>710-865080545012</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/865080545012.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/en/ProductDetail/Wurth-Elektronik/865080545012?qs=sGAEpiMZZMvwFf0viD3Y3aZipiehufnXd0sMoxxC1VosESYZCg0Q6Q%3D%3D</t>
+  </si>
+  <si>
+    <t>CAP_SMD_D6.3xL7.7mm</t>
   </si>
 </sst>
 </file>
@@ -12308,7 +12336,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -12373,8 +12401,6 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -18476,6 +18502,649 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FE2008B-4BF4-4C9A-883A-FEE5873AEAF4}">
+  <dimension ref="A1:N14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetData>
+    <row r="1" spans="1:14" ht="16" customHeight="1">
+      <c r="A1" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="24" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="16" customHeight="1">
+      <c r="A2" s="7" t="s">
+        <v>1911</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>1912</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>1913</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>1914</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>1858</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>1915</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>1916</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>1917</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>1918</v>
+      </c>
+      <c r="L2" s="7" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M2" s="13" t="s">
+        <v>1919</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="16" customHeight="1">
+      <c r="A3" s="7" t="s">
+        <v>1920</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>1921</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>1922</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>1923</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>1924</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>1925</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I3" s="15" t="s">
+        <v>1926</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>1927</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>1918</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>1923</v>
+      </c>
+      <c r="N3" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="16" customHeight="1">
+      <c r="A4" s="7" t="s">
+        <v>1928</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>1929</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>1930</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>1904</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>1931</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>1932</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>1933</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>1934</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>1935</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>1918</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>1904</v>
+      </c>
+      <c r="N4" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="16" customHeight="1">
+      <c r="A5" s="7" t="s">
+        <v>1936</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>1937</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>1938</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>1856</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>1939</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>1877</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>1940</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I5" s="25" t="s">
+        <v>1941</v>
+      </c>
+      <c r="J5" s="25" t="s">
+        <v>1942</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>1943</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M5" s="13" t="s">
+        <v>1856</v>
+      </c>
+      <c r="N5" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="16" customHeight="1">
+      <c r="A6" s="7" t="s">
+        <v>1944</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>1945</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>1946</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>1947</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>1948</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>1868</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>1949</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>1950</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>1951</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>1918</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>1904</v>
+      </c>
+      <c r="N6" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="16" customHeight="1">
+      <c r="A7" s="7" t="s">
+        <v>1952</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>1953</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>1954</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>1955</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>1956</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>1957</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>1958</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="18" t="s">
+        <v>1959</v>
+      </c>
+      <c r="J7" s="18" t="s">
+        <v>1960</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>1918</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M7" s="7" t="s">
+        <v>1955</v>
+      </c>
+      <c r="N7" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="16" customHeight="1">
+      <c r="A8" s="7" t="s">
+        <v>1961</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>1962</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>1874</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>1963</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>1964</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>1965</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>1966</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I8" s="18" t="s">
+        <v>1967</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>1968</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>1918</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>1904</v>
+      </c>
+      <c r="N8" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="16" customHeight="1">
+      <c r="A9" s="7" t="s">
+        <v>1969</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>1970</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>1971</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>1963</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>1972</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>1973</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>1974</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I9" s="18" t="s">
+        <v>1975</v>
+      </c>
+      <c r="J9" s="18" t="s">
+        <v>1976</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>1918</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M9" s="7" t="s">
+        <v>1904</v>
+      </c>
+      <c r="N9" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="16" customHeight="1">
+      <c r="A10" s="16" t="s">
+        <v>1977</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>1978</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>1979</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>1980</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>1981</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>1982</v>
+      </c>
+      <c r="H10" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="I10" s="18" t="s">
+        <v>1983</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>1984</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>1918</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>1985</v>
+      </c>
+      <c r="N10" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="16" customHeight="1">
+      <c r="A11" s="16" t="s">
+        <v>1986</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>1987</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>1988</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>1989</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>1990</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>1957</v>
+      </c>
+      <c r="G11" s="17" t="s">
+        <v>1991</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I11" s="18" t="s">
+        <v>1992</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>1993</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>1918</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>1994</v>
+      </c>
+      <c r="N11" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="16" customHeight="1">
+      <c r="A12" s="16" t="s">
+        <v>1995</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>1996</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>1997</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>1875</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>1998</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>1999</v>
+      </c>
+      <c r="G12" s="17" t="s">
+        <v>2000</v>
+      </c>
+      <c r="H12" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="I12" s="18" t="s">
+        <v>2001</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>2002</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>1918</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M12" s="7" t="s">
+        <v>1881</v>
+      </c>
+      <c r="N12" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="16" t="s">
+        <v>2994</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>2995</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>2996</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>2997</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>2998</v>
+      </c>
+      <c r="F13" s="17" t="s">
+        <v>1957</v>
+      </c>
+      <c r="G13" s="17" t="s">
+        <v>2999</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I13" t="s">
+        <v>2993</v>
+      </c>
+      <c r="J13" s="26" t="s">
+        <v>2992</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>1943</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>1994</v>
+      </c>
+      <c r="N13" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="16" t="s">
+        <v>3693</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>3692</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>1997</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E14" t="s">
+        <v>3694</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>1858</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3695</v>
+      </c>
+      <c r="H14" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I14" s="26" t="s">
+        <v>3696</v>
+      </c>
+      <c r="J14" s="31" t="s">
+        <v>3697</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>1918</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M14" t="s">
+        <v>2047</v>
+      </c>
+      <c r="N14" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="15" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="I3" r:id="rId1" xr:uid="{00000000-0004-0000-0900-000000000000}"/>
+    <hyperlink ref="I5" r:id="rId2" xr:uid="{00000000-0004-0000-0900-000001000000}"/>
+    <hyperlink ref="J5" r:id="rId3" xr:uid="{00000000-0004-0000-0900-000002000000}"/>
+    <hyperlink ref="I7" r:id="rId4" xr:uid="{8F1A973E-B5AB-44F6-96AD-40713F29721B}"/>
+    <hyperlink ref="J7" r:id="rId5" display="https://www.mouser.es/ProductDetail/Vishay-Semiconductors/BZX55C5V1-TR?qs=WLTup5mM6hhy%252Bqloxl7%2FIQ%3D%3D&amp;utm_id=20109199436&amp;utm_source=google&amp;utm_medium=cpc&amp;utm_marketing_tactic=emeacorp&amp;gad_source=1&amp;gad_campaignid=20109199436&amp;gbraid=0AAAAADn_wf2RhF_lSG_YlgnN1Yzlq3oak&amp;gclid=Cj0KCQiAhtvMBhDBARIsAL26pjE6pviBOpVaBUJ07A83YFMQUf7QkOHJpiHMP9nHJbQo8SvNA6LellYaAlJaEALw_wcB" xr:uid="{F2496565-AD95-4399-945A-CAC2965FBB51}"/>
+    <hyperlink ref="I8" r:id="rId6" xr:uid="{0E407122-DEDC-4464-8361-A36EA45E6AB5}"/>
+    <hyperlink ref="J9" r:id="rId7" xr:uid="{3E5FFD60-2B94-43D5-BD33-FCAB73A614C5}"/>
+    <hyperlink ref="I9" r:id="rId8" xr:uid="{FAF085BE-308D-4591-BB1A-0398244BD98C}"/>
+    <hyperlink ref="I10" r:id="rId9" xr:uid="{43EA2952-ABB5-4F52-94F7-A96F82DE8560}"/>
+    <hyperlink ref="I11" r:id="rId10" xr:uid="{E8167B89-7FBA-4877-BC25-3D4C05ED8AA6}"/>
+    <hyperlink ref="I12" r:id="rId11" xr:uid="{C4B46D5B-BD3F-4DBC-A61E-40C494B3D177}"/>
+    <hyperlink ref="J13" r:id="rId12" xr:uid="{0C7D58F5-DE06-4F14-BC9F-F6688DDA76B4}"/>
+    <hyperlink ref="I14" r:id="rId13" xr:uid="{69D5D5EE-78C1-424D-8FB6-5CEE6BF86BEE}"/>
+    <hyperlink ref="J14" r:id="rId14" xr:uid="{E4E8D2D8-B131-437F-A58D-DE6AA7E926D6}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79E65951-BFD2-4888-A0A6-19D5130CB4A6}">
   <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -19546,7 +20215,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89BFA1EF-29B2-41E4-A9D1-F8E90A663FA1}">
   <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -20631,7 +21300,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ED8913B-580D-466F-B6D1-947424810FAF}">
   <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -20780,7 +21449,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B6F0D32-9CE2-4DF7-927E-42E7BA331F12}">
   <dimension ref="A1:O30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -21993,25 +22662,25 @@
       <c r="A28" t="s">
         <v>4005</v>
       </c>
-      <c r="B28" s="43" t="s">
+      <c r="B28" s="16" t="s">
         <v>4008</v>
       </c>
-      <c r="C28" s="43" t="s">
+      <c r="C28" s="16" t="s">
         <v>1694</v>
       </c>
       <c r="D28" s="16">
         <v>1206</v>
       </c>
-      <c r="E28" s="43" t="s">
+      <c r="E28" s="16" t="s">
         <v>4009</v>
       </c>
-      <c r="F28" s="43" t="s">
+      <c r="F28" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="G28" s="42" t="s">
+      <c r="G28" s="3" t="s">
         <v>4010</v>
       </c>
-      <c r="H28" s="43" t="s">
+      <c r="H28" s="16" t="s">
         <v>21</v>
       </c>
       <c r="I28" s="26" t="s">
@@ -22037,25 +22706,25 @@
       <c r="A29" t="s">
         <v>4006</v>
       </c>
-      <c r="B29" s="43" t="s">
+      <c r="B29" s="16" t="s">
         <v>4013</v>
       </c>
-      <c r="C29" s="43" t="s">
+      <c r="C29" s="16" t="s">
         <v>1748</v>
       </c>
       <c r="D29" s="16">
         <v>1206</v>
       </c>
-      <c r="E29" s="43" t="s">
+      <c r="E29" s="16" t="s">
         <v>4014</v>
       </c>
-      <c r="F29" s="43" t="s">
+      <c r="F29" s="16" t="s">
         <v>1516</v>
       </c>
-      <c r="G29" s="42" t="s">
+      <c r="G29" s="3" t="s">
         <v>4015</v>
       </c>
-      <c r="H29" s="43" t="s">
+      <c r="H29" s="16" t="s">
         <v>21</v>
       </c>
       <c r="I29" s="26" t="s">
@@ -22081,25 +22750,25 @@
       <c r="A30" t="s">
         <v>4007</v>
       </c>
-      <c r="B30" s="43" t="s">
+      <c r="B30" s="16" t="s">
         <v>4018</v>
       </c>
-      <c r="C30" s="43" t="s">
+      <c r="C30" s="16" t="s">
         <v>1703</v>
       </c>
       <c r="D30" s="16">
         <v>1206</v>
       </c>
-      <c r="E30" s="43" t="s">
+      <c r="E30" s="16" t="s">
         <v>4019</v>
       </c>
-      <c r="F30" s="43" t="s">
+      <c r="F30" s="16" t="s">
         <v>1696</v>
       </c>
-      <c r="G30" s="42" t="s">
+      <c r="G30" s="3" t="s">
         <v>4020</v>
       </c>
-      <c r="H30" s="43" t="s">
+      <c r="H30" s="16" t="s">
         <v>21</v>
       </c>
       <c r="I30" s="26" t="s">
@@ -22161,7 +22830,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA7E41C9-E62B-4149-A5B5-E7986E8877E6}">
   <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -22309,7 +22978,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FAFF3B6-AF11-4BFB-8078-829FF6F2F366}">
   <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -22458,7 +23127,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E5535EA-E186-4751-BC7F-9B3A0221302E}">
   <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -22607,7 +23276,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C98E1A12-072F-4773-8CB5-47FFE077E85B}">
   <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -23038,7 +23707,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{316C64E0-14FB-467C-956A-E132FAFB0232}">
   <dimension ref="A1:N1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -23092,7 +23761,114 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFB39079-151D-4B88-9E1F-4966291E2A6B}">
+  <dimension ref="A1:N3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
+        <v>4023</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4024</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4025</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4026</v>
+      </c>
+      <c r="E2" s="35" t="s">
+        <v>4027</v>
+      </c>
+      <c r="F2" t="s">
+        <v>2910</v>
+      </c>
+      <c r="G2" t="s">
+        <v>4028</v>
+      </c>
+      <c r="H2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>4029</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>4030</v>
+      </c>
+      <c r="K2" t="s">
+        <v>2914</v>
+      </c>
+      <c r="L2" t="s">
+        <v>61</v>
+      </c>
+      <c r="M2" t="s">
+        <v>4031</v>
+      </c>
+      <c r="N2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="E3" s="35"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="I2" r:id="rId1" xr:uid="{7F4E5802-B153-4D0C-8879-C0514F223C95}"/>
+    <hyperlink ref="J2" r:id="rId2" xr:uid="{5FC5E7A4-977E-401E-AA44-8F2BD7941973}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{201D74E2-3547-4E9B-8216-09A22645AC2A}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -23194,158 +23970,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E05CC479-3669-40F7-BE22-BA5CFBFF29E9}">
-  <dimension ref="A1:N3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
-  <cols>
-    <col min="5" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" t="s">
-        <v>2906</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2907</v>
-      </c>
-      <c r="C2" t="s">
-        <v>2908</v>
-      </c>
-      <c r="D2" t="s">
-        <v>2909</v>
-      </c>
-      <c r="E2" s="35" t="s">
-        <v>3205</v>
-      </c>
-      <c r="F2" t="s">
-        <v>2910</v>
-      </c>
-      <c r="G2" t="s">
-        <v>2911</v>
-      </c>
-      <c r="H2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>2912</v>
-      </c>
-      <c r="J2" t="s">
-        <v>2913</v>
-      </c>
-      <c r="K2" t="s">
-        <v>2914</v>
-      </c>
-      <c r="L2" t="s">
-        <v>61</v>
-      </c>
-      <c r="M2" t="s">
-        <v>2915</v>
-      </c>
-      <c r="N2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
-        <v>3201</v>
-      </c>
-      <c r="B3" t="s">
-        <v>3202</v>
-      </c>
-      <c r="C3" t="s">
-        <v>3203</v>
-      </c>
-      <c r="D3" t="s">
-        <v>3204</v>
-      </c>
-      <c r="E3" s="35" t="s">
-        <v>3206</v>
-      </c>
-      <c r="F3" t="s">
-        <v>2910</v>
-      </c>
-      <c r="G3" t="s">
-        <v>3207</v>
-      </c>
-      <c r="H3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>3208</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>3209</v>
-      </c>
-      <c r="K3" t="s">
-        <v>2914</v>
-      </c>
-      <c r="L3" t="s">
-        <v>61</v>
-      </c>
-      <c r="M3" t="s">
-        <v>3210</v>
-      </c>
-      <c r="N3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="15" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="I2" r:id="rId1" xr:uid="{BB2EDAB8-75EB-46D2-BA14-384BF06E1A6E}"/>
-    <hyperlink ref="I3" r:id="rId2" xr:uid="{8F6B3EB5-F217-4353-ABA9-F461982FB5ED}"/>
-    <hyperlink ref="J3" r:id="rId3" xr:uid="{E90B210E-79B4-494B-B985-7D11C4705F7B}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59BC8B2E-A067-463D-937A-30E88D8BECD0}">
   <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -23540,7 +24165,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4185B0A-D162-4EBC-935B-7159E365DD54}">
   <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -23689,7 +24314,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4BBBCF5-BAC9-459C-ABE9-2526B85FD81E}">
   <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -24157,7 +24782,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E9EB2F5-2977-493B-BFA2-5CD20F8A3BC4}">
   <dimension ref="A1:O3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -24315,7 +24940,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69A1C46E-DEF3-467B-A5BD-162AB66E6A86}">
   <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -25398,7 +26023,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE14AD29-8DB0-4C42-AB91-A73B867AE121}">
   <dimension ref="A1:N77"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -28614,6 +29239,157 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E05CC479-3669-40F7-BE22-BA5CFBFF29E9}">
+  <dimension ref="A1:N3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="5" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
+        <v>2906</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2907</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2908</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2909</v>
+      </c>
+      <c r="E2" s="35" t="s">
+        <v>3205</v>
+      </c>
+      <c r="F2" t="s">
+        <v>2910</v>
+      </c>
+      <c r="G2" t="s">
+        <v>2911</v>
+      </c>
+      <c r="H2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>2912</v>
+      </c>
+      <c r="J2" t="s">
+        <v>2913</v>
+      </c>
+      <c r="K2" t="s">
+        <v>2914</v>
+      </c>
+      <c r="L2" t="s">
+        <v>61</v>
+      </c>
+      <c r="M2" t="s">
+        <v>2915</v>
+      </c>
+      <c r="N2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>3201</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3202</v>
+      </c>
+      <c r="C3" t="s">
+        <v>3203</v>
+      </c>
+      <c r="D3" t="s">
+        <v>3204</v>
+      </c>
+      <c r="E3" s="35" t="s">
+        <v>3206</v>
+      </c>
+      <c r="F3" t="s">
+        <v>2910</v>
+      </c>
+      <c r="G3" t="s">
+        <v>3207</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>3208</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>3209</v>
+      </c>
+      <c r="K3" t="s">
+        <v>2914</v>
+      </c>
+      <c r="L3" t="s">
+        <v>61</v>
+      </c>
+      <c r="M3" t="s">
+        <v>3210</v>
+      </c>
+      <c r="N3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="15" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="I2" r:id="rId1" xr:uid="{BB2EDAB8-75EB-46D2-BA14-384BF06E1A6E}"/>
+    <hyperlink ref="I3" r:id="rId2" xr:uid="{8F6B3EB5-F217-4353-ABA9-F461982FB5ED}"/>
+    <hyperlink ref="J3" r:id="rId3" xr:uid="{E90B210E-79B4-494B-B985-7D11C4705F7B}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E940ACE-72CF-4504-B730-2719484575BC}">
   <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -28765,7 +29541,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60E8291E-4293-4634-B9E9-80CB520CA181}">
   <dimension ref="A1:N192"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -37398,7 +38174,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81F9848D-6D60-47C0-9F84-A561FE4F106E}">
   <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -37825,7 +38601,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01C6B0FD-D8A3-44EC-9532-03DDA232F922}">
   <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -38020,7 +38796,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D956EFE-E955-4E62-8478-2294E6413DC1}">
   <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -38168,7 +38944,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{652841DA-3619-42EE-A536-61B58BE1B457}">
   <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -38578,647 +39354,4 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FE2008B-4BF4-4C9A-883A-FEE5873AEAF4}">
-  <dimension ref="A1:N14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
-  <sheetData>
-    <row r="1" spans="1:14" ht="16" customHeight="1">
-      <c r="A1" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="24" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="24" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="24" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" ht="16" customHeight="1">
-      <c r="A2" s="7" t="s">
-        <v>1911</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>1912</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>1913</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>1914</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>1858</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>1915</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>1916</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>1917</v>
-      </c>
-      <c r="K2" s="7" t="s">
-        <v>1918</v>
-      </c>
-      <c r="L2" s="7" t="s">
-        <v>1910</v>
-      </c>
-      <c r="M2" s="13" t="s">
-        <v>1919</v>
-      </c>
-      <c r="N2" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" ht="16" customHeight="1">
-      <c r="A3" s="7" t="s">
-        <v>1920</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>1921</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>1922</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>1923</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>1924</v>
-      </c>
-      <c r="F3" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>1925</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I3" s="15" t="s">
-        <v>1926</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>1927</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>1918</v>
-      </c>
-      <c r="L3" s="7" t="s">
-        <v>1910</v>
-      </c>
-      <c r="M3" s="7" t="s">
-        <v>1923</v>
-      </c>
-      <c r="N3" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="16" customHeight="1">
-      <c r="A4" s="7" t="s">
-        <v>1928</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>1929</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>1930</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>1904</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>1931</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>1932</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>1933</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>1934</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>1935</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>1918</v>
-      </c>
-      <c r="L4" s="7" t="s">
-        <v>1910</v>
-      </c>
-      <c r="M4" s="7" t="s">
-        <v>1904</v>
-      </c>
-      <c r="N4" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="16" customHeight="1">
-      <c r="A5" s="7" t="s">
-        <v>1936</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>1937</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>1938</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>1856</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>1939</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>1877</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>1940</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I5" s="25" t="s">
-        <v>1941</v>
-      </c>
-      <c r="J5" s="25" t="s">
-        <v>1942</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>1943</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>1910</v>
-      </c>
-      <c r="M5" s="13" t="s">
-        <v>1856</v>
-      </c>
-      <c r="N5" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="16" customHeight="1">
-      <c r="A6" s="7" t="s">
-        <v>1944</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>1945</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>1946</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>1947</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>1948</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>1868</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>1949</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>1950</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>1951</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>1918</v>
-      </c>
-      <c r="L6" s="7" t="s">
-        <v>1910</v>
-      </c>
-      <c r="M6" s="7" t="s">
-        <v>1904</v>
-      </c>
-      <c r="N6" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="16" customHeight="1">
-      <c r="A7" s="7" t="s">
-        <v>1952</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>1953</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>1954</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>1955</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>1956</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>1957</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>1958</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="I7" s="18" t="s">
-        <v>1959</v>
-      </c>
-      <c r="J7" s="18" t="s">
-        <v>1960</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>1918</v>
-      </c>
-      <c r="L7" s="7" t="s">
-        <v>1910</v>
-      </c>
-      <c r="M7" s="7" t="s">
-        <v>1955</v>
-      </c>
-      <c r="N7" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="16" customHeight="1">
-      <c r="A8" s="7" t="s">
-        <v>1961</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>1962</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>1874</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>1963</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>1964</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>1965</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>1966</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I8" s="18" t="s">
-        <v>1967</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>1968</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>1918</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>1910</v>
-      </c>
-      <c r="M8" s="7" t="s">
-        <v>1904</v>
-      </c>
-      <c r="N8" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="16" customHeight="1">
-      <c r="A9" s="7" t="s">
-        <v>1969</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>1970</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>1963</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>1972</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>1973</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>1974</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I9" s="18" t="s">
-        <v>1975</v>
-      </c>
-      <c r="J9" s="18" t="s">
-        <v>1976</v>
-      </c>
-      <c r="K9" s="7" t="s">
-        <v>1918</v>
-      </c>
-      <c r="L9" s="7" t="s">
-        <v>1910</v>
-      </c>
-      <c r="M9" s="7" t="s">
-        <v>1904</v>
-      </c>
-      <c r="N9" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="16" customHeight="1">
-      <c r="A10" s="16" t="s">
-        <v>1977</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>1978</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>1979</v>
-      </c>
-      <c r="D10" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="E10" s="17" t="s">
-        <v>1980</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>1981</v>
-      </c>
-      <c r="G10" s="16" t="s">
-        <v>1982</v>
-      </c>
-      <c r="H10" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="I10" s="18" t="s">
-        <v>1983</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>1984</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>1918</v>
-      </c>
-      <c r="L10" s="7" t="s">
-        <v>1910</v>
-      </c>
-      <c r="M10" s="16" t="s">
-        <v>1985</v>
-      </c>
-      <c r="N10" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="16" customHeight="1">
-      <c r="A11" s="16" t="s">
-        <v>1986</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>1987</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>1988</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>1989</v>
-      </c>
-      <c r="E11" s="17" t="s">
-        <v>1990</v>
-      </c>
-      <c r="F11" s="17" t="s">
-        <v>1957</v>
-      </c>
-      <c r="G11" s="17" t="s">
-        <v>1991</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="I11" s="18" t="s">
-        <v>1992</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>1993</v>
-      </c>
-      <c r="K11" s="7" t="s">
-        <v>1918</v>
-      </c>
-      <c r="L11" s="7" t="s">
-        <v>1910</v>
-      </c>
-      <c r="M11" s="16" t="s">
-        <v>1994</v>
-      </c>
-      <c r="N11" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="16" customHeight="1">
-      <c r="A12" s="16" t="s">
-        <v>1995</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>1996</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>1997</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>1875</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>1998</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>1999</v>
-      </c>
-      <c r="G12" s="17" t="s">
-        <v>2000</v>
-      </c>
-      <c r="H12" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="I12" s="18" t="s">
-        <v>2001</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>2002</v>
-      </c>
-      <c r="K12" s="7" t="s">
-        <v>1918</v>
-      </c>
-      <c r="L12" s="7" t="s">
-        <v>1910</v>
-      </c>
-      <c r="M12" s="7" t="s">
-        <v>1881</v>
-      </c>
-      <c r="N12" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="16" t="s">
-        <v>2994</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>2995</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>2996</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>2997</v>
-      </c>
-      <c r="E13" s="17" t="s">
-        <v>2998</v>
-      </c>
-      <c r="F13" s="17" t="s">
-        <v>1957</v>
-      </c>
-      <c r="G13" s="17" t="s">
-        <v>2999</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="I13" t="s">
-        <v>2993</v>
-      </c>
-      <c r="J13" s="26" t="s">
-        <v>2992</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>1943</v>
-      </c>
-      <c r="L13" s="7" t="s">
-        <v>1910</v>
-      </c>
-      <c r="M13" s="16" t="s">
-        <v>1994</v>
-      </c>
-      <c r="N13" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" s="16" t="s">
-        <v>3693</v>
-      </c>
-      <c r="B14" s="16" t="s">
-        <v>3692</v>
-      </c>
-      <c r="C14" s="16" t="s">
-        <v>1997</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E14" t="s">
-        <v>3694</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>1858</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>3695</v>
-      </c>
-      <c r="H14" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="I14" s="26" t="s">
-        <v>3696</v>
-      </c>
-      <c r="J14" s="31" t="s">
-        <v>3697</v>
-      </c>
-      <c r="K14" s="7" t="s">
-        <v>1918</v>
-      </c>
-      <c r="L14" s="7" t="s">
-        <v>1910</v>
-      </c>
-      <c r="M14" t="s">
-        <v>2047</v>
-      </c>
-      <c r="N14" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="15" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="I3" r:id="rId1" xr:uid="{00000000-0004-0000-0900-000000000000}"/>
-    <hyperlink ref="I5" r:id="rId2" xr:uid="{00000000-0004-0000-0900-000001000000}"/>
-    <hyperlink ref="J5" r:id="rId3" xr:uid="{00000000-0004-0000-0900-000002000000}"/>
-    <hyperlink ref="I7" r:id="rId4" xr:uid="{8F1A973E-B5AB-44F6-96AD-40713F29721B}"/>
-    <hyperlink ref="J7" r:id="rId5" display="https://www.mouser.es/ProductDetail/Vishay-Semiconductors/BZX55C5V1-TR?qs=WLTup5mM6hhy%252Bqloxl7%2FIQ%3D%3D&amp;utm_id=20109199436&amp;utm_source=google&amp;utm_medium=cpc&amp;utm_marketing_tactic=emeacorp&amp;gad_source=1&amp;gad_campaignid=20109199436&amp;gbraid=0AAAAADn_wf2RhF_lSG_YlgnN1Yzlq3oak&amp;gclid=Cj0KCQiAhtvMBhDBARIsAL26pjE6pviBOpVaBUJ07A83YFMQUf7QkOHJpiHMP9nHJbQo8SvNA6LellYaAlJaEALw_wcB" xr:uid="{F2496565-AD95-4399-945A-CAC2965FBB51}"/>
-    <hyperlink ref="I8" r:id="rId6" xr:uid="{0E407122-DEDC-4464-8361-A36EA45E6AB5}"/>
-    <hyperlink ref="J9" r:id="rId7" xr:uid="{3E5FFD60-2B94-43D5-BD33-FCAB73A614C5}"/>
-    <hyperlink ref="I9" r:id="rId8" xr:uid="{FAF085BE-308D-4591-BB1A-0398244BD98C}"/>
-    <hyperlink ref="I10" r:id="rId9" xr:uid="{43EA2952-ABB5-4F52-94F7-A96F82DE8560}"/>
-    <hyperlink ref="I11" r:id="rId10" xr:uid="{E8167B89-7FBA-4877-BC25-3D4C05ED8AA6}"/>
-    <hyperlink ref="I12" r:id="rId11" xr:uid="{C4B46D5B-BD3F-4DBC-A61E-40C494B3D177}"/>
-    <hyperlink ref="J13" r:id="rId12" xr:uid="{0C7D58F5-DE06-4F14-BC9F-F6688DDA76B4}"/>
-    <hyperlink ref="I14" r:id="rId13" xr:uid="{69D5D5EE-78C1-424D-8FB6-5CEE6BF86BEE}"/>
-    <hyperlink ref="J14" r:id="rId14" xr:uid="{E4E8D2D8-B131-437F-A58D-DE6AA7E926D6}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14555C9A-C152-490F-833E-6CC2CC5B4082}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C073111-5ADB-4259-B3A9-B2F2C16A743E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25812" yWindow="2292" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25812" yWindow="2292" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8126" uniqueCount="4032">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8140" uniqueCount="4038">
   <si>
     <t>ID</t>
   </si>
@@ -12146,6 +12146,24 @@
   </si>
   <si>
     <t>CAP_SMD_D6.3xL7.7mm</t>
+  </si>
+  <si>
+    <t>010-0192</t>
+  </si>
+  <si>
+    <t>Thick Film Resistors - SMD WRIS-RSKS 3 kOhms 1 % 0.1 W 0603 AEC-Q200</t>
+  </si>
+  <si>
+    <t>560112116128</t>
+  </si>
+  <si>
+    <t>710-560112116128</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/560112116128.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/en/ProductDetail/Wurth-Elektronik/560112116128?qs=mELouGlnn3d9zmvF5OWSLQ%3D%3D</t>
   </si>
 </sst>
 </file>
@@ -12336,7 +12354,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -12401,6 +12419,8 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -29543,7 +29563,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60E8291E-4293-4634-B9E9-80CB520CA181}">
-  <dimension ref="A1:N192"/>
+  <dimension ref="A1:N193"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="3" max="3" width="19.90625" customWidth="1"/>
@@ -37990,6 +38010,50 @@
         <v>57</v>
       </c>
       <c r="N192" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="193" spans="1:14">
+      <c r="A193" s="16" t="s">
+        <v>4032</v>
+      </c>
+      <c r="B193" t="s">
+        <v>4033</v>
+      </c>
+      <c r="C193" s="16" t="s">
+        <v>3638</v>
+      </c>
+      <c r="D193" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="E193" s="42" t="s">
+        <v>4034</v>
+      </c>
+      <c r="F193" s="30" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G193" s="43" t="s">
+        <v>4035</v>
+      </c>
+      <c r="H193" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I193" s="26" t="s">
+        <v>4036</v>
+      </c>
+      <c r="J193" s="2" t="s">
+        <v>4037</v>
+      </c>
+      <c r="K193" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L193" s="17" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M193" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="N193" t="s">
         <v>25</v>
       </c>
     </row>
@@ -38168,9 +38232,11 @@
     <hyperlink ref="I191" r:id="rId170" xr:uid="{1A8D28AA-426F-4991-A638-E362EF62E8B7}"/>
     <hyperlink ref="J191" r:id="rId171" xr:uid="{0D368A4C-5099-4A8A-AFA4-4A14478071B4}"/>
     <hyperlink ref="I192" r:id="rId172" xr:uid="{22F61D15-F86A-45C4-8028-A72154D709C5}"/>
+    <hyperlink ref="I193" r:id="rId173" xr:uid="{07829D1D-2983-449B-882E-3547A4DE1790}"/>
+    <hyperlink ref="J193" r:id="rId174" xr:uid="{09130F36-EB0C-4DF6-9294-3943018EB965}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId173"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId175"/>
 </worksheet>
 </file>
 

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C073111-5ADB-4259-B3A9-B2F2C16A743E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91F5C328-6A90-4B21-84D4-FEF872235481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25812" yWindow="2292" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25812" yWindow="2292" windowWidth="23256" windowHeight="12456" firstSheet="21" activeTab="25" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8140" uniqueCount="4038">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8152" uniqueCount="4044">
   <si>
     <t>ID</t>
   </si>
@@ -12164,6 +12164,24 @@
   </si>
   <si>
     <t>https://www.mouser.es/en/ProductDetail/Wurth-Elektronik/560112116128?qs=mELouGlnn3d9zmvF5OWSLQ%3D%3D</t>
+  </si>
+  <si>
+    <t>110-0071</t>
+  </si>
+  <si>
+    <t>Headers &amp; Wire Housings WR-MPC4 4.20mm Male 8Pin Dual Angld Hdr</t>
+  </si>
+  <si>
+    <t>THT 4,2mm</t>
+  </si>
+  <si>
+    <t>710-64900821022</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/64900821022.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/en/ProductDetail/Wurth-Elektronik/64900821022?qs=2kOmHSv6VfTuXY%252Btdsgz%252BA%3D%3D</t>
   </si>
 </sst>
 </file>
@@ -12354,7 +12372,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -12419,8 +12437,9 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -29177,6 +29196,50 @@
         <v>25</v>
       </c>
     </row>
+    <row r="72" spans="1:14">
+      <c r="A72" s="16" t="s">
+        <v>4038</v>
+      </c>
+      <c r="B72" s="43" t="s">
+        <v>4039</v>
+      </c>
+      <c r="C72" s="43" t="s">
+        <v>2513</v>
+      </c>
+      <c r="D72" s="16" t="s">
+        <v>4040</v>
+      </c>
+      <c r="E72" s="44">
+        <v>64900821022</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G72" s="42" t="s">
+        <v>4041</v>
+      </c>
+      <c r="H72" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I72" s="26" t="s">
+        <v>4042</v>
+      </c>
+      <c r="J72" s="26" t="s">
+        <v>4043</v>
+      </c>
+      <c r="K72" s="17" t="s">
+        <v>2533</v>
+      </c>
+      <c r="L72" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M72" s="44">
+        <v>64900821022</v>
+      </c>
+      <c r="N72" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
     <row r="73" spans="1:14">
       <c r="M73" s="40"/>
     </row>
@@ -29253,6 +29316,8 @@
     <hyperlink ref="J70" r:id="rId65" xr:uid="{03F14566-E754-46FF-B4A8-8273B9090065}"/>
     <hyperlink ref="I71" r:id="rId66" xr:uid="{96F2E17A-16DE-48A9-8D88-69602C1C2F6E}"/>
     <hyperlink ref="J71" r:id="rId67" xr:uid="{F7B2F86A-80EA-4ECB-93DF-E8DCEAA063DF}"/>
+    <hyperlink ref="I72" r:id="rId68" xr:uid="{3FD52375-437E-497D-BBC8-5C178AB310AA}"/>
+    <hyperlink ref="J72" r:id="rId69" xr:uid="{EAAEE1FA-CC92-4E8E-932F-2025B40D678E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -38026,13 +38091,13 @@
       <c r="D193" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="E193" s="42" t="s">
+      <c r="E193" s="20" t="s">
         <v>4034</v>
       </c>
       <c r="F193" s="30" t="s">
         <v>2100</v>
       </c>
-      <c r="G193" s="43" t="s">
+      <c r="G193" s="30" t="s">
         <v>4035</v>
       </c>
       <c r="H193" s="16" t="s">

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91F5C328-6A90-4B21-84D4-FEF872235481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC99B7BE-E5D8-4DB3-A211-CB87C067F14E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25812" yWindow="2292" windowWidth="23256" windowHeight="12456" firstSheet="21" activeTab="25" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" firstSheet="21" activeTab="25" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8152" uniqueCount="4044">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8166" uniqueCount="4053">
   <si>
     <t>ID</t>
   </si>
@@ -12182,6 +12182,33 @@
   </si>
   <si>
     <t>https://www.mouser.es/en/ProductDetail/Wurth-Elektronik/64900821022?qs=2kOmHSv6VfTuXY%252Btdsgz%252BA%3D%3D</t>
+  </si>
+  <si>
+    <t>110-0072</t>
+  </si>
+  <si>
+    <t>Automotive Connectors 2Pos 90deg PCB Flng Mnt Rcpt Tin potted</t>
+  </si>
+  <si>
+    <t>THT 6,7mm</t>
+  </si>
+  <si>
+    <t>ATP13-2P-BM04GRY</t>
+  </si>
+  <si>
+    <t>Amphenol Sine Systems</t>
+  </si>
+  <si>
+    <t>654-ATP13-2P-BM04GRY</t>
+  </si>
+  <si>
+    <t>https://www.amphenol-sine.com/pdf/datasheet/ATP13-2P-BM04GRY.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/en/ProductDetail/Amphenol-SINE-Systems/ATP13-2P-BM04GRY?qs=OTrKUuiFdkbRMxe%252BxsSZwA%3D%3D</t>
+  </si>
+  <si>
+    <t>ATP13-2P</t>
   </si>
 </sst>
 </file>
@@ -12372,7 +12399,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -12439,7 +12466,8 @@
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -29200,22 +29228,22 @@
       <c r="A72" s="16" t="s">
         <v>4038</v>
       </c>
-      <c r="B72" s="43" t="s">
+      <c r="B72" s="16" t="s">
         <v>4039</v>
       </c>
-      <c r="C72" s="43" t="s">
+      <c r="C72" s="16" t="s">
         <v>2513</v>
       </c>
       <c r="D72" s="16" t="s">
         <v>4040</v>
       </c>
-      <c r="E72" s="44">
+      <c r="E72" s="20">
         <v>64900821022</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>2100</v>
       </c>
-      <c r="G72" s="42" t="s">
+      <c r="G72" s="3" t="s">
         <v>4041</v>
       </c>
       <c r="H72" s="16" t="s">
@@ -29233,7 +29261,7 @@
       <c r="L72" s="7" t="s">
         <v>2572</v>
       </c>
-      <c r="M72" s="44">
+      <c r="M72" s="20">
         <v>64900821022</v>
       </c>
       <c r="N72" s="7" t="s">
@@ -29241,7 +29269,48 @@
       </c>
     </row>
     <row r="73" spans="1:14">
-      <c r="M73" s="40"/>
+      <c r="A73" s="16" t="s">
+        <v>4044</v>
+      </c>
+      <c r="B73" s="43" t="s">
+        <v>4045</v>
+      </c>
+      <c r="C73" s="43" t="s">
+        <v>2170</v>
+      </c>
+      <c r="D73" s="43" t="s">
+        <v>4046</v>
+      </c>
+      <c r="E73" s="43" t="s">
+        <v>4047</v>
+      </c>
+      <c r="F73" s="44" t="s">
+        <v>4048</v>
+      </c>
+      <c r="G73" s="42" t="s">
+        <v>4049</v>
+      </c>
+      <c r="H73" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I73" s="26" t="s">
+        <v>4050</v>
+      </c>
+      <c r="J73" s="26" t="s">
+        <v>4051</v>
+      </c>
+      <c r="K73" s="45" t="s">
+        <v>2176</v>
+      </c>
+      <c r="L73" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="M73" s="43" t="s">
+        <v>4052</v>
+      </c>
+      <c r="N73" s="7" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="77" spans="1:14">
       <c r="I77" s="40"/>
@@ -29318,6 +29387,8 @@
     <hyperlink ref="J71" r:id="rId67" xr:uid="{F7B2F86A-80EA-4ECB-93DF-E8DCEAA063DF}"/>
     <hyperlink ref="I72" r:id="rId68" xr:uid="{3FD52375-437E-497D-BBC8-5C178AB310AA}"/>
     <hyperlink ref="J72" r:id="rId69" xr:uid="{EAAEE1FA-CC92-4E8E-932F-2025B40D678E}"/>
+    <hyperlink ref="I73" r:id="rId70" xr:uid="{BEBF4596-6961-45FE-98BF-66C1250C4174}"/>
+    <hyperlink ref="J73" r:id="rId71" xr:uid="{B0F0D27D-2D3D-4199-9067-2A3FBADE7648}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC99B7BE-E5D8-4DB3-A211-CB87C067F14E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4235B249-C6B6-4632-BAF5-38B9C2EE1155}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" firstSheet="21" activeTab="25" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25812" yWindow="2292" windowWidth="23256" windowHeight="12456" firstSheet="12" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8166" uniqueCount="4053">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8179" uniqueCount="4058">
   <si>
     <t>ID</t>
   </si>
@@ -12209,6 +12209,21 @@
   </si>
   <si>
     <t>ATP13-2P</t>
+  </si>
+  <si>
+    <t>040-0030</t>
+  </si>
+  <si>
+    <t>Surface Mount Fuses JB12S SMD Fuse 63V 10A Slow 1206 3.2mm X 1.6mm</t>
+  </si>
+  <si>
+    <t>JB12S1002R</t>
+  </si>
+  <si>
+    <t>603-JB12S1002R</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/en/ProductDetail/YAGEO/JB12S1002R?qs=iLKYxzqNS77KhcIWcFZ8Jg%3D%3D</t>
   </si>
 </sst>
 </file>
@@ -12399,7 +12414,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -12466,8 +12481,6 @@
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -21518,7 +21531,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B6F0D32-9CE2-4DF7-927E-42E7BA331F12}">
-  <dimension ref="A1:O30"/>
+  <dimension ref="A1:O31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="13" max="13" width="13.36328125" customWidth="1"/>
@@ -22854,6 +22867,50 @@
         <v>1701</v>
       </c>
       <c r="N30" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" t="s">
+        <v>4053</v>
+      </c>
+      <c r="B31" s="43" t="s">
+        <v>4054</v>
+      </c>
+      <c r="C31" s="43" t="s">
+        <v>1754</v>
+      </c>
+      <c r="D31" s="16">
+        <v>1206</v>
+      </c>
+      <c r="E31" s="43" t="s">
+        <v>4055</v>
+      </c>
+      <c r="F31" s="43" t="s">
+        <v>60</v>
+      </c>
+      <c r="G31" s="42" t="s">
+        <v>4056</v>
+      </c>
+      <c r="H31" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="I31" s="26" t="s">
+        <v>4011</v>
+      </c>
+      <c r="J31" s="26" t="s">
+        <v>4057</v>
+      </c>
+      <c r="K31" s="17" t="s">
+        <v>1700</v>
+      </c>
+      <c r="L31" t="s">
+        <v>55</v>
+      </c>
+      <c r="M31" s="7" t="s">
+        <v>1701</v>
+      </c>
+      <c r="N31" t="s">
         <v>25</v>
       </c>
     </row>
@@ -22892,6 +22949,8 @@
     <hyperlink ref="J29" r:id="rId30" xr:uid="{0F119F88-FF89-4B12-848E-7BBFE27299F5}"/>
     <hyperlink ref="I30" r:id="rId31" xr:uid="{C229C9D4-3F37-4DBD-9352-BF5A898D0314}"/>
     <hyperlink ref="J30" r:id="rId32" xr:uid="{B4F8AF74-EF6D-49F1-9CE8-29F632F7A754}"/>
+    <hyperlink ref="I31" r:id="rId33" xr:uid="{912C6D59-6DD8-4011-9862-E5A138D7CA88}"/>
+    <hyperlink ref="J31" r:id="rId34" xr:uid="{1B54DD8B-3D21-4E72-85BA-7DE1FAD354B9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -29272,22 +29331,22 @@
       <c r="A73" s="16" t="s">
         <v>4044</v>
       </c>
-      <c r="B73" s="43" t="s">
+      <c r="B73" s="16" t="s">
         <v>4045</v>
       </c>
-      <c r="C73" s="43" t="s">
+      <c r="C73" s="16" t="s">
         <v>2170</v>
       </c>
-      <c r="D73" s="43" t="s">
+      <c r="D73" s="16" t="s">
         <v>4046</v>
       </c>
-      <c r="E73" s="43" t="s">
+      <c r="E73" s="16" t="s">
         <v>4047</v>
       </c>
-      <c r="F73" s="44" t="s">
+      <c r="F73" s="30" t="s">
         <v>4048</v>
       </c>
-      <c r="G73" s="42" t="s">
+      <c r="G73" s="3" t="s">
         <v>4049</v>
       </c>
       <c r="H73" s="16" t="s">
@@ -29299,13 +29358,13 @@
       <c r="J73" s="26" t="s">
         <v>4051</v>
       </c>
-      <c r="K73" s="45" t="s">
+      <c r="K73" s="17" t="s">
         <v>2176</v>
       </c>
       <c r="L73" s="7" t="s">
         <v>2572</v>
       </c>
-      <c r="M73" s="43" t="s">
+      <c r="M73" s="16" t="s">
         <v>4052</v>
       </c>
       <c r="N73" s="7" t="s">

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4235B249-C6B6-4632-BAF5-38B9C2EE1155}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ADE0EC3-3018-4F1A-B8F6-A072442F8C12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25812" yWindow="2292" windowWidth="23256" windowHeight="12456" firstSheet="12" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25812" yWindow="2292" windowWidth="23256" windowHeight="12456" firstSheet="10" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8179" uniqueCount="4058">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8220" uniqueCount="4076">
   <si>
     <t>ID</t>
   </si>
@@ -12224,6 +12224,60 @@
   </si>
   <si>
     <t>https://www.mouser.es/en/ProductDetail/YAGEO/JB12S1002R?qs=iLKYxzqNS77KhcIWcFZ8Jg%3D%3D</t>
+  </si>
+  <si>
+    <t>015-0009</t>
+  </si>
+  <si>
+    <t>Current Sense Resistors - SMD TLRP 1206 1.0W R005 1% 100PPM 5K RL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5mΩ 1W ±1% </t>
+  </si>
+  <si>
+    <t>TLRP2B10ER005FTD</t>
+  </si>
+  <si>
+    <t>279-TLRP2B10ER005FTD</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/datasheet/3/80/46/ENG_DS_1773449_4_D3.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/en/ProductDetail/TE-Connectivity-Holsworthy/TLRP2B10ER005FTD?qs=QNEnbhJQKvZ8E9Cd3elZSA%3D%3D</t>
+  </si>
+  <si>
+    <t>015-0010</t>
+  </si>
+  <si>
+    <t>Current Sense Resistors - SMD RLW73 B2 1% R010 600ppm 1k RL</t>
+  </si>
+  <si>
+    <t>10mΩ 750mW ±1%</t>
+  </si>
+  <si>
+    <t>RLW73B2FR010TDF</t>
+  </si>
+  <si>
+    <t>279-RLW73B2FR010TDF</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/en/ProductDetail/TE-Connectivity-CGS/RLW73B2FR010TDF?qs=8Wlm6%252BaMh8Rd4lNQaStk%252BQ%3D%3D</t>
+  </si>
+  <si>
+    <t>040-0031</t>
+  </si>
+  <si>
+    <t>Surface Mount Fuses JB12S SMD Fuse 63V 5A Slow 1206 3.2mm X 1.6mm</t>
+  </si>
+  <si>
+    <t>JB12S5001R</t>
+  </si>
+  <si>
+    <t>603-JB12S5001R</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/en/ProductDetail/YAGEO/JB12S5001R?qs=iLKYxzqNS7562RQIsLPvYw%3D%3D</t>
   </si>
 </sst>
 </file>
@@ -12414,7 +12468,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -12479,7 +12533,6 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
@@ -21531,7 +21584,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B6F0D32-9CE2-4DF7-927E-42E7BA331F12}">
-  <dimension ref="A1:O31"/>
+  <dimension ref="A1:O32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="13" max="13" width="13.36328125" customWidth="1"/>
@@ -22874,25 +22927,25 @@
       <c r="A31" t="s">
         <v>4053</v>
       </c>
-      <c r="B31" s="43" t="s">
+      <c r="B31" s="16" t="s">
         <v>4054</v>
       </c>
-      <c r="C31" s="43" t="s">
+      <c r="C31" s="16" t="s">
         <v>1754</v>
       </c>
       <c r="D31" s="16">
         <v>1206</v>
       </c>
-      <c r="E31" s="43" t="s">
+      <c r="E31" s="16" t="s">
         <v>4055</v>
       </c>
-      <c r="F31" s="43" t="s">
+      <c r="F31" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="G31" s="42" t="s">
+      <c r="G31" s="3" t="s">
         <v>4056</v>
       </c>
-      <c r="H31" s="43" t="s">
+      <c r="H31" s="16" t="s">
         <v>21</v>
       </c>
       <c r="I31" s="26" t="s">
@@ -22911,6 +22964,50 @@
         <v>1701</v>
       </c>
       <c r="N31" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" t="s">
+        <v>4071</v>
+      </c>
+      <c r="B32" s="42" t="s">
+        <v>4072</v>
+      </c>
+      <c r="C32" s="42" t="s">
+        <v>1692</v>
+      </c>
+      <c r="D32" s="16">
+        <v>1206</v>
+      </c>
+      <c r="E32" s="42" t="s">
+        <v>4073</v>
+      </c>
+      <c r="F32" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="G32" t="s">
+        <v>4074</v>
+      </c>
+      <c r="H32" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="I32" s="26" t="s">
+        <v>4011</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>4075</v>
+      </c>
+      <c r="K32" s="17" t="s">
+        <v>1700</v>
+      </c>
+      <c r="L32" t="s">
+        <v>55</v>
+      </c>
+      <c r="M32" s="7" t="s">
+        <v>1701</v>
+      </c>
+      <c r="N32" t="s">
         <v>25</v>
       </c>
     </row>
@@ -22951,6 +23048,8 @@
     <hyperlink ref="J30" r:id="rId32" xr:uid="{B4F8AF74-EF6D-49F1-9CE8-29F632F7A754}"/>
     <hyperlink ref="I31" r:id="rId33" xr:uid="{912C6D59-6DD8-4011-9862-E5A138D7CA88}"/>
     <hyperlink ref="J31" r:id="rId34" xr:uid="{1B54DD8B-3D21-4E72-85BA-7DE1FAD354B9}"/>
+    <hyperlink ref="I32" r:id="rId35" xr:uid="{BB2566A3-B905-4C4D-9CFF-2A1A7A61DA85}"/>
+    <hyperlink ref="J32" r:id="rId36" xr:uid="{80802204-A2D9-4DFF-95F9-BC9A208CDE12}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -38437,7 +38536,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81F9848D-6D60-47C0-9F84-A561FE4F106E}">
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="20.26953125" customWidth="1"/>
@@ -38836,6 +38935,94 @@
         <v>3987</v>
       </c>
       <c r="N9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
+        <v>4058</v>
+      </c>
+      <c r="B10" t="s">
+        <v>4059</v>
+      </c>
+      <c r="C10" t="s">
+        <v>4060</v>
+      </c>
+      <c r="D10" s="35" t="s">
+        <v>249</v>
+      </c>
+      <c r="E10" t="s">
+        <v>4061</v>
+      </c>
+      <c r="F10" t="s">
+        <v>2192</v>
+      </c>
+      <c r="G10" t="s">
+        <v>4062</v>
+      </c>
+      <c r="H10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>4063</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>4064</v>
+      </c>
+      <c r="K10" t="s">
+        <v>34</v>
+      </c>
+      <c r="L10" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M10" s="17" t="s">
+        <v>1645</v>
+      </c>
+      <c r="N10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" t="s">
+        <v>4065</v>
+      </c>
+      <c r="B11" t="s">
+        <v>4066</v>
+      </c>
+      <c r="C11" t="s">
+        <v>4067</v>
+      </c>
+      <c r="D11" t="s">
+        <v>3982</v>
+      </c>
+      <c r="E11" t="s">
+        <v>4068</v>
+      </c>
+      <c r="F11" t="s">
+        <v>2192</v>
+      </c>
+      <c r="G11" t="s">
+        <v>4069</v>
+      </c>
+      <c r="H11" t="s">
+        <v>21</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>3997</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>4070</v>
+      </c>
+      <c r="K11" t="s">
+        <v>34</v>
+      </c>
+      <c r="L11" t="s">
+        <v>1648</v>
+      </c>
+      <c r="M11" s="17" t="s">
+        <v>3987</v>
+      </c>
+      <c r="N11" t="s">
         <v>25</v>
       </c>
     </row>
@@ -38856,9 +39043,13 @@
     <hyperlink ref="J8" r:id="rId12" xr:uid="{2522A19B-C8CE-448A-B70B-CFD7C4AFEEF0}"/>
     <hyperlink ref="I9" r:id="rId13" xr:uid="{6C0457D9-CE57-4F5A-8777-E39EA4F17352}"/>
     <hyperlink ref="J9" r:id="rId14" xr:uid="{BA2A9F42-701A-48EA-BFA8-1B1F3BDDF2F6}"/>
+    <hyperlink ref="I10" r:id="rId15" xr:uid="{2428C7CE-5D0C-41C3-BF1F-988F71D4EF48}"/>
+    <hyperlink ref="J10" r:id="rId16" xr:uid="{15EF6D95-7C3C-42B3-90E3-4546110523C9}"/>
+    <hyperlink ref="I11" r:id="rId17" xr:uid="{6467E5F2-4786-4C6B-A3A3-F0D4C5A67B79}"/>
+    <hyperlink ref="J11" r:id="rId18" xr:uid="{40DA6A61-E97A-4D1C-9CF4-22EC82276332}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId15"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId19"/>
 </worksheet>
 </file>
 

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ADE0EC3-3018-4F1A-B8F6-A072442F8C12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DC15771-E635-4DEA-A791-499F4B5B14CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25812" yWindow="2292" windowWidth="23256" windowHeight="12456" firstSheet="10" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25812" yWindow="2292" windowWidth="23256" windowHeight="12456" firstSheet="22" activeTab="26" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -39,6 +39,7 @@
     <sheet name="090 - Processor" sheetId="18" r:id="rId24"/>
     <sheet name="100 - Electromechanicals" sheetId="15" r:id="rId25"/>
     <sheet name="110 - Connectors" sheetId="13" r:id="rId26"/>
+    <sheet name="115 - Test Points" sheetId="29" r:id="rId27"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -50,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8220" uniqueCount="4076">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8248" uniqueCount="4082">
   <si>
     <t>ID</t>
   </si>
@@ -12278,6 +12279,24 @@
   </si>
   <si>
     <t>https://www.mouser.es/en/ProductDetail/YAGEO/JB12S5001R?qs=iLKYxzqNS7562RQIsLPvYw%3D%3D</t>
+  </si>
+  <si>
+    <t>115-0000</t>
+  </si>
+  <si>
+    <t>Plate to fabri</t>
+  </si>
+  <si>
+    <t>2mm</t>
+  </si>
+  <si>
+    <t>Plate</t>
+  </si>
+  <si>
+    <t>eUSR_SchLibrary/eUSR_SchLibrary - TestPoints.SchLib</t>
+  </si>
+  <si>
+    <t>Plate_2mm</t>
   </si>
 </sst>
 </file>
@@ -12468,7 +12487,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -12533,7 +12552,6 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -22971,16 +22989,16 @@
       <c r="A32" t="s">
         <v>4071</v>
       </c>
-      <c r="B32" s="42" t="s">
+      <c r="B32" s="16" t="s">
         <v>4072</v>
       </c>
-      <c r="C32" s="42" t="s">
+      <c r="C32" s="16" t="s">
         <v>1692</v>
       </c>
       <c r="D32" s="16">
         <v>1206</v>
       </c>
-      <c r="E32" s="42" t="s">
+      <c r="E32" s="16" t="s">
         <v>4073</v>
       </c>
       <c r="F32" s="16" t="s">
@@ -22989,7 +23007,7 @@
       <c r="G32" t="s">
         <v>4074</v>
       </c>
-      <c r="H32" s="42" t="s">
+      <c r="H32" s="16" t="s">
         <v>21</v>
       </c>
       <c r="I32" s="26" t="s">
@@ -25167,7 +25185,7 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69A1C46E-DEF3-467B-A5BD-162AB66E6A86}">
-  <dimension ref="A1:N24"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:14">
@@ -26224,7 +26242,11 @@
         <v>25</v>
       </c>
     </row>
+    <row r="25" spans="1:14">
+      <c r="A25" s="16"/>
+    </row>
   </sheetData>
+  <phoneticPr fontId="15" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="J2" r:id="rId1" xr:uid="{00000000-0004-0000-1C00-000000000000}"/>
     <hyperlink ref="I9" r:id="rId2" xr:uid="{00000000-0004-0000-1C00-000001000000}"/>
@@ -29548,6 +29570,104 @@
     <hyperlink ref="I73" r:id="rId70" xr:uid="{BEBF4596-6961-45FE-98BF-66C1250C4174}"/>
     <hyperlink ref="J73" r:id="rId71" xr:uid="{B0F0D27D-2D3D-4199-9067-2A3FBADE7648}"/>
   </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CA19F58-1F35-4F25-A924-B809C68C5457}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="24" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
+        <v>4076</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>4077</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>4078</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" s="16" t="s">
+        <v>4079</v>
+      </c>
+      <c r="L2" s="16" t="s">
+        <v>4080</v>
+      </c>
+      <c r="M2" s="16" t="s">
+        <v>4081</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DC15771-E635-4DEA-A791-499F4B5B14CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBD534D5-C995-4D9E-8F7A-DA58D9B04565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25812" yWindow="2292" windowWidth="23256" windowHeight="12456" firstSheet="22" activeTab="26" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10710" yWindow="0" windowWidth="10920" windowHeight="13770" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -21,25 +21,26 @@
     <sheet name="015 - Resistors - Shunt" sheetId="7" r:id="rId6"/>
     <sheet name="020 - Inductor" sheetId="5" r:id="rId7"/>
     <sheet name="023 - Inductor - CMM" sheetId="16" r:id="rId8"/>
-    <sheet name="030 - Diode - Rectifier" sheetId="9" r:id="rId9"/>
-    <sheet name="031 - Diode - Schottky" sheetId="11" r:id="rId10"/>
-    <sheet name="032 - Diode - TVS" sheetId="14" r:id="rId11"/>
-    <sheet name="033 - Diode - LED" sheetId="12" r:id="rId12"/>
-    <sheet name="035 - Varistor " sheetId="27" r:id="rId13"/>
-    <sheet name="040 - Fuses" sheetId="10" r:id="rId14"/>
-    <sheet name="041 - Optoisolators" sheetId="26" r:id="rId15"/>
-    <sheet name="043 - Transistors" sheetId="21" r:id="rId16"/>
-    <sheet name="045 - Crystal" sheetId="19" r:id="rId17"/>
-    <sheet name="050 - ICs - Analog" sheetId="2" r:id="rId18"/>
-    <sheet name="051 - ICs - Digital" sheetId="24" r:id="rId19"/>
-    <sheet name="055 - Drivers" sheetId="20" r:id="rId20"/>
-    <sheet name="060 - Sensor" sheetId="3" r:id="rId21"/>
-    <sheet name="062 - Amplifiers" sheetId="25" r:id="rId22"/>
-    <sheet name="070 - Power Supply" sheetId="8" r:id="rId23"/>
-    <sheet name="090 - Processor" sheetId="18" r:id="rId24"/>
-    <sheet name="100 - Electromechanicals" sheetId="15" r:id="rId25"/>
-    <sheet name="110 - Connectors" sheetId="13" r:id="rId26"/>
-    <sheet name="115 - Test Points" sheetId="29" r:id="rId27"/>
+    <sheet name="025 - Inductor - Ferrite" sheetId="30" r:id="rId9"/>
+    <sheet name="030 - Diode - Rectifier" sheetId="9" r:id="rId10"/>
+    <sheet name="031 - Diode - Schottky" sheetId="11" r:id="rId11"/>
+    <sheet name="032 - Diode - TVS" sheetId="14" r:id="rId12"/>
+    <sheet name="033 - Diode - LED" sheetId="12" r:id="rId13"/>
+    <sheet name="035 - Varistor " sheetId="27" r:id="rId14"/>
+    <sheet name="040 - Fuses" sheetId="10" r:id="rId15"/>
+    <sheet name="041 - Optoisolators" sheetId="26" r:id="rId16"/>
+    <sheet name="043 - Transistors" sheetId="21" r:id="rId17"/>
+    <sheet name="045 - Crystal" sheetId="19" r:id="rId18"/>
+    <sheet name="050 - ICs - Analog" sheetId="2" r:id="rId19"/>
+    <sheet name="051 - ICs - Digital" sheetId="24" r:id="rId20"/>
+    <sheet name="055 - Drivers" sheetId="20" r:id="rId21"/>
+    <sheet name="060 - Sensor" sheetId="3" r:id="rId22"/>
+    <sheet name="062 - Amplifiers" sheetId="25" r:id="rId23"/>
+    <sheet name="070 - Power Supply" sheetId="8" r:id="rId24"/>
+    <sheet name="090 - Processor" sheetId="18" r:id="rId25"/>
+    <sheet name="100 - Electromechanicals" sheetId="15" r:id="rId26"/>
+    <sheet name="110 - Connectors" sheetId="13" r:id="rId27"/>
+    <sheet name="115 - Test Points" sheetId="29" r:id="rId28"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -51,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8248" uniqueCount="4082">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8275" uniqueCount="4090">
   <si>
     <t>ID</t>
   </si>
@@ -12297,6 +12298,30 @@
   </si>
   <si>
     <t>Plate_2mm</t>
+  </si>
+  <si>
+    <t>025-0000</t>
+  </si>
+  <si>
+    <t>Ferrite Beads WE-TMSB 1KOhms 480mA 0402 0.48OhmsFerrite Beads WE-TMSB 1KOhms 480mA 0402 0.48Ohms</t>
+  </si>
+  <si>
+    <t>1kΩ 480mA</t>
+  </si>
+  <si>
+    <t>710-74269241102</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/74269241102.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/en/ProductDetail/Wurth-Elektronik/74269241102?qs=sGAEpiMZZMt1hubY80%2Fs8KH3ycnB7WcGH5zBhJgtJewoq2%2Fz%252B%252BrYnA%3D%3D</t>
+  </si>
+  <si>
+    <t>IND_FB</t>
+  </si>
+  <si>
+    <t>IND 0402</t>
   </si>
 </sst>
 </file>
@@ -18653,6 +18678,418 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{652841DA-3619-42EE-A536-61B58BE1B457}">
+  <dimension ref="A1:N9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" s="7" t="s">
+        <v>1832</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>1833</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>1834</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>1835</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>1836</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>1837</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>1838</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>1839</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>1840</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>1841</v>
+      </c>
+      <c r="L2" s="7" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M2" s="7" t="s">
+        <v>1842</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="7" t="s">
+        <v>1843</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>1844</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>1845</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>1846</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>1847</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>1848</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>1849</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>1850</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>1851</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>1841</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>1852</v>
+      </c>
+      <c r="N3" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="7" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>1854</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>1855</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>1856</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>1857</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>1858</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>1859</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>1860</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>1861</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>1862</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>1863</v>
+      </c>
+      <c r="N4" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="7" t="s">
+        <v>1864</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>1865</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>1866</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>1867</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>1868</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>1869</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I5" s="15" t="s">
+        <v>1870</v>
+      </c>
+      <c r="J5" s="15" t="s">
+        <v>1871</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>1841</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>1866</v>
+      </c>
+      <c r="N5" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="7" t="s">
+        <v>1872</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>1873</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>1874</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>1875</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>1876</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>1877</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>1878</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>1879</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>1880</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>1841</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>1881</v>
+      </c>
+      <c r="N6" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="7" t="s">
+        <v>1882</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>1883</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>1884</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>1885</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>1886</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>1887</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>1888</v>
+      </c>
+      <c r="H7" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>1889</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>1890</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>1841</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>1891</v>
+      </c>
+      <c r="N7" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="16" t="s">
+        <v>1892</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>1893</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>1894</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>1895</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>1896</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>1897</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>1898</v>
+      </c>
+      <c r="H8" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" s="18" t="s">
+        <v>1899</v>
+      </c>
+      <c r="J8" s="18" t="s">
+        <v>1900</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>1841</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>1895</v>
+      </c>
+      <c r="N8" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="16" t="s">
+        <v>1901</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>1902</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>1903</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>1904</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>1905</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>1906</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>1907</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>1908</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>1909</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>1841</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>1910</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>1904</v>
+      </c>
+      <c r="N9" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="I5" r:id="rId1" xr:uid="{00000000-0004-0000-0800-000000000000}"/>
+    <hyperlink ref="J5" r:id="rId2" xr:uid="{00000000-0004-0000-0800-000001000000}"/>
+    <hyperlink ref="I8" r:id="rId3" xr:uid="{ABAB45EA-9261-4561-98A3-C830A74C7893}"/>
+    <hyperlink ref="J8" r:id="rId4" xr:uid="{E0090D85-56DB-4EF7-BD41-6F63EB17645B}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FE2008B-4BF4-4C9A-883A-FEE5873AEAF4}">
   <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -19295,7 +19732,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79E65951-BFD2-4888-A0A6-19D5130CB4A6}">
   <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -20366,7 +20803,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89BFA1EF-29B2-41E4-A9D1-F8E90A663FA1}">
   <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -21451,7 +21888,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ED8913B-580D-466F-B6D1-947424810FAF}">
   <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -21600,7 +22037,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B6F0D32-9CE2-4DF7-927E-42E7BA331F12}">
   <dimension ref="A1:O32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -23073,7 +23510,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA7E41C9-E62B-4149-A5B5-E7986E8877E6}">
   <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -23221,7 +23658,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FAFF3B6-AF11-4BFB-8078-829FF6F2F366}">
   <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -23370,7 +23807,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E5535EA-E186-4751-BC7F-9B3A0221302E}">
   <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -23519,7 +23956,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C98E1A12-072F-4773-8CB5-47FFE077E85B}">
   <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -23950,60 +24387,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{316C64E0-14FB-467C-956A-E132FAFB0232}">
-  <dimension ref="A1:N1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
-  <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFB39079-151D-4B88-9E1F-4966291E2A6B}">
   <dimension ref="A1:N3"/>
@@ -24112,6 +24495,60 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{316C64E0-14FB-467C-956A-E132FAFB0232}">
+  <dimension ref="A1:N1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{201D74E2-3547-4E9B-8216-09A22645AC2A}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -24213,7 +24650,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59BC8B2E-A067-463D-937A-30E88D8BECD0}">
   <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -24408,7 +24845,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4185B0A-D162-4EBC-935B-7159E365DD54}">
   <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -24557,7 +24994,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4BBBCF5-BAC9-459C-ABE9-2526B85FD81E}">
   <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -25025,7 +25462,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E9EB2F5-2977-493B-BFA2-5CD20F8A3BC4}">
   <dimension ref="A1:O3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -25183,7 +25620,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69A1C46E-DEF3-467B-A5BD-162AB66E6A86}">
   <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -26270,7 +26707,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE14AD29-8DB0-4C42-AB91-A73B867AE121}">
   <dimension ref="A1:N77"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -29574,7 +30011,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CA19F58-1F35-4F25-A924-B809C68C5457}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -39517,9 +39954,12 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{652841DA-3619-42EE-A536-61B58BE1B457}">
-  <dimension ref="A1:N9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59A9FAC0-03F3-45B5-A0EF-8375716CA489}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="5" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
@@ -39566,363 +40006,53 @@
       </c>
     </row>
     <row r="2" spans="1:14">
-      <c r="A2" s="7" t="s">
-        <v>1832</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>1833</v>
-      </c>
-      <c r="C2" s="23" t="s">
-        <v>1834</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>1835</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>1836</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>1837</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>1838</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>1839</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>1840</v>
-      </c>
-      <c r="K2" s="7" t="s">
-        <v>1841</v>
-      </c>
-      <c r="L2" s="7" t="s">
-        <v>1910</v>
-      </c>
-      <c r="M2" s="7" t="s">
-        <v>1842</v>
-      </c>
-      <c r="N2" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="7" t="s">
-        <v>1843</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>1844</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>1845</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>1846</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>1847</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>1848</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>1849</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>1850</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>1851</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>1841</v>
-      </c>
-      <c r="L3" s="7" t="s">
-        <v>1910</v>
-      </c>
-      <c r="M3" s="7" t="s">
-        <v>1852</v>
-      </c>
-      <c r="N3" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="7" t="s">
-        <v>1853</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>1854</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>1855</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>1856</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>1857</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>1858</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>1859</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>1860</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>1861</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>1862</v>
-      </c>
-      <c r="L4" s="7" t="s">
-        <v>1910</v>
-      </c>
-      <c r="M4" s="7" t="s">
-        <v>1863</v>
-      </c>
-      <c r="N4" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="7" t="s">
-        <v>1864</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>1865</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>1866</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>1867</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>1868</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>1869</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I5" s="15" t="s">
-        <v>1870</v>
-      </c>
-      <c r="J5" s="15" t="s">
-        <v>1871</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>1841</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>1910</v>
-      </c>
-      <c r="M5" s="7" t="s">
-        <v>1866</v>
-      </c>
-      <c r="N5" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="7" t="s">
-        <v>1872</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>1873</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>1874</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>1875</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>1876</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>1877</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>1878</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>1879</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>1880</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>1841</v>
-      </c>
-      <c r="L6" s="7" t="s">
-        <v>1910</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>1881</v>
-      </c>
-      <c r="N6" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="7" t="s">
-        <v>1882</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>1883</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>1884</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>1885</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>1886</v>
-      </c>
-      <c r="F7" s="16" t="s">
-        <v>1887</v>
-      </c>
-      <c r="G7" s="16" t="s">
-        <v>1888</v>
-      </c>
-      <c r="H7" s="16" t="s">
+      <c r="A2" t="s">
+        <v>4082</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4083</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4084</v>
+      </c>
+      <c r="D2" s="35" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2">
+        <v>74269241102</v>
+      </c>
+      <c r="F2" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G2" t="s">
+        <v>4085</v>
+      </c>
+      <c r="H2" t="s">
         <v>21</v>
       </c>
-      <c r="I7" s="3" t="s">
-        <v>1889</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>1890</v>
-      </c>
-      <c r="K7" s="16" t="s">
-        <v>1841</v>
-      </c>
-      <c r="L7" s="7" t="s">
-        <v>1910</v>
-      </c>
-      <c r="M7" s="16" t="s">
-        <v>1891</v>
-      </c>
-      <c r="N7" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="16" t="s">
-        <v>1892</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>1893</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>1894</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>1895</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>1896</v>
-      </c>
-      <c r="F8" s="16" t="s">
-        <v>1897</v>
-      </c>
-      <c r="G8" s="16" t="s">
-        <v>1898</v>
-      </c>
-      <c r="H8" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="I8" s="18" t="s">
-        <v>1899</v>
-      </c>
-      <c r="J8" s="18" t="s">
-        <v>1900</v>
-      </c>
-      <c r="K8" s="16" t="s">
-        <v>1841</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>1910</v>
-      </c>
-      <c r="M8" s="16" t="s">
-        <v>1895</v>
-      </c>
-      <c r="N8" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="16" t="s">
-        <v>1901</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>1902</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>1903</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>1904</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>1905</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>1906</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>1907</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>1908</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>1909</v>
-      </c>
-      <c r="K9" s="16" t="s">
-        <v>1841</v>
-      </c>
-      <c r="L9" s="7" t="s">
-        <v>1910</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>1904</v>
-      </c>
-      <c r="N9" s="7" t="s">
+      <c r="I2" s="2" t="s">
+        <v>4086</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>4087</v>
+      </c>
+      <c r="K2" t="s">
+        <v>4088</v>
+      </c>
+      <c r="L2" t="s">
+        <v>2904</v>
+      </c>
+      <c r="M2" s="17" t="s">
+        <v>4089</v>
+      </c>
+      <c r="N2" t="s">
         <v>25</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="I5" r:id="rId1" xr:uid="{00000000-0004-0000-0800-000000000000}"/>
-    <hyperlink ref="J5" r:id="rId2" xr:uid="{00000000-0004-0000-0800-000001000000}"/>
-    <hyperlink ref="I8" r:id="rId3" xr:uid="{ABAB45EA-9261-4561-98A3-C830A74C7893}"/>
-    <hyperlink ref="J8" r:id="rId4" xr:uid="{E0090D85-56DB-4EF7-BD41-6F63EB17645B}"/>
+    <hyperlink ref="I2" r:id="rId1" xr:uid="{B79A2E0D-8840-4FA9-93E6-684C01D461D7}"/>
+    <hyperlink ref="J2" r:id="rId2" xr:uid="{77C32199-B506-4398-8F93-0071913D156B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/eUSR_Database.xlsx
+++ b/eUSR_Database.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LIB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Javier\Desktop\MOTO\LIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBD534D5-C995-4D9E-8F7A-DA58D9B04565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D9F1710-DA72-4BCB-A729-9827A484C635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10710" yWindow="0" windowWidth="10920" windowHeight="13770" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="13" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="001 - Capacitors - SMD Ceramics" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8275" uniqueCount="4090">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8317" uniqueCount="4115">
   <si>
     <t>ID</t>
   </si>
@@ -12322,6 +12322,81 @@
   </si>
   <si>
     <t>IND 0402</t>
+  </si>
+  <si>
+    <t>041-0003</t>
+  </si>
+  <si>
+    <t>Optoacopladores para salidas de transistores WL-OCPT 35V 5KVrms 10pF Dip 4 S-Type</t>
+  </si>
+  <si>
+    <t>DIP-4</t>
+  </si>
+  <si>
+    <t>710-140817142400</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/catalog/datasheet/140817142400.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/es/ProductDetail/Wurth-Elektronik/140817142400?qs=81r%252BiQLm7BQPLeRqqgk3BQ%3D%3D</t>
+  </si>
+  <si>
+    <t>100-0024</t>
+  </si>
+  <si>
+    <t>Relés universales SPST-NO Flux-Tight 24VDC High-Capacity</t>
+  </si>
+  <si>
+    <t>200mW 8,3mA coil</t>
+  </si>
+  <si>
+    <t>20,5x7,2x15,3mm</t>
+  </si>
+  <si>
+    <t>G5NB-1A-E-DC24</t>
+  </si>
+  <si>
+    <t>Aratas</t>
+  </si>
+  <si>
+    <t>653-G5NB-1A-E-DC24</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/datasheet/3/39/1/J143-E1.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/es/ProductDetail/Aratas/G5NB-1A-E-DC24?qs=3jhwTwe4bOHjt65REhrORA%3D%3D</t>
+  </si>
+  <si>
+    <t>RELE G5NB-1A</t>
+  </si>
+  <si>
+    <t>G5NB-1A</t>
+  </si>
+  <si>
+    <t>010-0193</t>
+  </si>
+  <si>
+    <t>Resistores de película gruesa - SMD 0.5W 2.2Kohm 1% AEC-Q200</t>
+  </si>
+  <si>
+    <t>0.5W 2.2Kohm 1%</t>
+  </si>
+  <si>
+    <t>SG73P1JTTD2201F</t>
+  </si>
+  <si>
+    <t>660-SG73P1JTTD2201F</t>
+  </si>
+  <si>
+    <t>https://www.koaspeer.com/pdfs/SG73P.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.es/es/ProductDetail/KOA-Speer/SG73P1JTTD2201F?qs=sGAEpiMZZMtlubZbdhIBIMav4eZf%2FxzgRyo3bnq6lCo%3D</t>
+  </si>
+  <si>
+    <t>140817142400</t>
   </si>
 </sst>
 </file>
@@ -12331,7 +12406,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -12461,6 +12536,18 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -12512,7 +12599,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -12577,6 +12664,13 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -12861,22 +12955,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N129"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="11.1796875" customWidth="1"/>
-    <col min="2" max="2" width="29.6328125" customWidth="1"/>
-    <col min="3" max="3" width="14.90625" customWidth="1"/>
-    <col min="4" max="4" width="8.81640625" customWidth="1"/>
-    <col min="5" max="5" width="12.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.6328125" customWidth="1"/>
-    <col min="7" max="7" width="15.453125" customWidth="1"/>
-    <col min="8" max="8" width="12.453125" customWidth="1"/>
-    <col min="9" max="9" width="11.1796875" customWidth="1"/>
-    <col min="10" max="10" width="14.7265625" customWidth="1"/>
+    <col min="1" max="1" width="11.21875" customWidth="1"/>
+    <col min="2" max="2" width="29.6640625" customWidth="1"/>
+    <col min="3" max="3" width="14.88671875" customWidth="1"/>
+    <col min="4" max="4" width="8.77734375" customWidth="1"/>
+    <col min="5" max="5" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" customWidth="1"/>
+    <col min="7" max="7" width="15.44140625" customWidth="1"/>
+    <col min="8" max="8" width="12.44140625" customWidth="1"/>
+    <col min="9" max="9" width="11.21875" customWidth="1"/>
+    <col min="10" max="10" width="14.77734375" customWidth="1"/>
     <col min="11" max="11" width="12" customWidth="1"/>
-    <col min="12" max="12" width="13.1796875" customWidth="1"/>
-    <col min="13" max="13" width="12.54296875" customWidth="1"/>
-    <col min="14" max="14" width="17.6328125" customWidth="1"/>
+    <col min="12" max="12" width="13.21875" customWidth="1"/>
+    <col min="13" max="13" width="12.5546875" customWidth="1"/>
+    <col min="14" max="14" width="17.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="13.5" customHeight="1">
@@ -12923,7 +13017,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="14" customHeight="1">
+    <row r="2" spans="1:14" ht="13.95" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>58</v>
       </c>
@@ -12967,7 +13061,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="14" customHeight="1">
+    <row r="3" spans="1:14" ht="13.95" customHeight="1">
       <c r="A3" s="4" t="s">
         <v>73</v>
       </c>
@@ -13011,7 +13105,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="14" customHeight="1">
+    <row r="4" spans="1:14" ht="13.95" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>81</v>
       </c>
@@ -13055,7 +13149,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="14" customHeight="1">
+    <row r="5" spans="1:14" ht="13.95" customHeight="1">
       <c r="A5" s="4" t="s">
         <v>88</v>
       </c>
@@ -13099,7 +13193,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="14" customHeight="1">
+    <row r="6" spans="1:14" ht="13.95" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>95</v>
       </c>
@@ -13143,7 +13237,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="14" customHeight="1">
+    <row r="7" spans="1:14" ht="13.95" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>103</v>
       </c>
@@ -13187,7 +13281,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="14" customHeight="1">
+    <row r="8" spans="1:14" ht="13.95" customHeight="1">
       <c r="A8" s="4" t="s">
         <v>110</v>
       </c>
@@ -13231,7 +13325,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="14" customHeight="1">
+    <row r="9" spans="1:14" ht="13.95" customHeight="1">
       <c r="A9" s="4" t="s">
         <v>117</v>
       </c>
@@ -13275,7 +13369,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="14" customHeight="1">
+    <row r="10" spans="1:14" ht="13.95" customHeight="1">
       <c r="A10" s="4" t="s">
         <v>124</v>
       </c>
@@ -13319,7 +13413,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="14" customHeight="1">
+    <row r="11" spans="1:14" ht="13.95" customHeight="1">
       <c r="A11" s="4" t="s">
         <v>131</v>
       </c>
@@ -13363,7 +13457,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="14" customHeight="1">
+    <row r="12" spans="1:14" ht="13.95" customHeight="1">
       <c r="A12" s="4" t="s">
         <v>138</v>
       </c>
@@ -13407,7 +13501,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="14" customHeight="1">
+    <row r="13" spans="1:14" ht="13.95" customHeight="1">
       <c r="A13" s="4" t="s">
         <v>145</v>
       </c>
@@ -13451,7 +13545,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="14" customHeight="1">
+    <row r="14" spans="1:14" ht="13.95" customHeight="1">
       <c r="A14" s="4" t="s">
         <v>153</v>
       </c>
@@ -13495,7 +13589,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="14" customHeight="1">
+    <row r="15" spans="1:14" ht="13.95" customHeight="1">
       <c r="A15" s="4" t="s">
         <v>160</v>
       </c>
@@ -13539,7 +13633,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="14" customHeight="1">
+    <row r="16" spans="1:14" ht="13.95" customHeight="1">
       <c r="A16" s="4" t="s">
         <v>167</v>
       </c>
@@ -13583,7 +13677,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="14" customHeight="1">
+    <row r="17" spans="1:14" ht="13.95" customHeight="1">
       <c r="A17" s="4" t="s">
         <v>174</v>
       </c>
@@ -13627,7 +13721,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="14" customHeight="1">
+    <row r="18" spans="1:14" ht="13.95" customHeight="1">
       <c r="A18" s="4" t="s">
         <v>180</v>
       </c>
@@ -13671,7 +13765,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="14" customHeight="1">
+    <row r="19" spans="1:14" ht="13.95" customHeight="1">
       <c r="A19" s="4" t="s">
         <v>187</v>
       </c>
@@ -13715,7 +13809,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="14" customHeight="1">
+    <row r="20" spans="1:14" ht="13.95" customHeight="1">
       <c r="A20" s="4" t="s">
         <v>194</v>
       </c>
@@ -13759,7 +13853,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="14" customHeight="1">
+    <row r="21" spans="1:14" ht="13.95" customHeight="1">
       <c r="A21" s="4" t="s">
         <v>201</v>
       </c>
@@ -13803,7 +13897,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="14" customHeight="1">
+    <row r="22" spans="1:14" ht="13.95" customHeight="1">
       <c r="A22" s="4" t="s">
         <v>208</v>
       </c>
@@ -13847,7 +13941,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="14" customHeight="1">
+    <row r="23" spans="1:14" ht="13.95" customHeight="1">
       <c r="A23" s="4" t="s">
         <v>216</v>
       </c>
@@ -13891,7 +13985,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="14" customHeight="1">
+    <row r="24" spans="1:14" ht="13.95" customHeight="1">
       <c r="A24" s="4" t="s">
         <v>223</v>
       </c>
@@ -13935,7 +14029,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="14" customHeight="1">
+    <row r="25" spans="1:14" ht="13.95" customHeight="1">
       <c r="A25" s="4" t="s">
         <v>230</v>
       </c>
@@ -13979,7 +14073,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="14" customHeight="1">
+    <row r="26" spans="1:14" ht="13.95" customHeight="1">
       <c r="A26" s="4" t="s">
         <v>237</v>
       </c>
@@ -14023,7 +14117,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="14" customHeight="1">
+    <row r="27" spans="1:14" ht="13.95" customHeight="1">
       <c r="A27" s="4" t="s">
         <v>246</v>
       </c>
@@ -14067,7 +14161,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="14" customHeight="1">
+    <row r="28" spans="1:14" ht="13.95" customHeight="1">
       <c r="A28" s="4" t="s">
         <v>254</v>
       </c>
@@ -14111,7 +14205,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="14" customHeight="1">
+    <row r="29" spans="1:14" ht="13.95" customHeight="1">
       <c r="A29" s="4" t="s">
         <v>261</v>
       </c>
@@ -14155,7 +14249,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="14" customHeight="1">
+    <row r="30" spans="1:14" ht="13.95" customHeight="1">
       <c r="A30" s="4" t="s">
         <v>268</v>
       </c>
@@ -14199,7 +14293,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="14" customHeight="1">
+    <row r="31" spans="1:14" ht="13.95" customHeight="1">
       <c r="A31" s="4" t="s">
         <v>275</v>
       </c>
@@ -14243,7 +14337,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="14" customHeight="1">
+    <row r="32" spans="1:14" ht="13.95" customHeight="1">
       <c r="A32" s="4" t="s">
         <v>282</v>
       </c>
@@ -14287,7 +14381,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="14" customHeight="1">
+    <row r="33" spans="1:14" ht="13.95" customHeight="1">
       <c r="A33" s="4" t="s">
         <v>288</v>
       </c>
@@ -14331,7 +14425,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="1:14" ht="14" customHeight="1">
+    <row r="34" spans="1:14" ht="13.95" customHeight="1">
       <c r="A34" s="4" t="s">
         <v>295</v>
       </c>
@@ -14375,7 +14469,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="1:14" ht="14" customHeight="1">
+    <row r="35" spans="1:14" ht="13.95" customHeight="1">
       <c r="A35" s="4" t="s">
         <v>302</v>
       </c>
@@ -14419,7 +14513,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:14" ht="14" customHeight="1">
+    <row r="36" spans="1:14" ht="13.95" customHeight="1">
       <c r="A36" s="4" t="s">
         <v>308</v>
       </c>
@@ -14463,7 +14557,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:14" ht="14" customHeight="1">
+    <row r="37" spans="1:14" ht="13.95" customHeight="1">
       <c r="A37" s="4" t="s">
         <v>315</v>
       </c>
@@ -14507,7 +14601,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:14" ht="14" customHeight="1">
+    <row r="38" spans="1:14" ht="13.95" customHeight="1">
       <c r="A38" s="4" t="s">
         <v>322</v>
       </c>
@@ -14551,7 +14645,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:14" ht="14" customHeight="1">
+    <row r="39" spans="1:14" ht="13.95" customHeight="1">
       <c r="A39" s="4" t="s">
         <v>329</v>
       </c>
@@ -14595,7 +14689,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="40" spans="1:14" ht="14" customHeight="1">
+    <row r="40" spans="1:14" ht="13.95" customHeight="1">
       <c r="A40" s="4" t="s">
         <v>336</v>
       </c>
@@ -14639,7 +14733,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="41" spans="1:14" ht="14" customHeight="1">
+    <row r="41" spans="1:14" ht="13.95" customHeight="1">
       <c r="A41" s="4" t="s">
         <v>343</v>
       </c>
@@ -14683,7 +14777,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="42" spans="1:14" ht="14" customHeight="1">
+    <row r="42" spans="1:14" ht="13.95" customHeight="1">
       <c r="A42" s="4" t="s">
         <v>350</v>
       </c>
@@ -14727,7 +14821,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="43" spans="1:14" ht="14" customHeight="1">
+    <row r="43" spans="1:14" ht="13.95" customHeight="1">
       <c r="A43" s="4" t="s">
         <v>357</v>
       </c>
@@ -14771,7 +14865,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="44" spans="1:14" ht="14" customHeight="1">
+    <row r="44" spans="1:14" ht="13.95" customHeight="1">
       <c r="A44" s="4" t="s">
         <v>364</v>
       </c>
@@ -14815,7 +14909,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="45" spans="1:14" ht="14" customHeight="1">
+    <row r="45" spans="1:14" ht="13.95" customHeight="1">
       <c r="A45" s="4" t="s">
         <v>371</v>
       </c>
@@ -14859,7 +14953,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="1:14" ht="14" customHeight="1">
+    <row r="46" spans="1:14" ht="13.95" customHeight="1">
       <c r="A46" s="4" t="s">
         <v>378</v>
       </c>
@@ -14903,7 +14997,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="47" spans="1:14" ht="14" customHeight="1">
+    <row r="47" spans="1:14" ht="13.95" customHeight="1">
       <c r="A47" s="4" t="s">
         <v>384</v>
       </c>
@@ -14947,7 +15041,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="48" spans="1:14" ht="14" customHeight="1">
+    <row r="48" spans="1:14" ht="13.95" customHeight="1">
       <c r="A48" s="4" t="s">
         <v>391</v>
       </c>
@@ -14991,7 +15085,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="49" spans="1:14" ht="14" customHeight="1">
+    <row r="49" spans="1:14" ht="13.95" customHeight="1">
       <c r="A49" s="4" t="s">
         <v>398</v>
       </c>
@@ -15035,7 +15129,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="50" spans="1:14" ht="14" customHeight="1">
+    <row r="50" spans="1:14" ht="13.95" customHeight="1">
       <c r="A50" s="4" t="s">
         <v>405</v>
       </c>
@@ -15079,7 +15173,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="51" spans="1:14" ht="14" customHeight="1">
+    <row r="51" spans="1:14" ht="13.95" customHeight="1">
       <c r="A51" s="4" t="s">
         <v>413</v>
       </c>
@@ -15123,7 +15217,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="52" spans="1:14" ht="14" customHeight="1">
+    <row r="52" spans="1:14" ht="13.95" customHeight="1">
       <c r="A52" s="4" t="s">
         <v>420</v>
       </c>
@@ -15167,7 +15261,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="53" spans="1:14" ht="14" customHeight="1">
+    <row r="53" spans="1:14" ht="13.95" customHeight="1">
       <c r="A53" s="4" t="s">
         <v>427</v>
       </c>
@@ -15211,7 +15305,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="54" spans="1:14" ht="14" customHeight="1">
+    <row r="54" spans="1:14" ht="13.95" customHeight="1">
       <c r="A54" s="4" t="s">
         <v>434</v>
       </c>
@@ -15255,7 +15349,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="55" spans="1:14" ht="14" customHeight="1">
+    <row r="55" spans="1:14" ht="13.95" customHeight="1">
       <c r="A55" s="4" t="s">
         <v>441</v>
       </c>
@@ -15299,7 +15393,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="56" spans="1:14" ht="14" customHeight="1">
+    <row r="56" spans="1:14" ht="13.95" customHeight="1">
       <c r="A56" s="4" t="s">
         <v>448</v>
       </c>
@@ -15343,7 +15437,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="57" spans="1:14" ht="14" customHeight="1">
+    <row r="57" spans="1:14" ht="13.95" customHeight="1">
       <c r="A57" s="4" t="s">
         <v>455</v>
       </c>
@@ -15385,7 +15479,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="58" spans="1:14" ht="14" customHeight="1">
+    <row r="58" spans="1:14" ht="13.95" customHeight="1">
       <c r="A58" s="4" t="s">
         <v>461</v>
       </c>
@@ -15429,7 +15523,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="59" spans="1:14" ht="14" customHeight="1">
+    <row r="59" spans="1:14" ht="13.95" customHeight="1">
       <c r="A59" s="4" t="s">
         <v>467</v>
       </c>
@@ -15473,7 +15567,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="1:14" ht="14" customHeight="1">
+    <row r="60" spans="1:14" ht="13.95" customHeight="1">
       <c r="A60" s="4" t="s">
         <v>474</v>
       </c>
@@ -15517,7 +15611,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="61" spans="1:14" ht="14" customHeight="1">
+    <row r="61" spans="1:14" ht="13.95" customHeight="1">
       <c r="A61" s="4" t="s">
         <v>482</v>
       </c>
@@ -15561,7 +15655,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="62" spans="1:14" ht="14" customHeight="1">
+    <row r="62" spans="1:14" ht="13.95" customHeight="1">
       <c r="A62" s="4" t="s">
         <v>490</v>
       </c>
@@ -15605,7 +15699,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="63" spans="1:14" ht="14" customHeight="1">
+    <row r="63" spans="1:14" ht="13.95" customHeight="1">
       <c r="A63" s="4" t="s">
         <v>497</v>
       </c>
@@ -15649,7 +15743,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="64" spans="1:14" ht="14" customHeight="1">
+    <row r="64" spans="1:14" ht="13.95" customHeight="1">
       <c r="A64" s="4" t="s">
         <v>504</v>
       </c>
@@ -15693,7 +15787,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="65" spans="1:14" ht="14" customHeight="1">
+    <row r="65" spans="1:14" ht="13.95" customHeight="1">
       <c r="A65" s="4" t="s">
         <v>511</v>
       </c>
@@ -15737,7 +15831,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="66" spans="1:14" ht="14" customHeight="1">
+    <row r="66" spans="1:14" ht="13.95" customHeight="1">
       <c r="A66" s="4" t="s">
         <v>517</v>
       </c>
@@ -15781,7 +15875,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="67" spans="1:14" ht="14" customHeight="1">
+    <row r="67" spans="1:14" ht="13.95" customHeight="1">
       <c r="A67" s="4" t="s">
         <v>525</v>
       </c>
@@ -15825,7 +15919,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="68" spans="1:14" ht="14" customHeight="1">
+    <row r="68" spans="1:14" ht="13.95" customHeight="1">
       <c r="A68" s="4" t="s">
         <v>531</v>
       </c>
@@ -15869,7 +15963,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="69" spans="1:14" ht="14" customHeight="1">
+    <row r="69" spans="1:14" ht="13.95" customHeight="1">
       <c r="A69" s="4" t="s">
         <v>538</v>
       </c>
@@ -15913,7 +16007,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="70" spans="1:14" ht="14" customHeight="1">
+    <row r="70" spans="1:14" ht="13.95" customHeight="1">
       <c r="A70" s="4" t="s">
         <v>545</v>
       </c>
@@ -15957,7 +16051,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="71" spans="1:14" ht="14" customHeight="1">
+    <row r="71" spans="1:14" ht="13.95" customHeight="1">
       <c r="A71" s="4" t="s">
         <v>552</v>
       </c>
@@ -16001,7 +16095,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="72" spans="1:14" ht="14" customHeight="1">
+    <row r="72" spans="1:14" ht="13.95" customHeight="1">
       <c r="A72" s="4" t="s">
         <v>560</v>
       </c>
@@ -16045,7 +16139,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="73" spans="1:14" ht="14" customHeight="1">
+    <row r="73" spans="1:14" ht="13.95" customHeight="1">
       <c r="A73" s="4" t="s">
         <v>567</v>
       </c>
@@ -16089,7 +16183,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="74" spans="1:14" ht="14" customHeight="1">
+    <row r="74" spans="1:14" ht="13.95" customHeight="1">
       <c r="A74" s="4" t="s">
         <v>574</v>
       </c>
@@ -16133,7 +16227,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="75" spans="1:14" ht="14" customHeight="1">
+    <row r="75" spans="1:14" ht="13.95" customHeight="1">
       <c r="A75" s="4" t="s">
         <v>582</v>
       </c>
@@ -16177,7 +16271,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="76" spans="1:14" ht="14" customHeight="1">
+    <row r="76" spans="1:14" ht="13.95" customHeight="1">
       <c r="A76" s="4" t="s">
         <v>589</v>
       </c>
@@ -16221,7 +16315,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="77" spans="1:14" ht="14" customHeight="1">
+    <row r="77" spans="1:14" ht="13.95" customHeight="1">
       <c r="A77" s="4" t="s">
         <v>595</v>
       </c>
@@ -16265,7 +16359,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="78" spans="1:14" ht="14" customHeight="1">
+    <row r="78" spans="1:14" ht="13.95" customHeight="1">
       <c r="A78" s="4" t="s">
         <v>602</v>
       </c>
@@ -16309,7 +16403,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="79" spans="1:14" ht="14" customHeight="1">
+    <row r="79" spans="1:14" ht="13.95" customHeight="1">
       <c r="A79" s="4" t="s">
         <v>608</v>
       </c>
@@ -16353,7 +16447,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="80" spans="1:14" ht="14" customHeight="1">
+    <row r="80" spans="1:14" ht="13.95" customHeight="1">
       <c r="A80" s="4" t="s">
         <v>615</v>
       </c>
@@ -16397,7 +16491,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="81" spans="1:14" ht="14" customHeight="1">
+    <row r="81" spans="1:14" ht="13.95" customHeight="1">
       <c r="A81" s="4" t="s">
         <v>622</v>
       </c>
@@ -16441,7 +16535,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="82" spans="1:14" ht="14" customHeight="1">
+    <row r="82" spans="1:14" ht="13.95" customHeight="1">
       <c r="A82" s="4" t="s">
         <v>628</v>
       </c>
@@ -16485,7 +16579,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="83" spans="1:14" ht="14" customHeight="1">
+    <row r="83" spans="1:14" ht="13.95" customHeight="1">
       <c r="A83" s="4" t="s">
         <v>635</v>
       </c>
@@ -16529,7 +16623,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="84" spans="1:14" ht="14" customHeight="1">
+    <row r="84" spans="1:14" ht="13.95" customHeight="1">
       <c r="A84" s="4" t="s">
         <v>642</v>
       </c>
@@ -16573,7 +16667,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="85" spans="1:14" ht="14" customHeight="1">
+    <row r="85" spans="1:14" ht="13.95" customHeight="1">
       <c r="A85" s="4" t="s">
         <v>643</v>
       </c>
@@ -16617,7 +16711,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="86" spans="1:14" ht="14" customHeight="1">
+    <row r="86" spans="1:14" ht="13.95" customHeight="1">
       <c r="A86" s="4" t="s">
         <v>650</v>
       </c>
@@ -16661,7 +16755,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="87" spans="1:14" ht="14" customHeight="1">
+    <row r="87" spans="1:14" ht="13.95" customHeight="1">
       <c r="A87" s="4" t="s">
         <v>656</v>
       </c>
@@ -16705,7 +16799,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="88" spans="1:14" ht="14" customHeight="1">
+    <row r="88" spans="1:14" ht="13.95" customHeight="1">
       <c r="A88" s="4" t="s">
         <v>663</v>
       </c>
@@ -16749,7 +16843,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="89" spans="1:14" ht="14" customHeight="1">
+    <row r="89" spans="1:14" ht="13.95" customHeight="1">
       <c r="A89" s="4" t="s">
         <v>670</v>
       </c>
@@ -16793,7 +16887,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="90" spans="1:14" ht="14" customHeight="1">
+    <row r="90" spans="1:14" ht="13.95" customHeight="1">
       <c r="A90" s="4" t="s">
         <v>677</v>
       </c>
@@ -16837,7 +16931,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="91" spans="1:14" ht="14" customHeight="1">
+    <row r="91" spans="1:14" ht="13.95" customHeight="1">
       <c r="A91" s="4" t="s">
         <v>684</v>
       </c>
@@ -16881,7 +16975,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="92" spans="1:14" ht="14" customHeight="1">
+    <row r="92" spans="1:14" ht="13.95" customHeight="1">
       <c r="A92" s="4" t="s">
         <v>691</v>
       </c>
@@ -18680,7 +18774,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{652841DA-3619-42EE-A536-61B58BE1B457}">
   <dimension ref="A1:N9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
@@ -19092,9 +19186,9 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FE2008B-4BF4-4C9A-883A-FEE5873AEAF4}">
   <dimension ref="A1:N14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="16" customHeight="1">
+    <row r="1" spans="1:14" ht="16.05" customHeight="1">
       <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
@@ -19138,7 +19232,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="16" customHeight="1">
+    <row r="2" spans="1:14" ht="16.05" customHeight="1">
       <c r="A2" s="7" t="s">
         <v>1911</v>
       </c>
@@ -19182,7 +19276,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="16" customHeight="1">
+    <row r="3" spans="1:14" ht="16.05" customHeight="1">
       <c r="A3" s="7" t="s">
         <v>1920</v>
       </c>
@@ -19226,7 +19320,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="16" customHeight="1">
+    <row r="4" spans="1:14" ht="16.05" customHeight="1">
       <c r="A4" s="7" t="s">
         <v>1928</v>
       </c>
@@ -19270,7 +19364,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="16" customHeight="1">
+    <row r="5" spans="1:14" ht="16.05" customHeight="1">
       <c r="A5" s="7" t="s">
         <v>1936</v>
       </c>
@@ -19314,7 +19408,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="16" customHeight="1">
+    <row r="6" spans="1:14" ht="16.05" customHeight="1">
       <c r="A6" s="7" t="s">
         <v>1944</v>
       </c>
@@ -19358,7 +19452,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="16" customHeight="1">
+    <row r="7" spans="1:14" ht="16.05" customHeight="1">
       <c r="A7" s="7" t="s">
         <v>1952</v>
       </c>
@@ -19402,7 +19496,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="16" customHeight="1">
+    <row r="8" spans="1:14" ht="16.05" customHeight="1">
       <c r="A8" s="7" t="s">
         <v>1961</v>
       </c>
@@ -19446,7 +19540,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="16" customHeight="1">
+    <row r="9" spans="1:14" ht="16.05" customHeight="1">
       <c r="A9" s="7" t="s">
         <v>1969</v>
       </c>
@@ -19490,7 +19584,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="16" customHeight="1">
+    <row r="10" spans="1:14" ht="16.05" customHeight="1">
       <c r="A10" s="16" t="s">
         <v>1977</v>
       </c>
@@ -19534,7 +19628,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="16" customHeight="1">
+    <row r="11" spans="1:14" ht="16.05" customHeight="1">
       <c r="A11" s="16" t="s">
         <v>1986</v>
       </c>
@@ -19578,7 +19672,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="16" customHeight="1">
+    <row r="12" spans="1:14" ht="16.05" customHeight="1">
       <c r="A12" s="16" t="s">
         <v>1995</v>
       </c>
@@ -19735,9 +19829,9 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79E65951-BFD2-4888-A0A6-19D5130CB4A6}">
   <dimension ref="A1:N24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="41.1796875" customWidth="1"/>
+    <col min="2" max="2" width="41.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -20806,9 +20900,9 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89BFA1EF-29B2-41E4-A9D1-F8E90A663FA1}">
   <dimension ref="A1:N24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="14.5" customHeight="1">
+    <row r="1" spans="1:14" ht="14.55" customHeight="1">
       <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
@@ -21160,7 +21254,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="14.5" customHeight="1">
+    <row r="9" spans="1:14" ht="14.55" customHeight="1">
       <c r="A9" s="7" t="s">
         <v>2827</v>
       </c>
@@ -21891,7 +21985,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ED8913B-580D-466F-B6D1-947424810FAF}">
   <dimension ref="A1:N3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
@@ -22040,10 +22134,10 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B6F0D32-9CE2-4DF7-927E-42E7BA331F12}">
   <dimension ref="A1:O32"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="13" max="13" width="13.36328125" customWidth="1"/>
-    <col min="14" max="14" width="16.1796875" customWidth="1"/>
+    <col min="13" max="13" width="13.33203125" customWidth="1"/>
+    <col min="14" max="14" width="16.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
@@ -23512,8 +23606,11 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA7E41C9-E62B-4149-A5B5-E7986E8877E6}">
-  <dimension ref="A1:N3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <dimension ref="A1:N4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="5" max="5" width="11.88671875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
@@ -23644,6 +23741,50 @@
         <v>3939</v>
       </c>
       <c r="N3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>4090</v>
+      </c>
+      <c r="B4" s="42" t="s">
+        <v>4091</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
+        <v>4092</v>
+      </c>
+      <c r="E4" s="44" t="s">
+        <v>4114</v>
+      </c>
+      <c r="F4" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G4" s="43" t="s">
+        <v>4093</v>
+      </c>
+      <c r="H4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" t="s">
+        <v>4094</v>
+      </c>
+      <c r="J4" t="s">
+        <v>4095</v>
+      </c>
+      <c r="K4" s="37" t="s">
+        <v>3647</v>
+      </c>
+      <c r="L4" t="s">
+        <v>3648</v>
+      </c>
+      <c r="M4" t="s">
+        <v>4092</v>
+      </c>
+      <c r="N4" t="s">
         <v>25</v>
       </c>
     </row>
@@ -23655,13 +23796,14 @@
     <hyperlink ref="J3" r:id="rId3" xr:uid="{6CF2E8FA-2871-441E-B367-030778224566}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FAFF3B6-AF11-4BFB-8078-829FF6F2F366}">
   <dimension ref="A1:N3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="32" t="s">
@@ -23810,7 +23952,7 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E5535EA-E186-4751-BC7F-9B3A0221302E}">
   <dimension ref="A1:N3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="32" t="s">
@@ -23959,17 +24101,17 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C98E1A12-072F-4773-8CB5-47FFE077E85B}">
   <dimension ref="A1:N9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="43.7265625" customWidth="1"/>
-    <col min="5" max="5" width="16.1796875" customWidth="1"/>
-    <col min="6" max="6" width="17.81640625" customWidth="1"/>
-    <col min="7" max="7" width="16.7265625" customWidth="1"/>
-    <col min="9" max="9" width="24.7265625" customWidth="1"/>
-    <col min="10" max="10" width="23.6328125" customWidth="1"/>
-    <col min="12" max="12" width="32.453125" customWidth="1"/>
-    <col min="13" max="13" width="14.90625" customWidth="1"/>
-    <col min="14" max="14" width="21.81640625" customWidth="1"/>
+    <col min="2" max="2" width="43.77734375" customWidth="1"/>
+    <col min="5" max="5" width="16.21875" customWidth="1"/>
+    <col min="6" max="6" width="17.77734375" customWidth="1"/>
+    <col min="7" max="7" width="16.77734375" customWidth="1"/>
+    <col min="9" max="9" width="24.77734375" customWidth="1"/>
+    <col min="10" max="10" width="23.6640625" customWidth="1"/>
+    <col min="12" max="12" width="32.44140625" customWidth="1"/>
+    <col min="13" max="13" width="14.88671875" customWidth="1"/>
+    <col min="14" max="14" width="21.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -24390,7 +24532,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFB39079-151D-4B88-9E1F-4966291E2A6B}">
   <dimension ref="A1:N3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
@@ -24497,7 +24639,7 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{316C64E0-14FB-467C-956A-E132FAFB0232}">
   <dimension ref="A1:N1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
@@ -24551,7 +24693,7 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{201D74E2-3547-4E9B-8216-09A22645AC2A}">
   <dimension ref="A1:N2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="32" t="s">
@@ -24653,7 +24795,7 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59BC8B2E-A067-463D-937A-30E88D8BECD0}">
   <dimension ref="A1:N4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
@@ -24848,7 +24990,7 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4185B0A-D162-4EBC-935B-7159E365DD54}">
   <dimension ref="A1:N3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
@@ -24997,9 +25139,9 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4BBBCF5-BAC9-459C-ABE9-2526B85FD81E}">
   <dimension ref="A1:N10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="4" max="4" width="17.54296875" customWidth="1"/>
+    <col min="4" max="4" width="17.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -25465,7 +25607,7 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac